--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -59574,6 +59574,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2575">
+      <c r="A2575" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2575" t="n">
+        <v>183822</v>
+      </c>
+      <c r="C2575" t="n">
+        <v>4.8899998664856</v>
+      </c>
+      <c r="D2575" t="n">
+        <v>4.80600023269653</v>
+      </c>
+      <c r="E2575" t="n">
+        <v>4.88000011444092</v>
+      </c>
+      <c r="F2575" t="n">
+        <v>4.81799983978271</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -59597,6 +59597,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2576">
+      <c r="A2576" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2576" t="n">
+        <v>292915</v>
+      </c>
+      <c r="C2576" t="n">
+        <v>4.84999990463257</v>
+      </c>
+      <c r="D2576" t="n">
+        <v>4.77400016784668</v>
+      </c>
+      <c r="E2576" t="n">
+        <v>4.79199981689453</v>
+      </c>
+      <c r="F2576" t="n">
+        <v>4.82800006866455</v>
+      </c>
+      <c r="G2576" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -59620,6 +59620,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>204908</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>4.8899998664856</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>4.81199979782104</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>4.82800006866455</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>4.85799980163574</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -59643,6 +59643,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2578">
+      <c r="A2578" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2578" t="n">
+        <v>241712</v>
+      </c>
+      <c r="C2578" t="n">
+        <v>4.94199991226196</v>
+      </c>
+      <c r="D2578" t="n">
+        <v>4.85599994659424</v>
+      </c>
+      <c r="E2578" t="n">
+        <v>4.88600015640259</v>
+      </c>
+      <c r="F2578" t="n">
+        <v>4.94000005722046</v>
+      </c>
+      <c r="G2578" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -59484,22 +59484,22 @@
     </row>
     <row r="2571">
       <c r="A2571" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2571" t="n">
-        <v>219982</v>
+        <v>174387</v>
       </c>
       <c r="C2571" t="n">
-        <v>5.05000019073486</v>
+        <v>5.06500005722046</v>
       </c>
       <c r="D2571" t="n">
-        <v>4.96600008010864</v>
+        <v>4.98600006103516</v>
       </c>
       <c r="E2571" t="n">
-        <v>5.02500009536743</v>
+        <v>4.98600006103516</v>
       </c>
       <c r="F2571" t="n">
-        <v>4.9980001449585</v>
+        <v>5.00500011444092</v>
       </c>
       <c r="G2571" t="s">
         <v>7</v>
@@ -59507,22 +59507,22 @@
     </row>
     <row r="2572">
       <c r="A2572" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2572" t="n">
-        <v>751498</v>
+        <v>219982</v>
       </c>
       <c r="C2572" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="D2572" t="n">
+        <v>4.96600008010864</v>
+      </c>
+      <c r="E2572" t="n">
+        <v>5.02500009536743</v>
+      </c>
+      <c r="F2572" t="n">
         <v>4.9980001449585</v>
-      </c>
-      <c r="D2572" t="n">
-        <v>4.92399978637695</v>
-      </c>
-      <c r="E2572" t="n">
-        <v>4.96400022506714</v>
-      </c>
-      <c r="F2572" t="n">
-        <v>4.93400001525879</v>
       </c>
       <c r="G2572" t="s">
         <v>7</v>
@@ -59530,22 +59530,22 @@
     </row>
     <row r="2573">
       <c r="A2573" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2573" t="n">
-        <v>249366</v>
+        <v>751498</v>
       </c>
       <c r="C2573" t="n">
-        <v>4.9520001411438</v>
+        <v>4.9980001449585</v>
       </c>
       <c r="D2573" t="n">
-        <v>4.86999988555908</v>
+        <v>4.92399978637695</v>
       </c>
       <c r="E2573" t="n">
+        <v>4.96400022506714</v>
+      </c>
+      <c r="F2573" t="n">
         <v>4.93400001525879</v>
-      </c>
-      <c r="F2573" t="n">
-        <v>4.88600015640259</v>
       </c>
       <c r="G2573" t="s">
         <v>7</v>
@@ -59553,22 +59553,22 @@
     </row>
     <row r="2574">
       <c r="A2574" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2574" t="n">
-        <v>229813</v>
+        <v>249366</v>
       </c>
       <c r="C2574" t="n">
-        <v>4.94799995422363</v>
+        <v>4.9520001411438</v>
       </c>
       <c r="D2574" t="n">
-        <v>4.86600017547607</v>
+        <v>4.86999988555908</v>
       </c>
       <c r="E2574" t="n">
-        <v>4.90399980545044</v>
+        <v>4.93400001525879</v>
       </c>
       <c r="F2574" t="n">
-        <v>4.88000011444092</v>
+        <v>4.88600015640259</v>
       </c>
       <c r="G2574" t="s">
         <v>7</v>
@@ -59576,22 +59576,22 @@
     </row>
     <row r="2575">
       <c r="A2575" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2575" t="n">
-        <v>183822</v>
+        <v>229813</v>
       </c>
       <c r="C2575" t="n">
-        <v>4.8899998664856</v>
+        <v>4.94799995422363</v>
       </c>
       <c r="D2575" t="n">
-        <v>4.80600023269653</v>
+        <v>4.86600017547607</v>
       </c>
       <c r="E2575" t="n">
+        <v>4.90399980545044</v>
+      </c>
+      <c r="F2575" t="n">
         <v>4.88000011444092</v>
-      </c>
-      <c r="F2575" t="n">
-        <v>4.81799983978271</v>
       </c>
       <c r="G2575" t="s">
         <v>7</v>
@@ -59599,22 +59599,22 @@
     </row>
     <row r="2576">
       <c r="A2576" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2576" t="n">
-        <v>292915</v>
+        <v>183822</v>
       </c>
       <c r="C2576" t="n">
-        <v>4.84999990463257</v>
+        <v>4.8899998664856</v>
       </c>
       <c r="D2576" t="n">
-        <v>4.77400016784668</v>
+        <v>4.80600023269653</v>
       </c>
       <c r="E2576" t="n">
-        <v>4.79199981689453</v>
+        <v>4.88000011444092</v>
       </c>
       <c r="F2576" t="n">
-        <v>4.82800006866455</v>
+        <v>4.81799983978271</v>
       </c>
       <c r="G2576" t="s">
         <v>7</v>
@@ -59622,22 +59622,22 @@
     </row>
     <row r="2577">
       <c r="A2577" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2577" t="n">
-        <v>204908</v>
+        <v>292915</v>
       </c>
       <c r="C2577" t="n">
-        <v>4.8899998664856</v>
+        <v>4.84999990463257</v>
       </c>
       <c r="D2577" t="n">
-        <v>4.81199979782104</v>
+        <v>4.77400016784668</v>
       </c>
       <c r="E2577" t="n">
+        <v>4.79199981689453</v>
+      </c>
+      <c r="F2577" t="n">
         <v>4.82800006866455</v>
-      </c>
-      <c r="F2577" t="n">
-        <v>4.85799980163574</v>
       </c>
       <c r="G2577" t="s">
         <v>7</v>
@@ -59645,24 +59645,47 @@
     </row>
     <row r="2578">
       <c r="A2578" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2578" t="n">
-        <v>241712</v>
+        <v>204908</v>
       </c>
       <c r="C2578" t="n">
-        <v>4.94199991226196</v>
+        <v>4.8899998664856</v>
       </c>
       <c r="D2578" t="n">
-        <v>4.85599994659424</v>
+        <v>4.81199979782104</v>
       </c>
       <c r="E2578" t="n">
-        <v>4.88600015640259</v>
+        <v>4.82800006866455</v>
       </c>
       <c r="F2578" t="n">
-        <v>4.94000005722046</v>
+        <v>4.85799980163574</v>
       </c>
       <c r="G2578" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2579" t="n">
+        <v>356834</v>
+      </c>
+      <c r="C2579" t="n">
+        <v>4.95599985122681</v>
+      </c>
+      <c r="D2579" t="n">
+        <v>4.88800001144409</v>
+      </c>
+      <c r="E2579" t="n">
+        <v>4.94999980926514</v>
+      </c>
+      <c r="F2579" t="n">
+        <v>4.92399978637695</v>
+      </c>
+      <c r="G2579" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103874206543</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103874206543</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26321363449097</v>
+        <v>2.26321339607239</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24303984642029</v>
+        <v>2.24304008483887</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G6" t="n">
-        <v>2.30482149124146</v>
+        <v>2.30482125282288</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>2.33256006240845</v>
+        <v>2.33255982398987</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33256006240845</v>
+        <v>2.33255982398987</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34895086288452</v>
+        <v>2.3489511013031</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26951742172241</v>
+        <v>2.26951766014099</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29599547386169</v>
+        <v>2.29599571228027</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3111252784729</v>
+        <v>2.31112551689148</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28590893745422</v>
+        <v>2.28590869903564</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29725623130798</v>
+        <v>2.29725646972656</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103874206543</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3350818157196</v>
+        <v>2.33508157730103</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32877731323242</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.75</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G27" t="n">
-        <v>2.34516835212708</v>
+        <v>2.34516859054565</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G29" t="n">
-        <v>2.38299345970154</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G31" t="n">
-        <v>2.38299345970154</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32877731323242</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G34" t="n">
-        <v>2.2884304523468</v>
+        <v>2.28843069076538</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25060510635376</v>
+        <v>2.25060486793518</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G39" t="n">
-        <v>2.20521473884583</v>
+        <v>2.2052149772644</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G41" t="n">
-        <v>2.22664880752563</v>
+        <v>2.22664904594421</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>2.21908402442932</v>
+        <v>2.21908378601074</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G44" t="n">
-        <v>2.19638848304749</v>
+        <v>2.19638895988464</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G45" t="n">
-        <v>2.22034525871277</v>
+        <v>2.22034478187561</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22538805007935</v>
+        <v>2.22538828849792</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G48" t="n">
-        <v>2.23925757408142</v>
+        <v>2.2392578125</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.26951742172241</v>
+        <v>2.26951766014099</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.23169255256653</v>
+        <v>2.23169231414795</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G54" t="n">
-        <v>2.18378067016602</v>
+        <v>2.18378043174744</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G57" t="n">
-        <v>2.17369341850281</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.20773649215698</v>
+        <v>2.2077362537384</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>2.16865062713623</v>
+        <v>2.16865038871765</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.149738073349</v>
+        <v>2.14973783493042</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G69" t="n">
-        <v>2.149738073349</v>
+        <v>2.14973783493042</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G70" t="n">
-        <v>2.13965082168579</v>
+        <v>2.13965106010437</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G71" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.99465394020081</v>
+        <v>1.9946540594101</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195863723755</v>
+        <v>1.97195875644684</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93161189556122</v>
+        <v>1.93161153793335</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>1.92909014225006</v>
+        <v>1.92909038066864</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>1.92278587818146</v>
+        <v>1.92278575897217</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>1.90387308597565</v>
+        <v>1.90387332439423</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.90387308597565</v>
+        <v>1.90387332439423</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>1.92782926559448</v>
+        <v>1.92782938480377</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G88" t="n">
-        <v>1.97574162483215</v>
+        <v>1.97574138641357</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G90" t="n">
-        <v>1.99339306354523</v>
+        <v>1.99339330196381</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G91" t="n">
-        <v>2.01356673240662</v>
+        <v>2.01356649398804</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G92" t="n">
-        <v>2.01104521751404</v>
+        <v>2.01104497909546</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G94" t="n">
-        <v>1.974480509758</v>
+        <v>1.97448039054871</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>1.95430672168732</v>
+        <v>1.9543069601059</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G96" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213218688965</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G100" t="n">
-        <v>1.89504730701447</v>
+        <v>1.89504754543304</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G104" t="n">
-        <v>2.08921694755554</v>
+        <v>2.08921718597412</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147885322571</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>2.08669567108154</v>
+        <v>2.08669543266296</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147885322571</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147885322571</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G115" t="n">
-        <v>2.11569499969482</v>
+        <v>2.11569476127625</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G117" t="n">
-        <v>2.14469432830811</v>
+        <v>2.14469456672668</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G118" t="n">
-        <v>2.14091181755066</v>
+        <v>2.14091157913208</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>2.19008445739746</v>
+        <v>2.19008469581604</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G126" t="n">
-        <v>2.14847683906555</v>
+        <v>2.14847660064697</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G128" t="n">
-        <v>2.17369341850281</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>2.13460731506348</v>
+        <v>2.13460755348206</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G131" t="n">
-        <v>2.11191201210022</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>2.11191201210022</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G134" t="n">
-        <v>2.04256558418274</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G135" t="n">
-        <v>2.04256558418274</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G136" t="n">
-        <v>2.02617502212524</v>
+        <v>2.02617526054382</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.04256558418274</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213218688965</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G140" t="n">
-        <v>1.97069764137268</v>
+        <v>1.97069776058197</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.02365326881409</v>
+        <v>2.02365303039551</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>2.01734948158264</v>
+        <v>2.01734924316406</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G144" t="n">
-        <v>2.07282590866089</v>
+        <v>2.07282662391663</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G145" t="n">
-        <v>2.06400036811829</v>
+        <v>2.06400012969971</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11191201210022</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G148" t="n">
-        <v>2.149738073349</v>
+        <v>2.14973783493042</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G153" t="n">
-        <v>2.09552121162415</v>
+        <v>2.0955216884613</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>2.08669567108154</v>
+        <v>2.08669543266296</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G161" t="n">
-        <v>2.14469432830811</v>
+        <v>2.14469456672668</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G164" t="n">
-        <v>2.14595532417297</v>
+        <v>2.14595484733582</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G166" t="n">
-        <v>2.17243313789368</v>
+        <v>2.1724328994751</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>2.21277952194214</v>
+        <v>2.2127799987793</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.2884304523468</v>
+        <v>2.28843069076538</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>2.27582168579102</v>
+        <v>2.27582192420959</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35147261619568</v>
+        <v>2.35147285461426</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G173" t="n">
-        <v>2.37290692329407</v>
+        <v>2.37290668487549</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40190625190735</v>
+        <v>2.40190601348877</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G175" t="n">
-        <v>2.35399436950684</v>
+        <v>2.35399413108826</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.32877731323242</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G177" t="n">
-        <v>2.34012484550476</v>
+        <v>2.34012532234192</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G178" t="n">
-        <v>2.4031674861908</v>
+        <v>2.40316724777222</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G179" t="n">
-        <v>2.38299345970154</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G186" t="n">
-        <v>2.41703677177429</v>
+        <v>2.41703653335571</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38299345970154</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.75</v>
       </c>
       <c r="G188" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G189" t="n">
-        <v>2.36534190177917</v>
+        <v>2.36534214019775</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.75</v>
       </c>
       <c r="G192" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G193" t="n">
-        <v>2.3552553653717</v>
+        <v>2.35525488853455</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G194" t="n">
-        <v>2.38047218322754</v>
+        <v>2.38047194480896</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.75</v>
       </c>
       <c r="G195" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.75</v>
       </c>
       <c r="G198" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G203" t="n">
-        <v>2.43847107887268</v>
+        <v>2.43847060203552</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G204" t="n">
-        <v>2.43090558052063</v>
+        <v>2.43090581893921</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.45864462852478</v>
+        <v>2.45864415168762</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G211" t="n">
-        <v>2.41535925865173</v>
+        <v>2.41535878181458</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G212" t="n">
-        <v>2.39816308021545</v>
+        <v>2.39816284179688</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G213" t="n">
-        <v>2.46826958656311</v>
+        <v>2.46826934814453</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G214" t="n">
-        <v>2.5119206905365</v>
+        <v>2.51192045211792</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G215" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721119880676</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>2.50001573562622</v>
+        <v>2.50001549720764</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694684028625</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G218" t="n">
-        <v>2.48149681091309</v>
+        <v>2.48149704933167</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.75</v>
       </c>
       <c r="G219" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.50001573562622</v>
+        <v>2.50001549720764</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.75</v>
       </c>
       <c r="G221" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.75</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G226" t="n">
-        <v>2.48546504974365</v>
+        <v>2.48546528816223</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G227" t="n">
-        <v>2.50530648231506</v>
+        <v>2.50530695915222</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G228" t="n">
-        <v>2.51324319839478</v>
+        <v>2.51324343681335</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>2.49340224266052</v>
+        <v>2.49340200424194</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694684028625</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.75</v>
       </c>
       <c r="G231" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.75</v>
       </c>
       <c r="G232" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.75</v>
       </c>
       <c r="G235" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.75</v>
       </c>
       <c r="G236" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G238" t="n">
-        <v>2.45239639282227</v>
+        <v>2.45239615440369</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G240" t="n">
-        <v>2.49207878112793</v>
+        <v>2.49207901954651</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46033334732056</v>
+        <v>2.46033263206482</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694684028625</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694684028625</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>2.49340224266052</v>
+        <v>2.49340200424194</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>2.44578242301941</v>
+        <v>2.44578218460083</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>2.44975090026855</v>
+        <v>2.44975066184998</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.46033334732056</v>
+        <v>2.46033263206482</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G263" t="n">
-        <v>2.57144474983215</v>
+        <v>2.57144451141357</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G270" t="n">
-        <v>2.52382516860962</v>
+        <v>2.52382564544678</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>2.53308439254761</v>
+        <v>2.53308463096619</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G272" t="n">
-        <v>2.51324319839478</v>
+        <v>2.51324343681335</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G273" t="n">
-        <v>2.50001573562622</v>
+        <v>2.50001549720764</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.49340224266052</v>
+        <v>2.49340200424194</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G280" t="n">
-        <v>2.44842791557312</v>
+        <v>2.4484281539917</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G281" t="n">
-        <v>2.42858648300171</v>
+        <v>2.42858624458313</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G283" t="n">
-        <v>2.45901012420654</v>
+        <v>2.45900988578796</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G286" t="n">
-        <v>2.46430110931396</v>
+        <v>2.46430134773254</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G288" t="n">
-        <v>2.49869322776794</v>
+        <v>2.49869275093079</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54366636276245</v>
+        <v>2.54366660118103</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G291" t="n">
-        <v>2.53837561607361</v>
+        <v>2.53837585449219</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G292" t="n">
-        <v>2.53573036193848</v>
+        <v>2.5357301235199</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G294" t="n">
-        <v>2.5304388999939</v>
+        <v>2.53043913841248</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G299" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721119880676</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53308439254761</v>
+        <v>2.53308463096619</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G301" t="n">
-        <v>2.53573036193848</v>
+        <v>2.5357301235199</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G304" t="n">
-        <v>2.56350779533386</v>
+        <v>2.56350803375244</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G306" t="n">
-        <v>2.59922242164612</v>
+        <v>2.5992226600647</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G307" t="n">
-        <v>2.60583639144897</v>
+        <v>2.60583662986755</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60583639144897</v>
+        <v>2.60583662986755</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.57276749610901</v>
+        <v>2.57276773452759</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G311" t="n">
-        <v>2.59128594398499</v>
+        <v>2.59128618240356</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G312" t="n">
-        <v>2.58864092826843</v>
+        <v>2.58864068984985</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G313" t="n">
-        <v>2.62700057029724</v>
+        <v>2.62700033187866</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G318" t="n">
-        <v>2.68917012214661</v>
+        <v>2.68917036056519</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G319" t="n">
-        <v>2.67594265937805</v>
+        <v>2.67594242095947</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>2.67858815193176</v>
+        <v>2.67858839035034</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G322" t="n">
-        <v>2.64816498756409</v>
+        <v>2.64816474914551</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>2.69842934608459</v>
+        <v>2.69842982292175</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G327" t="n">
-        <v>2.68784761428833</v>
+        <v>2.68784737586975</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G328" t="n">
-        <v>2.68784761428833</v>
+        <v>2.68784737586975</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>2.65874648094177</v>
+        <v>2.65874671936035</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G337" t="n">
-        <v>2.78837704658508</v>
+        <v>2.78837728500366</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.85054659843445</v>
+        <v>2.85054683685303</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G339" t="n">
-        <v>2.84790110588074</v>
+        <v>2.8479015827179</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G340" t="n">
-        <v>2.88758444786072</v>
+        <v>2.88758420944214</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G347" t="n">
-        <v>2.96430420875549</v>
+        <v>2.96430444717407</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G348" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>2.99340534210205</v>
+        <v>2.99340486526489</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G351" t="n">
-        <v>3.01456904411316</v>
+        <v>3.01456880569458</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03837847709656</v>
+        <v>3.03837871551514</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G354" t="n">
-        <v>3.10583972930908</v>
+        <v>3.10583925247192</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G355" t="n">
-        <v>3.03441047668457</v>
+        <v>3.03441071510315</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.0092785358429</v>
+        <v>3.00927829742432</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G357" t="n">
-        <v>2.99605059623718</v>
+        <v>2.9960503578186</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>3.01456904411316</v>
+        <v>3.01456880569458</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>3.0423469543457</v>
+        <v>3.04234671592712</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05557465553284</v>
+        <v>3.05557489395142</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G364" t="n">
-        <v>3.02515125274658</v>
+        <v>3.02515149116516</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G367" t="n">
-        <v>2.98282313346863</v>
+        <v>2.98282289505005</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G368" t="n">
-        <v>2.97091841697693</v>
+        <v>2.97091817855835</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G371" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G372" t="n">
-        <v>3.04896116256714</v>
+        <v>3.04896092414856</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G373" t="n">
-        <v>3.02250552177429</v>
+        <v>3.02250576019287</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G375" t="n">
-        <v>2.85054659843445</v>
+        <v>2.85054683685303</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.87700223922729</v>
+        <v>2.87700200080872</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G377" t="n">
-        <v>2.84922432899475</v>
+        <v>2.84922409057617</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G379" t="n">
-        <v>2.86509704589844</v>
+        <v>2.86509680747986</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>2.84393310546875</v>
+        <v>2.84393286705017</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85980629920959</v>
+        <v>2.85980606079102</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G382" t="n">
-        <v>2.85451507568359</v>
+        <v>2.85451531410217</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G383" t="n">
-        <v>2.8307056427002</v>
+        <v>2.83070540428162</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G385" t="n">
-        <v>2.84922432899475</v>
+        <v>2.84922409057617</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.87700223922729</v>
+        <v>2.87700200080872</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.84525585174561</v>
+        <v>2.84525561332703</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705453872681</v>
+        <v>2.78705501556396</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80689573287964</v>
+        <v>2.8068962097168</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G391" t="n">
-        <v>2.76589035987854</v>
+        <v>2.76589059829712</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>2.80689573287964</v>
+        <v>2.8068962097168</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>2.71165704727173</v>
+        <v>2.71165728569031</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>2.75398564338684</v>
+        <v>2.75398540496826</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G395" t="n">
-        <v>2.66800618171692</v>
+        <v>2.66800594329834</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69446086883545</v>
+        <v>2.69446110725403</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G398" t="n">
-        <v>2.68652439117432</v>
+        <v>2.6865246295929</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G399" t="n">
-        <v>2.75266289710999</v>
+        <v>2.75266313552856</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.75927662849426</v>
+        <v>2.75927639007568</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G402" t="n">
-        <v>2.75663137435913</v>
+        <v>2.75663113594055</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>2.79102277755737</v>
+        <v>2.79102253913879</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73943543434143</v>
+        <v>2.73943519592285</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G409" t="n">
-        <v>2.76589035987854</v>
+        <v>2.76589059829712</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G410" t="n">
-        <v>2.72620797157288</v>
+        <v>2.72620749473572</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>2.67991065979004</v>
+        <v>2.67991089820862</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G413" t="n">
-        <v>2.76324486732483</v>
+        <v>2.76324462890625</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>2.75927662849426</v>
+        <v>2.75927639007568</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G415" t="n">
-        <v>2.78044080734253</v>
+        <v>2.78044104576111</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G416" t="n">
-        <v>2.79102277755737</v>
+        <v>2.79102253913879</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G418" t="n">
-        <v>2.86906552314758</v>
+        <v>2.869065284729</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G419" t="n">
-        <v>2.87303400039673</v>
+        <v>2.87303352355957</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G421" t="n">
-        <v>2.88890695571899</v>
+        <v>2.88890719413757</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G422" t="n">
-        <v>2.86377453804016</v>
+        <v>2.86377429962158</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G424" t="n">
-        <v>2.84790110588074</v>
+        <v>2.8479015827179</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G426" t="n">
-        <v>2.81483221054077</v>
+        <v>2.81483244895935</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G429" t="n">
-        <v>2.84790110588074</v>
+        <v>2.8479015827179</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.85054659843445</v>
+        <v>2.85054683685303</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G434" t="n">
-        <v>2.894198179245</v>
+        <v>2.89419770240784</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94181776046753</v>
+        <v>2.94181752204895</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G440" t="n">
-        <v>3.00795555114746</v>
+        <v>3.00795483589172</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G441" t="n">
-        <v>2.98282313346863</v>
+        <v>2.98282289505005</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.93652653694153</v>
+        <v>2.93652629852295</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520355224609</v>
+        <v>2.93520402908325</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G444" t="n">
-        <v>2.94181776046753</v>
+        <v>2.94181752204895</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>2.95636773109436</v>
+        <v>2.95636749267578</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>2.95636773109436</v>
+        <v>2.95636749267578</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G451" t="n">
-        <v>3.01721453666687</v>
+        <v>3.01721429824829</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00398659706116</v>
+        <v>3.00398683547974</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>2.99605059623718</v>
+        <v>2.9960503578186</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92991209030151</v>
+        <v>2.92991232872009</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G458" t="n">
-        <v>2.98282313346863</v>
+        <v>2.98282289505005</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94710874557495</v>
+        <v>2.94710803031921</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G462" t="n">
-        <v>2.89684343338013</v>
+        <v>2.89684367179871</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88361573219299</v>
+        <v>2.88361597061157</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.92672944068909</v>
+        <v>2.92672896385193</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G469" t="n">
-        <v>2.87145590782166</v>
+        <v>2.87145566940308</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G471" t="n">
-        <v>2.80650901794434</v>
+        <v>2.80650925636292</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G473" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G475" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>2.81894564628601</v>
+        <v>2.81894588470459</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G483" t="n">
-        <v>2.93502020835876</v>
+        <v>2.93502044677734</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G485" t="n">
-        <v>2.99858474731445</v>
+        <v>2.99858498573303</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G486" t="n">
-        <v>3.01240301132202</v>
+        <v>3.01240277290344</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.97371101379395</v>
+        <v>2.9737114906311</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G490" t="n">
-        <v>3.02345776557922</v>
+        <v>3.02345752716064</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97785663604736</v>
+        <v>2.97785711288452</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G493" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818399429321</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G494" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818399429321</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G496" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818399429321</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>2.99858474731445</v>
+        <v>2.99858498573303</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G498" t="n">
-        <v>3.03036689758301</v>
+        <v>3.03036713600159</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G499" t="n">
-        <v>2.97509336471558</v>
+        <v>2.97509384155273</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G500" t="n">
-        <v>2.97923874855042</v>
+        <v>2.97923898696899</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G501" t="n">
-        <v>2.9405472278595</v>
+        <v>2.94054746627808</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G502" t="n">
-        <v>2.95851111412048</v>
+        <v>2.95851159095764</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G504" t="n">
-        <v>3.0317485332489</v>
+        <v>3.03174829483032</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>3.10498642921448</v>
+        <v>3.10498571395874</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G507" t="n">
-        <v>3.11051321029663</v>
+        <v>3.11051297187805</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G508" t="n">
-        <v>3.14229559898376</v>
+        <v>3.14229536056519</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G509" t="n">
-        <v>3.08840417861938</v>
+        <v>3.08840346336365</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G510" t="n">
-        <v>3.07182216644287</v>
+        <v>3.07182192802429</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>3.05385804176331</v>
+        <v>3.05385828018188</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G515" t="n">
-        <v>3.04418563842773</v>
+        <v>3.04418516159058</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G516" t="n">
-        <v>3.02760338783264</v>
+        <v>3.02760314941406</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G517" t="n">
-        <v>3.02760338783264</v>
+        <v>3.02760314941406</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G518" t="n">
-        <v>2.99443912506104</v>
+        <v>2.99443936347961</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G519" t="n">
-        <v>3.0096390247345</v>
+        <v>3.00963926315308</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G520" t="n">
-        <v>3.03036689758301</v>
+        <v>3.03036713600159</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G521" t="n">
-        <v>3.02345776557922</v>
+        <v>3.02345752716064</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G524" t="n">
-        <v>2.99305701255798</v>
+        <v>2.9930567741394</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G525" t="n">
-        <v>2.99582123756409</v>
+        <v>2.99582099914551</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G527" t="n">
-        <v>2.91843819618225</v>
+        <v>2.91843795776367</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>2.90185594558716</v>
+        <v>2.90185618400574</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94331121444702</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.25</v>
       </c>
       <c r="G533" t="n">
-        <v>2.93640184402466</v>
+        <v>2.93640208244324</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G534" t="n">
-        <v>2.87283754348755</v>
+        <v>2.87283730506897</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94607496261597</v>
+        <v>2.94607472419739</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G538" t="n">
-        <v>2.94607496261597</v>
+        <v>2.94607472419739</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>2.94331121444702</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.92811059951782</v>
+        <v>2.9281108379364</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.99443912506104</v>
+        <v>2.99443936347961</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97371101379395</v>
+        <v>2.9737114906311</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06491279602051</v>
+        <v>3.06491255760193</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G548" t="n">
-        <v>3.00134825706482</v>
+        <v>3.00134801864624</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G549" t="n">
-        <v>3.01240301132202</v>
+        <v>3.01240277290344</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G551" t="n">
-        <v>2.91291046142578</v>
+        <v>2.91291069984436</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G552" t="n">
-        <v>2.92949271202087</v>
+        <v>2.92949247360229</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>2.95712971687317</v>
+        <v>2.95712947845459</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G555" t="n">
-        <v>2.95298409461975</v>
+        <v>2.95298433303833</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>2.84658265113831</v>
+        <v>2.84658241271973</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G563" t="n">
-        <v>2.76090884208679</v>
+        <v>2.76090908050537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G564" t="n">
-        <v>2.78440022468567</v>
+        <v>2.78439998626709</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75261759757996</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G568" t="n">
-        <v>2.71530818939209</v>
+        <v>2.71530795097351</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G572" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G575" t="n">
-        <v>2.71668982505798</v>
+        <v>2.71669006347656</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>2.7360360622406</v>
+        <v>2.73603582382202</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G577" t="n">
-        <v>2.75261759757996</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G578" t="n">
-        <v>2.78716373443604</v>
+        <v>2.78716349601746</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G580" t="n">
-        <v>2.75123620033264</v>
+        <v>2.75123596191406</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>2.72221732139587</v>
+        <v>2.72221755981445</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G585" t="n">
-        <v>2.75261759757996</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G587" t="n">
-        <v>2.75814485549927</v>
+        <v>2.75814533233643</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G590" t="n">
-        <v>2.83276414871216</v>
+        <v>2.83276391029358</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G591" t="n">
-        <v>2.83967328071594</v>
+        <v>2.8396737575531</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G592" t="n">
-        <v>2.84243702888489</v>
+        <v>2.84243726730347</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G594" t="n">
-        <v>2.87836480140686</v>
+        <v>2.87836503982544</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G595" t="n">
-        <v>2.83552813529968</v>
+        <v>2.8355278968811</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>2.94331121444702</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>2.88527417182922</v>
+        <v>2.88527393341064</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>2.88803744316101</v>
+        <v>2.88803720474243</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G608" t="n">
-        <v>2.8590190410614</v>
+        <v>2.85901927947998</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G609" t="n">
-        <v>2.84520077705383</v>
+        <v>2.84520053863525</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G610" t="n">
-        <v>2.86869215965271</v>
+        <v>2.86869168281555</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>2.87421917915344</v>
+        <v>2.87421941757202</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G614" t="n">
-        <v>2.84520077705383</v>
+        <v>2.84520053863525</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G615" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G621" t="n">
-        <v>2.97509336471558</v>
+        <v>2.97509384155273</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G623" t="n">
-        <v>2.99443912506104</v>
+        <v>2.99443936347961</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G627" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898454666138</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G628" t="n">
-        <v>3.0096390247345</v>
+        <v>3.00963926315308</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G629" t="n">
-        <v>2.99443912506104</v>
+        <v>2.99443936347961</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G630" t="n">
-        <v>3.01240301132202</v>
+        <v>3.01240277290344</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G631" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898454666138</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G632" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898454666138</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G633" t="n">
-        <v>3.03313040733337</v>
+        <v>3.03313016891479</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G634" t="n">
-        <v>3.03036689758301</v>
+        <v>3.03036713600159</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G637" t="n">
-        <v>3.03451251983643</v>
+        <v>3.034512758255</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G638" t="n">
-        <v>3.02483940124512</v>
+        <v>3.02483916282654</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>3.08287692070007</v>
+        <v>3.08287668228149</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G641" t="n">
-        <v>3.08840417861938</v>
+        <v>3.08840346336365</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>3.0814950466156</v>
+        <v>3.08149480819702</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G644" t="n">
-        <v>3.09669494628906</v>
+        <v>3.09669470787048</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G645" t="n">
-        <v>3.13262271881104</v>
+        <v>3.13262248039246</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G646" t="n">
-        <v>3.14229559898376</v>
+        <v>3.14229536056519</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G647" t="n">
-        <v>3.0662944316864</v>
+        <v>3.06629490852356</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G649" t="n">
-        <v>3.09669494628906</v>
+        <v>3.09669470787048</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12294983863831</v>
+        <v>3.12295007705688</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G652" t="n">
-        <v>3.12709546089172</v>
+        <v>3.12709522247314</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G653" t="n">
-        <v>3.13262271881104</v>
+        <v>3.13262248039246</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G654" t="n">
-        <v>3.12294983863831</v>
+        <v>3.12295007705688</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G655" t="n">
-        <v>3.11742281913757</v>
+        <v>3.11742234230042</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G657" t="n">
-        <v>3.08840417861938</v>
+        <v>3.08840346336365</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G658" t="n">
-        <v>3.08840417861938</v>
+        <v>3.08840346336365</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>3.10498642921448</v>
+        <v>3.10498571395874</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>3.12294983863831</v>
+        <v>3.12295007705688</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13814973831177</v>
+        <v>3.13814997673035</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.55399990081787</v>
       </c>
       <c r="G663" t="n">
-        <v>3.14644122123718</v>
+        <v>3.1464409828186</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G664" t="n">
-        <v>3.12018585205078</v>
+        <v>3.12018609046936</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.5</v>
       </c>
       <c r="G665" t="n">
-        <v>3.10913157463074</v>
+        <v>3.10913109779358</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G666" t="n">
-        <v>3.10222268104553</v>
+        <v>3.10222244262695</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.10913157463074</v>
+        <v>3.10913109779358</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G668" t="n">
-        <v>3.10222268104553</v>
+        <v>3.10222244262695</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G669" t="n">
-        <v>3.26251554489136</v>
+        <v>3.26251578330994</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G670" t="n">
-        <v>3.31226134300232</v>
+        <v>3.31226110458374</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>3.34542560577393</v>
+        <v>3.34542536735535</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G673" t="n">
-        <v>3.36062550544739</v>
+        <v>3.36062574386597</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38411617279053</v>
+        <v>3.38411688804626</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G675" t="n">
-        <v>3.35924363136292</v>
+        <v>3.35924386978149</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G676" t="n">
-        <v>3.37997102737427</v>
+        <v>3.37997126579285</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>3.34542560577393</v>
+        <v>3.34542536735535</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>3.30535244941711</v>
+        <v>3.30535197257996</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G679" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G680" t="n">
-        <v>3.33022546768188</v>
+        <v>3.33022570610046</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G683" t="n">
-        <v>3.37858915328979</v>
+        <v>3.37858939170837</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G684" t="n">
-        <v>3.37444353103638</v>
+        <v>3.37444400787354</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G689" t="n">
-        <v>3.28047919273376</v>
+        <v>3.28047895431519</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G690" t="n">
-        <v>3.29015183448792</v>
+        <v>3.29015207290649</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31778883934021</v>
+        <v>3.31778860092163</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G693" t="n">
-        <v>3.35371685028076</v>
+        <v>3.35371661186218</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G694" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957098960876</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G695" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957098960876</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G696" t="n">
-        <v>3.33989810943604</v>
+        <v>3.33989858627319</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G697" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G698" t="n">
-        <v>3.3426616191864</v>
+        <v>3.34266185760498</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.32331585884094</v>
+        <v>3.3233163356781</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G700" t="n">
-        <v>3.31364297866821</v>
+        <v>3.31364321708679</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>3.37168002128601</v>
+        <v>3.37168073654175</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G702" t="n">
-        <v>3.36062550544739</v>
+        <v>3.36062574386597</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.37168002128601</v>
+        <v>3.37168073654175</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G705" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957098960876</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G706" t="n">
-        <v>3.38273477554321</v>
+        <v>3.38273501396179</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G707" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957098960876</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>3.38549900054932</v>
+        <v>3.38549876213074</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G712" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G713" t="n">
-        <v>3.36200737953186</v>
+        <v>3.36200785636902</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G714" t="n">
-        <v>3.37029838562012</v>
+        <v>3.3702986240387</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G715" t="n">
-        <v>3.4421968460083</v>
+        <v>3.44219756126404</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G716" t="n">
-        <v>3.4450786113739</v>
+        <v>3.44507884979248</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G718" t="n">
-        <v>3.46236896514893</v>
+        <v>3.46236944198608</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>3.46957325935364</v>
+        <v>3.4695737361908</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G722" t="n">
-        <v>3.4566056728363</v>
+        <v>3.45660591125488</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G725" t="n">
-        <v>3.55314302444458</v>
+        <v>3.55314326286316</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G727" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G729" t="n">
-        <v>3.67777609825134</v>
+        <v>3.67777681350708</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.125</v>
       </c>
       <c r="G730" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218564033508</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65976548194885</v>
+        <v>3.65976572036743</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>3.63455080986023</v>
+        <v>3.63455104827881</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>3.70659375190735</v>
+        <v>3.70659399032593</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G735" t="n">
-        <v>3.61293792724609</v>
+        <v>3.61293840408325</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>3.63094878196716</v>
+        <v>3.63094902038574</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>3.66336798667908</v>
+        <v>3.66336846351624</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G739" t="n">
-        <v>3.68498063087463</v>
+        <v>3.68498086929321</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>3.68858289718628</v>
+        <v>3.68858313560486</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G742" t="n">
-        <v>3.58484220504761</v>
+        <v>3.58484148979187</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.54449772834778</v>
+        <v>3.5444974899292</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>3.54449772834778</v>
+        <v>3.5444974899292</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G748" t="n">
-        <v>3.59924960136414</v>
+        <v>3.59924983978271</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G749" t="n">
-        <v>3.57619690895081</v>
+        <v>3.57619714736938</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G750" t="n">
-        <v>3.57763767242432</v>
+        <v>3.57763719558716</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G751" t="n">
-        <v>3.58051919937134</v>
+        <v>3.58051896095276</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G752" t="n">
-        <v>3.60933589935303</v>
+        <v>3.60933637619019</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.62014293670654</v>
+        <v>3.62014245986938</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G754" t="n">
-        <v>3.5978090763092</v>
+        <v>3.59780931472778</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G755" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G756" t="n">
-        <v>3.61293792724609</v>
+        <v>3.61293840408325</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>3.61654043197632</v>
+        <v>3.6165406703949</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G760" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G761" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57187414169312</v>
+        <v>3.57187366485596</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G764" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G765" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G766" t="n">
-        <v>3.57619690895081</v>
+        <v>3.57619714736938</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G767" t="n">
-        <v>3.59060525894165</v>
+        <v>3.59060502052307</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G769" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G771" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G772" t="n">
-        <v>3.67057204246521</v>
+        <v>3.67057251930237</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>3.61654043197632</v>
+        <v>3.6165406703949</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G776" t="n">
-        <v>3.70659375190735</v>
+        <v>3.70659399032593</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G777" t="n">
-        <v>3.70659375190735</v>
+        <v>3.70659399032593</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>3.67777609825134</v>
+        <v>3.67777681350708</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.72460412979126</v>
+        <v>3.7246036529541</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>3.75702381134033</v>
+        <v>3.75702357292175</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.71379852294922</v>
+        <v>3.71379828453064</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>3.71379852294922</v>
+        <v>3.71379828453064</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G785" t="n">
-        <v>3.77503418922424</v>
+        <v>3.77503371238708</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G786" t="n">
-        <v>3.73901295661926</v>
+        <v>3.73901271820068</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G787" t="n">
-        <v>3.73180866241455</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>3.72100257873535</v>
+        <v>3.72100234031677</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G790" t="n">
-        <v>3.68858289718628</v>
+        <v>3.68858313560486</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>3.72100257873535</v>
+        <v>3.72100234031677</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.71739983558655</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>3.62014293670654</v>
+        <v>3.62014245986938</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.68858289718628</v>
+        <v>3.68858313560486</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>3.67777609825134</v>
+        <v>3.67777681350708</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.125</v>
       </c>
       <c r="G800" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218564033508</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>5.125</v>
       </c>
       <c r="G801" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218564033508</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>3.67777609825134</v>
+        <v>3.67777681350708</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>3.69578719139099</v>
+        <v>3.69578742980957</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.67057204246521</v>
+        <v>3.67057251930237</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>5.125</v>
       </c>
       <c r="G807" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218564033508</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G808" t="n">
-        <v>3.67057204246521</v>
+        <v>3.67057251930237</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.73180866241455</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.73541069030762</v>
+        <v>3.73541045188904</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>3.68858289718628</v>
+        <v>3.68858313560486</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.73180866241455</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73180866241455</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G815" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G816" t="n">
-        <v>3.73180866241455</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342082977295</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>3.74981904029846</v>
+        <v>3.74981880187988</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>3.75702381134033</v>
+        <v>3.75702357292175</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>3.73901295661926</v>
+        <v>3.73901271820068</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>3.72460412979126</v>
+        <v>3.7246036529541</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342082977295</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G827" t="n">
-        <v>3.69938945770264</v>
+        <v>3.69938969612122</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>3.72460412979126</v>
+        <v>3.7246036529541</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G830" t="n">
-        <v>3.73180866241455</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>3.72460412979126</v>
+        <v>3.7246036529541</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G832" t="n">
-        <v>3.76062536239624</v>
+        <v>3.76062512397766</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584027290344</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G836" t="n">
-        <v>3.81465816497803</v>
+        <v>3.81465744972229</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342082977295</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>3.77503418922424</v>
+        <v>3.77503371238708</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584027290344</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.77863621711731</v>
+        <v>3.77863550186157</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>3.81465816497803</v>
+        <v>3.81465744972229</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148500442505</v>
+        <v>3.86148548126221</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>5.375</v>
       </c>
       <c r="G844" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229180335999</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.82186198234558</v>
+        <v>3.82186126708984</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>5.25</v>
       </c>
       <c r="G847" t="n">
-        <v>3.78223824501038</v>
+        <v>3.78223848342896</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G849" t="n">
-        <v>3.78944253921509</v>
+        <v>3.78944277763367</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G850" t="n">
-        <v>3.86508727073669</v>
+        <v>3.86508750915527</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>3.82906603813171</v>
+        <v>3.82906556129456</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G852" t="n">
-        <v>3.8903021812439</v>
+        <v>3.89030265808105</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G853" t="n">
-        <v>3.87589383125305</v>
+        <v>3.87589359283447</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80024933815002</v>
+        <v>3.80024886131287</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80024933815002</v>
+        <v>3.80024886131287</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80024933815002</v>
+        <v>3.80024886131287</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.85067892074585</v>
+        <v>3.85067844390869</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>3.83627009391785</v>
+        <v>3.83626985549927</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>3.84707713127136</v>
+        <v>3.8470766544342</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G862" t="n">
-        <v>3.83266830444336</v>
+        <v>3.83266806602478</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G863" t="n">
-        <v>3.81105494499207</v>
+        <v>3.81105518341064</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.375</v>
       </c>
       <c r="G866" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229180335999</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>3.90471053123474</v>
+        <v>3.90471076965332</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.375</v>
       </c>
       <c r="G869" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229180335999</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G871" t="n">
-        <v>3.83266830444336</v>
+        <v>3.83266806602478</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>3.83627009391785</v>
+        <v>3.83626985549927</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>3.80024933815002</v>
+        <v>3.80024886131287</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>3.83266830444336</v>
+        <v>3.83266806602478</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G878" t="n">
-        <v>3.92632341384888</v>
+        <v>3.9263231754303</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97315120697021</v>
+        <v>3.97315096855164</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>4.01997900009155</v>
+        <v>4.01997947692871</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.625</v>
       </c>
       <c r="G883" t="n">
-        <v>4.05239868164062</v>
+        <v>4.05239772796631</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>4.08841943740845</v>
+        <v>4.08841991424561</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.16406393051147</v>
+        <v>4.16406440734863</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18567657470703</v>
+        <v>4.18567752838135</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G892" t="n">
-        <v>4.1784725189209</v>
+        <v>4.17847299575806</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G893" t="n">
-        <v>4.19648361206055</v>
+        <v>4.19648313522339</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.21089220046997</v>
+        <v>4.21089172363281</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G896" t="n">
-        <v>4.27212762832642</v>
+        <v>4.27212810516357</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>4.29013872146606</v>
+        <v>4.29013919830322</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G898" t="n">
-        <v>4.31895542144775</v>
+        <v>4.31895637512207</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G903" t="n">
-        <v>4.32615995407104</v>
+        <v>4.32616090774536</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G904" t="n">
-        <v>4.35858011245728</v>
+        <v>4.35857963562012</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G907" t="n">
-        <v>4.3946008682251</v>
+        <v>4.39460039138794</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>4.18567657470703</v>
+        <v>4.18567752838135</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>4.11723661422729</v>
+        <v>4.11723709106445</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.89750671386719</v>
+        <v>3.89750647544861</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>3.77863621711731</v>
+        <v>3.77863550186157</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81825947761536</v>
+        <v>3.81825995445251</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.71739983558655</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G918" t="n">
-        <v>3.61654043197632</v>
+        <v>3.6165406703949</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G920" t="n">
-        <v>3.24624133110046</v>
+        <v>3.24624109268188</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.5</v>
       </c>
       <c r="G921" t="n">
-        <v>3.24191856384277</v>
+        <v>3.24191832542419</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G928" t="n">
-        <v>2.52437400817871</v>
+        <v>2.52437376976013</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G929" t="n">
-        <v>2.45809483528137</v>
+        <v>2.45809459686279</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.5</v>
       </c>
       <c r="G930" t="n">
-        <v>2.52149224281311</v>
+        <v>2.52149200439453</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G932" t="n">
-        <v>2.87305998802185</v>
+        <v>2.87306022644043</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G933" t="n">
-        <v>2.78949117660522</v>
+        <v>2.78949069976807</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G935" t="n">
-        <v>2.89035034179688</v>
+        <v>2.89035081863403</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G936" t="n">
-        <v>2.83127546310425</v>
+        <v>2.83127570152283</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G939" t="n">
-        <v>2.89035034179688</v>
+        <v>2.89035081863403</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98976945877075</v>
+        <v>2.98976969718933</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>2.97536087036133</v>
+        <v>2.97536110877991</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G946" t="n">
-        <v>3.01138186454773</v>
+        <v>3.01138210296631</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G949" t="n">
-        <v>2.92349004745483</v>
+        <v>2.92349028587341</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G950" t="n">
-        <v>2.91772675514221</v>
+        <v>2.91772699356079</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9105224609375</v>
+        <v>2.91052269935608</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G952" t="n">
-        <v>2.9047589302063</v>
+        <v>2.90475940704346</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G953" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G954" t="n">
-        <v>2.94654369354248</v>
+        <v>2.94654393196106</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G955" t="n">
-        <v>2.94654369354248</v>
+        <v>2.94654393196106</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G957" t="n">
-        <v>2.85576987266541</v>
+        <v>2.85577011108398</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G963" t="n">
-        <v>2.78228664398193</v>
+        <v>2.78228640556335</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>2.85288858413696</v>
+        <v>2.85288834571838</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G966" t="n">
-        <v>3.02434968948364</v>
+        <v>3.02434992790222</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G967" t="n">
-        <v>2.95230746269226</v>
+        <v>2.95230722427368</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G968" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G969" t="n">
-        <v>2.93357610702515</v>
+        <v>2.93357586860657</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>3.11038947105408</v>
+        <v>3.11038970947266</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G974" t="n">
-        <v>3.09673404693604</v>
+        <v>3.09673380851746</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>3.09521675109863</v>
+        <v>3.09521698951721</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G983" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625235557556</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G986" t="n">
-        <v>3.12556219100952</v>
+        <v>3.12556195259094</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G988" t="n">
-        <v>3.14528679847717</v>
+        <v>3.14528656005859</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G990" t="n">
-        <v>3.0603199005127</v>
+        <v>3.06031966209412</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G993" t="n">
-        <v>3.01631927490234</v>
+        <v>3.01631951332092</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G994" t="n">
-        <v>2.98900842666626</v>
+        <v>2.98900866508484</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G997" t="n">
-        <v>3.04362988471985</v>
+        <v>3.04363012313843</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.11949324607849</v>
+        <v>3.11949300765991</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.05728554725647</v>
+        <v>3.05728530883789</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.82210993766785</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.81604051589966</v>
+        <v>2.81604027748108</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.81604051589966</v>
+        <v>2.81604027748108</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.69769382476807</v>
+        <v>2.69769406318665</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.67038345336914</v>
+        <v>2.67038321495056</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.62486529350281</v>
+        <v>2.62486553192139</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.6461067199707</v>
+        <v>2.64610695838928</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.74928092956543</v>
+        <v>2.74928069114685</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.75990200042725</v>
+        <v>2.75990176200867</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.73562526702881</v>
+        <v>2.73562550544739</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.87217926979065</v>
+        <v>2.87217950820923</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.77052283287048</v>
+        <v>2.7705225944519</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.71134924888611</v>
+        <v>2.71134901046753</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.73259091377258</v>
+        <v>2.732590675354</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.67038345336914</v>
+        <v>2.67038321495056</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G1047" t="n">
-        <v>2.68707299232483</v>
+        <v>2.68707323074341</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.74624609947205</v>
+        <v>2.74624633789062</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.7083146572113</v>
+        <v>2.70831489562988</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.6552107334137</v>
+        <v>2.65521049499512</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.5307948589325</v>
+        <v>2.53079509735107</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.55051946640015</v>
+        <v>2.55051922798157</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.38665461540222</v>
+        <v>2.3866548538208</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.36844778060913</v>
+        <v>2.36844801902771</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.47769093513489</v>
+        <v>2.47769069671631</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.39727568626404</v>
+        <v>2.39727592468262</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.39120674133301</v>
+        <v>2.39120650291443</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.24858403205872</v>
+        <v>2.24858427047729</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.26072216033936</v>
+        <v>2.26072239875793</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.35327506065369</v>
+        <v>2.35327529907227</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.32444739341736</v>
+        <v>2.32444715499878</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.34113693237305</v>
+        <v>2.34113669395447</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.80693697929382</v>
+        <v>2.80693674087524</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.82210993766785</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.9404559135437</v>
+        <v>2.94045615196228</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.98900842666626</v>
+        <v>2.98900866508484</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.8266613483429</v>
+        <v>2.82666110992432</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.80693697929382</v>
+        <v>2.80693674087524</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.82817840576172</v>
+        <v>2.8281786441803</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.47199988365173</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.63396883010864</v>
+        <v>2.63396859169006</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.62486529350281</v>
+        <v>2.62486553192139</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.7083146572113</v>
+        <v>2.70831489562988</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.73259091377258</v>
+        <v>2.732590675354</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.73865985870361</v>
+        <v>2.73865962028503</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.71134924888611</v>
+        <v>2.71134901046753</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.67948651313782</v>
+        <v>2.6794867515564</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.55051946640015</v>
+        <v>2.55051922798157</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.65672779083252</v>
+        <v>2.6567280292511</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.76141905784607</v>
+        <v>2.76141929626465</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.78417778015137</v>
+        <v>2.78417801856995</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.82817840576172</v>
+        <v>2.8281786441803</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.89038610458374</v>
+        <v>2.89038634300232</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728194236755</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728194236755</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.94197344779968</v>
+        <v>2.9419732093811</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.11949324607849</v>
+        <v>3.11949300765991</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.0603199005127</v>
+        <v>3.06031966209412</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.02997469902039</v>
+        <v>3.02997446060181</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.01783633232117</v>
+        <v>3.01783657073975</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.96624970436096</v>
+        <v>2.96624994277954</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.93742179870605</v>
+        <v>2.93742156028748</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.24087405204773</v>
+        <v>3.24087429046631</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.28032302856445</v>
+        <v>3.28032279014587</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.25604653358459</v>
+        <v>3.25604677200317</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.28639197349548</v>
+        <v>3.2863917350769</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.27577114105225</v>
+        <v>3.27577090263367</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625235557556</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.12556219100952</v>
+        <v>3.12556195259094</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.05273389816284</v>
+        <v>3.05273365974426</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.01935410499573</v>
+        <v>3.01935386657715</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.00873327255249</v>
+        <v>3.00873303413391</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.92831778526306</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.93135261535645</v>
+        <v>2.93135237693787</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.92831778526306</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.90404200553894</v>
+        <v>2.90404176712036</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.89342093467712</v>
+        <v>2.89342069625854</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.86459302902222</v>
+        <v>2.86459279060364</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728194236755</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.00418138504028</v>
+        <v>3.0041811466217</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.06638860702515</v>
+        <v>3.06638884544373</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.11038947105408</v>
+        <v>3.11038970947266</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.07094073295593</v>
+        <v>3.07094049453735</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.08763074874878</v>
+        <v>3.0876305103302</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.06790637969971</v>
+        <v>3.06790614128113</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.10887265205383</v>
+        <v>3.10887241363525</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.0375611782074</v>
+        <v>3.03756093978882</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.03149199485779</v>
+        <v>3.03149175643921</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.01935410499573</v>
+        <v>3.01935386657715</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.90707612037659</v>
+        <v>2.90707635879517</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.90404200553894</v>
+        <v>2.90404176712036</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.92831778526306</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.8509373664856</v>
+        <v>2.85093760490417</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.78417778015137</v>
+        <v>2.78417801856995</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.86155843734741</v>
+        <v>2.86155867576599</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.92831778526306</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.98900842666626</v>
+        <v>2.98900866508484</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.93742179870605</v>
+        <v>2.93742156028748</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.82362675666809</v>
+        <v>2.82362699508667</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.82210993766785</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.80238509178162</v>
+        <v>2.8023853302002</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.81755757331848</v>
+        <v>2.81755781173706</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.82210993766785</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.78873014450073</v>
+        <v>2.78872990608215</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.74624609947205</v>
+        <v>2.74624633789062</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.92831778526306</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.08763074874878</v>
+        <v>3.0876305103302</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.99507737159729</v>
+        <v>2.99507761001587</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.07094073295593</v>
+        <v>3.07094049453735</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.07094073295593</v>
+        <v>3.07094049453735</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.08763074874878</v>
+        <v>3.0876305103302</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.0633544921875</v>
+        <v>3.06335473060608</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.02997469902039</v>
+        <v>3.02997446060181</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.05728554725647</v>
+        <v>3.05728530883789</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.06790637969971</v>
+        <v>3.06790614128113</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.02997469902039</v>
+        <v>3.02997446060181</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.05273389816284</v>
+        <v>3.05273365974426</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.03300881385803</v>
+        <v>3.03300905227661</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.94955968856812</v>
+        <v>2.94955992698669</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.96624970436096</v>
+        <v>2.96624994277954</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.91618013381958</v>
+        <v>2.916179895401</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.01631927490234</v>
+        <v>3.01631951332092</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.2135636806488</v>
+        <v>3.21356344223022</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.19990801811218</v>
+        <v>3.19990825653076</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.96321511268616</v>
+        <v>2.96321487426758</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.76141905784607</v>
+        <v>2.76141929626465</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.77810907363892</v>
+        <v>2.77810883522034</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1368" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728194236755</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.82210993766785</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.89190363883972</v>
+        <v>2.8919038772583</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.86155843734741</v>
+        <v>2.86155867576599</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.94197344779968</v>
+        <v>2.9419732093811</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.0603199005127</v>
+        <v>3.06031966209412</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.11949324607849</v>
+        <v>3.11949300765991</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.10887265205383</v>
+        <v>3.10887241363525</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.12556219100952</v>
+        <v>3.12556195259094</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.11038947105408</v>
+        <v>3.11038970947266</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.04362988471985</v>
+        <v>3.04363012313843</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.0845959186554</v>
+        <v>3.08459615707397</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.07094073295593</v>
+        <v>3.07094049453735</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.09976840019226</v>
+        <v>3.09976863861084</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.05728554725647</v>
+        <v>3.05728530883789</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.95259428024292</v>
+        <v>2.95259404182434</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.02997469902039</v>
+        <v>3.02997446060181</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.21052885055542</v>
+        <v>3.210529088974</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1483211517334</v>
+        <v>3.14832139015198</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.11494159698486</v>
+        <v>3.11494135856628</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.11494159698486</v>
+        <v>3.11494135856628</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.00569820404053</v>
+        <v>3.00569844245911</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.01631927490234</v>
+        <v>3.01631951332092</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.92831778526306</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.01631927490234</v>
+        <v>3.01631951332092</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.07397508621216</v>
+        <v>3.07397532463074</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.08763074874878</v>
+        <v>3.0876305103302</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.11038947105408</v>
+        <v>3.11038970947266</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625235557556</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.24846029281616</v>
+        <v>3.24846053123474</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.22114944458008</v>
+        <v>3.22114968299866</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.27577114105225</v>
+        <v>3.27577090263367</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.41535925865173</v>
+        <v>3.41535949707031</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.41991114616394</v>
+        <v>3.41991138458252</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.25</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.22418427467346</v>
+        <v>3.22418403625488</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.29094386100769</v>
+        <v>3.29094362258911</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.15742516517639</v>
+        <v>3.15742492675781</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.2135636806488</v>
+        <v>3.21356344223022</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.27880573272705</v>
+        <v>3.27880597114563</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.25604653358459</v>
+        <v>3.25604677200317</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.30459904670715</v>
+        <v>3.30459928512573</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.2135636806488</v>
+        <v>3.21356344223022</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.25149464607239</v>
+        <v>3.25149488449097</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.24087405204773</v>
+        <v>3.24087429046631</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24087405204773</v>
+        <v>3.24087429046631</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625235557556</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.06638860702515</v>
+        <v>3.06638884544373</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.93893885612488</v>
+        <v>2.93893909454346</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.99356055259705</v>
+        <v>2.99356031417847</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.05728554725647</v>
+        <v>3.05728530883789</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.12252759933472</v>
+        <v>3.1225278377533</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.97080159187317</v>
+        <v>2.97080135345459</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.03300881385803</v>
+        <v>3.03300905227661</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.05273389816284</v>
+        <v>3.05273365974426</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.08763074874878</v>
+        <v>3.0876305103302</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.19990801811218</v>
+        <v>3.19990825653076</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.18928718566895</v>
+        <v>3.18928742408752</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625235557556</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.2348051071167</v>
+        <v>3.23480486869812</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.31977200508118</v>
+        <v>3.3197717666626</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.22114944458008</v>
+        <v>3.22114968299866</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.28790950775146</v>
+        <v>3.28790974617004</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.21052885055542</v>
+        <v>3.210529088974</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.21052885055542</v>
+        <v>3.210529088974</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.2090117931366</v>
+        <v>3.20901155471802</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.12556219100952</v>
+        <v>3.12556195259094</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.0421130657196</v>
+        <v>3.04211282730103</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.07397508621216</v>
+        <v>3.07397532463074</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625235557556</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.1756317615509</v>
+        <v>3.17563152313232</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.05728554725647</v>
+        <v>3.05728530883789</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.0375611782074</v>
+        <v>3.03756093978882</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728194236755</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.79631614685059</v>
+        <v>2.79631590843201</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.73865985870361</v>
+        <v>2.73865962028503</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728194236755</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.81604051589966</v>
+        <v>2.81604027748108</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.81300592422485</v>
+        <v>2.81300616264343</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.76141905784607</v>
+        <v>2.76141929626465</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.82210993766785</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.79631614685059</v>
+        <v>2.79631590843201</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.8266613483429</v>
+        <v>2.82666110992432</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.87620711326599</v>
+        <v>2.87620687484741</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.01063823699951</v>
+        <v>3.01063847541809</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.05440664291382</v>
+        <v>3.0544068813324</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.9637439250946</v>
+        <v>2.96374368667603</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05753302574158</v>
+        <v>3.05753326416016</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.04815435409546</v>
+        <v>3.04815411567688</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.34671688079834</v>
+        <v>3.34671711921692</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.35609602928162</v>
+        <v>3.3560962677002</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.33264827728271</v>
+        <v>3.33264851570129</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.31701707839966</v>
+        <v>3.31701683998108</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.14819598197937</v>
+        <v>3.14819622039795</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.12943863868713</v>
+        <v>3.12943840026855</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.13256454467773</v>
+        <v>3.13256430625916</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.09817504882812</v>
+        <v>3.09817481040955</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.09504890441895</v>
+        <v>3.09504866600037</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.11537003517151</v>
+        <v>3.11536979675293</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.19509053230286</v>
+        <v>3.19509077072144</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.31701707839966</v>
+        <v>3.31701683998108</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G1651" t="n">
-        <v>3.28575396537781</v>
+        <v>3.28575420379639</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1653" t="n">
-        <v>3.25918006896973</v>
+        <v>3.25918030738831</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.27012228965759</v>
+        <v>3.27012205123901</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.38423275947571</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.32639575004578</v>
+        <v>3.32639598846436</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>4.34600019454956</v>
       </c>
       <c r="G1662" t="n">
-        <v>3.39673781394958</v>
+        <v>3.39673805236816</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.38423275947571</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1674" t="n">
-        <v>3.18571209907532</v>
+        <v>3.18571186065674</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.17945909500122</v>
+        <v>3.17945885658264</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.26543259620667</v>
+        <v>3.26543283462524</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.26543259620667</v>
+        <v>3.26543283462524</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.2451114654541</v>
+        <v>3.24511170387268</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.27324843406677</v>
+        <v>3.27324867248535</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.05440664291382</v>
+        <v>3.0544068813324</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G1705" t="n">
-        <v>3.0278332233429</v>
+        <v>3.02783298492432</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.21697497367859</v>
+        <v>3.21697521209717</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.21228575706482</v>
+        <v>3.21228551864624</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.28106451034546</v>
+        <v>3.28106427192688</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.21228575706482</v>
+        <v>3.21228551864624</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.27950119972229</v>
+        <v>3.27950143814087</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.28575396537781</v>
+        <v>3.28575420379639</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.21541166305542</v>
+        <v>3.215411901474</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.13569068908691</v>
+        <v>3.13569092750549</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.17945909500122</v>
+        <v>3.17945885658264</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.17945909500122</v>
+        <v>3.17945885658264</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.18571209907532</v>
+        <v>3.18571186065674</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.19978022575378</v>
+        <v>3.19977998733521</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.11849617958069</v>
+        <v>3.11849594116211</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.1435067653656</v>
+        <v>3.14350652694702</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08723306655884</v>
+        <v>3.08723282814026</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.13256454467773</v>
+        <v>3.13256430625916</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.12787485122681</v>
+        <v>3.12787508964539</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.09817504882812</v>
+        <v>3.09817481040955</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1753" t="n">
-        <v>3.14975929260254</v>
+        <v>3.14975953102112</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.05753302574158</v>
+        <v>3.05753326416016</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.07629108428955</v>
+        <v>3.07629084587097</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.04346442222595</v>
+        <v>3.04346466064453</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.0622227191925</v>
+        <v>3.06222248077393</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.05440664291382</v>
+        <v>3.0544068813324</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.97312259674072</v>
+        <v>2.9731228351593</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.07629108428955</v>
+        <v>3.07629084587097</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.04346442222595</v>
+        <v>3.04346466064453</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.05128049850464</v>
+        <v>3.05128026008606</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.91372275352478</v>
+        <v>2.9137225151062</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.90278053283691</v>
+        <v>2.90278077125549</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.88089632987976</v>
+        <v>2.88089656829834</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.89652824401855</v>
+        <v>2.89652800559998</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.91059637069702</v>
+        <v>2.91059613227844</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.90590691566467</v>
+        <v>2.90590715408325</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.84494376182556</v>
+        <v>2.84494400024414</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.84650707244873</v>
+        <v>2.84650683403015</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.92466497421265</v>
+        <v>2.92466473579407</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.91059637069702</v>
+        <v>2.91059613227844</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.89183831214905</v>
+        <v>2.89183855056763</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.87620711326599</v>
+        <v>2.87620687484741</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.87620711326599</v>
+        <v>2.87620687484741</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.90590691566467</v>
+        <v>2.90590715408325</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.85901212692261</v>
+        <v>2.85901236534119</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.84494376182556</v>
+        <v>2.84494400024414</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.82931232452393</v>
+        <v>2.82931208610535</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.83556485176086</v>
+        <v>2.83556509017944</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.81211757659912</v>
+        <v>2.8121178150177</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.80586504936218</v>
+        <v>2.8058648109436</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>3.45799994468689</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.70269680023193</v>
+        <v>2.70269656181335</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68393874168396</v>
+        <v>2.68393898010254</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.73864912986755</v>
+        <v>2.73864889144897</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.5557599067688</v>
+        <v>2.55576014518738</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.53700232505798</v>
+        <v>2.5370020866394</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.54950737953186</v>
+        <v>2.54950761795044</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -67556,6 +67556,32 @@
         <v>4.91599988937378</v>
       </c>
       <c r="H2584" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2585" t="n">
+        <v>180749</v>
+      </c>
+      <c r="C2585" t="n">
+        <v>5.0149998664856</v>
+      </c>
+      <c r="D2585" t="n">
+        <v>4.94000005722046</v>
+      </c>
+      <c r="E2585" t="n">
+        <v>4.96999979019165</v>
+      </c>
+      <c r="F2585" t="n">
+        <v>4.96000003814697</v>
+      </c>
+      <c r="G2585" t="n">
+        <v>4.96000003814697</v>
+      </c>
+      <c r="H2585" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24304008483887</v>
+        <v>2.24303984642029</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>2.33255982398987</v>
+        <v>2.33256006240845</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33255982398987</v>
+        <v>2.33256006240845</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38677620887756</v>
+        <v>2.38677597045898</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33886432647705</v>
+        <v>2.33886408805847</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33886432647705</v>
+        <v>2.33886408805847</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34895062446594</v>
+        <v>2.34895086288452</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G14" t="n">
-        <v>2.37921071052551</v>
+        <v>2.37921118736267</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>2.30734300613403</v>
+        <v>2.30734324455261</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26951766014099</v>
+        <v>2.26951789855957</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.30734300613403</v>
+        <v>2.30734324455261</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29599523544312</v>
+        <v>2.29599595069885</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.31112575531006</v>
+        <v>2.31112551689148</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28590869903564</v>
+        <v>2.28590846061707</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.33508205413818</v>
+        <v>2.33508133888245</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32877707481384</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G32" t="n">
-        <v>2.35903763771057</v>
+        <v>2.35903787612915</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32877707481384</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G34" t="n">
-        <v>2.2884304523468</v>
+        <v>2.28843021392822</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25060510635376</v>
+        <v>2.25060486793518</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.20647597312927</v>
+        <v>2.20647573471069</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G41" t="n">
-        <v>2.22664904594421</v>
+        <v>2.22664928436279</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.20647597312927</v>
+        <v>2.20647573471069</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>2.2190842628479</v>
+        <v>2.21908402442932</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G45" t="n">
-        <v>2.22034478187561</v>
+        <v>2.22034502029419</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G46" t="n">
-        <v>2.21404051780701</v>
+        <v>2.21404075622559</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G48" t="n">
-        <v>2.23925757408142</v>
+        <v>2.23925733566284</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G49" t="n">
-        <v>2.30608177185059</v>
+        <v>2.30608224868774</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.26951766014099</v>
+        <v>2.26951789855957</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G56" t="n">
-        <v>2.21151876449585</v>
+        <v>2.21151900291443</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.20773673057556</v>
+        <v>2.20773649215698</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G60" t="n">
-        <v>2.18251943588257</v>
+        <v>2.18251919746399</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15478110313416</v>
+        <v>2.15478086471558</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G62" t="n">
-        <v>2.17873692512512</v>
+        <v>2.17873740196228</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G63" t="n">
-        <v>2.17873692512512</v>
+        <v>2.17873740196228</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G65" t="n">
-        <v>2.14721584320068</v>
+        <v>2.14721608161926</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>2.16865062713623</v>
+        <v>2.16865038871765</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G70" t="n">
-        <v>2.13965106010437</v>
+        <v>2.13965082168579</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>2.1232602596283</v>
+        <v>2.12326002120972</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>2.13082528114319</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195887565613</v>
+        <v>1.97195899486542</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93161165714264</v>
+        <v>1.93161177635193</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>1.92909026145935</v>
+        <v>1.92908990383148</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G84" t="n">
-        <v>1.94800305366516</v>
+        <v>1.94800281524658</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>1.90387332439423</v>
+        <v>1.90387308597565</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.90387332439423</v>
+        <v>1.90387308597565</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>1.9278290271759</v>
+        <v>1.92782926559448</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G88" t="n">
-        <v>1.97574150562286</v>
+        <v>1.97574162483215</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G89" t="n">
-        <v>1.97321999073029</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G90" t="n">
-        <v>1.99339294433594</v>
+        <v>1.99339306354523</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G91" t="n">
-        <v>2.01356649398804</v>
+        <v>2.01356673240662</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G92" t="n">
-        <v>2.01104497909546</v>
+        <v>2.01104474067688</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>2.00474047660828</v>
+        <v>2.00474071502686</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G94" t="n">
-        <v>1.97448027133942</v>
+        <v>1.974480509758</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>1.95430672168732</v>
+        <v>1.95430660247803</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G96" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213230609894</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>1.97321999073029</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G98" t="n">
-        <v>1.91017723083496</v>
+        <v>1.91017746925354</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G100" t="n">
-        <v>1.89504718780518</v>
+        <v>1.89504742622375</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G102" t="n">
-        <v>2.00474047660828</v>
+        <v>2.00474071502686</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G104" t="n">
-        <v>2.0892174243927</v>
+        <v>2.08921694755554</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>2.06147813796997</v>
+        <v>2.06147861480713</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>2.08669519424438</v>
+        <v>2.08669567108154</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>2.06147813796997</v>
+        <v>2.06147861480713</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.06147813796997</v>
+        <v>2.06147861480713</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G112" t="n">
-        <v>2.07913064956665</v>
+        <v>2.07913041114807</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G114" t="n">
-        <v>2.08417344093323</v>
+        <v>2.08417367935181</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G115" t="n">
-        <v>2.11569476127625</v>
+        <v>2.11569499969482</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G117" t="n">
-        <v>2.14469408988953</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.13082528114319</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.15604186058044</v>
+        <v>2.1560423374176</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.15604186058044</v>
+        <v>2.1560423374176</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15352010726929</v>
+        <v>2.15351986885071</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>2.13460755348206</v>
+        <v>2.13460731506348</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G131" t="n">
-        <v>2.11191248893738</v>
+        <v>2.1119122505188</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>2.11191248893738</v>
+        <v>2.1119122505188</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G133" t="n">
-        <v>2.06904363632202</v>
+        <v>2.0690438747406</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G134" t="n">
-        <v>2.04256582260132</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G135" t="n">
-        <v>2.04256582260132</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G136" t="n">
-        <v>2.02617478370667</v>
+        <v>2.02617502212524</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.04256582260132</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213230609894</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G140" t="n">
-        <v>1.97069787979126</v>
+        <v>1.97069776058197</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.02365326881409</v>
+        <v>2.02365303039551</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>2.01734948158264</v>
+        <v>2.01734924316406</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G144" t="n">
-        <v>2.07282614707947</v>
+        <v>2.07282638549805</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11191248893738</v>
+        <v>2.1119122505188</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>2.152259349823</v>
+        <v>2.15225958824158</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G153" t="n">
-        <v>2.09552121162415</v>
+        <v>2.09552145004272</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>2.08669519424438</v>
+        <v>2.08669567108154</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.1232602596283</v>
+        <v>2.12326002120972</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>2.13082528114319</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G160" t="n">
-        <v>2.12704253196716</v>
+        <v>2.12704277038574</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G161" t="n">
-        <v>2.14469408988953</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G162" t="n">
-        <v>2.16234612464905</v>
+        <v>2.16234636306763</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G166" t="n">
-        <v>2.1724328994751</v>
+        <v>2.17243266105652</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>2.21277952194214</v>
+        <v>2.2127799987793</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.2884304523468</v>
+        <v>2.28843021392822</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>2.27582192420959</v>
+        <v>2.27582168579102</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G171" t="n">
-        <v>2.30734300613403</v>
+        <v>2.30734324455261</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35147285461426</v>
+        <v>2.35147261619568</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40190577507019</v>
+        <v>2.40190649032593</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G175" t="n">
-        <v>2.35399436950684</v>
+        <v>2.35399460792542</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.32877707481384</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G177" t="n">
-        <v>2.34012508392334</v>
+        <v>2.34012484550476</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G181" t="n">
-        <v>2.3918194770813</v>
+        <v>2.39181971549988</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G182" t="n">
-        <v>2.37038540840149</v>
+        <v>2.37038493156433</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G189" t="n">
-        <v>2.36534190177917</v>
+        <v>2.36534214019775</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G193" t="n">
-        <v>2.35525512695312</v>
+        <v>2.35525560379028</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G194" t="n">
-        <v>2.38047218322754</v>
+        <v>2.38047194480896</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G196" t="n">
-        <v>2.37038540840149</v>
+        <v>2.37038493156433</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G197" t="n">
-        <v>2.39308047294617</v>
+        <v>2.39308071136475</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.45234036445618</v>
+        <v>2.4523401260376</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G203" t="n">
-        <v>2.4384708404541</v>
+        <v>2.43847036361694</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G204" t="n">
-        <v>2.43090581893921</v>
+        <v>2.43090558052063</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G205" t="n">
-        <v>2.44603562355042</v>
+        <v>2.44603610038757</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.45864391326904</v>
+        <v>2.4586443901062</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.44603562355042</v>
+        <v>2.44603610038757</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>2.38677620887756</v>
+        <v>2.38677597045898</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G210" t="n">
-        <v>2.37038540840149</v>
+        <v>2.37038493156433</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G211" t="n">
-        <v>2.41535902023315</v>
+        <v>2.41535878181458</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G214" t="n">
-        <v>2.51192045211792</v>
+        <v>2.51192021369934</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G215" t="n">
-        <v>2.51721167564392</v>
+        <v>2.51721143722534</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>2.50001549720764</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G218" t="n">
-        <v>2.48149704933167</v>
+        <v>2.48149681091309</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.75</v>
       </c>
       <c r="G219" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.50001549720764</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.75</v>
       </c>
       <c r="G221" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.75</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G223" t="n">
-        <v>2.46562385559082</v>
+        <v>2.4656240940094</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G224" t="n">
-        <v>2.49737024307251</v>
+        <v>2.49737000465393</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G225" t="n">
-        <v>2.52250242233276</v>
+        <v>2.52250266075134</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G226" t="n">
-        <v>2.48546528816223</v>
+        <v>2.48546504974365</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G227" t="n">
-        <v>2.50530695915222</v>
+        <v>2.50530672073364</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G228" t="n">
-        <v>2.51324319839478</v>
+        <v>2.5132429599762</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.75</v>
       </c>
       <c r="G231" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.75</v>
       </c>
       <c r="G232" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.75</v>
       </c>
       <c r="G235" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.75</v>
       </c>
       <c r="G236" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G240" t="n">
-        <v>2.49207878112793</v>
+        <v>2.49207901954651</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46033263206482</v>
+        <v>2.4603328704834</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46165537834167</v>
+        <v>2.4616551399231</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G245" t="n">
-        <v>2.46165537834167</v>
+        <v>2.4616551399231</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G247" t="n">
-        <v>2.44445943832397</v>
+        <v>2.44445991516113</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46562385559082</v>
+        <v>2.4656240940094</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>2.44578218460083</v>
+        <v>2.44578266143799</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>2.44975090026855</v>
+        <v>2.44975066184998</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>2.45371913909912</v>
+        <v>2.45371890068054</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G256" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.46033263206482</v>
+        <v>2.4603328704834</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G261" t="n">
-        <v>2.5648307800293</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G263" t="n">
-        <v>2.57144451141357</v>
+        <v>2.57144474983215</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G265" t="n">
-        <v>2.5648307800293</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G267" t="n">
-        <v>2.55424904823303</v>
+        <v>2.55424857139587</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.5595395565033</v>
+        <v>2.55953979492188</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G270" t="n">
-        <v>2.52382493019104</v>
+        <v>2.5238254070282</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G272" t="n">
-        <v>2.51324319839478</v>
+        <v>2.5132429599762</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G273" t="n">
-        <v>2.50001549720764</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G276" t="n">
-        <v>2.46165537834167</v>
+        <v>2.4616551399231</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.48678827285767</v>
+        <v>2.48678803443909</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G279" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G280" t="n">
-        <v>2.44842791557312</v>
+        <v>2.4484281539917</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G281" t="n">
-        <v>2.42858624458313</v>
+        <v>2.42858648300171</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G282" t="n">
-        <v>2.43784618377686</v>
+        <v>2.43784594535828</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G283" t="n">
-        <v>2.45900964736938</v>
+        <v>2.45901012420654</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G284" t="n">
-        <v>2.4775288105011</v>
+        <v>2.47752857208252</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G285" t="n">
-        <v>2.46959233283997</v>
+        <v>2.46959209442139</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G288" t="n">
-        <v>2.49869298934937</v>
+        <v>2.49869275093079</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G290" t="n">
-        <v>2.5595395565033</v>
+        <v>2.55953979492188</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G291" t="n">
-        <v>2.53837561607361</v>
+        <v>2.53837537765503</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G293" t="n">
-        <v>2.53440761566162</v>
+        <v>2.53440713882446</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G295" t="n">
-        <v>2.53176212310791</v>
+        <v>2.53176188468933</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G297" t="n">
-        <v>2.52779340744019</v>
+        <v>2.52779364585876</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G299" t="n">
-        <v>2.51721167564392</v>
+        <v>2.51721143722534</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G304" t="n">
-        <v>2.56350803375244</v>
+        <v>2.56350827217102</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G305" t="n">
-        <v>2.61377310752869</v>
+        <v>2.61377286911011</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G306" t="n">
-        <v>2.59922242164612</v>
+        <v>2.59922289848328</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G310" t="n">
-        <v>2.58334946632385</v>
+        <v>2.58334922790527</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G312" t="n">
-        <v>2.58864068984985</v>
+        <v>2.58864045143127</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G313" t="n">
-        <v>2.62700033187866</v>
+        <v>2.62700057029724</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G316" t="n">
-        <v>2.60319089889526</v>
+        <v>2.60319113731384</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G317" t="n">
-        <v>2.67329692840576</v>
+        <v>2.67329668998718</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G319" t="n">
-        <v>2.67594265937805</v>
+        <v>2.67594242095947</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G320" t="n">
-        <v>2.6971070766449</v>
+        <v>2.69710683822632</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>2.67858815193176</v>
+        <v>2.67858839035034</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G324" t="n">
-        <v>2.66932845115662</v>
+        <v>2.6693286895752</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G325" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504403114319</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G326" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504403114319</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G327" t="n">
-        <v>2.68784761428833</v>
+        <v>2.68784785270691</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G328" t="n">
-        <v>2.68784761428833</v>
+        <v>2.68784785270691</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G329" t="n">
-        <v>2.70239758491516</v>
+        <v>2.70239782333374</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504403114319</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>2.68520164489746</v>
+        <v>2.68520188331604</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G332" t="n">
-        <v>2.70107507705688</v>
+        <v>2.70107531547546</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G333" t="n">
-        <v>2.70107507705688</v>
+        <v>2.70107531547546</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>2.65874624252319</v>
+        <v>2.65874671936035</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>2.67197442054749</v>
+        <v>2.67197418212891</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.74472618103027</v>
+        <v>2.74472641944885</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G337" t="n">
-        <v>2.78837752342224</v>
+        <v>2.78837704658508</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054659843445</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G339" t="n">
-        <v>2.84790182113647</v>
+        <v>2.8479015827179</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G340" t="n">
-        <v>2.88758444786072</v>
+        <v>2.88758420944214</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G342" t="n">
-        <v>2.90742588043213</v>
+        <v>2.90742540359497</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>2.94578552246094</v>
+        <v>2.94578576087952</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G344" t="n">
-        <v>2.95901298522949</v>
+        <v>2.95901322364807</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G346" t="n">
-        <v>2.97356367111206</v>
+        <v>2.97356343269348</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G347" t="n">
-        <v>2.96430397033691</v>
+        <v>2.96430420875549</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G348" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G349" t="n">
-        <v>2.95901298522949</v>
+        <v>2.95901322364807</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>2.99340510368347</v>
+        <v>2.99340486526489</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G351" t="n">
-        <v>3.01456928253174</v>
+        <v>3.01456904411316</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03837847709656</v>
+        <v>3.03837871551514</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G353" t="n">
-        <v>3.03176474571228</v>
+        <v>3.03176498413086</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G355" t="n">
-        <v>3.03441071510315</v>
+        <v>3.03441047668457</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>3.01456928253174</v>
+        <v>3.01456904411316</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>3.0423469543457</v>
+        <v>3.04234719276428</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>3.00266408920288</v>
+        <v>3.00266456604004</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>3.02911949157715</v>
+        <v>3.02911972999573</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05557441711426</v>
+        <v>3.05557417869568</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>3.00266408920288</v>
+        <v>3.00266456604004</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G368" t="n">
-        <v>2.97091817855835</v>
+        <v>2.97091794013977</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G370" t="n">
-        <v>2.97356367111206</v>
+        <v>2.97356343269348</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G371" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G372" t="n">
-        <v>3.04896092414856</v>
+        <v>3.04896068572998</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>2.94313955307007</v>
+        <v>2.94313979148865</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G375" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054659843445</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.87700200080872</v>
+        <v>2.87700223922729</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G377" t="n">
-        <v>2.84922432899475</v>
+        <v>2.84922409057617</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G378" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G379" t="n">
-        <v>2.86509680747986</v>
+        <v>2.86509704589844</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85980629920959</v>
+        <v>2.85980653762817</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G383" t="n">
-        <v>2.83070588111877</v>
+        <v>2.83070540428162</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G385" t="n">
-        <v>2.84922432899475</v>
+        <v>2.84922409057617</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.87700200080872</v>
+        <v>2.87700223922729</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.79763627052307</v>
+        <v>2.79763650894165</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705453872681</v>
+        <v>2.78705477714539</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80689573287964</v>
+        <v>2.80689597129822</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>2.80689573287964</v>
+        <v>2.80689597129822</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>2.71165728569031</v>
+        <v>2.71165680885315</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>2.75398564338684</v>
+        <v>2.75398540496826</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G396" t="n">
-        <v>2.67329692840576</v>
+        <v>2.67329668998718</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69446134567261</v>
+        <v>2.69446110725403</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G399" t="n">
-        <v>2.75266289710999</v>
+        <v>2.75266265869141</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G400" t="n">
-        <v>2.75001692771912</v>
+        <v>2.7500171661377</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.75927662849426</v>
+        <v>2.75927639007568</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74472618103027</v>
+        <v>2.74472641944885</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>2.79102277755737</v>
+        <v>2.79102230072021</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.66932845115662</v>
+        <v>2.6693286895752</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>2.6799111366272</v>
+        <v>2.67991089820862</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G413" t="n">
-        <v>2.76324486732483</v>
+        <v>2.76324462890625</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>2.75927662849426</v>
+        <v>2.75927639007568</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G415" t="n">
-        <v>2.78044056892395</v>
+        <v>2.78044080734253</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G416" t="n">
-        <v>2.79102277755737</v>
+        <v>2.79102230072021</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G417" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G419" t="n">
-        <v>2.87303376197815</v>
+        <v>2.87303352355957</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>2.91007137298584</v>
+        <v>2.91007113456726</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G421" t="n">
-        <v>2.88890719413757</v>
+        <v>2.88890671730042</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G424" t="n">
-        <v>2.84790182113647</v>
+        <v>2.8479015827179</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G425" t="n">
-        <v>2.79631376266479</v>
+        <v>2.79631400108337</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G427" t="n">
-        <v>2.79234576225281</v>
+        <v>2.79234552383423</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G428" t="n">
-        <v>2.83335113525391</v>
+        <v>2.83335089683533</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G429" t="n">
-        <v>2.84790182113647</v>
+        <v>2.8479015827179</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054659843445</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.89022970199585</v>
+        <v>2.89022922515869</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G435" t="n">
-        <v>2.90610313415527</v>
+        <v>2.90610289573669</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99208188056946</v>
+        <v>2.99208211898804</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G440" t="n">
-        <v>3.0079550743103</v>
+        <v>3.00795531272888</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.93652629852295</v>
+        <v>2.93652606010437</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520379066467</v>
+        <v>2.93520355224609</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>2.95636773109436</v>
+        <v>2.95636749267578</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>2.95636773109436</v>
+        <v>2.95636749267578</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G448" t="n">
-        <v>2.99737358093262</v>
+        <v>2.99737334251404</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G449" t="n">
-        <v>2.99075937271118</v>
+        <v>2.9907591342926</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.99208188056946</v>
+        <v>2.99208211898804</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G451" t="n">
-        <v>3.01721429824829</v>
+        <v>3.01721405982971</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G453" t="n">
-        <v>2.99737358093262</v>
+        <v>2.99737334251404</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00398659706116</v>
+        <v>3.00398707389832</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G455" t="n">
-        <v>2.99737358093262</v>
+        <v>2.99737334251404</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92991209030151</v>
+        <v>2.92991232872009</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G460" t="n">
-        <v>3.01589202880859</v>
+        <v>3.01589155197144</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G462" t="n">
-        <v>2.89684343338013</v>
+        <v>2.89684367179871</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88361573219299</v>
+        <v>2.88361597061157</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G464" t="n">
-        <v>2.89080119132996</v>
+        <v>2.89080142974854</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>2.89494705200195</v>
+        <v>2.89494681358337</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G468" t="n">
-        <v>2.88112854957581</v>
+        <v>2.88112831115723</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>2.75676274299622</v>
+        <v>2.75676345825195</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G471" t="n">
-        <v>2.80650949478149</v>
+        <v>2.80650901794434</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G472" t="n">
-        <v>2.84796476364136</v>
+        <v>2.8479642868042</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G473" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G475" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>2.81894612312317</v>
+        <v>2.81894588470459</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>2.79130911827087</v>
+        <v>2.79130887985229</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G480" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.86731004714966</v>
+        <v>2.86731052398682</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G482" t="n">
-        <v>2.92258334159851</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G484" t="n">
-        <v>2.96542024612427</v>
+        <v>2.96542048454285</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G485" t="n">
-        <v>2.99858498573303</v>
+        <v>2.99858474731445</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G487" t="n">
-        <v>2.99029350280762</v>
+        <v>2.9902937412262</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.9737114906311</v>
+        <v>2.97371125221252</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97785687446594</v>
+        <v>2.97785663604736</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>2.95989346504211</v>
+        <v>2.95989322662354</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G495" t="n">
-        <v>2.99029350280762</v>
+        <v>2.9902937412262</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>2.99858498573303</v>
+        <v>2.99858474731445</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G500" t="n">
-        <v>2.97923898696899</v>
+        <v>2.97923851013184</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G503" t="n">
-        <v>3.01793050765991</v>
+        <v>3.01793026924133</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G504" t="n">
-        <v>3.03174829483032</v>
+        <v>3.03174877166748</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G505" t="n">
-        <v>3.05109405517578</v>
+        <v>3.05109429359436</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G509" t="n">
-        <v>3.08840370178223</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>3.04556679725647</v>
+        <v>3.04556703567505</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>3.05385828018188</v>
+        <v>3.05385780334473</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>3.04556679725647</v>
+        <v>3.04556703567505</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G514" t="n">
-        <v>3.05109405517578</v>
+        <v>3.05109429359436</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G515" t="n">
-        <v>3.04418540000916</v>
+        <v>3.04418516159058</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G516" t="n">
-        <v>3.02760291099548</v>
+        <v>3.02760338783264</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G517" t="n">
-        <v>3.02760291099548</v>
+        <v>3.02760338783264</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G519" t="n">
-        <v>3.0096390247345</v>
+        <v>3.00963926315308</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G525" t="n">
-        <v>2.99582099914551</v>
+        <v>2.99582076072693</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G526" t="n">
-        <v>2.92258334159851</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>2.90185570716858</v>
+        <v>2.90185594558716</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>2.92258334159851</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G532" t="n">
-        <v>2.93087434768677</v>
+        <v>2.93087458610535</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94192934036255</v>
+        <v>2.94192910194397</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>2.91152882575989</v>
+        <v>2.91152930259705</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.9281108379364</v>
+        <v>2.92811059951782</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G542" t="n">
-        <v>2.95989346504211</v>
+        <v>2.95989322662354</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>2.99167561531067</v>
+        <v>2.99167513847351</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.9737114906311</v>
+        <v>2.97371125221252</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06491255760193</v>
+        <v>3.06491279602051</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G548" t="n">
-        <v>3.00134825706482</v>
+        <v>3.00134801864624</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G550" t="n">
-        <v>2.97232985496521</v>
+        <v>2.97232937812805</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G552" t="n">
-        <v>2.92949247360229</v>
+        <v>2.92949271202087</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>2.95712971687317</v>
+        <v>2.95712995529175</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G556" t="n">
-        <v>2.90323758125305</v>
+        <v>2.90323805809021</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G557" t="n">
-        <v>2.90047407150269</v>
+        <v>2.90047430992126</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.85349178314209</v>
+        <v>2.85349202156067</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G560" t="n">
-        <v>2.87007355690002</v>
+        <v>2.87007403373718</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>2.84658265113831</v>
+        <v>2.84658241271973</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G564" t="n">
-        <v>2.78439998626709</v>
+        <v>2.78440022468567</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76367235183716</v>
+        <v>2.76367259025574</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G566" t="n">
-        <v>2.77610874176025</v>
+        <v>2.77610921859741</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77749037742615</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G570" t="n">
-        <v>2.73327207565308</v>
+        <v>2.73327231407166</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G571" t="n">
-        <v>2.74847197532654</v>
+        <v>2.74847221374512</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G572" t="n">
-        <v>2.77749037742615</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G573" t="n">
-        <v>2.76505398750305</v>
+        <v>2.76505422592163</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>2.74985432624817</v>
+        <v>2.74985408782959</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G575" t="n">
-        <v>2.71668982505798</v>
+        <v>2.71669006347656</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>2.73603558540344</v>
+        <v>2.73603582382202</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G577" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G579" t="n">
-        <v>2.74847197532654</v>
+        <v>2.74847221374512</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G580" t="n">
-        <v>2.75123620033264</v>
+        <v>2.75123572349548</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77749037742615</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74985432624817</v>
+        <v>2.74985408782959</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G585" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G586" t="n">
-        <v>2.74018120765686</v>
+        <v>2.74018144607544</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G587" t="n">
-        <v>2.75814485549927</v>
+        <v>2.75814533233643</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73879909515381</v>
+        <v>2.73879957199097</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G590" t="n">
-        <v>2.83276438713074</v>
+        <v>2.83276414871216</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G591" t="n">
-        <v>2.83967328071594</v>
+        <v>2.83967351913452</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G592" t="n">
-        <v>2.84243702888489</v>
+        <v>2.84243679046631</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>2.89494705200195</v>
+        <v>2.89494681358337</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G594" t="n">
-        <v>2.87836503982544</v>
+        <v>2.87836480140686</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G599" t="n">
-        <v>2.91014695167542</v>
+        <v>2.91014671325684</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>2.88527393341064</v>
+        <v>2.8852744102478</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G602" t="n">
-        <v>2.90047407150269</v>
+        <v>2.90047430992126</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G604" t="n">
-        <v>2.92120146751404</v>
+        <v>2.9212019443512</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>2.88803744316101</v>
+        <v>2.88803768157959</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G606" t="n">
-        <v>2.84796476364136</v>
+        <v>2.8479642868042</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G607" t="n">
-        <v>2.88112854957581</v>
+        <v>2.88112831115723</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G609" t="n">
-        <v>2.84520077705383</v>
+        <v>2.84520053863525</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G611" t="n">
-        <v>2.91152882575989</v>
+        <v>2.91152930259705</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G612" t="n">
-        <v>2.90323758125305</v>
+        <v>2.90323805809021</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>2.87421941757202</v>
+        <v>2.87421917915344</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G614" t="n">
-        <v>2.84520077705383</v>
+        <v>2.84520053863525</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G615" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G616" t="n">
-        <v>2.89080119132996</v>
+        <v>2.89080142974854</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G618" t="n">
-        <v>2.92120146751404</v>
+        <v>2.9212019443512</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G619" t="n">
-        <v>2.93087434768677</v>
+        <v>2.93087458610535</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G622" t="n">
-        <v>2.98338413238525</v>
+        <v>2.98338437080383</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G627" t="n">
-        <v>3.02898454666138</v>
+        <v>3.02898526191711</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G628" t="n">
-        <v>3.0096390247345</v>
+        <v>3.00963926315308</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G631" t="n">
-        <v>3.02898454666138</v>
+        <v>3.02898526191711</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G632" t="n">
-        <v>3.02898454666138</v>
+        <v>3.02898526191711</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G635" t="n">
-        <v>3.05109405517578</v>
+        <v>3.05109429359436</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G637" t="n">
-        <v>3.034512758255</v>
+        <v>3.03451251983643</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G641" t="n">
-        <v>3.08840370178223</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>3.08149480819702</v>
+        <v>3.0814950466156</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G644" t="n">
-        <v>3.09669470787048</v>
+        <v>3.09669518470764</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G645" t="n">
-        <v>3.13262248039246</v>
+        <v>3.13262271881104</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G648" t="n">
-        <v>3.04694867134094</v>
+        <v>3.04694890975952</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G649" t="n">
-        <v>3.09669470787048</v>
+        <v>3.09669518470764</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G651" t="n">
-        <v>3.10360455513</v>
+        <v>3.10360431671143</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G653" t="n">
-        <v>3.13262248039246</v>
+        <v>3.13262271881104</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G657" t="n">
-        <v>3.08840370178223</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G658" t="n">
-        <v>3.08840370178223</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>3.11189556121826</v>
+        <v>3.11189532279968</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13814949989319</v>
+        <v>3.13814997673035</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G664" t="n">
-        <v>3.12018609046936</v>
+        <v>3.12018585205078</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.5</v>
       </c>
       <c r="G665" t="n">
-        <v>3.10913157463074</v>
+        <v>3.10913133621216</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G666" t="n">
-        <v>3.10222244262695</v>
+        <v>3.10222220420837</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.10913157463074</v>
+        <v>3.10913133621216</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G668" t="n">
-        <v>3.10222244262695</v>
+        <v>3.10222220420837</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G669" t="n">
-        <v>3.26251530647278</v>
+        <v>3.26251554489136</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>3.34542512893677</v>
+        <v>3.34542536735535</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G673" t="n">
-        <v>3.36062598228455</v>
+        <v>3.36062574386597</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38411641120911</v>
+        <v>3.38411712646484</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G675" t="n">
-        <v>3.35924386978149</v>
+        <v>3.35924339294434</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>3.34542512893677</v>
+        <v>3.34542536735535</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G682" t="n">
-        <v>3.35648012161255</v>
+        <v>3.35647988319397</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G683" t="n">
-        <v>3.37858939170837</v>
+        <v>3.37858963012695</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G685" t="n">
-        <v>3.36615300178528</v>
+        <v>3.36615347862244</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G686" t="n">
-        <v>3.36615300178528</v>
+        <v>3.36615347862244</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G687" t="n">
-        <v>3.36615300178528</v>
+        <v>3.36615347862244</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G688" t="n">
-        <v>3.32469820976257</v>
+        <v>3.32469773292542</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G690" t="n">
-        <v>3.29015231132507</v>
+        <v>3.29015254974365</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31778883934021</v>
+        <v>3.31778836250305</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G692" t="n">
-        <v>3.31087923049927</v>
+        <v>3.31087970733643</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G693" t="n">
-        <v>3.35371685028076</v>
+        <v>3.35371613502502</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G694" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957098960876</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G695" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957098960876</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G696" t="n">
-        <v>3.33989787101746</v>
+        <v>3.33989810943604</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G698" t="n">
-        <v>3.3426616191864</v>
+        <v>3.34266209602356</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.32331609725952</v>
+        <v>3.32331562042236</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G700" t="n">
-        <v>3.31364345550537</v>
+        <v>3.31364321708679</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>3.37168025970459</v>
+        <v>3.37168049812317</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G702" t="n">
-        <v>3.36062598228455</v>
+        <v>3.36062574386597</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.37168025970459</v>
+        <v>3.37168049812317</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G704" t="n">
-        <v>3.35648012161255</v>
+        <v>3.35647988319397</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G705" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957098960876</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G706" t="n">
-        <v>3.38273501396179</v>
+        <v>3.38273477554321</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G707" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957098960876</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G708" t="n">
-        <v>3.34127950668335</v>
+        <v>3.34127974510193</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G710" t="n">
-        <v>3.32469820976257</v>
+        <v>3.32469773292542</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>3.38549900054932</v>
+        <v>3.38549852371216</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G714" t="n">
-        <v>3.37029838562012</v>
+        <v>3.37029814720154</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G716" t="n">
-        <v>3.4450786113739</v>
+        <v>3.44507884979248</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.80800008773804</v>
       </c>
       <c r="G717" t="n">
-        <v>3.46380972862244</v>
+        <v>3.46380996704102</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G718" t="n">
-        <v>3.46236944198608</v>
+        <v>3.4623692035675</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G719" t="n">
-        <v>3.46092796325684</v>
+        <v>3.46092820167542</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G720" t="n">
-        <v>3.48110008239746</v>
+        <v>3.48109984397888</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G722" t="n">
-        <v>3.45660543441772</v>
+        <v>3.4566056728363</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G723" t="n">
-        <v>3.48110008239746</v>
+        <v>3.48109984397888</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>3.49406743049622</v>
+        <v>3.49406766891479</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G725" t="n">
-        <v>3.553142786026</v>
+        <v>3.55314302444458</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G727" t="n">
-        <v>3.60069108009338</v>
+        <v>3.60069060325623</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5</v>
       </c>
       <c r="G728" t="n">
-        <v>3.60213160514832</v>
+        <v>3.60213136672974</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G729" t="n">
-        <v>3.67777633666992</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65976595878601</v>
+        <v>3.65976572036743</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659375190735</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G734" t="n">
-        <v>3.65256190299988</v>
+        <v>3.65256214141846</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G735" t="n">
-        <v>3.61293792724609</v>
+        <v>3.61293816566467</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G736" t="n">
-        <v>3.68137884140015</v>
+        <v>3.68137812614441</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>3.63094878196716</v>
+        <v>3.63094902038574</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>3.66336846351624</v>
+        <v>3.6633677482605</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G739" t="n">
-        <v>3.68498039245605</v>
+        <v>3.68498086929321</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>3.68858313560486</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G741" t="n">
-        <v>3.62374472618103</v>
+        <v>3.62374448776245</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G742" t="n">
-        <v>3.58484172821045</v>
+        <v>3.58484125137329</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.5444974899292</v>
+        <v>3.54449796676636</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G744" t="n">
-        <v>3.59492754936218</v>
+        <v>3.59492683410645</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>3.5444974899292</v>
+        <v>3.54449796676636</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G747" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573387145996</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G748" t="n">
-        <v>3.59924983978271</v>
+        <v>3.59925007820129</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G749" t="n">
-        <v>3.57619619369507</v>
+        <v>3.57619643211365</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G750" t="n">
-        <v>3.57763743400574</v>
+        <v>3.57763719558716</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G751" t="n">
-        <v>3.58051896095276</v>
+        <v>3.5805184841156</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G752" t="n">
-        <v>3.60933589935303</v>
+        <v>3.60933637619019</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G755" t="n">
-        <v>3.60069108009338</v>
+        <v>3.60069060325623</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G756" t="n">
-        <v>3.61293792724609</v>
+        <v>3.61293816566467</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60213160514832</v>
+        <v>3.60213136672974</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573387145996</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60069108009338</v>
+        <v>3.60069060325623</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G761" t="n">
-        <v>3.60069108009338</v>
+        <v>3.60069060325623</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G762" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573387145996</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57187366485596</v>
+        <v>3.57187414169312</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G764" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907772064209</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G765" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907772064209</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G766" t="n">
-        <v>3.57619619369507</v>
+        <v>3.57619643211365</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G768" t="n">
-        <v>3.62374472618103</v>
+        <v>3.62374448776245</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G769" t="n">
-        <v>3.60069108009338</v>
+        <v>3.60069060325623</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.56611013412476</v>
+        <v>3.56611084938049</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G771" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907772064209</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G772" t="n">
-        <v>3.67057275772095</v>
+        <v>3.67057204246521</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>3.71019554138184</v>
+        <v>3.71019577980042</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G775" t="n">
-        <v>3.6669704914093</v>
+        <v>3.66697025299072</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G776" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659375190735</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G777" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659375190735</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>3.67777633666992</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.74621725082397</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.72460389137268</v>
+        <v>3.72460436820984</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>3.76782989501953</v>
+        <v>3.76782917976379</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>3.75702404975891</v>
+        <v>3.75702357292175</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.71379828453064</v>
+        <v>3.71379804611206</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>3.71379828453064</v>
+        <v>3.71379804611206</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G785" t="n">
-        <v>3.77503395080566</v>
+        <v>3.77503347396851</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G786" t="n">
-        <v>3.7390124797821</v>
+        <v>3.73901343345642</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G787" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>3.72100210189819</v>
+        <v>3.72100186347961</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G790" t="n">
-        <v>3.68858313560486</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>3.72100210189819</v>
+        <v>3.72100186347961</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.71739983558655</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G794" t="n">
-        <v>3.67417430877686</v>
+        <v>3.67417407035828</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.64175510406494</v>
+        <v>3.64175486564636</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>3.71019554138184</v>
+        <v>3.71019577980042</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.68858313560486</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>3.67777633666992</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>3.67777633666992</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>3.6669704914093</v>
+        <v>3.66697025299072</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.67417430877686</v>
+        <v>3.67417407035828</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>3.69578766822815</v>
+        <v>3.69578719139099</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.67057275772095</v>
+        <v>3.67057204246521</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G808" t="n">
-        <v>3.67057275772095</v>
+        <v>3.67057204246521</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G811" t="n">
-        <v>3.71019554138184</v>
+        <v>3.71019577980042</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>3.68858313560486</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G815" t="n">
-        <v>3.74621725082397</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G816" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>3.74621725082397</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>3.74621725082397</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>3.74981951713562</v>
+        <v>3.74981927871704</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>3.75702404975891</v>
+        <v>3.75702357292175</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>3.7390124797821</v>
+        <v>3.73901343345642</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>3.76782989501953</v>
+        <v>3.76782917976379</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>3.72460389137268</v>
+        <v>3.72460436820984</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G826" t="n">
-        <v>3.68137884140015</v>
+        <v>3.68137812614441</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>3.72460389137268</v>
+        <v>3.72460436820984</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G830" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>3.72460389137268</v>
+        <v>3.72460436820984</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G832" t="n">
-        <v>3.76062560081482</v>
+        <v>3.7606258392334</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.78584027290344</v>
+        <v>3.7858407497406</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G834" t="n">
-        <v>3.79304432868958</v>
+        <v>3.79304456710815</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>3.82546377182007</v>
+        <v>3.82546424865723</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>3.77503395080566</v>
+        <v>3.77503347396851</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.78584027290344</v>
+        <v>3.7858407497406</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.77863621711731</v>
+        <v>3.77863597869873</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148500442505</v>
+        <v>3.86148476600647</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>5.375</v>
       </c>
       <c r="G844" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>5.25</v>
       </c>
       <c r="G847" t="n">
-        <v>3.78223848342896</v>
+        <v>3.78223824501038</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G849" t="n">
-        <v>3.78944301605225</v>
+        <v>3.78944253921509</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G850" t="n">
-        <v>3.86508750915527</v>
+        <v>3.86508727073669</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>3.82906556129456</v>
+        <v>3.82906579971313</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G852" t="n">
-        <v>3.89030265808105</v>
+        <v>3.89030194282532</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G853" t="n">
-        <v>3.87589406967163</v>
+        <v>3.87589383125305</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80024909973145</v>
+        <v>3.80024933815002</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80024909973145</v>
+        <v>3.80024933815002</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80024909973145</v>
+        <v>3.80024933815002</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.85067892074585</v>
+        <v>3.85067868232727</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>3.83626985549927</v>
+        <v>3.83627009391785</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>3.84707689285278</v>
+        <v>3.84707713127136</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G863" t="n">
-        <v>3.81105518341064</v>
+        <v>3.8110556602478</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>3.8578827381134</v>
+        <v>3.85788345336914</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.375</v>
       </c>
       <c r="G866" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>3.90831351280212</v>
+        <v>3.90831327438354</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.375</v>
       </c>
       <c r="G869" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.88309836387634</v>
+        <v>3.88309788703918</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91191482543945</v>
+        <v>3.91191506385803</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>3.83626985549927</v>
+        <v>3.83627009391785</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>3.80024909973145</v>
+        <v>3.80024933815002</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G876" t="n">
-        <v>3.91191482543945</v>
+        <v>3.91191506385803</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91191482543945</v>
+        <v>3.91191506385803</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G878" t="n">
-        <v>3.92632341384888</v>
+        <v>3.9263231754303</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G879" t="n">
-        <v>3.95874238014221</v>
+        <v>3.95874285697937</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99836659431458</v>
+        <v>3.998366355896</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97315144538879</v>
+        <v>3.97315192222595</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.625</v>
       </c>
       <c r="G883" t="n">
-        <v>4.05239772796631</v>
+        <v>4.05239820480347</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>4.07040929794312</v>
+        <v>4.07040882110596</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>4.08841896057129</v>
+        <v>4.08841943740845</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.16406440734863</v>
+        <v>4.16406393051147</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G892" t="n">
-        <v>4.1784725189209</v>
+        <v>4.17847299575806</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.21089172363281</v>
+        <v>4.21089220046997</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G895" t="n">
-        <v>4.25411796569824</v>
+        <v>4.2541184425354</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G896" t="n">
-        <v>4.27212762832642</v>
+        <v>4.27212810516357</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G899" t="n">
-        <v>4.31175184249878</v>
+        <v>4.31175136566162</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G903" t="n">
-        <v>4.3261604309082</v>
+        <v>4.32616090774536</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G904" t="n">
-        <v>4.35857963562012</v>
+        <v>4.35858011245728</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G905" t="n">
-        <v>4.39820241928101</v>
+        <v>4.39820289611816</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G907" t="n">
-        <v>4.39460039138794</v>
+        <v>4.3946008682251</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>4.35497760772705</v>
+        <v>4.35497713088989</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>4.11723709106445</v>
+        <v>4.11723661422729</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G911" t="n">
-        <v>4.14965629577637</v>
+        <v>4.14965581893921</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G914" t="n">
-        <v>3.71019554138184</v>
+        <v>3.71019577980042</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>3.77863621711731</v>
+        <v>3.77863597869873</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81825995445251</v>
+        <v>3.81825947761536</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.71739983558655</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G919" t="n">
-        <v>3.33413290977478</v>
+        <v>3.3341326713562</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G920" t="n">
-        <v>3.24624109268188</v>
+        <v>3.24624085426331</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G924" t="n">
-        <v>2.68863105773926</v>
+        <v>2.68863129615784</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G925" t="n">
-        <v>2.70448040962219</v>
+        <v>2.70448064804077</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.75</v>
       </c>
       <c r="G926" t="n">
-        <v>2.70159864425659</v>
+        <v>2.70159888267517</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G933" t="n">
-        <v>2.78949093818665</v>
+        <v>2.78949069976807</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G934" t="n">
-        <v>2.86873769760132</v>
+        <v>2.86873745918274</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G935" t="n">
-        <v>2.89035081863403</v>
+        <v>2.89035058021545</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>2.93933939933777</v>
+        <v>2.93933963775635</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G938" t="n">
-        <v>2.86873769760132</v>
+        <v>2.86873745918274</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G939" t="n">
-        <v>2.89035081863403</v>
+        <v>2.89035058021545</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96815633773804</v>
+        <v>2.96815657615662</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98976945877075</v>
+        <v>2.98976969718933</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>3.02579045295715</v>
+        <v>3.02579069137573</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G943" t="n">
-        <v>3.02579045295715</v>
+        <v>3.02579069137573</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G944" t="n">
-        <v>2.94798493385315</v>
+        <v>2.94798469543457</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>2.97536087036133</v>
+        <v>2.97536110877991</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G947" t="n">
-        <v>2.9494252204895</v>
+        <v>2.94942545890808</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G949" t="n">
-        <v>2.92349028587341</v>
+        <v>2.92348980903625</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G950" t="n">
-        <v>2.91772699356079</v>
+        <v>2.91772675514221</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9105224609375</v>
+        <v>2.91052222251892</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G952" t="n">
-        <v>2.90475940704346</v>
+        <v>2.90475916862488</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G954" t="n">
-        <v>2.94654393196106</v>
+        <v>2.94654417037964</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G955" t="n">
-        <v>2.94654393196106</v>
+        <v>2.94654417037964</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G957" t="n">
-        <v>2.85577011108398</v>
+        <v>2.85577034950256</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G958" t="n">
-        <v>2.84136152267456</v>
+        <v>2.84136176109314</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G959" t="n">
-        <v>2.79237246513367</v>
+        <v>2.79237270355225</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>2.79525423049927</v>
+        <v>2.79525446891785</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G964" t="n">
-        <v>2.75346946716309</v>
+        <v>2.75346970558167</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G970" t="n">
-        <v>2.99553251266479</v>
+        <v>2.99553275108337</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G971" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>3.11038947105408</v>
+        <v>3.1103892326355</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>3.09521675109863</v>
+        <v>3.09521698951721</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G976" t="n">
-        <v>3.0861132144928</v>
+        <v>3.08611345291138</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G977" t="n">
-        <v>3.26363325119019</v>
+        <v>3.26363301277161</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G979" t="n">
-        <v>3.4669463634491</v>
+        <v>3.46694612503052</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.33797907829285</v>
+        <v>3.33797931671143</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G982" t="n">
-        <v>3.24694323539734</v>
+        <v>3.24694347381592</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G983" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G986" t="n">
-        <v>3.12556219100952</v>
+        <v>3.12556195259094</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>3.13466548919678</v>
+        <v>3.13466572761536</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>3.10280346870422</v>
+        <v>3.1028037071228</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G993" t="n">
-        <v>3.01631951332092</v>
+        <v>3.01631903648376</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G997" t="n">
-        <v>3.04362988471985</v>
+        <v>3.04363012313843</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.17714929580688</v>
+        <v>3.17714953422546</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.04059529304504</v>
+        <v>3.04059553146362</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.80086803436279</v>
+        <v>2.80086779594421</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.72803926467896</v>
+        <v>2.72803902626038</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.69769406318665</v>
+        <v>2.69769430160522</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.63852071762085</v>
+        <v>2.63852047920227</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.62486529350281</v>
+        <v>2.62486505508423</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.61576175689697</v>
+        <v>2.61576151847839</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.64610695838928</v>
+        <v>2.64610719680786</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.74928092956543</v>
+        <v>2.74928069114685</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.75990176200867</v>
+        <v>2.75990200042725</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.73562526702881</v>
+        <v>2.73562550544739</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.76597094535828</v>
+        <v>2.7659707069397</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.87217926979065</v>
+        <v>2.87217903137207</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.89645528793335</v>
+        <v>2.89645576477051</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.77052235603333</v>
+        <v>2.7705225944519</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.73714303970337</v>
+        <v>2.73714280128479</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.77355694770813</v>
+        <v>2.77355718612671</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.72803926467896</v>
+        <v>2.72803902626038</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.71134924888611</v>
+        <v>2.71134948730469</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.73714303970337</v>
+        <v>2.73714280128479</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.732590675354</v>
+        <v>2.73259091377258</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.67493510246277</v>
+        <v>2.67493486404419</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.67190074920654</v>
+        <v>2.67190051078796</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.71893572807312</v>
+        <v>2.71893548965454</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G1050" t="n">
-        <v>2.70528030395508</v>
+        <v>2.70528054237366</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.66279721260071</v>
+        <v>2.66279697418213</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.72348761558533</v>
+        <v>2.72348737716675</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.7083146572113</v>
+        <v>2.70831513404846</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.72803926467896</v>
+        <v>2.72803902626038</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>3.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.65521025657654</v>
+        <v>2.6552107334137</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.55051946640015</v>
+        <v>2.55051922798157</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.46858692169189</v>
+        <v>2.46858739852905</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.45796608924866</v>
+        <v>2.45796632766724</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.38665509223938</v>
+        <v>2.3866548538208</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.47769069671631</v>
+        <v>2.47769093513489</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.43520736694336</v>
+        <v>2.43520712852478</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.46858692169189</v>
+        <v>2.46858739852905</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.40334486961365</v>
+        <v>2.40334510803223</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.45189738273621</v>
+        <v>2.45189762115479</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38513779640198</v>
+        <v>2.38513803482056</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.19851446151733</v>
+        <v>2.19851422309875</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.23796343803406</v>
+        <v>2.2379629611969</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.34265446662903</v>
+        <v>2.34265422821045</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.78569507598877</v>
+        <v>2.78569531440735</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.74321174621582</v>
+        <v>2.7432119846344</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.9768705368042</v>
+        <v>2.97687029838562</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.82666158676147</v>
+        <v>2.8266613483429</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.85245513916016</v>
+        <v>2.852454662323</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.8327305316925</v>
+        <v>2.83273029327393</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.80086803436279</v>
+        <v>2.80086779594421</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.8327305316925</v>
+        <v>2.83273029327393</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.81452322006226</v>
+        <v>2.81452298164368</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.67796945571899</v>
+        <v>2.67796921730042</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.62486529350281</v>
+        <v>2.62486505508423</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.7083146572113</v>
+        <v>2.70831513404846</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.72955656051636</v>
+        <v>2.72955632209778</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.72955656051636</v>
+        <v>2.72955632209778</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.732590675354</v>
+        <v>2.73259091377258</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.73866009712219</v>
+        <v>2.73865985870361</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.71134924888611</v>
+        <v>2.71134948730469</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.72045278549194</v>
+        <v>2.72045302391052</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.73714303970337</v>
+        <v>2.73714280128479</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.55051946640015</v>
+        <v>2.55051922798157</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.57631301879883</v>
+        <v>2.57631278038025</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.65369343757629</v>
+        <v>2.65369319915771</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.69465947151184</v>
+        <v>2.69465970993042</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.84486818313599</v>
+        <v>2.84486865997314</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.92528319358826</v>
+        <v>2.92528343200684</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.87976551055908</v>
+        <v>2.8797652721405</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.87521386146545</v>
+        <v>2.87521362304688</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.83728194236755</v>
+        <v>2.83728218078613</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.83728194236755</v>
+        <v>2.83728218078613</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.12101006507874</v>
+        <v>3.12101030349731</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.96624970436096</v>
+        <v>2.96624946594238</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.28032302856445</v>
+        <v>3.28032326698303</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.2863917350769</v>
+        <v>3.28639197349548</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.27577090263367</v>
+        <v>3.27577114105225</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.28335738182068</v>
+        <v>3.28335785865784</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.21204662322998</v>
+        <v>3.21204614639282</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.18321824073792</v>
+        <v>3.18321847915649</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.1741144657135</v>
+        <v>3.17411470413208</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.1710798740387</v>
+        <v>3.17108011245728</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.18321824073792</v>
+        <v>3.18321847915649</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.17714929580688</v>
+        <v>3.17714953422546</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.19232201576233</v>
+        <v>3.19232177734375</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.17259740829468</v>
+        <v>3.1725971698761</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.12556219100952</v>
+        <v>3.12556195259094</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.0861132144928</v>
+        <v>3.08611345291138</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.10735511779785</v>
+        <v>3.10735487937927</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.01935386657715</v>
+        <v>3.01935362815857</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.92224884033203</v>
+        <v>2.92224907875061</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.93135237693787</v>
+        <v>2.93135261535645</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.93590426445007</v>
+        <v>2.93590402603149</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.91921424865723</v>
+        <v>2.91921448707581</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.96776700019836</v>
+        <v>2.96776676177979</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.89645528793335</v>
+        <v>2.89645576477051</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.91011071205139</v>
+        <v>2.91011095046997</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.89645528793335</v>
+        <v>2.89645576477051</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.84638595581055</v>
+        <v>2.84638571739197</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.86459302902222</v>
+        <v>2.86459279060364</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.83728194236755</v>
+        <v>2.83728218078613</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.89797258377075</v>
+        <v>2.89797282218933</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.10280346870422</v>
+        <v>3.1028037071228</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.11038947105408</v>
+        <v>3.1103892326355</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.11190676689148</v>
+        <v>3.11190700531006</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.06790637969971</v>
+        <v>3.06790614128113</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.12101006507874</v>
+        <v>3.12101030349731</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.16197657585144</v>
+        <v>3.16197681427002</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.03756093978882</v>
+        <v>3.03756141662598</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.03149175643921</v>
+        <v>3.03149199485779</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.01935386657715</v>
+        <v>3.01935362815857</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.89645528793335</v>
+        <v>2.89645576477051</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.91011071205139</v>
+        <v>2.91011095046997</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.8509373664856</v>
+        <v>2.85093760490417</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.86155867576599</v>
+        <v>2.86155819892883</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.91011071205139</v>
+        <v>2.91011095046997</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.88583469390869</v>
+        <v>2.88583445549011</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.87673091888428</v>
+        <v>2.87673115730286</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.7932813167572</v>
+        <v>2.79328155517578</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.82969617843628</v>
+        <v>2.8296959400177</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.82362675666809</v>
+        <v>2.82362651824951</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.80238509178162</v>
+        <v>2.8023853302002</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.81755781173706</v>
+        <v>2.81755757331848</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.78721261024475</v>
+        <v>2.78721237182617</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.77355694770813</v>
+        <v>2.77355718612671</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.72803926467896</v>
+        <v>2.72803902626038</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.97231841087341</v>
+        <v>2.97231864929199</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.0633544921875</v>
+        <v>3.06335425376892</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.0466639995575</v>
+        <v>3.04666447639465</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.06790637969971</v>
+        <v>3.06790614128113</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>4</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.03452634811401</v>
+        <v>3.03452658653259</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.94349050521851</v>
+        <v>2.94349074363708</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.96624970436096</v>
+        <v>2.96624946594238</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.91011071205139</v>
+        <v>2.91011095046997</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.87521386146545</v>
+        <v>2.87521362304688</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.92073154449463</v>
+        <v>2.92073130607605</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.97383594512939</v>
+        <v>2.97383570671082</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.01631951332092</v>
+        <v>3.01631903648376</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.23783993721008</v>
+        <v>3.2378396987915</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.17259740829468</v>
+        <v>3.1725971698761</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.16349387168884</v>
+        <v>3.16349363327026</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.19687366485596</v>
+        <v>3.19687390327454</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.19990801811218</v>
+        <v>3.19990825653076</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.1270797252655</v>
+        <v>3.12707948684692</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.96321487426758</v>
+        <v>2.96321511268616</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.77810907363892</v>
+        <v>2.77810859680176</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.84638595581055</v>
+        <v>2.84638571739197</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1363" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.92073154449463</v>
+        <v>2.92073130607605</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1366" t="n">
-        <v>2.91921424865723</v>
+        <v>2.91921448707581</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1367" t="n">
-        <v>2.87673091888428</v>
+        <v>2.87673115730286</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1368" t="n">
-        <v>2.83728194236755</v>
+        <v>2.83728218078613</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1369" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.8919038772583</v>
+        <v>2.89190363883972</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.86155867576599</v>
+        <v>2.86155819892883</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>2.91314554214478</v>
+        <v>2.9131453037262</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.97231841087341</v>
+        <v>2.97231864929199</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.98142218589783</v>
+        <v>2.98142242431641</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.12101006507874</v>
+        <v>3.12101030349731</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.12556219100952</v>
+        <v>3.12556195259094</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.11038947105408</v>
+        <v>3.1103892326355</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.13618302345276</v>
+        <v>3.13618278503418</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.04362988471985</v>
+        <v>3.04363012313843</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.08307886123657</v>
+        <v>3.08307909965515</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.09976863861084</v>
+        <v>3.09976887702942</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.0648717880249</v>
+        <v>3.06487154960632</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.95259404182434</v>
+        <v>2.95259428024292</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.08156156539917</v>
+        <v>3.08156132698059</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.16197657585144</v>
+        <v>3.16197681427002</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1483211517334</v>
+        <v>3.14832139015198</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.1270797252655</v>
+        <v>3.12707948684692</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.07852721214294</v>
+        <v>3.07852673530579</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.11494112014771</v>
+        <v>3.11494135856628</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.10432076454163</v>
+        <v>3.10432052612305</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.10735511779785</v>
+        <v>3.10735487937927</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.11494112014771</v>
+        <v>3.11494135856628</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.00569820404053</v>
+        <v>3.00569844245911</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.01631951332092</v>
+        <v>3.01631903648376</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.78266048431396</v>
+        <v>2.78266096115112</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.91921424865723</v>
+        <v>2.91921448707581</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.9768705368042</v>
+        <v>2.97687029838562</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.01631951332092</v>
+        <v>3.01631903648376</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.03452634811401</v>
+        <v>3.03452658653259</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.11038947105408</v>
+        <v>3.1103892326355</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.13011407852173</v>
+        <v>3.13011384010315</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.21204662322998</v>
+        <v>3.21204614639282</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.24694323539734</v>
+        <v>3.24694347381592</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.24846053123474</v>
+        <v>3.24846076965332</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.22114968299866</v>
+        <v>3.22114944458008</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.27577090263367</v>
+        <v>3.27577114105225</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.35770344734192</v>
+        <v>3.3577036857605</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.55646514892578</v>
+        <v>3.5564649105072</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.36225533485413</v>
+        <v>3.36225509643555</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.36073756217957</v>
+        <v>3.36073780059814</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.37591052055359</v>
+        <v>3.37591028213501</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.33797907829285</v>
+        <v>3.33797931671143</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.34253120422363</v>
+        <v>3.34253072738647</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.31066823005676</v>
+        <v>3.31066799163818</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.37439346313477</v>
+        <v>3.37439322471619</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.26666808128357</v>
+        <v>3.26666784286499</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.25452947616577</v>
+        <v>3.25452971458435</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.30459904670715</v>
+        <v>3.30459928512573</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.23177099227905</v>
+        <v>3.23177075386047</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.23632192611694</v>
+        <v>3.2363224029541</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.26666808128357</v>
+        <v>3.26666784286499</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.2590811252594</v>
+        <v>3.25908088684082</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.30308222770691</v>
+        <v>3.30308198928833</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.2621157169342</v>
+        <v>3.26211595535278</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.95562887191772</v>
+        <v>2.95562863349915</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.09218239784241</v>
+        <v>3.09218263626099</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.05121636390686</v>
+        <v>3.05121612548828</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.07549262046814</v>
+        <v>3.07549238204956</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.07852721214294</v>
+        <v>3.07852673530579</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.97080135345459</v>
+        <v>2.97080111503601</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.026939868927</v>
+        <v>3.02694010734558</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.10280346870422</v>
+        <v>3.1028037071228</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.19990801811218</v>
+        <v>3.19990825653076</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.2332878112793</v>
+        <v>3.23328804969788</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.22114968299866</v>
+        <v>3.22114944458008</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.25756430625916</v>
+        <v>3.25756406784058</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.23177099227905</v>
+        <v>3.23177075386047</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.22266697883606</v>
+        <v>3.22266721725464</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.23783993721008</v>
+        <v>3.2378396987915</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.17866659164429</v>
+        <v>3.17866635322571</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.1710798740387</v>
+        <v>3.17108011245728</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.19232201576233</v>
+        <v>3.19232177734375</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.20749425888062</v>
+        <v>3.20749449729919</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11190676689148</v>
+        <v>3.11190700531006</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.12556219100952</v>
+        <v>3.12556195259094</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.04211330413818</v>
+        <v>3.04211282730103</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.1741144657135</v>
+        <v>3.17411470413208</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.13466548919678</v>
+        <v>3.13466572761536</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.03756093978882</v>
+        <v>3.03756141662598</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.83728194236755</v>
+        <v>2.83728218078613</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.83879947662354</v>
+        <v>2.83879971504211</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.83121299743652</v>
+        <v>2.8312132358551</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.79631590843201</v>
+        <v>2.79631614685059</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.73866009712219</v>
+        <v>2.73865985870361</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.83728194236755</v>
+        <v>2.83728218078613</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.84638595581055</v>
+        <v>2.84638571739197</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.91314554214478</v>
+        <v>2.9131453037262</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.78569507598877</v>
+        <v>2.78569531440735</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.75838446617126</v>
+        <v>2.75838422775269</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.77355694770813</v>
+        <v>2.77355718612671</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.79631590843201</v>
+        <v>2.79631614685059</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.82666158676147</v>
+        <v>2.8266613483429</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.7932813167572</v>
+        <v>2.79328155517578</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.94342255592346</v>
+        <v>2.94342279434204</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.00751185417175</v>
+        <v>3.00751209259033</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.01063823699951</v>
+        <v>3.01063847541809</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.05596995353699</v>
+        <v>3.05596971511841</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.05440640449524</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.96374368667603</v>
+        <v>2.9637439250946</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.982501745224</v>
+        <v>2.98250150680542</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.05596995353699</v>
+        <v>3.05596971511841</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.14194321632385</v>
+        <v>3.14194345474243</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.17164349555969</v>
+        <v>3.17164325714111</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.31545400619507</v>
+        <v>3.31545376777649</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.34671688079834</v>
+        <v>3.34671711921692</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.35609602928162</v>
+        <v>3.35609579086304</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.29044318199158</v>
+        <v>3.29044342041016</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.30763792991638</v>
+        <v>3.3076376914978</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.36078524589539</v>
+        <v>3.36078548431396</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>4.31400012969971</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.37172746658325</v>
+        <v>3.37172770500183</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.35765886306763</v>
+        <v>3.35765862464905</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>4.25</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.32170653343201</v>
+        <v>3.32170629501343</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.17476963996887</v>
+        <v>3.17476940155029</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.15601205825806</v>
+        <v>3.15601181983948</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.12943840026855</v>
+        <v>3.12943863868713</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.13256430625916</v>
+        <v>3.13256454467773</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.09817504882812</v>
+        <v>3.0981752872467</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.09504866600037</v>
+        <v>3.09504890441895</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.16851735115051</v>
+        <v>3.16851711273193</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.19509053230286</v>
+        <v>3.19509077072144</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.29044318199158</v>
+        <v>3.29044342041016</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.27481198310852</v>
+        <v>3.27481174468994</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.22635364532471</v>
+        <v>3.22635388374329</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1653" t="n">
-        <v>3.25918030738831</v>
+        <v>3.25918006896973</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.27012205123901</v>
+        <v>3.27012228965759</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.38423275947571</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>4.25</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.32170653343201</v>
+        <v>3.32170629501343</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.34359073638916</v>
+        <v>3.34359049797058</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>4.34600019454956</v>
       </c>
       <c r="G1662" t="n">
-        <v>3.39673781394958</v>
+        <v>3.39673805236816</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.40924310684204</v>
+        <v>3.40924286842346</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.37485337257385</v>
+        <v>3.37485361099243</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.38423275947571</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G1668" t="n">
-        <v>3.23729610443115</v>
+        <v>3.23729634284973</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1672" t="n">
-        <v>3.20446968078613</v>
+        <v>3.20446944236755</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1674" t="n">
-        <v>3.18571186065674</v>
+        <v>3.18571209907532</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.14663290977478</v>
+        <v>3.14663314819336</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.17945909500122</v>
+        <v>3.1794593334198</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.26543283462524</v>
+        <v>3.26543259620667</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.26543283462524</v>
+        <v>3.26543259620667</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.24511194229126</v>
+        <v>3.24511170387268</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.27481198310852</v>
+        <v>3.27481174468994</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.27324867248535</v>
+        <v>3.27324891090393</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.23729610443115</v>
+        <v>3.23729634284973</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.2247908115387</v>
+        <v>3.22479057312012</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.15757513046265</v>
+        <v>3.15757489204407</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.22635364532471</v>
+        <v>3.22635388374329</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.06378579139709</v>
+        <v>3.06378555297852</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.05440640449524</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.95280194282532</v>
+        <v>2.95280170440674</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.00125956535339</v>
+        <v>3.00125932693481</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G1705" t="n">
-        <v>3.02783298492432</v>
+        <v>3.0278332233429</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.00907516479492</v>
+        <v>3.00907492637634</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1713" t="n">
-        <v>3.20446968078613</v>
+        <v>3.20446944236755</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.24354863166809</v>
+        <v>3.24354887008667</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.27950119972229</v>
+        <v>3.27950143814087</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.28262734413147</v>
+        <v>3.28262758255005</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>4.25</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.32170653343201</v>
+        <v>3.32170629501343</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1726" t="n">
-        <v>3.24980092048645</v>
+        <v>3.24980115890503</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.22166466712952</v>
+        <v>3.22166442871094</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.17945909500122</v>
+        <v>3.1794593334198</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.1732063293457</v>
+        <v>3.17320656776428</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.17945909500122</v>
+        <v>3.1794593334198</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.20446968078613</v>
+        <v>3.20446944236755</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.21072220802307</v>
+        <v>3.21072196960449</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.18571186065674</v>
+        <v>3.18571209907532</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.15288519859314</v>
+        <v>3.15288543701172</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.11849594116211</v>
+        <v>3.11849617958069</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.13256430625916</v>
+        <v>3.13256454467773</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.17164349555969</v>
+        <v>3.17164325714111</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.09661173820496</v>
+        <v>3.09661197662354</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.09817504882812</v>
+        <v>3.0981752872467</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.15601205825806</v>
+        <v>3.15601181983948</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1756" t="n">
-        <v>3.13412809371948</v>
+        <v>3.1341278553009</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.07629084587097</v>
+        <v>3.07629108428955</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.05596995353699</v>
+        <v>3.05596971511841</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691193580627</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.05440640449524</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.9731228351593</v>
+        <v>2.97312259674072</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.07629084587097</v>
+        <v>3.07629108428955</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.04190135002136</v>
+        <v>3.04190158843994</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.03721213340759</v>
+        <v>3.03721189498901</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.06065940856934</v>
+        <v>3.06065917015076</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.00907516479492</v>
+        <v>3.00907492637634</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.88089632987976</v>
+        <v>2.88089656829834</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.84181761741638</v>
+        <v>2.8418173789978</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.84650683403015</v>
+        <v>2.84650707244873</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.90434408187866</v>
+        <v>2.90434384346008</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.82305955886841</v>
+        <v>2.82305979728699</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.80586504936218</v>
+        <v>2.8058648109436</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68393850326538</v>
+        <v>2.68393874168396</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70894956588745</v>
+        <v>2.70894932746887</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.65580201148987</v>
+        <v>2.65580177307129</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.65267610549927</v>
+        <v>2.65267586708069</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.64017033576965</v>
+        <v>2.64017057418823</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.65580201148987</v>
+        <v>2.65580177307129</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.55576014518738</v>
+        <v>2.5557599067688</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.6245391368866</v>
+        <v>2.62453889846802</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.57764434814453</v>
+        <v>2.57764410972595</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.50287127494812</v>
+        <v>2.50287103652954</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.53453207015991</v>
+        <v>2.53453230857849</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.61951661109924</v>
+        <v>2.61951637268066</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.77948665618896</v>
+        <v>2.77948689460754</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.69616889953613</v>
+        <v>2.69616913795471</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.74449324607849</v>
+        <v>2.74449348449707</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.84614133834839</v>
+        <v>2.84614109992981</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.86780405044556</v>
+        <v>2.86780381202698</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.86280512809753</v>
+        <v>2.86280488967896</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.80614876747131</v>
+        <v>2.80614852905273</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.82781147956848</v>
+        <v>2.8278112411499</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.84780740737915</v>
+        <v>2.84780764579773</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.79281783103943</v>
+        <v>2.79281759262085</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.78448605537415</v>
+        <v>2.78448581695557</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.84114241600037</v>
+        <v>2.84114217758179</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.76282334327698</v>
+        <v>2.7628231048584</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.7178316116333</v>
+        <v>2.71783185005188</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.72116422653198</v>
+        <v>2.72116446495056</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.7594907283783</v>
+        <v>2.75949048995972</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.74282693862915</v>
+        <v>2.74282717704773</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.12275695800781</v>
+        <v>3.12275671958923</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.1394202709198</v>
+        <v>3.13942050933838</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.23773574829102</v>
+        <v>3.23773550987244</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.28772664070129</v>
+        <v>3.28772640228271</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.22273850440979</v>
+        <v>3.22273826599121</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.17941308021545</v>
+        <v>3.17941284179688</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.11609125137329</v>
+        <v>3.11609148979187</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.10109424591064</v>
+        <v>3.10109400749207</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.12275695800781</v>
+        <v>3.12275671958923</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.16441583633423</v>
+        <v>3.16441607475281</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.24273467063904</v>
+        <v>3.24273490905762</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.24273467063904</v>
+        <v>3.24273490905762</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.34105014801025</v>
+        <v>3.34104990959167</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.36104607582092</v>
+        <v>3.3610463142395</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -67634,6 +67634,32 @@
         <v>4.94199991226196</v>
       </c>
       <c r="H2587" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2588" t="n">
+        <v>1197498</v>
+      </c>
+      <c r="C2588" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D2588" t="n">
+        <v>4.85799980163574</v>
+      </c>
+      <c r="E2588" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="F2588" t="n">
+        <v>4.85799980163574</v>
+      </c>
+      <c r="G2588" t="n">
+        <v>4.85799980163574</v>
+      </c>
+      <c r="H2588" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -59958,8 +59958,31 @@
       <c r="E2591" t="n">
         <v>4.90799999237061</v>
       </c>
-      <c r="F2591"/>
+      <c r="F2591" t="n">
+        <v>4.92999982833862</v>
+      </c>
       <c r="G2591" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2592" t="n">
+        <v>269290</v>
+      </c>
+      <c r="C2592" t="n">
+        <v>4.96400022506714</v>
+      </c>
+      <c r="D2592" t="n">
+        <v>4.91200017929077</v>
+      </c>
+      <c r="E2592" t="n">
+        <v>4.94000005722046</v>
+      </c>
+      <c r="F2592"/>
+      <c r="G2592" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -59981,8 +59981,31 @@
       <c r="E2592" t="n">
         <v>4.94000005722046</v>
       </c>
-      <c r="F2592"/>
+      <c r="F2592" t="n">
+        <v>4.92999982833862</v>
+      </c>
       <c r="G2592" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2593" t="n">
+        <v>409570</v>
+      </c>
+      <c r="C2593" t="n">
+        <v>4.94399976730347</v>
+      </c>
+      <c r="D2593" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="E2593" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="F2593"/>
+      <c r="G2593" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -60004,8 +60004,31 @@
       <c r="E2593" t="n">
         <v>4.92999982833862</v>
       </c>
-      <c r="F2593"/>
+      <c r="F2593" t="n">
+        <v>4.69999980926514</v>
+      </c>
       <c r="G2593" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2594" t="n">
+        <v>523746</v>
+      </c>
+      <c r="C2594" t="n">
+        <v>4.77799987792969</v>
+      </c>
+      <c r="D2594" t="n">
+        <v>4.69799995422363</v>
+      </c>
+      <c r="E2594" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="F2594"/>
+      <c r="G2594" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -60027,8 +60027,31 @@
       <c r="E2594" t="n">
         <v>4.69999980926514</v>
       </c>
-      <c r="F2594"/>
+      <c r="F2594" t="n">
+        <v>4.72800016403198</v>
+      </c>
       <c r="G2594" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>287181</v>
+      </c>
+      <c r="C2595" t="n">
+        <v>4.76800012588501</v>
+      </c>
+      <c r="D2595" t="n">
+        <v>4.66599988937378</v>
+      </c>
+      <c r="E2595" t="n">
+        <v>4.76599979400635</v>
+      </c>
+      <c r="F2595"/>
+      <c r="G2595" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -60057,6 +60057,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2596">
+      <c r="A2596" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2596" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C2596" t="n">
+        <v>4.78999996185303</v>
+      </c>
+      <c r="D2596" t="n">
+        <v>4.72599983215332</v>
+      </c>
+      <c r="E2596" t="n">
+        <v>4.73799991607666</v>
+      </c>
+      <c r="F2596" t="n">
+        <v>4.72599983215332</v>
+      </c>
+      <c r="G2596" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26321339607239</v>
+        <v>2.26321363449097</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24304056167603</v>
+        <v>2.24304032325745</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G6" t="n">
-        <v>2.30482149124146</v>
+        <v>2.30482125282288</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G12" t="n">
-        <v>2.31238627433777</v>
+        <v>2.31238603591919</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34895062446594</v>
+        <v>2.34895086288452</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G14" t="n">
-        <v>2.37921118736267</v>
+        <v>2.37921094894409</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26951766014099</v>
+        <v>2.26951789855957</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28590846061707</v>
+        <v>2.28590869903564</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.33508133888245</v>
+        <v>2.3350818157196</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877779006958</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G27" t="n">
-        <v>2.34516859054565</v>
+        <v>2.34516835212708</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877779006958</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G34" t="n">
-        <v>2.2884304523468</v>
+        <v>2.28843021392822</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25060510635376</v>
+        <v>2.25060486793518</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21782326698303</v>
+        <v>2.21782302856445</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G39" t="n">
-        <v>2.2052149772644</v>
+        <v>2.20521473884583</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.20647549629211</v>
+        <v>2.20647573471069</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.20647549629211</v>
+        <v>2.20647573471069</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G47" t="n">
-        <v>2.2253885269165</v>
+        <v>2.22538828849792</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.26951766014099</v>
+        <v>2.26951789855957</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26699614524841</v>
+        <v>2.26699590682983</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.23169255256653</v>
+        <v>2.23169231414795</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.21782326698303</v>
+        <v>2.21782302856445</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G54" t="n">
-        <v>2.18378067016602</v>
+        <v>2.18378043174744</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G55" t="n">
-        <v>2.19134545326233</v>
+        <v>2.19134569168091</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G56" t="n">
-        <v>2.21151924133301</v>
+        <v>2.21151876449585</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G57" t="n">
-        <v>2.17369341850281</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G58" t="n">
-        <v>2.16108512878418</v>
+        <v>2.16108536720276</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.20773673057556</v>
+        <v>2.20773649215698</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15478110313416</v>
+        <v>2.15478134155273</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G64" t="n">
-        <v>2.16991114616394</v>
+        <v>2.16991090774536</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343309402466</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.14973783493042</v>
+        <v>2.149738073349</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G69" t="n">
-        <v>2.14973783493042</v>
+        <v>2.149738073349</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G70" t="n">
-        <v>2.13965082168579</v>
+        <v>2.13965129852295</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G71" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343309402466</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>2.12326002120972</v>
+        <v>2.12325978279114</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>2.13082551956177</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.12452101707458</v>
+        <v>2.12452077865601</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.12452101707458</v>
+        <v>2.12452077865601</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.99465417861938</v>
+        <v>1.9946540594101</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195863723755</v>
+        <v>1.97195875644684</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93161189556122</v>
+        <v>1.93161165714264</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G81" t="n">
-        <v>1.93917679786682</v>
+        <v>1.93917644023895</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>1.92909014225006</v>
+        <v>1.92908978462219</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>1.92278587818146</v>
+        <v>1.92278575897217</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G84" t="n">
-        <v>1.948002576828</v>
+        <v>1.94800269603729</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>1.90387308597565</v>
+        <v>1.90387332439423</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.90387308597565</v>
+        <v>1.90387332439423</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>1.92782926559448</v>
+        <v>1.92782950401306</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G89" t="n">
-        <v>1.97321939468384</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G90" t="n">
-        <v>1.99339306354523</v>
+        <v>1.99339282512665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G92" t="n">
-        <v>2.01104474067688</v>
+        <v>2.01104497909546</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>1.95430719852448</v>
+        <v>1.9543069601059</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G96" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213254451752</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>1.97321939468384</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G98" t="n">
-        <v>1.91017735004425</v>
+        <v>1.91017746925354</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89126479625702</v>
+        <v>1.8912650346756</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G100" t="n">
-        <v>1.89504718780518</v>
+        <v>1.89504730701447</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G101" t="n">
-        <v>1.93917679786682</v>
+        <v>1.93917644023895</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G104" t="n">
-        <v>2.08921718597412</v>
+        <v>2.08921694755554</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G105" t="n">
-        <v>2.05643534660339</v>
+        <v>2.05643558502197</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G107" t="n">
-        <v>2.07030439376831</v>
+        <v>2.07030415534973</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>2.08669543266296</v>
+        <v>2.08669567108154</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G112" t="n">
-        <v>2.07913088798523</v>
+        <v>2.07913041114807</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G113" t="n">
-        <v>2.07030439376831</v>
+        <v>2.07030415534973</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G114" t="n">
-        <v>2.08417367935181</v>
+        <v>2.08417344093323</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343309402466</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G117" t="n">
-        <v>2.14469456672668</v>
+        <v>2.14469408988953</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343309402466</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.13082551956177</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.1560423374176</v>
+        <v>2.15604162216187</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>2.19008469581604</v>
+        <v>2.19008421897888</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G125" t="n">
-        <v>2.16991114616394</v>
+        <v>2.16991090774536</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.1560423374176</v>
+        <v>2.15604162216187</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G128" t="n">
-        <v>2.17369341850281</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15352034568787</v>
+        <v>2.15352010726929</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>2.13460731506348</v>
+        <v>2.13460755348206</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G133" t="n">
-        <v>2.0690438747406</v>
+        <v>2.06904363632202</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G134" t="n">
-        <v>2.04256629943848</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G135" t="n">
-        <v>2.04256629943848</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.04256629943848</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213254451752</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G140" t="n">
-        <v>1.97069799900055</v>
+        <v>1.97069811820984</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.02365350723267</v>
+        <v>2.02365326881409</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>2.01734900474548</v>
+        <v>2.01734924316406</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>2.05643534660339</v>
+        <v>2.05643558502197</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G144" t="n">
-        <v>2.07282638549805</v>
+        <v>2.07282662391663</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G145" t="n">
-        <v>2.06400012969971</v>
+        <v>2.06400036811829</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.13712906837463</v>
+        <v>2.13712954521179</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G148" t="n">
-        <v>2.14973783493042</v>
+        <v>2.149738073349</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>2.14343333244324</v>
+        <v>2.14343309402466</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G151" t="n">
-        <v>2.16486787796021</v>
+        <v>2.16486763954163</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G153" t="n">
-        <v>2.09552097320557</v>
+        <v>2.09552145004272</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>2.08669543266296</v>
+        <v>2.08669567108154</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.12326002120972</v>
+        <v>2.12325978279114</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G156" t="n">
-        <v>2.13712906837463</v>
+        <v>2.13712954521179</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G157" t="n">
-        <v>2.12452101707458</v>
+        <v>2.12452077865601</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.12452101707458</v>
+        <v>2.12452077865601</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>2.13082551956177</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G160" t="n">
-        <v>2.12704253196716</v>
+        <v>2.12704277038574</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G161" t="n">
-        <v>2.14469456672668</v>
+        <v>2.14469408988953</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G162" t="n">
-        <v>2.16234588623047</v>
+        <v>2.16234612464905</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G163" t="n">
-        <v>2.16108512878418</v>
+        <v>2.16108536720276</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G165" t="n">
-        <v>2.17621517181396</v>
+        <v>2.17621541023254</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>2.21277976036072</v>
+        <v>2.21277952194214</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.2884304523468</v>
+        <v>2.28843021392822</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>2.27582192420959</v>
+        <v>2.27582168579102</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35147261619568</v>
+        <v>2.35147285461426</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40190625190735</v>
+        <v>2.40190649032593</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G175" t="n">
-        <v>2.35399436950684</v>
+        <v>2.35399413108826</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877779006958</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G177" t="n">
-        <v>2.34012460708618</v>
+        <v>2.34012484550476</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G178" t="n">
-        <v>2.4031674861908</v>
+        <v>2.40316724777222</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.32247304916382</v>
+        <v>2.3224732875824</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G182" t="n">
-        <v>2.37038493156433</v>
+        <v>2.37038564682007</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G185" t="n">
-        <v>2.37164640426636</v>
+        <v>2.3716459274292</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G186" t="n">
-        <v>2.41703677177429</v>
+        <v>2.41703653335571</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G189" t="n">
-        <v>2.36534190177917</v>
+        <v>2.3653416633606</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.35777711868286</v>
+        <v>2.35777688026428</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G196" t="n">
-        <v>2.37038493156433</v>
+        <v>2.37038564682007</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G197" t="n">
-        <v>2.39308023452759</v>
+        <v>2.39308047294617</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>2.42964482307434</v>
+        <v>2.42964506149292</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.45234036445618</v>
+        <v>2.4523401260376</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G204" t="n">
-        <v>2.43090581893921</v>
+        <v>2.43090558052063</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.4586443901062</v>
+        <v>2.45864462852478</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G210" t="n">
-        <v>2.37038493156433</v>
+        <v>2.37038564682007</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G212" t="n">
-        <v>2.39816331863403</v>
+        <v>2.39816308021545</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G213" t="n">
-        <v>2.46826934814453</v>
+        <v>2.46826958656311</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>2.50001573562622</v>
+        <v>2.5000159740448</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694684028625</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.50001573562622</v>
+        <v>2.5000159740448</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G223" t="n">
-        <v>2.46562385559082</v>
+        <v>2.46562361717224</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G224" t="n">
-        <v>2.49737000465393</v>
+        <v>2.49737024307251</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G225" t="n">
-        <v>2.52250242233276</v>
+        <v>2.52250218391418</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G228" t="n">
-        <v>2.5132429599762</v>
+        <v>2.51324319839478</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694684028625</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356033325195</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694684028625</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694684028625</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46562385559082</v>
+        <v>2.46562361717224</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G251" t="n">
-        <v>2.43387770652771</v>
+        <v>2.43387746810913</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>2.45371890068054</v>
+        <v>2.45371913909912</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356033325195</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G259" t="n">
-        <v>2.50927472114563</v>
+        <v>2.50927495956421</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G263" t="n">
-        <v>2.57144474983215</v>
+        <v>2.57144451141357</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G264" t="n">
-        <v>2.56218504905701</v>
+        <v>2.56218528747559</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G266" t="n">
-        <v>2.56615376472473</v>
+        <v>2.56615352630615</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.55954003334045</v>
+        <v>2.55953979492188</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G269" t="n">
-        <v>2.54498958587646</v>
+        <v>2.54498934745789</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>2.53308439254761</v>
+        <v>2.53308463096619</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G272" t="n">
-        <v>2.5132429599762</v>
+        <v>2.51324319839478</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G273" t="n">
-        <v>2.50001573562622</v>
+        <v>2.5000159740448</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356033325195</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356033325195</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.48678779602051</v>
+        <v>2.48678827285767</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G280" t="n">
-        <v>2.44842791557312</v>
+        <v>2.44842767715454</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G281" t="n">
-        <v>2.42858672142029</v>
+        <v>2.42858648300171</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G282" t="n">
-        <v>2.43784594535828</v>
+        <v>2.43784618377686</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G283" t="n">
-        <v>2.45900988578796</v>
+        <v>2.45901012420654</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G284" t="n">
-        <v>2.47752857208252</v>
+        <v>2.4775288105011</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G286" t="n">
-        <v>2.46430087089539</v>
+        <v>2.46430110931396</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>2.43652319908142</v>
+        <v>2.43652296066284</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G288" t="n">
-        <v>2.49869322776794</v>
+        <v>2.49869275093079</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G290" t="n">
-        <v>2.55954003334045</v>
+        <v>2.55953979492188</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G292" t="n">
-        <v>2.53573036193848</v>
+        <v>2.5357301235199</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G293" t="n">
-        <v>2.53440737724304</v>
+        <v>2.53440761566162</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G296" t="n">
-        <v>2.5410213470459</v>
+        <v>2.54102110862732</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53308439254761</v>
+        <v>2.53308463096619</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G301" t="n">
-        <v>2.53573036193848</v>
+        <v>2.5357301235199</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G306" t="n">
-        <v>2.59922289848328</v>
+        <v>2.5992226600647</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G307" t="n">
-        <v>2.60583639144897</v>
+        <v>2.60583662986755</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60583639144897</v>
+        <v>2.60583662986755</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.57276725769043</v>
+        <v>2.57276749610901</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G310" t="n">
-        <v>2.58334970474243</v>
+        <v>2.58334922790527</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G311" t="n">
-        <v>2.59128570556641</v>
+        <v>2.59128618240356</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G312" t="n">
-        <v>2.58864092826843</v>
+        <v>2.58864045143127</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G319" t="n">
-        <v>2.67594265937805</v>
+        <v>2.67594218254089</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G320" t="n">
-        <v>2.6971070766449</v>
+        <v>2.69710683822632</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>2.67858815193176</v>
+        <v>2.67858839035034</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G325" t="n">
-        <v>2.70504355430603</v>
+        <v>2.70504331588745</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G326" t="n">
-        <v>2.70504355430603</v>
+        <v>2.70504331588745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>2.70504355430603</v>
+        <v>2.70504331588745</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G332" t="n">
-        <v>2.70107483863831</v>
+        <v>2.70107507705688</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G333" t="n">
-        <v>2.70107483863831</v>
+        <v>2.70107507705688</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>2.67197418212891</v>
+        <v>2.67197442054749</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.74472641944885</v>
+        <v>2.74472618103027</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G337" t="n">
-        <v>2.78837704658508</v>
+        <v>2.78837728500366</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.85054707527161</v>
+        <v>2.85054731369019</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G341" t="n">
-        <v>2.9034571647644</v>
+        <v>2.90345740318298</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G342" t="n">
-        <v>2.90742540359497</v>
+        <v>2.90742564201355</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>2.94578576087952</v>
+        <v>2.94578552246094</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G345" t="n">
-        <v>2.94843125343323</v>
+        <v>2.94843101501465</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G346" t="n">
-        <v>2.97356295585632</v>
+        <v>2.97356367111206</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>2.99340510368347</v>
+        <v>2.99340486526489</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G353" t="n">
-        <v>3.03176522254944</v>
+        <v>3.03176498413086</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G354" t="n">
-        <v>3.1058394908905</v>
+        <v>3.10583972930908</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G357" t="n">
-        <v>2.99605059623718</v>
+        <v>2.99605083465576</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>3.04234719276428</v>
+        <v>3.0423469543457</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>3.02911949157715</v>
+        <v>3.02911925315857</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>2.98943662643433</v>
+        <v>2.98943710327148</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>2.99869585037231</v>
+        <v>2.99869608879089</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G370" t="n">
-        <v>2.97356295585632</v>
+        <v>2.97356367111206</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G372" t="n">
-        <v>3.04896116256714</v>
+        <v>3.04896092414856</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G373" t="n">
-        <v>3.02250599861145</v>
+        <v>3.02250552177429</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>2.94314002990723</v>
+        <v>2.94314026832581</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G375" t="n">
-        <v>2.85054707527161</v>
+        <v>2.85054731369019</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.87700200080872</v>
+        <v>2.87700176239014</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G377" t="n">
-        <v>2.84922432899475</v>
+        <v>2.84922385215759</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G378" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G379" t="n">
-        <v>2.86509704589844</v>
+        <v>2.86509680747986</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>2.84393334388733</v>
+        <v>2.84393310546875</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85980606079102</v>
+        <v>2.85980629920959</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G382" t="n">
-        <v>2.85451507568359</v>
+        <v>2.85451531410217</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G385" t="n">
-        <v>2.84922432899475</v>
+        <v>2.84922385215759</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.87700200080872</v>
+        <v>2.87700176239014</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.84525585174561</v>
+        <v>2.84525609016418</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.79763698577881</v>
+        <v>2.79763674736023</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705430030823</v>
+        <v>2.78705453872681</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80689549446106</v>
+        <v>2.80689597129822</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>2.80689549446106</v>
+        <v>2.80689597129822</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>2.71165680885315</v>
+        <v>2.71165704727173</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>2.75398540496826</v>
+        <v>2.75398564338684</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G399" t="n">
-        <v>2.75266265869141</v>
+        <v>2.75266289710999</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.7592761516571</v>
+        <v>2.75927686691284</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G402" t="n">
-        <v>2.75663137435913</v>
+        <v>2.75663113594055</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G403" t="n">
-        <v>2.76456713676453</v>
+        <v>2.76456761360168</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G404" t="n">
-        <v>2.72885298728943</v>
+        <v>2.72885322570801</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G405" t="n">
-        <v>2.72885298728943</v>
+        <v>2.72885322570801</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74472641944885</v>
+        <v>2.74472618103027</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73943519592285</v>
+        <v>2.73943543434143</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G413" t="n">
-        <v>2.76324486732483</v>
+        <v>2.76324462890625</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>2.7592761516571</v>
+        <v>2.75927686691284</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G415" t="n">
-        <v>2.78044080734253</v>
+        <v>2.78044056892395</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G417" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G419" t="n">
-        <v>2.87303400039673</v>
+        <v>2.87303328514099</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>2.91007113456726</v>
+        <v>2.91007089614868</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G423" t="n">
-        <v>2.89287543296814</v>
+        <v>2.89287519454956</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G425" t="n">
-        <v>2.79631423950195</v>
+        <v>2.79631400108337</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G427" t="n">
-        <v>2.79234576225281</v>
+        <v>2.79234528541565</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G428" t="n">
-        <v>2.83335089683533</v>
+        <v>2.83335113525391</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86642050743103</v>
+        <v>2.86642003059387</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G431" t="n">
-        <v>2.86642050743103</v>
+        <v>2.86642003059387</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.85054707527161</v>
+        <v>2.85054731369019</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G435" t="n">
-        <v>2.90610313415527</v>
+        <v>2.90610289573669</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G436" t="n">
-        <v>2.93123531341553</v>
+        <v>2.93123579025269</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G438" t="n">
-        <v>2.97885489463806</v>
+        <v>2.9788544178009</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.93652629852295</v>
+        <v>2.93652653694153</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520355224609</v>
+        <v>2.93520331382751</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>2.95636749267578</v>
+        <v>2.95636773109436</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>2.95636749267578</v>
+        <v>2.95636773109436</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G449" t="n">
-        <v>2.99075937271118</v>
+        <v>2.99075961112976</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G451" t="n">
-        <v>3.01721477508545</v>
+        <v>3.01721453666687</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G452" t="n">
-        <v>2.97885489463806</v>
+        <v>2.9788544178009</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>2.99605059623718</v>
+        <v>2.99605083465576</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G459" t="n">
-        <v>2.98943662643433</v>
+        <v>2.98943710327148</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G460" t="n">
-        <v>3.01589179039001</v>
+        <v>3.01589131355286</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94710850715637</v>
+        <v>2.94710803031921</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G462" t="n">
-        <v>2.89684391021729</v>
+        <v>2.89684367179871</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88361597061157</v>
+        <v>2.88361644744873</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G467" t="n">
-        <v>2.90876531600952</v>
+        <v>2.90876507759094</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G468" t="n">
-        <v>2.88112878799438</v>
+        <v>2.88112854957581</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>2.75676321983337</v>
+        <v>2.75676369667053</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G473" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454677581787</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G474" t="n">
-        <v>2.88251042366028</v>
+        <v>2.88251066207886</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G475" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454677581787</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G486" t="n">
-        <v>3.01240277290344</v>
+        <v>3.01240348815918</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G487" t="n">
-        <v>2.99029350280762</v>
+        <v>2.9902937412262</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931214332581</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.97371101379395</v>
+        <v>2.9737114906311</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97785687446594</v>
+        <v>2.9778573513031</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>2.95989298820496</v>
+        <v>2.95989322662354</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G493" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818399429321</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G494" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818399429321</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G495" t="n">
-        <v>2.99029350280762</v>
+        <v>2.9902937412262</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G496" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818399429321</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G502" t="n">
-        <v>2.95851135253906</v>
+        <v>2.95851111412048</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G503" t="n">
-        <v>3.01793050765991</v>
+        <v>3.01793026924133</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G504" t="n">
-        <v>3.0317485332489</v>
+        <v>3.03174877166748</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G505" t="n">
-        <v>3.05109429359436</v>
+        <v>3.05109405517578</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>3.1049861907959</v>
+        <v>3.10498571395874</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G507" t="n">
-        <v>3.11051344871521</v>
+        <v>3.11051297187805</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G509" t="n">
-        <v>3.08840346336365</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G510" t="n">
-        <v>3.07182216644287</v>
+        <v>3.07182192802429</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>3.04556703567505</v>
+        <v>3.04556679725647</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>3.05385780334473</v>
+        <v>3.05385828018188</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>3.04556703567505</v>
+        <v>3.04556679725647</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G514" t="n">
-        <v>3.05109429359436</v>
+        <v>3.05109405517578</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G518" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G519" t="n">
-        <v>3.00963926315308</v>
+        <v>3.00963950157166</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931214332581</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G524" t="n">
-        <v>2.99305701255798</v>
+        <v>2.9930567741394</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G525" t="n">
-        <v>2.99582099914551</v>
+        <v>2.99582076072693</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G527" t="n">
-        <v>2.91843771934509</v>
+        <v>2.91843843460083</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G529" t="n">
-        <v>2.91981983184814</v>
+        <v>2.91981959342957</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94331121444702</v>
+        <v>2.94331097602844</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G534" t="n">
-        <v>2.87283754348755</v>
+        <v>2.87283778190613</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94607496261597</v>
+        <v>2.94607448577881</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G538" t="n">
-        <v>2.94607496261597</v>
+        <v>2.94607448577881</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>2.94331121444702</v>
+        <v>2.94331097602844</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.9281108379364</v>
+        <v>2.92811107635498</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G542" t="n">
-        <v>2.95989298820496</v>
+        <v>2.95989322662354</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97371101379395</v>
+        <v>2.9737114906311</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06491279602051</v>
+        <v>3.06491231918335</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G548" t="n">
-        <v>3.0013484954834</v>
+        <v>3.00134778022766</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G549" t="n">
-        <v>3.01240277290344</v>
+        <v>3.01240348815918</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G550" t="n">
-        <v>2.97232961654663</v>
+        <v>2.97232985496521</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G551" t="n">
-        <v>2.91291046142578</v>
+        <v>2.91291093826294</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>2.95712947845459</v>
+        <v>2.95712971687317</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G555" t="n">
-        <v>2.95298409461975</v>
+        <v>2.95298457145691</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G557" t="n">
-        <v>2.90047430992126</v>
+        <v>2.90047407150269</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G558" t="n">
-        <v>2.89632844924927</v>
+        <v>2.89632868766785</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>2.84658265113831</v>
+        <v>2.84658241271973</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G563" t="n">
-        <v>2.76090884208679</v>
+        <v>2.76090860366821</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76367211341858</v>
+        <v>2.76367235183716</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G568" t="n">
-        <v>2.71530842781067</v>
+        <v>2.71530818939209</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G573" t="n">
-        <v>2.76505398750305</v>
+        <v>2.76505422592163</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>2.74985408782959</v>
+        <v>2.74985384941101</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G575" t="n">
-        <v>2.71669006347656</v>
+        <v>2.71668982505798</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>2.73603582382202</v>
+        <v>2.73603558540344</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G580" t="n">
-        <v>2.75123596191406</v>
+        <v>2.75123572349548</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74985408782959</v>
+        <v>2.74985384941101</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>2.72221732139587</v>
+        <v>2.72221755981445</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G587" t="n">
-        <v>2.75814509391785</v>
+        <v>2.75814485549927</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G588" t="n">
-        <v>2.73050856590271</v>
+        <v>2.73050832748413</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G591" t="n">
-        <v>2.83967328071594</v>
+        <v>2.83967351913452</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G595" t="n">
-        <v>2.83552813529968</v>
+        <v>2.83552765846252</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G596" t="n">
-        <v>2.86040091514587</v>
+        <v>2.86040043830872</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G597" t="n">
-        <v>2.88389182090759</v>
+        <v>2.88389205932617</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>2.94331121444702</v>
+        <v>2.94331097602844</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G599" t="n">
-        <v>2.91014695167542</v>
+        <v>2.91014671325684</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G600" t="n">
-        <v>2.89909219741821</v>
+        <v>2.89909267425537</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>2.88527417182922</v>
+        <v>2.88527393341064</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G602" t="n">
-        <v>2.90047430992126</v>
+        <v>2.90047407150269</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.90876531600952</v>
+        <v>2.90876507759094</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>2.88803744316101</v>
+        <v>2.88803768157959</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G607" t="n">
-        <v>2.88112878799438</v>
+        <v>2.88112854957581</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G608" t="n">
-        <v>2.8590190410614</v>
+        <v>2.85901927947998</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>2.87421917915344</v>
+        <v>2.87421941757202</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G615" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454677581787</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G617" t="n">
-        <v>2.89632844924927</v>
+        <v>2.89632868766785</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G620" t="n">
-        <v>2.89909219741821</v>
+        <v>2.89909267425537</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G623" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931214332581</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G627" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G628" t="n">
-        <v>3.00963926315308</v>
+        <v>3.00963950157166</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G629" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G630" t="n">
-        <v>3.01240277290344</v>
+        <v>3.01240348815918</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G631" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G632" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G633" t="n">
-        <v>3.03313040733337</v>
+        <v>3.03313064575195</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G635" t="n">
-        <v>3.05109429359436</v>
+        <v>3.05109405517578</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G637" t="n">
-        <v>3.03451204299927</v>
+        <v>3.03451251983643</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G638" t="n">
-        <v>3.02483940124512</v>
+        <v>3.02483916282654</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>3.08287644386292</v>
+        <v>3.08287668228149</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G641" t="n">
-        <v>3.08840346336365</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>3.08149480819702</v>
+        <v>3.0814950466156</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G644" t="n">
-        <v>3.09669518470764</v>
+        <v>3.09669494628906</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G645" t="n">
-        <v>3.13262248039246</v>
+        <v>3.13262271881104</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G647" t="n">
-        <v>3.06629467010498</v>
+        <v>3.0662944316864</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G648" t="n">
-        <v>3.04694843292236</v>
+        <v>3.0469491481781</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G649" t="n">
-        <v>3.09669518470764</v>
+        <v>3.09669494628906</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12294936180115</v>
+        <v>3.12295031547546</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G651" t="n">
-        <v>3.10360407829285</v>
+        <v>3.10360455513</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G653" t="n">
-        <v>3.13262248039246</v>
+        <v>3.13262271881104</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G654" t="n">
-        <v>3.12294936180115</v>
+        <v>3.12295031547546</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G657" t="n">
-        <v>3.08840346336365</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G658" t="n">
-        <v>3.08840346336365</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>3.1049861907959</v>
+        <v>3.10498571395874</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>3.11189532279968</v>
+        <v>3.1118950843811</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>3.12294936180115</v>
+        <v>3.12295031547546</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13814997673035</v>
+        <v>3.13815021514893</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.55399990081787</v>
       </c>
       <c r="G663" t="n">
-        <v>3.14644050598145</v>
+        <v>3.14644122123718</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.5</v>
       </c>
       <c r="G665" t="n">
-        <v>3.10913109779358</v>
+        <v>3.10913181304932</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G666" t="n">
-        <v>3.10222220420837</v>
+        <v>3.10222196578979</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.10913109779358</v>
+        <v>3.10913181304932</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G668" t="n">
-        <v>3.10222220420837</v>
+        <v>3.10222196578979</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G669" t="n">
-        <v>3.26251554489136</v>
+        <v>3.26251578330994</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G670" t="n">
-        <v>3.31226181983948</v>
+        <v>3.3122615814209</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>3.34542536735535</v>
+        <v>3.34542512893677</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G673" t="n">
-        <v>3.36062550544739</v>
+        <v>3.36062526702881</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38411664962769</v>
+        <v>3.38411688804626</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>3.34542536735535</v>
+        <v>3.34542512893677</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G681" t="n">
-        <v>3.31502485275269</v>
+        <v>3.31502509117126</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G682" t="n">
-        <v>3.35647964477539</v>
+        <v>3.35648036003113</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G684" t="n">
-        <v>3.37444400787354</v>
+        <v>3.37444424629211</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G685" t="n">
-        <v>3.3661527633667</v>
+        <v>3.36615300178528</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G686" t="n">
-        <v>3.3661527633667</v>
+        <v>3.36615300178528</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G687" t="n">
-        <v>3.3661527633667</v>
+        <v>3.36615300178528</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G693" t="n">
-        <v>3.35371613502502</v>
+        <v>3.35371661186218</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G694" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G695" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G696" t="n">
-        <v>3.33989810943604</v>
+        <v>3.33989834785461</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G698" t="n">
-        <v>3.34266185760498</v>
+        <v>3.3426616191864</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.32331585884094</v>
+        <v>3.32331609725952</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>3.37168025970459</v>
+        <v>3.37168049812317</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G702" t="n">
-        <v>3.36062550544739</v>
+        <v>3.36062526702881</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.37168025970459</v>
+        <v>3.37168049812317</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G704" t="n">
-        <v>3.35647964477539</v>
+        <v>3.35648036003113</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G705" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G706" t="n">
-        <v>3.38273501396179</v>
+        <v>3.38273525238037</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G707" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G708" t="n">
-        <v>3.34127998352051</v>
+        <v>3.34128022193909</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G709" t="n">
-        <v>3.33437132835388</v>
+        <v>3.3343710899353</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>3.38549900054932</v>
+        <v>3.38549876213074</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G713" t="n">
-        <v>3.3620080947876</v>
+        <v>3.36200785636902</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G716" t="n">
-        <v>3.44507884979248</v>
+        <v>3.44507908821106</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.80800008773804</v>
       </c>
       <c r="G717" t="n">
-        <v>3.46380972862244</v>
+        <v>3.46380996704102</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G718" t="n">
-        <v>3.46236944198608</v>
+        <v>3.4623692035675</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G719" t="n">
-        <v>3.46092796325684</v>
+        <v>3.46092820167542</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>3.46957278251648</v>
+        <v>3.46957325935364</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G722" t="n">
-        <v>3.4566056728363</v>
+        <v>3.45660543441772</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G725" t="n">
-        <v>3.553142786026</v>
+        <v>3.55314302444458</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G726" t="n">
-        <v>3.57475543022156</v>
+        <v>3.57475566864014</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G727" t="n">
-        <v>3.60069131851196</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5</v>
       </c>
       <c r="G728" t="n">
-        <v>3.60213160514832</v>
+        <v>3.60213136672974</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G729" t="n">
-        <v>3.6777765750885</v>
+        <v>3.67777609825134</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.125</v>
       </c>
       <c r="G730" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65976619720459</v>
+        <v>3.65976572036743</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>3.63455080986023</v>
+        <v>3.63455057144165</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659375190735</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G734" t="n">
-        <v>3.65256118774414</v>
+        <v>3.65256190299988</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G736" t="n">
-        <v>3.68137860298157</v>
+        <v>3.68137907981873</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G741" t="n">
-        <v>3.62374472618103</v>
+        <v>3.62374496459961</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G742" t="n">
-        <v>3.58484125137329</v>
+        <v>3.58484148979187</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.5444974899292</v>
+        <v>3.54449772834778</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G744" t="n">
-        <v>3.59492754936218</v>
+        <v>3.59492707252502</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G745" t="n">
-        <v>3.52288484573364</v>
+        <v>3.52288508415222</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>3.5444974899292</v>
+        <v>3.54449772834778</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G748" t="n">
-        <v>3.59924983978271</v>
+        <v>3.59925007820129</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G749" t="n">
-        <v>3.57619667053223</v>
+        <v>3.57619643211365</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G751" t="n">
-        <v>3.58051872253418</v>
+        <v>3.58051896095276</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G752" t="n">
-        <v>3.60933613777161</v>
+        <v>3.60933589935303</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.62014222145081</v>
+        <v>3.62014269828796</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G754" t="n">
-        <v>3.59780955314636</v>
+        <v>3.59780931472778</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G755" t="n">
-        <v>3.60069131851196</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>3.61654019355774</v>
+        <v>3.61654043197632</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5</v>
       </c>
       <c r="G758" t="n">
-        <v>3.60213160514832</v>
+        <v>3.60213136672974</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60069131851196</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G761" t="n">
-        <v>3.60069131851196</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G764" t="n">
-        <v>3.57907843589783</v>
+        <v>3.57907819747925</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G765" t="n">
-        <v>3.57907843589783</v>
+        <v>3.57907819747925</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G766" t="n">
-        <v>3.57619667053223</v>
+        <v>3.57619643211365</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G768" t="n">
-        <v>3.62374472618103</v>
+        <v>3.62374496459961</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G769" t="n">
-        <v>3.60069131851196</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.56611013412476</v>
+        <v>3.56611061096191</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G771" t="n">
-        <v>3.57907843589783</v>
+        <v>3.57907819747925</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G772" t="n">
-        <v>3.67057228088379</v>
+        <v>3.67057180404663</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>3.71019554138184</v>
+        <v>3.71019601821899</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>3.61654019355774</v>
+        <v>3.61654043197632</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G775" t="n">
-        <v>3.66697025299072</v>
+        <v>3.66697001457214</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G776" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659375190735</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G777" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659375190735</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>3.6777765750885</v>
+        <v>3.67777609825134</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.72460412979126</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>3.76783037185669</v>
+        <v>3.76782989501953</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>3.75702357292175</v>
+        <v>3.75702333450317</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.71379780769348</v>
+        <v>3.71379828453064</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>3.71379780769348</v>
+        <v>3.71379828453064</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G785" t="n">
-        <v>3.77503323554993</v>
+        <v>3.77503395080566</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G786" t="n">
-        <v>3.73901295661926</v>
+        <v>3.7390124797821</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G787" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G788" t="n">
-        <v>3.70299172401428</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>3.72100234031677</v>
+        <v>3.72100186347961</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>3.72100234031677</v>
+        <v>3.72100186347961</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.71740031242371</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G793" t="n">
-        <v>3.70299172401428</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G794" t="n">
-        <v>3.67417454719543</v>
+        <v>3.67417430877686</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.64175510406494</v>
+        <v>3.64175486564636</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>3.62014222145081</v>
+        <v>3.62014269828796</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>3.71019554138184</v>
+        <v>3.71019601821899</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>3.6777765750885</v>
+        <v>3.67777609825134</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.125</v>
       </c>
       <c r="G800" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>5.125</v>
       </c>
       <c r="G801" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>3.6777765750885</v>
+        <v>3.67777609825134</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>3.66697025299072</v>
+        <v>3.66697001457214</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.67417454719543</v>
+        <v>3.67417430877686</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.67057228088379</v>
+        <v>3.67057180404663</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>5.125</v>
       </c>
       <c r="G807" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G808" t="n">
-        <v>3.67057228088379</v>
+        <v>3.67057180404663</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.73541069030762</v>
+        <v>3.73541045188904</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G811" t="n">
-        <v>3.71019554138184</v>
+        <v>3.71019601821899</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G815" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G816" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342178344727</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>3.74981927871704</v>
+        <v>3.74981904029846</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>3.75702357292175</v>
+        <v>3.75702333450317</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>3.73901295661926</v>
+        <v>3.7390124797821</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>3.76783037185669</v>
+        <v>3.76782989501953</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>3.72460412979126</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342178344727</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G826" t="n">
-        <v>3.68137860298157</v>
+        <v>3.68137907981873</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G827" t="n">
-        <v>3.69938921928406</v>
+        <v>3.69938945770264</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G828" t="n">
-        <v>3.70299172401428</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>3.72460412979126</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G830" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>3.72460412979126</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G832" t="n">
-        <v>3.76062512397766</v>
+        <v>3.76062536239624</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.78584027290344</v>
+        <v>3.7858407497406</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G834" t="n">
-        <v>3.79304480552673</v>
+        <v>3.79304432868958</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>3.82546424865723</v>
+        <v>3.82546377182007</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342178344727</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>3.77503323554993</v>
+        <v>3.77503395080566</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.78584027290344</v>
+        <v>3.7858407497406</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.77863669395447</v>
+        <v>3.77863621711731</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148595809937</v>
+        <v>3.86148524284363</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>5.375</v>
       </c>
       <c r="G844" t="n">
-        <v>3.87229156494141</v>
+        <v>3.87229180335999</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.82186102867126</v>
+        <v>3.82186222076416</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>5.25</v>
       </c>
       <c r="G847" t="n">
-        <v>3.78223872184753</v>
+        <v>3.78223824501038</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G849" t="n">
-        <v>3.78944253921509</v>
+        <v>3.78944277763367</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G850" t="n">
-        <v>3.86508679389954</v>
+        <v>3.86508727073669</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>3.82906603813171</v>
+        <v>3.82906627655029</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G853" t="n">
-        <v>3.87589383125305</v>
+        <v>3.87589359283447</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80024933815002</v>
+        <v>3.80024886131287</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80024933815002</v>
+        <v>3.80024886131287</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G857" t="n">
-        <v>3.80385088920593</v>
+        <v>3.80385136604309</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80024933815002</v>
+        <v>3.80024886131287</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.85067892074585</v>
+        <v>3.85067820549011</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>3.83627009391785</v>
+        <v>3.83627033233643</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>3.85788321495056</v>
+        <v>3.8578827381134</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.375</v>
       </c>
       <c r="G866" t="n">
-        <v>3.87229156494141</v>
+        <v>3.87229180335999</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>3.90831279754639</v>
+        <v>3.90831303596497</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.375</v>
       </c>
       <c r="G869" t="n">
-        <v>3.87229156494141</v>
+        <v>3.87229180335999</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.88309788703918</v>
+        <v>3.88309764862061</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>3.83627009391785</v>
+        <v>3.83627033233643</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>3.80024933815002</v>
+        <v>3.80024886131287</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G878" t="n">
-        <v>3.92632341384888</v>
+        <v>3.9263231754303</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G879" t="n">
-        <v>3.95874238014221</v>
+        <v>3.95874261856079</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99836659431458</v>
+        <v>3.998366355896</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97315073013306</v>
+        <v>3.97315096855164</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>4.01997900009155</v>
+        <v>4.01997947692871</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.625</v>
       </c>
       <c r="G883" t="n">
-        <v>4.05239868164062</v>
+        <v>4.05239820480347</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G885" t="n">
-        <v>4.06680631637573</v>
+        <v>4.06680679321289</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>4.08841943740845</v>
+        <v>4.08841991424561</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18567752838135</v>
+        <v>4.18567705154419</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>4.24691343307495</v>
+        <v>4.24691295623779</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G895" t="n">
-        <v>4.25411748886108</v>
+        <v>4.25411796569824</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>4.29013872146606</v>
+        <v>4.29013919830322</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G898" t="n">
-        <v>4.31895589828491</v>
+        <v>4.31895542144775</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G904" t="n">
-        <v>4.35858011245728</v>
+        <v>4.35857963562012</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G905" t="n">
-        <v>4.39820241928101</v>
+        <v>4.39820337295532</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G906" t="n">
-        <v>4.42702007293701</v>
+        <v>4.42701959609985</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>4.35497665405273</v>
+        <v>4.35497760772705</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>4.18567752838135</v>
+        <v>4.18567705154419</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>4.11723661422729</v>
+        <v>4.11723613739014</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.89750576019287</v>
+        <v>3.89750719070435</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G914" t="n">
-        <v>3.71019554138184</v>
+        <v>3.71019601821899</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>3.77863669395447</v>
+        <v>3.77863621711731</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81825947761536</v>
+        <v>3.81826019287109</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.71740031242371</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G918" t="n">
-        <v>3.61654019355774</v>
+        <v>3.61654043197632</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G919" t="n">
-        <v>3.3341326713562</v>
+        <v>3.33413314819336</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G920" t="n">
-        <v>3.24624133110046</v>
+        <v>3.24624109268188</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.5</v>
       </c>
       <c r="G921" t="n">
-        <v>3.24191832542419</v>
+        <v>3.24191904067993</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G923" t="n">
-        <v>2.86585593223572</v>
+        <v>2.86585569381714</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G925" t="n">
-        <v>2.70448017120361</v>
+        <v>2.70448040962219</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G928" t="n">
-        <v>2.52437376976013</v>
+        <v>2.52437400817871</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G931" t="n">
-        <v>2.61082530021667</v>
+        <v>2.6108250617981</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G933" t="n">
-        <v>2.78949093818665</v>
+        <v>2.78949069976807</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G934" t="n">
-        <v>2.86873769760132</v>
+        <v>2.8687379360199</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G935" t="n">
-        <v>2.89035034179688</v>
+        <v>2.89035081863403</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G936" t="n">
-        <v>2.83127546310425</v>
+        <v>2.83127570152283</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>2.93933963775635</v>
+        <v>2.93933916091919</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G938" t="n">
-        <v>2.86873769760132</v>
+        <v>2.8687379360199</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G939" t="n">
-        <v>2.89035034179688</v>
+        <v>2.89035081863403</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98976945877075</v>
+        <v>2.98976922035217</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>3.02579045295715</v>
+        <v>3.02579069137573</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G943" t="n">
-        <v>3.02579045295715</v>
+        <v>3.02579069137573</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G947" t="n">
-        <v>2.9494252204895</v>
+        <v>2.94942545890808</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G948" t="n">
-        <v>2.85432934761047</v>
+        <v>2.85432910919189</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G949" t="n">
-        <v>2.92349052429199</v>
+        <v>2.92349028587341</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G950" t="n">
-        <v>2.91772699356079</v>
+        <v>2.91772675514221</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9105224609375</v>
+        <v>2.91052222251892</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G953" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G954" t="n">
-        <v>2.94654417037964</v>
+        <v>2.94654393196106</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G955" t="n">
-        <v>2.94654417037964</v>
+        <v>2.94654393196106</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G957" t="n">
-        <v>2.85577011108398</v>
+        <v>2.85576987266541</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G959" t="n">
-        <v>2.79237270355225</v>
+        <v>2.79237246513367</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G960" t="n">
-        <v>2.85432934761047</v>
+        <v>2.85432910919189</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>2.79525423049927</v>
+        <v>2.79525446891785</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G963" t="n">
-        <v>2.78228664398193</v>
+        <v>2.78228640556335</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>2.85288834571838</v>
+        <v>2.8528881072998</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G967" t="n">
-        <v>2.9523069858551</v>
+        <v>2.95230746269226</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G968" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>3.09521698951721</v>
+        <v>3.09521675109863</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G979" t="n">
-        <v>3.4669463634491</v>
+        <v>3.46694660186768</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.33797931671143</v>
+        <v>3.33797883987427</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G983" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G987" t="n">
-        <v>3.15287327766418</v>
+        <v>3.15287303924561</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>3.13466572761536</v>
+        <v>3.13466548919678</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G990" t="n">
-        <v>3.06031966209412</v>
+        <v>3.0603199005127</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>3.1028037071228</v>
+        <v>3.10280346870422</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G995" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G996" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G997" t="n">
-        <v>3.04362988471985</v>
+        <v>3.04363012313843</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G998" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.80086755752563</v>
+        <v>2.80086779594421</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.69769382476807</v>
+        <v>2.69769406318665</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.67038297653198</v>
+        <v>2.67038321495056</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.63852047920227</v>
+        <v>2.63852071762085</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.62486529350281</v>
+        <v>2.62486553192139</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.61424446105957</v>
+        <v>2.61424469947815</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.61576151847839</v>
+        <v>2.61576175689697</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.64610695838928</v>
+        <v>2.6461067199707</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.86914491653442</v>
+        <v>2.86914467811584</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.83424782752991</v>
+        <v>2.83424758911133</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.77052235603333</v>
+        <v>2.7705225944519</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.67038297653198</v>
+        <v>2.67038321495056</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.69314241409302</v>
+        <v>2.69314217567444</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.67190051078796</v>
+        <v>2.67190027236938</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.74624609947205</v>
+        <v>2.74624633789062</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.66279673576355</v>
+        <v>2.66279697418213</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.5717613697052</v>
+        <v>2.57176113128662</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.5717613697052</v>
+        <v>2.57176113128662</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.51258778572083</v>
+        <v>2.5125880241394</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.45644903182983</v>
+        <v>2.45644927024841</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.45796656608582</v>
+        <v>2.45796632766724</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.38665509223938</v>
+        <v>2.3866548538208</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.36844801902771</v>
+        <v>2.36844778060913</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.41093134880066</v>
+        <v>2.41093111038208</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.44734525680542</v>
+        <v>2.447345495224</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.40637946128845</v>
+        <v>2.40637969970703</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.40334510803223</v>
+        <v>2.40334486961365</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38513803482056</v>
+        <v>2.38513779640198</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.39120674133301</v>
+        <v>2.39120697975159</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.31382656097412</v>
+        <v>2.31382632255554</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.24858403205872</v>
+        <v>2.24858427047729</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.3244469165802</v>
+        <v>2.32444715499878</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.37603425979614</v>
+        <v>2.37603402137756</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.34113693237305</v>
+        <v>2.34113717079163</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.74017763137817</v>
+        <v>2.74017715454102</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.82514381408691</v>
+        <v>2.82514405250549</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.8327305316925</v>
+        <v>2.83273029327393</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.77962636947632</v>
+        <v>2.77962613105774</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.80086755752563</v>
+        <v>2.80086779594421</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.82059240341187</v>
+        <v>2.82059216499329</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.8281786441803</v>
+        <v>2.82817888259888</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.8327305316925</v>
+        <v>2.83273029327393</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.81452322006226</v>
+        <v>2.81452345848083</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.47199988365173</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.63396883010864</v>
+        <v>2.63396859169006</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.62486529350281</v>
+        <v>2.62486553192139</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.72955632209778</v>
+        <v>2.72955656051636</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.72955632209778</v>
+        <v>2.72955656051636</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.72045278549194</v>
+        <v>2.72045302391052</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.58693385124207</v>
+        <v>2.58693361282349</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.57631278038025</v>
+        <v>2.57631301879883</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.65065884590149</v>
+        <v>2.65065860748291</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.65672779083252</v>
+        <v>2.6567280292511</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.76141929626465</v>
+        <v>2.76141905784607</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.78417801856995</v>
+        <v>2.78417778015137</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.84183406829834</v>
+        <v>2.84183430671692</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.86914491653442</v>
+        <v>2.86914467811584</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.84486865997314</v>
+        <v>2.84486842155457</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.90100717544556</v>
+        <v>2.90100693702698</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.8281786441803</v>
+        <v>2.82817888259888</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.87976574897766</v>
+        <v>2.87976551055908</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.87521362304688</v>
+        <v>2.87521386146545</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.12101030349731</v>
+        <v>3.12101006507874</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.06031966209412</v>
+        <v>3.0603199005127</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.93742156028748</v>
+        <v>2.9374213218689</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.3000476360321</v>
+        <v>3.30004739761353</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.28335762023926</v>
+        <v>3.28335785865784</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.14680361747742</v>
+        <v>3.146803855896</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.20142531394958</v>
+        <v>3.20142507553101</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.19232201576233</v>
+        <v>3.19232177734375</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.17259740829468</v>
+        <v>3.1725971698761</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.00873303413391</v>
+        <v>3.00873279571533</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.02542281150818</v>
+        <v>3.02542304992676</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.92831826210022</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.95107698440552</v>
+        <v>2.95107674598694</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.92224884033203</v>
+        <v>2.92224907875061</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.93135237693787</v>
+        <v>2.93135261535645</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.93590426445007</v>
+        <v>2.93590450286865</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.94500756263733</v>
+        <v>2.94500780105591</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.92831826210022</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.90100717544556</v>
+        <v>2.90100693702698</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.86459302902222</v>
+        <v>2.8645932674408</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.82059240341187</v>
+        <v>2.82059216499329</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.06638884544373</v>
+        <v>3.0663890838623</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.1028037071228</v>
+        <v>3.10280346870422</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.07094073295593</v>
+        <v>3.07094049453735</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.11190700531006</v>
+        <v>3.11190676689148</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.12101030349731</v>
+        <v>3.12101006507874</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.16197681427002</v>
+        <v>3.16197657585144</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.03756093978882</v>
+        <v>3.0375611782074</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.03149199485779</v>
+        <v>3.03149175643921</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.90707612037659</v>
+        <v>2.90707635879517</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.92831826210022</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066173553467</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.89493799209595</v>
+        <v>2.89493823051453</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.8509373664856</v>
+        <v>2.85093760490417</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.77659153938293</v>
+        <v>2.77659177780151</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.78417801856995</v>
+        <v>2.78417778015137</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.86155843734741</v>
+        <v>2.86155819892883</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066173553467</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.90100717544556</v>
+        <v>2.90100693702698</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.92831826210022</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.93742156028748</v>
+        <v>2.9374213218689</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.88431739807129</v>
+        <v>2.88431715965271</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066173553467</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066173553467</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.88431739807129</v>
+        <v>2.88431715965271</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.77659153938293</v>
+        <v>2.77659177780151</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.74624609947205</v>
+        <v>2.74624633789062</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.87824821472168</v>
+        <v>2.87824845314026</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.92831826210022</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.97231841087341</v>
+        <v>2.97231864929199</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.07094073295593</v>
+        <v>3.07094049453735</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.07094073295593</v>
+        <v>3.07094049453735</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.04666447639465</v>
+        <v>3.04666423797607</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480221748352</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.03907823562622</v>
+        <v>3.0390784740448</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.99962949752808</v>
+        <v>2.9996292591095</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.87521362304688</v>
+        <v>2.87521386146545</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.92073130607605</v>
+        <v>2.92073154449463</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.15287327766418</v>
+        <v>3.15287303924561</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.2378396987915</v>
+        <v>3.23783946037292</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.21356320381165</v>
+        <v>3.21356344223022</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.17259740829468</v>
+        <v>3.1725971698761</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.19990825653076</v>
+        <v>3.19990801811218</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.12707996368408</v>
+        <v>3.1270797252655</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.99659466743469</v>
+        <v>2.99659490585327</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.95107698440552</v>
+        <v>2.95107674598694</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.94652509689331</v>
+        <v>2.94652533531189</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.76141929626465</v>
+        <v>2.76141905784607</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.77810859680176</v>
+        <v>2.77810883522034</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>2.83424782752991</v>
+        <v>2.83424758911133</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.92073130607605</v>
+        <v>2.92073154449463</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1369" t="n">
-        <v>2.86914491653442</v>
+        <v>2.86914467811584</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.84942007064819</v>
+        <v>2.84942030906677</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G1373" t="n">
-        <v>2.85852384567261</v>
+        <v>2.85852360725403</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.86155843734741</v>
+        <v>2.86155819892883</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1378" t="n">
-        <v>2.95107698440552</v>
+        <v>2.95107674598694</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.97231841087341</v>
+        <v>2.97231864929199</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.98142218589783</v>
+        <v>2.98142194747925</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.06031966209412</v>
+        <v>3.0603199005127</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.12101030349731</v>
+        <v>3.12101006507874</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13163089752197</v>
+        <v>3.13163113594055</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.15287327766418</v>
+        <v>3.15287303924561</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.14680361747742</v>
+        <v>3.146803855896</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.14680361747742</v>
+        <v>3.146803855896</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.11797571182251</v>
+        <v>3.11797595024109</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.04362988471985</v>
+        <v>3.04363012313843</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.0845959186554</v>
+        <v>3.08459615707397</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.07094073295593</v>
+        <v>3.07094049453735</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.15590715408325</v>
+        <v>3.15590739250183</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.06487154960632</v>
+        <v>3.0648717880249</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.9525945186615</v>
+        <v>2.95259428024292</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.15590715408325</v>
+        <v>3.15590739250183</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.23935699462891</v>
+        <v>3.23935723304749</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.08156132698059</v>
+        <v>3.08156108856201</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.16197681427002</v>
+        <v>3.16197657585144</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1483211517334</v>
+        <v>3.14832091331482</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.12707996368408</v>
+        <v>3.1270797252655</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.11494135856628</v>
+        <v>3.11494159698486</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.11494135856628</v>
+        <v>3.11494159698486</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.00569844245911</v>
+        <v>3.00569820404053</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.92831826210022</v>
+        <v>2.92831802368164</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.94500756263733</v>
+        <v>2.94500780105591</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480221748352</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576777458191</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576777458191</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.13011384010315</v>
+        <v>3.13011360168457</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.24846053123474</v>
+        <v>3.24846029281616</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.22114968299866</v>
+        <v>3.22114944458008</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.40929055213928</v>
+        <v>3.40929007530212</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.5564649105072</v>
+        <v>3.55646514892578</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.41991138458252</v>
+        <v>3.41991090774536</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.36225533485413</v>
+        <v>3.36225557327271</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.36073803901672</v>
+        <v>3.36073780059814</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.37591052055359</v>
+        <v>3.37591075897217</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.33797931671143</v>
+        <v>3.33797883987427</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.3243236541748</v>
+        <v>3.32432389259338</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.34253072738647</v>
+        <v>3.34253096580505</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.31066799163818</v>
+        <v>3.31066846847534</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.37439346313477</v>
+        <v>3.37439322471619</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.35466885566711</v>
+        <v>3.35466861724854</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.25</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.22418451309204</v>
+        <v>3.22418403625488</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.29094362258911</v>
+        <v>3.29094386100769</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.15742468833923</v>
+        <v>3.15742492675781</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.21356320381165</v>
+        <v>3.21356344223022</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.21356320381165</v>
+        <v>3.21356344223022</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.23177075386047</v>
+        <v>3.23177051544189</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.23935699462891</v>
+        <v>3.23935723304749</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.23632216453552</v>
+        <v>3.2363224029541</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.3000476360321</v>
+        <v>3.30004739761353</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.25908136367798</v>
+        <v>3.2590811252594</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.25149512290955</v>
+        <v>3.25149488449097</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.30308222770691</v>
+        <v>3.30308198928833</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.06638884544373</v>
+        <v>3.0663890838623</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576777458191</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.09218239784241</v>
+        <v>3.09218263626099</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.07549238204956</v>
+        <v>3.07549262046814</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.13314843177795</v>
+        <v>3.13314867019653</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.1225278377533</v>
+        <v>3.12252759933472</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.02542281150818</v>
+        <v>3.02542304992676</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.97080111503601</v>
+        <v>2.97080135345459</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480221748352</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.03907823562622</v>
+        <v>3.0390784740448</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.1028037071228</v>
+        <v>3.10280346870422</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.11797571182251</v>
+        <v>3.11797595024109</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.19990825653076</v>
+        <v>3.19990801811218</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.23480534553528</v>
+        <v>3.23480486869812</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.22114968299866</v>
+        <v>3.22114944458008</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.25756454467773</v>
+        <v>3.25756430625916</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.23177075386047</v>
+        <v>3.23177051544189</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.23935699462891</v>
+        <v>3.23935723304749</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.2378396987915</v>
+        <v>3.23783946037292</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.17866635322571</v>
+        <v>3.17866659164429</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.19232201576233</v>
+        <v>3.19232177734375</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.20749449729919</v>
+        <v>3.20749425888062</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.15287327766418</v>
+        <v>3.15287303924561</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11190700531006</v>
+        <v>3.11190676689148</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.13163089752197</v>
+        <v>3.13163113594055</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.11797571182251</v>
+        <v>3.11797595024109</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.05425119400024</v>
+        <v>3.05425095558167</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.17563199996948</v>
+        <v>3.1756317615509</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.13466572761536</v>
+        <v>3.13466548919678</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.03756093978882</v>
+        <v>3.0375611782074</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.76141929626465</v>
+        <v>2.76141905784607</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.94342279434204</v>
+        <v>2.94342255592346</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.9996964931488</v>
+        <v>2.99969625473022</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.01063823699951</v>
+        <v>3.01063847541809</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.02626991271973</v>
+        <v>3.02626967430115</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.98250150680542</v>
+        <v>2.982501745224</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05753302574158</v>
+        <v>3.05753326416016</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.31545400619507</v>
+        <v>3.31545424461365</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.29825901985168</v>
+        <v>3.29825878143311</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.34671688079834</v>
+        <v>3.34671664237976</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.3560962677002</v>
+        <v>3.35609602928162</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.30451202392578</v>
+        <v>3.3045117855072</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.33264875411987</v>
+        <v>3.33264827728271</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.35765910148621</v>
+        <v>3.35765886306763</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.2873170375824</v>
+        <v>3.28731679916382</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.30138516426086</v>
+        <v>3.30138564109802</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>4.25</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.32170653343201</v>
+        <v>3.32170605659485</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.31389045715332</v>
+        <v>3.31389021873474</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.31701707839966</v>
+        <v>3.31701683998108</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.27793765068054</v>
+        <v>3.27793788909912</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.17476963996887</v>
+        <v>3.17476940155029</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.14819622039795</v>
+        <v>3.14819598197937</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.12943816184998</v>
+        <v>3.12943840026855</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.16851711273193</v>
+        <v>3.16851735115051</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.27481174468994</v>
+        <v>3.27481198310852</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.25761723518372</v>
+        <v>3.25761699676514</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.31701707839966</v>
+        <v>3.31701683998108</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.27168560028076</v>
+        <v>3.27168536186218</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.2873170375824</v>
+        <v>3.28731679916382</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.22635364532471</v>
+        <v>3.22635388374329</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.33890104293823</v>
+        <v>3.33890080451965</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.38423228263855</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>4.25</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.32170653343201</v>
+        <v>3.32170605659485</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.31389045715332</v>
+        <v>3.31389021873474</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.30451202392578</v>
+        <v>3.3045117855072</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.343590259552</v>
+        <v>3.34359073638916</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>4.34600019454956</v>
       </c>
       <c r="G1662" t="n">
-        <v>3.39673781394958</v>
+        <v>3.39673829078674</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.40924310684204</v>
+        <v>3.40924286842346</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.38423228263855</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G1668" t="n">
-        <v>3.23729586601257</v>
+        <v>3.23729634284973</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1669" t="n">
-        <v>3.25761723518372</v>
+        <v>3.25761699676514</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1673" t="n">
-        <v>3.19196462631226</v>
+        <v>3.19196438789368</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1674" t="n">
-        <v>3.18571186065674</v>
+        <v>3.18571209907532</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.14663314819336</v>
+        <v>3.14663290977478</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.20915913581848</v>
+        <v>3.20915937423706</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.22791695594788</v>
+        <v>3.22791719436646</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.27168560028076</v>
+        <v>3.27168536186218</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.27481174468994</v>
+        <v>3.27481198310852</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.23729586601257</v>
+        <v>3.23729634284973</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.2247908115387</v>
+        <v>3.22479057312012</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.15757489204407</v>
+        <v>3.15757513046265</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.22635364532471</v>
+        <v>3.22635388374329</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.08410668373108</v>
+        <v>3.08410692214966</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.9559280872345</v>
+        <v>2.95592784881592</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92779111862183</v>
+        <v>2.92779135704041</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.00907492637634</v>
+        <v>3.00907516479492</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.13100147247314</v>
+        <v>3.13100171089172</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.21697521209717</v>
+        <v>3.21697497367859</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.21228551864624</v>
+        <v>3.21228575706482</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.21228551864624</v>
+        <v>3.21228575706482</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.24354863166809</v>
+        <v>3.24354839324951</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.28262734413147</v>
+        <v>3.28262758255005</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>4.25</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.32170653343201</v>
+        <v>3.32170605659485</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.21541166305542</v>
+        <v>3.21541142463684</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.22791695594788</v>
+        <v>3.22791719436646</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1726" t="n">
-        <v>3.24980115890503</v>
+        <v>3.24980139732361</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.2216649055481</v>
+        <v>3.22166466712952</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.13569092750549</v>
+        <v>3.13569116592407</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.18571186065674</v>
+        <v>3.18571209907532</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.19196462631226</v>
+        <v>3.19196438789368</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.15288519859314</v>
+        <v>3.15288543701172</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.16382789611816</v>
+        <v>3.16382765769958</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08723282814026</v>
+        <v>3.08723306655884</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.12318587303162</v>
+        <v>3.12318563461304</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.09661197662354</v>
+        <v>3.09661173820496</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.11693286895752</v>
+        <v>3.1169331073761</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1754" t="n">
-        <v>3.15913796424866</v>
+        <v>3.15913820266724</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.05753302574158</v>
+        <v>3.05753326416016</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.03564882278442</v>
+        <v>3.035649061203</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.04346466064453</v>
+        <v>3.04346489906311</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.06222224235535</v>
+        <v>3.06222248077393</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.02626991271973</v>
+        <v>3.02626967430115</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.04033851623535</v>
+        <v>3.04033827781677</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.02001738548279</v>
+        <v>3.02001762390137</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.04190158843994</v>
+        <v>3.04190135002136</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.03721189498901</v>
+        <v>3.03721213340759</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.04346466064453</v>
+        <v>3.04346489906311</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.06065917015076</v>
+        <v>3.06065940856934</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.00907492637634</v>
+        <v>3.00907516479492</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.9559280872345</v>
+        <v>2.95592784881592</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.91059613227844</v>
+        <v>2.91059637069702</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.90590691566467</v>
+        <v>2.90590667724609</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.88245964050293</v>
+        <v>2.88245940208435</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.84494400024414</v>
+        <v>2.84494376182556</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.88245964050293</v>
+        <v>2.88245940208435</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.91059613227844</v>
+        <v>2.91059637069702</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.90590691566467</v>
+        <v>2.90590667724609</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.84494400024414</v>
+        <v>2.84494376182556</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.82305979728699</v>
+        <v>2.82305955886841</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.82931208610535</v>
+        <v>2.82931232452393</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.81211733818054</v>
+        <v>2.81211757659912</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.7230179309845</v>
+        <v>2.72301769256592</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.73864912986755</v>
+        <v>2.73864936828613</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.70425963401794</v>
+        <v>2.70425987243652</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.6245391368866</v>
+        <v>2.62453889846802</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.57764434814453</v>
+        <v>2.57764410972595</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.54950761795044</v>
+        <v>2.54950737953186</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.48229193687439</v>
+        <v>2.48229169845581</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.48454141616821</v>
+        <v>2.48454165458679</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.61951661109924</v>
+        <v>2.61951637268066</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.68950343132019</v>
+        <v>2.68950319290161</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.73116254806519</v>
+        <v>2.73116230964661</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.74782633781433</v>
+        <v>2.74782609939575</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.73116254806519</v>
+        <v>2.73116230964661</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.74615979194641</v>
+        <v>2.74615955352783</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.74782633781433</v>
+        <v>2.74782609939575</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.75782418251038</v>
+        <v>2.75782442092896</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.72949600219727</v>
+        <v>2.72949624061584</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.71949791908264</v>
+        <v>2.71949768066406</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.69616913795471</v>
+        <v>2.69616889953613</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.73116254806519</v>
+        <v>2.73116230964661</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.75782418251038</v>
+        <v>2.75782442092896</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.8244788646698</v>
+        <v>2.82447862625122</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.84780764579773</v>
+        <v>2.84780740737915</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.8178129196167</v>
+        <v>2.81781315803528</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.73282885551453</v>
+        <v>2.73282861709595</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.83281064033508</v>
+        <v>2.8328104019165</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.83281064033508</v>
+        <v>2.8328104019165</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.83281064033508</v>
+        <v>2.8328104019165</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.8244788646698</v>
+        <v>2.82447862625122</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.84114217758179</v>
+        <v>2.84114241600037</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.71449875831604</v>
+        <v>2.71449899673462</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.74615979194641</v>
+        <v>2.74615955352783</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.74615979194641</v>
+        <v>2.74615955352783</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.73282885551453</v>
+        <v>2.73282861709595</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.73116254806519</v>
+        <v>2.73116230964661</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.7728214263916</v>
+        <v>2.77282166481018</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.7178316116333</v>
+        <v>2.71783137321472</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.72449707984924</v>
+        <v>2.72449684143066</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.70116806030273</v>
+        <v>2.70116829872131</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.70949983596802</v>
+        <v>2.7095000743866</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.74782633781433</v>
+        <v>2.74782609939575</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.75282526016235</v>
+        <v>2.75282502174377</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.73282885551453</v>
+        <v>2.73282861709595</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.12275671958923</v>
+        <v>3.12275695800781</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.13942050933838</v>
+        <v>3.1394202709198</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.23773527145386</v>
+        <v>3.23773550987244</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.21607303619385</v>
+        <v>3.21607279777527</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.17941308021545</v>
+        <v>3.17941331863403</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.12275671958923</v>
+        <v>3.12275695800781</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.20607471466064</v>
+        <v>3.20607495307922</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.18607831001282</v>
+        <v>3.1860785484314</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.31105542182922</v>
+        <v>3.3110556602478</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.31772065162659</v>
+        <v>3.31772089004517</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.34105014801025</v>
+        <v>3.34104990959167</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.31772065162659</v>
+        <v>3.31772089004517</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -67920,6 +67920,32 @@
         <v>4.65399980545044</v>
       </c>
       <c r="H2598" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2599" t="n">
+        <v>699582</v>
+      </c>
+      <c r="C2599" t="n">
+        <v>4.81799983978271</v>
+      </c>
+      <c r="D2599" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="E2599" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="F2599" t="n">
+        <v>4.79199981689453</v>
+      </c>
+      <c r="G2599" t="n">
+        <v>4.79199981689453</v>
+      </c>
+      <c r="H2599" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26321363449097</v>
+        <v>2.26321387290955</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24304032325745</v>
+        <v>2.24304008483887</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G6" t="n">
-        <v>2.30482125282288</v>
+        <v>2.30482149124146</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>2.33256006240845</v>
+        <v>2.33255982398987</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33256006240845</v>
+        <v>2.33255982398987</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38677597045898</v>
+        <v>2.38677644729614</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33886432647705</v>
+        <v>2.33886408805847</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33886432647705</v>
+        <v>2.33886408805847</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G12" t="n">
-        <v>2.31238603591919</v>
+        <v>2.31238651275635</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G14" t="n">
-        <v>2.37921094894409</v>
+        <v>2.37921118736267</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408138275146</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26951789855957</v>
+        <v>2.26951766014099</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29599547386169</v>
+        <v>2.29599523544312</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3111252784729</v>
+        <v>2.31112575531006</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29725623130798</v>
+        <v>2.29725646972656</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32877779006958</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.75</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408138275146</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G27" t="n">
-        <v>2.34516835212708</v>
+        <v>2.34516859054565</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G28" t="n">
-        <v>2.37542843818665</v>
+        <v>2.37542867660522</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G29" t="n">
-        <v>2.3829939365387</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G31" t="n">
-        <v>2.3829939365387</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G32" t="n">
-        <v>2.35903763771057</v>
+        <v>2.35903787612915</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32877779006958</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G34" t="n">
-        <v>2.28843021392822</v>
+        <v>2.28843069076538</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25060486793518</v>
+        <v>2.25060510635376</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21782302856445</v>
+        <v>2.21782350540161</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G39" t="n">
-        <v>2.20521473884583</v>
+        <v>2.20521450042725</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.20647573471069</v>
+        <v>2.20647549629211</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G41" t="n">
-        <v>2.22664904594421</v>
+        <v>2.22664928436279</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.20647573471069</v>
+        <v>2.20647549629211</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>2.2190842628479</v>
+        <v>2.21908378601074</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G44" t="n">
-        <v>2.19638895988464</v>
+        <v>2.19638872146606</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G46" t="n">
-        <v>2.21404075622559</v>
+        <v>2.21404051780701</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22538828849792</v>
+        <v>2.22538805007935</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G48" t="n">
-        <v>2.23925757408142</v>
+        <v>2.2392578125</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G49" t="n">
-        <v>2.30608248710632</v>
+        <v>2.30608224868774</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.26951789855957</v>
+        <v>2.26951766014099</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.23169231414795</v>
+        <v>2.23169279098511</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.21782302856445</v>
+        <v>2.21782350540161</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G57" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G58" t="n">
-        <v>2.16108536720276</v>
+        <v>2.16108512878418</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.20773649215698</v>
+        <v>2.20773673057556</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15478134155273</v>
+        <v>2.15478086471558</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G62" t="n">
-        <v>2.1787371635437</v>
+        <v>2.17873692512512</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G63" t="n">
-        <v>2.1787371635437</v>
+        <v>2.17873692512512</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G64" t="n">
-        <v>2.16991090774536</v>
+        <v>2.16991114616394</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G65" t="n">
-        <v>2.14721608161926</v>
+        <v>2.14721584320068</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>2.16865062713623</v>
+        <v>2.16865038871765</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>2.14343309402466</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.149738073349</v>
+        <v>2.14973783493042</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G69" t="n">
-        <v>2.149738073349</v>
+        <v>2.14973783493042</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G71" t="n">
-        <v>2.14343309402466</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G77" t="n">
-        <v>2.06778264045715</v>
+        <v>2.06778311729431</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.9946540594101</v>
+        <v>1.99465394020081</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195875644684</v>
+        <v>1.97195887565613</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G81" t="n">
-        <v>1.93917644023895</v>
+        <v>1.93917691707611</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>1.92908978462219</v>
+        <v>1.92909014225006</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>1.92278575897217</v>
+        <v>1.92278587818146</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G84" t="n">
-        <v>1.94800269603729</v>
+        <v>1.94800293445587</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>1.90387332439423</v>
+        <v>1.90387308597565</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.90387332439423</v>
+        <v>1.90387308597565</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>1.92782950401306</v>
+        <v>1.92782938480377</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G88" t="n">
-        <v>1.975741147995</v>
+        <v>1.97574126720428</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>2.00474095344543</v>
+        <v>2.00474071502686</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G94" t="n">
-        <v>1.974480509758</v>
+        <v>1.97448074817657</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>1.9543069601059</v>
+        <v>1.95430731773376</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G96" t="n">
-        <v>1.99213254451752</v>
+        <v>1.99213230609894</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G98" t="n">
-        <v>1.91017746925354</v>
+        <v>1.91017758846283</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>1.8912650346756</v>
+        <v>1.89126467704773</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G100" t="n">
-        <v>1.89504730701447</v>
+        <v>1.89504742622375</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G101" t="n">
-        <v>1.93917644023895</v>
+        <v>1.93917691707611</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G102" t="n">
-        <v>2.00474095344543</v>
+        <v>2.00474071502686</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G103" t="n">
-        <v>2.02113175392151</v>
+        <v>2.02113151550293</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G105" t="n">
-        <v>2.05643558502197</v>
+        <v>2.05643582344055</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>2.06147837638855</v>
+        <v>2.06147861480713</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G107" t="n">
-        <v>2.07030415534973</v>
+        <v>2.07030439376831</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>2.08669567108154</v>
+        <v>2.08669543266296</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>2.06147837638855</v>
+        <v>2.06147861480713</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G110" t="n">
-        <v>2.06778264045715</v>
+        <v>2.06778311729431</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.06147837638855</v>
+        <v>2.06147861480713</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G112" t="n">
-        <v>2.07913041114807</v>
+        <v>2.07913017272949</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G113" t="n">
-        <v>2.07030415534973</v>
+        <v>2.07030439376831</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G114" t="n">
-        <v>2.08417344093323</v>
+        <v>2.08417391777039</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G115" t="n">
-        <v>2.11569476127625</v>
+        <v>2.1156952381134</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.14343309402466</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G117" t="n">
-        <v>2.14469408988953</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G118" t="n">
-        <v>2.14091181755066</v>
+        <v>2.14091157913208</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>2.14343309402466</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.15604162216187</v>
+        <v>2.1560423374176</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>2.19008421897888</v>
+        <v>2.19008445739746</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G124" t="n">
-        <v>2.16738939285278</v>
+        <v>2.16738963127136</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G125" t="n">
-        <v>2.16991090774536</v>
+        <v>2.16991114616394</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G126" t="n">
-        <v>2.14847660064697</v>
+        <v>2.14847683906555</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.15604162216187</v>
+        <v>2.1560423374176</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G128" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15352010726929</v>
+        <v>2.15352034568787</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>2.13460755348206</v>
+        <v>2.13460731506348</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G131" t="n">
-        <v>2.1119122505188</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>2.1119122505188</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G133" t="n">
-        <v>2.06904363632202</v>
+        <v>2.0690438747406</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G136" t="n">
-        <v>2.02617502212524</v>
+        <v>2.02617478370667</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>1.99213254451752</v>
+        <v>1.99213230609894</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G140" t="n">
-        <v>1.97069811820984</v>
+        <v>1.97069764137268</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.02365326881409</v>
+        <v>2.02365303039551</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>2.01734924316406</v>
+        <v>2.01734900474548</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>2.05643558502197</v>
+        <v>2.05643582344055</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G144" t="n">
-        <v>2.07282662391663</v>
+        <v>2.07282614707947</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.1119122505188</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.13712954521179</v>
+        <v>2.13712930679321</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G148" t="n">
-        <v>2.149738073349</v>
+        <v>2.14973783493042</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>2.15225958824158</v>
+        <v>2.15225911140442</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>2.14343309402466</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G151" t="n">
-        <v>2.16486763954163</v>
+        <v>2.16486787796021</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G152" t="n">
-        <v>2.12199902534485</v>
+        <v>2.12199926376343</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>2.08669567108154</v>
+        <v>2.08669543266296</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G156" t="n">
-        <v>2.13712954521179</v>
+        <v>2.13712930679321</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G160" t="n">
-        <v>2.12704277038574</v>
+        <v>2.12704253196716</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G161" t="n">
-        <v>2.14469408988953</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G163" t="n">
-        <v>2.16108536720276</v>
+        <v>2.16108512878418</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>2.21277952194214</v>
+        <v>2.21277976036072</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G168" t="n">
-        <v>2.331298828125</v>
+        <v>2.33129930496216</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.28843021392822</v>
+        <v>2.28843069076538</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>2.27582168579102</v>
+        <v>2.27582216262817</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35147285461426</v>
+        <v>2.35147261619568</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G173" t="n">
-        <v>2.37290692329407</v>
+        <v>2.37290716171265</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40190649032593</v>
+        <v>2.40190625190735</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.32877779006958</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G177" t="n">
-        <v>2.34012484550476</v>
+        <v>2.34012508392334</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G178" t="n">
-        <v>2.40316724777222</v>
+        <v>2.40316700935364</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G179" t="n">
-        <v>2.3829939365387</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.3224732875824</v>
+        <v>2.32247304916382</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G181" t="n">
-        <v>2.3918194770813</v>
+        <v>2.39181923866272</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G182" t="n">
-        <v>2.37038564682007</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G185" t="n">
-        <v>2.3716459274292</v>
+        <v>2.37164640426636</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G186" t="n">
-        <v>2.41703653335571</v>
+        <v>2.41703701019287</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G187" t="n">
-        <v>2.3829939365387</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.75</v>
       </c>
       <c r="G188" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408138275146</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G189" t="n">
-        <v>2.3653416633606</v>
+        <v>2.36534190177917</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.75</v>
       </c>
       <c r="G192" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408138275146</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G193" t="n">
-        <v>2.3552553653717</v>
+        <v>2.35525512695312</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G194" t="n">
-        <v>2.38047218322754</v>
+        <v>2.38047194480896</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.75</v>
       </c>
       <c r="G195" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408138275146</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G196" t="n">
-        <v>2.37038564682007</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G197" t="n">
-        <v>2.39308047294617</v>
+        <v>2.39308071136475</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.75</v>
       </c>
       <c r="G198" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408138275146</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>2.42964506149292</v>
+        <v>2.42964482307434</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>2.41451478004456</v>
+        <v>2.41451454162598</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.4523401260376</v>
+        <v>2.45234036445618</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G203" t="n">
-        <v>2.43847107887268</v>
+        <v>2.43847060203552</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>2.38677597045898</v>
+        <v>2.38677644729614</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G209" t="n">
-        <v>2.41451478004456</v>
+        <v>2.41451454162598</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G210" t="n">
-        <v>2.37038564682007</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G211" t="n">
-        <v>2.41535902023315</v>
+        <v>2.41535878181458</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G212" t="n">
-        <v>2.39816308021545</v>
+        <v>2.39816331863403</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G213" t="n">
-        <v>2.46826958656311</v>
+        <v>2.46826934814453</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G214" t="n">
-        <v>2.5119206905365</v>
+        <v>2.51192045211792</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G215" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721167564392</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>2.5000159740448</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>2.46694684028625</v>
+        <v>2.4669463634491</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.75</v>
       </c>
       <c r="G219" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.5000159740448</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.75</v>
       </c>
       <c r="G221" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.75</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G223" t="n">
-        <v>2.46562361717224</v>
+        <v>2.46562385559082</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G224" t="n">
-        <v>2.49737024307251</v>
+        <v>2.49737000465393</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G225" t="n">
-        <v>2.52250218391418</v>
+        <v>2.52250242233276</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G226" t="n">
-        <v>2.48546504974365</v>
+        <v>2.48546528816223</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>2.49340176582336</v>
+        <v>2.49340152740479</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>2.46694684028625</v>
+        <v>2.4669463634491</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.75</v>
       </c>
       <c r="G231" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.75</v>
       </c>
       <c r="G232" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G233" t="n">
-        <v>2.47620606422424</v>
+        <v>2.47620582580566</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.75</v>
       </c>
       <c r="G235" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.75</v>
       </c>
       <c r="G236" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017454147339</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G240" t="n">
-        <v>2.49207878112793</v>
+        <v>2.49207901954651</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>2.4603328704834</v>
+        <v>2.46033310890198</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G242" t="n">
-        <v>2.46165561676025</v>
+        <v>2.46165537834167</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>2.46694684028625</v>
+        <v>2.4669463634491</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G245" t="n">
-        <v>2.46165561676025</v>
+        <v>2.46165537834167</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>2.46694684028625</v>
+        <v>2.4669463634491</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G247" t="n">
-        <v>2.44445991516113</v>
+        <v>2.44445967674255</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46562361717224</v>
+        <v>2.46562385559082</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>2.49340176582336</v>
+        <v>2.49340152740479</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>2.44578242301941</v>
+        <v>2.44578266143799</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G251" t="n">
-        <v>2.43387746810913</v>
+        <v>2.43387770652771</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488355636597</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G256" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488355636597</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.4603328704834</v>
+        <v>2.46033310890198</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G259" t="n">
-        <v>2.50927495956421</v>
+        <v>2.50927472114563</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>2.51456594467163</v>
+        <v>2.51456618309021</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G261" t="n">
-        <v>2.5648307800293</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55689430236816</v>
+        <v>2.55689454078674</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G263" t="n">
-        <v>2.57144451141357</v>
+        <v>2.57144474983215</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G265" t="n">
-        <v>2.5648307800293</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G266" t="n">
-        <v>2.56615352630615</v>
+        <v>2.56615376472473</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G269" t="n">
-        <v>2.54498934745789</v>
+        <v>2.54498958587646</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G270" t="n">
-        <v>2.5238254070282</v>
+        <v>2.52382516860962</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>2.53308463096619</v>
+        <v>2.53308439254761</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G273" t="n">
-        <v>2.5000159740448</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.49340176582336</v>
+        <v>2.49340152740479</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G276" t="n">
-        <v>2.46165561676025</v>
+        <v>2.46165537834167</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.48678827285767</v>
+        <v>2.48678803443909</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G279" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488355636597</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G280" t="n">
-        <v>2.44842767715454</v>
+        <v>2.4484281539917</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G281" t="n">
-        <v>2.42858648300171</v>
+        <v>2.42858672142029</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G282" t="n">
-        <v>2.43784618377686</v>
+        <v>2.43784594535828</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G283" t="n">
-        <v>2.45901012420654</v>
+        <v>2.45901036262512</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G285" t="n">
-        <v>2.46959209442139</v>
+        <v>2.46959185600281</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G288" t="n">
-        <v>2.49869275093079</v>
+        <v>2.49869298934937</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54366683959961</v>
+        <v>2.54366660118103</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G291" t="n">
-        <v>2.53837561607361</v>
+        <v>2.53837585449219</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G292" t="n">
-        <v>2.5357301235199</v>
+        <v>2.53573060035706</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G293" t="n">
-        <v>2.53440761566162</v>
+        <v>2.53440713882446</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G295" t="n">
-        <v>2.53176188468933</v>
+        <v>2.53176212310791</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G296" t="n">
-        <v>2.54102110862732</v>
+        <v>2.5410213470459</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G298" t="n">
-        <v>2.51456594467163</v>
+        <v>2.51456618309021</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G299" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721167564392</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53308463096619</v>
+        <v>2.53308439254761</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G301" t="n">
-        <v>2.5357301235199</v>
+        <v>2.53573060035706</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53969812393188</v>
+        <v>2.53969836235046</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.53969812393188</v>
+        <v>2.53969836235046</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G304" t="n">
-        <v>2.56350779533386</v>
+        <v>2.56350803375244</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G307" t="n">
-        <v>2.60583662986755</v>
+        <v>2.60583639144897</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60583662986755</v>
+        <v>2.60583639144897</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G311" t="n">
-        <v>2.59128618240356</v>
+        <v>2.59128570556641</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G313" t="n">
-        <v>2.62700033187866</v>
+        <v>2.62700057029724</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G316" t="n">
-        <v>2.60319089889526</v>
+        <v>2.60319113731384</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G317" t="n">
-        <v>2.67329692840576</v>
+        <v>2.67329668998718</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G318" t="n">
-        <v>2.68917012214661</v>
+        <v>2.68917036056519</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G319" t="n">
-        <v>2.67594218254089</v>
+        <v>2.67594265937805</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G320" t="n">
-        <v>2.69710683822632</v>
+        <v>2.69710659980774</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>2.67858839035034</v>
+        <v>2.67858815193176</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>2.69842958450317</v>
+        <v>2.69842934608459</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G325" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G326" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G327" t="n">
-        <v>2.68784737586975</v>
+        <v>2.68784761428833</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G328" t="n">
-        <v>2.68784737586975</v>
+        <v>2.68784761428833</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G329" t="n">
-        <v>2.70239806175232</v>
+        <v>2.70239758491516</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G332" t="n">
-        <v>2.70107507705688</v>
+        <v>2.70107531547546</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G333" t="n">
-        <v>2.70107507705688</v>
+        <v>2.70107531547546</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>2.67197442054749</v>
+        <v>2.67197418212891</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G337" t="n">
-        <v>2.78837728500366</v>
+        <v>2.7883768081665</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.85054731369019</v>
+        <v>2.85054659843445</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G339" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G341" t="n">
-        <v>2.90345740318298</v>
+        <v>2.90345692634583</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G342" t="n">
-        <v>2.90742564201355</v>
+        <v>2.90742516517639</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>2.94578552246094</v>
+        <v>2.94578576087952</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G346" t="n">
-        <v>2.97356367111206</v>
+        <v>2.97356343269348</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G347" t="n">
-        <v>2.96430420875549</v>
+        <v>2.96430397033691</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G348" t="n">
-        <v>2.96827220916748</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G351" t="n">
-        <v>3.01456880569458</v>
+        <v>3.01456928253174</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G354" t="n">
-        <v>3.10583972930908</v>
+        <v>3.1058394908905</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G355" t="n">
-        <v>3.03440999984741</v>
+        <v>3.03441071510315</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.00927805900574</v>
+        <v>3.00927829742432</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>3.01456880569458</v>
+        <v>3.01456928253174</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>3.0423469543457</v>
+        <v>3.04234719276428</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G360" t="n">
-        <v>3.04631543159485</v>
+        <v>3.04631519317627</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>3.00266408920288</v>
+        <v>3.00266432762146</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>3.02911925315857</v>
+        <v>3.02911949157715</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05557465553284</v>
+        <v>3.05557417869568</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G364" t="n">
-        <v>3.025151014328</v>
+        <v>3.02515125274658</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>2.98943710327148</v>
+        <v>2.98943662643433</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>3.00266408920288</v>
+        <v>3.00266432762146</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G367" t="n">
-        <v>2.98282289505005</v>
+        <v>2.98282265663147</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G368" t="n">
-        <v>2.97091841697693</v>
+        <v>2.97091817855835</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>2.99869608879089</v>
+        <v>2.99869585037231</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G370" t="n">
-        <v>2.97356367111206</v>
+        <v>2.97356343269348</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G371" t="n">
-        <v>2.96827220916748</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>2.94314026832581</v>
+        <v>2.94313979148865</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G375" t="n">
-        <v>2.85054731369019</v>
+        <v>2.85054659843445</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.87700176239014</v>
+        <v>2.87700223922729</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G377" t="n">
-        <v>2.84922385215759</v>
+        <v>2.84922432899475</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G379" t="n">
-        <v>2.86509680747986</v>
+        <v>2.86509704589844</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G382" t="n">
-        <v>2.85451531410217</v>
+        <v>2.85451555252075</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G383" t="n">
-        <v>2.8307056427002</v>
+        <v>2.83070588111877</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G385" t="n">
-        <v>2.84922385215759</v>
+        <v>2.84922432899475</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.87700176239014</v>
+        <v>2.87700223922729</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.84525609016418</v>
+        <v>2.84525585174561</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705453872681</v>
+        <v>2.78705477714539</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>2.75398564338684</v>
+        <v>2.75398540496826</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G396" t="n">
-        <v>2.67329692840576</v>
+        <v>2.67329668998718</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69446110725403</v>
+        <v>2.69446134567261</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G399" t="n">
-        <v>2.75266289710999</v>
+        <v>2.75266265869141</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G400" t="n">
-        <v>2.75001740455627</v>
+        <v>2.7500171661377</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.75927686691284</v>
+        <v>2.75927639007568</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G403" t="n">
-        <v>2.76456761360168</v>
+        <v>2.76456737518311</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G404" t="n">
-        <v>2.72885322570801</v>
+        <v>2.72885274887085</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G405" t="n">
-        <v>2.72885322570801</v>
+        <v>2.72885274887085</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>2.79102277755737</v>
+        <v>2.79102253913879</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73943543434143</v>
+        <v>2.73943519592285</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>2.67991089820862</v>
+        <v>2.6799111366272</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G413" t="n">
-        <v>2.76324462890625</v>
+        <v>2.76324439048767</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>2.75927686691284</v>
+        <v>2.75927639007568</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G416" t="n">
-        <v>2.79102277755737</v>
+        <v>2.79102253913879</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G418" t="n">
-        <v>2.86906552314758</v>
+        <v>2.86906504631042</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G419" t="n">
-        <v>2.87303328514099</v>
+        <v>2.87303400039673</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>2.91007089614868</v>
+        <v>2.91007137298584</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G421" t="n">
-        <v>2.88890695571899</v>
+        <v>2.88890719413757</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G424" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G427" t="n">
-        <v>2.79234528541565</v>
+        <v>2.79234552383423</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G429" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.85054731369019</v>
+        <v>2.85054659843445</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.89022970199585</v>
+        <v>2.89022946357727</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G434" t="n">
-        <v>2.894198179245</v>
+        <v>2.89419794082642</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G436" t="n">
-        <v>2.93123579025269</v>
+        <v>2.93123555183411</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94181704521179</v>
+        <v>2.94181728363037</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G438" t="n">
-        <v>2.9788544178009</v>
+        <v>2.97885465621948</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99208235740662</v>
+        <v>2.99208211898804</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G440" t="n">
-        <v>3.0079550743103</v>
+        <v>3.00795555114746</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G441" t="n">
-        <v>2.98282289505005</v>
+        <v>2.98282265663147</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.93652653694153</v>
+        <v>2.93652629852295</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520331382751</v>
+        <v>2.93520379066467</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G444" t="n">
-        <v>2.94181704521179</v>
+        <v>2.94181728363037</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96827220916748</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G448" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G449" t="n">
-        <v>2.99075961112976</v>
+        <v>2.99075937271118</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.99208235740662</v>
+        <v>2.99208211898804</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G451" t="n">
-        <v>3.01721453666687</v>
+        <v>3.01721429824829</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G452" t="n">
-        <v>2.9788544178009</v>
+        <v>2.97885465621948</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G453" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00398707389832</v>
+        <v>3.00398659706116</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G455" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G458" t="n">
-        <v>2.98282289505005</v>
+        <v>2.98282265663147</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G459" t="n">
-        <v>2.98943710327148</v>
+        <v>2.98943662643433</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94710803031921</v>
+        <v>2.94710826873779</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G462" t="n">
-        <v>2.89684367179871</v>
+        <v>2.89684319496155</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88361644744873</v>
+        <v>2.88361620903015</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>2.89494681358337</v>
+        <v>2.89494705200195</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G467" t="n">
-        <v>2.90876507759094</v>
+        <v>2.90876531600952</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>2.75676369667053</v>
+        <v>2.75676321983337</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G471" t="n">
-        <v>2.80650925636292</v>
+        <v>2.80650901794434</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G472" t="n">
-        <v>2.84796476364136</v>
+        <v>2.84796452522278</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G473" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G474" t="n">
-        <v>2.88251066207886</v>
+        <v>2.8825101852417</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G475" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>2.79130911827087</v>
+        <v>2.79130887985229</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G480" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G482" t="n">
-        <v>2.92258381843567</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G486" t="n">
-        <v>3.01240348815918</v>
+        <v>3.0124032497406</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G487" t="n">
-        <v>2.9902937412262</v>
+        <v>2.99029350280762</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.01931214332581</v>
+        <v>3.01931190490723</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.9737114906311</v>
+        <v>2.97371125221252</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>2.9778573513031</v>
+        <v>2.97785663604736</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G493" t="n">
-        <v>2.96818399429321</v>
+        <v>2.96818375587463</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G494" t="n">
-        <v>2.96818399429321</v>
+        <v>2.96818375587463</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G495" t="n">
-        <v>2.9902937412262</v>
+        <v>2.99029350280762</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G496" t="n">
-        <v>2.96818399429321</v>
+        <v>2.96818375587463</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G501" t="n">
-        <v>2.94054746627808</v>
+        <v>2.94054770469666</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G502" t="n">
-        <v>2.95851111412048</v>
+        <v>2.95851159095764</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G503" t="n">
-        <v>3.01793026924133</v>
+        <v>3.01793074607849</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G504" t="n">
-        <v>3.03174877166748</v>
+        <v>3.0317485332489</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>3.10498571395874</v>
+        <v>3.1049861907959</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G507" t="n">
-        <v>3.11051297187805</v>
+        <v>3.11051344871521</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G508" t="n">
-        <v>3.14229536056519</v>
+        <v>3.14229583740234</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G510" t="n">
-        <v>3.07182192802429</v>
+        <v>3.07182216644287</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>3.04556679725647</v>
+        <v>3.04556703567505</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>3.05385828018188</v>
+        <v>3.05385804176331</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>3.04556679725647</v>
+        <v>3.04556703567505</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G515" t="n">
-        <v>3.04418516159058</v>
+        <v>3.04418540000916</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G519" t="n">
-        <v>3.00963950157166</v>
+        <v>3.0096390247345</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>3.04003953933716</v>
+        <v>3.04004001617432</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>3.01931214332581</v>
+        <v>3.01931190490723</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G524" t="n">
-        <v>2.9930567741394</v>
+        <v>2.99305701255798</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G525" t="n">
-        <v>2.99582076072693</v>
+        <v>2.99582052230835</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G526" t="n">
-        <v>2.92258381843567</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G527" t="n">
-        <v>2.91843843460083</v>
+        <v>2.91843795776367</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>2.90185594558716</v>
+        <v>2.90185618400574</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G529" t="n">
-        <v>2.91981959342957</v>
+        <v>2.91981983184814</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>2.92258381843567</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94331097602844</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G532" t="n">
-        <v>2.93087482452393</v>
+        <v>2.93087458610535</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.25</v>
       </c>
       <c r="G533" t="n">
-        <v>2.93640184402466</v>
+        <v>2.93640160560608</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G534" t="n">
-        <v>2.87283778190613</v>
+        <v>2.87283754348755</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G536" t="n">
-        <v>2.95160174369812</v>
+        <v>2.9516019821167</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94192934036255</v>
+        <v>2.94192886352539</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>2.94331097602844</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>2.91152906417847</v>
+        <v>2.91152930259705</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.92811107635498</v>
+        <v>2.9281108379364</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>2.99167513847351</v>
+        <v>2.99167537689209</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G545" t="n">
-        <v>2.96265721321106</v>
+        <v>2.96265697479248</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.9737114906311</v>
+        <v>2.97371125221252</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06491231918335</v>
+        <v>3.06491279602051</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G548" t="n">
-        <v>3.00134778022766</v>
+        <v>3.00134825706482</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G549" t="n">
-        <v>3.01240348815918</v>
+        <v>3.0124032497406</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G550" t="n">
-        <v>2.97232985496521</v>
+        <v>2.97232961654663</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G551" t="n">
-        <v>2.91291093826294</v>
+        <v>2.91291046142578</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G554" t="n">
-        <v>2.96265721321106</v>
+        <v>2.96265697479248</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G555" t="n">
-        <v>2.95298457145691</v>
+        <v>2.95298433303833</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G556" t="n">
-        <v>2.90323805809021</v>
+        <v>2.90323781967163</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G557" t="n">
-        <v>2.90047407150269</v>
+        <v>2.90047430992126</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G558" t="n">
-        <v>2.89632868766785</v>
+        <v>2.89632892608643</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G560" t="n">
-        <v>2.87007355690002</v>
+        <v>2.87007403373718</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G563" t="n">
-        <v>2.76090860366821</v>
+        <v>2.76090884208679</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G564" t="n">
-        <v>2.78439998626709</v>
+        <v>2.78440022468567</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76367235183716</v>
+        <v>2.76367259025574</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77749109268188</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G571" t="n">
-        <v>2.74847197532654</v>
+        <v>2.74847221374512</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G572" t="n">
-        <v>2.77749109268188</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G573" t="n">
-        <v>2.76505422592163</v>
+        <v>2.76505398750305</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G575" t="n">
-        <v>2.71668982505798</v>
+        <v>2.71669006347656</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G577" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G579" t="n">
-        <v>2.74847197532654</v>
+        <v>2.74847221374512</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G580" t="n">
-        <v>2.75123572349548</v>
+        <v>2.75123620033264</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77749109268188</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G583" t="n">
-        <v>2.77334547042847</v>
+        <v>2.77334523200989</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>2.72221755981445</v>
+        <v>2.72221732139587</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G585" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G586" t="n">
-        <v>2.74018120765686</v>
+        <v>2.74018144607544</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G587" t="n">
-        <v>2.75814485549927</v>
+        <v>2.75814509391785</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73879957199097</v>
+        <v>2.73879933357239</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>2.89494681358337</v>
+        <v>2.89494705200195</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G594" t="n">
-        <v>2.87836456298828</v>
+        <v>2.87836480140686</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G595" t="n">
-        <v>2.83552765846252</v>
+        <v>2.8355278968811</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G596" t="n">
-        <v>2.86040043830872</v>
+        <v>2.86040091514587</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>2.94331097602844</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G599" t="n">
-        <v>2.91014671325684</v>
+        <v>2.91014647483826</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G600" t="n">
-        <v>2.89909267425537</v>
+        <v>2.89909291267395</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>2.88527393341064</v>
+        <v>2.88527417182922</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G602" t="n">
-        <v>2.90047407150269</v>
+        <v>2.90047430992126</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.90876507759094</v>
+        <v>2.90876531600952</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>2.88803768157959</v>
+        <v>2.88803744316101</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G606" t="n">
-        <v>2.84796476364136</v>
+        <v>2.84796452522278</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G608" t="n">
-        <v>2.85901927947998</v>
+        <v>2.8590190410614</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G609" t="n">
-        <v>2.84520077705383</v>
+        <v>2.84520030021667</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G610" t="n">
-        <v>2.86869192123413</v>
+        <v>2.86869168281555</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G611" t="n">
-        <v>2.91152906417847</v>
+        <v>2.91152930259705</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G612" t="n">
-        <v>2.90323805809021</v>
+        <v>2.90323781967163</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>2.87421941757202</v>
+        <v>2.87421917915344</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G614" t="n">
-        <v>2.84520077705383</v>
+        <v>2.84520030021667</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G615" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G617" t="n">
-        <v>2.89632868766785</v>
+        <v>2.89632892608643</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G619" t="n">
-        <v>2.93087482452393</v>
+        <v>2.93087458610535</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G620" t="n">
-        <v>2.89909267425537</v>
+        <v>2.89909291267395</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G622" t="n">
-        <v>2.98338437080383</v>
+        <v>2.98338413238525</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G624" t="n">
-        <v>2.96265721321106</v>
+        <v>2.96265697479248</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.01931214332581</v>
+        <v>3.01931190490723</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>3.04003953933716</v>
+        <v>3.04004001617432</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G628" t="n">
-        <v>3.00963950157166</v>
+        <v>3.0096390247345</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G630" t="n">
-        <v>3.01240348815918</v>
+        <v>3.0124032497406</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G633" t="n">
-        <v>3.03313064575195</v>
+        <v>3.03313016891479</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.04003953933716</v>
+        <v>3.04004001617432</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G638" t="n">
-        <v>3.02483916282654</v>
+        <v>3.02483940124512</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>3.04003953933716</v>
+        <v>3.04004001617432</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>3.0814950466156</v>
+        <v>3.08149480819702</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G644" t="n">
-        <v>3.09669494628906</v>
+        <v>3.0966944694519</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G646" t="n">
-        <v>3.14229536056519</v>
+        <v>3.14229583740234</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G647" t="n">
-        <v>3.0662944316864</v>
+        <v>3.06629467010498</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G649" t="n">
-        <v>3.09669494628906</v>
+        <v>3.0966944694519</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12295031547546</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G651" t="n">
-        <v>3.10360455513</v>
+        <v>3.10360431671143</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G652" t="n">
-        <v>3.12709522247314</v>
+        <v>3.12709546089172</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G654" t="n">
-        <v>3.12295031547546</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>3.10498571395874</v>
+        <v>3.1049861907959</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>3.1118950843811</v>
+        <v>3.11189532279968</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>3.12295031547546</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13815021514893</v>
+        <v>3.13814973831177</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.55399990081787</v>
       </c>
       <c r="G663" t="n">
-        <v>3.14644122123718</v>
+        <v>3.1464409828186</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G664" t="n">
-        <v>3.12018585205078</v>
+        <v>3.12018609046936</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.5</v>
       </c>
       <c r="G665" t="n">
-        <v>3.10913181304932</v>
+        <v>3.10913157463074</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.10913181304932</v>
+        <v>3.10913157463074</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G669" t="n">
-        <v>3.26251578330994</v>
+        <v>3.26251530647278</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G670" t="n">
-        <v>3.3122615814209</v>
+        <v>3.31226110458374</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>3.34542512893677</v>
+        <v>3.34542560577393</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G672" t="n">
-        <v>3.34680700302124</v>
+        <v>3.34680724143982</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G673" t="n">
-        <v>3.36062526702881</v>
+        <v>3.36062574386597</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G675" t="n">
-        <v>3.35924410820007</v>
+        <v>3.35924339294434</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G676" t="n">
-        <v>3.37997126579285</v>
+        <v>3.37997150421143</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>3.34542512893677</v>
+        <v>3.34542560577393</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>3.30535221099854</v>
+        <v>3.30535197257996</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G679" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G680" t="n">
-        <v>3.33022522926331</v>
+        <v>3.33022570610046</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G682" t="n">
-        <v>3.35648036003113</v>
+        <v>3.35647988319397</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G683" t="n">
-        <v>3.37858939170837</v>
+        <v>3.37858986854553</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G684" t="n">
-        <v>3.37444424629211</v>
+        <v>3.37444376945496</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G685" t="n">
-        <v>3.36615300178528</v>
+        <v>3.36615324020386</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G686" t="n">
-        <v>3.36615300178528</v>
+        <v>3.36615324020386</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G687" t="n">
-        <v>3.36615300178528</v>
+        <v>3.36615324020386</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G688" t="n">
-        <v>3.32469797134399</v>
+        <v>3.32469773292542</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G690" t="n">
-        <v>3.29015207290649</v>
+        <v>3.29015254974365</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31778836250305</v>
+        <v>3.31778860092163</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G693" t="n">
-        <v>3.35371661186218</v>
+        <v>3.35371613502502</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G696" t="n">
-        <v>3.33989834785461</v>
+        <v>3.33989810943604</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G697" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.32331609725952</v>
+        <v>3.32331585884094</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G702" t="n">
-        <v>3.36062526702881</v>
+        <v>3.36062574386597</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G704" t="n">
-        <v>3.35648036003113</v>
+        <v>3.35647988319397</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G706" t="n">
-        <v>3.38273525238037</v>
+        <v>3.38273501396179</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G708" t="n">
-        <v>3.34128022193909</v>
+        <v>3.34127974510193</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G710" t="n">
-        <v>3.32469797134399</v>
+        <v>3.32469773292542</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>3.38549876213074</v>
+        <v>3.38549852371216</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G712" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G714" t="n">
-        <v>3.37029838562012</v>
+        <v>3.37029814720154</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G716" t="n">
-        <v>3.44507908821106</v>
+        <v>3.44507884979248</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.80800008773804</v>
       </c>
       <c r="G717" t="n">
-        <v>3.46380996704102</v>
+        <v>3.46381020545959</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G718" t="n">
-        <v>3.4623692035675</v>
+        <v>3.46236944198608</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G719" t="n">
-        <v>3.46092820167542</v>
+        <v>3.46092844009399</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G720" t="n">
-        <v>3.48110008239746</v>
+        <v>3.48109984397888</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>3.46957325935364</v>
+        <v>3.46957302093506</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G722" t="n">
-        <v>3.45660543441772</v>
+        <v>3.4566056728363</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G723" t="n">
-        <v>3.48110008239746</v>
+        <v>3.48109984397888</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>3.49406766891479</v>
+        <v>3.49406790733337</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G726" t="n">
-        <v>3.57475566864014</v>
+        <v>3.57475519180298</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G729" t="n">
-        <v>3.67777609825134</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.125</v>
       </c>
       <c r="G730" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218468666077</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>3.63455057144165</v>
+        <v>3.63455104827881</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G735" t="n">
-        <v>3.61293816566467</v>
+        <v>3.61293792724609</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G736" t="n">
-        <v>3.68137907981873</v>
+        <v>3.68137836456299</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G739" t="n">
-        <v>3.68498086929321</v>
+        <v>3.68498039245605</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>3.68858289718628</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G741" t="n">
-        <v>3.62374496459961</v>
+        <v>3.62374448776245</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G747" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G752" t="n">
-        <v>3.60933589935303</v>
+        <v>3.60933637619019</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.62014269828796</v>
+        <v>3.62014245986938</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G756" t="n">
-        <v>3.61293816566467</v>
+        <v>3.61293792724609</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>3.61654043197632</v>
+        <v>3.61654019355774</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G762" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57187390327454</v>
+        <v>3.57187438011169</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G768" t="n">
-        <v>3.62374496459961</v>
+        <v>3.62374448776245</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G772" t="n">
-        <v>3.67057180404663</v>
+        <v>3.67057228088379</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>3.61654043197632</v>
+        <v>3.61654019355774</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>3.67777609825134</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>3.76782989501953</v>
+        <v>3.76782941818237</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.71379828453064</v>
+        <v>3.71379804611206</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>3.71379828453064</v>
+        <v>3.71379804611206</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G785" t="n">
-        <v>3.77503395080566</v>
+        <v>3.77503347396851</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G786" t="n">
-        <v>3.7390124797821</v>
+        <v>3.73901295661926</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G788" t="n">
-        <v>3.70299100875854</v>
+        <v>3.7029914855957</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>3.72100186347961</v>
+        <v>3.72100234031677</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G790" t="n">
-        <v>3.68858289718628</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>3.72100186347961</v>
+        <v>3.72100234031677</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G793" t="n">
-        <v>3.70299100875854</v>
+        <v>3.7029914855957</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.64175486564636</v>
+        <v>3.64175534248352</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>3.62014269828796</v>
+        <v>3.62014245986938</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.68858289718628</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>3.67777609825134</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.125</v>
       </c>
       <c r="G800" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218468666077</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>5.125</v>
       </c>
       <c r="G801" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218468666077</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>3.67777609825134</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.67057180404663</v>
+        <v>3.67057228088379</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>5.125</v>
       </c>
       <c r="G807" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218468666077</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G808" t="n">
-        <v>3.67057180404663</v>
+        <v>3.67057228088379</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>3.68858289718628</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342178344727</v>
+        <v>3.75342130661011</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>3.7390124797821</v>
+        <v>3.73901295661926</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>3.76782989501953</v>
+        <v>3.76782941818237</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342178344727</v>
+        <v>3.75342130661011</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G826" t="n">
-        <v>3.68137907981873</v>
+        <v>3.68137836456299</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G828" t="n">
-        <v>3.70299100875854</v>
+        <v>3.7029914855957</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G832" t="n">
-        <v>3.76062536239624</v>
+        <v>3.76062488555908</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584027290344</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G834" t="n">
-        <v>3.79304432868958</v>
+        <v>3.79304480552673</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>3.82546377182007</v>
+        <v>3.82546424865723</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342178344727</v>
+        <v>3.75342130661011</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>3.77503395080566</v>
+        <v>3.77503347396851</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584027290344</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.77863621711731</v>
+        <v>3.77863597869873</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148524284363</v>
+        <v>3.86148476600647</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>5.375</v>
       </c>
       <c r="G844" t="n">
-        <v>3.87229180335999</v>
+        <v>3.87229132652283</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.82186222076416</v>
+        <v>3.821861743927</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.7966468334198</v>
+        <v>3.79664731025696</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G852" t="n">
-        <v>3.8903021812439</v>
+        <v>3.89030265808105</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G853" t="n">
-        <v>3.87589359283447</v>
+        <v>3.87589406967163</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80024886131287</v>
+        <v>3.80024933815002</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G855" t="n">
-        <v>3.7966468334198</v>
+        <v>3.79664731025696</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80024886131287</v>
+        <v>3.80024933815002</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80024886131287</v>
+        <v>3.80024933815002</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>3.83627033233643</v>
+        <v>3.83626985549927</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G863" t="n">
-        <v>3.81105542182922</v>
+        <v>3.8110556602478</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>3.7966468334198</v>
+        <v>3.79664731025696</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>3.8578827381134</v>
+        <v>3.85788321495056</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.375</v>
       </c>
       <c r="G866" t="n">
-        <v>3.87229180335999</v>
+        <v>3.87229132652283</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>3.90831303596497</v>
+        <v>3.90831351280212</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>3.9047110080719</v>
+        <v>3.90471076965332</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.375</v>
       </c>
       <c r="G869" t="n">
-        <v>3.87229180335999</v>
+        <v>3.87229132652283</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>3.83627033233643</v>
+        <v>3.83626985549927</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>3.80024886131287</v>
+        <v>3.80024933815002</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G879" t="n">
-        <v>3.95874261856079</v>
+        <v>3.95874214172363</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G880" t="n">
-        <v>3.998366355896</v>
+        <v>3.99836683273315</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>4.01997947692871</v>
+        <v>4.01997900009155</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.625</v>
       </c>
       <c r="G883" t="n">
-        <v>4.05239820480347</v>
+        <v>4.05239772796631</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G885" t="n">
-        <v>4.06680679321289</v>
+        <v>4.06680631637573</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>4.2180962562561</v>
+        <v>4.21809577941895</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>4.21449375152588</v>
+        <v>4.21449422836304</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G892" t="n">
-        <v>4.17847299575806</v>
+        <v>4.17847347259521</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G896" t="n">
-        <v>4.27212810516357</v>
+        <v>4.27212858200073</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G899" t="n">
-        <v>4.31175184249878</v>
+        <v>4.31175136566162</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>4.26492404937744</v>
+        <v>4.2649245262146</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G905" t="n">
-        <v>4.39820337295532</v>
+        <v>4.39820289611816</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>4.11723613739014</v>
+        <v>4.11723661422729</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G912" t="n">
-        <v>4.06320476531982</v>
+        <v>4.06320428848267</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.89750719070435</v>
+        <v>3.89750671386719</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>3.77863621711731</v>
+        <v>3.77863597869873</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81826019287109</v>
+        <v>3.81825971603394</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G918" t="n">
-        <v>3.61654043197632</v>
+        <v>3.61654019355774</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G919" t="n">
-        <v>3.33413314819336</v>
+        <v>3.3341326713562</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.5</v>
       </c>
       <c r="G921" t="n">
-        <v>3.24191904067993</v>
+        <v>3.24191856384277</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G923" t="n">
-        <v>2.86585569381714</v>
+        <v>2.86585593223572</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G924" t="n">
-        <v>2.68863105773926</v>
+        <v>2.68863129615784</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G925" t="n">
-        <v>2.70448040962219</v>
+        <v>2.70448064804077</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.75</v>
       </c>
       <c r="G926" t="n">
-        <v>2.70159888267517</v>
+        <v>2.70159912109375</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G927" t="n">
-        <v>2.58921241760254</v>
+        <v>2.58921217918396</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G929" t="n">
-        <v>2.45809459686279</v>
+        <v>2.45809483528137</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G932" t="n">
-        <v>2.87306022644043</v>
+        <v>2.87305998802185</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G935" t="n">
-        <v>2.89035081863403</v>
+        <v>2.89035058021545</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>2.93933916091919</v>
+        <v>2.93933939933777</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G939" t="n">
-        <v>2.89035081863403</v>
+        <v>2.89035058021545</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96815657615662</v>
+        <v>2.96815633773804</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98976922035217</v>
+        <v>2.98976945877075</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G944" t="n">
-        <v>2.94798469543457</v>
+        <v>2.94798445701599</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G954" t="n">
-        <v>2.94654393196106</v>
+        <v>2.94654417037964</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G955" t="n">
-        <v>2.94654393196106</v>
+        <v>2.94654417037964</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G957" t="n">
-        <v>2.85576987266541</v>
+        <v>2.85577011108398</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>2.8528881072998</v>
+        <v>2.85288834571838</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G972" t="n">
-        <v>3.12404489517212</v>
+        <v>3.12404465675354</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>3.09521675109863</v>
+        <v>3.09521698951721</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G976" t="n">
-        <v>3.0861132144928</v>
+        <v>3.08611345291138</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G977" t="n">
-        <v>3.26363348960876</v>
+        <v>3.26363325119019</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G979" t="n">
-        <v>3.46694660186768</v>
+        <v>3.4669463634491</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.33797883987427</v>
+        <v>3.33797931671143</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G984" t="n">
-        <v>3.12404489517212</v>
+        <v>3.12404465675354</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>3.13466548919678</v>
+        <v>3.13466596603394</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>3.10280346870422</v>
+        <v>3.1028037071228</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G995" t="n">
-        <v>3.07245802879333</v>
+        <v>3.07245826721191</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G996" t="n">
-        <v>3.07245802879333</v>
+        <v>3.07245826721191</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G997" t="n">
-        <v>3.04363012313843</v>
+        <v>3.04362988471985</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G998" t="n">
-        <v>3.07245802879333</v>
+        <v>3.07245826721191</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.17714929580688</v>
+        <v>3.17714953422546</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.04059529304504</v>
+        <v>3.04059553146362</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.80086779594421</v>
+        <v>2.80086755752563</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.68555569648743</v>
+        <v>2.68555593490601</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.67038321495056</v>
+        <v>2.67038297653198</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.63852071762085</v>
+        <v>2.63852047920227</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.62486553192139</v>
+        <v>2.62486529350281</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.61576175689697</v>
+        <v>2.61576151847839</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.6461067199707</v>
+        <v>2.64610695838928</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.74928116798401</v>
+        <v>2.74928092956543</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.73562550544739</v>
+        <v>2.73562526702881</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.7659707069397</v>
+        <v>2.76597094535828</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.89645528793335</v>
+        <v>2.89645552635193</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.7705225944519</v>
+        <v>2.77052235603333</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.69921112060547</v>
+        <v>2.69921135902405</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.67038321495056</v>
+        <v>2.67038297653198</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.67190027236938</v>
+        <v>2.67190074920654</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.74624633789062</v>
+        <v>2.74624609947205</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.7083146572113</v>
+        <v>2.70831489562988</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.57176113128662</v>
+        <v>2.5717613697052</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.57176113128662</v>
+        <v>2.5717613697052</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.5125880241394</v>
+        <v>2.51258778572083</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.55051946640015</v>
+        <v>2.55051922798157</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.45644927024841</v>
+        <v>2.45644903182983</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.36844778060913</v>
+        <v>2.36844801902771</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.40637969970703</v>
+        <v>2.40637946128845</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.40334486961365</v>
+        <v>2.40334510803223</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38513779640198</v>
+        <v>2.38513803482056</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.39120697975159</v>
+        <v>2.39120674133301</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.31382632255554</v>
+        <v>2.31382656097412</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.23796319961548</v>
+        <v>2.2379629611969</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.35327506065369</v>
+        <v>2.35327529907227</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.32444715499878</v>
+        <v>2.3244469165802</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.37603402137756</v>
+        <v>2.37603425979614</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.34113717079163</v>
+        <v>2.34113693237305</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.74017715454102</v>
+        <v>2.74017763137817</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.77962613105774</v>
+        <v>2.7796266078949</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.80086779594421</v>
+        <v>2.80086755752563</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.82059216499329</v>
+        <v>2.82059240341187</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.81452345848083</v>
+        <v>2.81452322006226</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.69921112060547</v>
+        <v>2.69921135902405</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.67796969413757</v>
+        <v>2.67796945571899</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.47199988365173</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.63396859169006</v>
+        <v>2.63396883010864</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.62486553192139</v>
+        <v>2.62486529350281</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.7083146572113</v>
+        <v>2.70831489562988</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.72955656051636</v>
+        <v>2.72955632209778</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.72955656051636</v>
+        <v>2.72955632209778</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.58693361282349</v>
+        <v>2.58693385124207</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.55051946640015</v>
+        <v>2.55051922798157</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.57631301879883</v>
+        <v>2.57631278038025</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.65065860748291</v>
+        <v>2.65065884590149</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.6567280292511</v>
+        <v>2.65672779083252</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.69465923309326</v>
+        <v>2.69465947151184</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.84183430671692</v>
+        <v>2.84183406829834</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.84486842155457</v>
+        <v>2.84486865997314</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.87521386146545</v>
+        <v>2.87521362304688</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.94197344779968</v>
+        <v>2.94197368621826</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.12101006507874</v>
+        <v>3.12101030349731</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.99052572250366</v>
+        <v>2.99052596092224</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.9374213218689</v>
+        <v>2.93742156028748</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.13314867019653</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.24087405204773</v>
+        <v>3.24087429046631</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.30004739761353</v>
+        <v>3.3000476360321</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.28335785865784</v>
+        <v>3.28335762023926</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.2120463848114</v>
+        <v>3.21204614639282</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.18321824073792</v>
+        <v>3.18321847915649</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.18321824073792</v>
+        <v>3.18321847915649</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.17714929580688</v>
+        <v>3.17714953422546</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.146803855896</v>
+        <v>3.14680361747742</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.0861132144928</v>
+        <v>3.08611345291138</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.05273389816284</v>
+        <v>3.05273365974426</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.00873279571533</v>
+        <v>3.00873303413391</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.02542304992676</v>
+        <v>3.02542281150818</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.95107674598694</v>
+        <v>2.95107698440552</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.93135261535645</v>
+        <v>2.93135237693787</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.93590450286865</v>
+        <v>2.93590426445007</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.90404200553894</v>
+        <v>2.90404176712036</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.91921424865723</v>
+        <v>2.91921448707581</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.89645528793335</v>
+        <v>2.89645552635193</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.89645528793335</v>
+        <v>2.89645552635193</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.84638595581055</v>
+        <v>2.84638571739197</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.8645932674408</v>
+        <v>2.86459302902222</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.82059216499329</v>
+        <v>2.82059240341187</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.0663890838623</v>
+        <v>3.06638884544373</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.10280346870422</v>
+        <v>3.1028037071228</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.11190676689148</v>
+        <v>3.11190700531006</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.12101006507874</v>
+        <v>3.12101030349731</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.1498384475708</v>
+        <v>3.14983820915222</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.16197657585144</v>
+        <v>3.16197681427002</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.10887217521667</v>
+        <v>3.10887241363525</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.13314867019653</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.03149175643921</v>
+        <v>3.03149199485779</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.90707635879517</v>
+        <v>2.90707612037659</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.89645528793335</v>
+        <v>2.89645552635193</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.90404200553894</v>
+        <v>2.90404176712036</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.87066173553467</v>
+        <v>2.87066197395325</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.89493823051453</v>
+        <v>2.89493799209595</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.80997157096863</v>
+        <v>2.80997133255005</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.86155819892883</v>
+        <v>2.86155843734741</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.87066173553467</v>
+        <v>2.87066197395325</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.99052572250366</v>
+        <v>2.99052596092224</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.9374213218689</v>
+        <v>2.93742156028748</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.88431715965271</v>
+        <v>2.88431739807129</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.87066173553467</v>
+        <v>2.87066197395325</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.87066173553467</v>
+        <v>2.87066197395325</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.88431715965271</v>
+        <v>2.88431739807129</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.87369632720947</v>
+        <v>2.87369656562805</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.88128304481506</v>
+        <v>2.88128280639648</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.87673115730286</v>
+        <v>2.87673139572144</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.82362675666809</v>
+        <v>2.82362651824951</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.78721261024475</v>
+        <v>2.78721237182617</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.74624633789062</v>
+        <v>2.74624609947205</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.87824845314026</v>
+        <v>2.87824821472168</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.97231864929199</v>
+        <v>2.97231841087341</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.13314867019653</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.0390784740448</v>
+        <v>3.03907823562622</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.05273389816284</v>
+        <v>3.05273365974426</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.87521386146545</v>
+        <v>2.87521362304688</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.92073154449463</v>
+        <v>2.92073130607605</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.19990801811218</v>
+        <v>3.19990825653076</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.99659490585327</v>
+        <v>2.99659466743469</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.95107674598694</v>
+        <v>2.95107698440552</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.94652533531189</v>
+        <v>2.94652509689331</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.77810883522034</v>
+        <v>2.77810859680176</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.84638595581055</v>
+        <v>2.84638571739197</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.92073154449463</v>
+        <v>2.92073130607605</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1366" t="n">
-        <v>2.91921424865723</v>
+        <v>2.91921448707581</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1367" t="n">
-        <v>2.87673115730286</v>
+        <v>2.87673139572144</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1369" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.84942030906677</v>
+        <v>2.84942007064819</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.86155819892883</v>
+        <v>2.86155843734741</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.94197344779968</v>
+        <v>2.94197368621826</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1378" t="n">
-        <v>2.95107674598694</v>
+        <v>2.95107698440552</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.97231864929199</v>
+        <v>2.97231841087341</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.98142194747925</v>
+        <v>2.98142218589783</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.12101006507874</v>
+        <v>3.12101030349731</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.10887217521667</v>
+        <v>3.10887241363525</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.146803855896</v>
+        <v>3.14680361747742</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.146803855896</v>
+        <v>3.14680361747742</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.11797595024109</v>
+        <v>3.11797571182251</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.04363012313843</v>
+        <v>3.04362988471985</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.08459615707397</v>
+        <v>3.0845959186554</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.15590739250183</v>
+        <v>3.15590715408325</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.0648717880249</v>
+        <v>3.06487154960632</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.15590739250183</v>
+        <v>3.15590715408325</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.23935723304749</v>
+        <v>3.23935699462891</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.16197657585144</v>
+        <v>3.16197681427002</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.14832091331482</v>
+        <v>3.1483211517334</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.07852745056152</v>
+        <v>3.07852721214294</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.11494159698486</v>
+        <v>3.11494135856628</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.11494159698486</v>
+        <v>3.11494135856628</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.00569820404053</v>
+        <v>3.00569844245911</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.77507448196411</v>
+        <v>2.77507424354553</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.68555569648743</v>
+        <v>2.68555593490601</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.78266048431396</v>
+        <v>2.78266072273254</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.91921424865723</v>
+        <v>2.91921448707581</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.87369632720947</v>
+        <v>2.87369656562805</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.05576777458191</v>
+        <v>3.05576801300049</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.05576777458191</v>
+        <v>3.05576801300049</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.2120463848114</v>
+        <v>3.21204614639282</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.24846029281616</v>
+        <v>3.24846076965332</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.18018341064453</v>
+        <v>3.18018364906311</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.40929007530212</v>
+        <v>3.40929055213928</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.41535925865173</v>
+        <v>3.41535949707031</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.55646514892578</v>
+        <v>3.5564649105072</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.41991090774536</v>
+        <v>3.41991114616394</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.36225557327271</v>
+        <v>3.36225533485413</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.37591075897217</v>
+        <v>3.37591052055359</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.33797883987427</v>
+        <v>3.33797931671143</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.34253096580505</v>
+        <v>3.34253072738647</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.31066846847534</v>
+        <v>3.31066799163818</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.35466861724854</v>
+        <v>3.35466885566711</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.19535613059998</v>
+        <v>3.1953558921814</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.25</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.22418403625488</v>
+        <v>3.22418427467346</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.29094386100769</v>
+        <v>3.29094362258911</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.19535613059998</v>
+        <v>3.1953558921814</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.30459928512573</v>
+        <v>3.30459904670715</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.23177051544189</v>
+        <v>3.23177075386047</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.23935723304749</v>
+        <v>3.23935699462891</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.2363224029541</v>
+        <v>3.23632216453552</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.30004739761353</v>
+        <v>3.3000476360321</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.24087405204773</v>
+        <v>3.24087429046631</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.2621157169342</v>
+        <v>3.26211595535278</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24087405204773</v>
+        <v>3.24087429046631</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.0663890838623</v>
+        <v>3.06638884544373</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.05576777458191</v>
+        <v>3.05576801300049</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.09218263626099</v>
+        <v>3.09218239784241</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.07549262046814</v>
+        <v>3.07549238204956</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.13314867019653</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.19535613059998</v>
+        <v>3.1953558921814</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.12252759933472</v>
+        <v>3.1225278377533</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.07852745056152</v>
+        <v>3.07852721214294</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.02542304992676</v>
+        <v>3.02542281150818</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.99052572250366</v>
+        <v>2.99052596092224</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.97080135345459</v>
+        <v>2.97080111503601</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.0390784740448</v>
+        <v>3.03907823562622</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.05273389816284</v>
+        <v>3.05273365974426</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.10280346870422</v>
+        <v>3.1028037071228</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.11797595024109</v>
+        <v>3.11797571182251</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.19990801811218</v>
+        <v>3.19990825653076</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.16956281661987</v>
+        <v>3.16956257820129</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.23480486869812</v>
+        <v>3.2348051071167</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.31977152824402</v>
+        <v>3.3197717666626</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.28790950775146</v>
+        <v>3.28790974617004</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.23177051544189</v>
+        <v>3.23177075386047</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.23935723304749</v>
+        <v>3.23935699462891</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.17866659164429</v>
+        <v>3.17866635322571</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.20749425888062</v>
+        <v>3.20749449729919</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11190676689148</v>
+        <v>3.11190700531006</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.11797595024109</v>
+        <v>3.11797571182251</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.05425095558167</v>
+        <v>3.05425119400024</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.19535613059998</v>
+        <v>3.1953558921814</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.13466548919678</v>
+        <v>3.13466596603394</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.83121299743652</v>
+        <v>2.8312132358551</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.84638595581055</v>
+        <v>2.84638571739197</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210969924927</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.99969625473022</v>
+        <v>2.9996964931488</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.00751209259033</v>
+        <v>3.00751233100891</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.96374368667603</v>
+        <v>2.9637439250946</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.02626967430115</v>
+        <v>3.02626991271973</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.982501745224</v>
+        <v>2.98250150680542</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.17164373397827</v>
+        <v>3.17164349555969</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.27637457847595</v>
+        <v>3.27637481689453</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.31545424461365</v>
+        <v>3.31545376777649</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.25605368614197</v>
+        <v>3.25605392456055</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.34671664237976</v>
+        <v>3.34671711921692</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.3045117855072</v>
+        <v>3.30451202392578</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.33264827728271</v>
+        <v>3.33264851570129</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.36078524589539</v>
+        <v>3.36078548431396</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>4.31400012969971</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.37172746658325</v>
+        <v>3.37172770500183</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.28731679916382</v>
+        <v>3.2873170375824</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.30138564109802</v>
+        <v>3.30138516426086</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>4.25</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.32170605659485</v>
+        <v>3.32170629501343</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.31389021873474</v>
+        <v>3.31389045715332</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.31701683998108</v>
+        <v>3.31701707839966</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.27793788909912</v>
+        <v>3.27793765068054</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.14819598197937</v>
+        <v>3.14819622039795</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.13256430625916</v>
+        <v>3.13256454467773</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.16851735115051</v>
+        <v>3.16851711273193</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.27481198310852</v>
+        <v>3.27481174468994</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.25761699676514</v>
+        <v>3.25761723518372</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.31701683998108</v>
+        <v>3.31701707839966</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.28731679916382</v>
+        <v>3.2873170375824</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.33890080451965</v>
+        <v>3.33890104293823</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.38423252105713</v>
+        <v>3.38423228263855</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>4.25</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.32170605659485</v>
+        <v>3.32170629501343</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.31389021873474</v>
+        <v>3.31389045715332</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.3045117855072</v>
+        <v>3.30451202392578</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.34359073638916</v>
+        <v>3.343590259552</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>4.34600019454956</v>
       </c>
       <c r="G1662" t="n">
-        <v>3.39673829078674</v>
+        <v>3.39673805236816</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1664" t="n">
-        <v>3.41549587249756</v>
+        <v>3.41549563407898</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.37797999382019</v>
+        <v>3.37798023223877</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.38423252105713</v>
+        <v>3.38423228263855</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G1668" t="n">
-        <v>3.23729634284973</v>
+        <v>3.23729610443115</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1669" t="n">
-        <v>3.25761699676514</v>
+        <v>3.25761723518372</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G1671" t="n">
-        <v>3.25605368614197</v>
+        <v>3.25605392456055</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1673" t="n">
-        <v>3.19196438789368</v>
+        <v>3.19196462631226</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1674" t="n">
-        <v>3.18571209907532</v>
+        <v>3.18571186065674</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.14663290977478</v>
+        <v>3.14663314819336</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.17945909500122</v>
+        <v>3.1794593334198</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.20915937423706</v>
+        <v>3.20915913581848</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.22791719436646</v>
+        <v>3.22791695594788</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.26543283462524</v>
+        <v>3.26543259620667</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.26543283462524</v>
+        <v>3.26543259620667</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.24511170387268</v>
+        <v>3.2451114654541</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.27481198310852</v>
+        <v>3.27481174468994</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.27324867248535</v>
+        <v>3.27324891090393</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.23729634284973</v>
+        <v>3.23729610443115</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.15757513046265</v>
+        <v>3.15757489204407</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.08410692214966</v>
+        <v>3.08410668373108</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.95592784881592</v>
+        <v>2.9559280872345</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92779135704041</v>
+        <v>2.92779111862183</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.00907516479492</v>
+        <v>3.00907492637634</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.13100171089172</v>
+        <v>3.13100147247314</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.21697497367859</v>
+        <v>3.21697521209717</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.21228575706482</v>
+        <v>3.21228551864624</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.21228575706482</v>
+        <v>3.21228551864624</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.24354839324951</v>
+        <v>3.24354863166809</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.27950143814087</v>
+        <v>3.27950167655945</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.29982233047485</v>
+        <v>3.29982256889343</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>4.25</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.32170605659485</v>
+        <v>3.32170629501343</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.21541142463684</v>
+        <v>3.21541166305542</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.22791719436646</v>
+        <v>3.22791695594788</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.13569116592407</v>
+        <v>3.13569092750549</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.17945909500122</v>
+        <v>3.1794593334198</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.17945909500122</v>
+        <v>3.1794593334198</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.18571209907532</v>
+        <v>3.18571186065674</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.19196438789368</v>
+        <v>3.19196462631226</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08723306655884</v>
+        <v>3.08723282814026</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.13256430625916</v>
+        <v>3.13256454467773</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.17164373397827</v>
+        <v>3.17164349555969</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.12318563461304</v>
+        <v>3.12318587303162</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.09661173820496</v>
+        <v>3.09661197662354</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.10442757606506</v>
+        <v>3.10442781448364</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.1169331073761</v>
+        <v>3.11693286895752</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1754" t="n">
-        <v>3.15913820266724</v>
+        <v>3.15913796424866</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.035649061203</v>
+        <v>3.03564882278442</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.04346489906311</v>
+        <v>3.04346466064453</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.06222248077393</v>
+        <v>3.06222224235535</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.02626967430115</v>
+        <v>3.02626991271973</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.04033827781677</v>
+        <v>3.04033851623535</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.02001762390137</v>
+        <v>3.02001738548279</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.03721213340759</v>
+        <v>3.03721189498901</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.04346489906311</v>
+        <v>3.04346466064453</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.06065940856934</v>
+        <v>3.06065917015076</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.00907516479492</v>
+        <v>3.00907492637634</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.95592784881592</v>
+        <v>2.9559280872345</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.90590667724609</v>
+        <v>2.90590691566467</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.88245940208435</v>
+        <v>2.88245964050293</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.88245940208435</v>
+        <v>2.88245964050293</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.89496493339539</v>
+        <v>2.89496469497681</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.89496493339539</v>
+        <v>2.89496469497681</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.90590667724609</v>
+        <v>2.90590691566467</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.85901236534119</v>
+        <v>2.85901212692261</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.82305955886841</v>
+        <v>2.82305979728699</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.82931232452393</v>
+        <v>2.82931208610535</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.81211757659912</v>
+        <v>2.81211733818054</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>3.45799994468689</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.70269656181335</v>
+        <v>2.70269680023193</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.72301769256592</v>
+        <v>2.7230179309845</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.73864936828613</v>
+        <v>2.73864912986755</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.70425987243652</v>
+        <v>2.70425963401794</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.54950737953186</v>
+        <v>2.54950761795044</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.49792313575745</v>
+        <v>2.49792337417603</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.48454165458679</v>
+        <v>2.48454141616821</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.61951637268066</v>
+        <v>2.61951661109924</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.68950319290161</v>
+        <v>2.68950343132019</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.73116230964661</v>
+        <v>2.73116254806519</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.74782609939575</v>
+        <v>2.74782633781433</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.73116230964661</v>
+        <v>2.73116254806519</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.74782609939575</v>
+        <v>2.74782633781433</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.75782442092896</v>
+        <v>2.75782418251038</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.72949624061584</v>
+        <v>2.72949600219727</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.71949768066406</v>
+        <v>2.71949791908264</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.69616889953613</v>
+        <v>2.69616913795471</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.73116230964661</v>
+        <v>2.73116254806519</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.75782442092896</v>
+        <v>2.75782418251038</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.82447862625122</v>
+        <v>2.8244788646698</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.84780740737915</v>
+        <v>2.84780764579773</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.81781315803528</v>
+        <v>2.8178129196167</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.73282861709595</v>
+        <v>2.73282885551453</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.8328104019165</v>
+        <v>2.83281064033508</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.8328104019165</v>
+        <v>2.83281064033508</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.8328104019165</v>
+        <v>2.83281064033508</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.82447862625122</v>
+        <v>2.8244788646698</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.84114241600037</v>
+        <v>2.84114217758179</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.71449899673462</v>
+        <v>2.71449875831604</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.73282861709595</v>
+        <v>2.73282885551453</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.73116230964661</v>
+        <v>2.73116254806519</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.77282166481018</v>
+        <v>2.7728214263916</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.71783137321472</v>
+        <v>2.7178316116333</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.72449684143066</v>
+        <v>2.72449707984924</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.70116829872131</v>
+        <v>2.70116806030273</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.7095000743866</v>
+        <v>2.70949983596802</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.74782609939575</v>
+        <v>2.74782633781433</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.75282502174377</v>
+        <v>2.75282526016235</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.73282861709595</v>
+        <v>2.73282885551453</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.12275695800781</v>
+        <v>3.12275671958923</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.1394202709198</v>
+        <v>3.13942050933838</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.23773550987244</v>
+        <v>3.23773527145386</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.21607279777527</v>
+        <v>3.21607303619385</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.17941331863403</v>
+        <v>3.17941308021545</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.12275695800781</v>
+        <v>3.12275671958923</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.20607495307922</v>
+        <v>3.20607471466064</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.1860785484314</v>
+        <v>3.18607831001282</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.3110556602478</v>
+        <v>3.31105542182922</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.31772089004517</v>
+        <v>3.31772065162659</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.34104990959167</v>
+        <v>3.34105014801025</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.31772089004517</v>
+        <v>3.31772065162659</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -67946,6 +67946,32 @@
         <v>4.79199981689453</v>
       </c>
       <c r="H2599" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2600" t="n">
+        <v>332485</v>
+      </c>
+      <c r="C2600" t="n">
+        <v>4.83400011062622</v>
+      </c>
+      <c r="D2600" t="n">
+        <v>4.75400018692017</v>
+      </c>
+      <c r="E2600" t="n">
+        <v>4.7960000038147</v>
+      </c>
+      <c r="F2600" t="n">
+        <v>4.80800008773804</v>
+      </c>
+      <c r="G2600" t="n">
+        <v>4.80800008773804</v>
+      </c>
+      <c r="H2600" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26321339607239</v>
+        <v>2.26321315765381</v>
       </c>
       <c r="H4" t="n">
         <v>8182968</v>
@@ -514,7 +514,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24304032325745</v>
+        <v>2.24304008483887</v>
       </c>
       <c r="H5" t="n">
         <v>6798460</v>
@@ -543,7 +543,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G6" t="n">
-        <v>2.30482149124146</v>
+        <v>2.3048210144043</v>
       </c>
       <c r="H6" t="n">
         <v>4016992</v>
@@ -659,7 +659,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33886408805847</v>
+        <v>2.33886432647705</v>
       </c>
       <c r="H10" t="n">
         <v>883891</v>
@@ -688,7 +688,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33886408805847</v>
+        <v>2.33886432647705</v>
       </c>
       <c r="H11" t="n">
         <v>2186928</v>
@@ -746,7 +746,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34895086288452</v>
+        <v>2.3489511013031</v>
       </c>
       <c r="H13" t="n">
         <v>1874026</v>
@@ -775,7 +775,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G14" t="n">
-        <v>2.37921118736267</v>
+        <v>2.37921142578125</v>
       </c>
       <c r="H14" t="n">
         <v>2690138</v>
@@ -833,7 +833,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>2.30734324455261</v>
+        <v>2.30734348297119</v>
       </c>
       <c r="H16" t="n">
         <v>1485896</v>
@@ -862,7 +862,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26951789855957</v>
+        <v>2.26951766014099</v>
       </c>
       <c r="H17" t="n">
         <v>1072096</v>
@@ -891,7 +891,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.30734324455261</v>
+        <v>2.30734348297119</v>
       </c>
       <c r="H18" t="n">
         <v>911844</v>
@@ -949,7 +949,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.31112575531006</v>
+        <v>2.31112551689148</v>
       </c>
       <c r="H20" t="n">
         <v>526824</v>
@@ -1007,7 +1007,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2972559928894</v>
+        <v>2.29725646972656</v>
       </c>
       <c r="H22" t="n">
         <v>1078374</v>
@@ -1065,7 +1065,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.33508157730103</v>
+        <v>2.33508205413818</v>
       </c>
       <c r="H24" t="n">
         <v>434879</v>
@@ -1094,7 +1094,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877707481384</v>
       </c>
       <c r="H25" t="n">
         <v>276607</v>
@@ -1210,7 +1210,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G29" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H29" t="n">
         <v>796842</v>
@@ -1239,7 +1239,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>2.39560174942017</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H30" t="n">
         <v>934202</v>
@@ -1268,7 +1268,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G31" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H31" t="n">
         <v>738518</v>
@@ -1297,7 +1297,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G32" t="n">
-        <v>2.35903739929199</v>
+        <v>2.35903763771057</v>
       </c>
       <c r="H32" t="n">
         <v>1087468</v>
@@ -1326,7 +1326,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877707481384</v>
       </c>
       <c r="H33" t="n">
         <v>635450</v>
@@ -1413,7 +1413,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25060486793518</v>
+        <v>2.25060534477234</v>
       </c>
       <c r="H36" t="n">
         <v>2171688</v>
@@ -1442,7 +1442,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21782302856445</v>
+        <v>2.21782326698303</v>
       </c>
       <c r="H37" t="n">
         <v>2049268</v>
@@ -1500,7 +1500,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G39" t="n">
-        <v>2.2052149772644</v>
+        <v>2.20521473884583</v>
       </c>
       <c r="H39" t="n">
         <v>724649</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.20647573471069</v>
+        <v>2.20647549629211</v>
       </c>
       <c r="H40" t="n">
         <v>582571</v>
@@ -1558,7 +1558,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G41" t="n">
-        <v>2.22664904594421</v>
+        <v>2.22664928436279</v>
       </c>
       <c r="H41" t="n">
         <v>494397</v>
@@ -1587,7 +1587,7 @@
         <v>3.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.20647573471069</v>
+        <v>2.20647549629211</v>
       </c>
       <c r="H42" t="n">
         <v>671983</v>
@@ -1616,7 +1616,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>2.21908402442932</v>
+        <v>2.2190842628479</v>
       </c>
       <c r="H43" t="n">
         <v>692846</v>
@@ -1645,7 +1645,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G44" t="n">
-        <v>2.19638919830322</v>
+        <v>2.19638872146606</v>
       </c>
       <c r="H44" t="n">
         <v>845586</v>
@@ -1674,7 +1674,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G45" t="n">
-        <v>2.22034502029419</v>
+        <v>2.22034478187561</v>
       </c>
       <c r="H45" t="n">
         <v>679381</v>
@@ -1732,7 +1732,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22538828849792</v>
+        <v>2.22538876533508</v>
       </c>
       <c r="H47" t="n">
         <v>657985</v>
@@ -1761,7 +1761,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G48" t="n">
-        <v>2.23925757408142</v>
+        <v>2.2392578125</v>
       </c>
       <c r="H48" t="n">
         <v>716322</v>
@@ -1819,7 +1819,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.26951789855957</v>
+        <v>2.26951766014099</v>
       </c>
       <c r="H50" t="n">
         <v>664973</v>
@@ -1848,7 +1848,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26699590682983</v>
+        <v>2.26699614524841</v>
       </c>
       <c r="H51" t="n">
         <v>503049</v>
@@ -1877,7 +1877,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.23169255256653</v>
+        <v>2.23169207572937</v>
       </c>
       <c r="H52" t="n">
         <v>743120</v>
@@ -1906,7 +1906,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.21782302856445</v>
+        <v>2.21782326698303</v>
       </c>
       <c r="H53" t="n">
         <v>1181993</v>
@@ -1935,7 +1935,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G54" t="n">
-        <v>2.18378043174744</v>
+        <v>2.18378067016602</v>
       </c>
       <c r="H54" t="n">
         <v>792898</v>
@@ -1964,7 +1964,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G55" t="n">
-        <v>2.19134545326233</v>
+        <v>2.19134569168091</v>
       </c>
       <c r="H55" t="n">
         <v>308634</v>
@@ -1993,7 +1993,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G56" t="n">
-        <v>2.21151900291443</v>
+        <v>2.21151924133301</v>
       </c>
       <c r="H56" t="n">
         <v>170592</v>
@@ -2051,7 +2051,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G58" t="n">
-        <v>2.16108536720276</v>
+        <v>2.16108512878418</v>
       </c>
       <c r="H58" t="n">
         <v>856086</v>
@@ -2167,7 +2167,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G62" t="n">
-        <v>2.1787371635437</v>
+        <v>2.17873692512512</v>
       </c>
       <c r="H62" t="n">
         <v>1348975</v>
@@ -2196,7 +2196,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G63" t="n">
-        <v>2.1787371635437</v>
+        <v>2.17873692512512</v>
       </c>
       <c r="H63" t="n">
         <v>323909</v>
@@ -2254,7 +2254,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G65" t="n">
-        <v>2.14721608161926</v>
+        <v>2.1472156047821</v>
       </c>
       <c r="H65" t="n">
         <v>1473153</v>
@@ -2312,7 +2312,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H67" t="n">
         <v>887821</v>
@@ -2428,7 +2428,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G71" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H71" t="n">
         <v>213630</v>
@@ -2486,7 +2486,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>2.13082528114319</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H73" t="n">
         <v>768752</v>
@@ -2602,7 +2602,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G77" t="n">
-        <v>2.06778287887573</v>
+        <v>2.06778311729431</v>
       </c>
       <c r="H77" t="n">
         <v>1178471</v>
@@ -2660,7 +2660,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195899486542</v>
+        <v>1.97195887565613</v>
       </c>
       <c r="H79" t="n">
         <v>3135081</v>
@@ -2689,7 +2689,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93161177635193</v>
+        <v>1.93161165714264</v>
       </c>
       <c r="H80" t="n">
         <v>2685175</v>
@@ -2747,7 +2747,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>1.92908990383148</v>
+        <v>1.92909026145935</v>
       </c>
       <c r="H82" t="n">
         <v>1535844</v>
@@ -2776,7 +2776,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>1.92278599739075</v>
+        <v>1.92278587818146</v>
       </c>
       <c r="H83" t="n">
         <v>1876379</v>
@@ -2805,7 +2805,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G84" t="n">
-        <v>1.94800281524658</v>
+        <v>1.94800305366516</v>
       </c>
       <c r="H84" t="n">
         <v>3748342</v>
@@ -2892,7 +2892,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>1.92782914638519</v>
+        <v>1.92782926559448</v>
       </c>
       <c r="H87" t="n">
         <v>1922023</v>
@@ -2921,7 +2921,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G88" t="n">
-        <v>1.975741147995</v>
+        <v>1.97574126720428</v>
       </c>
       <c r="H88" t="n">
         <v>1064202</v>
@@ -2950,7 +2950,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G89" t="n">
-        <v>1.973219871521</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H89" t="n">
         <v>736410</v>
@@ -3095,7 +3095,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G94" t="n">
-        <v>1.97448039054871</v>
+        <v>1.97448074817657</v>
       </c>
       <c r="H94" t="n">
         <v>1497058</v>
@@ -3153,7 +3153,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G96" t="n">
-        <v>1.99213218688965</v>
+        <v>1.99213242530823</v>
       </c>
       <c r="H96" t="n">
         <v>3064119</v>
@@ -3182,7 +3182,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>1.973219871521</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H97" t="n">
         <v>1754313</v>
@@ -3240,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89126491546631</v>
+        <v>1.89126479625702</v>
       </c>
       <c r="H99" t="n">
         <v>3568973</v>
@@ -3269,7 +3269,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G100" t="n">
-        <v>1.89504754543304</v>
+        <v>1.89504742622375</v>
       </c>
       <c r="H100" t="n">
         <v>1788951</v>
@@ -3356,7 +3356,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G103" t="n">
-        <v>2.02113151550293</v>
+        <v>2.02113175392151</v>
       </c>
       <c r="H103" t="n">
         <v>877058</v>
@@ -3385,7 +3385,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G104" t="n">
-        <v>2.08921694755554</v>
+        <v>2.0892174243927</v>
       </c>
       <c r="H104" t="n">
         <v>8365602</v>
@@ -3414,7 +3414,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G105" t="n">
-        <v>2.05643534660339</v>
+        <v>2.05643558502197</v>
       </c>
       <c r="H105" t="n">
         <v>1912960</v>
@@ -3472,7 +3472,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G107" t="n">
-        <v>2.07030439376831</v>
+        <v>2.07030487060547</v>
       </c>
       <c r="H107" t="n">
         <v>701279</v>
@@ -3559,7 +3559,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G110" t="n">
-        <v>2.06778287887573</v>
+        <v>2.06778311729431</v>
       </c>
       <c r="H110" t="n">
         <v>677592</v>
@@ -3617,7 +3617,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G112" t="n">
-        <v>2.07913064956665</v>
+        <v>2.07913088798523</v>
       </c>
       <c r="H112" t="n">
         <v>627812</v>
@@ -3646,7 +3646,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G113" t="n">
-        <v>2.07030439376831</v>
+        <v>2.07030487060547</v>
       </c>
       <c r="H113" t="n">
         <v>483565</v>
@@ -3733,7 +3733,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H116" t="n">
         <v>959348</v>
@@ -3762,7 +3762,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G117" t="n">
-        <v>2.14469408988953</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H117" t="n">
         <v>680193</v>
@@ -3820,7 +3820,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H119" t="n">
         <v>854222</v>
@@ -3849,7 +3849,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.13082528114319</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H120" t="n">
         <v>713419</v>
@@ -3936,7 +3936,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>2.19008445739746</v>
+        <v>2.19008469581604</v>
       </c>
       <c r="H123" t="n">
         <v>976460</v>
@@ -3965,7 +3965,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G124" t="n">
-        <v>2.1673891544342</v>
+        <v>2.16738963127136</v>
       </c>
       <c r="H124" t="n">
         <v>711853</v>
@@ -4023,7 +4023,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G126" t="n">
-        <v>2.14847660064697</v>
+        <v>2.14847683906555</v>
       </c>
       <c r="H126" t="n">
         <v>602771</v>
@@ -4110,7 +4110,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15352010726929</v>
+        <v>2.15352034568787</v>
       </c>
       <c r="H129" t="n">
         <v>520370</v>
@@ -4139,7 +4139,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>2.13460731506348</v>
+        <v>2.13460755348206</v>
       </c>
       <c r="H130" t="n">
         <v>1255649</v>
@@ -4168,7 +4168,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G131" t="n">
-        <v>2.1119122505188</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H131" t="n">
         <v>982502</v>
@@ -4197,7 +4197,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>2.1119122505188</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H132" t="n">
         <v>983090</v>
@@ -4255,7 +4255,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G134" t="n">
-        <v>2.0425660610199</v>
+        <v>2.04256582260132</v>
       </c>
       <c r="H134" t="n">
         <v>446178</v>
@@ -4284,7 +4284,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G135" t="n">
-        <v>2.0425660610199</v>
+        <v>2.04256582260132</v>
       </c>
       <c r="H135" t="n">
         <v>1021203</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.0425660610199</v>
+        <v>2.04256582260132</v>
       </c>
       <c r="H138" t="n">
         <v>873840</v>
@@ -4400,7 +4400,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>1.99213218688965</v>
+        <v>1.99213242530823</v>
       </c>
       <c r="H139" t="n">
         <v>526097</v>
@@ -4429,7 +4429,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G140" t="n">
-        <v>1.97069752216339</v>
+        <v>1.97069811820984</v>
       </c>
       <c r="H140" t="n">
         <v>655592</v>
@@ -4487,7 +4487,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>2.01734900474548</v>
+        <v>2.01734924316406</v>
       </c>
       <c r="H142" t="n">
         <v>1211840</v>
@@ -4516,7 +4516,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>2.05643534660339</v>
+        <v>2.05643558502197</v>
       </c>
       <c r="H143" t="n">
         <v>591488</v>
@@ -4574,7 +4574,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G145" t="n">
-        <v>2.06400036811829</v>
+        <v>2.06400012969971</v>
       </c>
       <c r="H145" t="n">
         <v>430023</v>
@@ -4603,7 +4603,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.1119122505188</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H146" t="n">
         <v>1000881</v>
@@ -4632,7 +4632,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.13712954521179</v>
+        <v>2.13712906837463</v>
       </c>
       <c r="H147" t="n">
         <v>886586</v>
@@ -4719,7 +4719,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343357086182</v>
       </c>
       <c r="H150" t="n">
         <v>618937</v>
@@ -4777,7 +4777,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G152" t="n">
-        <v>2.12199926376343</v>
+        <v>2.12199902534485</v>
       </c>
       <c r="H152" t="n">
         <v>878730</v>
@@ -4893,7 +4893,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G156" t="n">
-        <v>2.13712954521179</v>
+        <v>2.13712906837463</v>
       </c>
       <c r="H156" t="n">
         <v>566431</v>
@@ -4980,7 +4980,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>2.13082528114319</v>
+        <v>2.13082504272461</v>
       </c>
       <c r="H159" t="n">
         <v>442504</v>
@@ -5038,7 +5038,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G161" t="n">
-        <v>2.14469408988953</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H161" t="n">
         <v>513353</v>
@@ -5067,7 +5067,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G162" t="n">
-        <v>2.16234636306763</v>
+        <v>2.16234612464905</v>
       </c>
       <c r="H162" t="n">
         <v>835730</v>
@@ -5096,7 +5096,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G163" t="n">
-        <v>2.16108536720276</v>
+        <v>2.16108512878418</v>
       </c>
       <c r="H163" t="n">
         <v>472501</v>
@@ -5125,7 +5125,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G164" t="n">
-        <v>2.14595556259155</v>
+        <v>2.14595508575439</v>
       </c>
       <c r="H164" t="n">
         <v>656848</v>
@@ -5154,7 +5154,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G165" t="n">
-        <v>2.17621493339539</v>
+        <v>2.17621564865112</v>
       </c>
       <c r="H165" t="n">
         <v>699653</v>
@@ -5183,7 +5183,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G166" t="n">
-        <v>2.1724328994751</v>
+        <v>2.17243266105652</v>
       </c>
       <c r="H166" t="n">
         <v>716925</v>
@@ -5241,7 +5241,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G168" t="n">
-        <v>2.33129906654358</v>
+        <v>2.33129930496216</v>
       </c>
       <c r="H168" t="n">
         <v>1990731</v>
@@ -5328,7 +5328,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G171" t="n">
-        <v>2.30734324455261</v>
+        <v>2.30734348297119</v>
       </c>
       <c r="H171" t="n">
         <v>1058400</v>
@@ -5357,7 +5357,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35147261619568</v>
+        <v>2.35147285461426</v>
       </c>
       <c r="H172" t="n">
         <v>1771997</v>
@@ -5386,7 +5386,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G173" t="n">
-        <v>2.37290692329407</v>
+        <v>2.37290668487549</v>
       </c>
       <c r="H173" t="n">
         <v>970626</v>
@@ -5415,7 +5415,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40190649032593</v>
+        <v>2.40190601348877</v>
       </c>
       <c r="H174" t="n">
         <v>1365898</v>
@@ -5444,7 +5444,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G175" t="n">
-        <v>2.35399413108826</v>
+        <v>2.35399436950684</v>
       </c>
       <c r="H175" t="n">
         <v>1120304</v>
@@ -5473,7 +5473,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877707481384</v>
       </c>
       <c r="H176" t="n">
         <v>959599</v>
@@ -5531,7 +5531,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G178" t="n">
-        <v>2.40316724777222</v>
+        <v>2.4031674861908</v>
       </c>
       <c r="H178" t="n">
         <v>2956792</v>
@@ -5560,7 +5560,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G179" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H179" t="n">
         <v>1073722</v>
@@ -5618,7 +5618,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G181" t="n">
-        <v>2.39181923866272</v>
+        <v>2.3918194770813</v>
       </c>
       <c r="H181" t="n">
         <v>1136549</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>2.39560174942017</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H183" t="n">
         <v>1547599</v>
@@ -5705,7 +5705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>2.39560174942017</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H184" t="n">
         <v>1699128</v>
@@ -5734,7 +5734,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G185" t="n">
-        <v>2.37164616584778</v>
+        <v>2.37164640426636</v>
       </c>
       <c r="H185" t="n">
         <v>808007</v>
@@ -5792,7 +5792,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H187" t="n">
         <v>1275111</v>
@@ -5850,7 +5850,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G189" t="n">
-        <v>2.36534214019775</v>
+        <v>2.36534190177917</v>
       </c>
       <c r="H189" t="n">
         <v>713369</v>
@@ -5966,7 +5966,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G193" t="n">
-        <v>2.35525488853455</v>
+        <v>2.35525560379028</v>
       </c>
       <c r="H193" t="n">
         <v>554537</v>
@@ -6140,7 +6140,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39560174942017</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H199" t="n">
         <v>1166747</v>
@@ -6198,7 +6198,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>2.41451454162598</v>
+        <v>2.41451478004456</v>
       </c>
       <c r="H201" t="n">
         <v>963400</v>
@@ -6227,7 +6227,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.4523401260376</v>
+        <v>2.45234036445618</v>
       </c>
       <c r="H202" t="n">
         <v>1065606</v>
@@ -6256,7 +6256,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G203" t="n">
-        <v>2.43847060203552</v>
+        <v>2.43847107887268</v>
       </c>
       <c r="H203" t="n">
         <v>749019</v>
@@ -6314,7 +6314,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G205" t="n">
-        <v>2.44603610038757</v>
+        <v>2.44603586196899</v>
       </c>
       <c r="H205" t="n">
         <v>915733</v>
@@ -6343,7 +6343,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.4586443901062</v>
+        <v>2.45864415168762</v>
       </c>
       <c r="H206" t="n">
         <v>901759</v>
@@ -6372,7 +6372,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.44603610038757</v>
+        <v>2.44603586196899</v>
       </c>
       <c r="H207" t="n">
         <v>364301</v>
@@ -6430,7 +6430,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G209" t="n">
-        <v>2.41451454162598</v>
+        <v>2.41451478004456</v>
       </c>
       <c r="H209" t="n">
         <v>3815639</v>
@@ -6546,7 +6546,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G213" t="n">
-        <v>2.46826934814453</v>
+        <v>2.46826958656311</v>
       </c>
       <c r="H213" t="n">
         <v>1893893</v>
@@ -6604,7 +6604,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G215" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721167564392</v>
       </c>
       <c r="H215" t="n">
         <v>1570341</v>
@@ -6662,7 +6662,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>2.46694684028625</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H217" t="n">
         <v>1320391</v>
@@ -6691,7 +6691,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G218" t="n">
-        <v>2.48149681091309</v>
+        <v>2.48149704933167</v>
       </c>
       <c r="H218" t="n">
         <v>2972831</v>
@@ -6836,7 +6836,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G223" t="n">
-        <v>2.46562385559082</v>
+        <v>2.4656240940094</v>
       </c>
       <c r="H223" t="n">
         <v>1097041</v>
@@ -6894,7 +6894,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G225" t="n">
-        <v>2.52250242233276</v>
+        <v>2.52250266075134</v>
       </c>
       <c r="H225" t="n">
         <v>1838179</v>
@@ -6923,7 +6923,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G226" t="n">
-        <v>2.48546528816223</v>
+        <v>2.48546504974365</v>
       </c>
       <c r="H226" t="n">
         <v>1137067</v>
@@ -6952,7 +6952,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G227" t="n">
-        <v>2.50530695915222</v>
+        <v>2.50530672073364</v>
       </c>
       <c r="H227" t="n">
         <v>982862</v>
@@ -7039,7 +7039,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>2.46694684028625</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H230" t="n">
         <v>3703950</v>
@@ -7126,7 +7126,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G233" t="n">
-        <v>2.47620582580566</v>
+        <v>2.47620606422424</v>
       </c>
       <c r="H233" t="n">
         <v>1547243</v>
@@ -7155,7 +7155,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H234" t="n">
         <v>365542</v>
@@ -7271,7 +7271,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G238" t="n">
-        <v>2.45239639282227</v>
+        <v>2.45239615440369</v>
       </c>
       <c r="H238" t="n">
         <v>975866</v>
@@ -7358,7 +7358,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46033263206482</v>
+        <v>2.46033310890198</v>
       </c>
       <c r="H241" t="n">
         <v>454792</v>
@@ -7416,7 +7416,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>2.46694684028625</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H243" t="n">
         <v>279712</v>
@@ -7503,7 +7503,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>2.46694684028625</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H246" t="n">
         <v>235874</v>
@@ -7561,7 +7561,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46562385559082</v>
+        <v>2.4656240940094</v>
       </c>
       <c r="H248" t="n">
         <v>879735</v>
@@ -7619,7 +7619,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>2.44578218460083</v>
+        <v>2.44578242301941</v>
       </c>
       <c r="H250" t="n">
         <v>1123635</v>
@@ -7706,7 +7706,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>2.44975090026855</v>
+        <v>2.44975113868713</v>
       </c>
       <c r="H253" t="n">
         <v>622270</v>
@@ -7735,7 +7735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>2.45371890068054</v>
+        <v>2.45371866226196</v>
       </c>
       <c r="H254" t="n">
         <v>628873</v>
@@ -7764,7 +7764,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488307952881</v>
       </c>
       <c r="H255" t="n">
         <v>460966</v>
@@ -7793,7 +7793,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G256" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488307952881</v>
       </c>
       <c r="H256" t="n">
         <v>262852</v>
@@ -7822,7 +7822,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.46033263206482</v>
+        <v>2.46033310890198</v>
       </c>
       <c r="H257" t="n">
         <v>563597</v>
@@ -7851,7 +7851,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H258" t="n">
         <v>335894</v>
@@ -7880,7 +7880,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G259" t="n">
-        <v>2.50927472114563</v>
+        <v>2.50927495956421</v>
       </c>
       <c r="H259" t="n">
         <v>381908</v>
@@ -7938,7 +7938,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G261" t="n">
-        <v>2.5648307800293</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H261" t="n">
         <v>524937</v>
@@ -7967,7 +7967,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55689430236816</v>
+        <v>2.55689406394958</v>
       </c>
       <c r="H262" t="n">
         <v>748895</v>
@@ -7996,7 +7996,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G263" t="n">
-        <v>2.57144451141357</v>
+        <v>2.57144474983215</v>
       </c>
       <c r="H263" t="n">
         <v>328662</v>
@@ -8025,7 +8025,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G264" t="n">
-        <v>2.56218552589417</v>
+        <v>2.56218528747559</v>
       </c>
       <c r="H264" t="n">
         <v>625175</v>
@@ -8054,7 +8054,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G265" t="n">
-        <v>2.5648307800293</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H265" t="n">
         <v>514836</v>
@@ -8199,7 +8199,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G270" t="n">
-        <v>2.52382516860962</v>
+        <v>2.5238254070282</v>
       </c>
       <c r="H270" t="n">
         <v>321976</v>
@@ -8228,7 +8228,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>2.53308439254761</v>
+        <v>2.53308463096619</v>
       </c>
       <c r="H271" t="n">
         <v>286015</v>
@@ -8344,7 +8344,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H275" t="n">
         <v>409245</v>
@@ -8402,7 +8402,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H277" t="n">
         <v>374003</v>
@@ -8460,7 +8460,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G279" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488307952881</v>
       </c>
       <c r="H279" t="n">
         <v>167600</v>
@@ -8518,7 +8518,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G281" t="n">
-        <v>2.42858648300171</v>
+        <v>2.42858672142029</v>
       </c>
       <c r="H281" t="n">
         <v>622612</v>
@@ -8605,7 +8605,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G284" t="n">
-        <v>2.47752857208252</v>
+        <v>2.47752904891968</v>
       </c>
       <c r="H284" t="n">
         <v>405263</v>
@@ -8634,7 +8634,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G285" t="n">
-        <v>2.46959209442139</v>
+        <v>2.46959185600281</v>
       </c>
       <c r="H285" t="n">
         <v>426920</v>
@@ -8663,7 +8663,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G286" t="n">
-        <v>2.46430087089539</v>
+        <v>2.46430110931396</v>
       </c>
       <c r="H286" t="n">
         <v>238031</v>
@@ -8721,7 +8721,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G288" t="n">
-        <v>2.49869275093079</v>
+        <v>2.49869298934937</v>
       </c>
       <c r="H288" t="n">
         <v>633611</v>
@@ -8866,7 +8866,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G293" t="n">
-        <v>2.53440737724304</v>
+        <v>2.53440761566162</v>
       </c>
       <c r="H293" t="n">
         <v>472169</v>
@@ -8895,7 +8895,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G294" t="n">
-        <v>2.5304388999939</v>
+        <v>2.53043913841248</v>
       </c>
       <c r="H294" t="n">
         <v>973552</v>
@@ -8924,7 +8924,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G295" t="n">
-        <v>2.53176164627075</v>
+        <v>2.53176188468933</v>
       </c>
       <c r="H295" t="n">
         <v>569194</v>
@@ -8982,7 +8982,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G297" t="n">
-        <v>2.52779388427734</v>
+        <v>2.52779340744019</v>
       </c>
       <c r="H297" t="n">
         <v>420940</v>
@@ -9040,7 +9040,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G299" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721167564392</v>
       </c>
       <c r="H299" t="n">
         <v>254927</v>
@@ -9069,7 +9069,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53308439254761</v>
+        <v>2.53308463096619</v>
       </c>
       <c r="H300" t="n">
         <v>622766</v>
@@ -9127,7 +9127,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53969812393188</v>
+        <v>2.53969860076904</v>
       </c>
       <c r="H302" t="n">
         <v>350932</v>
@@ -9156,7 +9156,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.53969812393188</v>
+        <v>2.53969860076904</v>
       </c>
       <c r="H303" t="n">
         <v>764260</v>
@@ -9243,7 +9243,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G306" t="n">
-        <v>2.5992226600647</v>
+        <v>2.59922242164612</v>
       </c>
       <c r="H306" t="n">
         <v>581605</v>
@@ -9272,7 +9272,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G307" t="n">
-        <v>2.60583662986755</v>
+        <v>2.60583639144897</v>
       </c>
       <c r="H307" t="n">
         <v>525000</v>
@@ -9301,7 +9301,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60583662986755</v>
+        <v>2.60583639144897</v>
       </c>
       <c r="H308" t="n">
         <v>474886</v>
@@ -9330,7 +9330,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.57276773452759</v>
+        <v>2.57276749610901</v>
       </c>
       <c r="H309" t="n">
         <v>811458</v>
@@ -9359,7 +9359,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G310" t="n">
-        <v>2.58334970474243</v>
+        <v>2.58334946632385</v>
       </c>
       <c r="H310" t="n">
         <v>282406</v>
@@ -9388,7 +9388,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G311" t="n">
-        <v>2.59128570556641</v>
+        <v>2.59128618240356</v>
       </c>
       <c r="H311" t="n">
         <v>463030</v>
@@ -9417,7 +9417,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G312" t="n">
-        <v>2.5886402130127</v>
+        <v>2.58864068984985</v>
       </c>
       <c r="H312" t="n">
         <v>672881</v>
@@ -9446,7 +9446,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G313" t="n">
-        <v>2.62700033187866</v>
+        <v>2.62700057029724</v>
       </c>
       <c r="H313" t="n">
         <v>774969</v>
@@ -9475,7 +9475,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G314" t="n">
-        <v>2.6098051071167</v>
+        <v>2.60980463027954</v>
       </c>
       <c r="H314" t="n">
         <v>445032</v>
@@ -9504,7 +9504,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G315" t="n">
-        <v>2.6098051071167</v>
+        <v>2.60980463027954</v>
       </c>
       <c r="H315" t="n">
         <v>562538</v>
@@ -9562,7 +9562,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G317" t="n">
-        <v>2.67329716682434</v>
+        <v>2.67329668998718</v>
       </c>
       <c r="H317" t="n">
         <v>1408139</v>
@@ -9591,7 +9591,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G318" t="n">
-        <v>2.68917036056519</v>
+        <v>2.68917012214661</v>
       </c>
       <c r="H318" t="n">
         <v>660904</v>
@@ -9678,7 +9678,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>2.67858815193176</v>
+        <v>2.67858839035034</v>
       </c>
       <c r="H321" t="n">
         <v>476349</v>
@@ -9765,7 +9765,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G324" t="n">
-        <v>2.66932845115662</v>
+        <v>2.6693286895752</v>
       </c>
       <c r="H324" t="n">
         <v>337409</v>
@@ -9794,7 +9794,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G325" t="n">
-        <v>2.70504307746887</v>
+        <v>2.70504331588745</v>
       </c>
       <c r="H325" t="n">
         <v>687242</v>
@@ -9823,7 +9823,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G326" t="n">
-        <v>2.70504307746887</v>
+        <v>2.70504331588745</v>
       </c>
       <c r="H326" t="n">
         <v>753657</v>
@@ -9852,7 +9852,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G327" t="n">
-        <v>2.68784737586975</v>
+        <v>2.68784785270691</v>
       </c>
       <c r="H327" t="n">
         <v>473695</v>
@@ -9881,7 +9881,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G328" t="n">
-        <v>2.68784737586975</v>
+        <v>2.68784785270691</v>
       </c>
       <c r="H328" t="n">
         <v>332487</v>
@@ -9939,7 +9939,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>2.70504307746887</v>
+        <v>2.70504331588745</v>
       </c>
       <c r="H330" t="n">
         <v>618999</v>
@@ -9997,7 +9997,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G332" t="n">
-        <v>2.70107507705688</v>
+        <v>2.70107483863831</v>
       </c>
       <c r="H332" t="n">
         <v>431759</v>
@@ -10026,7 +10026,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G333" t="n">
-        <v>2.70107507705688</v>
+        <v>2.70107483863831</v>
       </c>
       <c r="H333" t="n">
         <v>1317493</v>
@@ -10055,7 +10055,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>2.65874671936035</v>
+        <v>2.65874648094177</v>
       </c>
       <c r="H334" t="n">
         <v>564957</v>
@@ -10171,7 +10171,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.85054659843445</v>
+        <v>2.85054683685303</v>
       </c>
       <c r="H338" t="n">
         <v>1428133</v>
@@ -10229,7 +10229,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G340" t="n">
-        <v>2.8875846862793</v>
+        <v>2.88758420944214</v>
       </c>
       <c r="H340" t="n">
         <v>1378600</v>
@@ -10316,7 +10316,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>2.94578552246094</v>
+        <v>2.94578528404236</v>
       </c>
       <c r="H343" t="n">
         <v>1446520</v>
@@ -10374,7 +10374,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G345" t="n">
-        <v>2.94843125343323</v>
+        <v>2.94843101501465</v>
       </c>
       <c r="H345" t="n">
         <v>1014769</v>
@@ -10403,7 +10403,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G346" t="n">
-        <v>2.97356367111206</v>
+        <v>2.9735631942749</v>
       </c>
       <c r="H346" t="n">
         <v>613331</v>
@@ -10432,7 +10432,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G347" t="n">
-        <v>2.96430444717407</v>
+        <v>2.96430420875549</v>
       </c>
       <c r="H347" t="n">
         <v>1313359</v>
@@ -10519,7 +10519,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>2.99340462684631</v>
+        <v>2.99340534210205</v>
       </c>
       <c r="H350" t="n">
         <v>996164</v>
@@ -10577,7 +10577,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03837871551514</v>
+        <v>3.03837847709656</v>
       </c>
       <c r="H352" t="n">
         <v>949730</v>
@@ -10606,7 +10606,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G353" t="n">
-        <v>3.03176498413086</v>
+        <v>3.03176474571228</v>
       </c>
       <c r="H353" t="n">
         <v>617623</v>
@@ -10635,7 +10635,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G354" t="n">
-        <v>3.10583925247192</v>
+        <v>3.1058394908905</v>
       </c>
       <c r="H354" t="n">
         <v>888394</v>
@@ -10664,7 +10664,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G355" t="n">
-        <v>3.03441047668457</v>
+        <v>3.03441071510315</v>
       </c>
       <c r="H355" t="n">
         <v>1590596</v>
@@ -10693,7 +10693,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.00927829742432</v>
+        <v>3.0092785358429</v>
       </c>
       <c r="H356" t="n">
         <v>1663888</v>
@@ -10722,7 +10722,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G357" t="n">
-        <v>2.9960503578186</v>
+        <v>2.99605083465576</v>
       </c>
       <c r="H357" t="n">
         <v>1097676</v>
@@ -10809,7 +10809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G360" t="n">
-        <v>3.04631495475769</v>
+        <v>3.04631519317627</v>
       </c>
       <c r="H360" t="n">
         <v>1279493</v>
@@ -10867,7 +10867,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>3.02911972999573</v>
+        <v>3.02911901473999</v>
       </c>
       <c r="H362" t="n">
         <v>894876</v>
@@ -11012,7 +11012,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G367" t="n">
-        <v>2.98282289505005</v>
+        <v>2.98282241821289</v>
       </c>
       <c r="H367" t="n">
         <v>331590</v>
@@ -11041,7 +11041,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G368" t="n">
-        <v>2.97091817855835</v>
+        <v>2.97091794013977</v>
       </c>
       <c r="H368" t="n">
         <v>274659</v>
@@ -11070,7 +11070,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>2.99869608879089</v>
+        <v>2.99869585037231</v>
       </c>
       <c r="H369" t="n">
         <v>327121</v>
@@ -11099,7 +11099,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G370" t="n">
-        <v>2.97356367111206</v>
+        <v>2.9735631942749</v>
       </c>
       <c r="H370" t="n">
         <v>934664</v>
@@ -11186,7 +11186,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G373" t="n">
-        <v>3.02250599861145</v>
+        <v>3.02250576019287</v>
       </c>
       <c r="H373" t="n">
         <v>820789</v>
@@ -11215,7 +11215,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>2.94313955307007</v>
+        <v>2.94313979148865</v>
       </c>
       <c r="H374" t="n">
         <v>861518</v>
@@ -11244,7 +11244,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G375" t="n">
-        <v>2.85054659843445</v>
+        <v>2.85054683685303</v>
       </c>
       <c r="H375" t="n">
         <v>2514673</v>
@@ -11273,7 +11273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.87700200080872</v>
+        <v>2.87700223922729</v>
       </c>
       <c r="H376" t="n">
         <v>558785</v>
@@ -11331,7 +11331,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G378" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H378" t="n">
         <v>654476</v>
@@ -11360,7 +11360,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G379" t="n">
-        <v>2.86509704589844</v>
+        <v>2.86509680747986</v>
       </c>
       <c r="H379" t="n">
         <v>765727</v>
@@ -11418,7 +11418,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85980653762817</v>
+        <v>2.85980629920959</v>
       </c>
       <c r="H381" t="n">
         <v>559669</v>
@@ -11447,7 +11447,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G382" t="n">
-        <v>2.85451555252075</v>
+        <v>2.85451531410217</v>
       </c>
       <c r="H382" t="n">
         <v>516590</v>
@@ -11505,7 +11505,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H384" t="n">
         <v>424777</v>
@@ -11563,7 +11563,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.87700200080872</v>
+        <v>2.87700223922729</v>
       </c>
       <c r="H386" t="n">
         <v>431245</v>
@@ -11592,7 +11592,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.84525585174561</v>
+        <v>2.84525609016418</v>
       </c>
       <c r="H387" t="n">
         <v>570613</v>
@@ -11621,7 +11621,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.79763674736023</v>
+        <v>2.79763650894165</v>
       </c>
       <c r="H388" t="n">
         <v>888381</v>
@@ -11650,7 +11650,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705430030823</v>
+        <v>2.78705477714539</v>
       </c>
       <c r="H389" t="n">
         <v>1087808</v>
@@ -11766,7 +11766,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>2.71165704727173</v>
+        <v>2.71165728569031</v>
       </c>
       <c r="H393" t="n">
         <v>1017959</v>
@@ -11795,7 +11795,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>2.75398540496826</v>
+        <v>2.75398564338684</v>
       </c>
       <c r="H394" t="n">
         <v>1009068</v>
@@ -11853,7 +11853,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G396" t="n">
-        <v>2.67329716682434</v>
+        <v>2.67329668998718</v>
       </c>
       <c r="H396" t="n">
         <v>563261</v>
@@ -11882,7 +11882,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69446134567261</v>
+        <v>2.69446110725403</v>
       </c>
       <c r="H397" t="n">
         <v>848281</v>
@@ -11998,7 +11998,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.75927639007568</v>
+        <v>2.75927662849426</v>
       </c>
       <c r="H401" t="n">
         <v>543737</v>
@@ -12056,7 +12056,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G403" t="n">
-        <v>2.76456737518311</v>
+        <v>2.76456761360168</v>
       </c>
       <c r="H403" t="n">
         <v>371911</v>
@@ -12085,7 +12085,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G404" t="n">
-        <v>2.72885322570801</v>
+        <v>2.72885298728943</v>
       </c>
       <c r="H404" t="n">
         <v>250945</v>
@@ -12114,7 +12114,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G405" t="n">
-        <v>2.72885322570801</v>
+        <v>2.72885298728943</v>
       </c>
       <c r="H405" t="n">
         <v>549004</v>
@@ -12259,7 +12259,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G410" t="n">
-        <v>2.7262077331543</v>
+        <v>2.72620749473572</v>
       </c>
       <c r="H410" t="n">
         <v>884762</v>
@@ -12288,7 +12288,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.66932845115662</v>
+        <v>2.6693286895752</v>
       </c>
       <c r="H411" t="n">
         <v>843867</v>
@@ -12317,7 +12317,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>2.6799111366272</v>
+        <v>2.67991089820862</v>
       </c>
       <c r="H412" t="n">
         <v>388086</v>
@@ -12346,7 +12346,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G413" t="n">
-        <v>2.76324486732483</v>
+        <v>2.76324462890625</v>
       </c>
       <c r="H413" t="n">
         <v>701284</v>
@@ -12375,7 +12375,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>2.75927639007568</v>
+        <v>2.75927662849426</v>
       </c>
       <c r="H414" t="n">
         <v>581298</v>
@@ -12462,7 +12462,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G417" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H417" t="n">
         <v>1518103</v>
@@ -12549,7 +12549,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>2.91007113456726</v>
+        <v>2.91007137298584</v>
       </c>
       <c r="H420" t="n">
         <v>721209</v>
@@ -12578,7 +12578,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G421" t="n">
-        <v>2.88890671730042</v>
+        <v>2.88890695571899</v>
       </c>
       <c r="H421" t="n">
         <v>630370</v>
@@ -12607,7 +12607,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G422" t="n">
-        <v>2.86377453804016</v>
+        <v>2.86377429962158</v>
       </c>
       <c r="H422" t="n">
         <v>747318</v>
@@ -12636,7 +12636,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G423" t="n">
-        <v>2.89287519454956</v>
+        <v>2.89287495613098</v>
       </c>
       <c r="H423" t="n">
         <v>451656</v>
@@ -12752,7 +12752,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G427" t="n">
-        <v>2.79234528541565</v>
+        <v>2.79234552383423</v>
       </c>
       <c r="H427" t="n">
         <v>495666</v>
@@ -12781,7 +12781,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G428" t="n">
-        <v>2.83335065841675</v>
+        <v>2.83335113525391</v>
       </c>
       <c r="H428" t="n">
         <v>634478</v>
@@ -12839,7 +12839,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86642026901245</v>
+        <v>2.86642003059387</v>
       </c>
       <c r="H430" t="n">
         <v>602501</v>
@@ -12868,7 +12868,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G431" t="n">
-        <v>2.86642026901245</v>
+        <v>2.86642003059387</v>
       </c>
       <c r="H431" t="n">
         <v>546107</v>
@@ -12897,7 +12897,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.85054659843445</v>
+        <v>2.85054683685303</v>
       </c>
       <c r="H432" t="n">
         <v>482261</v>
@@ -12926,7 +12926,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.89022946357727</v>
+        <v>2.89022970199585</v>
       </c>
       <c r="H433" t="n">
         <v>641837</v>
@@ -12955,7 +12955,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G434" t="n">
-        <v>2.894198179245</v>
+        <v>2.89419770240784</v>
       </c>
       <c r="H434" t="n">
         <v>713486</v>
@@ -13071,7 +13071,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G438" t="n">
-        <v>2.97885465621948</v>
+        <v>2.97885489463806</v>
       </c>
       <c r="H438" t="n">
         <v>726631</v>
@@ -13100,7 +13100,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99208235740662</v>
+        <v>2.99208211898804</v>
       </c>
       <c r="H439" t="n">
         <v>796136</v>
@@ -13129,7 +13129,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G440" t="n">
-        <v>3.0079550743103</v>
+        <v>3.00795555114746</v>
       </c>
       <c r="H440" t="n">
         <v>894728</v>
@@ -13158,7 +13158,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G441" t="n">
-        <v>2.98282289505005</v>
+        <v>2.98282241821289</v>
       </c>
       <c r="H441" t="n">
         <v>916165</v>
@@ -13187,7 +13187,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.93652606010437</v>
+        <v>2.93652629852295</v>
       </c>
       <c r="H442" t="n">
         <v>698038</v>
@@ -13216,7 +13216,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520379066467</v>
+        <v>2.93520402908325</v>
       </c>
       <c r="H443" t="n">
         <v>1018294</v>
@@ -13274,7 +13274,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>2.9563672542572</v>
+        <v>2.95636773109436</v>
       </c>
       <c r="H445" t="n">
         <v>229109</v>
@@ -13332,7 +13332,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>2.9563672542572</v>
+        <v>2.95636773109436</v>
       </c>
       <c r="H447" t="n">
         <v>241939</v>
@@ -13419,7 +13419,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.99208235740662</v>
+        <v>2.99208211898804</v>
       </c>
       <c r="H450" t="n">
         <v>365775</v>
@@ -13448,7 +13448,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G451" t="n">
-        <v>3.01721477508545</v>
+        <v>3.01721405982971</v>
       </c>
       <c r="H451" t="n">
         <v>457814</v>
@@ -13477,7 +13477,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G452" t="n">
-        <v>2.97885465621948</v>
+        <v>2.97885489463806</v>
       </c>
       <c r="H452" t="n">
         <v>461639</v>
@@ -13535,7 +13535,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00398731231689</v>
+        <v>3.00398683547974</v>
       </c>
       <c r="H454" t="n">
         <v>359122</v>
@@ -13593,7 +13593,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>2.9960503578186</v>
+        <v>2.99605083465576</v>
       </c>
       <c r="H456" t="n">
         <v>373559</v>
@@ -13622,7 +13622,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92991209030151</v>
+        <v>2.92991232872009</v>
       </c>
       <c r="H457" t="n">
         <v>493247</v>
@@ -13651,7 +13651,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G458" t="n">
-        <v>2.98282289505005</v>
+        <v>2.98282241821289</v>
       </c>
       <c r="H458" t="n">
         <v>732536</v>
@@ -13738,7 +13738,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94710850715637</v>
+        <v>2.94710826873779</v>
       </c>
       <c r="H461" t="n">
         <v>1603800</v>
@@ -13767,7 +13767,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G462" t="n">
-        <v>2.89684319496155</v>
+        <v>2.89684367179871</v>
       </c>
       <c r="H462" t="n">
         <v>974266</v>
@@ -13796,7 +13796,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88361597061157</v>
+        <v>2.88361573219299</v>
       </c>
       <c r="H463" t="n">
         <v>1131048</v>
@@ -13825,7 +13825,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G464" t="n">
-        <v>2.89080142974854</v>
+        <v>2.89080119132996</v>
       </c>
       <c r="H464" t="n">
         <v>642124</v>
@@ -13854,7 +13854,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.92672944068909</v>
+        <v>2.92672896385193</v>
       </c>
       <c r="H465" t="n">
         <v>391973</v>
@@ -13912,7 +13912,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G467" t="n">
-        <v>2.90876531600952</v>
+        <v>2.90876507759094</v>
       </c>
       <c r="H467" t="n">
         <v>575040</v>
@@ -14057,7 +14057,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G472" t="n">
-        <v>2.84796452522278</v>
+        <v>2.84796476364136</v>
       </c>
       <c r="H472" t="n">
         <v>612992</v>
@@ -14086,7 +14086,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G473" t="n">
-        <v>2.86454629898071</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H473" t="n">
         <v>617354</v>
@@ -14115,7 +14115,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G474" t="n">
-        <v>2.8825101852417</v>
+        <v>2.88250994682312</v>
       </c>
       <c r="H474" t="n">
         <v>648999</v>
@@ -14144,7 +14144,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G475" t="n">
-        <v>2.86454629898071</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H475" t="n">
         <v>676249</v>
@@ -14231,7 +14231,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>2.79130887985229</v>
+        <v>2.79130911827087</v>
       </c>
       <c r="H478" t="n">
         <v>484051</v>
@@ -14318,7 +14318,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.86731028556824</v>
+        <v>2.86731004714966</v>
       </c>
       <c r="H481" t="n">
         <v>2001875</v>
@@ -14347,7 +14347,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G482" t="n">
-        <v>2.92258381843567</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H482" t="n">
         <v>1544814</v>
@@ -14376,7 +14376,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G483" t="n">
-        <v>2.93502020835876</v>
+        <v>2.93502044677734</v>
       </c>
       <c r="H483" t="n">
         <v>910184</v>
@@ -14492,7 +14492,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G487" t="n">
-        <v>2.9902937412262</v>
+        <v>2.99029350280762</v>
       </c>
       <c r="H487" t="n">
         <v>672094</v>
@@ -14521,7 +14521,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.01931214332581</v>
+        <v>3.01931190490723</v>
       </c>
       <c r="H488" t="n">
         <v>1239936</v>
@@ -14550,7 +14550,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.97371125221252</v>
+        <v>2.97371101379395</v>
       </c>
       <c r="H489" t="n">
         <v>488412</v>
@@ -14579,7 +14579,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G490" t="n">
-        <v>3.02345776557922</v>
+        <v>3.02345752716064</v>
       </c>
       <c r="H490" t="n">
         <v>692474</v>
@@ -14608,7 +14608,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97785687446594</v>
+        <v>2.97785711288452</v>
       </c>
       <c r="H491" t="n">
         <v>736849</v>
@@ -14637,7 +14637,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>2.95989274978638</v>
+        <v>2.95989346504211</v>
       </c>
       <c r="H492" t="n">
         <v>427110</v>
@@ -14666,7 +14666,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G493" t="n">
-        <v>2.96818399429321</v>
+        <v>2.96818423271179</v>
       </c>
       <c r="H493" t="n">
         <v>355874</v>
@@ -14695,7 +14695,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G494" t="n">
-        <v>2.96818399429321</v>
+        <v>2.96818423271179</v>
       </c>
       <c r="H494" t="n">
         <v>219739</v>
@@ -14724,7 +14724,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G495" t="n">
-        <v>2.9902937412262</v>
+        <v>2.99029350280762</v>
       </c>
       <c r="H495" t="n">
         <v>390621</v>
@@ -14753,7 +14753,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G496" t="n">
-        <v>2.96818399429321</v>
+        <v>2.96818423271179</v>
       </c>
       <c r="H496" t="n">
         <v>351475</v>
@@ -14840,7 +14840,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G499" t="n">
-        <v>2.97509360313416</v>
+        <v>2.97509336471558</v>
       </c>
       <c r="H499" t="n">
         <v>576760</v>
@@ -14869,7 +14869,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G500" t="n">
-        <v>2.97923827171326</v>
+        <v>2.97923898696899</v>
       </c>
       <c r="H500" t="n">
         <v>1148402</v>
@@ -14898,7 +14898,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G501" t="n">
-        <v>2.94054746627808</v>
+        <v>2.94054770469666</v>
       </c>
       <c r="H501" t="n">
         <v>933889</v>
@@ -14956,7 +14956,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G503" t="n">
-        <v>3.01793050765991</v>
+        <v>3.01793026924133</v>
       </c>
       <c r="H503" t="n">
         <v>748907</v>
@@ -15043,7 +15043,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>3.1049861907959</v>
+        <v>3.10498595237732</v>
       </c>
       <c r="H506" t="n">
         <v>709039</v>
@@ -15072,7 +15072,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G507" t="n">
-        <v>3.11051321029663</v>
+        <v>3.11051297187805</v>
       </c>
       <c r="H507" t="n">
         <v>760040</v>
@@ -15101,7 +15101,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G508" t="n">
-        <v>3.14229536056519</v>
+        <v>3.14229559898376</v>
       </c>
       <c r="H508" t="n">
         <v>516954</v>
@@ -15130,7 +15130,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G509" t="n">
-        <v>3.08840346336365</v>
+        <v>3.08840370178223</v>
       </c>
       <c r="H509" t="n">
         <v>334744</v>
@@ -15159,7 +15159,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G510" t="n">
-        <v>3.07182216644287</v>
+        <v>3.07182192802429</v>
       </c>
       <c r="H510" t="n">
         <v>253760</v>
@@ -15188,7 +15188,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>3.04556703567505</v>
+        <v>3.04556679725647</v>
       </c>
       <c r="H511" t="n">
         <v>278984</v>
@@ -15217,7 +15217,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>3.05385804176331</v>
+        <v>3.05385828018188</v>
       </c>
       <c r="H512" t="n">
         <v>428701</v>
@@ -15246,7 +15246,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>3.04556703567505</v>
+        <v>3.04556679725647</v>
       </c>
       <c r="H513" t="n">
         <v>227183</v>
@@ -15304,7 +15304,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G515" t="n">
-        <v>3.04418540000916</v>
+        <v>3.04418563842773</v>
       </c>
       <c r="H515" t="n">
         <v>485465</v>
@@ -15333,7 +15333,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G516" t="n">
-        <v>3.02760291099548</v>
+        <v>3.02760314941406</v>
       </c>
       <c r="H516" t="n">
         <v>310444</v>
@@ -15362,7 +15362,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G517" t="n">
-        <v>3.02760291099548</v>
+        <v>3.02760314941406</v>
       </c>
       <c r="H517" t="n">
         <v>648168</v>
@@ -15391,7 +15391,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G518" t="n">
-        <v>2.99443960189819</v>
+        <v>2.99443936347961</v>
       </c>
       <c r="H518" t="n">
         <v>854391</v>
@@ -15420,7 +15420,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G519" t="n">
-        <v>3.00963926315308</v>
+        <v>3.0096390247345</v>
       </c>
       <c r="H519" t="n">
         <v>260832</v>
@@ -15478,7 +15478,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G521" t="n">
-        <v>3.02345776557922</v>
+        <v>3.02345752716064</v>
       </c>
       <c r="H521" t="n">
         <v>343913</v>
@@ -15536,7 +15536,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>3.01931214332581</v>
+        <v>3.01931190490723</v>
       </c>
       <c r="H523" t="n">
         <v>289490</v>
@@ -15565,7 +15565,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G524" t="n">
-        <v>2.9930567741394</v>
+        <v>2.99305701255798</v>
       </c>
       <c r="H524" t="n">
         <v>1167836</v>
@@ -15594,7 +15594,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G525" t="n">
-        <v>2.99582099914551</v>
+        <v>2.99582123756409</v>
       </c>
       <c r="H525" t="n">
         <v>364917</v>
@@ -15623,7 +15623,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G526" t="n">
-        <v>2.92258381843567</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H526" t="n">
         <v>778954</v>
@@ -15681,7 +15681,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>2.90185618400574</v>
+        <v>2.90185546875</v>
       </c>
       <c r="H528" t="n">
         <v>301253</v>
@@ -15710,7 +15710,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G529" t="n">
-        <v>2.91982007026672</v>
+        <v>2.91981959342957</v>
       </c>
       <c r="H529" t="n">
         <v>295775</v>
@@ -15739,7 +15739,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>2.92258381843567</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H530" t="n">
         <v>347945</v>
@@ -15768,7 +15768,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>2.9433114528656</v>
+        <v>2.94331169128418</v>
       </c>
       <c r="H531" t="n">
         <v>440550</v>
@@ -15826,7 +15826,7 @@
         <v>4.25</v>
       </c>
       <c r="G533" t="n">
-        <v>2.93640208244324</v>
+        <v>2.93640184402466</v>
       </c>
       <c r="H533" t="n">
         <v>173706</v>
@@ -15855,7 +15855,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G534" t="n">
-        <v>2.87283730506897</v>
+        <v>2.87283754348755</v>
       </c>
       <c r="H534" t="n">
         <v>449592</v>
@@ -15884,7 +15884,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94607448577881</v>
+        <v>2.94607496261597</v>
       </c>
       <c r="H535" t="n">
         <v>538665</v>
@@ -15913,7 +15913,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G536" t="n">
-        <v>2.9516019821167</v>
+        <v>2.95160222053528</v>
       </c>
       <c r="H536" t="n">
         <v>547729</v>
@@ -15971,7 +15971,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G538" t="n">
-        <v>2.94607448577881</v>
+        <v>2.94607496261597</v>
       </c>
       <c r="H538" t="n">
         <v>458621</v>
@@ -16000,7 +16000,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>2.9433114528656</v>
+        <v>2.94331169128418</v>
       </c>
       <c r="H539" t="n">
         <v>279372</v>
@@ -16058,7 +16058,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.92811107635498</v>
+        <v>2.9281108379364</v>
       </c>
       <c r="H541" t="n">
         <v>404056</v>
@@ -16087,7 +16087,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G542" t="n">
-        <v>2.95989274978638</v>
+        <v>2.95989346504211</v>
       </c>
       <c r="H542" t="n">
         <v>542766</v>
@@ -16116,7 +16116,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.99443960189819</v>
+        <v>2.99443936347961</v>
       </c>
       <c r="H543" t="n">
         <v>678637</v>
@@ -16203,7 +16203,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97371125221252</v>
+        <v>2.97371101379395</v>
       </c>
       <c r="H546" t="n">
         <v>335573</v>
@@ -16232,7 +16232,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06491231918335</v>
+        <v>3.06491255760193</v>
       </c>
       <c r="H547" t="n">
         <v>681594</v>
@@ -16261,7 +16261,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G548" t="n">
-        <v>3.00134801864624</v>
+        <v>3.00134825706482</v>
       </c>
       <c r="H548" t="n">
         <v>523849</v>
@@ -16406,7 +16406,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>2.95712971687317</v>
+        <v>2.95712947845459</v>
       </c>
       <c r="H553" t="n">
         <v>433139</v>
@@ -16464,7 +16464,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G555" t="n">
-        <v>2.95298385620117</v>
+        <v>2.95298433303833</v>
       </c>
       <c r="H555" t="n">
         <v>212164</v>
@@ -16493,7 +16493,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G556" t="n">
-        <v>2.90323829650879</v>
+        <v>2.90323781967163</v>
       </c>
       <c r="H556" t="n">
         <v>274776</v>
@@ -16522,7 +16522,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G557" t="n">
-        <v>2.90047430992126</v>
+        <v>2.90047383308411</v>
       </c>
       <c r="H557" t="n">
         <v>1783781</v>
@@ -16551,7 +16551,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G558" t="n">
-        <v>2.89632844924927</v>
+        <v>2.89632868766785</v>
       </c>
       <c r="H558" t="n">
         <v>319927</v>
@@ -16580,7 +16580,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.85349154472351</v>
+        <v>2.85349178314209</v>
       </c>
       <c r="H559" t="n">
         <v>633026</v>
@@ -16754,7 +16754,7 @@
         <v>4</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76367211341858</v>
+        <v>2.76367235183716</v>
       </c>
       <c r="H565" t="n">
         <v>473255</v>
@@ -16812,7 +16812,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75261735916138</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H567" t="n">
         <v>559095</v>
@@ -16841,7 +16841,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G568" t="n">
-        <v>2.71530818939209</v>
+        <v>2.71530842781067</v>
       </c>
       <c r="H568" t="n">
         <v>476384</v>
@@ -16899,7 +16899,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G570" t="n">
-        <v>2.7332718372345</v>
+        <v>2.73327231407166</v>
       </c>
       <c r="H570" t="n">
         <v>306755</v>
@@ -16928,7 +16928,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G571" t="n">
-        <v>2.7484724521637</v>
+        <v>2.74847221374512</v>
       </c>
       <c r="H571" t="n">
         <v>214980</v>
@@ -16986,7 +16986,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G573" t="n">
-        <v>2.76505398750305</v>
+        <v>2.76505422592163</v>
       </c>
       <c r="H573" t="n">
         <v>274810</v>
@@ -17044,7 +17044,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G575" t="n">
-        <v>2.7166895866394</v>
+        <v>2.71668982505798</v>
       </c>
       <c r="H575" t="n">
         <v>399828</v>
@@ -17073,7 +17073,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>2.73603558540344</v>
+        <v>2.73603582382202</v>
       </c>
       <c r="H576" t="n">
         <v>219577</v>
@@ -17102,7 +17102,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G577" t="n">
-        <v>2.75261735916138</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H577" t="n">
         <v>253623</v>
@@ -17160,7 +17160,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G579" t="n">
-        <v>2.7484724521637</v>
+        <v>2.74847221374512</v>
       </c>
       <c r="H579" t="n">
         <v>295742</v>
@@ -17189,7 +17189,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G580" t="n">
-        <v>2.75123596191406</v>
+        <v>2.75123643875122</v>
       </c>
       <c r="H580" t="n">
         <v>406170</v>
@@ -17334,7 +17334,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G585" t="n">
-        <v>2.75261735916138</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H585" t="n">
         <v>331776</v>
@@ -17363,7 +17363,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G586" t="n">
-        <v>2.74018120765686</v>
+        <v>2.74018144607544</v>
       </c>
       <c r="H586" t="n">
         <v>165727</v>
@@ -17450,7 +17450,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73879957199097</v>
+        <v>2.73879909515381</v>
       </c>
       <c r="H589" t="n">
         <v>665011</v>
@@ -17537,7 +17537,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G592" t="n">
-        <v>2.84243702888489</v>
+        <v>2.84243726730347</v>
       </c>
       <c r="H592" t="n">
         <v>810244</v>
@@ -17682,7 +17682,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G597" t="n">
-        <v>2.88389205932617</v>
+        <v>2.88389182090759</v>
       </c>
       <c r="H597" t="n">
         <v>605764</v>
@@ -17711,7 +17711,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>2.9433114528656</v>
+        <v>2.94331169128418</v>
       </c>
       <c r="H598" t="n">
         <v>1052192</v>
@@ -17740,7 +17740,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G599" t="n">
-        <v>2.91014719009399</v>
+        <v>2.91014695167542</v>
       </c>
       <c r="H599" t="n">
         <v>1120884</v>
@@ -17827,7 +17827,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G602" t="n">
-        <v>2.90047430992126</v>
+        <v>2.90047383308411</v>
       </c>
       <c r="H602" t="n">
         <v>1324299</v>
@@ -17856,7 +17856,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.90876531600952</v>
+        <v>2.90876507759094</v>
       </c>
       <c r="H603" t="n">
         <v>845447</v>
@@ -17885,7 +17885,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G604" t="n">
-        <v>2.9212019443512</v>
+        <v>2.92120170593262</v>
       </c>
       <c r="H604" t="n">
         <v>500397</v>
@@ -17914,7 +17914,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>2.88803744316101</v>
+        <v>2.88803768157959</v>
       </c>
       <c r="H605" t="n">
         <v>796514</v>
@@ -17943,7 +17943,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G606" t="n">
-        <v>2.84796452522278</v>
+        <v>2.84796476364136</v>
       </c>
       <c r="H606" t="n">
         <v>745572</v>
@@ -18030,7 +18030,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G609" t="n">
-        <v>2.84520077705383</v>
+        <v>2.84520053863525</v>
       </c>
       <c r="H609" t="n">
         <v>365525</v>
@@ -18059,7 +18059,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G610" t="n">
-        <v>2.86869215965271</v>
+        <v>2.86869168281555</v>
       </c>
       <c r="H610" t="n">
         <v>802117</v>
@@ -18117,7 +18117,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G612" t="n">
-        <v>2.90323829650879</v>
+        <v>2.90323781967163</v>
       </c>
       <c r="H612" t="n">
         <v>379452</v>
@@ -18146,7 +18146,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>2.87421941757202</v>
+        <v>2.87421917915344</v>
       </c>
       <c r="H613" t="n">
         <v>527133</v>
@@ -18175,7 +18175,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G614" t="n">
-        <v>2.84520077705383</v>
+        <v>2.84520053863525</v>
       </c>
       <c r="H614" t="n">
         <v>683120</v>
@@ -18204,7 +18204,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G615" t="n">
-        <v>2.86454629898071</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H615" t="n">
         <v>695451</v>
@@ -18233,7 +18233,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G616" t="n">
-        <v>2.89080142974854</v>
+        <v>2.89080119132996</v>
       </c>
       <c r="H616" t="n">
         <v>255638</v>
@@ -18262,7 +18262,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G617" t="n">
-        <v>2.89632844924927</v>
+        <v>2.89632868766785</v>
       </c>
       <c r="H617" t="n">
         <v>507785</v>
@@ -18291,7 +18291,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G618" t="n">
-        <v>2.9212019443512</v>
+        <v>2.92120170593262</v>
       </c>
       <c r="H618" t="n">
         <v>836606</v>
@@ -18378,7 +18378,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G621" t="n">
-        <v>2.97509360313416</v>
+        <v>2.97509336471558</v>
       </c>
       <c r="H621" t="n">
         <v>601405</v>
@@ -18407,7 +18407,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G622" t="n">
-        <v>2.98338437080383</v>
+        <v>2.98338413238525</v>
       </c>
       <c r="H622" t="n">
         <v>557576</v>
@@ -18436,7 +18436,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G623" t="n">
-        <v>2.99443960189819</v>
+        <v>2.99443936347961</v>
       </c>
       <c r="H623" t="n">
         <v>220839</v>
@@ -18494,7 +18494,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.01931214332581</v>
+        <v>3.01931190490723</v>
       </c>
       <c r="H625" t="n">
         <v>641122</v>
@@ -18552,7 +18552,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G627" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H627" t="n">
         <v>241326</v>
@@ -18581,7 +18581,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G628" t="n">
-        <v>3.00963926315308</v>
+        <v>3.0096390247345</v>
       </c>
       <c r="H628" t="n">
         <v>380571</v>
@@ -18610,7 +18610,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G629" t="n">
-        <v>2.99443960189819</v>
+        <v>2.99443936347961</v>
       </c>
       <c r="H629" t="n">
         <v>363346</v>
@@ -18668,7 +18668,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G631" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H631" t="n">
         <v>472455</v>
@@ -18697,7 +18697,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G632" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H632" t="n">
         <v>518046</v>
@@ -18726,7 +18726,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G633" t="n">
-        <v>3.03313016891479</v>
+        <v>3.03313040733337</v>
       </c>
       <c r="H633" t="n">
         <v>428715</v>
@@ -18842,7 +18842,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G637" t="n">
-        <v>3.03451251983643</v>
+        <v>3.034512758255</v>
       </c>
       <c r="H637" t="n">
         <v>362948</v>
@@ -18871,7 +18871,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G638" t="n">
-        <v>3.02483916282654</v>
+        <v>3.02483940124512</v>
       </c>
       <c r="H638" t="n">
         <v>187474</v>
@@ -18900,7 +18900,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>3.08287644386292</v>
+        <v>3.08287668228149</v>
       </c>
       <c r="H639" t="n">
         <v>455246</v>
@@ -18929,7 +18929,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G640" t="n">
-        <v>3.08011293411255</v>
+        <v>3.08011269569397</v>
       </c>
       <c r="H640" t="n">
         <v>539646</v>
@@ -18958,7 +18958,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G641" t="n">
-        <v>3.08840346336365</v>
+        <v>3.08840370178223</v>
       </c>
       <c r="H641" t="n">
         <v>313925</v>
@@ -19016,7 +19016,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>3.08149456977844</v>
+        <v>3.08149480819702</v>
       </c>
       <c r="H643" t="n">
         <v>293010</v>
@@ -19045,7 +19045,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G644" t="n">
-        <v>3.09669494628906</v>
+        <v>3.0966944694519</v>
       </c>
       <c r="H644" t="n">
         <v>242340</v>
@@ -19103,7 +19103,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G646" t="n">
-        <v>3.14229536056519</v>
+        <v>3.14229559898376</v>
       </c>
       <c r="H646" t="n">
         <v>601188</v>
@@ -19161,7 +19161,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G648" t="n">
-        <v>3.04694867134094</v>
+        <v>3.04694890975952</v>
       </c>
       <c r="H648" t="n">
         <v>341481</v>
@@ -19190,7 +19190,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G649" t="n">
-        <v>3.09669494628906</v>
+        <v>3.0966944694519</v>
       </c>
       <c r="H649" t="n">
         <v>458945</v>
@@ -19248,7 +19248,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G651" t="n">
-        <v>3.10360431671143</v>
+        <v>3.10360407829285</v>
       </c>
       <c r="H651" t="n">
         <v>725248</v>
@@ -19277,7 +19277,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G652" t="n">
-        <v>3.12709522247314</v>
+        <v>3.12709546089172</v>
       </c>
       <c r="H652" t="n">
         <v>655086</v>
@@ -19364,7 +19364,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G655" t="n">
-        <v>3.11742234230042</v>
+        <v>3.11742281913757</v>
       </c>
       <c r="H655" t="n">
         <v>774559</v>
@@ -19393,7 +19393,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G656" t="n">
-        <v>3.08978605270386</v>
+        <v>3.08978581428528</v>
       </c>
       <c r="H656" t="n">
         <v>451701</v>
@@ -19422,7 +19422,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G657" t="n">
-        <v>3.08840346336365</v>
+        <v>3.08840370178223</v>
       </c>
       <c r="H657" t="n">
         <v>649670</v>
@@ -19451,7 +19451,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G658" t="n">
-        <v>3.08840346336365</v>
+        <v>3.08840370178223</v>
       </c>
       <c r="H658" t="n">
         <v>463243</v>
@@ -19480,7 +19480,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>3.1049861907959</v>
+        <v>3.10498595237732</v>
       </c>
       <c r="H659" t="n">
         <v>713844</v>
@@ -19567,7 +19567,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13815021514893</v>
+        <v>3.13814973831177</v>
       </c>
       <c r="H662" t="n">
         <v>519012</v>
@@ -19654,7 +19654,7 @@
         <v>4.5</v>
       </c>
       <c r="G665" t="n">
-        <v>3.10913109779358</v>
+        <v>3.10913133621216</v>
       </c>
       <c r="H665" t="n">
         <v>605477</v>
@@ -19712,7 +19712,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.10913109779358</v>
+        <v>3.10913133621216</v>
       </c>
       <c r="H667" t="n">
         <v>591269</v>
@@ -19799,7 +19799,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G670" t="n">
-        <v>3.3122615814209</v>
+        <v>3.31226134300232</v>
       </c>
       <c r="H670" t="n">
         <v>1432256</v>
@@ -19857,7 +19857,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G672" t="n">
-        <v>3.34680724143982</v>
+        <v>3.3468074798584</v>
       </c>
       <c r="H672" t="n">
         <v>697587</v>
@@ -19886,7 +19886,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G673" t="n">
-        <v>3.36062550544739</v>
+        <v>3.36062574386597</v>
       </c>
       <c r="H673" t="n">
         <v>702541</v>
@@ -19915,7 +19915,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38411688804626</v>
+        <v>3.38411641120911</v>
       </c>
       <c r="H674" t="n">
         <v>577089</v>
@@ -19944,7 +19944,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G675" t="n">
-        <v>3.35924410820007</v>
+        <v>3.35924363136292</v>
       </c>
       <c r="H675" t="n">
         <v>374930</v>
@@ -20031,7 +20031,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>3.30535197257996</v>
+        <v>3.30535244941711</v>
       </c>
       <c r="H678" t="n">
         <v>478581</v>
@@ -20118,7 +20118,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G681" t="n">
-        <v>3.31502485275269</v>
+        <v>3.31502532958984</v>
       </c>
       <c r="H681" t="n">
         <v>329531</v>
@@ -20147,7 +20147,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G682" t="n">
-        <v>3.35648012161255</v>
+        <v>3.35647988319397</v>
       </c>
       <c r="H682" t="n">
         <v>547505</v>
@@ -20176,7 +20176,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G683" t="n">
-        <v>3.37858963012695</v>
+        <v>3.37858939170837</v>
       </c>
       <c r="H683" t="n">
         <v>448925</v>
@@ -20234,7 +20234,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G685" t="n">
-        <v>3.36615324020386</v>
+        <v>3.36615347862244</v>
       </c>
       <c r="H685" t="n">
         <v>497823</v>
@@ -20263,7 +20263,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G686" t="n">
-        <v>3.36615324020386</v>
+        <v>3.36615347862244</v>
       </c>
       <c r="H686" t="n">
         <v>412491</v>
@@ -20292,7 +20292,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G687" t="n">
-        <v>3.36615324020386</v>
+        <v>3.36615347862244</v>
       </c>
       <c r="H687" t="n">
         <v>264276</v>
@@ -20321,7 +20321,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G688" t="n">
-        <v>3.32469773292542</v>
+        <v>3.32469820976257</v>
       </c>
       <c r="H688" t="n">
         <v>384931</v>
@@ -20350,7 +20350,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G689" t="n">
-        <v>3.28047895431519</v>
+        <v>3.28047919273376</v>
       </c>
       <c r="H689" t="n">
         <v>367827</v>
@@ -20379,7 +20379,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G690" t="n">
-        <v>3.29015159606934</v>
+        <v>3.29015183448792</v>
       </c>
       <c r="H690" t="n">
         <v>515539</v>
@@ -20408,7 +20408,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31778860092163</v>
+        <v>3.31778883934021</v>
       </c>
       <c r="H691" t="n">
         <v>207705</v>
@@ -20437,7 +20437,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G692" t="n">
-        <v>3.31087923049927</v>
+        <v>3.31087946891785</v>
       </c>
       <c r="H692" t="n">
         <v>270176</v>
@@ -20495,7 +20495,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G694" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H694" t="n">
         <v>378541</v>
@@ -20524,7 +20524,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G695" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H695" t="n">
         <v>334779</v>
@@ -20611,7 +20611,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G698" t="n">
-        <v>3.34266185760498</v>
+        <v>3.34266138076782</v>
       </c>
       <c r="H698" t="n">
         <v>268858</v>
@@ -20640,7 +20640,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.3233163356781</v>
+        <v>3.32331585884094</v>
       </c>
       <c r="H699" t="n">
         <v>272666</v>
@@ -20669,7 +20669,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G700" t="n">
-        <v>3.31364345550537</v>
+        <v>3.31364321708679</v>
       </c>
       <c r="H700" t="n">
         <v>621856</v>
@@ -20698,7 +20698,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>3.37168025970459</v>
+        <v>3.37168073654175</v>
       </c>
       <c r="H701" t="n">
         <v>1574407</v>
@@ -20727,7 +20727,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G702" t="n">
-        <v>3.36062550544739</v>
+        <v>3.36062574386597</v>
       </c>
       <c r="H702" t="n">
         <v>244864</v>
@@ -20756,7 +20756,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.37168025970459</v>
+        <v>3.37168073654175</v>
       </c>
       <c r="H703" t="n">
         <v>496384</v>
@@ -20785,7 +20785,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G704" t="n">
-        <v>3.35648012161255</v>
+        <v>3.35647988319397</v>
       </c>
       <c r="H704" t="n">
         <v>234747</v>
@@ -20814,7 +20814,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G705" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H705" t="n">
         <v>215533</v>
@@ -20872,7 +20872,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G707" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H707" t="n">
         <v>440703</v>
@@ -20930,7 +20930,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G709" t="n">
-        <v>3.33437132835388</v>
+        <v>3.33437085151672</v>
       </c>
       <c r="H709" t="n">
         <v>886827</v>
@@ -20959,7 +20959,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G710" t="n">
-        <v>3.32469773292542</v>
+        <v>3.32469820976257</v>
       </c>
       <c r="H710" t="n">
         <v>248745</v>
@@ -20988,7 +20988,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>3.38549876213074</v>
+        <v>3.38549900054932</v>
       </c>
       <c r="H711" t="n">
         <v>312454</v>
@@ -21046,7 +21046,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G713" t="n">
-        <v>3.36200737953186</v>
+        <v>3.36200761795044</v>
       </c>
       <c r="H713" t="n">
         <v>399022</v>
@@ -21075,7 +21075,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G714" t="n">
-        <v>3.3702986240387</v>
+        <v>3.37029838562012</v>
       </c>
       <c r="H714" t="n">
         <v>307384</v>
@@ -21133,7 +21133,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G716" t="n">
-        <v>3.44507884979248</v>
+        <v>3.4450786113739</v>
       </c>
       <c r="H716" t="n">
         <v>338239</v>
@@ -21162,7 +21162,7 @@
         <v>4.80800008773804</v>
       </c>
       <c r="G717" t="n">
-        <v>3.46380949020386</v>
+        <v>3.46380996704102</v>
       </c>
       <c r="H717" t="n">
         <v>205826</v>
@@ -21191,7 +21191,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G718" t="n">
-        <v>3.4623692035675</v>
+        <v>3.46236896514893</v>
       </c>
       <c r="H718" t="n">
         <v>296407</v>
@@ -21220,7 +21220,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G719" t="n">
-        <v>3.46092844009399</v>
+        <v>3.46092796325684</v>
       </c>
       <c r="H719" t="n">
         <v>505932</v>
@@ -21249,7 +21249,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G720" t="n">
-        <v>3.48110008239746</v>
+        <v>3.48109984397888</v>
       </c>
       <c r="H720" t="n">
         <v>314563</v>
@@ -21278,7 +21278,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>3.46957302093506</v>
+        <v>3.46957325935364</v>
       </c>
       <c r="H721" t="n">
         <v>1025779</v>
@@ -21307,7 +21307,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G722" t="n">
-        <v>3.45660519599915</v>
+        <v>3.45660591125488</v>
       </c>
       <c r="H722" t="n">
         <v>697211</v>
@@ -21336,7 +21336,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G723" t="n">
-        <v>3.48110008239746</v>
+        <v>3.48109984397888</v>
       </c>
       <c r="H723" t="n">
         <v>368085</v>
@@ -21394,7 +21394,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G725" t="n">
-        <v>3.55314302444458</v>
+        <v>3.553142786026</v>
       </c>
       <c r="H725" t="n">
         <v>854127</v>
@@ -21423,7 +21423,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G726" t="n">
-        <v>3.57475519180298</v>
+        <v>3.57475590705872</v>
       </c>
       <c r="H726" t="n">
         <v>985537</v>
@@ -21510,7 +21510,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G729" t="n">
-        <v>3.67777681350708</v>
+        <v>3.67777633666992</v>
       </c>
       <c r="H729" t="n">
         <v>630184</v>
@@ -21539,7 +21539,7 @@
         <v>5.125</v>
       </c>
       <c r="G730" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H730" t="n">
         <v>660523</v>
@@ -21568,7 +21568,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65976548194885</v>
+        <v>3.65976572036743</v>
       </c>
       <c r="H731" t="n">
         <v>458971</v>
@@ -21597,7 +21597,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>3.63455104827881</v>
+        <v>3.63455080986023</v>
       </c>
       <c r="H732" t="n">
         <v>418405</v>
@@ -21626,7 +21626,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>3.70659375190735</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H733" t="n">
         <v>827997</v>
@@ -21655,7 +21655,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G734" t="n">
-        <v>3.6525616645813</v>
+        <v>3.65256190299988</v>
       </c>
       <c r="H734" t="n">
         <v>522904</v>
@@ -21684,7 +21684,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G735" t="n">
-        <v>3.61293816566467</v>
+        <v>3.61293792724609</v>
       </c>
       <c r="H735" t="n">
         <v>404107</v>
@@ -21713,7 +21713,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G736" t="n">
-        <v>3.68137836456299</v>
+        <v>3.68137860298157</v>
       </c>
       <c r="H736" t="n">
         <v>430174</v>
@@ -21742,7 +21742,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>3.63094878196716</v>
+        <v>3.63094902038574</v>
       </c>
       <c r="H737" t="n">
         <v>602362</v>
@@ -21771,7 +21771,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>3.66336798667908</v>
+        <v>3.66336846351624</v>
       </c>
       <c r="H738" t="n">
         <v>726479</v>
@@ -21800,7 +21800,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G739" t="n">
-        <v>3.68498086929321</v>
+        <v>3.68498039245605</v>
       </c>
       <c r="H739" t="n">
         <v>2546011</v>
@@ -21829,7 +21829,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>3.68858289718628</v>
+        <v>3.68858337402344</v>
       </c>
       <c r="H740" t="n">
         <v>394292</v>
@@ -21887,7 +21887,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G742" t="n">
-        <v>3.58484125137329</v>
+        <v>3.58484148979187</v>
       </c>
       <c r="H742" t="n">
         <v>346299</v>
@@ -21916,7 +21916,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.5444974899292</v>
+        <v>3.54449772834778</v>
       </c>
       <c r="H743" t="n">
         <v>449069</v>
@@ -21945,7 +21945,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G744" t="n">
-        <v>3.59492778778076</v>
+        <v>3.59492802619934</v>
       </c>
       <c r="H744" t="n">
         <v>517127</v>
@@ -22003,7 +22003,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>3.5444974899292</v>
+        <v>3.54449772834778</v>
       </c>
       <c r="H746" t="n">
         <v>1059414</v>
@@ -22032,7 +22032,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G747" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H747" t="n">
         <v>607759</v>
@@ -22061,7 +22061,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G748" t="n">
-        <v>3.59925031661987</v>
+        <v>3.59924960136414</v>
       </c>
       <c r="H748" t="n">
         <v>415115</v>
@@ -22090,7 +22090,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G749" t="n">
-        <v>3.57619619369507</v>
+        <v>3.57619643211365</v>
       </c>
       <c r="H749" t="n">
         <v>582111</v>
@@ -22119,7 +22119,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G750" t="n">
-        <v>3.57763695716858</v>
+        <v>3.57763767242432</v>
       </c>
       <c r="H750" t="n">
         <v>333644</v>
@@ -22177,7 +22177,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G752" t="n">
-        <v>3.60933637619019</v>
+        <v>3.60933613777161</v>
       </c>
       <c r="H752" t="n">
         <v>272384</v>
@@ -22206,7 +22206,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.62014222145081</v>
+        <v>3.62014269828796</v>
       </c>
       <c r="H753" t="n">
         <v>353573</v>
@@ -22293,7 +22293,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G756" t="n">
-        <v>3.61293816566467</v>
+        <v>3.61293792724609</v>
       </c>
       <c r="H756" t="n">
         <v>299037</v>
@@ -22322,7 +22322,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>3.61654019355774</v>
+        <v>3.61654043197632</v>
       </c>
       <c r="H757" t="n">
         <v>392000</v>
@@ -22380,7 +22380,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H759" t="n">
         <v>333042</v>
@@ -22467,7 +22467,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G762" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H762" t="n">
         <v>233504</v>
@@ -22525,7 +22525,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G764" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H764" t="n">
         <v>136835</v>
@@ -22554,7 +22554,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G765" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H765" t="n">
         <v>363470</v>
@@ -22583,7 +22583,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G766" t="n">
-        <v>3.57619619369507</v>
+        <v>3.57619643211365</v>
       </c>
       <c r="H766" t="n">
         <v>852645</v>
@@ -22699,7 +22699,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.56611037254333</v>
+        <v>3.56611013412476</v>
       </c>
       <c r="H770" t="n">
         <v>220728</v>
@@ -22728,7 +22728,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G771" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H771" t="n">
         <v>473966</v>
@@ -22815,7 +22815,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>3.61654019355774</v>
+        <v>3.61654043197632</v>
       </c>
       <c r="H774" t="n">
         <v>365000</v>
@@ -22844,7 +22844,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G775" t="n">
-        <v>3.66697001457214</v>
+        <v>3.66697025299072</v>
       </c>
       <c r="H775" t="n">
         <v>116327</v>
@@ -22873,7 +22873,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G776" t="n">
-        <v>3.70659375190735</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H776" t="n">
         <v>535968</v>
@@ -22902,7 +22902,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G777" t="n">
-        <v>3.70659375190735</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H777" t="n">
         <v>394359</v>
@@ -22931,7 +22931,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>3.67777681350708</v>
+        <v>3.67777633666992</v>
       </c>
       <c r="H778" t="n">
         <v>510087</v>
@@ -22960,7 +22960,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H779" t="n">
         <v>537475</v>
@@ -22989,7 +22989,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.72460412979126</v>
+        <v>3.72460460662842</v>
       </c>
       <c r="H780" t="n">
         <v>198706</v>
@@ -23018,7 +23018,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>3.76782941818237</v>
+        <v>3.76782965660095</v>
       </c>
       <c r="H781" t="n">
         <v>213433</v>
@@ -23076,7 +23076,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.71379852294922</v>
+        <v>3.71379780769348</v>
       </c>
       <c r="H783" t="n">
         <v>188130</v>
@@ -23105,7 +23105,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>3.71379852294922</v>
+        <v>3.71379780769348</v>
       </c>
       <c r="H784" t="n">
         <v>217194</v>
@@ -23134,7 +23134,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G785" t="n">
-        <v>3.77503418922424</v>
+        <v>3.77503347396851</v>
       </c>
       <c r="H785" t="n">
         <v>221413</v>
@@ -23192,7 +23192,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G787" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H787" t="n">
         <v>298424</v>
@@ -23221,7 +23221,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G788" t="n">
-        <v>3.70299124717712</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H788" t="n">
         <v>296476</v>
@@ -23279,7 +23279,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G790" t="n">
-        <v>3.68858289718628</v>
+        <v>3.68858337402344</v>
       </c>
       <c r="H790" t="n">
         <v>402408</v>
@@ -23337,7 +23337,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.71740031242371</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H792" t="n">
         <v>225935</v>
@@ -23366,7 +23366,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G793" t="n">
-        <v>3.70299124717712</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H793" t="n">
         <v>262081</v>
@@ -23395,7 +23395,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G794" t="n">
-        <v>3.67417454719543</v>
+        <v>3.67417407035828</v>
       </c>
       <c r="H794" t="n">
         <v>251245</v>
@@ -23424,7 +23424,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.6417555809021</v>
+        <v>3.64175486564636</v>
       </c>
       <c r="H795" t="n">
         <v>413188</v>
@@ -23453,7 +23453,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>3.62014222145081</v>
+        <v>3.62014269828796</v>
       </c>
       <c r="H796" t="n">
         <v>385770</v>
@@ -23511,7 +23511,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.68858289718628</v>
+        <v>3.68858337402344</v>
       </c>
       <c r="H798" t="n">
         <v>166019</v>
@@ -23540,7 +23540,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>3.67777681350708</v>
+        <v>3.67777633666992</v>
       </c>
       <c r="H799" t="n">
         <v>119947</v>
@@ -23569,7 +23569,7 @@
         <v>5.125</v>
       </c>
       <c r="G800" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H800" t="n">
         <v>156322</v>
@@ -23598,7 +23598,7 @@
         <v>5.125</v>
       </c>
       <c r="G801" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H801" t="n">
         <v>257011</v>
@@ -23627,7 +23627,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>3.67777681350708</v>
+        <v>3.67777633666992</v>
       </c>
       <c r="H802" t="n">
         <v>357933</v>
@@ -23656,7 +23656,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>3.66697001457214</v>
+        <v>3.66697025299072</v>
       </c>
       <c r="H803" t="n">
         <v>178529</v>
@@ -23685,7 +23685,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.67417454719543</v>
+        <v>3.67417407035828</v>
       </c>
       <c r="H804" t="n">
         <v>184382</v>
@@ -23714,7 +23714,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>3.69578742980957</v>
+        <v>3.69578766822815</v>
       </c>
       <c r="H805" t="n">
         <v>390641</v>
@@ -23772,7 +23772,7 @@
         <v>5.125</v>
       </c>
       <c r="G807" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H807" t="n">
         <v>331891</v>
@@ -23830,7 +23830,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H809" t="n">
         <v>629355</v>
@@ -23859,7 +23859,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.73541045188904</v>
+        <v>3.7354109287262</v>
       </c>
       <c r="H810" t="n">
         <v>395323</v>
@@ -23917,7 +23917,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>3.68858289718628</v>
+        <v>3.68858337402344</v>
       </c>
       <c r="H812" t="n">
         <v>198291</v>
@@ -23946,7 +23946,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H813" t="n">
         <v>202688</v>
@@ -23975,7 +23975,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H814" t="n">
         <v>370664</v>
@@ -24004,7 +24004,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G815" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H815" t="n">
         <v>312178</v>
@@ -24033,7 +24033,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G816" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H816" t="n">
         <v>225018</v>
@@ -24062,7 +24062,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H817" t="n">
         <v>140668</v>
@@ -24091,7 +24091,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H818" t="n">
         <v>255505</v>
@@ -24120,7 +24120,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342106819153</v>
       </c>
       <c r="H819" t="n">
         <v>228708</v>
@@ -24236,7 +24236,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>3.76782941818237</v>
+        <v>3.76782965660095</v>
       </c>
       <c r="H823" t="n">
         <v>438530</v>
@@ -24265,7 +24265,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>3.72460412979126</v>
+        <v>3.72460460662842</v>
       </c>
       <c r="H824" t="n">
         <v>343423</v>
@@ -24294,7 +24294,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342106819153</v>
       </c>
       <c r="H825" t="n">
         <v>242523</v>
@@ -24323,7 +24323,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G826" t="n">
-        <v>3.68137836456299</v>
+        <v>3.68137860298157</v>
       </c>
       <c r="H826" t="n">
         <v>229614</v>
@@ -24381,7 +24381,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G828" t="n">
-        <v>3.70299124717712</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H828" t="n">
         <v>168676</v>
@@ -24410,7 +24410,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>3.72460412979126</v>
+        <v>3.72460460662842</v>
       </c>
       <c r="H829" t="n">
         <v>248488</v>
@@ -24439,7 +24439,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G830" t="n">
-        <v>3.73180818557739</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H830" t="n">
         <v>177186</v>
@@ -24468,7 +24468,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>3.72460412979126</v>
+        <v>3.72460460662842</v>
       </c>
       <c r="H831" t="n">
         <v>204215</v>
@@ -24497,7 +24497,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G832" t="n">
-        <v>3.76062512397766</v>
+        <v>3.76062536239624</v>
       </c>
       <c r="H832" t="n">
         <v>268201</v>
@@ -24526,7 +24526,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584027290344</v>
       </c>
       <c r="H833" t="n">
         <v>158358</v>
@@ -24555,7 +24555,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G834" t="n">
-        <v>3.79304504394531</v>
+        <v>3.79304432868958</v>
       </c>
       <c r="H834" t="n">
         <v>288604</v>
@@ -24642,7 +24642,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342130661011</v>
+        <v>3.75342106819153</v>
       </c>
       <c r="H837" t="n">
         <v>261649</v>
@@ -24671,7 +24671,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>3.77503418922424</v>
+        <v>3.77503347396851</v>
       </c>
       <c r="H838" t="n">
         <v>184338</v>
@@ -24700,7 +24700,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>3.76422739028931</v>
+        <v>3.76422786712646</v>
       </c>
       <c r="H839" t="n">
         <v>155864</v>
@@ -24729,7 +24729,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584027290344</v>
       </c>
       <c r="H840" t="n">
         <v>309517</v>
@@ -24758,7 +24758,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.77863645553589</v>
+        <v>3.77863597869873</v>
       </c>
       <c r="H841" t="n">
         <v>231779</v>
@@ -24816,7 +24816,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148548126221</v>
+        <v>3.86148500442505</v>
       </c>
       <c r="H843" t="n">
         <v>518806</v>
@@ -24845,7 +24845,7 @@
         <v>5.375</v>
       </c>
       <c r="G844" t="n">
-        <v>3.87229132652283</v>
+        <v>3.87229204177856</v>
       </c>
       <c r="H844" t="n">
         <v>150028</v>
@@ -24874,7 +24874,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.82186222076416</v>
+        <v>3.82186126708984</v>
       </c>
       <c r="H845" t="n">
         <v>210214</v>
@@ -24903,7 +24903,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664754867554</v>
       </c>
       <c r="H846" t="n">
         <v>882140</v>
@@ -24932,7 +24932,7 @@
         <v>5.25</v>
       </c>
       <c r="G847" t="n">
-        <v>3.78223848342896</v>
+        <v>3.7822380065918</v>
       </c>
       <c r="H847" t="n">
         <v>330835</v>
@@ -24961,7 +24961,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>3.76422739028931</v>
+        <v>3.76422786712646</v>
       </c>
       <c r="H848" t="n">
         <v>621281</v>
@@ -24990,7 +24990,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G849" t="n">
-        <v>3.78944277763367</v>
+        <v>3.78944325447083</v>
       </c>
       <c r="H849" t="n">
         <v>309778</v>
@@ -25019,7 +25019,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G850" t="n">
-        <v>3.86508703231812</v>
+        <v>3.86508750915527</v>
       </c>
       <c r="H850" t="n">
         <v>585661</v>
@@ -25048,7 +25048,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>3.82906651496887</v>
+        <v>3.82906556129456</v>
       </c>
       <c r="H851" t="n">
         <v>1005431</v>
@@ -25135,7 +25135,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80024886131287</v>
+        <v>3.80024909973145</v>
       </c>
       <c r="H854" t="n">
         <v>521291</v>
@@ -25164,7 +25164,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664754867554</v>
       </c>
       <c r="H855" t="n">
         <v>531608</v>
@@ -25193,7 +25193,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80024886131287</v>
+        <v>3.80024909973145</v>
       </c>
       <c r="H856" t="n">
         <v>340183</v>
@@ -25222,7 +25222,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G857" t="n">
-        <v>3.80385088920593</v>
+        <v>3.80385136604309</v>
       </c>
       <c r="H857" t="n">
         <v>236744</v>
@@ -25251,7 +25251,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80024886131287</v>
+        <v>3.80024909973145</v>
       </c>
       <c r="H858" t="n">
         <v>247892</v>
@@ -25280,7 +25280,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.85067844390869</v>
+        <v>3.85067892074585</v>
       </c>
       <c r="H859" t="n">
         <v>429041</v>
@@ -25309,7 +25309,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>3.83626985549927</v>
+        <v>3.83627033233643</v>
       </c>
       <c r="H860" t="n">
         <v>202317</v>
@@ -25338,7 +25338,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>3.8470766544342</v>
+        <v>3.84707641601562</v>
       </c>
       <c r="H861" t="n">
         <v>142215</v>
@@ -25367,7 +25367,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G862" t="n">
-        <v>3.8326678276062</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H862" t="n">
         <v>423140</v>
@@ -25425,7 +25425,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664754867554</v>
       </c>
       <c r="H864" t="n">
         <v>272878</v>
@@ -25454,7 +25454,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>3.8578827381134</v>
+        <v>3.85788321495056</v>
       </c>
       <c r="H865" t="n">
         <v>856594</v>
@@ -25483,7 +25483,7 @@
         <v>5.375</v>
       </c>
       <c r="G866" t="n">
-        <v>3.87229132652283</v>
+        <v>3.87229204177856</v>
       </c>
       <c r="H866" t="n">
         <v>334082</v>
@@ -25512,7 +25512,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>3.90831279754639</v>
+        <v>3.90831351280212</v>
       </c>
       <c r="H867" t="n">
         <v>679193</v>
@@ -25541,7 +25541,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>3.90471124649048</v>
+        <v>3.9047110080719</v>
       </c>
       <c r="H868" t="n">
         <v>1580647</v>
@@ -25570,7 +25570,7 @@
         <v>5.375</v>
       </c>
       <c r="G869" t="n">
-        <v>3.87229132652283</v>
+        <v>3.87229204177856</v>
       </c>
       <c r="H869" t="n">
         <v>307691</v>
@@ -25599,7 +25599,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.88309836387634</v>
+        <v>3.88309788703918</v>
       </c>
       <c r="H870" t="n">
         <v>376869</v>
@@ -25628,7 +25628,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G871" t="n">
-        <v>3.8326678276062</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H871" t="n">
         <v>429811</v>
@@ -25657,7 +25657,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91191458702087</v>
+        <v>3.91191482543945</v>
       </c>
       <c r="H872" t="n">
         <v>627265</v>
@@ -25686,7 +25686,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>3.83626985549927</v>
+        <v>3.83627033233643</v>
       </c>
       <c r="H873" t="n">
         <v>626080</v>
@@ -25715,7 +25715,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>3.80024886131287</v>
+        <v>3.80024909973145</v>
       </c>
       <c r="H874" t="n">
         <v>558719</v>
@@ -25744,7 +25744,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>3.8326678276062</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H875" t="n">
         <v>683792</v>
@@ -25773,7 +25773,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G876" t="n">
-        <v>3.91191458702087</v>
+        <v>3.91191482543945</v>
       </c>
       <c r="H876" t="n">
         <v>933919</v>
@@ -25802,7 +25802,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91191458702087</v>
+        <v>3.91191482543945</v>
       </c>
       <c r="H877" t="n">
         <v>497300</v>
@@ -25831,7 +25831,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G878" t="n">
-        <v>3.92632365226746</v>
+        <v>3.92632341384888</v>
       </c>
       <c r="H878" t="n">
         <v>368905</v>
@@ -25860,7 +25860,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G879" t="n">
-        <v>3.95874238014221</v>
+        <v>3.95874285697937</v>
       </c>
       <c r="H879" t="n">
         <v>433161</v>
@@ -25918,7 +25918,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97315096855164</v>
+        <v>3.97315144538879</v>
       </c>
       <c r="H881" t="n">
         <v>255729</v>
@@ -25947,7 +25947,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>4.01997900009155</v>
+        <v>4.01997852325439</v>
       </c>
       <c r="H882" t="n">
         <v>458370</v>
@@ -25976,7 +25976,7 @@
         <v>5.625</v>
       </c>
       <c r="G883" t="n">
-        <v>4.05239868164062</v>
+        <v>4.05239820480347</v>
       </c>
       <c r="H883" t="n">
         <v>369585</v>
@@ -26034,7 +26034,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G885" t="n">
-        <v>4.06680631637573</v>
+        <v>4.06680679321289</v>
       </c>
       <c r="H885" t="n">
         <v>226888</v>
@@ -26063,7 +26063,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>4.08841991424561</v>
+        <v>4.08841896057129</v>
       </c>
       <c r="H886" t="n">
         <v>668689</v>
@@ -26092,7 +26092,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.16406440734863</v>
+        <v>4.16406393051147</v>
       </c>
       <c r="H887" t="n">
         <v>1025480</v>
@@ -26121,7 +26121,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>4.21809577941895</v>
+        <v>4.2180962562561</v>
       </c>
       <c r="H888" t="n">
         <v>1316501</v>
@@ -26150,7 +26150,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18567705154419</v>
+        <v>4.18567752838135</v>
       </c>
       <c r="H889" t="n">
         <v>1255135</v>
@@ -26179,7 +26179,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>4.21449375152588</v>
+        <v>4.21449422836304</v>
       </c>
       <c r="H890" t="n">
         <v>286810</v>
@@ -26208,7 +26208,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>4.24691390991211</v>
+        <v>4.24691343307495</v>
       </c>
       <c r="H891" t="n">
         <v>470536</v>
@@ -26324,7 +26324,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G895" t="n">
-        <v>4.25411796569824</v>
+        <v>4.25411748886108</v>
       </c>
       <c r="H895" t="n">
         <v>810508</v>
@@ -26411,7 +26411,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G898" t="n">
-        <v>4.31895589828491</v>
+        <v>4.31895637512207</v>
       </c>
       <c r="H898" t="n">
         <v>927247</v>
@@ -26440,7 +26440,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G899" t="n">
-        <v>4.31175136566162</v>
+        <v>4.31175184249878</v>
       </c>
       <c r="H899" t="n">
         <v>306181</v>
@@ -26469,7 +26469,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>4.29374074935913</v>
+        <v>4.29374122619629</v>
       </c>
       <c r="H900" t="n">
         <v>741766</v>
@@ -26527,7 +26527,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>4.29374074935913</v>
+        <v>4.29374122619629</v>
       </c>
       <c r="H902" t="n">
         <v>663557</v>
@@ -26556,7 +26556,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G903" t="n">
-        <v>4.32615995407104</v>
+        <v>4.32616090774536</v>
       </c>
       <c r="H903" t="n">
         <v>982085</v>
@@ -26585,7 +26585,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G904" t="n">
-        <v>4.35858011245728</v>
+        <v>4.35857963562012</v>
       </c>
       <c r="H904" t="n">
         <v>597979</v>
@@ -26614,7 +26614,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G905" t="n">
-        <v>4.39820289611816</v>
+        <v>4.39820241928101</v>
       </c>
       <c r="H905" t="n">
         <v>530337</v>
@@ -26643,7 +26643,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G906" t="n">
-        <v>4.42702007293701</v>
+        <v>4.42702054977417</v>
       </c>
       <c r="H906" t="n">
         <v>303177</v>
@@ -26730,7 +26730,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>4.18567705154419</v>
+        <v>4.18567752838135</v>
       </c>
       <c r="H909" t="n">
         <v>1255336</v>
@@ -26759,7 +26759,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>4.11723709106445</v>
+        <v>4.11723661422729</v>
       </c>
       <c r="H910" t="n">
         <v>1141771</v>
@@ -26846,7 +26846,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.89750647544861</v>
+        <v>3.89750671386719</v>
       </c>
       <c r="H913" t="n">
         <v>1781293</v>
@@ -26904,7 +26904,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>3.77863645553589</v>
+        <v>3.77863597869873</v>
       </c>
       <c r="H915" t="n">
         <v>1709583</v>
@@ -26962,7 +26962,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.71740031242371</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H917" t="n">
         <v>905147</v>
@@ -26991,7 +26991,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G918" t="n">
-        <v>3.61654019355774</v>
+        <v>3.61654043197632</v>
       </c>
       <c r="H918" t="n">
         <v>832462</v>
@@ -27020,7 +27020,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G919" t="n">
-        <v>3.33413314819336</v>
+        <v>3.33413290977478</v>
       </c>
       <c r="H919" t="n">
         <v>2052459</v>
@@ -27049,7 +27049,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G920" t="n">
-        <v>3.24624133110046</v>
+        <v>3.24624109268188</v>
       </c>
       <c r="H920" t="n">
         <v>847418</v>
@@ -27078,7 +27078,7 @@
         <v>4.5</v>
       </c>
       <c r="G921" t="n">
-        <v>3.24191832542419</v>
+        <v>3.24191856384277</v>
       </c>
       <c r="H921" t="n">
         <v>1478690</v>
@@ -27136,7 +27136,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G923" t="n">
-        <v>2.8658561706543</v>
+        <v>2.86585569381714</v>
       </c>
       <c r="H923" t="n">
         <v>2005867</v>
@@ -27252,7 +27252,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G927" t="n">
-        <v>2.58921265602112</v>
+        <v>2.58921241760254</v>
       </c>
       <c r="H927" t="n">
         <v>1414173</v>
@@ -27281,7 +27281,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G928" t="n">
-        <v>2.52437400817871</v>
+        <v>2.52437376976013</v>
       </c>
       <c r="H928" t="n">
         <v>823310</v>
@@ -27339,7 +27339,7 @@
         <v>3.5</v>
       </c>
       <c r="G930" t="n">
-        <v>2.52149200439453</v>
+        <v>2.52149224281311</v>
       </c>
       <c r="H930" t="n">
         <v>1518410</v>
@@ -27426,7 +27426,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G933" t="n">
-        <v>2.78949069976807</v>
+        <v>2.78949093818665</v>
       </c>
       <c r="H933" t="n">
         <v>826614</v>
@@ -27484,7 +27484,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G935" t="n">
-        <v>2.89035081863403</v>
+        <v>2.89035058021545</v>
       </c>
       <c r="H935" t="n">
         <v>943520</v>
@@ -27542,7 +27542,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>2.93933963775635</v>
+        <v>2.93933939933777</v>
       </c>
       <c r="H937" t="n">
         <v>798516</v>
@@ -27600,7 +27600,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G939" t="n">
-        <v>2.89035081863403</v>
+        <v>2.89035058021545</v>
       </c>
       <c r="H939" t="n">
         <v>639112</v>
@@ -27658,7 +27658,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98976969718933</v>
+        <v>2.98976945877075</v>
       </c>
       <c r="H941" t="n">
         <v>464684</v>
@@ -27687,7 +27687,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>3.02579069137573</v>
+        <v>3.02579045295715</v>
       </c>
       <c r="H942" t="n">
         <v>878459</v>
@@ -27716,7 +27716,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G943" t="n">
-        <v>3.02579069137573</v>
+        <v>3.02579045295715</v>
       </c>
       <c r="H943" t="n">
         <v>717288</v>
@@ -27745,7 +27745,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G944" t="n">
-        <v>2.94798469543457</v>
+        <v>2.94798445701599</v>
       </c>
       <c r="H944" t="n">
         <v>974453</v>
@@ -27774,7 +27774,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>2.97536087036133</v>
+        <v>2.97536063194275</v>
       </c>
       <c r="H945" t="n">
         <v>961948</v>
@@ -27803,7 +27803,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G946" t="n">
-        <v>3.01138186454773</v>
+        <v>3.01138210296631</v>
       </c>
       <c r="H946" t="n">
         <v>521324</v>
@@ -27832,7 +27832,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G947" t="n">
-        <v>2.94942545890808</v>
+        <v>2.9494252204895</v>
       </c>
       <c r="H947" t="n">
         <v>765074</v>
@@ -27861,7 +27861,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G948" t="n">
-        <v>2.85432934761047</v>
+        <v>2.85432910919189</v>
       </c>
       <c r="H948" t="n">
         <v>792857</v>
@@ -27919,7 +27919,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G950" t="n">
-        <v>2.91772675514221</v>
+        <v>2.91772699356079</v>
       </c>
       <c r="H950" t="n">
         <v>718280</v>
@@ -27948,7 +27948,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.91052269935608</v>
+        <v>2.91052222251892</v>
       </c>
       <c r="H951" t="n">
         <v>231048</v>
@@ -28035,7 +28035,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G954" t="n">
-        <v>2.94654369354248</v>
+        <v>2.94654393196106</v>
       </c>
       <c r="H954" t="n">
         <v>399289</v>
@@ -28064,7 +28064,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G955" t="n">
-        <v>2.94654369354248</v>
+        <v>2.94654393196106</v>
       </c>
       <c r="H955" t="n">
         <v>650178</v>
@@ -28122,7 +28122,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G957" t="n">
-        <v>2.85577034950256</v>
+        <v>2.85576987266541</v>
       </c>
       <c r="H957" t="n">
         <v>405808</v>
@@ -28209,7 +28209,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G960" t="n">
-        <v>2.85432934761047</v>
+        <v>2.85432910919189</v>
       </c>
       <c r="H960" t="n">
         <v>238118</v>
@@ -28296,7 +28296,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G963" t="n">
-        <v>2.78228664398193</v>
+        <v>2.78228688240051</v>
       </c>
       <c r="H963" t="n">
         <v>329641</v>
@@ -28325,7 +28325,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G964" t="n">
-        <v>2.75346946716309</v>
+        <v>2.75346922874451</v>
       </c>
       <c r="H964" t="n">
         <v>407303</v>
@@ -28383,7 +28383,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G966" t="n">
-        <v>3.02434992790222</v>
+        <v>3.02434945106506</v>
       </c>
       <c r="H966" t="n">
         <v>586431</v>
@@ -28412,7 +28412,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G967" t="n">
-        <v>2.95230746269226</v>
+        <v>2.95230722427368</v>
       </c>
       <c r="H967" t="n">
         <v>775973</v>
@@ -28470,7 +28470,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G969" t="n">
-        <v>2.93357634544373</v>
+        <v>2.93357610702515</v>
       </c>
       <c r="H969" t="n">
         <v>560198</v>
@@ -28499,7 +28499,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G970" t="n">
-        <v>2.99553275108337</v>
+        <v>2.99553298950195</v>
       </c>
       <c r="H970" t="n">
         <v>1758990</v>
@@ -28528,7 +28528,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G971" t="n">
-        <v>3.04969906806946</v>
+        <v>3.04969882965088</v>
       </c>
       <c r="H971" t="n">
         <v>839198</v>
@@ -28557,7 +28557,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G972" t="n">
-        <v>3.1240451335907</v>
+        <v>3.12404465675354</v>
       </c>
       <c r="H972" t="n">
         <v>1072358</v>
@@ -28615,7 +28615,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G974" t="n">
-        <v>3.09673380851746</v>
+        <v>3.09673404693604</v>
       </c>
       <c r="H974" t="n">
         <v>1705780</v>
@@ -28644,7 +28644,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>3.09521722793579</v>
+        <v>3.09521675109863</v>
       </c>
       <c r="H975" t="n">
         <v>785616</v>
@@ -28731,7 +28731,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G978" t="n">
-        <v>3.36984133720398</v>
+        <v>3.36984157562256</v>
       </c>
       <c r="H978" t="n">
         <v>1837773</v>
@@ -28760,7 +28760,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G979" t="n">
-        <v>3.4669463634491</v>
+        <v>3.46694612503052</v>
       </c>
       <c r="H979" t="n">
         <v>1270556</v>
@@ -28818,7 +28818,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.33797907829285</v>
+        <v>3.33797931671143</v>
       </c>
       <c r="H981" t="n">
         <v>1863975</v>
@@ -28847,7 +28847,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G982" t="n">
-        <v>3.24694347381592</v>
+        <v>3.24694323539734</v>
       </c>
       <c r="H982" t="n">
         <v>979427</v>
@@ -28876,7 +28876,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G983" t="n">
-        <v>3.18625235557556</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H983" t="n">
         <v>1121954</v>
@@ -28905,7 +28905,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G984" t="n">
-        <v>3.1240451335907</v>
+        <v>3.12404465675354</v>
       </c>
       <c r="H984" t="n">
         <v>1636453</v>
@@ -28963,7 +28963,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G986" t="n">
-        <v>3.12556195259094</v>
+        <v>3.1255624294281</v>
       </c>
       <c r="H986" t="n">
         <v>593457</v>
@@ -28992,7 +28992,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G987" t="n">
-        <v>3.15287327766418</v>
+        <v>3.15287303924561</v>
       </c>
       <c r="H987" t="n">
         <v>849857</v>
@@ -29021,7 +29021,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G988" t="n">
-        <v>3.14528632164001</v>
+        <v>3.14528679847717</v>
       </c>
       <c r="H988" t="n">
         <v>927499</v>
@@ -29079,7 +29079,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G990" t="n">
-        <v>3.0603199005127</v>
+        <v>3.06031966209412</v>
       </c>
       <c r="H990" t="n">
         <v>808635</v>
@@ -29166,7 +29166,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G993" t="n">
-        <v>3.01631951332092</v>
+        <v>3.01631927490234</v>
       </c>
       <c r="H993" t="n">
         <v>608831</v>
@@ -29369,7 +29369,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1000" t="n">
         <v>344826</v>
@@ -29514,7 +29514,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1005" t="n">
         <v>475389</v>
@@ -29572,7 +29572,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1007" t="n">
         <v>2396617</v>
@@ -29804,7 +29804,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.67038321495056</v>
+        <v>2.67038345336914</v>
       </c>
       <c r="H1015" t="n">
         <v>720352</v>
@@ -29833,7 +29833,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.63852047920227</v>
+        <v>2.63852071762085</v>
       </c>
       <c r="H1016" t="n">
         <v>694882</v>
@@ -29862,7 +29862,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.62486553192139</v>
+        <v>2.62486529350281</v>
       </c>
       <c r="H1017" t="n">
         <v>635963</v>
@@ -29891,7 +29891,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.61424422264099</v>
+        <v>2.61424446105957</v>
       </c>
       <c r="H1018" t="n">
         <v>419154</v>
@@ -29920,7 +29920,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.61576151847839</v>
+        <v>2.61576175689697</v>
       </c>
       <c r="H1019" t="n">
         <v>913484</v>
@@ -29949,7 +29949,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.62941741943359</v>
+        <v>2.62941718101501</v>
       </c>
       <c r="H1020" t="n">
         <v>742850</v>
@@ -29978,7 +29978,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.64610695838928</v>
+        <v>2.64610719680786</v>
       </c>
       <c r="H1021" t="n">
         <v>439971</v>
@@ -30007,7 +30007,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.74928092956543</v>
+        <v>2.74928116798401</v>
       </c>
       <c r="H1022" t="n">
         <v>923790</v>
@@ -30036,7 +30036,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.75990176200867</v>
+        <v>2.75990200042725</v>
       </c>
       <c r="H1023" t="n">
         <v>902165</v>
@@ -30094,7 +30094,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.7659707069397</v>
+        <v>2.76597094535828</v>
       </c>
       <c r="H1025" t="n">
         <v>968819</v>
@@ -30152,7 +30152,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1027" t="n">
         <v>934600</v>
@@ -30239,7 +30239,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.83424758911133</v>
+        <v>2.83424782752991</v>
       </c>
       <c r="H1030" t="n">
         <v>690968</v>
@@ -30268,7 +30268,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.7705225944519</v>
+        <v>2.77052235603333</v>
       </c>
       <c r="H1031" t="n">
         <v>652124</v>
@@ -30413,7 +30413,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.77355718612671</v>
+        <v>2.77355694770813</v>
       </c>
       <c r="H1036" t="n">
         <v>610073</v>
@@ -30558,7 +30558,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.67038321495056</v>
+        <v>2.67038345336914</v>
       </c>
       <c r="H1041" t="n">
         <v>686287</v>
@@ -30587,7 +30587,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.67493510246277</v>
+        <v>2.67493486404419</v>
       </c>
       <c r="H1042" t="n">
         <v>642529</v>
@@ -30674,7 +30674,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.67190051078796</v>
+        <v>2.67190074920654</v>
       </c>
       <c r="H1045" t="n">
         <v>696676</v>
@@ -30703,7 +30703,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.6825213432312</v>
+        <v>2.68252158164978</v>
       </c>
       <c r="H1046" t="n">
         <v>397383</v>
@@ -30732,7 +30732,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G1047" t="n">
-        <v>2.68707323074341</v>
+        <v>2.68707299232483</v>
       </c>
       <c r="H1047" t="n">
         <v>1068852</v>
@@ -30848,7 +30848,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.66279673576355</v>
+        <v>2.66279697418213</v>
       </c>
       <c r="H1051" t="n">
         <v>342136</v>
@@ -30877,7 +30877,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.72348737716675</v>
+        <v>2.72348761558533</v>
       </c>
       <c r="H1052" t="n">
         <v>1420563</v>
@@ -30906,7 +30906,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.7083146572113</v>
+        <v>2.70831489562988</v>
       </c>
       <c r="H1053" t="n">
         <v>628815</v>
@@ -30993,7 +30993,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.5717613697052</v>
+        <v>2.57176113128662</v>
       </c>
       <c r="H1056" t="n">
         <v>853267</v>
@@ -31022,7 +31022,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.55658841133118</v>
+        <v>2.55658864974976</v>
       </c>
       <c r="H1057" t="n">
         <v>603020</v>
@@ -31051,7 +31051,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.5717613697052</v>
+        <v>2.57176113128662</v>
       </c>
       <c r="H1058" t="n">
         <v>683921</v>
@@ -31080,7 +31080,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.53079533576965</v>
+        <v>2.53079509735107</v>
       </c>
       <c r="H1059" t="n">
         <v>516757</v>
@@ -31109,7 +31109,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.51258778572083</v>
+        <v>2.5125880241394</v>
       </c>
       <c r="H1060" t="n">
         <v>752381</v>
@@ -31138,7 +31138,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.55051970481873</v>
+        <v>2.55051946640015</v>
       </c>
       <c r="H1061" t="n">
         <v>420030</v>
@@ -31167,7 +31167,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.46858692169189</v>
+        <v>2.46858716011047</v>
       </c>
       <c r="H1062" t="n">
         <v>768004</v>
@@ -31283,7 +31283,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.36844801902771</v>
+        <v>2.36844778060913</v>
       </c>
       <c r="H1066" t="n">
         <v>904125</v>
@@ -31312,7 +31312,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.47769069671631</v>
+        <v>2.47769093513489</v>
       </c>
       <c r="H1067" t="n">
         <v>1137561</v>
@@ -31341,7 +31341,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.41093134880066</v>
+        <v>2.41093111038208</v>
       </c>
       <c r="H1068" t="n">
         <v>680772</v>
@@ -31370,7 +31370,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.43520760536194</v>
+        <v>2.43520736694336</v>
       </c>
       <c r="H1069" t="n">
         <v>605908</v>
@@ -31399,7 +31399,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.447345495224</v>
+        <v>2.44734573364258</v>
       </c>
       <c r="H1070" t="n">
         <v>553996</v>
@@ -31428,7 +31428,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.46858692169189</v>
+        <v>2.46858716011047</v>
       </c>
       <c r="H1071" t="n">
         <v>496827</v>
@@ -31544,7 +31544,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.40637946128845</v>
+        <v>2.40637969970703</v>
       </c>
       <c r="H1075" t="n">
         <v>559400</v>
@@ -31631,7 +31631,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.39727568626404</v>
+        <v>2.39727592468262</v>
       </c>
       <c r="H1078" t="n">
         <v>366713</v>
@@ -31689,7 +31689,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.39120674133301</v>
+        <v>2.39120650291443</v>
       </c>
       <c r="H1080" t="n">
         <v>414523</v>
@@ -31805,7 +31805,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.23796343803406</v>
+        <v>2.23796319961548</v>
       </c>
       <c r="H1084" t="n">
         <v>592578</v>
@@ -31834,7 +31834,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.26072239875793</v>
+        <v>2.26072216033936</v>
       </c>
       <c r="H1085" t="n">
         <v>923284</v>
@@ -32037,7 +32037,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1092" t="n">
         <v>1364511</v>
@@ -32066,7 +32066,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.78569531440735</v>
+        <v>2.78569507598877</v>
       </c>
       <c r="H1093" t="n">
         <v>1101842</v>
@@ -32095,7 +32095,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.74017739295959</v>
+        <v>2.74017715454102</v>
       </c>
       <c r="H1094" t="n">
         <v>1055336</v>
@@ -32240,7 +32240,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.90252423286438</v>
+        <v>2.90252447128296</v>
       </c>
       <c r="H1099" t="n">
         <v>633533</v>
@@ -32356,7 +32356,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.96169757843018</v>
+        <v>2.96169781684875</v>
       </c>
       <c r="H1103" t="n">
         <v>675063</v>
@@ -32414,7 +32414,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.90859365463257</v>
+        <v>2.90859341621399</v>
       </c>
       <c r="H1105" t="n">
         <v>594134</v>
@@ -32443,7 +32443,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.79479885101318</v>
+        <v>2.7947986125946</v>
       </c>
       <c r="H1106" t="n">
         <v>1402040</v>
@@ -32472,7 +32472,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.82514405250549</v>
+        <v>2.82514381408691</v>
       </c>
       <c r="H1107" t="n">
         <v>704595</v>
@@ -32530,7 +32530,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.852454662323</v>
+        <v>2.85245490074158</v>
       </c>
       <c r="H1109" t="n">
         <v>368913</v>
@@ -32588,7 +32588,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.79935073852539</v>
+        <v>2.79935050010681</v>
       </c>
       <c r="H1111" t="n">
         <v>531696</v>
@@ -32617,7 +32617,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.79479885101318</v>
+        <v>2.7947986125946</v>
       </c>
       <c r="H1112" t="n">
         <v>343500</v>
@@ -32733,7 +32733,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.82059216499329</v>
+        <v>2.82059240341187</v>
       </c>
       <c r="H1116" t="n">
         <v>859726</v>
@@ -32762,7 +32762,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.82817840576172</v>
+        <v>2.8281786441803</v>
       </c>
       <c r="H1117" t="n">
         <v>699859</v>
@@ -32936,7 +32936,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.62486553192139</v>
+        <v>2.62486529350281</v>
       </c>
       <c r="H1123" t="n">
         <v>380734</v>
@@ -32965,7 +32965,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.7083146572113</v>
+        <v>2.70831489562988</v>
       </c>
       <c r="H1124" t="n">
         <v>765787</v>
@@ -32994,7 +32994,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.76445364952087</v>
+        <v>2.76445317268372</v>
       </c>
       <c r="H1125" t="n">
         <v>545031</v>
@@ -33023,7 +33023,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.72955632209778</v>
+        <v>2.72955656051636</v>
       </c>
       <c r="H1126" t="n">
         <v>513240</v>
@@ -33052,7 +33052,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.72955632209778</v>
+        <v>2.72955656051636</v>
       </c>
       <c r="H1127" t="n">
         <v>569458</v>
@@ -33168,7 +33168,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.73866009712219</v>
+        <v>2.73865985870361</v>
       </c>
       <c r="H1131" t="n">
         <v>621804</v>
@@ -33255,7 +33255,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.71438384056091</v>
+        <v>2.71438407897949</v>
       </c>
       <c r="H1134" t="n">
         <v>478250</v>
@@ -33284,7 +33284,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.72045302391052</v>
+        <v>2.72045278549194</v>
       </c>
       <c r="H1135" t="n">
         <v>354515</v>
@@ -33342,7 +33342,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.71438384056091</v>
+        <v>2.71438407897949</v>
       </c>
       <c r="H1137" t="n">
         <v>373671</v>
@@ -33400,7 +33400,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.7690052986145</v>
+        <v>2.76900553703308</v>
       </c>
       <c r="H1139" t="n">
         <v>618522</v>
@@ -33458,7 +33458,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.58693361282349</v>
+        <v>2.58693385124207</v>
       </c>
       <c r="H1141" t="n">
         <v>1073863</v>
@@ -33487,7 +33487,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.55051970481873</v>
+        <v>2.55051946640015</v>
       </c>
       <c r="H1142" t="n">
         <v>912227</v>
@@ -33603,7 +33603,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.65369319915771</v>
+        <v>2.65369343757629</v>
       </c>
       <c r="H1146" t="n">
         <v>533317</v>
@@ -33632,7 +33632,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.6567280292511</v>
+        <v>2.65672779083252</v>
       </c>
       <c r="H1147" t="n">
         <v>304370</v>
@@ -33661,7 +33661,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.69465947151184</v>
+        <v>2.69465970993042</v>
       </c>
       <c r="H1148" t="n">
         <v>373933</v>
@@ -33690,7 +33690,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.76141929626465</v>
+        <v>2.76141905784607</v>
       </c>
       <c r="H1149" t="n">
         <v>1012948</v>
@@ -33719,7 +33719,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.78417825698853</v>
+        <v>2.78417801856995</v>
       </c>
       <c r="H1150" t="n">
         <v>597089</v>
@@ -33748,7 +33748,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.84183430671692</v>
+        <v>2.84183406829834</v>
       </c>
       <c r="H1151" t="n">
         <v>888872</v>
@@ -33777,7 +33777,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1152" t="n">
         <v>625554</v>
@@ -33835,7 +33835,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.92528343200684</v>
+        <v>2.92528319358826</v>
       </c>
       <c r="H1154" t="n">
         <v>1212331</v>
@@ -33864,7 +33864,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.90100717544556</v>
+        <v>2.90100693702698</v>
       </c>
       <c r="H1155" t="n">
         <v>1086715</v>
@@ -33893,7 +33893,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.82817840576172</v>
+        <v>2.8281786441803</v>
       </c>
       <c r="H1156" t="n">
         <v>1242794</v>
@@ -33922,7 +33922,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.8903865814209</v>
+        <v>2.89038610458374</v>
       </c>
       <c r="H1157" t="n">
         <v>740083</v>
@@ -33980,7 +33980,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.8752133846283</v>
+        <v>2.87521386146545</v>
       </c>
       <c r="H1159" t="n">
         <v>329197</v>
@@ -34067,7 +34067,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.9419732093811</v>
+        <v>2.94197344779968</v>
       </c>
       <c r="H1162" t="n">
         <v>906831</v>
@@ -34154,7 +34154,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.0603199005127</v>
+        <v>3.06031966209412</v>
       </c>
       <c r="H1165" t="n">
         <v>859551</v>
@@ -34183,7 +34183,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.02997446060181</v>
+        <v>3.02997493743896</v>
       </c>
       <c r="H1166" t="n">
         <v>761418</v>
@@ -34270,7 +34270,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.99052548408508</v>
+        <v>2.99052572250366</v>
       </c>
       <c r="H1169" t="n">
         <v>1569670</v>
@@ -34299,7 +34299,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.96624946594238</v>
+        <v>2.96624970436096</v>
       </c>
       <c r="H1170" t="n">
         <v>774545</v>
@@ -34357,7 +34357,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.13314867019653</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H1172" t="n">
         <v>913192</v>
@@ -34415,7 +34415,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.30004739761353</v>
+        <v>3.3000476360321</v>
       </c>
       <c r="H1174" t="n">
         <v>1347515</v>
@@ -34444,7 +34444,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.31825470924377</v>
+        <v>3.3182544708252</v>
       </c>
       <c r="H1175" t="n">
         <v>1017835</v>
@@ -34502,7 +34502,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.25604677200317</v>
+        <v>3.25604653358459</v>
       </c>
       <c r="H1177" t="n">
         <v>784664</v>
@@ -34531,7 +34531,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.28639197349548</v>
+        <v>3.2863917350769</v>
       </c>
       <c r="H1178" t="n">
         <v>774498</v>
@@ -34618,7 +34618,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.21204614639282</v>
+        <v>3.2120463848114</v>
       </c>
       <c r="H1181" t="n">
         <v>792459</v>
@@ -34676,7 +34676,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.1741144657135</v>
+        <v>3.17411470413208</v>
       </c>
       <c r="H1183" t="n">
         <v>795009</v>
@@ -34705,7 +34705,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.16804552078247</v>
+        <v>3.16804575920105</v>
       </c>
       <c r="H1184" t="n">
         <v>742349</v>
@@ -34734,7 +34734,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.18625235557556</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1185" t="n">
         <v>456650</v>
@@ -34763,7 +34763,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.17108011245728</v>
+        <v>3.1710798740387</v>
       </c>
       <c r="H1186" t="n">
         <v>503000</v>
@@ -34850,7 +34850,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.146803855896</v>
+        <v>3.14680361747742</v>
       </c>
       <c r="H1189" t="n">
         <v>1453339</v>
@@ -34908,7 +34908,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.19232201576233</v>
+        <v>3.19232177734375</v>
       </c>
       <c r="H1191" t="n">
         <v>694833</v>
@@ -34937,7 +34937,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.17259764671326</v>
+        <v>3.17259740829468</v>
       </c>
       <c r="H1192" t="n">
         <v>860479</v>
@@ -34966,7 +34966,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.12556195259094</v>
+        <v>3.1255624294281</v>
       </c>
       <c r="H1193" t="n">
         <v>683853</v>
@@ -35024,7 +35024,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.10735535621643</v>
+        <v>3.10735511779785</v>
       </c>
       <c r="H1195" t="n">
         <v>478326</v>
@@ -35111,7 +35111,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.01935362815857</v>
+        <v>3.01935410499573</v>
       </c>
       <c r="H1198" t="n">
         <v>1026278</v>
@@ -35198,7 +35198,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.0011465549469</v>
+        <v>3.00114679336548</v>
       </c>
       <c r="H1201" t="n">
         <v>1384665</v>
@@ -35227,7 +35227,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.92983555793762</v>
+        <v>2.92983531951904</v>
       </c>
       <c r="H1202" t="n">
         <v>1535372</v>
@@ -35256,7 +35256,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.96928429603577</v>
+        <v>2.96928381919861</v>
       </c>
       <c r="H1203" t="n">
         <v>1396664</v>
@@ -35285,7 +35285,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1204" t="n">
         <v>908366</v>
@@ -35430,7 +35430,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.92983555793762</v>
+        <v>2.92983531951904</v>
       </c>
       <c r="H1209" t="n">
         <v>740997</v>
@@ -35488,7 +35488,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.94500803947449</v>
+        <v>2.94500780105591</v>
       </c>
       <c r="H1211" t="n">
         <v>993107</v>
@@ -35517,7 +35517,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1212" t="n">
         <v>2717256</v>
@@ -35546,7 +35546,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.90404176712036</v>
+        <v>2.90404200553894</v>
       </c>
       <c r="H1213" t="n">
         <v>851897</v>
@@ -35604,7 +35604,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.96776676177979</v>
+        <v>2.96776700019836</v>
       </c>
       <c r="H1215" t="n">
         <v>677275</v>
@@ -35633,7 +35633,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.92983555793762</v>
+        <v>2.92983531951904</v>
       </c>
       <c r="H1216" t="n">
         <v>737122</v>
@@ -35662,7 +35662,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.90859365463257</v>
+        <v>2.90859341621399</v>
       </c>
       <c r="H1217" t="n">
         <v>642894</v>
@@ -35720,7 +35720,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.90100717544556</v>
+        <v>2.90100693702698</v>
       </c>
       <c r="H1219" t="n">
         <v>2209640</v>
@@ -35952,7 +35952,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.82059216499329</v>
+        <v>2.82059240341187</v>
       </c>
       <c r="H1227" t="n">
         <v>1267522</v>
@@ -36039,7 +36039,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.00418138504028</v>
+        <v>3.0041811466217</v>
       </c>
       <c r="H1230" t="n">
         <v>1490931</v>
@@ -36097,7 +36097,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.0011465549469</v>
+        <v>3.00114679336548</v>
       </c>
       <c r="H1232" t="n">
         <v>969460</v>
@@ -36242,7 +36242,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.11190700531006</v>
+        <v>3.11190676689148</v>
       </c>
       <c r="H1237" t="n">
         <v>1142315</v>
@@ -36358,7 +36358,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.16804552078247</v>
+        <v>3.16804575920105</v>
       </c>
       <c r="H1241" t="n">
         <v>1460048</v>
@@ -36445,7 +36445,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.10887217521667</v>
+        <v>3.10887241363525</v>
       </c>
       <c r="H1244" t="n">
         <v>1441700</v>
@@ -36474,7 +36474,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.13314867019653</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H1245" t="n">
         <v>775909</v>
@@ -36561,7 +36561,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.03149199485779</v>
+        <v>3.03149175643921</v>
       </c>
       <c r="H1248" t="n">
         <v>686709</v>
@@ -36590,7 +36590,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.01935362815857</v>
+        <v>3.01935410499573</v>
       </c>
       <c r="H1249" t="n">
         <v>606038</v>
@@ -36619,7 +36619,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.90859365463257</v>
+        <v>2.90859341621399</v>
       </c>
       <c r="H1250" t="n">
         <v>1509515</v>
@@ -36735,7 +36735,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.90404176712036</v>
+        <v>2.90404200553894</v>
       </c>
       <c r="H1254" t="n">
         <v>499348</v>
@@ -36764,7 +36764,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.93438696861267</v>
+        <v>2.93438720703125</v>
       </c>
       <c r="H1255" t="n">
         <v>440029</v>
@@ -36793,7 +36793,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1256" t="n">
         <v>547171</v>
@@ -36851,7 +36851,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.87066221237183</v>
+        <v>2.87066197395325</v>
       </c>
       <c r="H1258" t="n">
         <v>731494</v>
@@ -36880,7 +36880,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.89493799209595</v>
+        <v>2.89493823051453</v>
       </c>
       <c r="H1259" t="n">
         <v>393668</v>
@@ -36996,7 +36996,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.77659153938293</v>
+        <v>2.77659177780151</v>
       </c>
       <c r="H1263" t="n">
         <v>1286539</v>
@@ -37025,7 +37025,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.90859365463257</v>
+        <v>2.90859341621399</v>
       </c>
       <c r="H1264" t="n">
         <v>1495015</v>
@@ -37054,7 +37054,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.78417825698853</v>
+        <v>2.78417801856995</v>
       </c>
       <c r="H1265" t="n">
         <v>1007132</v>
@@ -37141,7 +37141,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.87066221237183</v>
+        <v>2.87066197395325</v>
       </c>
       <c r="H1268" t="n">
         <v>420158</v>
@@ -37170,7 +37170,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.90100717544556</v>
+        <v>2.90100693702698</v>
       </c>
       <c r="H1269" t="n">
         <v>435035</v>
@@ -37228,7 +37228,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1271" t="n">
         <v>496839</v>
@@ -37257,7 +37257,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.99052548408508</v>
+        <v>2.99052572250366</v>
       </c>
       <c r="H1272" t="n">
         <v>794703</v>
@@ -37373,7 +37373,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.88583445549011</v>
+        <v>2.88583469390869</v>
       </c>
       <c r="H1276" t="n">
         <v>961401</v>
@@ -37489,7 +37489,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.87066221237183</v>
+        <v>2.87066197395325</v>
       </c>
       <c r="H1280" t="n">
         <v>380270</v>
@@ -37518,7 +37518,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.87066221237183</v>
+        <v>2.87066197395325</v>
       </c>
       <c r="H1281" t="n">
         <v>293660</v>
@@ -37605,7 +37605,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.88128304481506</v>
+        <v>2.88128280639648</v>
       </c>
       <c r="H1284" t="n">
         <v>547091</v>
@@ -37634,7 +37634,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.87673115730286</v>
+        <v>2.87673091888428</v>
       </c>
       <c r="H1285" t="n">
         <v>355451</v>
@@ -37663,7 +37663,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.79328155517578</v>
+        <v>2.7932813167572</v>
       </c>
       <c r="H1286" t="n">
         <v>1137489</v>
@@ -37750,7 +37750,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.77659153938293</v>
+        <v>2.77659177780151</v>
       </c>
       <c r="H1289" t="n">
         <v>503418</v>
@@ -37779,7 +37779,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.81907534599304</v>
+        <v>2.81907486915588</v>
       </c>
       <c r="H1290" t="n">
         <v>1188135</v>
@@ -37924,7 +37924,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1295" t="n">
         <v>392380</v>
@@ -37953,7 +37953,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.8023853302002</v>
+        <v>2.80238509178162</v>
       </c>
       <c r="H1296" t="n">
         <v>416748</v>
@@ -38011,7 +38011,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1298" t="n">
         <v>289927</v>
@@ -38069,7 +38069,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.77355718612671</v>
+        <v>2.77355694770813</v>
       </c>
       <c r="H1300" t="n">
         <v>604686</v>
@@ -38127,7 +38127,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.7690052986145</v>
+        <v>2.76900553703308</v>
       </c>
       <c r="H1302" t="n">
         <v>844044</v>
@@ -38156,7 +38156,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.7690052986145</v>
+        <v>2.76900553703308</v>
       </c>
       <c r="H1303" t="n">
         <v>550632</v>
@@ -38214,7 +38214,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.79479885101318</v>
+        <v>2.7947986125946</v>
       </c>
       <c r="H1305" t="n">
         <v>555953</v>
@@ -38243,7 +38243,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.78872966766357</v>
+        <v>2.78872990608215</v>
       </c>
       <c r="H1306" t="n">
         <v>1331307</v>
@@ -38301,7 +38301,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.83576488494873</v>
+        <v>2.83576464653015</v>
       </c>
       <c r="H1308" t="n">
         <v>1430517</v>
@@ -38359,7 +38359,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1310" t="n">
         <v>815994</v>
@@ -38446,7 +38446,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.95714616775513</v>
+        <v>2.95714592933655</v>
       </c>
       <c r="H1313" t="n">
         <v>907238</v>
@@ -38533,7 +38533,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.99507737159729</v>
+        <v>2.99507761001587</v>
       </c>
       <c r="H1316" t="n">
         <v>973746</v>
@@ -38620,7 +38620,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.13314867019653</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H1319" t="n">
         <v>880164</v>
@@ -38707,7 +38707,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.02997446060181</v>
+        <v>3.02997493743896</v>
       </c>
       <c r="H1322" t="n">
         <v>728288</v>
@@ -38736,7 +38736,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.04666447639465</v>
+        <v>3.04666423797607</v>
       </c>
       <c r="H1323" t="n">
         <v>376389</v>
@@ -38765,7 +38765,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1324" t="n">
         <v>266169</v>
@@ -38823,7 +38823,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.02997446060181</v>
+        <v>3.02997493743896</v>
       </c>
       <c r="H1326" t="n">
         <v>245581</v>
@@ -38852,7 +38852,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480174064636</v>
       </c>
       <c r="H1327" t="n">
         <v>237191</v>
@@ -38939,7 +38939,7 @@
         <v>4</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.03452634811401</v>
+        <v>3.03452610969543</v>
       </c>
       <c r="H1330" t="n">
         <v>342826</v>
@@ -38997,7 +38997,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.9996292591095</v>
+        <v>2.99962949752808</v>
       </c>
       <c r="H1332" t="n">
         <v>451688</v>
@@ -39026,7 +39026,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.97990489006042</v>
+        <v>2.97990465164185</v>
       </c>
       <c r="H1333" t="n">
         <v>233108</v>
@@ -39113,7 +39113,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.96624946594238</v>
+        <v>2.96624970436096</v>
       </c>
       <c r="H1336" t="n">
         <v>591694</v>
@@ -39200,7 +39200,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.8752133846283</v>
+        <v>2.87521386146545</v>
       </c>
       <c r="H1339" t="n">
         <v>499459</v>
@@ -39287,7 +39287,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.01631951332092</v>
+        <v>3.01631927490234</v>
       </c>
       <c r="H1342" t="n">
         <v>772547</v>
@@ -39316,7 +39316,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.15287327766418</v>
+        <v>3.15287303924561</v>
       </c>
       <c r="H1343" t="n">
         <v>5050376</v>
@@ -39345,7 +39345,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.23783993721008</v>
+        <v>3.2378396987915</v>
       </c>
       <c r="H1344" t="n">
         <v>1846837</v>
@@ -39403,7 +39403,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.17259764671326</v>
+        <v>3.17259740829468</v>
       </c>
       <c r="H1346" t="n">
         <v>919731</v>
@@ -39519,7 +39519,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.19990801811218</v>
+        <v>3.19990825653076</v>
       </c>
       <c r="H1350" t="n">
         <v>882238</v>
@@ -39606,7 +39606,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1353" t="n">
         <v>563496</v>
@@ -39635,7 +39635,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.99659490585327</v>
+        <v>2.99659466743469</v>
       </c>
       <c r="H1354" t="n">
         <v>805425</v>
@@ -39693,7 +39693,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.94652509689331</v>
+        <v>2.94652533531189</v>
       </c>
       <c r="H1356" t="n">
         <v>628394</v>
@@ -39722,7 +39722,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.95714616775513</v>
+        <v>2.95714592933655</v>
       </c>
       <c r="H1357" t="n">
         <v>517977</v>
@@ -39780,7 +39780,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.76141929626465</v>
+        <v>2.76141905784607</v>
       </c>
       <c r="H1359" t="n">
         <v>1809573</v>
@@ -39809,7 +39809,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.81907534599304</v>
+        <v>2.81907486915588</v>
       </c>
       <c r="H1360" t="n">
         <v>956603</v>
@@ -39838,7 +39838,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.77810883522034</v>
+        <v>2.77810907363892</v>
       </c>
       <c r="H1361" t="n">
         <v>1161975</v>
@@ -39925,7 +39925,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>2.83424758911133</v>
+        <v>2.83424782752991</v>
       </c>
       <c r="H1364" t="n">
         <v>518021</v>
@@ -40012,7 +40012,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1367" t="n">
-        <v>2.87673115730286</v>
+        <v>2.87673091888428</v>
       </c>
       <c r="H1367" t="n">
         <v>432015</v>
@@ -40070,7 +40070,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1369" t="n">
-        <v>2.86914467811584</v>
+        <v>2.86914491653442</v>
       </c>
       <c r="H1369" t="n">
         <v>321175</v>
@@ -40099,7 +40099,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1370" t="n">
-        <v>2.79935073852539</v>
+        <v>2.79935050010681</v>
       </c>
       <c r="H1370" t="n">
         <v>319342</v>
@@ -40157,7 +40157,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1372" t="n">
         <v>249851</v>
@@ -40186,7 +40186,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G1373" t="n">
-        <v>2.85852408409119</v>
+        <v>2.85852384567261</v>
       </c>
       <c r="H1373" t="n">
         <v>349137</v>
@@ -40215,7 +40215,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.89190363883972</v>
+        <v>2.8919038772583</v>
       </c>
       <c r="H1374" t="n">
         <v>317269</v>
@@ -40273,7 +40273,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>2.9131453037262</v>
+        <v>2.91314554214478</v>
       </c>
       <c r="H1376" t="n">
         <v>508884</v>
@@ -40302,7 +40302,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.9419732093811</v>
+        <v>2.94197344779968</v>
       </c>
       <c r="H1377" t="n">
         <v>364719</v>
@@ -40447,7 +40447,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.98142218589783</v>
+        <v>2.98142242431641</v>
       </c>
       <c r="H1382" t="n">
         <v>344017</v>
@@ -40476,7 +40476,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.0603199005127</v>
+        <v>3.06031966209412</v>
       </c>
       <c r="H1383" t="n">
         <v>618444</v>
@@ -40621,7 +40621,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.10887217521667</v>
+        <v>3.10887241363525</v>
       </c>
       <c r="H1388" t="n">
         <v>886487</v>
@@ -40650,7 +40650,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.12556195259094</v>
+        <v>3.1255624294281</v>
       </c>
       <c r="H1389" t="n">
         <v>563771</v>
@@ -40737,7 +40737,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.15287327766418</v>
+        <v>3.15287303924561</v>
       </c>
       <c r="H1392" t="n">
         <v>600781</v>
@@ -40766,7 +40766,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1393" t="n">
         <v>343828</v>
@@ -40795,7 +40795,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.146803855896</v>
+        <v>3.14680361747742</v>
       </c>
       <c r="H1394" t="n">
         <v>501297</v>
@@ -40824,7 +40824,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.13618278503418</v>
+        <v>3.13618302345276</v>
       </c>
       <c r="H1395" t="n">
         <v>442760</v>
@@ -40853,7 +40853,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.146803855896</v>
+        <v>3.14680361747742</v>
       </c>
       <c r="H1396" t="n">
         <v>427709</v>
@@ -40998,7 +40998,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.08459615707397</v>
+        <v>3.08459639549255</v>
       </c>
       <c r="H1401" t="n">
         <v>359292</v>
@@ -41056,7 +41056,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.08307909965515</v>
+        <v>3.08307886123657</v>
       </c>
       <c r="H1403" t="n">
         <v>397905</v>
@@ -41085,7 +41085,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.15590715408325</v>
+        <v>3.15590763092041</v>
       </c>
       <c r="H1404" t="n">
         <v>368125</v>
@@ -41143,7 +41143,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1406" t="n">
         <v>278298</v>
@@ -41201,7 +41201,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.95259428024292</v>
+        <v>2.95259404182434</v>
       </c>
       <c r="H1408" t="n">
         <v>1114048</v>
@@ -41230,7 +41230,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.02997446060181</v>
+        <v>3.02997493743896</v>
       </c>
       <c r="H1409" t="n">
         <v>664173</v>
@@ -41259,7 +41259,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.15590715408325</v>
+        <v>3.15590763092041</v>
       </c>
       <c r="H1410" t="n">
         <v>993535</v>
@@ -41288,7 +41288,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.23935699462891</v>
+        <v>3.23935651779175</v>
       </c>
       <c r="H1411" t="n">
         <v>1097424</v>
@@ -41317,7 +41317,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.210529088974</v>
+        <v>3.21052885055542</v>
       </c>
       <c r="H1412" t="n">
         <v>433525</v>
@@ -41346,7 +41346,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.08156132698059</v>
+        <v>3.08156156539917</v>
       </c>
       <c r="H1413" t="n">
         <v>1369822</v>
@@ -41491,7 +41491,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.07852721214294</v>
+        <v>3.07852697372437</v>
       </c>
       <c r="H1418" t="n">
         <v>298915</v>
@@ -41607,7 +41607,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.10735535621643</v>
+        <v>3.10735511779785</v>
       </c>
       <c r="H1422" t="n">
         <v>919096</v>
@@ -41694,7 +41694,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.01631951332092</v>
+        <v>3.01631927490234</v>
       </c>
       <c r="H1425" t="n">
         <v>626343</v>
@@ -41723,7 +41723,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.92831802368164</v>
+        <v>2.92831778526306</v>
       </c>
       <c r="H1426" t="n">
         <v>366684</v>
@@ -41752,7 +41752,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.77507448196411</v>
+        <v>2.77507424354553</v>
       </c>
       <c r="H1427" t="n">
         <v>790685</v>
@@ -41897,7 +41897,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.94500803947449</v>
+        <v>2.94500780105591</v>
       </c>
       <c r="H1432" t="n">
         <v>631432</v>
@@ -41955,7 +41955,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.01631951332092</v>
+        <v>3.01631927490234</v>
       </c>
       <c r="H1434" t="n">
         <v>670259</v>
@@ -41984,7 +41984,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.04969906806946</v>
+        <v>3.04969882965088</v>
       </c>
       <c r="H1435" t="n">
         <v>593290</v>
@@ -42013,7 +42013,7 @@
         <v>4</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.03452634811401</v>
+        <v>3.03452610969543</v>
       </c>
       <c r="H1436" t="n">
         <v>340027</v>
@@ -42042,7 +42042,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.07397532463074</v>
+        <v>3.07397556304932</v>
       </c>
       <c r="H1437" t="n">
         <v>576360</v>
@@ -42071,7 +42071,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480174064636</v>
       </c>
       <c r="H1438" t="n">
         <v>336601</v>
@@ -42100,7 +42100,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.05576825141907</v>
+        <v>3.05576801300049</v>
       </c>
       <c r="H1439" t="n">
         <v>331126</v>
@@ -42129,7 +42129,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.04818177223206</v>
+        <v>3.04818201065063</v>
       </c>
       <c r="H1440" t="n">
         <v>387125</v>
@@ -42158,7 +42158,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.05576825141907</v>
+        <v>3.05576801300049</v>
       </c>
       <c r="H1441" t="n">
         <v>366787</v>
@@ -42245,7 +42245,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.13011407852173</v>
+        <v>3.13011360168457</v>
       </c>
       <c r="H1444" t="n">
         <v>542482</v>
@@ -42274,7 +42274,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.27425408363342</v>
+        <v>3.27425384521484</v>
       </c>
       <c r="H1445" t="n">
         <v>1962674</v>
@@ -42303,7 +42303,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.18625235557556</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1446" t="n">
         <v>1656008</v>
@@ -42332,7 +42332,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.21204614639282</v>
+        <v>3.2120463848114</v>
       </c>
       <c r="H1447" t="n">
         <v>371919</v>
@@ -42361,7 +42361,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.24694347381592</v>
+        <v>3.24694323539734</v>
       </c>
       <c r="H1448" t="n">
         <v>602536</v>
@@ -42390,7 +42390,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.24846029281616</v>
+        <v>3.24846053123474</v>
       </c>
       <c r="H1449" t="n">
         <v>506516</v>
@@ -42419,7 +42419,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.18018341064453</v>
+        <v>3.18018388748169</v>
       </c>
       <c r="H1450" t="n">
         <v>489654</v>
@@ -42448,7 +42448,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.22114992141724</v>
+        <v>3.22114968299866</v>
       </c>
       <c r="H1451" t="n">
         <v>258109</v>
@@ -42506,7 +42506,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.4092903137207</v>
+        <v>3.40929055213928</v>
       </c>
       <c r="H1453" t="n">
         <v>761354</v>
@@ -42593,7 +42593,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.5564649105072</v>
+        <v>3.55646514892578</v>
       </c>
       <c r="H1456" t="n">
         <v>1120632</v>
@@ -42622,7 +42622,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.56556868553162</v>
+        <v>3.56556844711304</v>
       </c>
       <c r="H1457" t="n">
         <v>669265</v>
@@ -42651,7 +42651,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.56556868553162</v>
+        <v>3.56556844711304</v>
       </c>
       <c r="H1458" t="n">
         <v>425019</v>
@@ -42680,7 +42680,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.41991114616394</v>
+        <v>3.41991138458252</v>
       </c>
       <c r="H1459" t="n">
         <v>599042</v>
@@ -42709,7 +42709,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.36225509643555</v>
+        <v>3.36225533485413</v>
       </c>
       <c r="H1460" t="n">
         <v>1645239</v>
@@ -42738,7 +42738,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.36073803901672</v>
+        <v>3.36073780059814</v>
       </c>
       <c r="H1461" t="n">
         <v>427156</v>
@@ -42796,7 +42796,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.33797907829285</v>
+        <v>3.33797931671143</v>
       </c>
       <c r="H1463" t="n">
         <v>285885</v>
@@ -42825,7 +42825,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.3243236541748</v>
+        <v>3.32432413101196</v>
       </c>
       <c r="H1464" t="n">
         <v>237388</v>
@@ -42854,7 +42854,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.34253072738647</v>
+        <v>3.34253120422363</v>
       </c>
       <c r="H1465" t="n">
         <v>331814</v>
@@ -42883,7 +42883,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.31066799163818</v>
+        <v>3.31066823005676</v>
       </c>
       <c r="H1466" t="n">
         <v>319646</v>
@@ -42941,7 +42941,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.35466909408569</v>
+        <v>3.35466885566711</v>
       </c>
       <c r="H1468" t="n">
         <v>357288</v>
@@ -42970,7 +42970,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.36984133720398</v>
+        <v>3.36984157562256</v>
       </c>
       <c r="H1469" t="n">
         <v>293364</v>
@@ -42999,7 +42999,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.27425408363342</v>
+        <v>3.27425384521484</v>
       </c>
       <c r="H1470" t="n">
         <v>481209</v>
@@ -43086,7 +43086,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.29094338417053</v>
+        <v>3.29094362258911</v>
       </c>
       <c r="H1473" t="n">
         <v>390507</v>
@@ -43115,7 +43115,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.15742468833923</v>
+        <v>3.15742492675781</v>
       </c>
       <c r="H1474" t="n">
         <v>569682</v>
@@ -43260,7 +43260,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.25604677200317</v>
+        <v>3.25604653358459</v>
       </c>
       <c r="H1479" t="n">
         <v>389274</v>
@@ -43318,7 +43318,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.30459928512573</v>
+        <v>3.30459904670715</v>
       </c>
       <c r="H1481" t="n">
         <v>452129</v>
@@ -43376,7 +43376,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.23177075386047</v>
+        <v>3.23177099227905</v>
       </c>
       <c r="H1483" t="n">
         <v>228707</v>
@@ -43405,7 +43405,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.23935699462891</v>
+        <v>3.23935651779175</v>
       </c>
       <c r="H1484" t="n">
         <v>261437</v>
@@ -43463,7 +43463,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.30004739761353</v>
+        <v>3.3000476360321</v>
       </c>
       <c r="H1486" t="n">
         <v>471587</v>
@@ -43695,7 +43695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.18625235557556</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1494" t="n">
         <v>518313</v>
@@ -43811,7 +43811,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.99356031417847</v>
+        <v>2.99356055259705</v>
       </c>
       <c r="H1498" t="n">
         <v>373985</v>
@@ -43869,7 +43869,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.05576825141907</v>
+        <v>3.05576801300049</v>
       </c>
       <c r="H1500" t="n">
         <v>328315</v>
@@ -43927,7 +43927,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1502" t="n">
         <v>143584</v>
@@ -43985,7 +43985,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.07549262046814</v>
+        <v>3.07549238204956</v>
       </c>
       <c r="H1504" t="n">
         <v>214319</v>
@@ -44014,7 +44014,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.13314867019653</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H1505" t="n">
         <v>285059</v>
@@ -44101,7 +44101,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.07852721214294</v>
+        <v>3.07852697372437</v>
       </c>
       <c r="H1508" t="n">
         <v>181143</v>
@@ -44130,7 +44130,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.02390575408936</v>
+        <v>3.02390551567078</v>
       </c>
       <c r="H1509" t="n">
         <v>408312</v>
@@ -44188,7 +44188,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.99052548408508</v>
+        <v>2.99052572250366</v>
       </c>
       <c r="H1511" t="n">
         <v>201084</v>
@@ -44217,7 +44217,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.96928429603577</v>
+        <v>2.96928381919861</v>
       </c>
       <c r="H1512" t="n">
         <v>345482</v>
@@ -44246,7 +44246,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.97080111503601</v>
+        <v>2.97080135345459</v>
       </c>
       <c r="H1513" t="n">
         <v>181894</v>
@@ -44275,7 +44275,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480174064636</v>
       </c>
       <c r="H1514" t="n">
         <v>243119</v>
@@ -44333,7 +44333,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.02694034576416</v>
+        <v>3.02694010734558</v>
       </c>
       <c r="H1516" t="n">
         <v>124790</v>
@@ -44391,7 +44391,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.04969906806946</v>
+        <v>3.04969882965088</v>
       </c>
       <c r="H1518" t="n">
         <v>105502</v>
@@ -44594,7 +44594,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.19990801811218</v>
+        <v>3.19990825653076</v>
       </c>
       <c r="H1525" t="n">
         <v>308905</v>
@@ -44623,7 +44623,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1526" t="n">
         <v>227220</v>
@@ -44652,7 +44652,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.18928718566895</v>
+        <v>3.18928742408752</v>
       </c>
       <c r="H1527" t="n">
         <v>216398</v>
@@ -44681,7 +44681,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.16956305503845</v>
+        <v>3.16956281661987</v>
       </c>
       <c r="H1528" t="n">
         <v>115488</v>
@@ -44710,7 +44710,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.18625235557556</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1529" t="n">
         <v>156797</v>
@@ -44739,7 +44739,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.23328804969788</v>
+        <v>3.2332878112793</v>
       </c>
       <c r="H1530" t="n">
         <v>390737</v>
@@ -44768,7 +44768,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.22570157051086</v>
+        <v>3.22570133209229</v>
       </c>
       <c r="H1531" t="n">
         <v>181014</v>
@@ -44797,7 +44797,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.2348051071167</v>
+        <v>3.23480534553528</v>
       </c>
       <c r="H1532" t="n">
         <v>196107</v>
@@ -44826,7 +44826,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.31977152824402</v>
+        <v>3.3197717666626</v>
       </c>
       <c r="H1533" t="n">
         <v>379962</v>
@@ -44855,7 +44855,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.22114992141724</v>
+        <v>3.22114968299866</v>
       </c>
       <c r="H1534" t="n">
         <v>421937</v>
@@ -44884,7 +44884,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.25756454467773</v>
+        <v>3.25756430625916</v>
       </c>
       <c r="H1535" t="n">
         <v>278442</v>
@@ -44913,7 +44913,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.28790926933289</v>
+        <v>3.28790950775146</v>
       </c>
       <c r="H1536" t="n">
         <v>422360</v>
@@ -44942,7 +44942,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.23177075386047</v>
+        <v>3.23177099227905</v>
       </c>
       <c r="H1537" t="n">
         <v>343058</v>
@@ -44971,7 +44971,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.23935699462891</v>
+        <v>3.23935651779175</v>
       </c>
       <c r="H1538" t="n">
         <v>123708</v>
@@ -45000,7 +45000,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.22266697883606</v>
+        <v>3.22266721725464</v>
       </c>
       <c r="H1539" t="n">
         <v>117559</v>
@@ -45029,7 +45029,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.22570157051086</v>
+        <v>3.22570133209229</v>
       </c>
       <c r="H1540" t="n">
         <v>79916</v>
@@ -45058,7 +45058,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.23783993721008</v>
+        <v>3.2378396987915</v>
       </c>
       <c r="H1541" t="n">
         <v>181142</v>
@@ -45087,7 +45087,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.210529088974</v>
+        <v>3.21052885055542</v>
       </c>
       <c r="H1542" t="n">
         <v>119327</v>
@@ -45116,7 +45116,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.210529088974</v>
+        <v>3.21052885055542</v>
       </c>
       <c r="H1543" t="n">
         <v>44780</v>
@@ -45174,7 +45174,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.17866659164429</v>
+        <v>3.17866635322571</v>
       </c>
       <c r="H1545" t="n">
         <v>211170</v>
@@ -45203,7 +45203,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.17108011245728</v>
+        <v>3.1710798740387</v>
       </c>
       <c r="H1546" t="n">
         <v>128014</v>
@@ -45232,7 +45232,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.19232201576233</v>
+        <v>3.19232177734375</v>
       </c>
       <c r="H1547" t="n">
         <v>147278</v>
@@ -45290,7 +45290,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.15287327766418</v>
+        <v>3.15287303924561</v>
       </c>
       <c r="H1549" t="n">
         <v>97630</v>
@@ -45319,7 +45319,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11190700531006</v>
+        <v>3.11190676689148</v>
       </c>
       <c r="H1550" t="n">
         <v>104079</v>
@@ -45348,7 +45348,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.12556195259094</v>
+        <v>3.1255624294281</v>
       </c>
       <c r="H1551" t="n">
         <v>95083</v>
@@ -45406,7 +45406,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.04211282730103</v>
+        <v>3.0421130657196</v>
       </c>
       <c r="H1553" t="n">
         <v>246704</v>
@@ -45464,7 +45464,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.04818177223206</v>
+        <v>3.04818201065063</v>
       </c>
       <c r="H1555" t="n">
         <v>65866</v>
@@ -45522,7 +45522,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.07397532463074</v>
+        <v>3.07397556304932</v>
       </c>
       <c r="H1557" t="n">
         <v>162365</v>
@@ -45551,7 +45551,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376926422119</v>
       </c>
       <c r="H1558" t="n">
         <v>185411</v>
@@ -45580,7 +45580,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.18625235557556</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1559" t="n">
         <v>310762</v>
@@ -45638,7 +45638,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.1741144657135</v>
+        <v>3.17411470413208</v>
       </c>
       <c r="H1561" t="n">
         <v>145308</v>
@@ -45667,7 +45667,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.12859654426575</v>
+        <v>3.12859702110291</v>
       </c>
       <c r="H1562" t="n">
         <v>99352</v>
@@ -45696,7 +45696,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.1756317615509</v>
+        <v>3.17563152313232</v>
       </c>
       <c r="H1563" t="n">
         <v>123173</v>
@@ -45783,7 +45783,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.05728530883789</v>
+        <v>3.05728554725647</v>
       </c>
       <c r="H1566" t="n">
         <v>135673</v>
@@ -45899,7 +45899,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.83879971504211</v>
+        <v>2.83879947662354</v>
       </c>
       <c r="H1570" t="n">
         <v>222045</v>
@@ -45986,7 +45986,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.73866009712219</v>
+        <v>2.73865985870361</v>
       </c>
       <c r="H1573" t="n">
         <v>294443</v>
@@ -46073,7 +46073,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.9131453037262</v>
+        <v>2.91314554214478</v>
       </c>
       <c r="H1576" t="n">
         <v>146290</v>
@@ -46131,7 +46131,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.78569531440735</v>
+        <v>2.78569507598877</v>
       </c>
       <c r="H1578" t="n">
         <v>222101</v>
@@ -46160,7 +46160,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.79935073852539</v>
+        <v>2.79935050010681</v>
       </c>
       <c r="H1579" t="n">
         <v>175350</v>
@@ -46189,7 +46189,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.79935073852539</v>
+        <v>2.79935050010681</v>
       </c>
       <c r="H1580" t="n">
         <v>242347</v>
@@ -46218,7 +46218,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.81300616264343</v>
+        <v>2.81300592422485</v>
       </c>
       <c r="H1581" t="n">
         <v>337756</v>
@@ -46247,7 +46247,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.75838422775269</v>
+        <v>2.75838446617126</v>
       </c>
       <c r="H1582" t="n">
         <v>159652</v>
@@ -46276,7 +46276,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.77355718612671</v>
+        <v>2.77355694770813</v>
       </c>
       <c r="H1583" t="n">
         <v>180777</v>
@@ -46305,7 +46305,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.76141929626465</v>
+        <v>2.76141905784607</v>
       </c>
       <c r="H1584" t="n">
         <v>193202</v>
@@ -46334,7 +46334,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.82210969924927</v>
+        <v>2.82210946083069</v>
       </c>
       <c r="H1585" t="n">
         <v>140503</v>
@@ -46392,7 +46392,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.83576488494873</v>
+        <v>2.83576464653015</v>
       </c>
       <c r="H1587" t="n">
         <v>208957</v>
@@ -46450,7 +46450,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.79328155517578</v>
+        <v>2.7932813167572</v>
       </c>
       <c r="H1589" t="n">
         <v>299482</v>
@@ -46479,7 +46479,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.87620687484741</v>
+        <v>2.87620711326599</v>
       </c>
       <c r="H1590" t="n">
         <v>313040</v>
@@ -46595,7 +46595,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.01063823699951</v>
+        <v>3.01063847541809</v>
       </c>
       <c r="H1594" t="n">
         <v>176564</v>
@@ -46653,7 +46653,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.0544068813324</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1596" t="n">
         <v>142847</v>
@@ -46711,7 +46711,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1598" t="n">
         <v>193796</v>
@@ -46740,7 +46740,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.96374368667603</v>
+        <v>2.9637439250946</v>
       </c>
       <c r="H1599" t="n">
         <v>447180</v>
@@ -46827,7 +46827,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.98250126838684</v>
+        <v>2.982501745224</v>
       </c>
       <c r="H1602" t="n">
         <v>358466</v>
@@ -46914,7 +46914,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.04815411567688</v>
+        <v>3.04815435409546</v>
       </c>
       <c r="H1605" t="n">
         <v>199394</v>
@@ -46943,7 +46943,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.14194345474243</v>
+        <v>3.14194321632385</v>
       </c>
       <c r="H1606" t="n">
         <v>1027100</v>
@@ -46972,7 +46972,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.17164373397827</v>
+        <v>3.17164325714111</v>
       </c>
       <c r="H1607" t="n">
         <v>912843</v>
@@ -47001,7 +47001,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.27637481689453</v>
+        <v>3.27637505531311</v>
       </c>
       <c r="H1608" t="n">
         <v>1344939</v>
@@ -47059,7 +47059,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.25605368614197</v>
+        <v>3.25605392456055</v>
       </c>
       <c r="H1610" t="n">
         <v>259772</v>
@@ -47146,7 +47146,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.3560962677002</v>
+        <v>3.35609602928162</v>
       </c>
       <c r="H1613" t="n">
         <v>205646</v>
@@ -47204,7 +47204,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.29044342041016</v>
+        <v>3.29044318199158</v>
       </c>
       <c r="H1615" t="n">
         <v>369273</v>
@@ -47262,7 +47262,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.30763792991638</v>
+        <v>3.3076376914978</v>
       </c>
       <c r="H1617" t="n">
         <v>409466</v>
@@ -47291,7 +47291,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.36078524589539</v>
+        <v>3.36078548431396</v>
       </c>
       <c r="H1618" t="n">
         <v>449061</v>
@@ -47320,7 +47320,7 @@
         <v>4.31400012969971</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.37172770500183</v>
+        <v>3.37172722816467</v>
       </c>
       <c r="H1619" t="n">
         <v>421861</v>
@@ -47378,7 +47378,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.32326984405518</v>
+        <v>3.3232696056366</v>
       </c>
       <c r="H1621" t="n">
         <v>404511</v>
@@ -47639,7 +47639,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.15601181983948</v>
+        <v>3.15601205825806</v>
       </c>
       <c r="H1630" t="n">
         <v>259444</v>
@@ -47668,7 +47668,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.1372537612915</v>
+        <v>3.13725399971008</v>
       </c>
       <c r="H1631" t="n">
         <v>224274</v>
@@ -47697,7 +47697,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.14819622039795</v>
+        <v>3.14819598197937</v>
       </c>
       <c r="H1632" t="n">
         <v>228241</v>
@@ -47755,7 +47755,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.1372537612915</v>
+        <v>3.13725399971008</v>
       </c>
       <c r="H1634" t="n">
         <v>122879</v>
@@ -47900,7 +47900,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.11537003517151</v>
+        <v>3.11536979675293</v>
       </c>
       <c r="H1639" t="n">
         <v>100419</v>
@@ -47929,7 +47929,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.16695404052734</v>
+        <v>3.16695427894592</v>
       </c>
       <c r="H1640" t="n">
         <v>251186</v>
@@ -47958,7 +47958,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.16851711273193</v>
+        <v>3.16851735115051</v>
       </c>
       <c r="H1641" t="n">
         <v>107139</v>
@@ -48016,7 +48016,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.19509077072144</v>
+        <v>3.19509053230286</v>
       </c>
       <c r="H1643" t="n">
         <v>90490</v>
@@ -48074,7 +48074,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.29044342041016</v>
+        <v>3.29044318199158</v>
       </c>
       <c r="H1645" t="n">
         <v>138844</v>
@@ -48393,7 +48393,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.38423252105713</v>
+        <v>3.38423275947571</v>
       </c>
       <c r="H1656" t="n">
         <v>233036</v>
@@ -48451,7 +48451,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.32639622688293</v>
+        <v>3.32639598846436</v>
       </c>
       <c r="H1658" t="n">
         <v>132296</v>
@@ -48538,7 +48538,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.34359049797058</v>
+        <v>3.34359073638916</v>
       </c>
       <c r="H1661" t="n">
         <v>255129</v>
@@ -48596,7 +48596,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.40924334526062</v>
+        <v>3.40924310684204</v>
       </c>
       <c r="H1663" t="n">
         <v>472093</v>
@@ -48625,7 +48625,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1664" t="n">
-        <v>3.41549587249756</v>
+        <v>3.41549563407898</v>
       </c>
       <c r="H1664" t="n">
         <v>196646</v>
@@ -48683,7 +48683,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.37797999382019</v>
+        <v>3.37798023223877</v>
       </c>
       <c r="H1666" t="n">
         <v>232444</v>
@@ -48712,7 +48712,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.38423252105713</v>
+        <v>3.38423275947571</v>
       </c>
       <c r="H1667" t="n">
         <v>164728</v>
@@ -48828,7 +48828,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G1671" t="n">
-        <v>3.25605368614197</v>
+        <v>3.25605392456055</v>
       </c>
       <c r="H1671" t="n">
         <v>245443</v>
@@ -48886,7 +48886,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1673" t="n">
-        <v>3.19196462631226</v>
+        <v>3.19196438789368</v>
       </c>
       <c r="H1673" t="n">
         <v>401389</v>
@@ -48915,7 +48915,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1674" t="n">
-        <v>3.18571186065674</v>
+        <v>3.18571209907532</v>
       </c>
       <c r="H1674" t="n">
         <v>190170</v>
@@ -48944,7 +48944,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.14663314819336</v>
+        <v>3.14663290977478</v>
       </c>
       <c r="H1675" t="n">
         <v>113108</v>
@@ -48973,7 +48973,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.17945885658264</v>
+        <v>3.17945909500122</v>
       </c>
       <c r="H1676" t="n">
         <v>427824</v>
@@ -49002,7 +49002,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.20915913581848</v>
+        <v>3.20915937423706</v>
       </c>
       <c r="H1677" t="n">
         <v>186125</v>
@@ -49118,7 +49118,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.2357325553894</v>
+        <v>3.23573279380798</v>
       </c>
       <c r="H1681" t="n">
         <v>155172</v>
@@ -49350,7 +49350,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.15757489204407</v>
+        <v>3.15757513046265</v>
       </c>
       <c r="H1689" t="n">
         <v>357386</v>
@@ -49466,7 +49466,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.02939605712891</v>
+        <v>3.02939629554749</v>
       </c>
       <c r="H1693" t="n">
         <v>576621</v>
@@ -49524,7 +49524,7 @@
         <v>4</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.1263120174408</v>
+        <v>3.12631177902222</v>
       </c>
       <c r="H1695" t="n">
         <v>378934</v>
@@ -49553,7 +49553,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.0544068813324</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1696" t="n">
         <v>504766</v>
@@ -49611,7 +49611,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.95592784881592</v>
+        <v>2.9559280872345</v>
       </c>
       <c r="H1698" t="n">
         <v>542528</v>
@@ -49640,7 +49640,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.95280194282532</v>
+        <v>2.95280170440674</v>
       </c>
       <c r="H1699" t="n">
         <v>464504</v>
@@ -49669,7 +49669,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.92779135704041</v>
+        <v>2.92779111862183</v>
       </c>
       <c r="H1700" t="n">
         <v>339373</v>
@@ -49727,7 +49727,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.00125932693481</v>
+        <v>3.00125956535339</v>
       </c>
       <c r="H1702" t="n">
         <v>623855</v>
@@ -49814,7 +49814,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G1705" t="n">
-        <v>3.02783298492432</v>
+        <v>3.0278332233429</v>
       </c>
       <c r="H1705" t="n">
         <v>521469</v>
@@ -49959,7 +49959,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.21697545051575</v>
+        <v>3.21697497367859</v>
       </c>
       <c r="H1710" t="n">
         <v>573601</v>
@@ -50017,7 +50017,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.21228551864624</v>
+        <v>3.21228575706482</v>
       </c>
       <c r="H1712" t="n">
         <v>219277</v>
@@ -50104,7 +50104,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.21228551864624</v>
+        <v>3.21228575706482</v>
       </c>
       <c r="H1715" t="n">
         <v>419873</v>
@@ -50365,7 +50365,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.215411901474</v>
+        <v>3.21541166305542</v>
       </c>
       <c r="H1724" t="n">
         <v>490656</v>
@@ -50539,7 +50539,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.17945885658264</v>
+        <v>3.17945909500122</v>
       </c>
       <c r="H1730" t="n">
         <v>1249080</v>
@@ -50568,7 +50568,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.17320680618286</v>
+        <v>3.1732063293457</v>
       </c>
       <c r="H1731" t="n">
         <v>384659</v>
@@ -50597,7 +50597,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.17945885658264</v>
+        <v>3.17945909500122</v>
       </c>
       <c r="H1732" t="n">
         <v>200219</v>
@@ -50655,7 +50655,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.21072196960449</v>
+        <v>3.21072220802307</v>
       </c>
       <c r="H1734" t="n">
         <v>340017</v>
@@ -50684,7 +50684,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.18571186065674</v>
+        <v>3.18571209907532</v>
       </c>
       <c r="H1735" t="n">
         <v>240241</v>
@@ -50713,7 +50713,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.19196462631226</v>
+        <v>3.19196438789368</v>
       </c>
       <c r="H1736" t="n">
         <v>291642</v>
@@ -50742,7 +50742,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.19977998733521</v>
+        <v>3.19978022575378</v>
       </c>
       <c r="H1737" t="n">
         <v>281064</v>
@@ -50771,7 +50771,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.1528856754303</v>
+        <v>3.15288519859314</v>
       </c>
       <c r="H1738" t="n">
         <v>187427</v>
@@ -50829,7 +50829,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.16382765769958</v>
+        <v>3.16382741928101</v>
       </c>
       <c r="H1740" t="n">
         <v>300213</v>
@@ -50858,7 +50858,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.16070151329041</v>
+        <v>3.16070127487183</v>
       </c>
       <c r="H1741" t="n">
         <v>77343</v>
@@ -50916,7 +50916,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08723306655884</v>
+        <v>3.08723282814026</v>
       </c>
       <c r="H1743" t="n">
         <v>413231</v>
@@ -50974,7 +50974,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.17164373397827</v>
+        <v>3.17164325714111</v>
       </c>
       <c r="H1745" t="n">
         <v>119164</v>
@@ -51003,7 +51003,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.12787508964539</v>
+        <v>3.12787485122681</v>
       </c>
       <c r="H1746" t="n">
         <v>485176</v>
@@ -51032,7 +51032,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.12318587303162</v>
+        <v>3.12318563461304</v>
       </c>
       <c r="H1747" t="n">
         <v>491645</v>
@@ -51177,7 +51177,7 @@
         <v>4</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.1263120174408</v>
+        <v>3.12631177902222</v>
       </c>
       <c r="H1752" t="n">
         <v>280969</v>
@@ -51235,7 +51235,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1754" t="n">
-        <v>3.15913796424866</v>
+        <v>3.15913820266724</v>
       </c>
       <c r="H1754" t="n">
         <v>410306</v>
@@ -51264,7 +51264,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.15601181983948</v>
+        <v>3.15601205825806</v>
       </c>
       <c r="H1755" t="n">
         <v>391398</v>
@@ -51293,7 +51293,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1756" t="n">
-        <v>3.13412761688232</v>
+        <v>3.1341278553009</v>
       </c>
       <c r="H1756" t="n">
         <v>185884</v>
@@ -51322,7 +51322,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G1757" t="n">
-        <v>3.1372537612915</v>
+        <v>3.13725399971008</v>
       </c>
       <c r="H1757" t="n">
         <v>161317</v>
@@ -51380,7 +51380,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.07629084587097</v>
+        <v>3.07629108428955</v>
       </c>
       <c r="H1759" t="n">
         <v>274254</v>
@@ -51612,7 +51612,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.0544068813324</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1767" t="n">
         <v>231550</v>
@@ -51670,7 +51670,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.9731228351593</v>
+        <v>2.97312259674072</v>
       </c>
       <c r="H1769" t="n">
         <v>759401</v>
@@ -51699,7 +51699,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.02939605712891</v>
+        <v>3.02939629554749</v>
       </c>
       <c r="H1770" t="n">
         <v>534154</v>
@@ -51757,7 +51757,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1772" t="n">
         <v>331989</v>
@@ -51873,7 +51873,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.02001762390137</v>
+        <v>3.02001738548279</v>
       </c>
       <c r="H1776" t="n">
         <v>300724</v>
@@ -51931,7 +51931,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.07629084587097</v>
+        <v>3.07629108428955</v>
       </c>
       <c r="H1778" t="n">
         <v>317996</v>
@@ -51960,7 +51960,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.04190158843994</v>
+        <v>3.04190135002136</v>
       </c>
       <c r="H1779" t="n">
         <v>280743</v>
@@ -51989,7 +51989,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.03095936775208</v>
+        <v>3.03095960617065</v>
       </c>
       <c r="H1780" t="n">
         <v>343443</v>
@@ -52163,7 +52163,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.05128026008606</v>
+        <v>3.05128049850464</v>
       </c>
       <c r="H1786" t="n">
         <v>378015</v>
@@ -52250,7 +52250,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.95592784881592</v>
+        <v>2.9559280872345</v>
       </c>
       <c r="H1789" t="n">
         <v>523389</v>
@@ -52279,7 +52279,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.9137225151062</v>
+        <v>2.91372275352478</v>
       </c>
       <c r="H1790" t="n">
         <v>835243</v>
@@ -52308,7 +52308,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.90278077125549</v>
+        <v>2.90278029441833</v>
       </c>
       <c r="H1791" t="n">
         <v>397165</v>
@@ -52337,7 +52337,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.88089656829834</v>
+        <v>2.88089632987976</v>
       </c>
       <c r="H1792" t="n">
         <v>398855</v>
@@ -52366,7 +52366,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.89652800559998</v>
+        <v>2.89652824401855</v>
       </c>
       <c r="H1793" t="n">
         <v>298260</v>
@@ -52482,7 +52482,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.85275959968567</v>
+        <v>2.85275983810425</v>
       </c>
       <c r="H1797" t="n">
         <v>348055</v>
@@ -52598,7 +52598,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.85744905471802</v>
+        <v>2.85744881629944</v>
       </c>
       <c r="H1801" t="n">
         <v>234603</v>
@@ -52627,7 +52627,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.85744905471802</v>
+        <v>2.85744881629944</v>
       </c>
       <c r="H1802" t="n">
         <v>217632</v>
@@ -52743,7 +52743,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.92466497421265</v>
+        <v>2.92466473579407</v>
       </c>
       <c r="H1806" t="n">
         <v>324520</v>
@@ -52888,7 +52888,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.87620687484741</v>
+        <v>2.87620711326599</v>
       </c>
       <c r="H1811" t="n">
         <v>265710</v>
@@ -52917,7 +52917,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.87620687484741</v>
+        <v>2.87620711326599</v>
       </c>
       <c r="H1812" t="n">
         <v>215725</v>
@@ -52975,7 +52975,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.90434408187866</v>
+        <v>2.90434384346008</v>
       </c>
       <c r="H1814" t="n">
         <v>263441</v>
@@ -53062,7 +53062,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.877769947052</v>
+        <v>2.87777018547058</v>
       </c>
       <c r="H1817" t="n">
         <v>356081</v>
@@ -53091,7 +53091,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.85901236534119</v>
+        <v>2.85901212692261</v>
       </c>
       <c r="H1818" t="n">
         <v>392072</v>
@@ -53149,7 +53149,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.82305979728699</v>
+        <v>2.82305955886841</v>
       </c>
       <c r="H1820" t="n">
         <v>491195</v>
@@ -53178,7 +53178,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.82931208610535</v>
+        <v>2.82931232452393</v>
       </c>
       <c r="H1821" t="n">
         <v>786924</v>
@@ -53236,7 +53236,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.81211757659912</v>
+        <v>2.81211733818054</v>
       </c>
       <c r="H1823" t="n">
         <v>525406</v>
@@ -53265,7 +53265,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.8058648109436</v>
+        <v>2.80586504936218</v>
       </c>
       <c r="H1824" t="n">
         <v>262774</v>
@@ -53323,7 +53323,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68393898010254</v>
+        <v>2.68393850326538</v>
       </c>
       <c r="H1826" t="n">
         <v>842330</v>
@@ -53352,7 +53352,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70894956588745</v>
+        <v>2.70894932746887</v>
       </c>
       <c r="H1827" t="n">
         <v>321163</v>
@@ -53381,7 +53381,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.72301769256592</v>
+        <v>2.72301745414734</v>
       </c>
       <c r="H1828" t="n">
         <v>487170</v>
@@ -53410,7 +53410,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.73864889144897</v>
+        <v>2.73864912986755</v>
       </c>
       <c r="H1829" t="n">
         <v>946979</v>
@@ -53439,7 +53439,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.70425987243652</v>
+        <v>2.70425963401794</v>
       </c>
       <c r="H1830" t="n">
         <v>451437</v>
@@ -53468,7 +53468,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.65580201148987</v>
+        <v>2.65580177307129</v>
       </c>
       <c r="H1831" t="n">
         <v>727062</v>
@@ -53497,7 +53497,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.65267562866211</v>
+        <v>2.65267586708069</v>
       </c>
       <c r="H1832" t="n">
         <v>378823</v>
@@ -53555,7 +53555,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.65580201148987</v>
+        <v>2.65580177307129</v>
       </c>
       <c r="H1834" t="n">
         <v>350276</v>
@@ -53642,7 +53642,7 @@
         <v>3.30200004577637</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.58077073097229</v>
+        <v>2.58077049255371</v>
       </c>
       <c r="H1837" t="n">
         <v>838954</v>
@@ -53671,7 +53671,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.62453889846802</v>
+        <v>2.6245391368866</v>
       </c>
       <c r="H1838" t="n">
         <v>574992</v>
@@ -53758,7 +53758,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.54950761795044</v>
+        <v>2.54950737953186</v>
       </c>
       <c r="H1841" t="n">
         <v>539251</v>
@@ -53903,7 +53903,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.50287103652954</v>
+        <v>2.50287127494812</v>
       </c>
       <c r="H1846" t="n">
         <v>602614</v>
@@ -53932,7 +53932,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.53453230857849</v>
+        <v>2.53453207015991</v>
       </c>
       <c r="H1847" t="n">
         <v>707112</v>
@@ -54048,7 +54048,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.61951637268066</v>
+        <v>2.61951661109924</v>
       </c>
       <c r="H1851" t="n">
         <v>370048</v>
@@ -54309,7 +54309,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.74615979194641</v>
+        <v>2.74615955352783</v>
       </c>
       <c r="H1860" t="n">
         <v>379448</v>
@@ -54367,7 +54367,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.77948689460754</v>
+        <v>2.77948665618896</v>
       </c>
       <c r="H1862" t="n">
         <v>577732</v>
@@ -54773,7 +54773,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.69616913795471</v>
+        <v>2.69616889953613</v>
       </c>
       <c r="H1876" t="n">
         <v>421865</v>
@@ -54918,7 +54918,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.74449348449707</v>
+        <v>2.74449324607849</v>
       </c>
       <c r="H1881" t="n">
         <v>257730</v>
@@ -55063,7 +55063,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.84614109992981</v>
+        <v>2.84614133834839</v>
       </c>
       <c r="H1886" t="n">
         <v>395393</v>
@@ -55179,7 +55179,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.86780381202698</v>
+        <v>2.86780405044556</v>
       </c>
       <c r="H1890" t="n">
         <v>655477</v>
@@ -55237,7 +55237,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.86280488967896</v>
+        <v>2.86280512809753</v>
       </c>
       <c r="H1892" t="n">
         <v>349116</v>
@@ -55353,7 +55353,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.80614852905273</v>
+        <v>2.80614876747131</v>
       </c>
       <c r="H1896" t="n">
         <v>426755</v>
@@ -55382,7 +55382,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.8278112411499</v>
+        <v>2.82781147956848</v>
       </c>
       <c r="H1897" t="n">
         <v>268702</v>
@@ -55411,7 +55411,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.84780764579773</v>
+        <v>2.84780740737915</v>
       </c>
       <c r="H1898" t="n">
         <v>325266</v>
@@ -55469,7 +55469,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.79281759262085</v>
+        <v>2.79281783103943</v>
       </c>
       <c r="H1900" t="n">
         <v>438756</v>
@@ -55701,7 +55701,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.78448581695557</v>
+        <v>2.78448605537415</v>
       </c>
       <c r="H1908" t="n">
         <v>413850</v>
@@ -56020,7 +56020,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.84114217758179</v>
+        <v>2.84114241600037</v>
       </c>
       <c r="H1919" t="n">
         <v>438124</v>
@@ -56049,7 +56049,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.7628231048584</v>
+        <v>2.76282334327698</v>
       </c>
       <c r="H1920" t="n">
         <v>1567570</v>
@@ -56107,7 +56107,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.74615979194641</v>
+        <v>2.74615955352783</v>
       </c>
       <c r="H1922" t="n">
         <v>303173</v>
@@ -56194,7 +56194,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.74615979194641</v>
+        <v>2.74615955352783</v>
       </c>
       <c r="H1925" t="n">
         <v>253905</v>
@@ -56368,7 +56368,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.71783185005188</v>
+        <v>2.7178316116333</v>
       </c>
       <c r="H1931" t="n">
         <v>294374</v>
@@ -56426,7 +56426,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.72116446495056</v>
+        <v>2.72116422653198</v>
       </c>
       <c r="H1933" t="n">
         <v>395549</v>
@@ -56571,7 +56571,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.75949048995972</v>
+        <v>2.7594907283783</v>
       </c>
       <c r="H1938" t="n">
         <v>478882</v>
@@ -56861,7 +56861,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.74282717704773</v>
+        <v>2.74282693862915</v>
       </c>
       <c r="H1948" t="n">
         <v>444594</v>
@@ -56948,7 +56948,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.12275671958923</v>
+        <v>3.12275695800781</v>
       </c>
       <c r="H1951" t="n">
         <v>3068307</v>
@@ -56977,7 +56977,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.13942050933838</v>
+        <v>3.1394202709198</v>
       </c>
       <c r="H1952" t="n">
         <v>2001061</v>
@@ -57035,7 +57035,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.23773550987244</v>
+        <v>3.23773574829102</v>
       </c>
       <c r="H1954" t="n">
         <v>1000550</v>
@@ -57180,7 +57180,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.28772640228271</v>
+        <v>3.28772664070129</v>
       </c>
       <c r="H1959" t="n">
         <v>759335</v>
@@ -57238,7 +57238,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.22273826599121</v>
+        <v>3.22273850440979</v>
       </c>
       <c r="H1961" t="n">
         <v>423991</v>
@@ -57267,7 +57267,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.17941284179688</v>
+        <v>3.17941308021545</v>
       </c>
       <c r="H1962" t="n">
         <v>831173</v>
@@ -57325,7 +57325,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.11609148979187</v>
+        <v>3.11609125137329</v>
       </c>
       <c r="H1964" t="n">
         <v>650589</v>
@@ -57412,7 +57412,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.10109400749207</v>
+        <v>3.10109424591064</v>
       </c>
       <c r="H1967" t="n">
         <v>586258</v>
@@ -57499,7 +57499,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.12275671958923</v>
+        <v>3.12275695800781</v>
       </c>
       <c r="H1970" t="n">
         <v>903295</v>
@@ -57557,7 +57557,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.16441607475281</v>
+        <v>3.16441583633423</v>
       </c>
       <c r="H1972" t="n">
         <v>316224</v>
@@ -57615,7 +57615,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.24273490905762</v>
+        <v>3.24273467063904</v>
       </c>
       <c r="H1974" t="n">
         <v>498769</v>
@@ -57644,7 +57644,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.24273490905762</v>
+        <v>3.24273467063904</v>
       </c>
       <c r="H1975" t="n">
         <v>535966</v>
@@ -57818,7 +57818,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.34104990959167</v>
+        <v>3.34105014801025</v>
       </c>
       <c r="H1981" t="n">
         <v>833546</v>
@@ -58050,7 +58050,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.3610463142395</v>
+        <v>3.36104607582092</v>
       </c>
       <c r="H1989" t="n">
         <v>763026</v>
@@ -75862,6 +75862,35 @@
         <v>361579</v>
       </c>
       <c r="I2603" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2604">
+      <c r="A2604" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2604" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2604" t="n">
+        <v>4.92399978637695</v>
+      </c>
+      <c r="D2604" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E2604" t="n">
+        <v>4.92399978637695</v>
+      </c>
+      <c r="F2604" t="n">
+        <v>4.9520001411438</v>
+      </c>
+      <c r="G2604" t="n">
+        <v>4.9520001411438</v>
+      </c>
+      <c r="H2604" t="n">
+        <v>830610</v>
+      </c>
+      <c r="I2604" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26321315765381</v>
+        <v>2.26321339607239</v>
       </c>
       <c r="H4" t="n">
         <v>8182968</v>
@@ -514,7 +514,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24304008483887</v>
+        <v>2.24303984642029</v>
       </c>
       <c r="H5" t="n">
         <v>6798460</v>
@@ -543,7 +543,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3048210144043</v>
+        <v>2.30482149124146</v>
       </c>
       <c r="H6" t="n">
         <v>4016992</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>2.33256006240845</v>
+        <v>2.33255958557129</v>
       </c>
       <c r="H7" t="n">
         <v>3592063</v>
@@ -601,7 +601,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33256006240845</v>
+        <v>2.33255958557129</v>
       </c>
       <c r="H8" t="n">
         <v>2256529</v>
@@ -630,7 +630,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38677620887756</v>
+        <v>2.38677644729614</v>
       </c>
       <c r="H9" t="n">
         <v>3631224</v>
@@ -717,7 +717,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G12" t="n">
-        <v>2.31238651275635</v>
+        <v>2.31238675117493</v>
       </c>
       <c r="H12" t="n">
         <v>1077176</v>
@@ -746,7 +746,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3489511013031</v>
+        <v>2.34895086288452</v>
       </c>
       <c r="H13" t="n">
         <v>1874026</v>
@@ -775,7 +775,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G14" t="n">
-        <v>2.37921142578125</v>
+        <v>2.37921118736267</v>
       </c>
       <c r="H14" t="n">
         <v>2690138</v>
@@ -862,7 +862,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26951766014099</v>
+        <v>2.26951789855957</v>
       </c>
       <c r="H17" t="n">
         <v>1072096</v>
@@ -1065,7 +1065,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.33508205413818</v>
+        <v>2.33508157730103</v>
       </c>
       <c r="H24" t="n">
         <v>434879</v>
@@ -1094,7 +1094,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32877707481384</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H25" t="n">
         <v>276607</v>
@@ -1152,7 +1152,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G27" t="n">
-        <v>2.34516859054565</v>
+        <v>2.3451681137085</v>
       </c>
       <c r="H27" t="n">
         <v>2312938</v>
@@ -1181,7 +1181,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G28" t="n">
-        <v>2.37542843818665</v>
+        <v>2.37542867660522</v>
       </c>
       <c r="H28" t="n">
         <v>1425652</v>
@@ -1210,7 +1210,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G29" t="n">
-        <v>2.38299345970154</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H29" t="n">
         <v>796842</v>
@@ -1239,7 +1239,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>2.39560222625732</v>
+        <v>2.39560198783875</v>
       </c>
       <c r="H30" t="n">
         <v>934202</v>
@@ -1268,7 +1268,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G31" t="n">
-        <v>2.38299345970154</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H31" t="n">
         <v>738518</v>
@@ -1297,7 +1297,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G32" t="n">
-        <v>2.35903763771057</v>
+        <v>2.35903739929199</v>
       </c>
       <c r="H32" t="n">
         <v>1087468</v>
@@ -1326,7 +1326,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32877707481384</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H33" t="n">
         <v>635450</v>
@@ -1384,7 +1384,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G35" t="n">
-        <v>2.23799681663513</v>
+        <v>2.23799657821655</v>
       </c>
       <c r="H35" t="n">
         <v>2200031</v>
@@ -1413,7 +1413,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25060534477234</v>
+        <v>2.25060510635376</v>
       </c>
       <c r="H36" t="n">
         <v>2171688</v>
@@ -1442,7 +1442,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21782326698303</v>
+        <v>2.21782350540161</v>
       </c>
       <c r="H37" t="n">
         <v>2049268</v>
@@ -1471,7 +1471,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.23799681663513</v>
+        <v>2.23799657821655</v>
       </c>
       <c r="H38" t="n">
         <v>508600</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.20647549629211</v>
+        <v>2.20647573471069</v>
       </c>
       <c r="H40" t="n">
         <v>582571</v>
@@ -1587,7 +1587,7 @@
         <v>3.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.20647549629211</v>
+        <v>2.20647573471069</v>
       </c>
       <c r="H42" t="n">
         <v>671983</v>
@@ -1645,7 +1645,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G44" t="n">
-        <v>2.19638872146606</v>
+        <v>2.19638895988464</v>
       </c>
       <c r="H44" t="n">
         <v>845586</v>
@@ -1674,7 +1674,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G45" t="n">
-        <v>2.22034478187561</v>
+        <v>2.22034525871277</v>
       </c>
       <c r="H45" t="n">
         <v>679381</v>
@@ -1732,7 +1732,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22538876533508</v>
+        <v>2.2253885269165</v>
       </c>
       <c r="H47" t="n">
         <v>657985</v>
@@ -1761,7 +1761,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G48" t="n">
-        <v>2.2392578125</v>
+        <v>2.23925757408142</v>
       </c>
       <c r="H48" t="n">
         <v>716322</v>
@@ -1790,7 +1790,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G49" t="n">
-        <v>2.30608224868774</v>
+        <v>2.30608201026917</v>
       </c>
       <c r="H49" t="n">
         <v>1124621</v>
@@ -1819,7 +1819,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.26951766014099</v>
+        <v>2.26951789855957</v>
       </c>
       <c r="H50" t="n">
         <v>664973</v>
@@ -1877,7 +1877,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.23169207572937</v>
+        <v>2.23169255256653</v>
       </c>
       <c r="H52" t="n">
         <v>743120</v>
@@ -1906,7 +1906,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.21782326698303</v>
+        <v>2.21782350540161</v>
       </c>
       <c r="H53" t="n">
         <v>1181993</v>
@@ -1935,7 +1935,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G54" t="n">
-        <v>2.18378067016602</v>
+        <v>2.18378043174744</v>
       </c>
       <c r="H54" t="n">
         <v>792898</v>
@@ -1993,7 +1993,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G56" t="n">
-        <v>2.21151924133301</v>
+        <v>2.21151900291443</v>
       </c>
       <c r="H56" t="n">
         <v>170592</v>
@@ -2051,7 +2051,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G58" t="n">
-        <v>2.16108512878418</v>
+        <v>2.16108536720276</v>
       </c>
       <c r="H58" t="n">
         <v>856086</v>
@@ -2080,7 +2080,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.20773649215698</v>
+        <v>2.20773673057556</v>
       </c>
       <c r="H59" t="n">
         <v>787033</v>
@@ -2109,7 +2109,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G60" t="n">
-        <v>2.18251943588257</v>
+        <v>2.18251991271973</v>
       </c>
       <c r="H60" t="n">
         <v>567481</v>
@@ -2167,7 +2167,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G62" t="n">
-        <v>2.17873692512512</v>
+        <v>2.1787371635437</v>
       </c>
       <c r="H62" t="n">
         <v>1348975</v>
@@ -2196,7 +2196,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G63" t="n">
-        <v>2.17873692512512</v>
+        <v>2.1787371635437</v>
       </c>
       <c r="H63" t="n">
         <v>323909</v>
@@ -2254,7 +2254,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G65" t="n">
-        <v>2.1472156047821</v>
+        <v>2.14721584320068</v>
       </c>
       <c r="H65" t="n">
         <v>1473153</v>
@@ -2283,7 +2283,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>2.16865038871765</v>
+        <v>2.16865015029907</v>
       </c>
       <c r="H66" t="n">
         <v>1102800</v>
@@ -2457,7 +2457,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>2.12325978279114</v>
+        <v>2.1232602596283</v>
       </c>
       <c r="H72" t="n">
         <v>1045976</v>
@@ -2544,7 +2544,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G75" t="n">
-        <v>2.12830352783203</v>
+        <v>2.12830328941345</v>
       </c>
       <c r="H75" t="n">
         <v>439704</v>
@@ -2602,7 +2602,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G77" t="n">
-        <v>2.06778311729431</v>
+        <v>2.06778287887573</v>
       </c>
       <c r="H77" t="n">
         <v>1178471</v>
@@ -2631,7 +2631,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.9946540594101</v>
+        <v>1.99465370178223</v>
       </c>
       <c r="H78" t="n">
         <v>2768628</v>
@@ -2660,7 +2660,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195887565613</v>
+        <v>1.97195863723755</v>
       </c>
       <c r="H79" t="n">
         <v>3135081</v>
@@ -2747,7 +2747,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>1.92909026145935</v>
+        <v>1.92909002304077</v>
       </c>
       <c r="H82" t="n">
         <v>1535844</v>
@@ -2776,7 +2776,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>1.92278587818146</v>
+        <v>1.92278563976288</v>
       </c>
       <c r="H83" t="n">
         <v>1876379</v>
@@ -2805,7 +2805,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G84" t="n">
-        <v>1.94800305366516</v>
+        <v>1.94800281524658</v>
       </c>
       <c r="H84" t="n">
         <v>3748342</v>
@@ -2921,7 +2921,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G88" t="n">
-        <v>1.97574126720428</v>
+        <v>1.97574150562286</v>
       </c>
       <c r="H88" t="n">
         <v>1064202</v>
@@ -2950,7 +2950,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G89" t="n">
-        <v>1.97321975231171</v>
+        <v>1.97321963310242</v>
       </c>
       <c r="H89" t="n">
         <v>736410</v>
@@ -2979,7 +2979,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G90" t="n">
-        <v>1.99339294433594</v>
+        <v>1.99339318275452</v>
       </c>
       <c r="H90" t="n">
         <v>1831237</v>
@@ -3037,7 +3037,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G92" t="n">
-        <v>2.01104497909546</v>
+        <v>2.01104521751404</v>
       </c>
       <c r="H92" t="n">
         <v>6813289</v>
@@ -3095,7 +3095,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G94" t="n">
-        <v>1.97448074817657</v>
+        <v>1.974480509758</v>
       </c>
       <c r="H94" t="n">
         <v>1497058</v>
@@ -3182,7 +3182,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>1.97321975231171</v>
+        <v>1.97321963310242</v>
       </c>
       <c r="H97" t="n">
         <v>1754313</v>
@@ -3211,7 +3211,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G98" t="n">
-        <v>1.91017735004425</v>
+        <v>1.91017758846283</v>
       </c>
       <c r="H98" t="n">
         <v>1613932</v>
@@ -3240,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89126479625702</v>
+        <v>1.89126467704773</v>
       </c>
       <c r="H99" t="n">
         <v>3568973</v>
@@ -3269,7 +3269,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G100" t="n">
-        <v>1.89504742622375</v>
+        <v>1.89504766464233</v>
       </c>
       <c r="H100" t="n">
         <v>1788951</v>
@@ -3385,7 +3385,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G104" t="n">
-        <v>2.0892174243927</v>
+        <v>2.08921718597412</v>
       </c>
       <c r="H104" t="n">
         <v>8365602</v>
@@ -3443,7 +3443,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147885322571</v>
       </c>
       <c r="H106" t="n">
         <v>1234594</v>
@@ -3472,7 +3472,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G107" t="n">
-        <v>2.07030487060547</v>
+        <v>2.07030463218689</v>
       </c>
       <c r="H107" t="n">
         <v>701279</v>
@@ -3501,7 +3501,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>2.08669567108154</v>
+        <v>2.08669543266296</v>
       </c>
       <c r="H108" t="n">
         <v>1496422</v>
@@ -3530,7 +3530,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147885322571</v>
       </c>
       <c r="H109" t="n">
         <v>908570</v>
@@ -3559,7 +3559,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G110" t="n">
-        <v>2.06778311729431</v>
+        <v>2.06778287887573</v>
       </c>
       <c r="H110" t="n">
         <v>677592</v>
@@ -3588,7 +3588,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147885322571</v>
       </c>
       <c r="H111" t="n">
         <v>436432</v>
@@ -3617,7 +3617,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G112" t="n">
-        <v>2.07913088798523</v>
+        <v>2.07913041114807</v>
       </c>
       <c r="H112" t="n">
         <v>627812</v>
@@ -3646,7 +3646,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G113" t="n">
-        <v>2.07030487060547</v>
+        <v>2.07030463218689</v>
       </c>
       <c r="H113" t="n">
         <v>483565</v>
@@ -3675,7 +3675,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G114" t="n">
-        <v>2.08417391777039</v>
+        <v>2.08417367935181</v>
       </c>
       <c r="H114" t="n">
         <v>255877</v>
@@ -3704,7 +3704,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G115" t="n">
-        <v>2.11569476127625</v>
+        <v>2.11569499969482</v>
       </c>
       <c r="H115" t="n">
         <v>1496867</v>
@@ -3762,7 +3762,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G117" t="n">
-        <v>2.14469432830811</v>
+        <v>2.14469456672668</v>
       </c>
       <c r="H117" t="n">
         <v>680193</v>
@@ -3791,7 +3791,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G118" t="n">
-        <v>2.14091181755066</v>
+        <v>2.14091157913208</v>
       </c>
       <c r="H118" t="n">
         <v>272440</v>
@@ -3907,7 +3907,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.15604186058044</v>
+        <v>2.15604209899902</v>
       </c>
       <c r="H122" t="n">
         <v>505790</v>
@@ -3936,7 +3936,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>2.19008469581604</v>
+        <v>2.19008445739746</v>
       </c>
       <c r="H123" t="n">
         <v>976460</v>
@@ -3965,7 +3965,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G124" t="n">
-        <v>2.16738963127136</v>
+        <v>2.16738939285278</v>
       </c>
       <c r="H124" t="n">
         <v>711853</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.15604186058044</v>
+        <v>2.15604209899902</v>
       </c>
       <c r="H127" t="n">
         <v>556151</v>
@@ -4168,7 +4168,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G131" t="n">
-        <v>2.11191248893738</v>
+        <v>2.11191201210022</v>
       </c>
       <c r="H131" t="n">
         <v>982502</v>
@@ -4197,7 +4197,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>2.11191248893738</v>
+        <v>2.11191201210022</v>
       </c>
       <c r="H132" t="n">
         <v>983090</v>
@@ -4255,7 +4255,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G134" t="n">
-        <v>2.04256582260132</v>
+        <v>2.04256629943848</v>
       </c>
       <c r="H134" t="n">
         <v>446178</v>
@@ -4284,7 +4284,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G135" t="n">
-        <v>2.04256582260132</v>
+        <v>2.04256629943848</v>
       </c>
       <c r="H135" t="n">
         <v>1021203</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.04256582260132</v>
+        <v>2.04256629943848</v>
       </c>
       <c r="H138" t="n">
         <v>873840</v>
@@ -4429,7 +4429,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G140" t="n">
-        <v>1.97069811820984</v>
+        <v>1.97069787979126</v>
       </c>
       <c r="H140" t="n">
         <v>655592</v>
@@ -4458,7 +4458,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.02365350723267</v>
+        <v>2.02365326881409</v>
       </c>
       <c r="H141" t="n">
         <v>1907530</v>
@@ -4487,7 +4487,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>2.01734924316406</v>
+        <v>2.01734948158264</v>
       </c>
       <c r="H142" t="n">
         <v>1211840</v>
@@ -4545,7 +4545,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G144" t="n">
-        <v>2.07282638549805</v>
+        <v>2.07282614707947</v>
       </c>
       <c r="H144" t="n">
         <v>820333</v>
@@ -4574,7 +4574,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G145" t="n">
-        <v>2.06400012969971</v>
+        <v>2.06400036811829</v>
       </c>
       <c r="H145" t="n">
         <v>430023</v>
@@ -4603,7 +4603,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11191248893738</v>
+        <v>2.11191201210022</v>
       </c>
       <c r="H146" t="n">
         <v>1000881</v>
@@ -4632,7 +4632,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.13712906837463</v>
+        <v>2.13712930679321</v>
       </c>
       <c r="H147" t="n">
         <v>886586</v>
@@ -4690,7 +4690,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>2.15225958824158</v>
+        <v>2.15225911140442</v>
       </c>
       <c r="H149" t="n">
         <v>659705</v>
@@ -4777,7 +4777,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G152" t="n">
-        <v>2.12199902534485</v>
+        <v>2.12199926376343</v>
       </c>
       <c r="H152" t="n">
         <v>878730</v>
@@ -4806,7 +4806,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G153" t="n">
-        <v>2.09552121162415</v>
+        <v>2.09552145004272</v>
       </c>
       <c r="H153" t="n">
         <v>692808</v>
@@ -4835,7 +4835,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>2.08669567108154</v>
+        <v>2.08669543266296</v>
       </c>
       <c r="H154" t="n">
         <v>352953</v>
@@ -4864,7 +4864,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.12325978279114</v>
+        <v>2.1232602596283</v>
       </c>
       <c r="H155" t="n">
         <v>607297</v>
@@ -4893,7 +4893,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G156" t="n">
-        <v>2.13712906837463</v>
+        <v>2.13712930679321</v>
       </c>
       <c r="H156" t="n">
         <v>566431</v>
@@ -5009,7 +5009,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G160" t="n">
-        <v>2.12704253196716</v>
+        <v>2.12704277038574</v>
       </c>
       <c r="H160" t="n">
         <v>735413</v>
@@ -5038,7 +5038,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G161" t="n">
-        <v>2.14469432830811</v>
+        <v>2.14469456672668</v>
       </c>
       <c r="H161" t="n">
         <v>513353</v>
@@ -5067,7 +5067,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G162" t="n">
-        <v>2.16234612464905</v>
+        <v>2.16234636306763</v>
       </c>
       <c r="H162" t="n">
         <v>835730</v>
@@ -5096,7 +5096,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G163" t="n">
-        <v>2.16108512878418</v>
+        <v>2.16108536720276</v>
       </c>
       <c r="H163" t="n">
         <v>472501</v>
@@ -5125,7 +5125,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G164" t="n">
-        <v>2.14595508575439</v>
+        <v>2.14595484733582</v>
       </c>
       <c r="H164" t="n">
         <v>656848</v>
@@ -5154,7 +5154,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G165" t="n">
-        <v>2.17621564865112</v>
+        <v>2.17621517181396</v>
       </c>
       <c r="H165" t="n">
         <v>699653</v>
@@ -5183,7 +5183,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G166" t="n">
-        <v>2.17243266105652</v>
+        <v>2.17243313789368</v>
       </c>
       <c r="H166" t="n">
         <v>716925</v>
@@ -5241,7 +5241,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G168" t="n">
-        <v>2.33129930496216</v>
+        <v>2.33129906654358</v>
       </c>
       <c r="H168" t="n">
         <v>1990731</v>
@@ -5299,7 +5299,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>2.27582168579102</v>
+        <v>2.27582192420959</v>
       </c>
       <c r="H170" t="n">
         <v>1446573</v>
@@ -5357,7 +5357,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35147285461426</v>
+        <v>2.3514723777771</v>
       </c>
       <c r="H172" t="n">
         <v>1771997</v>
@@ -5386,7 +5386,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G173" t="n">
-        <v>2.37290668487549</v>
+        <v>2.37290692329407</v>
       </c>
       <c r="H173" t="n">
         <v>970626</v>
@@ -5415,7 +5415,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40190601348877</v>
+        <v>2.40190649032593</v>
       </c>
       <c r="H174" t="n">
         <v>1365898</v>
@@ -5444,7 +5444,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G175" t="n">
-        <v>2.35399436950684</v>
+        <v>2.35399413108826</v>
       </c>
       <c r="H175" t="n">
         <v>1120304</v>
@@ -5473,7 +5473,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.32877707481384</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H176" t="n">
         <v>959599</v>
@@ -5531,7 +5531,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G178" t="n">
-        <v>2.4031674861908</v>
+        <v>2.40316700935364</v>
       </c>
       <c r="H178" t="n">
         <v>2956792</v>
@@ -5560,7 +5560,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G179" t="n">
-        <v>2.38299345970154</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H179" t="n">
         <v>1073722</v>
@@ -5618,7 +5618,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G181" t="n">
-        <v>2.3918194770813</v>
+        <v>2.39181971549988</v>
       </c>
       <c r="H181" t="n">
         <v>1136549</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>2.39560222625732</v>
+        <v>2.39560198783875</v>
       </c>
       <c r="H183" t="n">
         <v>1547599</v>
@@ -5705,7 +5705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>2.39560222625732</v>
+        <v>2.39560198783875</v>
       </c>
       <c r="H184" t="n">
         <v>1699128</v>
@@ -5734,7 +5734,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G185" t="n">
-        <v>2.37164640426636</v>
+        <v>2.37164616584778</v>
       </c>
       <c r="H185" t="n">
         <v>808007</v>
@@ -5792,7 +5792,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38299345970154</v>
+        <v>2.38299369812012</v>
       </c>
       <c r="H187" t="n">
         <v>1275111</v>
@@ -5966,7 +5966,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G193" t="n">
-        <v>2.35525560379028</v>
+        <v>2.35525512695312</v>
       </c>
       <c r="H193" t="n">
         <v>554537</v>
@@ -5995,7 +5995,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G194" t="n">
-        <v>2.38047218322754</v>
+        <v>2.38047194480896</v>
       </c>
       <c r="H194" t="n">
         <v>1119199</v>
@@ -6140,7 +6140,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39560222625732</v>
+        <v>2.39560198783875</v>
       </c>
       <c r="H199" t="n">
         <v>1166747</v>
@@ -6227,7 +6227,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.45234036445618</v>
+        <v>2.4523401260376</v>
       </c>
       <c r="H202" t="n">
         <v>1065606</v>
@@ -6256,7 +6256,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G203" t="n">
-        <v>2.43847107887268</v>
+        <v>2.4384708404541</v>
       </c>
       <c r="H203" t="n">
         <v>749019</v>
@@ -6343,7 +6343,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.45864415168762</v>
+        <v>2.45864462852478</v>
       </c>
       <c r="H206" t="n">
         <v>901759</v>
@@ -6401,7 +6401,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>2.38677620887756</v>
+        <v>2.38677644729614</v>
       </c>
       <c r="H208" t="n">
         <v>998514</v>
@@ -6604,7 +6604,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G215" t="n">
-        <v>2.51721167564392</v>
+        <v>2.51721143722534</v>
       </c>
       <c r="H215" t="n">
         <v>1570341</v>
@@ -6633,7 +6633,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>2.50001549720764</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H216" t="n">
         <v>1454747</v>
@@ -6662,7 +6662,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694612503052</v>
       </c>
       <c r="H217" t="n">
         <v>1320391</v>
@@ -6749,7 +6749,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.50001549720764</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H220" t="n">
         <v>1072019</v>
@@ -6836,7 +6836,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G223" t="n">
-        <v>2.4656240940094</v>
+        <v>2.46562385559082</v>
       </c>
       <c r="H223" t="n">
         <v>1097041</v>
@@ -6865,7 +6865,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G224" t="n">
-        <v>2.49737024307251</v>
+        <v>2.49737000465393</v>
       </c>
       <c r="H224" t="n">
         <v>1878448</v>
@@ -6894,7 +6894,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G225" t="n">
-        <v>2.52250266075134</v>
+        <v>2.52250242233276</v>
       </c>
       <c r="H225" t="n">
         <v>1838179</v>
@@ -6923,7 +6923,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G226" t="n">
-        <v>2.48546504974365</v>
+        <v>2.48546552658081</v>
       </c>
       <c r="H226" t="n">
         <v>1137067</v>
@@ -6981,7 +6981,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G228" t="n">
-        <v>2.51324319839478</v>
+        <v>2.51324343681335</v>
       </c>
       <c r="H228" t="n">
         <v>2456099</v>
@@ -7039,7 +7039,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694612503052</v>
       </c>
       <c r="H230" t="n">
         <v>3703950</v>
@@ -7155,7 +7155,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>2.47356009483337</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H234" t="n">
         <v>365542</v>
@@ -7329,7 +7329,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G240" t="n">
-        <v>2.49207901954651</v>
+        <v>2.49207925796509</v>
       </c>
       <c r="H240" t="n">
         <v>778808</v>
@@ -7416,7 +7416,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694612503052</v>
       </c>
       <c r="H243" t="n">
         <v>279712</v>
@@ -7503,7 +7503,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>2.46694660186768</v>
+        <v>2.46694612503052</v>
       </c>
       <c r="H246" t="n">
         <v>235874</v>
@@ -7561,7 +7561,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.4656240940094</v>
+        <v>2.46562385559082</v>
       </c>
       <c r="H248" t="n">
         <v>879735</v>
@@ -7619,7 +7619,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>2.44578242301941</v>
+        <v>2.44578266143799</v>
       </c>
       <c r="H250" t="n">
         <v>1123635</v>
@@ -7706,7 +7706,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>2.44975113868713</v>
+        <v>2.44975066184998</v>
       </c>
       <c r="H253" t="n">
         <v>622270</v>
@@ -7735,7 +7735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>2.45371866226196</v>
+        <v>2.45371913909912</v>
       </c>
       <c r="H254" t="n">
         <v>628873</v>
@@ -7764,7 +7764,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H255" t="n">
         <v>460966</v>
@@ -7793,7 +7793,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G256" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H256" t="n">
         <v>262852</v>
@@ -7851,7 +7851,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.47356009483337</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H258" t="n">
         <v>335894</v>
@@ -7938,7 +7938,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G261" t="n">
-        <v>2.56483101844788</v>
+        <v>2.5648307800293</v>
       </c>
       <c r="H261" t="n">
         <v>524937</v>
@@ -7967,7 +7967,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55689406394958</v>
+        <v>2.55689454078674</v>
       </c>
       <c r="H262" t="n">
         <v>748895</v>
@@ -8054,7 +8054,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G265" t="n">
-        <v>2.56483101844788</v>
+        <v>2.5648307800293</v>
       </c>
       <c r="H265" t="n">
         <v>514836</v>
@@ -8083,7 +8083,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G266" t="n">
-        <v>2.56615376472473</v>
+        <v>2.56615352630615</v>
       </c>
       <c r="H266" t="n">
         <v>481921</v>
@@ -8112,7 +8112,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G267" t="n">
-        <v>2.55424904823303</v>
+        <v>2.55424880981445</v>
       </c>
       <c r="H267" t="n">
         <v>614773</v>
@@ -8199,7 +8199,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G270" t="n">
-        <v>2.5238254070282</v>
+        <v>2.52382516860962</v>
       </c>
       <c r="H270" t="n">
         <v>321976</v>
@@ -8228,7 +8228,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>2.53308463096619</v>
+        <v>2.53308439254761</v>
       </c>
       <c r="H271" t="n">
         <v>286015</v>
@@ -8257,7 +8257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G272" t="n">
-        <v>2.51324319839478</v>
+        <v>2.51324343681335</v>
       </c>
       <c r="H272" t="n">
         <v>536735</v>
@@ -8286,7 +8286,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G273" t="n">
-        <v>2.50001549720764</v>
+        <v>2.50001573562622</v>
       </c>
       <c r="H273" t="n">
         <v>491516</v>
@@ -8344,7 +8344,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.47356009483337</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H275" t="n">
         <v>409245</v>
@@ -8402,7 +8402,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>2.47356009483337</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H277" t="n">
         <v>374003</v>
@@ -8460,7 +8460,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G279" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H279" t="n">
         <v>167600</v>
@@ -8489,7 +8489,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G280" t="n">
-        <v>2.44842791557312</v>
+        <v>2.4484281539917</v>
       </c>
       <c r="H280" t="n">
         <v>191020</v>
@@ -8547,7 +8547,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G282" t="n">
-        <v>2.43784594535828</v>
+        <v>2.43784618377686</v>
       </c>
       <c r="H282" t="n">
         <v>466984</v>
@@ -8692,7 +8692,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>2.43652296066284</v>
+        <v>2.43652319908142</v>
       </c>
       <c r="H287" t="n">
         <v>539242</v>
@@ -8721,7 +8721,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G288" t="n">
-        <v>2.49869298934937</v>
+        <v>2.49869275093079</v>
       </c>
       <c r="H288" t="n">
         <v>633611</v>
@@ -8808,7 +8808,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G291" t="n">
-        <v>2.53837585449219</v>
+        <v>2.53837561607361</v>
       </c>
       <c r="H291" t="n">
         <v>385349</v>
@@ -8837,7 +8837,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G292" t="n">
-        <v>2.5357301235199</v>
+        <v>2.53572988510132</v>
       </c>
       <c r="H292" t="n">
         <v>257047</v>
@@ -8895,7 +8895,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G294" t="n">
-        <v>2.53043913841248</v>
+        <v>2.5304388999939</v>
       </c>
       <c r="H294" t="n">
         <v>973552</v>
@@ -9040,7 +9040,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G299" t="n">
-        <v>2.51721167564392</v>
+        <v>2.51721143722534</v>
       </c>
       <c r="H299" t="n">
         <v>254927</v>
@@ -9069,7 +9069,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53308463096619</v>
+        <v>2.53308439254761</v>
       </c>
       <c r="H300" t="n">
         <v>622766</v>
@@ -9098,7 +9098,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G301" t="n">
-        <v>2.5357301235199</v>
+        <v>2.53572988510132</v>
       </c>
       <c r="H301" t="n">
         <v>356050</v>
@@ -9127,7 +9127,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53969860076904</v>
+        <v>2.53969812393188</v>
       </c>
       <c r="H302" t="n">
         <v>350932</v>
@@ -9156,7 +9156,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.53969860076904</v>
+        <v>2.53969812393188</v>
       </c>
       <c r="H303" t="n">
         <v>764260</v>
@@ -9185,7 +9185,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G304" t="n">
-        <v>2.56350803375244</v>
+        <v>2.56350779533386</v>
       </c>
       <c r="H304" t="n">
         <v>439623</v>
@@ -9214,7 +9214,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G305" t="n">
-        <v>2.61377310752869</v>
+        <v>2.61377286911011</v>
       </c>
       <c r="H305" t="n">
         <v>844898</v>
@@ -9243,7 +9243,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G306" t="n">
-        <v>2.59922242164612</v>
+        <v>2.59922289848328</v>
       </c>
       <c r="H306" t="n">
         <v>581605</v>
@@ -9272,7 +9272,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G307" t="n">
-        <v>2.60583639144897</v>
+        <v>2.60583662986755</v>
       </c>
       <c r="H307" t="n">
         <v>525000</v>
@@ -9301,7 +9301,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60583639144897</v>
+        <v>2.60583662986755</v>
       </c>
       <c r="H308" t="n">
         <v>474886</v>
@@ -9388,7 +9388,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G311" t="n">
-        <v>2.59128618240356</v>
+        <v>2.59128594398499</v>
       </c>
       <c r="H311" t="n">
         <v>463030</v>
@@ -9417,7 +9417,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G312" t="n">
-        <v>2.58864068984985</v>
+        <v>2.58864045143127</v>
       </c>
       <c r="H312" t="n">
         <v>672881</v>
@@ -9533,7 +9533,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G316" t="n">
-        <v>2.60319089889526</v>
+        <v>2.60319113731384</v>
       </c>
       <c r="H316" t="n">
         <v>439492</v>
@@ -9562,7 +9562,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G317" t="n">
-        <v>2.67329668998718</v>
+        <v>2.67329716682434</v>
       </c>
       <c r="H317" t="n">
         <v>1408139</v>
@@ -9591,7 +9591,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G318" t="n">
-        <v>2.68917012214661</v>
+        <v>2.68917036056519</v>
       </c>
       <c r="H318" t="n">
         <v>660904</v>
@@ -9707,7 +9707,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G322" t="n">
-        <v>2.64816498756409</v>
+        <v>2.64816474914551</v>
       </c>
       <c r="H322" t="n">
         <v>362068</v>
@@ -9736,7 +9736,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>2.69842934608459</v>
+        <v>2.69842982292175</v>
       </c>
       <c r="H323" t="n">
         <v>561708</v>
@@ -9765,7 +9765,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G324" t="n">
-        <v>2.6693286895752</v>
+        <v>2.66932845115662</v>
       </c>
       <c r="H324" t="n">
         <v>337409</v>
@@ -9852,7 +9852,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G327" t="n">
-        <v>2.68784785270691</v>
+        <v>2.68784737586975</v>
       </c>
       <c r="H327" t="n">
         <v>473695</v>
@@ -9881,7 +9881,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G328" t="n">
-        <v>2.68784785270691</v>
+        <v>2.68784737586975</v>
       </c>
       <c r="H328" t="n">
         <v>332487</v>
@@ -9910,7 +9910,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G329" t="n">
-        <v>2.70239806175232</v>
+        <v>2.70239782333374</v>
       </c>
       <c r="H329" t="n">
         <v>459573</v>
@@ -9968,7 +9968,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>2.68520212173462</v>
+        <v>2.68520188331604</v>
       </c>
       <c r="H331" t="n">
         <v>771787</v>
@@ -9997,7 +9997,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G332" t="n">
-        <v>2.70107483863831</v>
+        <v>2.70107531547546</v>
       </c>
       <c r="H332" t="n">
         <v>431759</v>
@@ -10026,7 +10026,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G333" t="n">
-        <v>2.70107483863831</v>
+        <v>2.70107531547546</v>
       </c>
       <c r="H333" t="n">
         <v>1317493</v>
@@ -10055,7 +10055,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>2.65874648094177</v>
+        <v>2.65874671936035</v>
       </c>
       <c r="H334" t="n">
         <v>564957</v>
@@ -10084,7 +10084,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>2.67197442054749</v>
+        <v>2.67197418212891</v>
       </c>
       <c r="H335" t="n">
         <v>708093</v>
@@ -10171,7 +10171,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054707527161</v>
       </c>
       <c r="H338" t="n">
         <v>1428133</v>
@@ -10229,7 +10229,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G340" t="n">
-        <v>2.88758420944214</v>
+        <v>2.88758444786072</v>
       </c>
       <c r="H340" t="n">
         <v>1378600</v>
@@ -10287,7 +10287,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G342" t="n">
-        <v>2.90742540359497</v>
+        <v>2.90742564201355</v>
       </c>
       <c r="H342" t="n">
         <v>1794819</v>
@@ -10316,7 +10316,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>2.94578528404236</v>
+        <v>2.94578576087952</v>
       </c>
       <c r="H343" t="n">
         <v>1446520</v>
@@ -10403,7 +10403,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G346" t="n">
-        <v>2.9735631942749</v>
+        <v>2.97356343269348</v>
       </c>
       <c r="H346" t="n">
         <v>613331</v>
@@ -10432,7 +10432,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G347" t="n">
-        <v>2.96430420875549</v>
+        <v>2.96430444717407</v>
       </c>
       <c r="H347" t="n">
         <v>1313359</v>
@@ -10461,7 +10461,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G348" t="n">
-        <v>2.96827220916748</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H348" t="n">
         <v>1065152</v>
@@ -10519,7 +10519,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>2.99340534210205</v>
+        <v>2.99340486526489</v>
       </c>
       <c r="H350" t="n">
         <v>996164</v>
@@ -10577,7 +10577,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03837847709656</v>
+        <v>3.03837871551514</v>
       </c>
       <c r="H352" t="n">
         <v>949730</v>
@@ -10606,7 +10606,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G353" t="n">
-        <v>3.03176474571228</v>
+        <v>3.03176498413086</v>
       </c>
       <c r="H353" t="n">
         <v>617623</v>
@@ -10635,7 +10635,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G354" t="n">
-        <v>3.1058394908905</v>
+        <v>3.10583996772766</v>
       </c>
       <c r="H354" t="n">
         <v>888394</v>
@@ -10664,7 +10664,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G355" t="n">
-        <v>3.03441071510315</v>
+        <v>3.03441023826599</v>
       </c>
       <c r="H355" t="n">
         <v>1590596</v>
@@ -10722,7 +10722,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G357" t="n">
-        <v>2.99605083465576</v>
+        <v>2.99605059623718</v>
       </c>
       <c r="H357" t="n">
         <v>1097676</v>
@@ -10780,7 +10780,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>3.0423469543457</v>
+        <v>3.04234647750854</v>
       </c>
       <c r="H359" t="n">
         <v>1263796</v>
@@ -10809,7 +10809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G360" t="n">
-        <v>3.04631519317627</v>
+        <v>3.04631543159485</v>
       </c>
       <c r="H360" t="n">
         <v>1279493</v>
@@ -10838,7 +10838,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>3.00266408920288</v>
+        <v>3.0026638507843</v>
       </c>
       <c r="H361" t="n">
         <v>1226436</v>
@@ -10867,7 +10867,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>3.02911901473999</v>
+        <v>3.02911949157715</v>
       </c>
       <c r="H362" t="n">
         <v>894876</v>
@@ -10896,7 +10896,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05557441711426</v>
+        <v>3.05557489395142</v>
       </c>
       <c r="H363" t="n">
         <v>841909</v>
@@ -10954,7 +10954,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>2.98943638801575</v>
+        <v>2.98943662643433</v>
       </c>
       <c r="H365" t="n">
         <v>511496</v>
@@ -10983,7 +10983,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>3.00266408920288</v>
+        <v>3.0026638507843</v>
       </c>
       <c r="H366" t="n">
         <v>585559</v>
@@ -11012,7 +11012,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G367" t="n">
-        <v>2.98282241821289</v>
+        <v>2.98282313346863</v>
       </c>
       <c r="H367" t="n">
         <v>331590</v>
@@ -11041,7 +11041,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G368" t="n">
-        <v>2.97091794013977</v>
+        <v>2.97091817855835</v>
       </c>
       <c r="H368" t="n">
         <v>274659</v>
@@ -11099,7 +11099,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G370" t="n">
-        <v>2.9735631942749</v>
+        <v>2.97356343269348</v>
       </c>
       <c r="H370" t="n">
         <v>934664</v>
@@ -11128,7 +11128,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G371" t="n">
-        <v>2.96827220916748</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H371" t="n">
         <v>609342</v>
@@ -11157,7 +11157,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G372" t="n">
-        <v>3.04896092414856</v>
+        <v>3.04896116256714</v>
       </c>
       <c r="H372" t="n">
         <v>836680</v>
@@ -11186,7 +11186,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G373" t="n">
-        <v>3.02250576019287</v>
+        <v>3.02250552177429</v>
       </c>
       <c r="H373" t="n">
         <v>820789</v>
@@ -11215,7 +11215,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>2.94313979148865</v>
+        <v>2.94313955307007</v>
       </c>
       <c r="H374" t="n">
         <v>861518</v>
@@ -11244,7 +11244,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G375" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054707527161</v>
       </c>
       <c r="H375" t="n">
         <v>2514673</v>
@@ -11273,7 +11273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.87700223922729</v>
+        <v>2.87700200080872</v>
       </c>
       <c r="H376" t="n">
         <v>558785</v>
@@ -11331,7 +11331,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G378" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H378" t="n">
         <v>654476</v>
@@ -11360,7 +11360,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G379" t="n">
-        <v>2.86509680747986</v>
+        <v>2.86509728431702</v>
       </c>
       <c r="H379" t="n">
         <v>765727</v>
@@ -11389,7 +11389,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>2.84393310546875</v>
+        <v>2.84393286705017</v>
       </c>
       <c r="H380" t="n">
         <v>657743</v>
@@ -11418,7 +11418,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85980629920959</v>
+        <v>2.85980606079102</v>
       </c>
       <c r="H381" t="n">
         <v>559669</v>
@@ -11447,7 +11447,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G382" t="n">
-        <v>2.85451531410217</v>
+        <v>2.85451483726501</v>
       </c>
       <c r="H382" t="n">
         <v>516590</v>
@@ -11476,7 +11476,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G383" t="n">
-        <v>2.8307056427002</v>
+        <v>2.83070588111877</v>
       </c>
       <c r="H383" t="n">
         <v>646536</v>
@@ -11505,7 +11505,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H384" t="n">
         <v>424777</v>
@@ -11563,7 +11563,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.87700223922729</v>
+        <v>2.87700200080872</v>
       </c>
       <c r="H386" t="n">
         <v>431245</v>
@@ -11650,7 +11650,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705477714539</v>
+        <v>2.78705453872681</v>
       </c>
       <c r="H389" t="n">
         <v>1087808</v>
@@ -11679,7 +11679,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80689597129822</v>
+        <v>2.80689549446106</v>
       </c>
       <c r="H390" t="n">
         <v>516731</v>
@@ -11737,7 +11737,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>2.80689597129822</v>
+        <v>2.80689549446106</v>
       </c>
       <c r="H392" t="n">
         <v>1039683</v>
@@ -11824,7 +11824,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G395" t="n">
-        <v>2.66800594329834</v>
+        <v>2.66800618171692</v>
       </c>
       <c r="H395" t="n">
         <v>1156626</v>
@@ -11853,7 +11853,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G396" t="n">
-        <v>2.67329668998718</v>
+        <v>2.67329716682434</v>
       </c>
       <c r="H396" t="n">
         <v>563261</v>
@@ -11882,7 +11882,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69446110725403</v>
+        <v>2.69446134567261</v>
       </c>
       <c r="H397" t="n">
         <v>848281</v>
@@ -11911,7 +11911,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G398" t="n">
-        <v>2.6865246295929</v>
+        <v>2.68652439117432</v>
       </c>
       <c r="H398" t="n">
         <v>458902</v>
@@ -11940,7 +11940,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G399" t="n">
-        <v>2.75266289710999</v>
+        <v>2.75266265869141</v>
       </c>
       <c r="H399" t="n">
         <v>1135051</v>
@@ -11998,7 +11998,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.75927662849426</v>
+        <v>2.75927639007568</v>
       </c>
       <c r="H401" t="n">
         <v>543737</v>
@@ -12027,7 +12027,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G402" t="n">
-        <v>2.75663113594055</v>
+        <v>2.75663137435913</v>
       </c>
       <c r="H402" t="n">
         <v>289481</v>
@@ -12085,7 +12085,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G404" t="n">
-        <v>2.72885298728943</v>
+        <v>2.72885322570801</v>
       </c>
       <c r="H404" t="n">
         <v>250945</v>
@@ -12114,7 +12114,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G405" t="n">
-        <v>2.72885298728943</v>
+        <v>2.72885322570801</v>
       </c>
       <c r="H405" t="n">
         <v>549004</v>
@@ -12172,7 +12172,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>2.79102253913879</v>
+        <v>2.79102230072021</v>
       </c>
       <c r="H407" t="n">
         <v>384104</v>
@@ -12259,7 +12259,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G410" t="n">
-        <v>2.72620749473572</v>
+        <v>2.72620797157288</v>
       </c>
       <c r="H410" t="n">
         <v>884762</v>
@@ -12288,7 +12288,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.6693286895752</v>
+        <v>2.66932845115662</v>
       </c>
       <c r="H411" t="n">
         <v>843867</v>
@@ -12317,7 +12317,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>2.67991089820862</v>
+        <v>2.67991065979004</v>
       </c>
       <c r="H412" t="n">
         <v>388086</v>
@@ -12346,7 +12346,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G413" t="n">
-        <v>2.76324462890625</v>
+        <v>2.76324439048767</v>
       </c>
       <c r="H413" t="n">
         <v>701284</v>
@@ -12375,7 +12375,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>2.75927662849426</v>
+        <v>2.75927639007568</v>
       </c>
       <c r="H414" t="n">
         <v>581298</v>
@@ -12433,7 +12433,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G416" t="n">
-        <v>2.79102253913879</v>
+        <v>2.79102230072021</v>
       </c>
       <c r="H416" t="n">
         <v>262750</v>
@@ -12462,7 +12462,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G417" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583782196045</v>
       </c>
       <c r="H417" t="n">
         <v>1518103</v>
@@ -12491,7 +12491,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G418" t="n">
-        <v>2.869065284729</v>
+        <v>2.86906552314758</v>
       </c>
       <c r="H418" t="n">
         <v>2152019</v>
@@ -12578,7 +12578,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G421" t="n">
-        <v>2.88890695571899</v>
+        <v>2.88890719413757</v>
       </c>
       <c r="H421" t="n">
         <v>630370</v>
@@ -12636,7 +12636,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G423" t="n">
-        <v>2.89287495613098</v>
+        <v>2.89287543296814</v>
       </c>
       <c r="H423" t="n">
         <v>451656</v>
@@ -12694,7 +12694,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G425" t="n">
-        <v>2.79631400108337</v>
+        <v>2.79631376266479</v>
       </c>
       <c r="H425" t="n">
         <v>548843</v>
@@ -12723,7 +12723,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G426" t="n">
-        <v>2.81483244895935</v>
+        <v>2.81483221054077</v>
       </c>
       <c r="H426" t="n">
         <v>783217</v>
@@ -12781,7 +12781,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G428" t="n">
-        <v>2.83335113525391</v>
+        <v>2.83335137367249</v>
       </c>
       <c r="H428" t="n">
         <v>634478</v>
@@ -12897,7 +12897,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054707527161</v>
       </c>
       <c r="H432" t="n">
         <v>482261</v>
@@ -12926,7 +12926,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.89022970199585</v>
+        <v>2.89022922515869</v>
       </c>
       <c r="H433" t="n">
         <v>641837</v>
@@ -12955,7 +12955,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G434" t="n">
-        <v>2.89419770240784</v>
+        <v>2.894198179245</v>
       </c>
       <c r="H434" t="n">
         <v>713486</v>
@@ -13013,7 +13013,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G436" t="n">
-        <v>2.93123531341553</v>
+        <v>2.93123507499695</v>
       </c>
       <c r="H436" t="n">
         <v>487422</v>
@@ -13100,7 +13100,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99208211898804</v>
+        <v>2.99208235740662</v>
       </c>
       <c r="H439" t="n">
         <v>796136</v>
@@ -13129,7 +13129,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G440" t="n">
-        <v>3.00795555114746</v>
+        <v>3.00795531272888</v>
       </c>
       <c r="H440" t="n">
         <v>894728</v>
@@ -13158,7 +13158,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G441" t="n">
-        <v>2.98282241821289</v>
+        <v>2.98282313346863</v>
       </c>
       <c r="H441" t="n">
         <v>916165</v>
@@ -13187,7 +13187,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.93652629852295</v>
+        <v>2.93652653694153</v>
       </c>
       <c r="H442" t="n">
         <v>698038</v>
@@ -13216,7 +13216,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520402908325</v>
+        <v>2.93520379066467</v>
       </c>
       <c r="H443" t="n">
         <v>1018294</v>
@@ -13303,7 +13303,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96827220916748</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H446" t="n">
         <v>588207</v>
@@ -13361,7 +13361,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G448" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H448" t="n">
         <v>369775</v>
@@ -13390,7 +13390,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G449" t="n">
-        <v>2.99075984954834</v>
+        <v>2.99075937271118</v>
       </c>
       <c r="H449" t="n">
         <v>251562</v>
@@ -13419,7 +13419,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.99208211898804</v>
+        <v>2.99208235740662</v>
       </c>
       <c r="H450" t="n">
         <v>365775</v>
@@ -13448,7 +13448,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G451" t="n">
-        <v>3.01721405982971</v>
+        <v>3.01721429824829</v>
       </c>
       <c r="H451" t="n">
         <v>457814</v>
@@ -13506,7 +13506,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G453" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H453" t="n">
         <v>403012</v>
@@ -13535,7 +13535,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00398683547974</v>
+        <v>3.00398659706116</v>
       </c>
       <c r="H454" t="n">
         <v>359122</v>
@@ -13564,7 +13564,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G455" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H455" t="n">
         <v>614167</v>
@@ -13593,7 +13593,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>2.99605083465576</v>
+        <v>2.99605059623718</v>
       </c>
       <c r="H456" t="n">
         <v>373559</v>
@@ -13651,7 +13651,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G458" t="n">
-        <v>2.98282241821289</v>
+        <v>2.98282313346863</v>
       </c>
       <c r="H458" t="n">
         <v>732536</v>
@@ -13680,7 +13680,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G459" t="n">
-        <v>2.98943638801575</v>
+        <v>2.98943662643433</v>
       </c>
       <c r="H459" t="n">
         <v>467969</v>
@@ -13709,7 +13709,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G460" t="n">
-        <v>3.01589202880859</v>
+        <v>3.01589179039001</v>
       </c>
       <c r="H460" t="n">
         <v>575173</v>
@@ -13738,7 +13738,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94710826873779</v>
+        <v>2.94710803031921</v>
       </c>
       <c r="H461" t="n">
         <v>1603800</v>
@@ -13796,7 +13796,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G463" t="n">
-        <v>2.88361573219299</v>
+        <v>2.88361597061157</v>
       </c>
       <c r="H463" t="n">
         <v>1131048</v>
@@ -13825,7 +13825,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G464" t="n">
-        <v>2.89080119132996</v>
+        <v>2.89080142974854</v>
       </c>
       <c r="H464" t="n">
         <v>642124</v>
@@ -13883,7 +13883,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>2.89494705200195</v>
+        <v>2.89494681358337</v>
       </c>
       <c r="H466" t="n">
         <v>816758</v>
@@ -13970,7 +13970,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G469" t="n">
-        <v>2.87145566940308</v>
+        <v>2.87145590782166</v>
       </c>
       <c r="H469" t="n">
         <v>1192667</v>
@@ -13999,7 +13999,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>2.75676321983337</v>
+        <v>2.75676298141479</v>
       </c>
       <c r="H470" t="n">
         <v>1222229</v>
@@ -14028,7 +14028,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G471" t="n">
-        <v>2.80650925636292</v>
+        <v>2.80650901794434</v>
       </c>
       <c r="H471" t="n">
         <v>766106</v>
@@ -14086,7 +14086,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G473" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H473" t="n">
         <v>617354</v>
@@ -14115,7 +14115,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G474" t="n">
-        <v>2.88250994682312</v>
+        <v>2.8825101852417</v>
       </c>
       <c r="H474" t="n">
         <v>648999</v>
@@ -14144,7 +14144,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G475" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H475" t="n">
         <v>676249</v>
@@ -14202,7 +14202,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>2.81894588470459</v>
+        <v>2.81894612312317</v>
       </c>
       <c r="H477" t="n">
         <v>580850</v>
@@ -14231,7 +14231,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>2.79130911827087</v>
+        <v>2.79130887985229</v>
       </c>
       <c r="H478" t="n">
         <v>484051</v>
@@ -14318,7 +14318,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.86731004714966</v>
+        <v>2.86731028556824</v>
       </c>
       <c r="H481" t="n">
         <v>2001875</v>
@@ -14347,7 +14347,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G482" t="n">
-        <v>2.92258358001709</v>
+        <v>2.92258334159851</v>
       </c>
       <c r="H482" t="n">
         <v>1544814</v>
@@ -14405,7 +14405,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G484" t="n">
-        <v>2.96542024612427</v>
+        <v>2.96542048454285</v>
       </c>
       <c r="H484" t="n">
         <v>1196522</v>
@@ -14521,7 +14521,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931166648865</v>
       </c>
       <c r="H488" t="n">
         <v>1239936</v>
@@ -14550,7 +14550,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.97371101379395</v>
+        <v>2.97371125221252</v>
       </c>
       <c r="H489" t="n">
         <v>488412</v>
@@ -14579,7 +14579,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G490" t="n">
-        <v>3.02345752716064</v>
+        <v>3.0234580039978</v>
       </c>
       <c r="H490" t="n">
         <v>692474</v>
@@ -14608,7 +14608,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97785711288452</v>
+        <v>2.9778573513031</v>
       </c>
       <c r="H491" t="n">
         <v>736849</v>
@@ -14811,7 +14811,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G498" t="n">
-        <v>3.03036713600159</v>
+        <v>3.03036665916443</v>
       </c>
       <c r="H498" t="n">
         <v>620501</v>
@@ -14840,7 +14840,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G499" t="n">
-        <v>2.97509336471558</v>
+        <v>2.97509360313416</v>
       </c>
       <c r="H499" t="n">
         <v>576760</v>
@@ -14869,7 +14869,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G500" t="n">
-        <v>2.97923898696899</v>
+        <v>2.97923874855042</v>
       </c>
       <c r="H500" t="n">
         <v>1148402</v>
@@ -14898,7 +14898,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G501" t="n">
-        <v>2.94054770469666</v>
+        <v>2.9405472278595</v>
       </c>
       <c r="H501" t="n">
         <v>933889</v>
@@ -15101,7 +15101,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G508" t="n">
-        <v>3.14229559898376</v>
+        <v>3.14229536056519</v>
       </c>
       <c r="H508" t="n">
         <v>516954</v>
@@ -15130,7 +15130,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G509" t="n">
-        <v>3.08840370178223</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H509" t="n">
         <v>334744</v>
@@ -15159,7 +15159,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G510" t="n">
-        <v>3.07182192802429</v>
+        <v>3.07182216644287</v>
       </c>
       <c r="H510" t="n">
         <v>253760</v>
@@ -15188,7 +15188,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>3.04556679725647</v>
+        <v>3.04556703567505</v>
       </c>
       <c r="H511" t="n">
         <v>278984</v>
@@ -15217,7 +15217,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>3.05385828018188</v>
+        <v>3.05385804176331</v>
       </c>
       <c r="H512" t="n">
         <v>428701</v>
@@ -15246,7 +15246,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>3.04556679725647</v>
+        <v>3.04556703567505</v>
       </c>
       <c r="H513" t="n">
         <v>227183</v>
@@ -15391,7 +15391,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G518" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H518" t="n">
         <v>854391</v>
@@ -15449,7 +15449,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G520" t="n">
-        <v>3.03036713600159</v>
+        <v>3.03036665916443</v>
       </c>
       <c r="H520" t="n">
         <v>232235</v>
@@ -15478,7 +15478,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G521" t="n">
-        <v>3.02345752716064</v>
+        <v>3.0234580039978</v>
       </c>
       <c r="H521" t="n">
         <v>343913</v>
@@ -15507,7 +15507,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>3.04003953933716</v>
+        <v>3.04003977775574</v>
       </c>
       <c r="H522" t="n">
         <v>255665</v>
@@ -15536,7 +15536,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931166648865</v>
       </c>
       <c r="H523" t="n">
         <v>289490</v>
@@ -15565,7 +15565,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G524" t="n">
-        <v>2.99305701255798</v>
+        <v>2.99305725097656</v>
       </c>
       <c r="H524" t="n">
         <v>1167836</v>
@@ -15594,7 +15594,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G525" t="n">
-        <v>2.99582123756409</v>
+        <v>2.99582099914551</v>
       </c>
       <c r="H525" t="n">
         <v>364917</v>
@@ -15623,7 +15623,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G526" t="n">
-        <v>2.92258358001709</v>
+        <v>2.92258334159851</v>
       </c>
       <c r="H526" t="n">
         <v>778954</v>
@@ -15652,7 +15652,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G527" t="n">
-        <v>2.91843795776367</v>
+        <v>2.91843819618225</v>
       </c>
       <c r="H527" t="n">
         <v>214673</v>
@@ -15710,7 +15710,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G529" t="n">
-        <v>2.91981959342957</v>
+        <v>2.91982007026672</v>
       </c>
       <c r="H529" t="n">
         <v>295775</v>
@@ -15739,7 +15739,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>2.92258358001709</v>
+        <v>2.92258334159851</v>
       </c>
       <c r="H530" t="n">
         <v>347945</v>
@@ -15768,7 +15768,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94331169128418</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H531" t="n">
         <v>440550</v>
@@ -15797,7 +15797,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G532" t="n">
-        <v>2.93087482452393</v>
+        <v>2.93087434768677</v>
       </c>
       <c r="H532" t="n">
         <v>357082</v>
@@ -15913,7 +15913,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G536" t="n">
-        <v>2.95160222053528</v>
+        <v>2.9516019821167</v>
       </c>
       <c r="H536" t="n">
         <v>547729</v>
@@ -15942,7 +15942,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94192934036255</v>
+        <v>2.94192910194397</v>
       </c>
       <c r="H537" t="n">
         <v>572190</v>
@@ -16000,7 +16000,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>2.94331169128418</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H539" t="n">
         <v>279372</v>
@@ -16029,7 +16029,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>2.91152882575989</v>
+        <v>2.91152906417847</v>
       </c>
       <c r="H540" t="n">
         <v>588609</v>
@@ -16058,7 +16058,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.9281108379364</v>
+        <v>2.92811107635498</v>
       </c>
       <c r="H541" t="n">
         <v>404056</v>
@@ -16116,7 +16116,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H543" t="n">
         <v>678637</v>
@@ -16174,7 +16174,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G545" t="n">
-        <v>2.96265721321106</v>
+        <v>2.96265697479248</v>
       </c>
       <c r="H545" t="n">
         <v>512771</v>
@@ -16203,7 +16203,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97371101379395</v>
+        <v>2.97371125221252</v>
       </c>
       <c r="H546" t="n">
         <v>335573</v>
@@ -16232,7 +16232,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06491255760193</v>
+        <v>3.06491279602051</v>
       </c>
       <c r="H547" t="n">
         <v>681594</v>
@@ -16261,7 +16261,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G548" t="n">
-        <v>3.00134825706482</v>
+        <v>3.00134801864624</v>
       </c>
       <c r="H548" t="n">
         <v>523849</v>
@@ -16406,7 +16406,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>2.95712947845459</v>
+        <v>2.95712995529175</v>
       </c>
       <c r="H553" t="n">
         <v>433139</v>
@@ -16435,7 +16435,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G554" t="n">
-        <v>2.96265721321106</v>
+        <v>2.96265697479248</v>
       </c>
       <c r="H554" t="n">
         <v>220522</v>
@@ -16464,7 +16464,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G555" t="n">
-        <v>2.95298433303833</v>
+        <v>2.95298409461975</v>
       </c>
       <c r="H555" t="n">
         <v>212164</v>
@@ -16522,7 +16522,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G557" t="n">
-        <v>2.90047383308411</v>
+        <v>2.90047407150269</v>
       </c>
       <c r="H557" t="n">
         <v>1783781</v>
@@ -16551,7 +16551,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G558" t="n">
-        <v>2.89632868766785</v>
+        <v>2.89632892608643</v>
       </c>
       <c r="H558" t="n">
         <v>319927</v>
@@ -16609,7 +16609,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G560" t="n">
-        <v>2.8700737953186</v>
+        <v>2.87007403373718</v>
       </c>
       <c r="H560" t="n">
         <v>244609</v>
@@ -16638,7 +16638,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>2.84658241271973</v>
+        <v>2.84658265113831</v>
       </c>
       <c r="H561" t="n">
         <v>476726</v>
@@ -16667,7 +16667,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G562" t="n">
-        <v>2.81341862678528</v>
+        <v>2.8134183883667</v>
       </c>
       <c r="H562" t="n">
         <v>864736</v>
@@ -16696,7 +16696,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G563" t="n">
-        <v>2.76090884208679</v>
+        <v>2.76090908050537</v>
       </c>
       <c r="H563" t="n">
         <v>625996</v>
@@ -16870,7 +16870,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H569" t="n">
         <v>246177</v>
@@ -16899,7 +16899,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G570" t="n">
-        <v>2.73327231407166</v>
+        <v>2.7332718372345</v>
       </c>
       <c r="H570" t="n">
         <v>306755</v>
@@ -16957,7 +16957,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G572" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H572" t="n">
         <v>457593</v>
@@ -16986,7 +16986,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G573" t="n">
-        <v>2.76505422592163</v>
+        <v>2.76505398750305</v>
       </c>
       <c r="H573" t="n">
         <v>274810</v>
@@ -17015,7 +17015,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>2.74985432624817</v>
+        <v>2.74985384941101</v>
       </c>
       <c r="H574" t="n">
         <v>474610</v>
@@ -17044,7 +17044,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G575" t="n">
-        <v>2.71668982505798</v>
+        <v>2.71669006347656</v>
       </c>
       <c r="H575" t="n">
         <v>399828</v>
@@ -17073,7 +17073,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>2.73603582382202</v>
+        <v>2.73603558540344</v>
       </c>
       <c r="H576" t="n">
         <v>219577</v>
@@ -17131,7 +17131,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G578" t="n">
-        <v>2.78716349601746</v>
+        <v>2.78716373443604</v>
       </c>
       <c r="H578" t="n">
         <v>440620</v>
@@ -17189,7 +17189,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G580" t="n">
-        <v>2.75123643875122</v>
+        <v>2.75123620033264</v>
       </c>
       <c r="H580" t="n">
         <v>406170</v>
@@ -17218,7 +17218,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H581" t="n">
         <v>202226</v>
@@ -17247,7 +17247,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74985432624817</v>
+        <v>2.74985384941101</v>
       </c>
       <c r="H582" t="n">
         <v>296696</v>
@@ -17363,7 +17363,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G586" t="n">
-        <v>2.74018144607544</v>
+        <v>2.74018120765686</v>
       </c>
       <c r="H586" t="n">
         <v>165727</v>
@@ -17450,7 +17450,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73879909515381</v>
+        <v>2.73879957199097</v>
       </c>
       <c r="H589" t="n">
         <v>665011</v>
@@ -17479,7 +17479,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G590" t="n">
-        <v>2.83276414871216</v>
+        <v>2.83276438713074</v>
       </c>
       <c r="H590" t="n">
         <v>1098750</v>
@@ -17508,7 +17508,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G591" t="n">
-        <v>2.83967351913452</v>
+        <v>2.8396737575531</v>
       </c>
       <c r="H591" t="n">
         <v>622596</v>
@@ -17537,7 +17537,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G592" t="n">
-        <v>2.84243726730347</v>
+        <v>2.84243702888489</v>
       </c>
       <c r="H592" t="n">
         <v>810244</v>
@@ -17566,7 +17566,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>2.89494705200195</v>
+        <v>2.89494681358337</v>
       </c>
       <c r="H593" t="n">
         <v>529768</v>
@@ -17624,7 +17624,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G595" t="n">
-        <v>2.8355278968811</v>
+        <v>2.83552765846252</v>
       </c>
       <c r="H595" t="n">
         <v>625694</v>
@@ -17653,7 +17653,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G596" t="n">
-        <v>2.86040067672729</v>
+        <v>2.86040091514587</v>
       </c>
       <c r="H596" t="n">
         <v>1036090</v>
@@ -17711,7 +17711,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>2.94331169128418</v>
+        <v>2.9433114528656</v>
       </c>
       <c r="H598" t="n">
         <v>1052192</v>
@@ -17769,7 +17769,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G600" t="n">
-        <v>2.89909219741821</v>
+        <v>2.89909243583679</v>
       </c>
       <c r="H600" t="n">
         <v>744183</v>
@@ -17827,7 +17827,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G602" t="n">
-        <v>2.90047383308411</v>
+        <v>2.90047407150269</v>
       </c>
       <c r="H602" t="n">
         <v>1324299</v>
@@ -17885,7 +17885,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G604" t="n">
-        <v>2.92120170593262</v>
+        <v>2.9212019443512</v>
       </c>
       <c r="H604" t="n">
         <v>500397</v>
@@ -18059,7 +18059,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G610" t="n">
-        <v>2.86869168281555</v>
+        <v>2.86869215965271</v>
       </c>
       <c r="H610" t="n">
         <v>802117</v>
@@ -18088,7 +18088,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G611" t="n">
-        <v>2.91152882575989</v>
+        <v>2.91152906417847</v>
       </c>
       <c r="H611" t="n">
         <v>402937</v>
@@ -18204,7 +18204,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G615" t="n">
-        <v>2.86454653739929</v>
+        <v>2.86454629898071</v>
       </c>
       <c r="H615" t="n">
         <v>695451</v>
@@ -18233,7 +18233,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G616" t="n">
-        <v>2.89080119132996</v>
+        <v>2.89080142974854</v>
       </c>
       <c r="H616" t="n">
         <v>255638</v>
@@ -18262,7 +18262,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G617" t="n">
-        <v>2.89632868766785</v>
+        <v>2.89632892608643</v>
       </c>
       <c r="H617" t="n">
         <v>507785</v>
@@ -18291,7 +18291,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G618" t="n">
-        <v>2.92120170593262</v>
+        <v>2.9212019443512</v>
       </c>
       <c r="H618" t="n">
         <v>836606</v>
@@ -18320,7 +18320,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G619" t="n">
-        <v>2.93087482452393</v>
+        <v>2.93087434768677</v>
       </c>
       <c r="H619" t="n">
         <v>258418</v>
@@ -18349,7 +18349,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G620" t="n">
-        <v>2.89909219741821</v>
+        <v>2.89909243583679</v>
       </c>
       <c r="H620" t="n">
         <v>492515</v>
@@ -18378,7 +18378,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G621" t="n">
-        <v>2.97509336471558</v>
+        <v>2.97509360313416</v>
       </c>
       <c r="H621" t="n">
         <v>601405</v>
@@ -18436,7 +18436,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G623" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H623" t="n">
         <v>220839</v>
@@ -18465,7 +18465,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G624" t="n">
-        <v>2.96265721321106</v>
+        <v>2.96265697479248</v>
       </c>
       <c r="H624" t="n">
         <v>486020</v>
@@ -18494,7 +18494,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931166648865</v>
       </c>
       <c r="H625" t="n">
         <v>641122</v>
@@ -18523,7 +18523,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>3.04003953933716</v>
+        <v>3.04003977775574</v>
       </c>
       <c r="H626" t="n">
         <v>1249599</v>
@@ -18552,7 +18552,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G627" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898454666138</v>
       </c>
       <c r="H627" t="n">
         <v>241326</v>
@@ -18610,7 +18610,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G629" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H629" t="n">
         <v>363346</v>
@@ -18668,7 +18668,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G631" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898454666138</v>
       </c>
       <c r="H631" t="n">
         <v>472455</v>
@@ -18697,7 +18697,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G632" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898454666138</v>
       </c>
       <c r="H632" t="n">
         <v>518046</v>
@@ -18755,7 +18755,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G634" t="n">
-        <v>3.03036713600159</v>
+        <v>3.03036665916443</v>
       </c>
       <c r="H634" t="n">
         <v>523810</v>
@@ -18813,7 +18813,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.04003953933716</v>
+        <v>3.04003977775574</v>
       </c>
       <c r="H636" t="n">
         <v>165327</v>
@@ -18900,7 +18900,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>3.08287668228149</v>
+        <v>3.08287644386292</v>
       </c>
       <c r="H639" t="n">
         <v>455246</v>
@@ -18929,7 +18929,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G640" t="n">
-        <v>3.08011269569397</v>
+        <v>3.08011317253113</v>
       </c>
       <c r="H640" t="n">
         <v>539646</v>
@@ -18958,7 +18958,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G641" t="n">
-        <v>3.08840370178223</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H641" t="n">
         <v>313925</v>
@@ -18987,7 +18987,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>3.04003953933716</v>
+        <v>3.04003977775574</v>
       </c>
       <c r="H642" t="n">
         <v>690661</v>
@@ -19045,7 +19045,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G644" t="n">
-        <v>3.0966944694519</v>
+        <v>3.09669518470764</v>
       </c>
       <c r="H644" t="n">
         <v>242340</v>
@@ -19074,7 +19074,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G645" t="n">
-        <v>3.13262248039246</v>
+        <v>3.13262271881104</v>
       </c>
       <c r="H645" t="n">
         <v>579860</v>
@@ -19103,7 +19103,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G646" t="n">
-        <v>3.14229559898376</v>
+        <v>3.14229536056519</v>
       </c>
       <c r="H646" t="n">
         <v>601188</v>
@@ -19132,7 +19132,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G647" t="n">
-        <v>3.06629490852356</v>
+        <v>3.06629514694214</v>
       </c>
       <c r="H647" t="n">
         <v>369408</v>
@@ -19161,7 +19161,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G648" t="n">
-        <v>3.04694890975952</v>
+        <v>3.04694867134094</v>
       </c>
       <c r="H648" t="n">
         <v>341481</v>
@@ -19190,7 +19190,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G649" t="n">
-        <v>3.0966944694519</v>
+        <v>3.09669518470764</v>
       </c>
       <c r="H649" t="n">
         <v>458945</v>
@@ -19219,7 +19219,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12294960021973</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H650" t="n">
         <v>592680</v>
@@ -19248,7 +19248,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G651" t="n">
-        <v>3.10360407829285</v>
+        <v>3.10360431671143</v>
       </c>
       <c r="H651" t="n">
         <v>725248</v>
@@ -19277,7 +19277,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G652" t="n">
-        <v>3.12709546089172</v>
+        <v>3.12709522247314</v>
       </c>
       <c r="H652" t="n">
         <v>655086</v>
@@ -19306,7 +19306,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G653" t="n">
-        <v>3.13262248039246</v>
+        <v>3.13262271881104</v>
       </c>
       <c r="H653" t="n">
         <v>547144</v>
@@ -19335,7 +19335,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G654" t="n">
-        <v>3.12294960021973</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H654" t="n">
         <v>440007</v>
@@ -19364,7 +19364,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G655" t="n">
-        <v>3.11742281913757</v>
+        <v>3.11742258071899</v>
       </c>
       <c r="H655" t="n">
         <v>774559</v>
@@ -19422,7 +19422,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G657" t="n">
-        <v>3.08840370178223</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H657" t="n">
         <v>649670</v>
@@ -19451,7 +19451,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G658" t="n">
-        <v>3.08840370178223</v>
+        <v>3.08840394020081</v>
       </c>
       <c r="H658" t="n">
         <v>463243</v>
@@ -19538,7 +19538,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>3.12294960021973</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H661" t="n">
         <v>500812</v>
@@ -19567,7 +19567,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13814973831177</v>
+        <v>3.13814949989319</v>
       </c>
       <c r="H662" t="n">
         <v>519012</v>
@@ -19654,7 +19654,7 @@
         <v>4.5</v>
       </c>
       <c r="G665" t="n">
-        <v>3.10913133621216</v>
+        <v>3.10913157463074</v>
       </c>
       <c r="H665" t="n">
         <v>605477</v>
@@ -19712,7 +19712,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.10913133621216</v>
+        <v>3.10913157463074</v>
       </c>
       <c r="H667" t="n">
         <v>591269</v>
@@ -19770,7 +19770,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G669" t="n">
-        <v>3.26251554489136</v>
+        <v>3.26251530647278</v>
       </c>
       <c r="H669" t="n">
         <v>2348370</v>
@@ -19828,7 +19828,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>3.34542536735535</v>
+        <v>3.34542560577393</v>
       </c>
       <c r="H671" t="n">
         <v>836124</v>
@@ -19857,7 +19857,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G672" t="n">
-        <v>3.3468074798584</v>
+        <v>3.34680724143982</v>
       </c>
       <c r="H672" t="n">
         <v>697587</v>
@@ -19886,7 +19886,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G673" t="n">
-        <v>3.36062574386597</v>
+        <v>3.36062526702881</v>
       </c>
       <c r="H673" t="n">
         <v>702541</v>
@@ -19915,7 +19915,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38411641120911</v>
+        <v>3.38411688804626</v>
       </c>
       <c r="H674" t="n">
         <v>577089</v>
@@ -19944,7 +19944,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G675" t="n">
-        <v>3.35924363136292</v>
+        <v>3.35924386978149</v>
       </c>
       <c r="H675" t="n">
         <v>374930</v>
@@ -19973,7 +19973,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G676" t="n">
-        <v>3.37997126579285</v>
+        <v>3.37997174263</v>
       </c>
       <c r="H676" t="n">
         <v>299664</v>
@@ -20002,7 +20002,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>3.34542536735535</v>
+        <v>3.34542560577393</v>
       </c>
       <c r="H677" t="n">
         <v>220591</v>
@@ -20031,7 +20031,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>3.30535244941711</v>
+        <v>3.30535197257996</v>
       </c>
       <c r="H678" t="n">
         <v>478581</v>
@@ -20060,7 +20060,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G679" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575296401978</v>
       </c>
       <c r="H679" t="n">
         <v>357536</v>
@@ -20118,7 +20118,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G681" t="n">
-        <v>3.31502532958984</v>
+        <v>3.31502485275269</v>
       </c>
       <c r="H681" t="n">
         <v>329531</v>
@@ -20176,7 +20176,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G683" t="n">
-        <v>3.37858939170837</v>
+        <v>3.37858963012695</v>
       </c>
       <c r="H683" t="n">
         <v>448925</v>
@@ -20205,7 +20205,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G684" t="n">
-        <v>3.37444400787354</v>
+        <v>3.37444376945496</v>
       </c>
       <c r="H684" t="n">
         <v>470290</v>
@@ -20234,7 +20234,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G685" t="n">
-        <v>3.36615347862244</v>
+        <v>3.36615324020386</v>
       </c>
       <c r="H685" t="n">
         <v>497823</v>
@@ -20263,7 +20263,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G686" t="n">
-        <v>3.36615347862244</v>
+        <v>3.36615324020386</v>
       </c>
       <c r="H686" t="n">
         <v>412491</v>
@@ -20292,7 +20292,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G687" t="n">
-        <v>3.36615347862244</v>
+        <v>3.36615324020386</v>
       </c>
       <c r="H687" t="n">
         <v>264276</v>
@@ -20321,7 +20321,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G688" t="n">
-        <v>3.32469820976257</v>
+        <v>3.32469749450684</v>
       </c>
       <c r="H688" t="n">
         <v>384931</v>
@@ -20379,7 +20379,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G690" t="n">
-        <v>3.29015183448792</v>
+        <v>3.29015207290649</v>
       </c>
       <c r="H690" t="n">
         <v>515539</v>
@@ -20408,7 +20408,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31778883934021</v>
+        <v>3.31778860092163</v>
       </c>
       <c r="H691" t="n">
         <v>207705</v>
@@ -20582,7 +20582,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G697" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575296401978</v>
       </c>
       <c r="H697" t="n">
         <v>426921</v>
@@ -20611,7 +20611,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G698" t="n">
-        <v>3.34266138076782</v>
+        <v>3.3426616191864</v>
       </c>
       <c r="H698" t="n">
         <v>268858</v>
@@ -20640,7 +20640,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.32331585884094</v>
+        <v>3.32331609725952</v>
       </c>
       <c r="H699" t="n">
         <v>272666</v>
@@ -20669,7 +20669,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G700" t="n">
-        <v>3.31364321708679</v>
+        <v>3.31364297866821</v>
       </c>
       <c r="H700" t="n">
         <v>621856</v>
@@ -20698,7 +20698,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>3.37168073654175</v>
+        <v>3.37168049812317</v>
       </c>
       <c r="H701" t="n">
         <v>1574407</v>
@@ -20727,7 +20727,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G702" t="n">
-        <v>3.36062574386597</v>
+        <v>3.36062526702881</v>
       </c>
       <c r="H702" t="n">
         <v>244864</v>
@@ -20756,7 +20756,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.37168073654175</v>
+        <v>3.37168049812317</v>
       </c>
       <c r="H703" t="n">
         <v>496384</v>
@@ -20843,7 +20843,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G706" t="n">
-        <v>3.38273525238037</v>
+        <v>3.38273501396179</v>
       </c>
       <c r="H706" t="n">
         <v>370437</v>
@@ -20901,7 +20901,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G708" t="n">
-        <v>3.34127998352051</v>
+        <v>3.34128022193909</v>
       </c>
       <c r="H708" t="n">
         <v>227136</v>
@@ -20930,7 +20930,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G709" t="n">
-        <v>3.33437085151672</v>
+        <v>3.3343710899353</v>
       </c>
       <c r="H709" t="n">
         <v>886827</v>
@@ -20959,7 +20959,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G710" t="n">
-        <v>3.32469820976257</v>
+        <v>3.32469749450684</v>
       </c>
       <c r="H710" t="n">
         <v>248745</v>
@@ -20988,7 +20988,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>3.38549900054932</v>
+        <v>3.38549876213074</v>
       </c>
       <c r="H711" t="n">
         <v>312454</v>
@@ -21017,7 +21017,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G712" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575296401978</v>
       </c>
       <c r="H712" t="n">
         <v>415959</v>
@@ -21046,7 +21046,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G713" t="n">
-        <v>3.36200761795044</v>
+        <v>3.36200785636902</v>
       </c>
       <c r="H713" t="n">
         <v>399022</v>
@@ -21075,7 +21075,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G714" t="n">
-        <v>3.37029838562012</v>
+        <v>3.3702986240387</v>
       </c>
       <c r="H714" t="n">
         <v>307384</v>
@@ -21133,7 +21133,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G716" t="n">
-        <v>3.4450786113739</v>
+        <v>3.44507884979248</v>
       </c>
       <c r="H716" t="n">
         <v>338239</v>
@@ -21220,7 +21220,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G719" t="n">
-        <v>3.46092796325684</v>
+        <v>3.46092820167542</v>
       </c>
       <c r="H719" t="n">
         <v>505932</v>
@@ -21249,7 +21249,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G720" t="n">
-        <v>3.48109984397888</v>
+        <v>3.48110008239746</v>
       </c>
       <c r="H720" t="n">
         <v>314563</v>
@@ -21278,7 +21278,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>3.46957325935364</v>
+        <v>3.46957302093506</v>
       </c>
       <c r="H721" t="n">
         <v>1025779</v>
@@ -21307,7 +21307,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G722" t="n">
-        <v>3.45660591125488</v>
+        <v>3.45660543441772</v>
       </c>
       <c r="H722" t="n">
         <v>697211</v>
@@ -21336,7 +21336,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G723" t="n">
-        <v>3.48109984397888</v>
+        <v>3.48110008239746</v>
       </c>
       <c r="H723" t="n">
         <v>368085</v>
@@ -21365,7 +21365,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>3.49406766891479</v>
+        <v>3.49406814575195</v>
       </c>
       <c r="H724" t="n">
         <v>1001017</v>
@@ -21394,7 +21394,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G725" t="n">
-        <v>3.553142786026</v>
+        <v>3.55314302444458</v>
       </c>
       <c r="H725" t="n">
         <v>854127</v>
@@ -21423,7 +21423,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G726" t="n">
-        <v>3.57475590705872</v>
+        <v>3.57475543022156</v>
       </c>
       <c r="H726" t="n">
         <v>985537</v>
@@ -21452,7 +21452,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G727" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H727" t="n">
         <v>685720</v>
@@ -21510,7 +21510,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G729" t="n">
-        <v>3.67777633666992</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H729" t="n">
         <v>630184</v>
@@ -21626,7 +21626,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659327507019</v>
       </c>
       <c r="H733" t="n">
         <v>827997</v>
@@ -21655,7 +21655,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G734" t="n">
-        <v>3.65256190299988</v>
+        <v>3.65256214141846</v>
       </c>
       <c r="H734" t="n">
         <v>522904</v>
@@ -21684,7 +21684,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G735" t="n">
-        <v>3.61293792724609</v>
+        <v>3.61293816566467</v>
       </c>
       <c r="H735" t="n">
         <v>404107</v>
@@ -21742,7 +21742,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>3.63094902038574</v>
+        <v>3.63094854354858</v>
       </c>
       <c r="H737" t="n">
         <v>602362</v>
@@ -21771,7 +21771,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>3.66336846351624</v>
+        <v>3.66336822509766</v>
       </c>
       <c r="H738" t="n">
         <v>726479</v>
@@ -21800,7 +21800,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G739" t="n">
-        <v>3.68498039245605</v>
+        <v>3.68498086929321</v>
       </c>
       <c r="H739" t="n">
         <v>2546011</v>
@@ -21829,7 +21829,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>3.68858337402344</v>
+        <v>3.68858289718628</v>
       </c>
       <c r="H740" t="n">
         <v>394292</v>
@@ -21858,7 +21858,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G741" t="n">
-        <v>3.62374472618103</v>
+        <v>3.62374448776245</v>
       </c>
       <c r="H741" t="n">
         <v>214957</v>
@@ -21887,7 +21887,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G742" t="n">
-        <v>3.58484148979187</v>
+        <v>3.58484125137329</v>
       </c>
       <c r="H742" t="n">
         <v>346299</v>
@@ -21916,7 +21916,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.54449772834778</v>
+        <v>3.54449796676636</v>
       </c>
       <c r="H743" t="n">
         <v>449069</v>
@@ -21945,7 +21945,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G744" t="n">
-        <v>3.59492802619934</v>
+        <v>3.59492754936218</v>
       </c>
       <c r="H744" t="n">
         <v>517127</v>
@@ -21974,7 +21974,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G745" t="n">
-        <v>3.52288484573364</v>
+        <v>3.52288508415222</v>
       </c>
       <c r="H745" t="n">
         <v>2145807</v>
@@ -22003,7 +22003,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>3.54449772834778</v>
+        <v>3.54449796676636</v>
       </c>
       <c r="H746" t="n">
         <v>1059414</v>
@@ -22032,7 +22032,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G747" t="n">
-        <v>3.60573363304138</v>
+        <v>3.60573410987854</v>
       </c>
       <c r="H747" t="n">
         <v>607759</v>
@@ -22061,7 +22061,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G748" t="n">
-        <v>3.59924960136414</v>
+        <v>3.59925007820129</v>
       </c>
       <c r="H748" t="n">
         <v>415115</v>
@@ -22148,7 +22148,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G751" t="n">
-        <v>3.58051896095276</v>
+        <v>3.58051872253418</v>
       </c>
       <c r="H751" t="n">
         <v>386818</v>
@@ -22206,7 +22206,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.62014269828796</v>
+        <v>3.62014293670654</v>
       </c>
       <c r="H753" t="n">
         <v>353573</v>
@@ -22235,7 +22235,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G754" t="n">
-        <v>3.59780931472778</v>
+        <v>3.59780955314636</v>
       </c>
       <c r="H754" t="n">
         <v>281615</v>
@@ -22264,7 +22264,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G755" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H755" t="n">
         <v>308092</v>
@@ -22293,7 +22293,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G756" t="n">
-        <v>3.61293792724609</v>
+        <v>3.61293816566467</v>
       </c>
       <c r="H756" t="n">
         <v>299037</v>
@@ -22322,7 +22322,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>3.61654043197632</v>
+        <v>3.61654019355774</v>
       </c>
       <c r="H757" t="n">
         <v>392000</v>
@@ -22380,7 +22380,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>3.60573363304138</v>
+        <v>3.60573410987854</v>
       </c>
       <c r="H759" t="n">
         <v>333042</v>
@@ -22409,7 +22409,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H760" t="n">
         <v>144620</v>
@@ -22438,7 +22438,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G761" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H761" t="n">
         <v>140253</v>
@@ -22467,7 +22467,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G762" t="n">
-        <v>3.60573363304138</v>
+        <v>3.60573410987854</v>
       </c>
       <c r="H762" t="n">
         <v>233504</v>
@@ -22641,7 +22641,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G768" t="n">
-        <v>3.62374472618103</v>
+        <v>3.62374448776245</v>
       </c>
       <c r="H768" t="n">
         <v>430153</v>
@@ -22670,7 +22670,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G769" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H769" t="n">
         <v>241517</v>
@@ -22757,7 +22757,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G772" t="n">
-        <v>3.67057228088379</v>
+        <v>3.67057251930237</v>
       </c>
       <c r="H772" t="n">
         <v>490175</v>
@@ -22815,7 +22815,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>3.61654043197632</v>
+        <v>3.61654019355774</v>
       </c>
       <c r="H774" t="n">
         <v>365000</v>
@@ -22844,7 +22844,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G775" t="n">
-        <v>3.66697025299072</v>
+        <v>3.66696977615356</v>
       </c>
       <c r="H775" t="n">
         <v>116327</v>
@@ -22873,7 +22873,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G776" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659327507019</v>
       </c>
       <c r="H776" t="n">
         <v>535968</v>
@@ -22902,7 +22902,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G777" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659327507019</v>
       </c>
       <c r="H777" t="n">
         <v>394359</v>
@@ -22931,7 +22931,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>3.67777633666992</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H778" t="n">
         <v>510087</v>
@@ -22960,7 +22960,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H779" t="n">
         <v>537475</v>
@@ -22989,7 +22989,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.72460460662842</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H780" t="n">
         <v>198706</v>
@@ -23047,7 +23047,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>3.75702357292175</v>
+        <v>3.75702309608459</v>
       </c>
       <c r="H782" t="n">
         <v>152644</v>
@@ -23076,7 +23076,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.71379780769348</v>
+        <v>3.71379828453064</v>
       </c>
       <c r="H783" t="n">
         <v>188130</v>
@@ -23105,7 +23105,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>3.71379780769348</v>
+        <v>3.71379828453064</v>
       </c>
       <c r="H784" t="n">
         <v>217194</v>
@@ -23134,7 +23134,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G785" t="n">
-        <v>3.77503347396851</v>
+        <v>3.77503371238708</v>
       </c>
       <c r="H785" t="n">
         <v>221413</v>
@@ -23192,7 +23192,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G787" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H787" t="n">
         <v>298424</v>
@@ -23221,7 +23221,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G788" t="n">
-        <v>3.70299100875854</v>
+        <v>3.70299172401428</v>
       </c>
       <c r="H788" t="n">
         <v>296476</v>
@@ -23250,7 +23250,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>3.72100210189819</v>
+        <v>3.72100234031677</v>
       </c>
       <c r="H789" t="n">
         <v>115274</v>
@@ -23279,7 +23279,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G790" t="n">
-        <v>3.68858337402344</v>
+        <v>3.68858289718628</v>
       </c>
       <c r="H790" t="n">
         <v>402408</v>
@@ -23308,7 +23308,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>3.72100210189819</v>
+        <v>3.72100234031677</v>
       </c>
       <c r="H791" t="n">
         <v>202767</v>
@@ -23337,7 +23337,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.71740007400513</v>
+        <v>3.71739959716797</v>
       </c>
       <c r="H792" t="n">
         <v>225935</v>
@@ -23366,7 +23366,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G793" t="n">
-        <v>3.70299100875854</v>
+        <v>3.70299172401428</v>
       </c>
       <c r="H793" t="n">
         <v>262081</v>
@@ -23453,7 +23453,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>3.62014269828796</v>
+        <v>3.62014293670654</v>
       </c>
       <c r="H796" t="n">
         <v>385770</v>
@@ -23511,7 +23511,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.68858337402344</v>
+        <v>3.68858289718628</v>
       </c>
       <c r="H798" t="n">
         <v>166019</v>
@@ -23540,7 +23540,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>3.67777633666992</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H799" t="n">
         <v>119947</v>
@@ -23627,7 +23627,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>3.67777633666992</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H802" t="n">
         <v>357933</v>
@@ -23656,7 +23656,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>3.66697025299072</v>
+        <v>3.66696977615356</v>
       </c>
       <c r="H803" t="n">
         <v>178529</v>
@@ -23714,7 +23714,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>3.69578766822815</v>
+        <v>3.69578742980957</v>
       </c>
       <c r="H805" t="n">
         <v>390641</v>
@@ -23743,7 +23743,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.67057228088379</v>
+        <v>3.67057251930237</v>
       </c>
       <c r="H806" t="n">
         <v>358329</v>
@@ -23801,7 +23801,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G808" t="n">
-        <v>3.67057228088379</v>
+        <v>3.67057251930237</v>
       </c>
       <c r="H808" t="n">
         <v>272752</v>
@@ -23830,7 +23830,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H809" t="n">
         <v>629355</v>
@@ -23917,7 +23917,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>3.68858337402344</v>
+        <v>3.68858289718628</v>
       </c>
       <c r="H812" t="n">
         <v>198291</v>
@@ -23946,7 +23946,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H813" t="n">
         <v>202688</v>
@@ -23975,7 +23975,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H814" t="n">
         <v>370664</v>
@@ -24004,7 +24004,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G815" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H815" t="n">
         <v>312178</v>
@@ -24033,7 +24033,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G816" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H816" t="n">
         <v>225018</v>
@@ -24062,7 +24062,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H817" t="n">
         <v>140668</v>
@@ -24091,7 +24091,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H818" t="n">
         <v>255505</v>
@@ -24120,7 +24120,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342106819153</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H819" t="n">
         <v>228708</v>
@@ -24149,7 +24149,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>3.74981904029846</v>
+        <v>3.74981880187988</v>
       </c>
       <c r="H820" t="n">
         <v>270294</v>
@@ -24178,7 +24178,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>3.75702357292175</v>
+        <v>3.75702309608459</v>
       </c>
       <c r="H821" t="n">
         <v>217419</v>
@@ -24265,7 +24265,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>3.72460460662842</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H824" t="n">
         <v>343423</v>
@@ -24294,7 +24294,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342106819153</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H825" t="n">
         <v>242523</v>
@@ -24352,7 +24352,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G827" t="n">
-        <v>3.69938969612122</v>
+        <v>3.69938898086548</v>
       </c>
       <c r="H827" t="n">
         <v>236994</v>
@@ -24381,7 +24381,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G828" t="n">
-        <v>3.70299100875854</v>
+        <v>3.70299172401428</v>
       </c>
       <c r="H828" t="n">
         <v>168676</v>
@@ -24410,7 +24410,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>3.72460460662842</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H829" t="n">
         <v>248488</v>
@@ -24439,7 +24439,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G830" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180818557739</v>
       </c>
       <c r="H830" t="n">
         <v>177186</v>
@@ -24468,7 +24468,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>3.72460460662842</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H831" t="n">
         <v>204215</v>
@@ -24526,7 +24526,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.78584027290344</v>
+        <v>3.7858407497406</v>
       </c>
       <c r="H833" t="n">
         <v>158358</v>
@@ -24555,7 +24555,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G834" t="n">
-        <v>3.79304432868958</v>
+        <v>3.79304480552673</v>
       </c>
       <c r="H834" t="n">
         <v>288604</v>
@@ -24584,7 +24584,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>3.82546424865723</v>
+        <v>3.82546377182007</v>
       </c>
       <c r="H835" t="n">
         <v>526098</v>
@@ -24613,7 +24613,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G836" t="n">
-        <v>3.81465744972229</v>
+        <v>3.81465792655945</v>
       </c>
       <c r="H836" t="n">
         <v>353172</v>
@@ -24642,7 +24642,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342106819153</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H837" t="n">
         <v>261649</v>
@@ -24671,7 +24671,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>3.77503347396851</v>
+        <v>3.77503371238708</v>
       </c>
       <c r="H838" t="n">
         <v>184338</v>
@@ -24729,7 +24729,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.78584027290344</v>
+        <v>3.7858407497406</v>
       </c>
       <c r="H840" t="n">
         <v>309517</v>
@@ -24758,7 +24758,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.77863597869873</v>
+        <v>3.77863621711731</v>
       </c>
       <c r="H841" t="n">
         <v>231779</v>
@@ -24787,7 +24787,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>3.81465744972229</v>
+        <v>3.81465792655945</v>
       </c>
       <c r="H842" t="n">
         <v>316067</v>
@@ -24816,7 +24816,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148500442505</v>
+        <v>3.86148548126221</v>
       </c>
       <c r="H843" t="n">
         <v>518806</v>
@@ -24845,7 +24845,7 @@
         <v>5.375</v>
       </c>
       <c r="G844" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H844" t="n">
         <v>150028</v>
@@ -24874,7 +24874,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.82186126708984</v>
+        <v>3.821861743927</v>
       </c>
       <c r="H845" t="n">
         <v>210214</v>
@@ -24903,7 +24903,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.79664754867554</v>
+        <v>3.79664707183838</v>
       </c>
       <c r="H846" t="n">
         <v>882140</v>
@@ -24932,7 +24932,7 @@
         <v>5.25</v>
       </c>
       <c r="G847" t="n">
-        <v>3.7822380065918</v>
+        <v>3.78223824501038</v>
       </c>
       <c r="H847" t="n">
         <v>330835</v>
@@ -24990,7 +24990,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G849" t="n">
-        <v>3.78944325447083</v>
+        <v>3.78944277763367</v>
       </c>
       <c r="H849" t="n">
         <v>309778</v>
@@ -25019,7 +25019,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G850" t="n">
-        <v>3.86508750915527</v>
+        <v>3.86508703231812</v>
       </c>
       <c r="H850" t="n">
         <v>585661</v>
@@ -25048,7 +25048,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>3.82906556129456</v>
+        <v>3.82906603813171</v>
       </c>
       <c r="H851" t="n">
         <v>1005431</v>
@@ -25106,7 +25106,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G853" t="n">
-        <v>3.87589359283447</v>
+        <v>3.87589311599731</v>
       </c>
       <c r="H853" t="n">
         <v>449570</v>
@@ -25135,7 +25135,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80024909973145</v>
+        <v>3.80024862289429</v>
       </c>
       <c r="H854" t="n">
         <v>521291</v>
@@ -25164,7 +25164,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79664754867554</v>
+        <v>3.79664707183838</v>
       </c>
       <c r="H855" t="n">
         <v>531608</v>
@@ -25193,7 +25193,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80024909973145</v>
+        <v>3.80024862289429</v>
       </c>
       <c r="H856" t="n">
         <v>340183</v>
@@ -25222,7 +25222,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G857" t="n">
-        <v>3.80385136604309</v>
+        <v>3.80385184288025</v>
       </c>
       <c r="H857" t="n">
         <v>236744</v>
@@ -25251,7 +25251,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80024909973145</v>
+        <v>3.80024862289429</v>
       </c>
       <c r="H858" t="n">
         <v>247892</v>
@@ -25280,7 +25280,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.85067892074585</v>
+        <v>3.85067844390869</v>
       </c>
       <c r="H859" t="n">
         <v>429041</v>
@@ -25338,7 +25338,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>3.84707641601562</v>
+        <v>3.84707689285278</v>
       </c>
       <c r="H861" t="n">
         <v>142215</v>
@@ -25367,7 +25367,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G862" t="n">
-        <v>3.83266878128052</v>
+        <v>3.83266854286194</v>
       </c>
       <c r="H862" t="n">
         <v>423140</v>
@@ -25425,7 +25425,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>3.79664754867554</v>
+        <v>3.79664707183838</v>
       </c>
       <c r="H864" t="n">
         <v>272878</v>
@@ -25483,7 +25483,7 @@
         <v>5.375</v>
       </c>
       <c r="G866" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H866" t="n">
         <v>334082</v>
@@ -25570,7 +25570,7 @@
         <v>5.375</v>
       </c>
       <c r="G869" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H869" t="n">
         <v>307691</v>
@@ -25628,7 +25628,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G871" t="n">
-        <v>3.83266878128052</v>
+        <v>3.83266854286194</v>
       </c>
       <c r="H871" t="n">
         <v>429811</v>
@@ -25715,7 +25715,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>3.80024909973145</v>
+        <v>3.80024862289429</v>
       </c>
       <c r="H874" t="n">
         <v>558719</v>
@@ -25744,7 +25744,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>3.83266878128052</v>
+        <v>3.83266854286194</v>
       </c>
       <c r="H875" t="n">
         <v>683792</v>
@@ -25831,7 +25831,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G878" t="n">
-        <v>3.92632341384888</v>
+        <v>3.92632293701172</v>
       </c>
       <c r="H878" t="n">
         <v>368905</v>
@@ -25860,7 +25860,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G879" t="n">
-        <v>3.95874285697937</v>
+        <v>3.95874238014221</v>
       </c>
       <c r="H879" t="n">
         <v>433161</v>
@@ -25947,7 +25947,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>4.01997852325439</v>
+        <v>4.01997900009155</v>
       </c>
       <c r="H882" t="n">
         <v>458370</v>
@@ -25976,7 +25976,7 @@
         <v>5.625</v>
       </c>
       <c r="G883" t="n">
-        <v>4.05239820480347</v>
+        <v>4.05239772796631</v>
       </c>
       <c r="H883" t="n">
         <v>369585</v>
@@ -26063,7 +26063,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>4.08841896057129</v>
+        <v>4.08841943740845</v>
       </c>
       <c r="H886" t="n">
         <v>668689</v>
@@ -26121,7 +26121,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>4.2180962562561</v>
+        <v>4.21809577941895</v>
       </c>
       <c r="H888" t="n">
         <v>1316501</v>
@@ -26150,7 +26150,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18567752838135</v>
+        <v>4.18567705154419</v>
       </c>
       <c r="H889" t="n">
         <v>1255135</v>
@@ -26266,7 +26266,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G893" t="n">
-        <v>4.19648313522339</v>
+        <v>4.19648361206055</v>
       </c>
       <c r="H893" t="n">
         <v>718224</v>
@@ -26353,7 +26353,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G896" t="n">
-        <v>4.27212810516357</v>
+        <v>4.27212858200073</v>
       </c>
       <c r="H896" t="n">
         <v>661972</v>
@@ -26411,7 +26411,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G898" t="n">
-        <v>4.31895637512207</v>
+        <v>4.31895589828491</v>
       </c>
       <c r="H898" t="n">
         <v>927247</v>
@@ -26440,7 +26440,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G899" t="n">
-        <v>4.31175184249878</v>
+        <v>4.31175136566162</v>
       </c>
       <c r="H899" t="n">
         <v>306181</v>
@@ -26556,7 +26556,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G903" t="n">
-        <v>4.32616090774536</v>
+        <v>4.3261604309082</v>
       </c>
       <c r="H903" t="n">
         <v>982085</v>
@@ -26585,7 +26585,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G904" t="n">
-        <v>4.35857963562012</v>
+        <v>4.35857915878296</v>
       </c>
       <c r="H904" t="n">
         <v>597979</v>
@@ -26614,7 +26614,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G905" t="n">
-        <v>4.39820241928101</v>
+        <v>4.39820289611816</v>
       </c>
       <c r="H905" t="n">
         <v>530337</v>
@@ -26643,7 +26643,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G906" t="n">
-        <v>4.42702054977417</v>
+        <v>4.42701959609985</v>
       </c>
       <c r="H906" t="n">
         <v>303177</v>
@@ -26730,7 +26730,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>4.18567752838135</v>
+        <v>4.18567705154419</v>
       </c>
       <c r="H909" t="n">
         <v>1255336</v>
@@ -26817,7 +26817,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G912" t="n">
-        <v>4.06320381164551</v>
+        <v>4.06320428848267</v>
       </c>
       <c r="H912" t="n">
         <v>1063569</v>
@@ -26904,7 +26904,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>3.77863597869873</v>
+        <v>3.77863621711731</v>
       </c>
       <c r="H915" t="n">
         <v>1709583</v>
@@ -26933,7 +26933,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81825995445251</v>
+        <v>3.81825947761536</v>
       </c>
       <c r="H916" t="n">
         <v>1032190</v>
@@ -26962,7 +26962,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.71740007400513</v>
+        <v>3.71739959716797</v>
       </c>
       <c r="H917" t="n">
         <v>905147</v>
@@ -26991,7 +26991,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G918" t="n">
-        <v>3.61654043197632</v>
+        <v>3.61654019355774</v>
       </c>
       <c r="H918" t="n">
         <v>832462</v>
@@ -27049,7 +27049,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G920" t="n">
-        <v>3.24624109268188</v>
+        <v>3.24624133110046</v>
       </c>
       <c r="H920" t="n">
         <v>847418</v>
@@ -27078,7 +27078,7 @@
         <v>4.5</v>
       </c>
       <c r="G921" t="n">
-        <v>3.24191856384277</v>
+        <v>3.24191880226135</v>
       </c>
       <c r="H921" t="n">
         <v>1478690</v>
@@ -27136,7 +27136,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G923" t="n">
-        <v>2.86585569381714</v>
+        <v>2.8658561706543</v>
       </c>
       <c r="H923" t="n">
         <v>2005867</v>
@@ -27223,7 +27223,7 @@
         <v>3.75</v>
       </c>
       <c r="G926" t="n">
-        <v>2.70159864425659</v>
+        <v>2.70159888267517</v>
       </c>
       <c r="H926" t="n">
         <v>1078695</v>
@@ -27252,7 +27252,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G927" t="n">
-        <v>2.58921241760254</v>
+        <v>2.58921217918396</v>
       </c>
       <c r="H927" t="n">
         <v>1414173</v>
@@ -27281,7 +27281,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G928" t="n">
-        <v>2.52437376976013</v>
+        <v>2.52437400817871</v>
       </c>
       <c r="H928" t="n">
         <v>823310</v>
@@ -27368,7 +27368,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G931" t="n">
-        <v>2.61082530021667</v>
+        <v>2.6108250617981</v>
       </c>
       <c r="H931" t="n">
         <v>1059073</v>
@@ -27455,7 +27455,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G934" t="n">
-        <v>2.8687379360199</v>
+        <v>2.86873769760132</v>
       </c>
       <c r="H934" t="n">
         <v>911009</v>
@@ -27542,7 +27542,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G937" t="n">
-        <v>2.93933939933777</v>
+        <v>2.93933963775635</v>
       </c>
       <c r="H937" t="n">
         <v>798516</v>
@@ -27571,7 +27571,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G938" t="n">
-        <v>2.8687379360199</v>
+        <v>2.86873769760132</v>
       </c>
       <c r="H938" t="n">
         <v>558451</v>
@@ -27687,7 +27687,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>3.02579045295715</v>
+        <v>3.02579021453857</v>
       </c>
       <c r="H942" t="n">
         <v>878459</v>
@@ -27716,7 +27716,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G943" t="n">
-        <v>3.02579045295715</v>
+        <v>3.02579021453857</v>
       </c>
       <c r="H943" t="n">
         <v>717288</v>
@@ -27977,7 +27977,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G952" t="n">
-        <v>2.90475916862488</v>
+        <v>2.9047589302063</v>
       </c>
       <c r="H952" t="n">
         <v>422359</v>
@@ -28035,7 +28035,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G954" t="n">
-        <v>2.94654393196106</v>
+        <v>2.94654369354248</v>
       </c>
       <c r="H954" t="n">
         <v>399289</v>
@@ -28064,7 +28064,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G955" t="n">
-        <v>2.94654393196106</v>
+        <v>2.94654369354248</v>
       </c>
       <c r="H955" t="n">
         <v>650178</v>
@@ -28122,7 +28122,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G957" t="n">
-        <v>2.85576987266541</v>
+        <v>2.85577011108398</v>
       </c>
       <c r="H957" t="n">
         <v>405808</v>
@@ -28151,7 +28151,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G958" t="n">
-        <v>2.84136152267456</v>
+        <v>2.84136176109314</v>
       </c>
       <c r="H958" t="n">
         <v>367139</v>
@@ -28180,7 +28180,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G959" t="n">
-        <v>2.79237246513367</v>
+        <v>2.79237222671509</v>
       </c>
       <c r="H959" t="n">
         <v>343820</v>
@@ -28267,7 +28267,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G962" t="n">
-        <v>2.78804969787598</v>
+        <v>2.78804993629456</v>
       </c>
       <c r="H962" t="n">
         <v>543234</v>
@@ -28296,7 +28296,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G963" t="n">
-        <v>2.78228688240051</v>
+        <v>2.78228664398193</v>
       </c>
       <c r="H963" t="n">
         <v>329641</v>
@@ -28325,7 +28325,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G964" t="n">
-        <v>2.75346922874451</v>
+        <v>2.75346946716309</v>
       </c>
       <c r="H964" t="n">
         <v>407303</v>
@@ -28383,7 +28383,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G966" t="n">
-        <v>3.02434945106506</v>
+        <v>3.02434992790222</v>
       </c>
       <c r="H966" t="n">
         <v>586431</v>
@@ -28412,7 +28412,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G967" t="n">
-        <v>2.95230722427368</v>
+        <v>2.9523069858551</v>
       </c>
       <c r="H967" t="n">
         <v>775973</v>
@@ -28528,7 +28528,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G971" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H971" t="n">
         <v>839198</v>
@@ -28557,7 +28557,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G972" t="n">
-        <v>3.12404465675354</v>
+        <v>3.12404489517212</v>
       </c>
       <c r="H972" t="n">
         <v>1072358</v>
@@ -28615,7 +28615,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G974" t="n">
-        <v>3.09673404693604</v>
+        <v>3.09673380851746</v>
       </c>
       <c r="H974" t="n">
         <v>1705780</v>
@@ -28644,7 +28644,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>3.09521675109863</v>
+        <v>3.09521698951721</v>
       </c>
       <c r="H975" t="n">
         <v>785616</v>
@@ -28702,7 +28702,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G977" t="n">
-        <v>3.26363325119019</v>
+        <v>3.26363301277161</v>
       </c>
       <c r="H977" t="n">
         <v>1389017</v>
@@ -28731,7 +28731,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G978" t="n">
-        <v>3.36984157562256</v>
+        <v>3.36984133720398</v>
       </c>
       <c r="H978" t="n">
         <v>1837773</v>
@@ -28789,7 +28789,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G980" t="n">
-        <v>3.4472222328186</v>
+        <v>3.44722199440002</v>
       </c>
       <c r="H980" t="n">
         <v>2133114</v>
@@ -28847,7 +28847,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G982" t="n">
-        <v>3.24694323539734</v>
+        <v>3.24694347381592</v>
       </c>
       <c r="H982" t="n">
         <v>979427</v>
@@ -28905,7 +28905,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G984" t="n">
-        <v>3.12404465675354</v>
+        <v>3.12404489517212</v>
       </c>
       <c r="H984" t="n">
         <v>1636453</v>
@@ -28963,7 +28963,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G986" t="n">
-        <v>3.1255624294281</v>
+        <v>3.12556219100952</v>
       </c>
       <c r="H986" t="n">
         <v>593457</v>
@@ -29021,7 +29021,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G988" t="n">
-        <v>3.14528679847717</v>
+        <v>3.14528656005859</v>
       </c>
       <c r="H988" t="n">
         <v>927499</v>
@@ -29195,7 +29195,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G994" t="n">
-        <v>2.98900866508484</v>
+        <v>2.98900842666626</v>
       </c>
       <c r="H994" t="n">
         <v>490566</v>
@@ -29224,7 +29224,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G995" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H995" t="n">
         <v>568790</v>
@@ -29253,7 +29253,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G996" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H996" t="n">
         <v>335015</v>
@@ -29311,7 +29311,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G998" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H998" t="n">
         <v>615615</v>
@@ -29369,7 +29369,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1000" t="n">
         <v>344826</v>
@@ -29427,7 +29427,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.19080448150635</v>
+        <v>3.19080424308777</v>
       </c>
       <c r="H1002" t="n">
         <v>891668</v>
@@ -29543,7 +29543,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1006" t="n">
         <v>1293031</v>
@@ -29746,7 +29746,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.68555569648743</v>
+        <v>2.68555593490601</v>
       </c>
       <c r="H1013" t="n">
         <v>1250858</v>
@@ -29804,7 +29804,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.67038345336914</v>
+        <v>2.67038321495056</v>
       </c>
       <c r="H1015" t="n">
         <v>720352</v>
@@ -29833,7 +29833,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.63852071762085</v>
+        <v>2.63852047920227</v>
       </c>
       <c r="H1016" t="n">
         <v>694882</v>
@@ -29862,7 +29862,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.62486529350281</v>
+        <v>2.62486553192139</v>
       </c>
       <c r="H1017" t="n">
         <v>635963</v>
@@ -29891,7 +29891,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.61424446105957</v>
+        <v>2.61424469947815</v>
       </c>
       <c r="H1018" t="n">
         <v>419154</v>
@@ -29920,7 +29920,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.61576175689697</v>
+        <v>2.61576151847839</v>
       </c>
       <c r="H1019" t="n">
         <v>913484</v>
@@ -30036,7 +30036,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.75990200042725</v>
+        <v>2.75990176200867</v>
       </c>
       <c r="H1023" t="n">
         <v>902165</v>
@@ -30065,7 +30065,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.73562574386597</v>
+        <v>2.73562550544739</v>
       </c>
       <c r="H1024" t="n">
         <v>1002369</v>
@@ -30094,7 +30094,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.76597094535828</v>
+        <v>2.7659707069397</v>
       </c>
       <c r="H1025" t="n">
         <v>968819</v>
@@ -30123,7 +30123,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1026" t="n">
         <v>442819</v>
@@ -30181,7 +30181,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.87217926979065</v>
+        <v>2.87217950820923</v>
       </c>
       <c r="H1028" t="n">
         <v>925709</v>
@@ -30210,7 +30210,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.89645552635193</v>
+        <v>2.89645528793335</v>
       </c>
       <c r="H1029" t="n">
         <v>1068446</v>
@@ -30268,7 +30268,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.77052235603333</v>
+        <v>2.7705225944519</v>
       </c>
       <c r="H1031" t="n">
         <v>652124</v>
@@ -30384,7 +30384,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1035" t="n">
         <v>648955</v>
@@ -30558,7 +30558,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.67038345336914</v>
+        <v>2.67038321495056</v>
       </c>
       <c r="H1041" t="n">
         <v>686287</v>
@@ -30587,7 +30587,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.67493486404419</v>
+        <v>2.67493510246277</v>
       </c>
       <c r="H1042" t="n">
         <v>642529</v>
@@ -30703,7 +30703,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.68252158164978</v>
+        <v>2.6825213432312</v>
       </c>
       <c r="H1046" t="n">
         <v>397383</v>
@@ -30761,7 +30761,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.74624633789062</v>
+        <v>2.74624609947205</v>
       </c>
       <c r="H1048" t="n">
         <v>1072571</v>
@@ -30790,7 +30790,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.71893572807312</v>
+        <v>2.7189359664917</v>
       </c>
       <c r="H1049" t="n">
         <v>740146</v>
@@ -30819,7 +30819,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G1050" t="n">
-        <v>2.70528030395508</v>
+        <v>2.7052800655365</v>
       </c>
       <c r="H1050" t="n">
         <v>521444</v>
@@ -31254,7 +31254,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.38665509223938</v>
+        <v>2.3866548538208</v>
       </c>
       <c r="H1065" t="n">
         <v>769602</v>
@@ -31312,7 +31312,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.47769093513489</v>
+        <v>2.47769069671631</v>
       </c>
       <c r="H1067" t="n">
         <v>1137561</v>
@@ -31457,7 +31457,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.45038032531738</v>
+        <v>2.4503800868988</v>
       </c>
       <c r="H1072" t="n">
         <v>540458</v>
@@ -31486,7 +31486,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.48072528839111</v>
+        <v>2.48072552680969</v>
       </c>
       <c r="H1073" t="n">
         <v>492607</v>
@@ -31544,7 +31544,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.40637969970703</v>
+        <v>2.40637922286987</v>
       </c>
       <c r="H1075" t="n">
         <v>559400</v>
@@ -31660,7 +31660,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.38513779640198</v>
+        <v>2.3851375579834</v>
       </c>
       <c r="H1079" t="n">
         <v>526953</v>
@@ -31689,7 +31689,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.39120650291443</v>
+        <v>2.39120674133301</v>
       </c>
       <c r="H1080" t="n">
         <v>414523</v>
@@ -31834,7 +31834,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.26072216033936</v>
+        <v>2.26072239875793</v>
       </c>
       <c r="H1085" t="n">
         <v>923284</v>
@@ -31921,7 +31921,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.37603425979614</v>
+        <v>2.37603402137756</v>
       </c>
       <c r="H1088" t="n">
         <v>749371</v>
@@ -31979,7 +31979,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.34265446662903</v>
+        <v>2.34265422821045</v>
       </c>
       <c r="H1090" t="n">
         <v>571552</v>
@@ -32095,7 +32095,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.74017715454102</v>
+        <v>2.74017739295959</v>
       </c>
       <c r="H1094" t="n">
         <v>1055336</v>
@@ -32153,7 +32153,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.90555906295776</v>
+        <v>2.90555882453918</v>
       </c>
       <c r="H1096" t="n">
         <v>1911630</v>
@@ -32182,7 +32182,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.9768705368042</v>
+        <v>2.97687029838562</v>
       </c>
       <c r="H1097" t="n">
         <v>1619676</v>
@@ -32211,7 +32211,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.94045615196228</v>
+        <v>2.9404559135437</v>
       </c>
       <c r="H1098" t="n">
         <v>1870774</v>
@@ -32240,7 +32240,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.90252447128296</v>
+        <v>2.90252423286438</v>
       </c>
       <c r="H1099" t="n">
         <v>633533</v>
@@ -32269,7 +32269,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1100" t="n">
         <v>1108441</v>
@@ -32298,7 +32298,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.9783878326416</v>
+        <v>2.97838759422302</v>
       </c>
       <c r="H1101" t="n">
         <v>1438331</v>
@@ -32327,7 +32327,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.98900866508484</v>
+        <v>2.98900842666626</v>
       </c>
       <c r="H1102" t="n">
         <v>1029441</v>
@@ -32356,7 +32356,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.96169781684875</v>
+        <v>2.96169805526733</v>
       </c>
       <c r="H1103" t="n">
         <v>675063</v>
@@ -32385,7 +32385,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.93286967277527</v>
+        <v>2.93286991119385</v>
       </c>
       <c r="H1104" t="n">
         <v>393211</v>
@@ -32443,7 +32443,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1106" t="n">
         <v>1402040</v>
@@ -32472,7 +32472,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.82514381408691</v>
+        <v>2.82514405250549</v>
       </c>
       <c r="H1107" t="n">
         <v>704595</v>
@@ -32501,7 +32501,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.8266613483429</v>
+        <v>2.82666158676147</v>
       </c>
       <c r="H1108" t="n">
         <v>610729</v>
@@ -32559,7 +32559,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.8327305316925</v>
+        <v>2.83273029327393</v>
       </c>
       <c r="H1110" t="n">
         <v>390191</v>
@@ -32617,7 +32617,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1112" t="n">
         <v>343500</v>
@@ -32646,7 +32646,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.77962636947632</v>
+        <v>2.77962613105774</v>
       </c>
       <c r="H1113" t="n">
         <v>500943</v>
@@ -32762,7 +32762,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.8281786441803</v>
+        <v>2.82817840576172</v>
       </c>
       <c r="H1117" t="n">
         <v>699859</v>
@@ -32791,7 +32791,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.8327305316925</v>
+        <v>2.83273029327393</v>
       </c>
       <c r="H1118" t="n">
         <v>903623</v>
@@ -32849,7 +32849,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1120" t="n">
         <v>1351121</v>
@@ -32936,7 +32936,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.62486529350281</v>
+        <v>2.62486553192139</v>
       </c>
       <c r="H1123" t="n">
         <v>380734</v>
@@ -32994,7 +32994,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.76445317268372</v>
+        <v>2.76445341110229</v>
       </c>
       <c r="H1125" t="n">
         <v>545031</v>
@@ -33255,7 +33255,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.71438407897949</v>
+        <v>2.71438384056091</v>
       </c>
       <c r="H1134" t="n">
         <v>478250</v>
@@ -33342,7 +33342,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.71438407897949</v>
+        <v>2.71438384056091</v>
       </c>
       <c r="H1137" t="n">
         <v>373671</v>
@@ -33400,7 +33400,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.76900553703308</v>
+        <v>2.7690052986145</v>
       </c>
       <c r="H1139" t="n">
         <v>618522</v>
@@ -33545,7 +33545,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.60362339019775</v>
+        <v>2.60362362861633</v>
       </c>
       <c r="H1144" t="n">
         <v>785344</v>
@@ -33574,7 +33574,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.65065860748291</v>
+        <v>2.65065884590149</v>
       </c>
       <c r="H1145" t="n">
         <v>698067</v>
@@ -33603,7 +33603,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.65369343757629</v>
+        <v>2.65369319915771</v>
       </c>
       <c r="H1146" t="n">
         <v>533317</v>
@@ -33632,7 +33632,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.65672779083252</v>
+        <v>2.6567280292511</v>
       </c>
       <c r="H1147" t="n">
         <v>304370</v>
@@ -33661,7 +33661,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.69465970993042</v>
+        <v>2.69465947151184</v>
       </c>
       <c r="H1148" t="n">
         <v>373933</v>
@@ -33690,7 +33690,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.76141905784607</v>
+        <v>2.76141929626465</v>
       </c>
       <c r="H1149" t="n">
         <v>1012948</v>
@@ -33748,7 +33748,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.84183406829834</v>
+        <v>2.84183382987976</v>
       </c>
       <c r="H1151" t="n">
         <v>888872</v>
@@ -33806,7 +33806,7 @@
         <v>3.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.84486842155457</v>
+        <v>2.84486818313599</v>
       </c>
       <c r="H1153" t="n">
         <v>806021</v>
@@ -33835,7 +33835,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.92528319358826</v>
+        <v>2.92528343200684</v>
       </c>
       <c r="H1154" t="n">
         <v>1212331</v>
@@ -33864,7 +33864,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1155" t="n">
         <v>1086715</v>
@@ -33893,7 +33893,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.8281786441803</v>
+        <v>2.82817840576172</v>
       </c>
       <c r="H1156" t="n">
         <v>1242794</v>
@@ -33922,7 +33922,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.89038610458374</v>
+        <v>2.8903865814209</v>
       </c>
       <c r="H1157" t="n">
         <v>740083</v>
@@ -34183,7 +34183,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.02997493743896</v>
+        <v>3.02997469902039</v>
       </c>
       <c r="H1166" t="n">
         <v>761418</v>
@@ -34212,7 +34212,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.06942319869995</v>
+        <v>3.06942367553711</v>
       </c>
       <c r="H1167" t="n">
         <v>834268</v>
@@ -34241,7 +34241,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.01783633232117</v>
+        <v>3.01783657073975</v>
       </c>
       <c r="H1168" t="n">
         <v>829113</v>
@@ -34386,7 +34386,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1173" t="n">
         <v>1864436</v>
@@ -34415,7 +34415,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.3000476360321</v>
+        <v>3.30004739761353</v>
       </c>
       <c r="H1174" t="n">
         <v>1347515</v>
@@ -34444,7 +34444,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.3182544708252</v>
+        <v>3.31825470924377</v>
       </c>
       <c r="H1175" t="n">
         <v>1017835</v>
@@ -34502,7 +34502,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.25604653358459</v>
+        <v>3.25604677200317</v>
       </c>
       <c r="H1177" t="n">
         <v>784664</v>
@@ -34531,7 +34531,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.2863917350769</v>
+        <v>3.28639197349548</v>
       </c>
       <c r="H1178" t="n">
         <v>774498</v>
@@ -34589,7 +34589,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.28335762023926</v>
+        <v>3.28335738182068</v>
       </c>
       <c r="H1180" t="n">
         <v>756830</v>
@@ -34647,7 +34647,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.18321824073792</v>
+        <v>3.18321847915649</v>
       </c>
       <c r="H1182" t="n">
         <v>635502</v>
@@ -34676,7 +34676,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.17411470413208</v>
+        <v>3.17411494255066</v>
       </c>
       <c r="H1183" t="n">
         <v>795009</v>
@@ -34763,7 +34763,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.1710798740387</v>
+        <v>3.17108011245728</v>
       </c>
       <c r="H1186" t="n">
         <v>503000</v>
@@ -34792,7 +34792,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.18321824073792</v>
+        <v>3.18321847915649</v>
       </c>
       <c r="H1187" t="n">
         <v>316805</v>
@@ -34879,7 +34879,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.20142531394958</v>
+        <v>3.20142507553101</v>
       </c>
       <c r="H1190" t="n">
         <v>941312</v>
@@ -34966,7 +34966,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.1255624294281</v>
+        <v>3.12556219100952</v>
       </c>
       <c r="H1193" t="n">
         <v>683853</v>
@@ -35082,7 +35082,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1197" t="n">
         <v>940024</v>
@@ -35111,7 +35111,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.01935410499573</v>
+        <v>3.01935386657715</v>
       </c>
       <c r="H1198" t="n">
         <v>1026278</v>
@@ -35169,7 +35169,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.02542281150818</v>
+        <v>3.02542304992676</v>
       </c>
       <c r="H1200" t="n">
         <v>906035</v>
@@ -35198,7 +35198,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.00114679336548</v>
+        <v>3.0011465549469</v>
       </c>
       <c r="H1201" t="n">
         <v>1384665</v>
@@ -35227,7 +35227,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1202" t="n">
         <v>1535372</v>
@@ -35314,7 +35314,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.95107674598694</v>
+        <v>2.95107698440552</v>
       </c>
       <c r="H1205" t="n">
         <v>771951</v>
@@ -35430,7 +35430,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1209" t="n">
         <v>740997</v>
@@ -35459,7 +35459,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1210" t="n">
         <v>941538</v>
@@ -35488,7 +35488,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.94500780105591</v>
+        <v>2.94500803947449</v>
       </c>
       <c r="H1211" t="n">
         <v>993107</v>
@@ -35546,7 +35546,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.90404200553894</v>
+        <v>2.90404176712036</v>
       </c>
       <c r="H1213" t="n">
         <v>851897</v>
@@ -35604,7 +35604,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.96776700019836</v>
+        <v>2.96776676177979</v>
       </c>
       <c r="H1215" t="n">
         <v>677275</v>
@@ -35633,7 +35633,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1216" t="n">
         <v>737122</v>
@@ -35691,7 +35691,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.89645552635193</v>
+        <v>2.89645528793335</v>
       </c>
       <c r="H1218" t="n">
         <v>1266372</v>
@@ -35720,7 +35720,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1219" t="n">
         <v>2209640</v>
@@ -35749,7 +35749,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.91011095046997</v>
+        <v>2.91011071205139</v>
       </c>
       <c r="H1220" t="n">
         <v>1296831</v>
@@ -35778,7 +35778,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.89645552635193</v>
+        <v>2.89645528793335</v>
       </c>
       <c r="H1221" t="n">
         <v>1820089</v>
@@ -35807,7 +35807,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.88280010223389</v>
+        <v>2.88279986381531</v>
       </c>
       <c r="H1222" t="n">
         <v>1397317</v>
@@ -35836,7 +35836,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.84638571739197</v>
+        <v>2.84638595581055</v>
       </c>
       <c r="H1223" t="n">
         <v>715482</v>
@@ -35894,7 +35894,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.88280010223389</v>
+        <v>2.88279986381531</v>
       </c>
       <c r="H1225" t="n">
         <v>905427</v>
@@ -36097,7 +36097,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.00114679336548</v>
+        <v>3.0011465549469</v>
       </c>
       <c r="H1232" t="n">
         <v>969460</v>
@@ -36126,7 +36126,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.06638884544373</v>
+        <v>3.06638860702515</v>
       </c>
       <c r="H1233" t="n">
         <v>1932001</v>
@@ -36242,7 +36242,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.11190676689148</v>
+        <v>3.11190700531006</v>
       </c>
       <c r="H1237" t="n">
         <v>1142315</v>
@@ -36300,7 +36300,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.06790637969971</v>
+        <v>3.06790614128113</v>
       </c>
       <c r="H1239" t="n">
         <v>1908890</v>
@@ -36561,7 +36561,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.03149175643921</v>
+        <v>3.03149199485779</v>
       </c>
       <c r="H1248" t="n">
         <v>686709</v>
@@ -36590,7 +36590,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.01935410499573</v>
+        <v>3.01935386657715</v>
       </c>
       <c r="H1249" t="n">
         <v>606038</v>
@@ -36648,7 +36648,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.90707635879517</v>
+        <v>2.90707659721375</v>
       </c>
       <c r="H1251" t="n">
         <v>955454</v>
@@ -36677,7 +36677,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.88280010223389</v>
+        <v>2.88279986381531</v>
       </c>
       <c r="H1252" t="n">
         <v>1133314</v>
@@ -36706,7 +36706,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.89645552635193</v>
+        <v>2.89645528793335</v>
       </c>
       <c r="H1253" t="n">
         <v>985545</v>
@@ -36735,7 +36735,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.90404200553894</v>
+        <v>2.90404176712036</v>
       </c>
       <c r="H1254" t="n">
         <v>499348</v>
@@ -36764,7 +36764,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.93438720703125</v>
+        <v>2.93438696861267</v>
       </c>
       <c r="H1255" t="n">
         <v>440029</v>
@@ -36822,7 +36822,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.91011095046997</v>
+        <v>2.91011071205139</v>
       </c>
       <c r="H1257" t="n">
         <v>559808</v>
@@ -36851,7 +36851,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066149711609</v>
       </c>
       <c r="H1258" t="n">
         <v>731494</v>
@@ -36909,7 +36909,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.88280010223389</v>
+        <v>2.88279986381531</v>
       </c>
       <c r="H1260" t="n">
         <v>515873</v>
@@ -36967,7 +36967,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.85093760490417</v>
+        <v>2.8509373664856</v>
       </c>
       <c r="H1262" t="n">
         <v>559507</v>
@@ -37112,7 +37112,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.86155867576599</v>
+        <v>2.86155843734741</v>
       </c>
       <c r="H1267" t="n">
         <v>580063</v>
@@ -37141,7 +37141,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066149711609</v>
       </c>
       <c r="H1268" t="n">
         <v>420158</v>
@@ -37170,7 +37170,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1269" t="n">
         <v>435035</v>
@@ -37199,7 +37199,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.91011095046997</v>
+        <v>2.91011071205139</v>
       </c>
       <c r="H1270" t="n">
         <v>446474</v>
@@ -37344,7 +37344,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.98900866508484</v>
+        <v>2.98900842666626</v>
       </c>
       <c r="H1275" t="n">
         <v>337586</v>
@@ -37402,7 +37402,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1277" t="n">
         <v>2406305</v>
@@ -37489,7 +37489,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066149711609</v>
       </c>
       <c r="H1280" t="n">
         <v>380270</v>
@@ -37518,7 +37518,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066149711609</v>
       </c>
       <c r="H1281" t="n">
         <v>293660</v>
@@ -37605,7 +37605,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.88128280639648</v>
+        <v>2.88128304481506</v>
       </c>
       <c r="H1284" t="n">
         <v>547091</v>
@@ -37692,7 +37692,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1287" t="n">
         <v>751635</v>
@@ -37721,7 +37721,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1288" t="n">
         <v>603892</v>
@@ -37837,7 +37837,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1292" t="n">
         <v>333025</v>
@@ -37866,7 +37866,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1293" t="n">
         <v>277477</v>
@@ -37982,7 +37982,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.81755757331848</v>
+        <v>2.81755781173706</v>
       </c>
       <c r="H1297" t="n">
         <v>609006</v>
@@ -38127,7 +38127,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.76900553703308</v>
+        <v>2.7690052986145</v>
       </c>
       <c r="H1302" t="n">
         <v>844044</v>
@@ -38156,7 +38156,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.76900553703308</v>
+        <v>2.7690052986145</v>
       </c>
       <c r="H1303" t="n">
         <v>550632</v>
@@ -38214,7 +38214,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1305" t="n">
         <v>555953</v>
@@ -38243,7 +38243,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.78872990608215</v>
+        <v>2.78873014450073</v>
       </c>
       <c r="H1306" t="n">
         <v>1331307</v>
@@ -38272,7 +38272,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.74624633789062</v>
+        <v>2.74624609947205</v>
       </c>
       <c r="H1307" t="n">
         <v>1806388</v>
@@ -38301,7 +38301,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.83576464653015</v>
+        <v>2.83576488494873</v>
       </c>
       <c r="H1308" t="n">
         <v>1430517</v>
@@ -38475,7 +38475,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.97231841087341</v>
+        <v>2.97231864929199</v>
       </c>
       <c r="H1314" t="n">
         <v>400767</v>
@@ -38533,7 +38533,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.99507761001587</v>
+        <v>2.99507713317871</v>
       </c>
       <c r="H1316" t="n">
         <v>973746</v>
@@ -38707,7 +38707,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.02997493743896</v>
+        <v>3.02997469902039</v>
       </c>
       <c r="H1322" t="n">
         <v>728288</v>
@@ -38736,7 +38736,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.04666423797607</v>
+        <v>3.04666447639465</v>
       </c>
       <c r="H1323" t="n">
         <v>376389</v>
@@ -38794,7 +38794,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.06790637969971</v>
+        <v>3.06790614128113</v>
       </c>
       <c r="H1325" t="n">
         <v>379317</v>
@@ -38823,7 +38823,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.02997493743896</v>
+        <v>3.02997469902039</v>
       </c>
       <c r="H1326" t="n">
         <v>245581</v>
@@ -38852,7 +38852,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.01480174064636</v>
+        <v>3.01480197906494</v>
       </c>
       <c r="H1327" t="n">
         <v>237191</v>
@@ -38910,7 +38910,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1329" t="n">
         <v>431327</v>
@@ -38939,7 +38939,7 @@
         <v>4</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.03452610969543</v>
+        <v>3.03452634811401</v>
       </c>
       <c r="H1330" t="n">
         <v>342826</v>
@@ -38968,7 +38968,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.03300905227661</v>
+        <v>3.03300881385803</v>
       </c>
       <c r="H1331" t="n">
         <v>337172</v>
@@ -38997,7 +38997,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.99962949752808</v>
+        <v>2.9996292591095</v>
       </c>
       <c r="H1332" t="n">
         <v>451688</v>
@@ -39026,7 +39026,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.97990465164185</v>
+        <v>2.97990489006042</v>
       </c>
       <c r="H1333" t="n">
         <v>233108</v>
@@ -39171,7 +39171,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.91011095046997</v>
+        <v>2.91011071205139</v>
       </c>
       <c r="H1338" t="n">
         <v>445579</v>
@@ -39345,7 +39345,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.2378396987915</v>
+        <v>3.23783993721008</v>
       </c>
       <c r="H1344" t="n">
         <v>1846837</v>
@@ -39374,7 +39374,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.21356344223022</v>
+        <v>3.2135636806488</v>
       </c>
       <c r="H1345" t="n">
         <v>1086205</v>
@@ -39461,7 +39461,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.15439009666443</v>
+        <v>3.15439033508301</v>
       </c>
       <c r="H1348" t="n">
         <v>596551</v>
@@ -39519,7 +39519,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.19990825653076</v>
+        <v>3.19990801811218</v>
       </c>
       <c r="H1350" t="n">
         <v>882238</v>
@@ -39548,7 +39548,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.19080448150635</v>
+        <v>3.19080424308777</v>
       </c>
       <c r="H1351" t="n">
         <v>684309</v>
@@ -39577,7 +39577,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.1270797252655</v>
+        <v>3.12707948684692</v>
       </c>
       <c r="H1352" t="n">
         <v>748528</v>
@@ -39606,7 +39606,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1353" t="n">
         <v>563496</v>
@@ -39635,7 +39635,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.99659466743469</v>
+        <v>2.99659514427185</v>
       </c>
       <c r="H1354" t="n">
         <v>805425</v>
@@ -39664,7 +39664,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.95107674598694</v>
+        <v>2.95107698440552</v>
       </c>
       <c r="H1355" t="n">
         <v>1271455</v>
@@ -39693,7 +39693,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.94652533531189</v>
+        <v>2.94652509689331</v>
       </c>
       <c r="H1356" t="n">
         <v>628394</v>
@@ -39751,7 +39751,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.96321487426758</v>
+        <v>2.963214635849</v>
       </c>
       <c r="H1358" t="n">
         <v>302352</v>
@@ -39780,7 +39780,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.76141905784607</v>
+        <v>2.76141929626465</v>
       </c>
       <c r="H1359" t="n">
         <v>1809573</v>
@@ -39867,7 +39867,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.84638571739197</v>
+        <v>2.84638595581055</v>
       </c>
       <c r="H1362" t="n">
         <v>704138</v>
@@ -39896,7 +39896,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1363" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1363" t="n">
         <v>709578</v>
@@ -40215,7 +40215,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.8919038772583</v>
+        <v>2.89190363883972</v>
       </c>
       <c r="H1374" t="n">
         <v>317269</v>
@@ -40244,7 +40244,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.86155867576599</v>
+        <v>2.86155843734741</v>
       </c>
       <c r="H1375" t="n">
         <v>434192</v>
@@ -40331,7 +40331,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1378" t="n">
-        <v>2.95107674598694</v>
+        <v>2.95107698440552</v>
       </c>
       <c r="H1378" t="n">
         <v>208238</v>
@@ -40389,7 +40389,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1380" t="n">
         <v>409979</v>
@@ -40418,7 +40418,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.97231841087341</v>
+        <v>2.97231864929199</v>
       </c>
       <c r="H1381" t="n">
         <v>360588</v>
@@ -40447,7 +40447,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.98142242431641</v>
+        <v>2.98142218589783</v>
       </c>
       <c r="H1382" t="n">
         <v>344017</v>
@@ -40650,7 +40650,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.1255624294281</v>
+        <v>3.12556219100952</v>
       </c>
       <c r="H1389" t="n">
         <v>563771</v>
@@ -40766,7 +40766,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1393" t="n">
         <v>343828</v>
@@ -40911,7 +40911,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.9753532409668</v>
+        <v>2.97535300254822</v>
       </c>
       <c r="H1398" t="n">
         <v>586772</v>
@@ -40998,7 +40998,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.08459639549255</v>
+        <v>3.08459615707397</v>
       </c>
       <c r="H1401" t="n">
         <v>359292</v>
@@ -41085,7 +41085,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.15590763092041</v>
+        <v>3.15590715408325</v>
       </c>
       <c r="H1404" t="n">
         <v>368125</v>
@@ -41230,7 +41230,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.02997493743896</v>
+        <v>3.02997469902039</v>
       </c>
       <c r="H1409" t="n">
         <v>664173</v>
@@ -41259,7 +41259,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.15590763092041</v>
+        <v>3.15590715408325</v>
       </c>
       <c r="H1410" t="n">
         <v>993535</v>
@@ -41288,7 +41288,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.23935651779175</v>
+        <v>3.23935675621033</v>
       </c>
       <c r="H1411" t="n">
         <v>1097424</v>
@@ -41317,7 +41317,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1412" t="n">
         <v>433525</v>
@@ -41404,7 +41404,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.15439009666443</v>
+        <v>3.15439033508301</v>
       </c>
       <c r="H1415" t="n">
         <v>333250</v>
@@ -41433,7 +41433,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1483211517334</v>
+        <v>3.14832139015198</v>
       </c>
       <c r="H1416" t="n">
         <v>319129</v>
@@ -41462,7 +41462,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.1270797252655</v>
+        <v>3.12707948684692</v>
       </c>
       <c r="H1417" t="n">
         <v>324389</v>
@@ -41491,7 +41491,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.07852697372437</v>
+        <v>3.07852721214294</v>
       </c>
       <c r="H1418" t="n">
         <v>298915</v>
@@ -41752,7 +41752,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.77507424354553</v>
+        <v>2.77507448196411</v>
       </c>
       <c r="H1427" t="n">
         <v>790685</v>
@@ -41781,7 +41781,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.68555569648743</v>
+        <v>2.68555593490601</v>
       </c>
       <c r="H1428" t="n">
         <v>1521754</v>
@@ -41810,7 +41810,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.78266048431396</v>
+        <v>2.78266096115112</v>
       </c>
       <c r="H1429" t="n">
         <v>1054096</v>
@@ -41897,7 +41897,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.94500780105591</v>
+        <v>2.94500803947449</v>
       </c>
       <c r="H1432" t="n">
         <v>631432</v>
@@ -41926,7 +41926,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.9768705368042</v>
+        <v>2.97687029838562</v>
       </c>
       <c r="H1433" t="n">
         <v>454366</v>
@@ -41984,7 +41984,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H1435" t="n">
         <v>593290</v>
@@ -42013,7 +42013,7 @@
         <v>4</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.03452610969543</v>
+        <v>3.03452634811401</v>
       </c>
       <c r="H1436" t="n">
         <v>340027</v>
@@ -42042,7 +42042,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.07397556304932</v>
+        <v>3.07397532463074</v>
       </c>
       <c r="H1437" t="n">
         <v>576360</v>
@@ -42071,7 +42071,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.01480174064636</v>
+        <v>3.01480197906494</v>
       </c>
       <c r="H1438" t="n">
         <v>336601</v>
@@ -42100,7 +42100,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576825141907</v>
       </c>
       <c r="H1439" t="n">
         <v>331126</v>
@@ -42129,7 +42129,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.04818201065063</v>
+        <v>3.04818177223206</v>
       </c>
       <c r="H1440" t="n">
         <v>387125</v>
@@ -42158,7 +42158,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576825141907</v>
       </c>
       <c r="H1441" t="n">
         <v>366787</v>
@@ -42245,7 +42245,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.13011360168457</v>
+        <v>3.13011407852173</v>
       </c>
       <c r="H1444" t="n">
         <v>542482</v>
@@ -42361,7 +42361,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.24694323539734</v>
+        <v>3.24694347381592</v>
       </c>
       <c r="H1448" t="n">
         <v>602536</v>
@@ -42390,7 +42390,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.24846053123474</v>
+        <v>3.24846076965332</v>
       </c>
       <c r="H1449" t="n">
         <v>506516</v>
@@ -42535,7 +42535,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.35770344734192</v>
+        <v>3.3577036857605</v>
       </c>
       <c r="H1454" t="n">
         <v>366607</v>
@@ -42564,7 +42564,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.41535949707031</v>
+        <v>3.41535925865173</v>
       </c>
       <c r="H1455" t="n">
         <v>502197</v>
@@ -42593,7 +42593,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.55646514892578</v>
+        <v>3.5564649105072</v>
       </c>
       <c r="H1456" t="n">
         <v>1120632</v>
@@ -42622,7 +42622,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.56556844711304</v>
+        <v>3.56556797027588</v>
       </c>
       <c r="H1457" t="n">
         <v>669265</v>
@@ -42651,7 +42651,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.56556844711304</v>
+        <v>3.56556797027588</v>
       </c>
       <c r="H1458" t="n">
         <v>425019</v>
@@ -42680,7 +42680,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.41991138458252</v>
+        <v>3.41991090774536</v>
       </c>
       <c r="H1459" t="n">
         <v>599042</v>
@@ -42709,7 +42709,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.36225533485413</v>
+        <v>3.36225509643555</v>
       </c>
       <c r="H1460" t="n">
         <v>1645239</v>
@@ -42854,7 +42854,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.34253120422363</v>
+        <v>3.34253096580505</v>
       </c>
       <c r="H1465" t="n">
         <v>331814</v>
@@ -42883,7 +42883,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.31066823005676</v>
+        <v>3.31066799163818</v>
       </c>
       <c r="H1466" t="n">
         <v>319646</v>
@@ -42912,7 +42912,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.37439346313477</v>
+        <v>3.37439298629761</v>
       </c>
       <c r="H1467" t="n">
         <v>351083</v>
@@ -42941,7 +42941,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.35466885566711</v>
+        <v>3.35466909408569</v>
       </c>
       <c r="H1468" t="n">
         <v>357288</v>
@@ -42970,7 +42970,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.36984157562256</v>
+        <v>3.36984133720398</v>
       </c>
       <c r="H1469" t="n">
         <v>293364</v>
@@ -43057,7 +43057,7 @@
         <v>4.25</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.22418427467346</v>
+        <v>3.22418403625488</v>
       </c>
       <c r="H1472" t="n">
         <v>288199</v>
@@ -43086,7 +43086,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.29094362258911</v>
+        <v>3.29094386100769</v>
       </c>
       <c r="H1473" t="n">
         <v>390507</v>
@@ -43115,7 +43115,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.15742492675781</v>
+        <v>3.15742468833923</v>
       </c>
       <c r="H1474" t="n">
         <v>569682</v>
@@ -43173,7 +43173,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.21356344223022</v>
+        <v>3.2135636806488</v>
       </c>
       <c r="H1476" t="n">
         <v>489346</v>
@@ -43231,7 +43231,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.26666784286499</v>
+        <v>3.26666808128357</v>
       </c>
       <c r="H1478" t="n">
         <v>317207</v>
@@ -43260,7 +43260,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.25604653358459</v>
+        <v>3.25604677200317</v>
       </c>
       <c r="H1479" t="n">
         <v>389274</v>
@@ -43347,7 +43347,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.21356344223022</v>
+        <v>3.2135636806488</v>
       </c>
       <c r="H1482" t="n">
         <v>147618</v>
@@ -43376,7 +43376,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.23177099227905</v>
+        <v>3.23177075386047</v>
       </c>
       <c r="H1483" t="n">
         <v>228707</v>
@@ -43405,7 +43405,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.23935651779175</v>
+        <v>3.23935675621033</v>
       </c>
       <c r="H1484" t="n">
         <v>261437</v>
@@ -43463,7 +43463,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.3000476360321</v>
+        <v>3.30004739761353</v>
       </c>
       <c r="H1486" t="n">
         <v>471587</v>
@@ -43492,7 +43492,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.26666784286499</v>
+        <v>3.26666808128357</v>
       </c>
       <c r="H1487" t="n">
         <v>389756</v>
@@ -43579,7 +43579,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1490" t="n">
         <v>164422</v>
@@ -43637,7 +43637,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.26211595535278</v>
+        <v>3.2621157169342</v>
       </c>
       <c r="H1492" t="n">
         <v>310794</v>
@@ -43666,7 +43666,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1493" t="n">
         <v>230814</v>
@@ -43724,7 +43724,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.06638884544373</v>
+        <v>3.06638860702515</v>
       </c>
       <c r="H1495" t="n">
         <v>608019</v>
@@ -43782,7 +43782,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.93893885612488</v>
+        <v>2.93893909454346</v>
       </c>
       <c r="H1497" t="n">
         <v>394520</v>
@@ -43869,7 +43869,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576825141907</v>
       </c>
       <c r="H1500" t="n">
         <v>328315</v>
@@ -43956,7 +43956,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.05121612548828</v>
+        <v>3.05121636390686</v>
       </c>
       <c r="H1503" t="n">
         <v>473568</v>
@@ -44101,7 +44101,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.07852697372437</v>
+        <v>3.07852721214294</v>
       </c>
       <c r="H1508" t="n">
         <v>181143</v>
@@ -44159,7 +44159,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.02542281150818</v>
+        <v>3.02542304992676</v>
       </c>
       <c r="H1510" t="n">
         <v>125926</v>
@@ -44246,7 +44246,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.97080135345459</v>
+        <v>2.97080159187317</v>
       </c>
       <c r="H1513" t="n">
         <v>181894</v>
@@ -44275,7 +44275,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.01480174064636</v>
+        <v>3.01480197906494</v>
       </c>
       <c r="H1514" t="n">
         <v>243119</v>
@@ -44304,7 +44304,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.03300905227661</v>
+        <v>3.03300881385803</v>
       </c>
       <c r="H1515" t="n">
         <v>189223</v>
@@ -44333,7 +44333,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.02694010734558</v>
+        <v>3.026939868927</v>
       </c>
       <c r="H1516" t="n">
         <v>124790</v>
@@ -44391,7 +44391,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H1518" t="n">
         <v>105502</v>
@@ -44420,7 +44420,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.05273365974426</v>
+        <v>3.05273389816284</v>
       </c>
       <c r="H1519" t="n">
         <v>220405</v>
@@ -44507,7 +44507,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.19383907318115</v>
+        <v>3.19383931159973</v>
       </c>
       <c r="H1522" t="n">
         <v>253011</v>
@@ -44594,7 +44594,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.19990825653076</v>
+        <v>3.19990801811218</v>
       </c>
       <c r="H1525" t="n">
         <v>308905</v>
@@ -44623,7 +44623,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1526" t="n">
         <v>227220</v>
@@ -44681,7 +44681,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.16956281661987</v>
+        <v>3.16956257820129</v>
       </c>
       <c r="H1528" t="n">
         <v>115488</v>
@@ -44768,7 +44768,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.22570133209229</v>
+        <v>3.22570157051086</v>
       </c>
       <c r="H1531" t="n">
         <v>181014</v>
@@ -44826,7 +44826,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.3197717666626</v>
+        <v>3.31977200508118</v>
       </c>
       <c r="H1533" t="n">
         <v>379962</v>
@@ -44913,7 +44913,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.28790950775146</v>
+        <v>3.28790926933289</v>
       </c>
       <c r="H1536" t="n">
         <v>422360</v>
@@ -44942,7 +44942,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.23177099227905</v>
+        <v>3.23177075386047</v>
       </c>
       <c r="H1537" t="n">
         <v>343058</v>
@@ -44971,7 +44971,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.23935651779175</v>
+        <v>3.23935675621033</v>
       </c>
       <c r="H1538" t="n">
         <v>123708</v>
@@ -45029,7 +45029,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.22570133209229</v>
+        <v>3.22570157051086</v>
       </c>
       <c r="H1540" t="n">
         <v>79916</v>
@@ -45058,7 +45058,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.2378396987915</v>
+        <v>3.23783993721008</v>
       </c>
       <c r="H1541" t="n">
         <v>181142</v>
@@ -45087,7 +45087,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1542" t="n">
         <v>119327</v>
@@ -45116,7 +45116,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1543" t="n">
         <v>44780</v>
@@ -45145,7 +45145,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.20901155471802</v>
+        <v>3.2090117931366</v>
       </c>
       <c r="H1544" t="n">
         <v>146185</v>
@@ -45174,7 +45174,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.17866635322571</v>
+        <v>3.17866611480713</v>
       </c>
       <c r="H1545" t="n">
         <v>211170</v>
@@ -45203,7 +45203,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.1710798740387</v>
+        <v>3.17108011245728</v>
       </c>
       <c r="H1546" t="n">
         <v>128014</v>
@@ -45261,7 +45261,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.20749449729919</v>
+        <v>3.20749425888062</v>
       </c>
       <c r="H1548" t="n">
         <v>102198</v>
@@ -45319,7 +45319,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11190676689148</v>
+        <v>3.11190700531006</v>
       </c>
       <c r="H1550" t="n">
         <v>104079</v>
@@ -45348,7 +45348,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.1255624294281</v>
+        <v>3.12556219100952</v>
       </c>
       <c r="H1551" t="n">
         <v>95083</v>
@@ -45406,7 +45406,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.0421130657196</v>
+        <v>3.04211282730103</v>
       </c>
       <c r="H1553" t="n">
         <v>246704</v>
@@ -45464,7 +45464,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.04818201065063</v>
+        <v>3.04818177223206</v>
       </c>
       <c r="H1555" t="n">
         <v>65866</v>
@@ -45493,7 +45493,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.05425095558167</v>
+        <v>3.05425071716309</v>
       </c>
       <c r="H1556" t="n">
         <v>111723</v>
@@ -45522,7 +45522,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.07397556304932</v>
+        <v>3.07397532463074</v>
       </c>
       <c r="H1557" t="n">
         <v>162365</v>
@@ -45551,7 +45551,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1558" t="n">
         <v>185411</v>
@@ -45638,7 +45638,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.17411470413208</v>
+        <v>3.17411494255066</v>
       </c>
       <c r="H1561" t="n">
         <v>145308</v>
@@ -46044,7 +46044,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.84638571739197</v>
+        <v>2.84638595581055</v>
       </c>
       <c r="H1575" t="n">
         <v>199190</v>
@@ -46305,7 +46305,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.76141905784607</v>
+        <v>2.76141929626465</v>
       </c>
       <c r="H1584" t="n">
         <v>193202</v>
@@ -46392,7 +46392,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.83576464653015</v>
+        <v>2.83576488494873</v>
       </c>
       <c r="H1587" t="n">
         <v>208957</v>
@@ -46421,7 +46421,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.8266613483429</v>
+        <v>2.82666158676147</v>
       </c>
       <c r="H1588" t="n">
         <v>170544</v>
@@ -46508,7 +46508,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.94342279434204</v>
+        <v>2.94342303276062</v>
       </c>
       <c r="H1591" t="n">
         <v>336971</v>
@@ -46566,7 +46566,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.00751209259033</v>
+        <v>3.00751185417175</v>
       </c>
       <c r="H1593" t="n">
         <v>386716</v>
@@ -46595,7 +46595,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.01063847541809</v>
+        <v>3.01063823699951</v>
       </c>
       <c r="H1594" t="n">
         <v>176564</v>
@@ -46624,7 +46624,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.05596995353699</v>
+        <v>3.05596971511841</v>
       </c>
       <c r="H1595" t="n">
         <v>313165</v>
@@ -46711,7 +46711,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.03095960617065</v>
+        <v>3.03095936775208</v>
       </c>
       <c r="H1598" t="n">
         <v>193796</v>
@@ -46740,7 +46740,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.9637439250946</v>
+        <v>2.96374368667603</v>
       </c>
       <c r="H1599" t="n">
         <v>447180</v>
@@ -46827,7 +46827,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.982501745224</v>
+        <v>2.98250150680542</v>
       </c>
       <c r="H1602" t="n">
         <v>358466</v>
@@ -46856,7 +46856,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.05753302574158</v>
+        <v>3.057532787323</v>
       </c>
       <c r="H1603" t="n">
         <v>330448</v>
@@ -46885,7 +46885,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.05596995353699</v>
+        <v>3.05596971511841</v>
       </c>
       <c r="H1604" t="n">
         <v>322041</v>
@@ -46914,7 +46914,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.04815435409546</v>
+        <v>3.04815411567688</v>
       </c>
       <c r="H1605" t="n">
         <v>199394</v>
@@ -46943,7 +46943,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.14194321632385</v>
+        <v>3.14194345474243</v>
       </c>
       <c r="H1606" t="n">
         <v>1027100</v>
@@ -46972,7 +46972,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.17164325714111</v>
+        <v>3.17164349555969</v>
       </c>
       <c r="H1607" t="n">
         <v>912843</v>
@@ -47001,7 +47001,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.27637505531311</v>
+        <v>3.27637481689453</v>
       </c>
       <c r="H1608" t="n">
         <v>1344939</v>
@@ -47059,7 +47059,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.25605392456055</v>
+        <v>3.25605368614197</v>
       </c>
       <c r="H1610" t="n">
         <v>259772</v>
@@ -47204,7 +47204,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.29044318199158</v>
+        <v>3.29044342041016</v>
       </c>
       <c r="H1615" t="n">
         <v>369273</v>
@@ -47233,7 +47233,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.33264851570129</v>
+        <v>3.33264875411987</v>
       </c>
       <c r="H1616" t="n">
         <v>184195</v>
@@ -47291,7 +47291,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.36078548431396</v>
+        <v>3.36078524589539</v>
       </c>
       <c r="H1618" t="n">
         <v>449061</v>
@@ -47320,7 +47320,7 @@
         <v>4.31400012969971</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.37172722816467</v>
+        <v>3.37172746658325</v>
       </c>
       <c r="H1619" t="n">
         <v>421861</v>
@@ -47639,7 +47639,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.15601205825806</v>
+        <v>3.15601181983948</v>
       </c>
       <c r="H1630" t="n">
         <v>259444</v>
@@ -47697,7 +47697,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.14819598197937</v>
+        <v>3.14819622039795</v>
       </c>
       <c r="H1632" t="n">
         <v>228241</v>
@@ -47813,7 +47813,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.09817504882812</v>
+        <v>3.0981752872467</v>
       </c>
       <c r="H1636" t="n">
         <v>122218</v>
@@ -47929,7 +47929,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.16695427894592</v>
+        <v>3.16695404052734</v>
       </c>
       <c r="H1640" t="n">
         <v>251186</v>
@@ -47958,7 +47958,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.16851735115051</v>
+        <v>3.16851711273193</v>
       </c>
       <c r="H1641" t="n">
         <v>107139</v>
@@ -48016,7 +48016,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.19509053230286</v>
+        <v>3.19509077072144</v>
       </c>
       <c r="H1643" t="n">
         <v>90490</v>
@@ -48074,7 +48074,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.29044318199158</v>
+        <v>3.29044342041016</v>
       </c>
       <c r="H1645" t="n">
         <v>138844</v>
@@ -48103,7 +48103,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.27481198310852</v>
+        <v>3.27481174468994</v>
       </c>
       <c r="H1646" t="n">
         <v>305247</v>
@@ -48190,7 +48190,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.2716851234436</v>
+        <v>3.27168536186218</v>
       </c>
       <c r="H1649" t="n">
         <v>136089</v>
@@ -48393,7 +48393,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.38423275947571</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1656" t="n">
         <v>233036</v>
@@ -48538,7 +48538,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.34359073638916</v>
+        <v>3.34359049797058</v>
       </c>
       <c r="H1661" t="n">
         <v>255129</v>
@@ -48654,7 +48654,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.37485337257385</v>
+        <v>3.37485361099243</v>
       </c>
       <c r="H1665" t="n">
         <v>211448</v>
@@ -48683,7 +48683,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.37798023223877</v>
+        <v>3.37797999382019</v>
       </c>
       <c r="H1666" t="n">
         <v>232444</v>
@@ -48712,7 +48712,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.38423275947571</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1667" t="n">
         <v>164728</v>
@@ -48828,7 +48828,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G1671" t="n">
-        <v>3.25605392456055</v>
+        <v>3.25605368614197</v>
       </c>
       <c r="H1671" t="n">
         <v>245443</v>
@@ -48857,7 +48857,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1672" t="n">
-        <v>3.20446968078613</v>
+        <v>3.20446944236755</v>
       </c>
       <c r="H1672" t="n">
         <v>412616</v>
@@ -48886,7 +48886,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1673" t="n">
-        <v>3.19196438789368</v>
+        <v>3.19196462631226</v>
       </c>
       <c r="H1673" t="n">
         <v>401389</v>
@@ -48944,7 +48944,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.14663290977478</v>
+        <v>3.14663314819336</v>
       </c>
       <c r="H1675" t="n">
         <v>113108</v>
@@ -49002,7 +49002,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.20915937423706</v>
+        <v>3.20915913581848</v>
       </c>
       <c r="H1677" t="n">
         <v>186125</v>
@@ -49147,7 +49147,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.24511170387268</v>
+        <v>3.24511194229126</v>
       </c>
       <c r="H1682" t="n">
         <v>103025</v>
@@ -49176,7 +49176,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.2716851234436</v>
+        <v>3.27168536186218</v>
       </c>
       <c r="H1683" t="n">
         <v>236129</v>
@@ -49205,7 +49205,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.27481198310852</v>
+        <v>3.27481174468994</v>
       </c>
       <c r="H1684" t="n">
         <v>150462</v>
@@ -49321,7 +49321,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.22479057312012</v>
+        <v>3.2247908115387</v>
       </c>
       <c r="H1688" t="n">
         <v>161789</v>
@@ -49350,7 +49350,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.15757513046265</v>
+        <v>3.15757489204407</v>
       </c>
       <c r="H1689" t="n">
         <v>357386</v>
@@ -49524,7 +49524,7 @@
         <v>4</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.12631177902222</v>
+        <v>3.1263120174408</v>
       </c>
       <c r="H1695" t="n">
         <v>378934</v>
@@ -49727,7 +49727,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.00125956535339</v>
+        <v>3.00125932693481</v>
       </c>
       <c r="H1702" t="n">
         <v>623855</v>
@@ -49843,7 +49843,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.00907516479492</v>
+        <v>3.00907492637634</v>
       </c>
       <c r="H1706" t="n">
         <v>223346</v>
@@ -49959,7 +49959,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.21697497367859</v>
+        <v>3.21697521209717</v>
       </c>
       <c r="H1710" t="n">
         <v>573601</v>
@@ -50017,7 +50017,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.21228575706482</v>
+        <v>3.21228551864624</v>
       </c>
       <c r="H1712" t="n">
         <v>219277</v>
@@ -50046,7 +50046,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1713" t="n">
-        <v>3.20446968078613</v>
+        <v>3.20446944236755</v>
       </c>
       <c r="H1713" t="n">
         <v>455560</v>
@@ -50104,7 +50104,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.21228575706482</v>
+        <v>3.21228551864624</v>
       </c>
       <c r="H1715" t="n">
         <v>419873</v>
@@ -50133,7 +50133,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.24354863166809</v>
+        <v>3.24354887008667</v>
       </c>
       <c r="H1716" t="n">
         <v>355918</v>
@@ -50568,7 +50568,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.1732063293457</v>
+        <v>3.17320656776428</v>
       </c>
       <c r="H1731" t="n">
         <v>384659</v>
@@ -50626,7 +50626,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.20446968078613</v>
+        <v>3.20446944236755</v>
       </c>
       <c r="H1733" t="n">
         <v>272832</v>
@@ -50655,7 +50655,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.21072220802307</v>
+        <v>3.21072196960449</v>
       </c>
       <c r="H1734" t="n">
         <v>340017</v>
@@ -50713,7 +50713,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.19196438789368</v>
+        <v>3.19196462631226</v>
       </c>
       <c r="H1736" t="n">
         <v>291642</v>
@@ -50829,7 +50829,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.16382741928101</v>
+        <v>3.16382765769958</v>
       </c>
       <c r="H1740" t="n">
         <v>300213</v>
@@ -50916,7 +50916,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08723282814026</v>
+        <v>3.08723306655884</v>
       </c>
       <c r="H1743" t="n">
         <v>413231</v>
@@ -50974,7 +50974,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.17164325714111</v>
+        <v>3.17164349555969</v>
       </c>
       <c r="H1745" t="n">
         <v>119164</v>
@@ -51003,7 +51003,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.12787485122681</v>
+        <v>3.12787508964539</v>
       </c>
       <c r="H1746" t="n">
         <v>485176</v>
@@ -51061,7 +51061,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.09661173820496</v>
+        <v>3.09661197662354</v>
       </c>
       <c r="H1748" t="n">
         <v>260833</v>
@@ -51090,7 +51090,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.10442757606506</v>
+        <v>3.10442733764648</v>
       </c>
       <c r="H1749" t="n">
         <v>336964</v>
@@ -51148,7 +51148,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.09817504882812</v>
+        <v>3.0981752872467</v>
       </c>
       <c r="H1751" t="n">
         <v>141683</v>
@@ -51177,7 +51177,7 @@
         <v>4</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.12631177902222</v>
+        <v>3.1263120174408</v>
       </c>
       <c r="H1752" t="n">
         <v>280969</v>
@@ -51235,7 +51235,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1754" t="n">
-        <v>3.15913820266724</v>
+        <v>3.15913796424866</v>
       </c>
       <c r="H1754" t="n">
         <v>410306</v>
@@ -51264,7 +51264,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.15601205825806</v>
+        <v>3.15601181983948</v>
       </c>
       <c r="H1755" t="n">
         <v>391398</v>
@@ -51351,7 +51351,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.05753302574158</v>
+        <v>3.057532787323</v>
       </c>
       <c r="H1758" t="n">
         <v>466472</v>
@@ -51467,7 +51467,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.04346466064453</v>
+        <v>3.04346489906311</v>
       </c>
       <c r="H1762" t="n">
         <v>262411</v>
@@ -51525,7 +51525,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.05596995353699</v>
+        <v>3.05596971511841</v>
       </c>
       <c r="H1764" t="n">
         <v>121885</v>
@@ -51583,7 +51583,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691193580627</v>
       </c>
       <c r="H1766" t="n">
         <v>179289</v>
@@ -51757,7 +51757,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.03095960617065</v>
+        <v>3.03095936775208</v>
       </c>
       <c r="H1772" t="n">
         <v>331989</v>
@@ -51786,7 +51786,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.04033827781677</v>
+        <v>3.04033851623535</v>
       </c>
       <c r="H1773" t="n">
         <v>361099</v>
@@ -51960,7 +51960,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.04190135002136</v>
+        <v>3.04190182685852</v>
       </c>
       <c r="H1779" t="n">
         <v>280743</v>
@@ -51989,7 +51989,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.03095960617065</v>
+        <v>3.03095936775208</v>
       </c>
       <c r="H1780" t="n">
         <v>343443</v>
@@ -52076,7 +52076,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.04346466064453</v>
+        <v>3.04346489906311</v>
       </c>
       <c r="H1783" t="n">
         <v>520467</v>
@@ -52221,7 +52221,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.00907516479492</v>
+        <v>3.00907492637634</v>
       </c>
       <c r="H1788" t="n">
         <v>280259</v>
@@ -52279,7 +52279,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.91372275352478</v>
+        <v>2.9137225151062</v>
       </c>
       <c r="H1790" t="n">
         <v>835243</v>
@@ -52308,7 +52308,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.90278029441833</v>
+        <v>2.90278053283691</v>
       </c>
       <c r="H1791" t="n">
         <v>397165</v>
@@ -52337,7 +52337,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.88089632987976</v>
+        <v>2.88089656829834</v>
       </c>
       <c r="H1792" t="n">
         <v>398855</v>
@@ -52395,7 +52395,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.91059637069702</v>
+        <v>2.91059613227844</v>
       </c>
       <c r="H1794" t="n">
         <v>339129</v>
@@ -52482,7 +52482,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.85275983810425</v>
+        <v>2.85275959968567</v>
       </c>
       <c r="H1797" t="n">
         <v>348055</v>
@@ -52598,7 +52598,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.85744881629944</v>
+        <v>2.85744905471802</v>
       </c>
       <c r="H1801" t="n">
         <v>234603</v>
@@ -52627,7 +52627,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.85744881629944</v>
+        <v>2.85744905471802</v>
       </c>
       <c r="H1802" t="n">
         <v>217632</v>
@@ -52743,7 +52743,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.92466473579407</v>
+        <v>2.92466497421265</v>
       </c>
       <c r="H1806" t="n">
         <v>324520</v>
@@ -52801,7 +52801,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.91059637069702</v>
+        <v>2.91059613227844</v>
       </c>
       <c r="H1808" t="n">
         <v>514235</v>
@@ -52859,7 +52859,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.89496493339539</v>
+        <v>2.89496517181396</v>
       </c>
       <c r="H1810" t="n">
         <v>137114</v>
@@ -53004,7 +53004,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.89496493339539</v>
+        <v>2.89496517181396</v>
       </c>
       <c r="H1815" t="n">
         <v>264713</v>
@@ -53149,7 +53149,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.82305955886841</v>
+        <v>2.82305979728699</v>
       </c>
       <c r="H1820" t="n">
         <v>491195</v>
@@ -53207,7 +53207,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.83556485176086</v>
+        <v>2.83556509017944</v>
       </c>
       <c r="H1822" t="n">
         <v>326021</v>
@@ -53265,7 +53265,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.80586504936218</v>
+        <v>2.8058648109436</v>
       </c>
       <c r="H1824" t="n">
         <v>262774</v>
@@ -53323,7 +53323,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68393850326538</v>
+        <v>2.68393874168396</v>
       </c>
       <c r="H1826" t="n">
         <v>842330</v>
@@ -53381,7 +53381,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.72301745414734</v>
+        <v>2.72301769256592</v>
       </c>
       <c r="H1828" t="n">
         <v>487170</v>
@@ -53410,7 +53410,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.73864912986755</v>
+        <v>2.73864936828613</v>
       </c>
       <c r="H1829" t="n">
         <v>946979</v>
@@ -53526,7 +53526,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.64017033576965</v>
+        <v>2.64017057418823</v>
       </c>
       <c r="H1833" t="n">
         <v>302854</v>
@@ -53642,7 +53642,7 @@
         <v>3.30200004577637</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.58077049255371</v>
+        <v>2.58077073097229</v>
       </c>
       <c r="H1837" t="n">
         <v>838954</v>
@@ -53845,7 +53845,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.48229169845581</v>
+        <v>2.48229193687439</v>
       </c>
       <c r="H1844" t="n">
         <v>1054318</v>
@@ -53903,7 +53903,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.50287127494812</v>
+        <v>2.50287103652954</v>
       </c>
       <c r="H1846" t="n">
         <v>602614</v>
@@ -53932,7 +53932,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.53453207015991</v>
+        <v>2.53453230857849</v>
       </c>
       <c r="H1847" t="n">
         <v>707112</v>
@@ -54048,7 +54048,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.61951661109924</v>
+        <v>2.61951637268066</v>
       </c>
       <c r="H1851" t="n">
         <v>370048</v>
@@ -54309,7 +54309,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1860" t="n">
         <v>379448</v>
@@ -54367,7 +54367,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.77948665618896</v>
+        <v>2.77948689460754</v>
       </c>
       <c r="H1862" t="n">
         <v>577732</v>
@@ -54773,7 +54773,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.69616889953613</v>
+        <v>2.69616913795471</v>
       </c>
       <c r="H1876" t="n">
         <v>421865</v>
@@ -54918,7 +54918,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.74449324607849</v>
+        <v>2.74449348449707</v>
       </c>
       <c r="H1881" t="n">
         <v>257730</v>
@@ -55063,7 +55063,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.84614133834839</v>
+        <v>2.84614109992981</v>
       </c>
       <c r="H1886" t="n">
         <v>395393</v>
@@ -55179,7 +55179,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.86780405044556</v>
+        <v>2.86780381202698</v>
       </c>
       <c r="H1890" t="n">
         <v>655477</v>
@@ -55237,7 +55237,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.86280512809753</v>
+        <v>2.86280488967896</v>
       </c>
       <c r="H1892" t="n">
         <v>349116</v>
@@ -55353,7 +55353,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.80614876747131</v>
+        <v>2.80614852905273</v>
       </c>
       <c r="H1896" t="n">
         <v>426755</v>
@@ -55382,7 +55382,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.82781147956848</v>
+        <v>2.8278112411499</v>
       </c>
       <c r="H1897" t="n">
         <v>268702</v>
@@ -55411,7 +55411,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.84780740737915</v>
+        <v>2.84780764579773</v>
       </c>
       <c r="H1898" t="n">
         <v>325266</v>
@@ -55469,7 +55469,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.79281783103943</v>
+        <v>2.79281759262085</v>
       </c>
       <c r="H1900" t="n">
         <v>438756</v>
@@ -55701,7 +55701,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.78448605537415</v>
+        <v>2.78448581695557</v>
       </c>
       <c r="H1908" t="n">
         <v>413850</v>
@@ -56020,7 +56020,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.84114241600037</v>
+        <v>2.84114217758179</v>
       </c>
       <c r="H1919" t="n">
         <v>438124</v>
@@ -56049,7 +56049,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.76282334327698</v>
+        <v>2.7628231048584</v>
       </c>
       <c r="H1920" t="n">
         <v>1567570</v>
@@ -56107,7 +56107,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1922" t="n">
         <v>303173</v>
@@ -56194,7 +56194,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.74615955352783</v>
+        <v>2.74615979194641</v>
       </c>
       <c r="H1925" t="n">
         <v>253905</v>
@@ -56368,7 +56368,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.7178316116333</v>
+        <v>2.71783185005188</v>
       </c>
       <c r="H1931" t="n">
         <v>294374</v>
@@ -56426,7 +56426,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.72116422653198</v>
+        <v>2.72116446495056</v>
       </c>
       <c r="H1933" t="n">
         <v>395549</v>
@@ -56571,7 +56571,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.7594907283783</v>
+        <v>2.75949048995972</v>
       </c>
       <c r="H1938" t="n">
         <v>478882</v>
@@ -56861,7 +56861,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.74282693862915</v>
+        <v>2.74282717704773</v>
       </c>
       <c r="H1948" t="n">
         <v>444594</v>
@@ -56948,7 +56948,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.12275695800781</v>
+        <v>3.12275671958923</v>
       </c>
       <c r="H1951" t="n">
         <v>3068307</v>
@@ -56977,7 +56977,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.1394202709198</v>
+        <v>3.13942050933838</v>
       </c>
       <c r="H1952" t="n">
         <v>2001061</v>
@@ -57035,7 +57035,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.23773574829102</v>
+        <v>3.23773550987244</v>
       </c>
       <c r="H1954" t="n">
         <v>1000550</v>
@@ -57180,7 +57180,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.28772664070129</v>
+        <v>3.28772640228271</v>
       </c>
       <c r="H1959" t="n">
         <v>759335</v>
@@ -57238,7 +57238,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.22273850440979</v>
+        <v>3.22273826599121</v>
       </c>
       <c r="H1961" t="n">
         <v>423991</v>
@@ -57267,7 +57267,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.17941308021545</v>
+        <v>3.17941284179688</v>
       </c>
       <c r="H1962" t="n">
         <v>831173</v>
@@ -57325,7 +57325,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.11609125137329</v>
+        <v>3.11609148979187</v>
       </c>
       <c r="H1964" t="n">
         <v>650589</v>
@@ -57412,7 +57412,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.10109424591064</v>
+        <v>3.10109400749207</v>
       </c>
       <c r="H1967" t="n">
         <v>586258</v>
@@ -57499,7 +57499,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.12275695800781</v>
+        <v>3.12275671958923</v>
       </c>
       <c r="H1970" t="n">
         <v>903295</v>
@@ -57557,7 +57557,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.16441583633423</v>
+        <v>3.16441607475281</v>
       </c>
       <c r="H1972" t="n">
         <v>316224</v>
@@ -57615,7 +57615,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.24273467063904</v>
+        <v>3.24273490905762</v>
       </c>
       <c r="H1974" t="n">
         <v>498769</v>
@@ -57644,7 +57644,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.24273467063904</v>
+        <v>3.24273490905762</v>
       </c>
       <c r="H1975" t="n">
         <v>535966</v>
@@ -57818,7 +57818,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.34105014801025</v>
+        <v>3.34104990959167</v>
       </c>
       <c r="H1981" t="n">
         <v>833546</v>
@@ -58050,7 +58050,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.36104607582092</v>
+        <v>3.3610463142395</v>
       </c>
       <c r="H1989" t="n">
         <v>763026</v>
@@ -75891,6 +75891,35 @@
         <v>830610</v>
       </c>
       <c r="I2604" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2605" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2605" t="n">
+        <v>4.98799991607666</v>
+      </c>
+      <c r="D2605" t="n">
+        <v>5.02500009536743</v>
+      </c>
+      <c r="E2605" t="n">
+        <v>4.95599985122681</v>
+      </c>
+      <c r="F2605" t="n">
+        <v>4.97800016403198</v>
+      </c>
+      <c r="G2605" t="n">
+        <v>4.97800016403198</v>
+      </c>
+      <c r="H2605" t="n">
+        <v>396172</v>
+      </c>
+      <c r="I2605" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.30103898048401</v>
+        <v>2.30103874206543</v>
       </c>
       <c r="H2" t="n">
         <v>73776221</v>
@@ -456,7 +456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.30103898048401</v>
+        <v>2.30103874206543</v>
       </c>
       <c r="H3" t="n">
         <v>8746746</v>
@@ -485,7 +485,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26321339607239</v>
+        <v>2.26321363449097</v>
       </c>
       <c r="H4" t="n">
         <v>8182968</v>
@@ -514,7 +514,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24303984642029</v>
+        <v>2.24304008483887</v>
       </c>
       <c r="H5" t="n">
         <v>6798460</v>
@@ -543,7 +543,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G6" t="n">
-        <v>2.30482149124146</v>
+        <v>2.3048210144043</v>
       </c>
       <c r="H6" t="n">
         <v>4016992</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>2.33255958557129</v>
+        <v>2.33256006240845</v>
       </c>
       <c r="H7" t="n">
         <v>3592063</v>
@@ -601,7 +601,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33255958557129</v>
+        <v>2.33256006240845</v>
       </c>
       <c r="H8" t="n">
         <v>2256529</v>
@@ -630,7 +630,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38677644729614</v>
+        <v>2.38677620887756</v>
       </c>
       <c r="H9" t="n">
         <v>3631224</v>
@@ -659,7 +659,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33886432647705</v>
+        <v>2.33886408805847</v>
       </c>
       <c r="H10" t="n">
         <v>883891</v>
@@ -688,7 +688,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33886432647705</v>
+        <v>2.33886408805847</v>
       </c>
       <c r="H11" t="n">
         <v>2186928</v>
@@ -775,7 +775,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G14" t="n">
-        <v>2.37921118736267</v>
+        <v>2.37921094894409</v>
       </c>
       <c r="H14" t="n">
         <v>2690138</v>
@@ -833,7 +833,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>2.30734348297119</v>
+        <v>2.30734324455261</v>
       </c>
       <c r="H16" t="n">
         <v>1485896</v>
@@ -891,7 +891,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.30734348297119</v>
+        <v>2.30734324455261</v>
       </c>
       <c r="H18" t="n">
         <v>911844</v>
@@ -920,7 +920,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29599547386169</v>
+        <v>2.29599523544312</v>
       </c>
       <c r="H19" t="n">
         <v>853812</v>
@@ -1007,7 +1007,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29725646972656</v>
+        <v>2.29725623130798</v>
       </c>
       <c r="H22" t="n">
         <v>1078374</v>
@@ -1036,7 +1036,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.30103898048401</v>
+        <v>2.30103874206543</v>
       </c>
       <c r="H23" t="n">
         <v>972167</v>
@@ -1065,7 +1065,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.33508157730103</v>
+        <v>2.3350818157196</v>
       </c>
       <c r="H24" t="n">
         <v>434879</v>
@@ -1094,7 +1094,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H25" t="n">
         <v>276607</v>
@@ -1152,7 +1152,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G27" t="n">
-        <v>2.3451681137085</v>
+        <v>2.34516859054565</v>
       </c>
       <c r="H27" t="n">
         <v>2312938</v>
@@ -1181,7 +1181,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G28" t="n">
-        <v>2.37542867660522</v>
+        <v>2.37542843818665</v>
       </c>
       <c r="H28" t="n">
         <v>1425652</v>
@@ -1210,7 +1210,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G29" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H29" t="n">
         <v>796842</v>
@@ -1239,7 +1239,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H30" t="n">
         <v>934202</v>
@@ -1268,7 +1268,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G31" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H31" t="n">
         <v>738518</v>
@@ -1326,7 +1326,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H33" t="n">
         <v>635450</v>
@@ -1384,7 +1384,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G35" t="n">
-        <v>2.23799657821655</v>
+        <v>2.23799681663513</v>
       </c>
       <c r="H35" t="n">
         <v>2200031</v>
@@ -1413,7 +1413,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25060510635376</v>
+        <v>2.25060486793518</v>
       </c>
       <c r="H36" t="n">
         <v>2171688</v>
@@ -1442,7 +1442,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21782350540161</v>
+        <v>2.21782302856445</v>
       </c>
       <c r="H37" t="n">
         <v>2049268</v>
@@ -1471,7 +1471,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.23799657821655</v>
+        <v>2.23799681663513</v>
       </c>
       <c r="H38" t="n">
         <v>508600</v>
@@ -1500,7 +1500,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G39" t="n">
-        <v>2.20521473884583</v>
+        <v>2.2052149772644</v>
       </c>
       <c r="H39" t="n">
         <v>724649</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.20647573471069</v>
+        <v>2.20647549629211</v>
       </c>
       <c r="H40" t="n">
         <v>582571</v>
@@ -1587,7 +1587,7 @@
         <v>3.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.20647573471069</v>
+        <v>2.20647549629211</v>
       </c>
       <c r="H42" t="n">
         <v>671983</v>
@@ -1616,7 +1616,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>2.2190842628479</v>
+        <v>2.21908402442932</v>
       </c>
       <c r="H43" t="n">
         <v>692846</v>
@@ -1645,7 +1645,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G44" t="n">
-        <v>2.19638895988464</v>
+        <v>2.19638872146606</v>
       </c>
       <c r="H44" t="n">
         <v>845586</v>
@@ -1674,7 +1674,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G45" t="n">
-        <v>2.22034525871277</v>
+        <v>2.22034478187561</v>
       </c>
       <c r="H45" t="n">
         <v>679381</v>
@@ -1703,7 +1703,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G46" t="n">
-        <v>2.21404075622559</v>
+        <v>2.21404099464417</v>
       </c>
       <c r="H46" t="n">
         <v>923623</v>
@@ -1732,7 +1732,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G47" t="n">
-        <v>2.2253885269165</v>
+        <v>2.22538828849792</v>
       </c>
       <c r="H47" t="n">
         <v>657985</v>
@@ -1790,7 +1790,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G49" t="n">
-        <v>2.30608201026917</v>
+        <v>2.30608224868774</v>
       </c>
       <c r="H49" t="n">
         <v>1124621</v>
@@ -1848,7 +1848,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26699614524841</v>
+        <v>2.26699590682983</v>
       </c>
       <c r="H51" t="n">
         <v>503049</v>
@@ -1877,7 +1877,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.23169255256653</v>
+        <v>2.23169231414795</v>
       </c>
       <c r="H52" t="n">
         <v>743120</v>
@@ -1906,7 +1906,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.21782350540161</v>
+        <v>2.21782302856445</v>
       </c>
       <c r="H53" t="n">
         <v>1181993</v>
@@ -1993,7 +1993,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G56" t="n">
-        <v>2.21151900291443</v>
+        <v>2.21151876449585</v>
       </c>
       <c r="H56" t="n">
         <v>170592</v>
@@ -2022,7 +2022,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G57" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H57" t="n">
         <v>823761</v>
@@ -2051,7 +2051,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G58" t="n">
-        <v>2.16108536720276</v>
+        <v>2.16108512878418</v>
       </c>
       <c r="H58" t="n">
         <v>856086</v>
@@ -2080,7 +2080,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.20773673057556</v>
+        <v>2.20773649215698</v>
       </c>
       <c r="H59" t="n">
         <v>787033</v>
@@ -2109,7 +2109,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G60" t="n">
-        <v>2.18251991271973</v>
+        <v>2.18251967430115</v>
       </c>
       <c r="H60" t="n">
         <v>567481</v>
@@ -2138,7 +2138,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15478110313416</v>
+        <v>2.15478134155273</v>
       </c>
       <c r="H61" t="n">
         <v>1863931</v>
@@ -2225,7 +2225,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G64" t="n">
-        <v>2.16991114616394</v>
+        <v>2.16991138458252</v>
       </c>
       <c r="H64" t="n">
         <v>368716</v>
@@ -2254,7 +2254,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G65" t="n">
-        <v>2.14721584320068</v>
+        <v>2.14721608161926</v>
       </c>
       <c r="H65" t="n">
         <v>1473153</v>
@@ -2283,7 +2283,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>2.16865015029907</v>
+        <v>2.16865038871765</v>
       </c>
       <c r="H66" t="n">
         <v>1102800</v>
@@ -2486,7 +2486,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>2.13082504272461</v>
+        <v>2.13082528114319</v>
       </c>
       <c r="H73" t="n">
         <v>768752</v>
@@ -2631,7 +2631,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.99465370178223</v>
+        <v>1.99465382099152</v>
       </c>
       <c r="H78" t="n">
         <v>2768628</v>
@@ -2660,7 +2660,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195863723755</v>
+        <v>1.97195887565613</v>
       </c>
       <c r="H79" t="n">
         <v>3135081</v>
@@ -2718,7 +2718,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G81" t="n">
-        <v>1.9391770362854</v>
+        <v>1.93917679786682</v>
       </c>
       <c r="H81" t="n">
         <v>2261017</v>
@@ -2776,7 +2776,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>1.92278563976288</v>
+        <v>1.92278587818146</v>
       </c>
       <c r="H83" t="n">
         <v>1876379</v>
@@ -2805,7 +2805,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G84" t="n">
-        <v>1.94800281524658</v>
+        <v>1.94800233840942</v>
       </c>
       <c r="H84" t="n">
         <v>3748342</v>
@@ -2950,7 +2950,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G89" t="n">
-        <v>1.97321963310242</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H89" t="n">
         <v>736410</v>
@@ -2979,7 +2979,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G90" t="n">
-        <v>1.99339318275452</v>
+        <v>1.99339294433594</v>
       </c>
       <c r="H90" t="n">
         <v>1831237</v>
@@ -3008,7 +3008,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G91" t="n">
-        <v>2.01356673240662</v>
+        <v>2.01356649398804</v>
       </c>
       <c r="H91" t="n">
         <v>1362913</v>
@@ -3095,7 +3095,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G94" t="n">
-        <v>1.974480509758</v>
+        <v>1.97448027133942</v>
       </c>
       <c r="H94" t="n">
         <v>1497058</v>
@@ -3153,7 +3153,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G96" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213218688965</v>
       </c>
       <c r="H96" t="n">
         <v>3064119</v>
@@ -3182,7 +3182,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>1.97321963310242</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H97" t="n">
         <v>1754313</v>
@@ -3211,7 +3211,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G98" t="n">
-        <v>1.91017758846283</v>
+        <v>1.91017735004425</v>
       </c>
       <c r="H98" t="n">
         <v>1613932</v>
@@ -3240,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89126467704773</v>
+        <v>1.8912650346756</v>
       </c>
       <c r="H99" t="n">
         <v>3568973</v>
@@ -3269,7 +3269,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G100" t="n">
-        <v>1.89504766464233</v>
+        <v>1.89504742622375</v>
       </c>
       <c r="H100" t="n">
         <v>1788951</v>
@@ -3298,7 +3298,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G101" t="n">
-        <v>1.9391770362854</v>
+        <v>1.93917679786682</v>
       </c>
       <c r="H101" t="n">
         <v>2183788</v>
@@ -3414,7 +3414,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G105" t="n">
-        <v>2.05643558502197</v>
+        <v>2.05643534660339</v>
       </c>
       <c r="H105" t="n">
         <v>1912960</v>
@@ -3443,7 +3443,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>2.06147885322571</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H106" t="n">
         <v>1234594</v>
@@ -3530,7 +3530,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>2.06147885322571</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H109" t="n">
         <v>908570</v>
@@ -3588,7 +3588,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.06147885322571</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H111" t="n">
         <v>436432</v>
@@ -3675,7 +3675,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G114" t="n">
-        <v>2.08417367935181</v>
+        <v>2.08417391777039</v>
       </c>
       <c r="H114" t="n">
         <v>255877</v>
@@ -3762,7 +3762,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G117" t="n">
-        <v>2.14469456672668</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H117" t="n">
         <v>680193</v>
@@ -3791,7 +3791,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G118" t="n">
-        <v>2.14091157913208</v>
+        <v>2.14091205596924</v>
       </c>
       <c r="H118" t="n">
         <v>272440</v>
@@ -3849,7 +3849,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.13082504272461</v>
+        <v>2.13082528114319</v>
       </c>
       <c r="H120" t="n">
         <v>713419</v>
@@ -3907,7 +3907,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.15604209899902</v>
+        <v>2.1560423374176</v>
       </c>
       <c r="H122" t="n">
         <v>505790</v>
@@ -3936,7 +3936,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>2.19008445739746</v>
+        <v>2.19008493423462</v>
       </c>
       <c r="H123" t="n">
         <v>976460</v>
@@ -3994,7 +3994,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G125" t="n">
-        <v>2.16991114616394</v>
+        <v>2.16991138458252</v>
       </c>
       <c r="H125" t="n">
         <v>416120</v>
@@ -4023,7 +4023,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G126" t="n">
-        <v>2.14847683906555</v>
+        <v>2.14847660064697</v>
       </c>
       <c r="H126" t="n">
         <v>602771</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.15604209899902</v>
+        <v>2.1560423374176</v>
       </c>
       <c r="H127" t="n">
         <v>556151</v>
@@ -4081,7 +4081,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G128" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H128" t="n">
         <v>638147</v>
@@ -4110,7 +4110,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15352034568787</v>
+        <v>2.15352010726929</v>
       </c>
       <c r="H129" t="n">
         <v>520370</v>
@@ -4139,7 +4139,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>2.13460755348206</v>
+        <v>2.13460731506348</v>
       </c>
       <c r="H130" t="n">
         <v>1255649</v>
@@ -4168,7 +4168,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G131" t="n">
-        <v>2.11191201210022</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H131" t="n">
         <v>982502</v>
@@ -4197,7 +4197,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>2.11191201210022</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H132" t="n">
         <v>983090</v>
@@ -4255,7 +4255,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G134" t="n">
-        <v>2.04256629943848</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H134" t="n">
         <v>446178</v>
@@ -4284,7 +4284,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G135" t="n">
-        <v>2.04256629943848</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H135" t="n">
         <v>1021203</v>
@@ -4342,7 +4342,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G137" t="n">
-        <v>2.02491402626038</v>
+        <v>2.02491426467896</v>
       </c>
       <c r="H137" t="n">
         <v>613132</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.04256629943848</v>
+        <v>2.0425660610199</v>
       </c>
       <c r="H138" t="n">
         <v>873840</v>
@@ -4400,7 +4400,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213218688965</v>
       </c>
       <c r="H139" t="n">
         <v>526097</v>
@@ -4516,7 +4516,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>2.05643558502197</v>
+        <v>2.05643534660339</v>
       </c>
       <c r="H143" t="n">
         <v>591488</v>
@@ -4545,7 +4545,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G144" t="n">
-        <v>2.07282614707947</v>
+        <v>2.07282638549805</v>
       </c>
       <c r="H144" t="n">
         <v>820333</v>
@@ -4574,7 +4574,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G145" t="n">
-        <v>2.06400036811829</v>
+        <v>2.06400012969971</v>
       </c>
       <c r="H145" t="n">
         <v>430023</v>
@@ -4603,7 +4603,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11191201210022</v>
+        <v>2.11191248893738</v>
       </c>
       <c r="H146" t="n">
         <v>1000881</v>
@@ -4632,7 +4632,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.13712930679321</v>
+        <v>2.13712906837463</v>
       </c>
       <c r="H147" t="n">
         <v>886586</v>
@@ -4690,7 +4690,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>2.15225911140442</v>
+        <v>2.152259349823</v>
       </c>
       <c r="H149" t="n">
         <v>659705</v>
@@ -4777,7 +4777,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G152" t="n">
-        <v>2.12199926376343</v>
+        <v>2.12199902534485</v>
       </c>
       <c r="H152" t="n">
         <v>878730</v>
@@ -4806,7 +4806,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G153" t="n">
-        <v>2.09552145004272</v>
+        <v>2.09552121162415</v>
       </c>
       <c r="H153" t="n">
         <v>692808</v>
@@ -4893,7 +4893,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G156" t="n">
-        <v>2.13712930679321</v>
+        <v>2.13712906837463</v>
       </c>
       <c r="H156" t="n">
         <v>566431</v>
@@ -4980,7 +4980,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>2.13082504272461</v>
+        <v>2.13082528114319</v>
       </c>
       <c r="H159" t="n">
         <v>442504</v>
@@ -5009,7 +5009,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G160" t="n">
-        <v>2.12704277038574</v>
+        <v>2.12704253196716</v>
       </c>
       <c r="H160" t="n">
         <v>735413</v>
@@ -5038,7 +5038,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G161" t="n">
-        <v>2.14469456672668</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H161" t="n">
         <v>513353</v>
@@ -5067,7 +5067,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G162" t="n">
-        <v>2.16234636306763</v>
+        <v>2.16234612464905</v>
       </c>
       <c r="H162" t="n">
         <v>835730</v>
@@ -5096,7 +5096,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G163" t="n">
-        <v>2.16108536720276</v>
+        <v>2.16108512878418</v>
       </c>
       <c r="H163" t="n">
         <v>472501</v>
@@ -5125,7 +5125,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G164" t="n">
-        <v>2.14595484733582</v>
+        <v>2.14595532417297</v>
       </c>
       <c r="H164" t="n">
         <v>656848</v>
@@ -5183,7 +5183,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G166" t="n">
-        <v>2.17243313789368</v>
+        <v>2.1724328994751</v>
       </c>
       <c r="H166" t="n">
         <v>716925</v>
@@ -5328,7 +5328,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G171" t="n">
-        <v>2.30734348297119</v>
+        <v>2.30734324455261</v>
       </c>
       <c r="H171" t="n">
         <v>1058400</v>
@@ -5386,7 +5386,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G173" t="n">
-        <v>2.37290692329407</v>
+        <v>2.37290716171265</v>
       </c>
       <c r="H173" t="n">
         <v>970626</v>
@@ -5415,7 +5415,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40190649032593</v>
+        <v>2.40190601348877</v>
       </c>
       <c r="H174" t="n">
         <v>1365898</v>
@@ -5444,7 +5444,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G175" t="n">
-        <v>2.35399413108826</v>
+        <v>2.35399389266968</v>
       </c>
       <c r="H175" t="n">
         <v>1120304</v>
@@ -5473,7 +5473,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877731323242</v>
       </c>
       <c r="H176" t="n">
         <v>959599</v>
@@ -5531,7 +5531,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G178" t="n">
-        <v>2.40316700935364</v>
+        <v>2.40316724777222</v>
       </c>
       <c r="H178" t="n">
         <v>2956792</v>
@@ -5560,7 +5560,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G179" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H179" t="n">
         <v>1073722</v>
@@ -5618,7 +5618,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G181" t="n">
-        <v>2.39181971549988</v>
+        <v>2.3918194770813</v>
       </c>
       <c r="H181" t="n">
         <v>1136549</v>
@@ -5647,7 +5647,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G182" t="n">
-        <v>2.37038516998291</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H182" t="n">
         <v>1371992</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H183" t="n">
         <v>1547599</v>
@@ -5705,7 +5705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H184" t="n">
         <v>1699128</v>
@@ -5792,7 +5792,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H187" t="n">
         <v>1275111</v>
@@ -5850,7 +5850,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G189" t="n">
-        <v>2.36534190177917</v>
+        <v>2.36534214019775</v>
       </c>
       <c r="H189" t="n">
         <v>713369</v>
@@ -5995,7 +5995,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G194" t="n">
-        <v>2.38047194480896</v>
+        <v>2.38047218322754</v>
       </c>
       <c r="H194" t="n">
         <v>1119199</v>
@@ -6053,7 +6053,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G196" t="n">
-        <v>2.37038516998291</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H196" t="n">
         <v>930629</v>
@@ -6140,7 +6140,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H199" t="n">
         <v>1166747</v>
@@ -6169,7 +6169,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>2.42964506149292</v>
+        <v>2.4296452999115</v>
       </c>
       <c r="H200" t="n">
         <v>722953</v>
@@ -6198,7 +6198,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>2.41451478004456</v>
+        <v>2.41451501846313</v>
       </c>
       <c r="H201" t="n">
         <v>963400</v>
@@ -6256,7 +6256,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G203" t="n">
-        <v>2.4384708404541</v>
+        <v>2.43847107887268</v>
       </c>
       <c r="H203" t="n">
         <v>749019</v>
@@ -6343,7 +6343,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.45864462852478</v>
+        <v>2.4586443901062</v>
       </c>
       <c r="H206" t="n">
         <v>901759</v>
@@ -6401,7 +6401,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>2.38677644729614</v>
+        <v>2.38677620887756</v>
       </c>
       <c r="H208" t="n">
         <v>998514</v>
@@ -6430,7 +6430,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G209" t="n">
-        <v>2.41451478004456</v>
+        <v>2.41451501846313</v>
       </c>
       <c r="H209" t="n">
         <v>3815639</v>
@@ -6459,7 +6459,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G210" t="n">
-        <v>2.37038516998291</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H210" t="n">
         <v>2706748</v>
@@ -6604,7 +6604,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G215" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721167564392</v>
       </c>
       <c r="H215" t="n">
         <v>1570341</v>
@@ -6662,7 +6662,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>2.46694612503052</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H217" t="n">
         <v>1320391</v>
@@ -6865,7 +6865,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G224" t="n">
-        <v>2.49737000465393</v>
+        <v>2.49737024307251</v>
       </c>
       <c r="H224" t="n">
         <v>1878448</v>
@@ -6923,7 +6923,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G226" t="n">
-        <v>2.48546552658081</v>
+        <v>2.48546504974365</v>
       </c>
       <c r="H226" t="n">
         <v>1137067</v>
@@ -6981,7 +6981,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G228" t="n">
-        <v>2.51324343681335</v>
+        <v>2.51324319839478</v>
       </c>
       <c r="H228" t="n">
         <v>2456099</v>
@@ -7039,7 +7039,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>2.46694612503052</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H230" t="n">
         <v>3703950</v>
@@ -7126,7 +7126,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G233" t="n">
-        <v>2.47620606422424</v>
+        <v>2.47620582580566</v>
       </c>
       <c r="H233" t="n">
         <v>1547243</v>
@@ -7155,7 +7155,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356033325195</v>
       </c>
       <c r="H234" t="n">
         <v>365542</v>
@@ -7271,7 +7271,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G238" t="n">
-        <v>2.45239615440369</v>
+        <v>2.45239639282227</v>
       </c>
       <c r="H238" t="n">
         <v>975866</v>
@@ -7358,7 +7358,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>2.46033310890198</v>
+        <v>2.4603328704834</v>
       </c>
       <c r="H241" t="n">
         <v>454792</v>
@@ -7416,7 +7416,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>2.46694612503052</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H243" t="n">
         <v>279712</v>
@@ -7503,7 +7503,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>2.46694612503052</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H246" t="n">
         <v>235874</v>
@@ -7532,7 +7532,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G247" t="n">
-        <v>2.44445967674255</v>
+        <v>2.44445991516113</v>
       </c>
       <c r="H247" t="n">
         <v>244557</v>
@@ -7735,7 +7735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>2.45371913909912</v>
+        <v>2.45371890068054</v>
       </c>
       <c r="H254" t="n">
         <v>628873</v>
@@ -7822,7 +7822,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.46033310890198</v>
+        <v>2.4603328704834</v>
       </c>
       <c r="H257" t="n">
         <v>563597</v>
@@ -7851,7 +7851,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356033325195</v>
       </c>
       <c r="H258" t="n">
         <v>335894</v>
@@ -7909,7 +7909,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>2.51456618309021</v>
+        <v>2.51456594467163</v>
       </c>
       <c r="H260" t="n">
         <v>440530</v>
@@ -7938,7 +7938,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G261" t="n">
-        <v>2.5648307800293</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H261" t="n">
         <v>524937</v>
@@ -7996,7 +7996,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G263" t="n">
-        <v>2.57144474983215</v>
+        <v>2.57144451141357</v>
       </c>
       <c r="H263" t="n">
         <v>328662</v>
@@ -8025,7 +8025,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G264" t="n">
-        <v>2.56218528747559</v>
+        <v>2.56218552589417</v>
       </c>
       <c r="H264" t="n">
         <v>625175</v>
@@ -8054,7 +8054,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G265" t="n">
-        <v>2.5648307800293</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H265" t="n">
         <v>514836</v>
@@ -8083,7 +8083,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G266" t="n">
-        <v>2.56615352630615</v>
+        <v>2.56615376472473</v>
       </c>
       <c r="H266" t="n">
         <v>481921</v>
@@ -8112,7 +8112,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G267" t="n">
-        <v>2.55424880981445</v>
+        <v>2.55424904823303</v>
       </c>
       <c r="H267" t="n">
         <v>614773</v>
@@ -8199,7 +8199,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G270" t="n">
-        <v>2.52382516860962</v>
+        <v>2.5238254070282</v>
       </c>
       <c r="H270" t="n">
         <v>321976</v>
@@ -8257,7 +8257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G272" t="n">
-        <v>2.51324343681335</v>
+        <v>2.51324319839478</v>
       </c>
       <c r="H272" t="n">
         <v>536735</v>
@@ -8344,7 +8344,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356033325195</v>
       </c>
       <c r="H275" t="n">
         <v>409245</v>
@@ -8402,7 +8402,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>2.47356057167053</v>
+        <v>2.47356033325195</v>
       </c>
       <c r="H277" t="n">
         <v>374003</v>
@@ -8489,7 +8489,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G280" t="n">
-        <v>2.4484281539917</v>
+        <v>2.44842767715454</v>
       </c>
       <c r="H280" t="n">
         <v>191020</v>
@@ -8518,7 +8518,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G281" t="n">
-        <v>2.42858672142029</v>
+        <v>2.42858648300171</v>
       </c>
       <c r="H281" t="n">
         <v>622612</v>
@@ -8547,7 +8547,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G282" t="n">
-        <v>2.43784618377686</v>
+        <v>2.43784594535828</v>
       </c>
       <c r="H282" t="n">
         <v>466984</v>
@@ -8605,7 +8605,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G284" t="n">
-        <v>2.47752904891968</v>
+        <v>2.4775288105011</v>
       </c>
       <c r="H284" t="n">
         <v>405263</v>
@@ -8866,7 +8866,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G293" t="n">
-        <v>2.53440761566162</v>
+        <v>2.53440737724304</v>
       </c>
       <c r="H293" t="n">
         <v>472169</v>
@@ -8953,7 +8953,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G296" t="n">
-        <v>2.54102110862732</v>
+        <v>2.54102087020874</v>
       </c>
       <c r="H296" t="n">
         <v>538902</v>
@@ -9011,7 +9011,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G298" t="n">
-        <v>2.51456618309021</v>
+        <v>2.51456594467163</v>
       </c>
       <c r="H298" t="n">
         <v>271055</v>
@@ -9040,7 +9040,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G299" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721167564392</v>
       </c>
       <c r="H299" t="n">
         <v>254927</v>
@@ -9127,7 +9127,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53969812393188</v>
+        <v>2.53969836235046</v>
       </c>
       <c r="H302" t="n">
         <v>350932</v>
@@ -9156,7 +9156,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.53969812393188</v>
+        <v>2.53969836235046</v>
       </c>
       <c r="H303" t="n">
         <v>764260</v>
@@ -9185,7 +9185,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G304" t="n">
-        <v>2.56350779533386</v>
+        <v>2.56350803375244</v>
       </c>
       <c r="H304" t="n">
         <v>439623</v>
@@ -9243,7 +9243,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G306" t="n">
-        <v>2.59922289848328</v>
+        <v>2.5992226600647</v>
       </c>
       <c r="H306" t="n">
         <v>581605</v>
@@ -9272,7 +9272,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G307" t="n">
-        <v>2.60583662986755</v>
+        <v>2.60583639144897</v>
       </c>
       <c r="H307" t="n">
         <v>525000</v>
@@ -9301,7 +9301,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60583662986755</v>
+        <v>2.60583639144897</v>
       </c>
       <c r="H308" t="n">
         <v>474886</v>
@@ -9388,7 +9388,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G311" t="n">
-        <v>2.59128594398499</v>
+        <v>2.59128618240356</v>
       </c>
       <c r="H311" t="n">
         <v>463030</v>
@@ -9475,7 +9475,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G314" t="n">
-        <v>2.60980463027954</v>
+        <v>2.60980486869812</v>
       </c>
       <c r="H314" t="n">
         <v>445032</v>
@@ -9504,7 +9504,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G315" t="n">
-        <v>2.60980463027954</v>
+        <v>2.60980486869812</v>
       </c>
       <c r="H315" t="n">
         <v>562538</v>
@@ -9533,7 +9533,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G316" t="n">
-        <v>2.60319113731384</v>
+        <v>2.60319089889526</v>
       </c>
       <c r="H316" t="n">
         <v>439492</v>
@@ -9562,7 +9562,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G317" t="n">
-        <v>2.67329716682434</v>
+        <v>2.67329692840576</v>
       </c>
       <c r="H317" t="n">
         <v>1408139</v>
@@ -9591,7 +9591,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G318" t="n">
-        <v>2.68917036056519</v>
+        <v>2.68917012214661</v>
       </c>
       <c r="H318" t="n">
         <v>660904</v>
@@ -9649,7 +9649,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G320" t="n">
-        <v>2.6971070766449</v>
+        <v>2.69710683822632</v>
       </c>
       <c r="H320" t="n">
         <v>496010</v>
@@ -9678,7 +9678,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>2.67858839035034</v>
+        <v>2.67858815193176</v>
       </c>
       <c r="H321" t="n">
         <v>476349</v>
@@ -9794,7 +9794,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G325" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H325" t="n">
         <v>687242</v>
@@ -9823,7 +9823,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G326" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H326" t="n">
         <v>753657</v>
@@ -9852,7 +9852,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G327" t="n">
-        <v>2.68784737586975</v>
+        <v>2.68784785270691</v>
       </c>
       <c r="H327" t="n">
         <v>473695</v>
@@ -9881,7 +9881,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G328" t="n">
-        <v>2.68784737586975</v>
+        <v>2.68784785270691</v>
       </c>
       <c r="H328" t="n">
         <v>332487</v>
@@ -9910,7 +9910,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G329" t="n">
-        <v>2.70239782333374</v>
+        <v>2.70239806175232</v>
       </c>
       <c r="H329" t="n">
         <v>459573</v>
@@ -9939,7 +9939,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H330" t="n">
         <v>618999</v>
@@ -9968,7 +9968,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>2.68520188331604</v>
+        <v>2.68520212173462</v>
       </c>
       <c r="H331" t="n">
         <v>771787</v>
@@ -9997,7 +9997,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G332" t="n">
-        <v>2.70107531547546</v>
+        <v>2.70107507705688</v>
       </c>
       <c r="H332" t="n">
         <v>431759</v>
@@ -10026,7 +10026,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G333" t="n">
-        <v>2.70107531547546</v>
+        <v>2.70107507705688</v>
       </c>
       <c r="H333" t="n">
         <v>1317493</v>
@@ -10055,7 +10055,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>2.65874671936035</v>
+        <v>2.65874648094177</v>
       </c>
       <c r="H334" t="n">
         <v>564957</v>
@@ -10113,7 +10113,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.74472641944885</v>
+        <v>2.74472618103027</v>
       </c>
       <c r="H336" t="n">
         <v>2911512</v>
@@ -10200,7 +10200,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G339" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H339" t="n">
         <v>425935</v>
@@ -10229,7 +10229,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G340" t="n">
-        <v>2.88758444786072</v>
+        <v>2.88758420944214</v>
       </c>
       <c r="H340" t="n">
         <v>1378600</v>
@@ -10258,7 +10258,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G341" t="n">
-        <v>2.9034571647644</v>
+        <v>2.90345692634583</v>
       </c>
       <c r="H341" t="n">
         <v>1248384</v>
@@ -10345,7 +10345,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G344" t="n">
-        <v>2.95901322364807</v>
+        <v>2.95901346206665</v>
       </c>
       <c r="H344" t="n">
         <v>1122926</v>
@@ -10374,7 +10374,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G345" t="n">
-        <v>2.94843101501465</v>
+        <v>2.94843149185181</v>
       </c>
       <c r="H345" t="n">
         <v>1014769</v>
@@ -10490,7 +10490,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G349" t="n">
-        <v>2.95901322364807</v>
+        <v>2.95901346206665</v>
       </c>
       <c r="H349" t="n">
         <v>794496</v>
@@ -10548,7 +10548,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G351" t="n">
-        <v>3.01456880569458</v>
+        <v>3.014568567276</v>
       </c>
       <c r="H351" t="n">
         <v>1271838</v>
@@ -10577,7 +10577,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03837871551514</v>
+        <v>3.03837895393372</v>
       </c>
       <c r="H352" t="n">
         <v>949730</v>
@@ -10606,7 +10606,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G353" t="n">
-        <v>3.03176498413086</v>
+        <v>3.0317645072937</v>
       </c>
       <c r="H353" t="n">
         <v>617623</v>
@@ -10635,7 +10635,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G354" t="n">
-        <v>3.10583996772766</v>
+        <v>3.1058394908905</v>
       </c>
       <c r="H354" t="n">
         <v>888394</v>
@@ -10693,7 +10693,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.0092785358429</v>
+        <v>3.00927829742432</v>
       </c>
       <c r="H356" t="n">
         <v>1663888</v>
@@ -10722,7 +10722,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G357" t="n">
-        <v>2.99605059623718</v>
+        <v>2.99605083465576</v>
       </c>
       <c r="H357" t="n">
         <v>1097676</v>
@@ -10751,7 +10751,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>3.01456880569458</v>
+        <v>3.014568567276</v>
       </c>
       <c r="H358" t="n">
         <v>1277481</v>
@@ -10780,7 +10780,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>3.04234647750854</v>
+        <v>3.04234671592712</v>
       </c>
       <c r="H359" t="n">
         <v>1263796</v>
@@ -10809,7 +10809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G360" t="n">
-        <v>3.04631543159485</v>
+        <v>3.04631519317627</v>
       </c>
       <c r="H360" t="n">
         <v>1279493</v>
@@ -10867,7 +10867,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>3.02911949157715</v>
+        <v>3.02911972999573</v>
       </c>
       <c r="H362" t="n">
         <v>894876</v>
@@ -10896,7 +10896,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05557489395142</v>
+        <v>3.05557441711426</v>
       </c>
       <c r="H363" t="n">
         <v>841909</v>
@@ -10925,7 +10925,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G364" t="n">
-        <v>3.02515125274658</v>
+        <v>3.02515077590942</v>
       </c>
       <c r="H364" t="n">
         <v>436276</v>
@@ -11070,7 +11070,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>2.99869585037231</v>
+        <v>2.99869608879089</v>
       </c>
       <c r="H369" t="n">
         <v>327121</v>
@@ -11186,7 +11186,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G373" t="n">
-        <v>3.02250552177429</v>
+        <v>3.02250576019287</v>
       </c>
       <c r="H373" t="n">
         <v>820789</v>
@@ -11215,7 +11215,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>2.94313955307007</v>
+        <v>2.94314026832581</v>
       </c>
       <c r="H374" t="n">
         <v>861518</v>
@@ -11331,7 +11331,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G378" t="n">
-        <v>2.85583782196045</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H378" t="n">
         <v>654476</v>
@@ -11389,7 +11389,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>2.84393286705017</v>
+        <v>2.84393310546875</v>
       </c>
       <c r="H380" t="n">
         <v>657743</v>
@@ -11418,7 +11418,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85980606079102</v>
+        <v>2.85980629920959</v>
       </c>
       <c r="H381" t="n">
         <v>559669</v>
@@ -11476,7 +11476,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G383" t="n">
-        <v>2.83070588111877</v>
+        <v>2.83070611953735</v>
       </c>
       <c r="H383" t="n">
         <v>646536</v>
@@ -11505,7 +11505,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85583782196045</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H384" t="n">
         <v>424777</v>
@@ -11592,7 +11592,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.84525609016418</v>
+        <v>2.84525585174561</v>
       </c>
       <c r="H387" t="n">
         <v>570613</v>
@@ -11621,7 +11621,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.79763650894165</v>
+        <v>2.79763627052307</v>
       </c>
       <c r="H388" t="n">
         <v>888381</v>
@@ -11650,7 +11650,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705453872681</v>
+        <v>2.78705430030823</v>
       </c>
       <c r="H389" t="n">
         <v>1087808</v>
@@ -11679,7 +11679,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80689549446106</v>
+        <v>2.80689573287964</v>
       </c>
       <c r="H390" t="n">
         <v>516731</v>
@@ -11737,7 +11737,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>2.80689549446106</v>
+        <v>2.80689573287964</v>
       </c>
       <c r="H392" t="n">
         <v>1039683</v>
@@ -11853,7 +11853,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G396" t="n">
-        <v>2.67329716682434</v>
+        <v>2.67329692840576</v>
       </c>
       <c r="H396" t="n">
         <v>563261</v>
@@ -11882,7 +11882,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69446134567261</v>
+        <v>2.69446110725403</v>
       </c>
       <c r="H397" t="n">
         <v>848281</v>
@@ -11911,7 +11911,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G398" t="n">
-        <v>2.68652439117432</v>
+        <v>2.68652415275574</v>
       </c>
       <c r="H398" t="n">
         <v>458902</v>
@@ -11940,7 +11940,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G399" t="n">
-        <v>2.75266265869141</v>
+        <v>2.75266289710999</v>
       </c>
       <c r="H399" t="n">
         <v>1135051</v>
@@ -12056,7 +12056,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G403" t="n">
-        <v>2.76456761360168</v>
+        <v>2.76456737518311</v>
       </c>
       <c r="H403" t="n">
         <v>371911</v>
@@ -12085,7 +12085,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G404" t="n">
-        <v>2.72885322570801</v>
+        <v>2.72885298728943</v>
       </c>
       <c r="H404" t="n">
         <v>250945</v>
@@ -12114,7 +12114,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G405" t="n">
-        <v>2.72885322570801</v>
+        <v>2.72885298728943</v>
       </c>
       <c r="H405" t="n">
         <v>549004</v>
@@ -12143,7 +12143,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74472641944885</v>
+        <v>2.74472618103027</v>
       </c>
       <c r="H406" t="n">
         <v>449646</v>
@@ -12172,7 +12172,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>2.79102230072021</v>
+        <v>2.79102253913879</v>
       </c>
       <c r="H407" t="n">
         <v>384104</v>
@@ -12259,7 +12259,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G410" t="n">
-        <v>2.72620797157288</v>
+        <v>2.7262077331543</v>
       </c>
       <c r="H410" t="n">
         <v>884762</v>
@@ -12317,7 +12317,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>2.67991065979004</v>
+        <v>2.6799111366272</v>
       </c>
       <c r="H412" t="n">
         <v>388086</v>
@@ -12346,7 +12346,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G413" t="n">
-        <v>2.76324439048767</v>
+        <v>2.76324462890625</v>
       </c>
       <c r="H413" t="n">
         <v>701284</v>
@@ -12433,7 +12433,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G416" t="n">
-        <v>2.79102230072021</v>
+        <v>2.79102253913879</v>
       </c>
       <c r="H416" t="n">
         <v>262750</v>
@@ -12462,7 +12462,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G417" t="n">
-        <v>2.85583782196045</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H417" t="n">
         <v>1518103</v>
@@ -12491,7 +12491,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G418" t="n">
-        <v>2.86906552314758</v>
+        <v>2.869065284729</v>
       </c>
       <c r="H418" t="n">
         <v>2152019</v>
@@ -12520,7 +12520,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G419" t="n">
-        <v>2.87303376197815</v>
+        <v>2.87303400039673</v>
       </c>
       <c r="H419" t="n">
         <v>1064225</v>
@@ -12549,7 +12549,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>2.91007137298584</v>
+        <v>2.91007089614868</v>
       </c>
       <c r="H420" t="n">
         <v>721209</v>
@@ -12578,7 +12578,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G421" t="n">
-        <v>2.88890719413757</v>
+        <v>2.88890695571899</v>
       </c>
       <c r="H421" t="n">
         <v>630370</v>
@@ -12636,7 +12636,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G423" t="n">
-        <v>2.89287543296814</v>
+        <v>2.89287519454956</v>
       </c>
       <c r="H423" t="n">
         <v>451656</v>
@@ -12665,7 +12665,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G424" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H424" t="n">
         <v>511038</v>
@@ -12694,7 +12694,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G425" t="n">
-        <v>2.79631376266479</v>
+        <v>2.79631400108337</v>
       </c>
       <c r="H425" t="n">
         <v>548843</v>
@@ -12723,7 +12723,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G426" t="n">
-        <v>2.81483221054077</v>
+        <v>2.81483197212219</v>
       </c>
       <c r="H426" t="n">
         <v>783217</v>
@@ -12752,7 +12752,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G427" t="n">
-        <v>2.79234552383423</v>
+        <v>2.79234528541565</v>
       </c>
       <c r="H427" t="n">
         <v>495666</v>
@@ -12781,7 +12781,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G428" t="n">
-        <v>2.83335137367249</v>
+        <v>2.83335113525391</v>
       </c>
       <c r="H428" t="n">
         <v>634478</v>
@@ -12810,7 +12810,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G429" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H429" t="n">
         <v>1135467</v>
@@ -12926,7 +12926,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.89022922515869</v>
+        <v>2.89022946357727</v>
       </c>
       <c r="H433" t="n">
         <v>641837</v>
@@ -12955,7 +12955,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G434" t="n">
-        <v>2.894198179245</v>
+        <v>2.89419794082642</v>
       </c>
       <c r="H434" t="n">
         <v>713486</v>
@@ -12984,7 +12984,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G435" t="n">
-        <v>2.90610265731812</v>
+        <v>2.90610289573669</v>
       </c>
       <c r="H435" t="n">
         <v>364698</v>
@@ -13013,7 +13013,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G436" t="n">
-        <v>2.93123507499695</v>
+        <v>2.93123531341553</v>
       </c>
       <c r="H436" t="n">
         <v>487422</v>
@@ -13042,7 +13042,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94181752204895</v>
+        <v>2.94181728363037</v>
       </c>
       <c r="H437" t="n">
         <v>413076</v>
@@ -13071,7 +13071,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G438" t="n">
-        <v>2.97885489463806</v>
+        <v>2.97885465621948</v>
       </c>
       <c r="H438" t="n">
         <v>726631</v>
@@ -13187,7 +13187,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.93652653694153</v>
+        <v>2.93652629852295</v>
       </c>
       <c r="H442" t="n">
         <v>698038</v>
@@ -13216,7 +13216,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520379066467</v>
+        <v>2.93520355224609</v>
       </c>
       <c r="H443" t="n">
         <v>1018294</v>
@@ -13245,7 +13245,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G444" t="n">
-        <v>2.94181752204895</v>
+        <v>2.94181728363037</v>
       </c>
       <c r="H444" t="n">
         <v>553049</v>
@@ -13274,7 +13274,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>2.95636773109436</v>
+        <v>2.95636749267578</v>
       </c>
       <c r="H445" t="n">
         <v>229109</v>
@@ -13332,7 +13332,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>2.95636773109436</v>
+        <v>2.95636749267578</v>
       </c>
       <c r="H447" t="n">
         <v>241939</v>
@@ -13361,7 +13361,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G448" t="n">
-        <v>2.99737310409546</v>
+        <v>2.99737334251404</v>
       </c>
       <c r="H448" t="n">
         <v>369775</v>
@@ -13390,7 +13390,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G449" t="n">
-        <v>2.99075937271118</v>
+        <v>2.99075984954834</v>
       </c>
       <c r="H449" t="n">
         <v>251562</v>
@@ -13477,7 +13477,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G452" t="n">
-        <v>2.97885489463806</v>
+        <v>2.97885465621948</v>
       </c>
       <c r="H452" t="n">
         <v>461639</v>
@@ -13506,7 +13506,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G453" t="n">
-        <v>2.99737310409546</v>
+        <v>2.99737334251404</v>
       </c>
       <c r="H453" t="n">
         <v>403012</v>
@@ -13535,7 +13535,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00398659706116</v>
+        <v>3.00398683547974</v>
       </c>
       <c r="H454" t="n">
         <v>359122</v>
@@ -13564,7 +13564,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G455" t="n">
-        <v>2.99737310409546</v>
+        <v>2.99737334251404</v>
       </c>
       <c r="H455" t="n">
         <v>614167</v>
@@ -13593,7 +13593,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>2.99605059623718</v>
+        <v>2.99605083465576</v>
       </c>
       <c r="H456" t="n">
         <v>373559</v>
@@ -13738,7 +13738,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94710803031921</v>
+        <v>2.94710826873779</v>
       </c>
       <c r="H461" t="n">
         <v>1603800</v>
@@ -13883,7 +13883,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>2.89494681358337</v>
+        <v>2.89494657516479</v>
       </c>
       <c r="H466" t="n">
         <v>816758</v>
@@ -14086,7 +14086,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G473" t="n">
-        <v>2.86454629898071</v>
+        <v>2.86454606056213</v>
       </c>
       <c r="H473" t="n">
         <v>617354</v>
@@ -14144,7 +14144,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G475" t="n">
-        <v>2.86454629898071</v>
+        <v>2.86454606056213</v>
       </c>
       <c r="H475" t="n">
         <v>676249</v>
@@ -14231,7 +14231,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>2.79130887985229</v>
+        <v>2.79130911827087</v>
       </c>
       <c r="H478" t="n">
         <v>484051</v>
@@ -14405,7 +14405,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G484" t="n">
-        <v>2.96542048454285</v>
+        <v>2.96542024612427</v>
       </c>
       <c r="H484" t="n">
         <v>1196522</v>
@@ -14550,7 +14550,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.97371125221252</v>
+        <v>2.9737114906311</v>
       </c>
       <c r="H489" t="n">
         <v>488412</v>
@@ -14579,7 +14579,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G490" t="n">
-        <v>3.0234580039978</v>
+        <v>3.02345776557922</v>
       </c>
       <c r="H490" t="n">
         <v>692474</v>
@@ -14608,7 +14608,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>2.9778573513031</v>
+        <v>2.97785711288452</v>
       </c>
       <c r="H491" t="n">
         <v>736849</v>
@@ -14637,7 +14637,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>2.95989346504211</v>
+        <v>2.95989322662354</v>
       </c>
       <c r="H492" t="n">
         <v>427110</v>
@@ -14811,7 +14811,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G498" t="n">
-        <v>3.03036665916443</v>
+        <v>3.03036689758301</v>
       </c>
       <c r="H498" t="n">
         <v>620501</v>
@@ -14869,7 +14869,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G500" t="n">
-        <v>2.97923874855042</v>
+        <v>2.97923922538757</v>
       </c>
       <c r="H500" t="n">
         <v>1148402</v>
@@ -14927,7 +14927,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G502" t="n">
-        <v>2.95851135253906</v>
+        <v>2.95851159095764</v>
       </c>
       <c r="H502" t="n">
         <v>717824</v>
@@ -15101,7 +15101,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G508" t="n">
-        <v>3.14229536056519</v>
+        <v>3.14229559898376</v>
       </c>
       <c r="H508" t="n">
         <v>516954</v>
@@ -15130,7 +15130,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G509" t="n">
-        <v>3.08840394020081</v>
+        <v>3.08840370178223</v>
       </c>
       <c r="H509" t="n">
         <v>334744</v>
@@ -15159,7 +15159,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G510" t="n">
-        <v>3.07182216644287</v>
+        <v>3.07182192802429</v>
       </c>
       <c r="H510" t="n">
         <v>253760</v>
@@ -15304,7 +15304,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G515" t="n">
-        <v>3.04418563842773</v>
+        <v>3.04418540000916</v>
       </c>
       <c r="H515" t="n">
         <v>485465</v>
@@ -15449,7 +15449,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G520" t="n">
-        <v>3.03036665916443</v>
+        <v>3.03036689758301</v>
       </c>
       <c r="H520" t="n">
         <v>232235</v>
@@ -15478,7 +15478,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G521" t="n">
-        <v>3.0234580039978</v>
+        <v>3.02345776557922</v>
       </c>
       <c r="H521" t="n">
         <v>343913</v>
@@ -15507,7 +15507,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H522" t="n">
         <v>255665</v>
@@ -15565,7 +15565,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G524" t="n">
-        <v>2.99305725097656</v>
+        <v>2.99305701255798</v>
       </c>
       <c r="H524" t="n">
         <v>1167836</v>
@@ -15594,7 +15594,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G525" t="n">
-        <v>2.99582099914551</v>
+        <v>2.99582123756409</v>
       </c>
       <c r="H525" t="n">
         <v>364917</v>
@@ -15710,7 +15710,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G529" t="n">
-        <v>2.91982007026672</v>
+        <v>2.91981983184814</v>
       </c>
       <c r="H529" t="n">
         <v>295775</v>
@@ -15797,7 +15797,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G532" t="n">
-        <v>2.93087434768677</v>
+        <v>2.93087458610535</v>
       </c>
       <c r="H532" t="n">
         <v>357082</v>
@@ -15855,7 +15855,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G534" t="n">
-        <v>2.87283754348755</v>
+        <v>2.87283730506897</v>
       </c>
       <c r="H534" t="n">
         <v>449592</v>
@@ -15884,7 +15884,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94607496261597</v>
+        <v>2.94607472419739</v>
       </c>
       <c r="H535" t="n">
         <v>538665</v>
@@ -15942,7 +15942,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94192910194397</v>
+        <v>2.94192934036255</v>
       </c>
       <c r="H537" t="n">
         <v>572190</v>
@@ -15971,7 +15971,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G538" t="n">
-        <v>2.94607496261597</v>
+        <v>2.94607472419739</v>
       </c>
       <c r="H538" t="n">
         <v>458621</v>
@@ -16029,7 +16029,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>2.91152906417847</v>
+        <v>2.91152882575989</v>
       </c>
       <c r="H540" t="n">
         <v>588609</v>
@@ -16058,7 +16058,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.92811107635498</v>
+        <v>2.9281108379364</v>
       </c>
       <c r="H541" t="n">
         <v>404056</v>
@@ -16087,7 +16087,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G542" t="n">
-        <v>2.95989346504211</v>
+        <v>2.95989322662354</v>
       </c>
       <c r="H542" t="n">
         <v>542766</v>
@@ -16145,7 +16145,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>2.99167537689209</v>
+        <v>2.99167513847351</v>
       </c>
       <c r="H544" t="n">
         <v>338875</v>
@@ -16203,7 +16203,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97371125221252</v>
+        <v>2.9737114906311</v>
       </c>
       <c r="H546" t="n">
         <v>335573</v>
@@ -16232,7 +16232,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06491279602051</v>
+        <v>3.06491255760193</v>
       </c>
       <c r="H547" t="n">
         <v>681594</v>
@@ -16261,7 +16261,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G548" t="n">
-        <v>3.00134801864624</v>
+        <v>3.00134825706482</v>
       </c>
       <c r="H548" t="n">
         <v>523849</v>
@@ -16464,7 +16464,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G555" t="n">
-        <v>2.95298409461975</v>
+        <v>2.95298433303833</v>
       </c>
       <c r="H555" t="n">
         <v>212164</v>
@@ -16551,7 +16551,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G558" t="n">
-        <v>2.89632892608643</v>
+        <v>2.89632868766785</v>
       </c>
       <c r="H558" t="n">
         <v>319927</v>
@@ -16609,7 +16609,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G560" t="n">
-        <v>2.87007403373718</v>
+        <v>2.8700737953186</v>
       </c>
       <c r="H560" t="n">
         <v>244609</v>
@@ -16638,7 +16638,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>2.84658265113831</v>
+        <v>2.84658241271973</v>
       </c>
       <c r="H561" t="n">
         <v>476726</v>
@@ -16667,7 +16667,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G562" t="n">
-        <v>2.8134183883667</v>
+        <v>2.81341862678528</v>
       </c>
       <c r="H562" t="n">
         <v>864736</v>
@@ -16696,7 +16696,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G563" t="n">
-        <v>2.76090908050537</v>
+        <v>2.76090884208679</v>
       </c>
       <c r="H563" t="n">
         <v>625996</v>
@@ -16725,7 +16725,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G564" t="n">
-        <v>2.78440022468567</v>
+        <v>2.78439998626709</v>
       </c>
       <c r="H564" t="n">
         <v>960404</v>
@@ -16870,7 +16870,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77749085426331</v>
+        <v>2.77749061584473</v>
       </c>
       <c r="H569" t="n">
         <v>246177</v>
@@ -16899,7 +16899,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G570" t="n">
-        <v>2.7332718372345</v>
+        <v>2.73327207565308</v>
       </c>
       <c r="H570" t="n">
         <v>306755</v>
@@ -16957,7 +16957,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G572" t="n">
-        <v>2.77749085426331</v>
+        <v>2.77749061584473</v>
       </c>
       <c r="H572" t="n">
         <v>457593</v>
@@ -16986,7 +16986,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G573" t="n">
-        <v>2.76505398750305</v>
+        <v>2.76505422592163</v>
       </c>
       <c r="H573" t="n">
         <v>274810</v>
@@ -17015,7 +17015,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>2.74985384941101</v>
+        <v>2.74985408782959</v>
       </c>
       <c r="H574" t="n">
         <v>474610</v>
@@ -17218,7 +17218,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77749085426331</v>
+        <v>2.77749061584473</v>
       </c>
       <c r="H581" t="n">
         <v>202226</v>
@@ -17247,7 +17247,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74985384941101</v>
+        <v>2.74985408782959</v>
       </c>
       <c r="H582" t="n">
         <v>296696</v>
@@ -17305,7 +17305,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>2.72221755981445</v>
+        <v>2.72221732139587</v>
       </c>
       <c r="H584" t="n">
         <v>349909</v>
@@ -17537,7 +17537,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G592" t="n">
-        <v>2.84243702888489</v>
+        <v>2.84243679046631</v>
       </c>
       <c r="H592" t="n">
         <v>810244</v>
@@ -17566,7 +17566,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>2.89494681358337</v>
+        <v>2.89494657516479</v>
       </c>
       <c r="H593" t="n">
         <v>529768</v>
@@ -17624,7 +17624,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G595" t="n">
-        <v>2.83552765846252</v>
+        <v>2.8355278968811</v>
       </c>
       <c r="H595" t="n">
         <v>625694</v>
@@ -17653,7 +17653,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G596" t="n">
-        <v>2.86040091514587</v>
+        <v>2.86040115356445</v>
       </c>
       <c r="H596" t="n">
         <v>1036090</v>
@@ -17740,7 +17740,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G599" t="n">
-        <v>2.91014695167542</v>
+        <v>2.91014719009399</v>
       </c>
       <c r="H599" t="n">
         <v>1120884</v>
@@ -17769,7 +17769,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G600" t="n">
-        <v>2.89909243583679</v>
+        <v>2.89909267425537</v>
       </c>
       <c r="H600" t="n">
         <v>744183</v>
@@ -18088,7 +18088,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G611" t="n">
-        <v>2.91152906417847</v>
+        <v>2.91152882575989</v>
       </c>
       <c r="H611" t="n">
         <v>402937</v>
@@ -18146,7 +18146,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>2.87421917915344</v>
+        <v>2.87421894073486</v>
       </c>
       <c r="H613" t="n">
         <v>527133</v>
@@ -18204,7 +18204,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G615" t="n">
-        <v>2.86454629898071</v>
+        <v>2.86454606056213</v>
       </c>
       <c r="H615" t="n">
         <v>695451</v>
@@ -18262,7 +18262,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G617" t="n">
-        <v>2.89632892608643</v>
+        <v>2.89632868766785</v>
       </c>
       <c r="H617" t="n">
         <v>507785</v>
@@ -18320,7 +18320,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G619" t="n">
-        <v>2.93087434768677</v>
+        <v>2.93087458610535</v>
       </c>
       <c r="H619" t="n">
         <v>258418</v>
@@ -18349,7 +18349,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G620" t="n">
-        <v>2.89909243583679</v>
+        <v>2.89909267425537</v>
       </c>
       <c r="H620" t="n">
         <v>492515</v>
@@ -18407,7 +18407,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G622" t="n">
-        <v>2.98338413238525</v>
+        <v>2.98338389396667</v>
       </c>
       <c r="H622" t="n">
         <v>557576</v>
@@ -18523,7 +18523,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H626" t="n">
         <v>1249599</v>
@@ -18726,7 +18726,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G633" t="n">
-        <v>3.03313040733337</v>
+        <v>3.03313016891479</v>
       </c>
       <c r="H633" t="n">
         <v>428715</v>
@@ -18755,7 +18755,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G634" t="n">
-        <v>3.03036665916443</v>
+        <v>3.03036689758301</v>
       </c>
       <c r="H634" t="n">
         <v>523810</v>
@@ -18813,7 +18813,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H636" t="n">
         <v>165327</v>
@@ -18900,7 +18900,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>3.08287644386292</v>
+        <v>3.08287620544434</v>
       </c>
       <c r="H639" t="n">
         <v>455246</v>
@@ -18929,7 +18929,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G640" t="n">
-        <v>3.08011317253113</v>
+        <v>3.08011341094971</v>
       </c>
       <c r="H640" t="n">
         <v>539646</v>
@@ -18958,7 +18958,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G641" t="n">
-        <v>3.08840394020081</v>
+        <v>3.08840370178223</v>
       </c>
       <c r="H641" t="n">
         <v>313925</v>
@@ -18987,7 +18987,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H642" t="n">
         <v>690661</v>
@@ -19103,7 +19103,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G646" t="n">
-        <v>3.14229536056519</v>
+        <v>3.14229559898376</v>
       </c>
       <c r="H646" t="n">
         <v>601188</v>
@@ -19132,7 +19132,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G647" t="n">
-        <v>3.06629514694214</v>
+        <v>3.06629467010498</v>
       </c>
       <c r="H647" t="n">
         <v>369408</v>
@@ -19364,7 +19364,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G655" t="n">
-        <v>3.11742258071899</v>
+        <v>3.11742234230042</v>
       </c>
       <c r="H655" t="n">
         <v>774559</v>
@@ -19422,7 +19422,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G657" t="n">
-        <v>3.08840394020081</v>
+        <v>3.08840370178223</v>
       </c>
       <c r="H657" t="n">
         <v>649670</v>
@@ -19451,7 +19451,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G658" t="n">
-        <v>3.08840394020081</v>
+        <v>3.08840370178223</v>
       </c>
       <c r="H658" t="n">
         <v>463243</v>
@@ -19509,7 +19509,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>3.11189532279968</v>
+        <v>3.1118950843811</v>
       </c>
       <c r="H660" t="n">
         <v>464575</v>
@@ -19567,7 +19567,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13814949989319</v>
+        <v>3.13814973831177</v>
       </c>
       <c r="H662" t="n">
         <v>519012</v>
@@ -19596,7 +19596,7 @@
         <v>4.55399990081787</v>
       </c>
       <c r="G663" t="n">
-        <v>3.1464409828186</v>
+        <v>3.14644145965576</v>
       </c>
       <c r="H663" t="n">
         <v>546629</v>
@@ -19683,7 +19683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G666" t="n">
-        <v>3.10222220420837</v>
+        <v>3.10222244262695</v>
       </c>
       <c r="H666" t="n">
         <v>406879</v>
@@ -19741,7 +19741,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G668" t="n">
-        <v>3.10222220420837</v>
+        <v>3.10222244262695</v>
       </c>
       <c r="H668" t="n">
         <v>802632</v>
@@ -19770,7 +19770,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G669" t="n">
-        <v>3.26251530647278</v>
+        <v>3.26251554489136</v>
       </c>
       <c r="H669" t="n">
         <v>2348370</v>
@@ -19828,7 +19828,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>3.34542560577393</v>
+        <v>3.34542536735535</v>
       </c>
       <c r="H671" t="n">
         <v>836124</v>
@@ -19915,7 +19915,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38411688804626</v>
+        <v>3.38411641120911</v>
       </c>
       <c r="H674" t="n">
         <v>577089</v>
@@ -19973,7 +19973,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G676" t="n">
-        <v>3.37997174263</v>
+        <v>3.37997126579285</v>
       </c>
       <c r="H676" t="n">
         <v>299664</v>
@@ -20002,7 +20002,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>3.34542560577393</v>
+        <v>3.34542536735535</v>
       </c>
       <c r="H677" t="n">
         <v>220591</v>
@@ -20031,7 +20031,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>3.30535197257996</v>
+        <v>3.30535173416138</v>
       </c>
       <c r="H678" t="n">
         <v>478581</v>
@@ -20176,7 +20176,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G683" t="n">
-        <v>3.37858963012695</v>
+        <v>3.37858915328979</v>
       </c>
       <c r="H683" t="n">
         <v>448925</v>
@@ -20321,7 +20321,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G688" t="n">
-        <v>3.32469749450684</v>
+        <v>3.32469773292542</v>
       </c>
       <c r="H688" t="n">
         <v>384931</v>
@@ -20350,7 +20350,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G689" t="n">
-        <v>3.28047919273376</v>
+        <v>3.28047966957092</v>
       </c>
       <c r="H689" t="n">
         <v>367827</v>
@@ -20379,7 +20379,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G690" t="n">
-        <v>3.29015207290649</v>
+        <v>3.29015183448792</v>
       </c>
       <c r="H690" t="n">
         <v>515539</v>
@@ -20437,7 +20437,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G692" t="n">
-        <v>3.31087946891785</v>
+        <v>3.31087923049927</v>
       </c>
       <c r="H692" t="n">
         <v>270176</v>
@@ -20466,7 +20466,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G693" t="n">
-        <v>3.35371661186218</v>
+        <v>3.35371613502502</v>
       </c>
       <c r="H693" t="n">
         <v>275517</v>
@@ -20495,7 +20495,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G694" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957075119019</v>
       </c>
       <c r="H694" t="n">
         <v>378541</v>
@@ -20524,7 +20524,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G695" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957075119019</v>
       </c>
       <c r="H695" t="n">
         <v>334779</v>
@@ -20640,7 +20640,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.32331609725952</v>
+        <v>3.32331562042236</v>
       </c>
       <c r="H699" t="n">
         <v>272666</v>
@@ -20669,7 +20669,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G700" t="n">
-        <v>3.31364297866821</v>
+        <v>3.31364345550537</v>
       </c>
       <c r="H700" t="n">
         <v>621856</v>
@@ -20814,7 +20814,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G705" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957075119019</v>
       </c>
       <c r="H705" t="n">
         <v>215533</v>
@@ -20843,7 +20843,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G706" t="n">
-        <v>3.38273501396179</v>
+        <v>3.38273453712463</v>
       </c>
       <c r="H706" t="n">
         <v>370437</v>
@@ -20872,7 +20872,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G707" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957075119019</v>
       </c>
       <c r="H707" t="n">
         <v>440703</v>
@@ -20930,7 +20930,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G709" t="n">
-        <v>3.3343710899353</v>
+        <v>3.33437061309814</v>
       </c>
       <c r="H709" t="n">
         <v>886827</v>
@@ -20959,7 +20959,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G710" t="n">
-        <v>3.32469749450684</v>
+        <v>3.32469773292542</v>
       </c>
       <c r="H710" t="n">
         <v>248745</v>
@@ -20988,7 +20988,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>3.38549876213074</v>
+        <v>3.38549828529358</v>
       </c>
       <c r="H711" t="n">
         <v>312454</v>
@@ -21133,7 +21133,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G716" t="n">
-        <v>3.44507884979248</v>
+        <v>3.44507837295532</v>
       </c>
       <c r="H716" t="n">
         <v>338239</v>
@@ -21162,7 +21162,7 @@
         <v>4.80800008773804</v>
       </c>
       <c r="G717" t="n">
-        <v>3.46380996704102</v>
+        <v>3.46381044387817</v>
       </c>
       <c r="H717" t="n">
         <v>205826</v>
@@ -21191,7 +21191,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G718" t="n">
-        <v>3.46236896514893</v>
+        <v>3.46236944198608</v>
       </c>
       <c r="H718" t="n">
         <v>296407</v>
@@ -21365,7 +21365,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>3.49406814575195</v>
+        <v>3.49406766891479</v>
       </c>
       <c r="H724" t="n">
         <v>1001017</v>
@@ -21423,7 +21423,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G726" t="n">
-        <v>3.57475543022156</v>
+        <v>3.57475590705872</v>
       </c>
       <c r="H726" t="n">
         <v>985537</v>
@@ -21597,7 +21597,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>3.63455080986023</v>
+        <v>3.63455104827881</v>
       </c>
       <c r="H732" t="n">
         <v>418405</v>
@@ -21626,7 +21626,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>3.70659327507019</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H733" t="n">
         <v>827997</v>
@@ -21858,7 +21858,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G741" t="n">
-        <v>3.62374448776245</v>
+        <v>3.62374496459961</v>
       </c>
       <c r="H741" t="n">
         <v>214957</v>
@@ -21916,7 +21916,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.54449796676636</v>
+        <v>3.54449772834778</v>
       </c>
       <c r="H743" t="n">
         <v>449069</v>
@@ -22003,7 +22003,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>3.54449796676636</v>
+        <v>3.54449772834778</v>
       </c>
       <c r="H746" t="n">
         <v>1059414</v>
@@ -22032,7 +22032,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G747" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H747" t="n">
         <v>607759</v>
@@ -22061,7 +22061,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G748" t="n">
-        <v>3.59925007820129</v>
+        <v>3.59924983978271</v>
       </c>
       <c r="H748" t="n">
         <v>415115</v>
@@ -22090,7 +22090,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G749" t="n">
-        <v>3.57619643211365</v>
+        <v>3.57619619369507</v>
       </c>
       <c r="H749" t="n">
         <v>582111</v>
@@ -22119,7 +22119,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G750" t="n">
-        <v>3.57763767242432</v>
+        <v>3.57763743400574</v>
       </c>
       <c r="H750" t="n">
         <v>333644</v>
@@ -22206,7 +22206,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.62014293670654</v>
+        <v>3.62014245986938</v>
       </c>
       <c r="H753" t="n">
         <v>353573</v>
@@ -22235,7 +22235,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G754" t="n">
-        <v>3.59780955314636</v>
+        <v>3.5978090763092</v>
       </c>
       <c r="H754" t="n">
         <v>281615</v>
@@ -22380,7 +22380,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H759" t="n">
         <v>333042</v>
@@ -22467,7 +22467,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G762" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H762" t="n">
         <v>233504</v>
@@ -22583,7 +22583,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G766" t="n">
-        <v>3.57619643211365</v>
+        <v>3.57619619369507</v>
       </c>
       <c r="H766" t="n">
         <v>852645</v>
@@ -22641,7 +22641,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G768" t="n">
-        <v>3.62374448776245</v>
+        <v>3.62374496459961</v>
       </c>
       <c r="H768" t="n">
         <v>430153</v>
@@ -22757,7 +22757,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G772" t="n">
-        <v>3.67057251930237</v>
+        <v>3.67057204246521</v>
       </c>
       <c r="H772" t="n">
         <v>490175</v>
@@ -22844,7 +22844,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G775" t="n">
-        <v>3.66696977615356</v>
+        <v>3.66697025299072</v>
       </c>
       <c r="H775" t="n">
         <v>116327</v>
@@ -22873,7 +22873,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G776" t="n">
-        <v>3.70659327507019</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H776" t="n">
         <v>535968</v>
@@ -22902,7 +22902,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G777" t="n">
-        <v>3.70659327507019</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H777" t="n">
         <v>394359</v>
@@ -23018,7 +23018,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>3.76782965660095</v>
+        <v>3.76783013343811</v>
       </c>
       <c r="H781" t="n">
         <v>213433</v>
@@ -23076,7 +23076,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.71379828453064</v>
+        <v>3.71379780769348</v>
       </c>
       <c r="H783" t="n">
         <v>188130</v>
@@ -23105,7 +23105,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>3.71379828453064</v>
+        <v>3.71379780769348</v>
       </c>
       <c r="H784" t="n">
         <v>217194</v>
@@ -23221,7 +23221,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G788" t="n">
-        <v>3.70299172401428</v>
+        <v>3.70299124717712</v>
       </c>
       <c r="H788" t="n">
         <v>296476</v>
@@ -23250,7 +23250,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>3.72100234031677</v>
+        <v>3.72100210189819</v>
       </c>
       <c r="H789" t="n">
         <v>115274</v>
@@ -23308,7 +23308,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>3.72100234031677</v>
+        <v>3.72100210189819</v>
       </c>
       <c r="H791" t="n">
         <v>202767</v>
@@ -23337,7 +23337,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.71739959716797</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H792" t="n">
         <v>225935</v>
@@ -23366,7 +23366,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G793" t="n">
-        <v>3.70299172401428</v>
+        <v>3.70299124717712</v>
       </c>
       <c r="H793" t="n">
         <v>262081</v>
@@ -23395,7 +23395,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G794" t="n">
-        <v>3.67417407035828</v>
+        <v>3.67417430877686</v>
       </c>
       <c r="H794" t="n">
         <v>251245</v>
@@ -23424,7 +23424,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.64175486564636</v>
+        <v>3.64175534248352</v>
       </c>
       <c r="H795" t="n">
         <v>413188</v>
@@ -23453,7 +23453,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>3.62014293670654</v>
+        <v>3.62014245986938</v>
       </c>
       <c r="H796" t="n">
         <v>385770</v>
@@ -23656,7 +23656,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>3.66696977615356</v>
+        <v>3.66697025299072</v>
       </c>
       <c r="H803" t="n">
         <v>178529</v>
@@ -23685,7 +23685,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.67417407035828</v>
+        <v>3.67417430877686</v>
       </c>
       <c r="H804" t="n">
         <v>184382</v>
@@ -23743,7 +23743,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.67057251930237</v>
+        <v>3.67057204246521</v>
       </c>
       <c r="H806" t="n">
         <v>358329</v>
@@ -23801,7 +23801,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G808" t="n">
-        <v>3.67057251930237</v>
+        <v>3.67057204246521</v>
       </c>
       <c r="H808" t="n">
         <v>272752</v>
@@ -23859,7 +23859,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.7354109287262</v>
+        <v>3.73541045188904</v>
       </c>
       <c r="H810" t="n">
         <v>395323</v>
@@ -24120,7 +24120,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342130661011</v>
       </c>
       <c r="H819" t="n">
         <v>228708</v>
@@ -24149,7 +24149,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>3.74981880187988</v>
+        <v>3.74981904029846</v>
       </c>
       <c r="H820" t="n">
         <v>270294</v>
@@ -24236,7 +24236,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>3.76782965660095</v>
+        <v>3.76783013343811</v>
       </c>
       <c r="H823" t="n">
         <v>438530</v>
@@ -24294,7 +24294,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342130661011</v>
       </c>
       <c r="H825" t="n">
         <v>242523</v>
@@ -24352,7 +24352,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G827" t="n">
-        <v>3.69938898086548</v>
+        <v>3.69938945770264</v>
       </c>
       <c r="H827" t="n">
         <v>236994</v>
@@ -24381,7 +24381,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G828" t="n">
-        <v>3.70299172401428</v>
+        <v>3.70299124717712</v>
       </c>
       <c r="H828" t="n">
         <v>168676</v>
@@ -24526,7 +24526,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584051132202</v>
       </c>
       <c r="H833" t="n">
         <v>158358</v>
@@ -24642,7 +24642,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342130661011</v>
       </c>
       <c r="H837" t="n">
         <v>261649</v>
@@ -24729,7 +24729,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584051132202</v>
       </c>
       <c r="H840" t="n">
         <v>309517</v>
@@ -24816,7 +24816,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148548126221</v>
+        <v>3.86148500442505</v>
       </c>
       <c r="H843" t="n">
         <v>518806</v>
@@ -24903,7 +24903,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664659500122</v>
       </c>
       <c r="H846" t="n">
         <v>882140</v>
@@ -24932,7 +24932,7 @@
         <v>5.25</v>
       </c>
       <c r="G847" t="n">
-        <v>3.78223824501038</v>
+        <v>3.78223872184753</v>
       </c>
       <c r="H847" t="n">
         <v>330835</v>
@@ -24990,7 +24990,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G849" t="n">
-        <v>3.78944277763367</v>
+        <v>3.78944325447083</v>
       </c>
       <c r="H849" t="n">
         <v>309778</v>
@@ -25019,7 +25019,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G850" t="n">
-        <v>3.86508703231812</v>
+        <v>3.86508750915527</v>
       </c>
       <c r="H850" t="n">
         <v>585661</v>
@@ -25048,7 +25048,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>3.82906603813171</v>
+        <v>3.82906556129456</v>
       </c>
       <c r="H851" t="n">
         <v>1005431</v>
@@ -25106,7 +25106,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G853" t="n">
-        <v>3.87589311599731</v>
+        <v>3.87589359283447</v>
       </c>
       <c r="H853" t="n">
         <v>449570</v>
@@ -25135,7 +25135,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80024862289429</v>
+        <v>3.80024909973145</v>
       </c>
       <c r="H854" t="n">
         <v>521291</v>
@@ -25164,7 +25164,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664659500122</v>
       </c>
       <c r="H855" t="n">
         <v>531608</v>
@@ -25193,7 +25193,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80024862289429</v>
+        <v>3.80024909973145</v>
       </c>
       <c r="H856" t="n">
         <v>340183</v>
@@ -25222,7 +25222,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G857" t="n">
-        <v>3.80385184288025</v>
+        <v>3.80385136604309</v>
       </c>
       <c r="H857" t="n">
         <v>236744</v>
@@ -25251,7 +25251,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80024862289429</v>
+        <v>3.80024909973145</v>
       </c>
       <c r="H858" t="n">
         <v>247892</v>
@@ -25309,7 +25309,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>3.83627033233643</v>
+        <v>3.83626985549927</v>
       </c>
       <c r="H860" t="n">
         <v>202317</v>
@@ -25338,7 +25338,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>3.84707689285278</v>
+        <v>3.84707641601562</v>
       </c>
       <c r="H861" t="n">
         <v>142215</v>
@@ -25367,7 +25367,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G862" t="n">
-        <v>3.83266854286194</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H862" t="n">
         <v>423140</v>
@@ -25425,7 +25425,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664659500122</v>
       </c>
       <c r="H864" t="n">
         <v>272878</v>
@@ -25599,7 +25599,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.88309788703918</v>
+        <v>3.88309836387634</v>
       </c>
       <c r="H870" t="n">
         <v>376869</v>
@@ -25628,7 +25628,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G871" t="n">
-        <v>3.83266854286194</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H871" t="n">
         <v>429811</v>
@@ -25657,7 +25657,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91191482543945</v>
+        <v>3.91191434860229</v>
       </c>
       <c r="H872" t="n">
         <v>627265</v>
@@ -25686,7 +25686,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>3.83627033233643</v>
+        <v>3.83626985549927</v>
       </c>
       <c r="H873" t="n">
         <v>626080</v>
@@ -25715,7 +25715,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>3.80024862289429</v>
+        <v>3.80024909973145</v>
       </c>
       <c r="H874" t="n">
         <v>558719</v>
@@ -25744,7 +25744,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>3.83266854286194</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H875" t="n">
         <v>683792</v>
@@ -25773,7 +25773,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G876" t="n">
-        <v>3.91191482543945</v>
+        <v>3.91191434860229</v>
       </c>
       <c r="H876" t="n">
         <v>933919</v>
@@ -25802,7 +25802,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91191482543945</v>
+        <v>3.91191434860229</v>
       </c>
       <c r="H877" t="n">
         <v>497300</v>
@@ -25831,7 +25831,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G878" t="n">
-        <v>3.92632293701172</v>
+        <v>3.92632341384888</v>
       </c>
       <c r="H878" t="n">
         <v>368905</v>
@@ -25860,7 +25860,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G879" t="n">
-        <v>3.95874238014221</v>
+        <v>3.95874285697937</v>
       </c>
       <c r="H879" t="n">
         <v>433161</v>
@@ -25889,7 +25889,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99836659431458</v>
+        <v>3.99836707115173</v>
       </c>
       <c r="H880" t="n">
         <v>518932</v>
@@ -25976,7 +25976,7 @@
         <v>5.625</v>
       </c>
       <c r="G883" t="n">
-        <v>4.05239772796631</v>
+        <v>4.05239820480347</v>
       </c>
       <c r="H883" t="n">
         <v>369585</v>
@@ -26005,7 +26005,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>4.07040882110596</v>
+        <v>4.0704083442688</v>
       </c>
       <c r="H884" t="n">
         <v>239745</v>
@@ -26063,7 +26063,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>4.08841943740845</v>
+        <v>4.08841896057129</v>
       </c>
       <c r="H886" t="n">
         <v>668689</v>
@@ -26121,7 +26121,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>4.21809577941895</v>
+        <v>4.2180962562561</v>
       </c>
       <c r="H888" t="n">
         <v>1316501</v>
@@ -26266,7 +26266,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G893" t="n">
-        <v>4.19648361206055</v>
+        <v>4.19648313522339</v>
       </c>
       <c r="H893" t="n">
         <v>718224</v>
@@ -26701,7 +26701,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>4.35497760772705</v>
+        <v>4.35497808456421</v>
       </c>
       <c r="H908" t="n">
         <v>758622</v>
@@ -26962,7 +26962,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.71739959716797</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H917" t="n">
         <v>905147</v>
@@ -27136,7 +27136,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G923" t="n">
-        <v>2.8658561706543</v>
+        <v>2.86585593223572</v>
       </c>
       <c r="H923" t="n">
         <v>2005867</v>
@@ -27252,7 +27252,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G927" t="n">
-        <v>2.58921217918396</v>
+        <v>2.58921241760254</v>
       </c>
       <c r="H927" t="n">
         <v>1414173</v>
@@ -27281,7 +27281,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G928" t="n">
-        <v>2.52437400817871</v>
+        <v>2.52437376976013</v>
       </c>
       <c r="H928" t="n">
         <v>823310</v>
@@ -27339,7 +27339,7 @@
         <v>3.5</v>
       </c>
       <c r="G930" t="n">
-        <v>2.52149224281311</v>
+        <v>2.52149200439453</v>
       </c>
       <c r="H930" t="n">
         <v>1518410</v>
@@ -27368,7 +27368,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G931" t="n">
-        <v>2.6108250617981</v>
+        <v>2.61082530021667</v>
       </c>
       <c r="H931" t="n">
         <v>1059073</v>
@@ -27629,7 +27629,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96815657615662</v>
+        <v>2.96815633773804</v>
       </c>
       <c r="H940" t="n">
         <v>1265202</v>
@@ -27687,7 +27687,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>3.02579021453857</v>
+        <v>3.02579045295715</v>
       </c>
       <c r="H942" t="n">
         <v>878459</v>
@@ -27716,7 +27716,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G943" t="n">
-        <v>3.02579021453857</v>
+        <v>3.02579045295715</v>
       </c>
       <c r="H943" t="n">
         <v>717288</v>
@@ -27919,7 +27919,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G950" t="n">
-        <v>2.91772699356079</v>
+        <v>2.91772675514221</v>
       </c>
       <c r="H950" t="n">
         <v>718280</v>
@@ -27977,7 +27977,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G952" t="n">
-        <v>2.9047589302063</v>
+        <v>2.90475916862488</v>
       </c>
       <c r="H952" t="n">
         <v>422359</v>
@@ -28180,7 +28180,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G959" t="n">
-        <v>2.79237222671509</v>
+        <v>2.79237246513367</v>
       </c>
       <c r="H959" t="n">
         <v>343820</v>
@@ -28267,7 +28267,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G962" t="n">
-        <v>2.78804993629456</v>
+        <v>2.78804969787598</v>
       </c>
       <c r="H962" t="n">
         <v>543234</v>
@@ -28325,7 +28325,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G964" t="n">
-        <v>2.75346946716309</v>
+        <v>2.75346970558167</v>
       </c>
       <c r="H964" t="n">
         <v>407303</v>
@@ -75905,7 +75905,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="D2605" t="n">
-        <v>5.02500009536743</v>
+        <v>5.03000020980835</v>
       </c>
       <c r="E2605" t="n">
         <v>4.95599985122681</v>
@@ -75920,6 +75920,35 @@
         <v>396172</v>
       </c>
       <c r="I2605" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2606" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2606" t="n">
+        <v>4.96600008010864</v>
+      </c>
+      <c r="D2606" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E2606" t="n">
+        <v>4.96600008010864</v>
+      </c>
+      <c r="F2606" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2606" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2606" t="n">
+        <v>332767</v>
+      </c>
+      <c r="I2606" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.30103898048401</v>
+        <v>2.30103921890259</v>
       </c>
       <c r="H2" t="n">
         <v>73776221</v>
@@ -456,7 +456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.30103898048401</v>
+        <v>2.30103921890259</v>
       </c>
       <c r="H3" t="n">
         <v>8746746</v>
@@ -485,7 +485,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26321387290955</v>
+        <v>2.26321339607239</v>
       </c>
       <c r="H4" t="n">
         <v>8182968</v>
@@ -514,7 +514,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24304032325745</v>
+        <v>2.24304008483887</v>
       </c>
       <c r="H5" t="n">
         <v>6798460</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>2.33256006240845</v>
+        <v>2.33256030082703</v>
       </c>
       <c r="H7" t="n">
         <v>3592063</v>
@@ -601,7 +601,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33256006240845</v>
+        <v>2.33256030082703</v>
       </c>
       <c r="H8" t="n">
         <v>2256529</v>
@@ -630,7 +630,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38677644729614</v>
+        <v>2.38677620887756</v>
       </c>
       <c r="H9" t="n">
         <v>3631224</v>
@@ -659,7 +659,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33886408805847</v>
+        <v>2.33886432647705</v>
       </c>
       <c r="H10" t="n">
         <v>883891</v>
@@ -688,7 +688,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33886408805847</v>
+        <v>2.33886432647705</v>
       </c>
       <c r="H11" t="n">
         <v>2186928</v>
@@ -804,7 +804,7 @@
         <v>3.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36408114433289</v>
+        <v>2.36408090591431</v>
       </c>
       <c r="H15" t="n">
         <v>910155</v>
@@ -833,7 +833,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>2.30734348297119</v>
+        <v>2.30734300613403</v>
       </c>
       <c r="H16" t="n">
         <v>1485896</v>
@@ -891,7 +891,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G18" t="n">
-        <v>2.30734348297119</v>
+        <v>2.30734300613403</v>
       </c>
       <c r="H18" t="n">
         <v>911844</v>
@@ -920,7 +920,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29599571228027</v>
+        <v>2.29599547386169</v>
       </c>
       <c r="H19" t="n">
         <v>853812</v>
@@ -978,7 +978,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28590846061707</v>
+        <v>2.28590869903564</v>
       </c>
       <c r="H21" t="n">
         <v>1248337</v>
@@ -1007,7 +1007,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29725623130798</v>
+        <v>2.29725646972656</v>
       </c>
       <c r="H22" t="n">
         <v>1078374</v>
@@ -1036,7 +1036,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.30103898048401</v>
+        <v>2.30103921890259</v>
       </c>
       <c r="H23" t="n">
         <v>972167</v>
@@ -1094,7 +1094,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877707481384</v>
       </c>
       <c r="H25" t="n">
         <v>276607</v>
@@ -1123,7 +1123,7 @@
         <v>3.75</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36408114433289</v>
+        <v>2.36408090591431</v>
       </c>
       <c r="H26" t="n">
         <v>594438</v>
@@ -1181,7 +1181,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G28" t="n">
-        <v>2.37542867660522</v>
+        <v>2.37542843818665</v>
       </c>
       <c r="H28" t="n">
         <v>1425652</v>
@@ -1210,7 +1210,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G29" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H29" t="n">
         <v>796842</v>
@@ -1239,7 +1239,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H30" t="n">
         <v>934202</v>
@@ -1268,7 +1268,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G31" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H31" t="n">
         <v>738518</v>
@@ -1326,7 +1326,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877707481384</v>
       </c>
       <c r="H33" t="n">
         <v>635450</v>
@@ -1355,7 +1355,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G34" t="n">
-        <v>2.28843021392822</v>
+        <v>2.2884304523468</v>
       </c>
       <c r="H34" t="n">
         <v>1661805</v>
@@ -1384,7 +1384,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G35" t="n">
-        <v>2.23799657821655</v>
+        <v>2.23799681663513</v>
       </c>
       <c r="H35" t="n">
         <v>2200031</v>
@@ -1413,7 +1413,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25060486793518</v>
+        <v>2.25060510635376</v>
       </c>
       <c r="H36" t="n">
         <v>2171688</v>
@@ -1442,7 +1442,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21782302856445</v>
+        <v>2.21782326698303</v>
       </c>
       <c r="H37" t="n">
         <v>2049268</v>
@@ -1471,7 +1471,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.23799657821655</v>
+        <v>2.23799681663513</v>
       </c>
       <c r="H38" t="n">
         <v>508600</v>
@@ -1500,7 +1500,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G39" t="n">
-        <v>2.20521473884583</v>
+        <v>2.20521450042725</v>
       </c>
       <c r="H39" t="n">
         <v>724649</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.20647549629211</v>
+        <v>2.20647573471069</v>
       </c>
       <c r="H40" t="n">
         <v>582571</v>
@@ -1587,7 +1587,7 @@
         <v>3.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.20647549629211</v>
+        <v>2.20647573471069</v>
       </c>
       <c r="H42" t="n">
         <v>671983</v>
@@ -1674,7 +1674,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G45" t="n">
-        <v>2.22034525871277</v>
+        <v>2.22034478187561</v>
       </c>
       <c r="H45" t="n">
         <v>679381</v>
@@ -1732,7 +1732,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22538781166077</v>
+        <v>2.22538876533508</v>
       </c>
       <c r="H47" t="n">
         <v>657985</v>
@@ -1790,7 +1790,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G49" t="n">
-        <v>2.30608201026917</v>
+        <v>2.30608224868774</v>
       </c>
       <c r="H49" t="n">
         <v>1124621</v>
@@ -1848,7 +1848,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26699614524841</v>
+        <v>2.26699590682983</v>
       </c>
       <c r="H51" t="n">
         <v>503049</v>
@@ -1877,7 +1877,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.23169231414795</v>
+        <v>2.23169207572937</v>
       </c>
       <c r="H52" t="n">
         <v>743120</v>
@@ -1906,7 +1906,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.21782302856445</v>
+        <v>2.21782326698303</v>
       </c>
       <c r="H53" t="n">
         <v>1181993</v>
@@ -1935,7 +1935,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G54" t="n">
-        <v>2.18378067016602</v>
+        <v>2.18378043174744</v>
       </c>
       <c r="H54" t="n">
         <v>792898</v>
@@ -2051,7 +2051,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G58" t="n">
-        <v>2.16108536720276</v>
+        <v>2.16108512878418</v>
       </c>
       <c r="H58" t="n">
         <v>856086</v>
@@ -2080,7 +2080,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.20773673057556</v>
+        <v>2.20773649215698</v>
       </c>
       <c r="H59" t="n">
         <v>787033</v>
@@ -2138,7 +2138,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15478110313416</v>
+        <v>2.15478134155273</v>
       </c>
       <c r="H61" t="n">
         <v>1863931</v>
@@ -2167,7 +2167,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G62" t="n">
-        <v>2.1787371635437</v>
+        <v>2.17873692512512</v>
       </c>
       <c r="H62" t="n">
         <v>1348975</v>
@@ -2196,7 +2196,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G63" t="n">
-        <v>2.1787371635437</v>
+        <v>2.17873692512512</v>
       </c>
       <c r="H63" t="n">
         <v>323909</v>
@@ -2225,7 +2225,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G64" t="n">
-        <v>2.16991114616394</v>
+        <v>2.16991090774536</v>
       </c>
       <c r="H64" t="n">
         <v>368716</v>
@@ -2254,7 +2254,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G65" t="n">
-        <v>2.14721608161926</v>
+        <v>2.14721584320068</v>
       </c>
       <c r="H65" t="n">
         <v>1473153</v>
@@ -2283,7 +2283,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>2.16865038871765</v>
+        <v>2.16865062713623</v>
       </c>
       <c r="H66" t="n">
         <v>1102800</v>
@@ -2312,7 +2312,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>2.14343357086182</v>
+        <v>2.1434338092804</v>
       </c>
       <c r="H67" t="n">
         <v>887821</v>
@@ -2341,7 +2341,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.14973783493042</v>
+        <v>2.14973759651184</v>
       </c>
       <c r="H68" t="n">
         <v>894808</v>
@@ -2370,7 +2370,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G69" t="n">
-        <v>2.14973783493042</v>
+        <v>2.14973759651184</v>
       </c>
       <c r="H69" t="n">
         <v>704511</v>
@@ -2399,7 +2399,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G70" t="n">
-        <v>2.13965106010437</v>
+        <v>2.13965082168579</v>
       </c>
       <c r="H70" t="n">
         <v>1079257</v>
@@ -2428,7 +2428,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G71" t="n">
-        <v>2.14343357086182</v>
+        <v>2.1434338092804</v>
       </c>
       <c r="H71" t="n">
         <v>213630</v>
@@ -2457,7 +2457,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>2.1232602596283</v>
+        <v>2.12326002120972</v>
       </c>
       <c r="H72" t="n">
         <v>1045976</v>
@@ -2486,7 +2486,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>2.13082504272461</v>
+        <v>2.13082528114319</v>
       </c>
       <c r="H73" t="n">
         <v>768752</v>
@@ -2515,7 +2515,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.12452077865601</v>
+        <v>2.12452054023743</v>
       </c>
       <c r="H74" t="n">
         <v>584909</v>
@@ -2544,7 +2544,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G75" t="n">
-        <v>2.12830328941345</v>
+        <v>2.12830352783203</v>
       </c>
       <c r="H75" t="n">
         <v>439704</v>
@@ -2573,7 +2573,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.12452077865601</v>
+        <v>2.12452054023743</v>
       </c>
       <c r="H76" t="n">
         <v>361920</v>
@@ -2631,7 +2631,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G78" t="n">
-        <v>1.99465394020081</v>
+        <v>1.9946540594101</v>
       </c>
       <c r="H78" t="n">
         <v>2768628</v>
@@ -2660,7 +2660,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195863723755</v>
+        <v>1.97195887565613</v>
       </c>
       <c r="H79" t="n">
         <v>3135081</v>
@@ -2718,7 +2718,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G81" t="n">
-        <v>1.93917727470398</v>
+        <v>1.93917679786682</v>
       </c>
       <c r="H81" t="n">
         <v>2261017</v>
@@ -2747,7 +2747,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>1.92908990383148</v>
+        <v>1.92908978462219</v>
       </c>
       <c r="H82" t="n">
         <v>1535844</v>
@@ -2805,7 +2805,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G84" t="n">
-        <v>1.94800281524658</v>
+        <v>1.94800305366516</v>
       </c>
       <c r="H84" t="n">
         <v>3748342</v>
@@ -2834,7 +2834,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>1.90387356281281</v>
+        <v>1.90387332439423</v>
       </c>
       <c r="H85" t="n">
         <v>1188561</v>
@@ -2863,7 +2863,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.90387356281281</v>
+        <v>1.90387332439423</v>
       </c>
       <c r="H86" t="n">
         <v>2920431</v>
@@ -2921,7 +2921,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G88" t="n">
-        <v>1.97574138641357</v>
+        <v>1.97574150562286</v>
       </c>
       <c r="H88" t="n">
         <v>1064202</v>
@@ -2950,7 +2950,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G89" t="n">
-        <v>1.97321939468384</v>
+        <v>1.97321999073029</v>
       </c>
       <c r="H89" t="n">
         <v>736410</v>
@@ -2979,7 +2979,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G90" t="n">
-        <v>1.99339306354523</v>
+        <v>1.99339294433594</v>
       </c>
       <c r="H90" t="n">
         <v>1831237</v>
@@ -3008,7 +3008,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G91" t="n">
-        <v>2.01356649398804</v>
+        <v>2.0135669708252</v>
       </c>
       <c r="H91" t="n">
         <v>1362913</v>
@@ -3037,7 +3037,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G92" t="n">
-        <v>2.01104497909546</v>
+        <v>2.01104474067688</v>
       </c>
       <c r="H92" t="n">
         <v>6813289</v>
@@ -3095,7 +3095,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G94" t="n">
-        <v>1.97448074817657</v>
+        <v>1.974480509758</v>
       </c>
       <c r="H94" t="n">
         <v>1497058</v>
@@ -3182,7 +3182,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>1.97321939468384</v>
+        <v>1.97321999073029</v>
       </c>
       <c r="H97" t="n">
         <v>1754313</v>
@@ -3211,7 +3211,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G98" t="n">
-        <v>1.91017746925354</v>
+        <v>1.91017758846283</v>
       </c>
       <c r="H98" t="n">
         <v>1613932</v>
@@ -3298,7 +3298,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G101" t="n">
-        <v>1.93917727470398</v>
+        <v>1.93917679786682</v>
       </c>
       <c r="H101" t="n">
         <v>2183788</v>
@@ -3385,7 +3385,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G104" t="n">
-        <v>2.08921718597412</v>
+        <v>2.0892174243927</v>
       </c>
       <c r="H104" t="n">
         <v>8365602</v>
@@ -3501,7 +3501,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>2.08669567108154</v>
+        <v>2.08669543266296</v>
       </c>
       <c r="H108" t="n">
         <v>1496422</v>
@@ -3617,7 +3617,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G112" t="n">
-        <v>2.07913064956665</v>
+        <v>2.07913088798523</v>
       </c>
       <c r="H112" t="n">
         <v>627812</v>
@@ -3675,7 +3675,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G114" t="n">
-        <v>2.08417391777039</v>
+        <v>2.08417367935181</v>
       </c>
       <c r="H114" t="n">
         <v>255877</v>
@@ -3733,7 +3733,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.14343357086182</v>
+        <v>2.1434338092804</v>
       </c>
       <c r="H116" t="n">
         <v>959348</v>
@@ -3762,7 +3762,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G117" t="n">
-        <v>2.14469456672668</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H117" t="n">
         <v>680193</v>
@@ -3791,7 +3791,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G118" t="n">
-        <v>2.14091205596924</v>
+        <v>2.14091181755066</v>
       </c>
       <c r="H118" t="n">
         <v>272440</v>
@@ -3820,7 +3820,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>2.14343357086182</v>
+        <v>2.1434338092804</v>
       </c>
       <c r="H119" t="n">
         <v>854222</v>
@@ -3849,7 +3849,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.13082504272461</v>
+        <v>2.13082528114319</v>
       </c>
       <c r="H120" t="n">
         <v>713419</v>
@@ -3936,7 +3936,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>2.19008469581604</v>
+        <v>2.19008445739746</v>
       </c>
       <c r="H123" t="n">
         <v>976460</v>
@@ -3994,7 +3994,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G125" t="n">
-        <v>2.16991114616394</v>
+        <v>2.16991090774536</v>
       </c>
       <c r="H125" t="n">
         <v>416120</v>
@@ -4226,7 +4226,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G133" t="n">
-        <v>2.06904363632202</v>
+        <v>2.0690438747406</v>
       </c>
       <c r="H133" t="n">
         <v>746353</v>
@@ -4342,7 +4342,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G137" t="n">
-        <v>2.02491402626038</v>
+        <v>2.02491426467896</v>
       </c>
       <c r="H137" t="n">
         <v>613132</v>
@@ -4429,7 +4429,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G140" t="n">
-        <v>1.97069799900055</v>
+        <v>1.97069811820984</v>
       </c>
       <c r="H140" t="n">
         <v>655592</v>
@@ -4458,7 +4458,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.02365326881409</v>
+        <v>2.02365350723267</v>
       </c>
       <c r="H141" t="n">
         <v>1907530</v>
@@ -4487,7 +4487,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>2.01734924316406</v>
+        <v>2.01734900474548</v>
       </c>
       <c r="H142" t="n">
         <v>1211840</v>
@@ -4632,7 +4632,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.13712954521179</v>
+        <v>2.13712930679321</v>
       </c>
       <c r="H147" t="n">
         <v>886586</v>
@@ -4661,7 +4661,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G148" t="n">
-        <v>2.14973783493042</v>
+        <v>2.14973759651184</v>
       </c>
       <c r="H148" t="n">
         <v>660518</v>
@@ -4690,7 +4690,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>2.15225911140442</v>
+        <v>2.152259349823</v>
       </c>
       <c r="H149" t="n">
         <v>659705</v>
@@ -4719,7 +4719,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>2.14343357086182</v>
+        <v>2.1434338092804</v>
       </c>
       <c r="H150" t="n">
         <v>618937</v>
@@ -4748,7 +4748,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G151" t="n">
-        <v>2.16486763954163</v>
+        <v>2.16486811637878</v>
       </c>
       <c r="H151" t="n">
         <v>993672</v>
@@ -4777,7 +4777,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G152" t="n">
-        <v>2.12199926376343</v>
+        <v>2.12199902534485</v>
       </c>
       <c r="H152" t="n">
         <v>878730</v>
@@ -4835,7 +4835,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>2.08669567108154</v>
+        <v>2.08669543266296</v>
       </c>
       <c r="H154" t="n">
         <v>352953</v>
@@ -4864,7 +4864,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.1232602596283</v>
+        <v>2.12326002120972</v>
       </c>
       <c r="H155" t="n">
         <v>607297</v>
@@ -4893,7 +4893,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G156" t="n">
-        <v>2.13712954521179</v>
+        <v>2.13712930679321</v>
       </c>
       <c r="H156" t="n">
         <v>566431</v>
@@ -4922,7 +4922,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G157" t="n">
-        <v>2.12452077865601</v>
+        <v>2.12452054023743</v>
       </c>
       <c r="H157" t="n">
         <v>566734</v>
@@ -4951,7 +4951,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.12452077865601</v>
+        <v>2.12452054023743</v>
       </c>
       <c r="H158" t="n">
         <v>451572</v>
@@ -4980,7 +4980,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>2.13082504272461</v>
+        <v>2.13082528114319</v>
       </c>
       <c r="H159" t="n">
         <v>442504</v>
@@ -5009,7 +5009,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G160" t="n">
-        <v>2.12704253196716</v>
+        <v>2.12704277038574</v>
       </c>
       <c r="H160" t="n">
         <v>735413</v>
@@ -5038,7 +5038,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G161" t="n">
-        <v>2.14469456672668</v>
+        <v>2.14469432830811</v>
       </c>
       <c r="H161" t="n">
         <v>513353</v>
@@ -5096,7 +5096,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G163" t="n">
-        <v>2.16108536720276</v>
+        <v>2.16108512878418</v>
       </c>
       <c r="H163" t="n">
         <v>472501</v>
@@ -5125,7 +5125,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G164" t="n">
-        <v>2.14595484733582</v>
+        <v>2.14595508575439</v>
       </c>
       <c r="H164" t="n">
         <v>656848</v>
@@ -5183,7 +5183,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G166" t="n">
-        <v>2.17243313789368</v>
+        <v>2.1724328994751</v>
       </c>
       <c r="H166" t="n">
         <v>716925</v>
@@ -5241,7 +5241,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G168" t="n">
-        <v>2.331298828125</v>
+        <v>2.33129930496216</v>
       </c>
       <c r="H168" t="n">
         <v>1990731</v>
@@ -5270,7 +5270,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.28843021392822</v>
+        <v>2.2884304523468</v>
       </c>
       <c r="H169" t="n">
         <v>1647290</v>
@@ -5299,7 +5299,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>2.27582168579102</v>
+        <v>2.27582192420959</v>
       </c>
       <c r="H170" t="n">
         <v>1446573</v>
@@ -5328,7 +5328,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G171" t="n">
-        <v>2.30734348297119</v>
+        <v>2.30734300613403</v>
       </c>
       <c r="H171" t="n">
         <v>1058400</v>
@@ -5357,7 +5357,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35147285461426</v>
+        <v>2.3514723777771</v>
       </c>
       <c r="H172" t="n">
         <v>1771997</v>
@@ -5415,7 +5415,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40190601348877</v>
+        <v>2.40190625190735</v>
       </c>
       <c r="H174" t="n">
         <v>1365898</v>
@@ -5444,7 +5444,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G175" t="n">
-        <v>2.35399389266968</v>
+        <v>2.35399436950684</v>
       </c>
       <c r="H175" t="n">
         <v>1120304</v>
@@ -5473,7 +5473,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.328777551651</v>
+        <v>2.32877707481384</v>
       </c>
       <c r="H176" t="n">
         <v>959599</v>
@@ -5560,7 +5560,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G179" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H179" t="n">
         <v>1073722</v>
@@ -5589,7 +5589,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.32247304916382</v>
+        <v>2.32247352600098</v>
       </c>
       <c r="H180" t="n">
         <v>1030102</v>
@@ -5618,7 +5618,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G181" t="n">
-        <v>2.39181971549988</v>
+        <v>2.3918194770813</v>
       </c>
       <c r="H181" t="n">
         <v>1136549</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H183" t="n">
         <v>1547599</v>
@@ -5705,7 +5705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H184" t="n">
         <v>1699128</v>
@@ -5734,7 +5734,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G185" t="n">
-        <v>2.37164616584778</v>
+        <v>2.37164640426636</v>
       </c>
       <c r="H185" t="n">
         <v>808007</v>
@@ -5792,7 +5792,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38299369812012</v>
+        <v>2.38299345970154</v>
       </c>
       <c r="H187" t="n">
         <v>1275111</v>
@@ -5821,7 +5821,7 @@
         <v>3.75</v>
       </c>
       <c r="G188" t="n">
-        <v>2.36408114433289</v>
+        <v>2.36408090591431</v>
       </c>
       <c r="H188" t="n">
         <v>550329</v>
@@ -5850,7 +5850,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G189" t="n">
-        <v>2.3653416633606</v>
+        <v>2.36534190177917</v>
       </c>
       <c r="H189" t="n">
         <v>713369</v>
@@ -5879,7 +5879,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G190" t="n">
-        <v>2.36281991004944</v>
+        <v>2.3628203868866</v>
       </c>
       <c r="H190" t="n">
         <v>864165</v>
@@ -5937,7 +5937,7 @@
         <v>3.75</v>
       </c>
       <c r="G192" t="n">
-        <v>2.36408114433289</v>
+        <v>2.36408090591431</v>
       </c>
       <c r="H192" t="n">
         <v>1026811</v>
@@ -6024,7 +6024,7 @@
         <v>3.75</v>
       </c>
       <c r="G195" t="n">
-        <v>2.36408114433289</v>
+        <v>2.36408090591431</v>
       </c>
       <c r="H195" t="n">
         <v>889289</v>
@@ -6082,7 +6082,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G197" t="n">
-        <v>2.39308023452759</v>
+        <v>2.39308047294617</v>
       </c>
       <c r="H197" t="n">
         <v>636944</v>
@@ -6111,7 +6111,7 @@
         <v>3.75</v>
       </c>
       <c r="G198" t="n">
-        <v>2.36408114433289</v>
+        <v>2.36408090591431</v>
       </c>
       <c r="H198" t="n">
         <v>542591</v>
@@ -6140,7 +6140,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39560198783875</v>
+        <v>2.39560222625732</v>
       </c>
       <c r="H199" t="n">
         <v>1166747</v>
@@ -6227,7 +6227,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.45234036445618</v>
+        <v>2.4523401260376</v>
       </c>
       <c r="H202" t="n">
         <v>1065606</v>
@@ -6285,7 +6285,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G204" t="n">
-        <v>2.43090558052063</v>
+        <v>2.43090581893921</v>
       </c>
       <c r="H204" t="n">
         <v>1339754</v>
@@ -6314,7 +6314,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G205" t="n">
-        <v>2.44603562355042</v>
+        <v>2.44603586196899</v>
       </c>
       <c r="H205" t="n">
         <v>915733</v>
@@ -6372,7 +6372,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.44603562355042</v>
+        <v>2.44603586196899</v>
       </c>
       <c r="H207" t="n">
         <v>364301</v>
@@ -6401,7 +6401,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>2.38677644729614</v>
+        <v>2.38677620887756</v>
       </c>
       <c r="H208" t="n">
         <v>998514</v>
@@ -6488,7 +6488,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G211" t="n">
-        <v>2.41535949707031</v>
+        <v>2.41535902023315</v>
       </c>
       <c r="H211" t="n">
         <v>902008</v>
@@ -6546,7 +6546,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G213" t="n">
-        <v>2.46826958656311</v>
+        <v>2.46826934814453</v>
       </c>
       <c r="H213" t="n">
         <v>1893893</v>
@@ -6604,7 +6604,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G215" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721167564392</v>
       </c>
       <c r="H215" t="n">
         <v>1570341</v>
@@ -6662,7 +6662,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>2.46694660186768</v>
+        <v>2.4669463634491</v>
       </c>
       <c r="H217" t="n">
         <v>1320391</v>
@@ -6720,7 +6720,7 @@
         <v>3.75</v>
       </c>
       <c r="G219" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017430305481</v>
       </c>
       <c r="H219" t="n">
         <v>1382829</v>
@@ -6778,7 +6778,7 @@
         <v>3.75</v>
       </c>
       <c r="G221" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017430305481</v>
       </c>
       <c r="H221" t="n">
         <v>514242</v>
@@ -6807,7 +6807,7 @@
         <v>3.75</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017430305481</v>
       </c>
       <c r="H222" t="n">
         <v>1022566</v>
@@ -6865,7 +6865,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G224" t="n">
-        <v>2.49737000465393</v>
+        <v>2.49737024307251</v>
       </c>
       <c r="H224" t="n">
         <v>1878448</v>
@@ -6923,7 +6923,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G226" t="n">
-        <v>2.48546528816223</v>
+        <v>2.48546504974365</v>
       </c>
       <c r="H226" t="n">
         <v>1137067</v>
@@ -6952,7 +6952,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G227" t="n">
-        <v>2.50530695915222</v>
+        <v>2.50530672073364</v>
       </c>
       <c r="H227" t="n">
         <v>982862</v>
@@ -6981,7 +6981,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G228" t="n">
-        <v>2.5132429599762</v>
+        <v>2.51324319839478</v>
       </c>
       <c r="H228" t="n">
         <v>2456099</v>
@@ -7039,7 +7039,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>2.46694660186768</v>
+        <v>2.4669463634491</v>
       </c>
       <c r="H230" t="n">
         <v>3703950</v>
@@ -7068,7 +7068,7 @@
         <v>3.75</v>
       </c>
       <c r="G231" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017430305481</v>
       </c>
       <c r="H231" t="n">
         <v>630800</v>
@@ -7097,7 +7097,7 @@
         <v>3.75</v>
       </c>
       <c r="G232" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017430305481</v>
       </c>
       <c r="H232" t="n">
         <v>2066418</v>
@@ -7155,7 +7155,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H234" t="n">
         <v>365542</v>
@@ -7184,7 +7184,7 @@
         <v>3.75</v>
       </c>
       <c r="G235" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017430305481</v>
       </c>
       <c r="H235" t="n">
         <v>612027</v>
@@ -7213,7 +7213,7 @@
         <v>3.75</v>
       </c>
       <c r="G236" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017430305481</v>
       </c>
       <c r="H236" t="n">
         <v>1886715</v>
@@ -7242,7 +7242,7 @@
         <v>3.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.48017406463623</v>
+        <v>2.48017430305481</v>
       </c>
       <c r="H237" t="n">
         <v>1004577</v>
@@ -7271,7 +7271,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G238" t="n">
-        <v>2.45239639282227</v>
+        <v>2.45239615440369</v>
       </c>
       <c r="H238" t="n">
         <v>975866</v>
@@ -7300,7 +7300,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G239" t="n">
-        <v>2.44049143791199</v>
+        <v>2.44049167633057</v>
       </c>
       <c r="H239" t="n">
         <v>504236</v>
@@ -7416,7 +7416,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>2.46694660186768</v>
+        <v>2.4669463634491</v>
       </c>
       <c r="H243" t="n">
         <v>279712</v>
@@ -7445,7 +7445,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>2.44049143791199</v>
+        <v>2.44049167633057</v>
       </c>
       <c r="H244" t="n">
         <v>950856</v>
@@ -7503,7 +7503,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>2.46694660186768</v>
+        <v>2.4669463634491</v>
       </c>
       <c r="H246" t="n">
         <v>235874</v>
@@ -7532,7 +7532,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G247" t="n">
-        <v>2.44445991516113</v>
+        <v>2.44445967674255</v>
       </c>
       <c r="H247" t="n">
         <v>244557</v>
@@ -7648,7 +7648,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G251" t="n">
-        <v>2.43387794494629</v>
+        <v>2.43387770652771</v>
       </c>
       <c r="H251" t="n">
         <v>968381</v>
@@ -7677,7 +7677,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G252" t="n">
-        <v>2.44049143791199</v>
+        <v>2.44049167633057</v>
       </c>
       <c r="H252" t="n">
         <v>1075100</v>
@@ -7706,7 +7706,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>2.44975066184998</v>
+        <v>2.44975090026855</v>
       </c>
       <c r="H253" t="n">
         <v>622270</v>
@@ -7764,7 +7764,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488307952881</v>
       </c>
       <c r="H255" t="n">
         <v>460966</v>
@@ -7793,7 +7793,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G256" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488307952881</v>
       </c>
       <c r="H256" t="n">
         <v>262852</v>
@@ -7851,7 +7851,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H258" t="n">
         <v>335894</v>
@@ -7909,7 +7909,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>2.51456594467163</v>
+        <v>2.51456618309021</v>
       </c>
       <c r="H260" t="n">
         <v>440530</v>
@@ -7938,7 +7938,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G261" t="n">
-        <v>2.56483101844788</v>
+        <v>2.56483125686646</v>
       </c>
       <c r="H261" t="n">
         <v>524937</v>
@@ -7967,7 +7967,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55689430236816</v>
+        <v>2.55689406394958</v>
       </c>
       <c r="H262" t="n">
         <v>748895</v>
@@ -7996,7 +7996,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G263" t="n">
-        <v>2.57144451141357</v>
+        <v>2.57144474983215</v>
       </c>
       <c r="H263" t="n">
         <v>328662</v>
@@ -8025,7 +8025,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G264" t="n">
-        <v>2.56218528747559</v>
+        <v>2.56218552589417</v>
       </c>
       <c r="H264" t="n">
         <v>625175</v>
@@ -8054,7 +8054,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G265" t="n">
-        <v>2.56483101844788</v>
+        <v>2.56483125686646</v>
       </c>
       <c r="H265" t="n">
         <v>514836</v>
@@ -8083,7 +8083,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G266" t="n">
-        <v>2.56615352630615</v>
+        <v>2.56615400314331</v>
       </c>
       <c r="H266" t="n">
         <v>481921</v>
@@ -8112,7 +8112,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G267" t="n">
-        <v>2.55424857139587</v>
+        <v>2.55424880981445</v>
       </c>
       <c r="H267" t="n">
         <v>614773</v>
@@ -8199,7 +8199,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G270" t="n">
-        <v>2.5238254070282</v>
+        <v>2.52382516860962</v>
       </c>
       <c r="H270" t="n">
         <v>321976</v>
@@ -8257,7 +8257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G272" t="n">
-        <v>2.5132429599762</v>
+        <v>2.51324319839478</v>
       </c>
       <c r="H272" t="n">
         <v>536735</v>
@@ -8344,7 +8344,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H275" t="n">
         <v>409245</v>
@@ -8402,7 +8402,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>2.47356033325195</v>
+        <v>2.47356009483337</v>
       </c>
       <c r="H277" t="n">
         <v>374003</v>
@@ -8431,7 +8431,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.48678827285767</v>
+        <v>2.48678803443909</v>
       </c>
       <c r="H278" t="n">
         <v>277590</v>
@@ -8460,7 +8460,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G279" t="n">
-        <v>2.47488331794739</v>
+        <v>2.47488307952881</v>
       </c>
       <c r="H279" t="n">
         <v>167600</v>
@@ -8489,7 +8489,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G280" t="n">
-        <v>2.44842767715454</v>
+        <v>2.44842791557312</v>
       </c>
       <c r="H280" t="n">
         <v>191020</v>
@@ -8518,7 +8518,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G281" t="n">
-        <v>2.42858624458313</v>
+        <v>2.42858672142029</v>
       </c>
       <c r="H281" t="n">
         <v>622612</v>
@@ -8634,7 +8634,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G285" t="n">
-        <v>2.46959233283997</v>
+        <v>2.46959185600281</v>
       </c>
       <c r="H285" t="n">
         <v>426920</v>
@@ -8692,7 +8692,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>2.43652319908142</v>
+        <v>2.43652272224426</v>
       </c>
       <c r="H287" t="n">
         <v>539242</v>
@@ -8721,7 +8721,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G288" t="n">
-        <v>2.49869298934937</v>
+        <v>2.49869275093079</v>
       </c>
       <c r="H288" t="n">
         <v>633611</v>
@@ -8750,7 +8750,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54366636276245</v>
+        <v>2.54366660118103</v>
       </c>
       <c r="H289" t="n">
         <v>849632</v>
@@ -8808,7 +8808,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G291" t="n">
-        <v>2.53837561607361</v>
+        <v>2.53837585449219</v>
       </c>
       <c r="H291" t="n">
         <v>385349</v>
@@ -8837,7 +8837,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G292" t="n">
-        <v>2.5357301235199</v>
+        <v>2.53573036193848</v>
       </c>
       <c r="H292" t="n">
         <v>257047</v>
@@ -8866,7 +8866,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G293" t="n">
-        <v>2.53440737724304</v>
+        <v>2.5344078540802</v>
       </c>
       <c r="H293" t="n">
         <v>472169</v>
@@ -8924,7 +8924,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G295" t="n">
-        <v>2.53176164627075</v>
+        <v>2.53176188468933</v>
       </c>
       <c r="H295" t="n">
         <v>569194</v>
@@ -8953,7 +8953,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G296" t="n">
-        <v>2.5410213470459</v>
+        <v>2.54102110862732</v>
       </c>
       <c r="H296" t="n">
         <v>538902</v>
@@ -8982,7 +8982,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G297" t="n">
-        <v>2.52779364585876</v>
+        <v>2.52779340744019</v>
       </c>
       <c r="H297" t="n">
         <v>420940</v>
@@ -9011,7 +9011,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G298" t="n">
-        <v>2.51456594467163</v>
+        <v>2.51456618309021</v>
       </c>
       <c r="H298" t="n">
         <v>271055</v>
@@ -9040,7 +9040,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G299" t="n">
-        <v>2.51721143722534</v>
+        <v>2.51721167564392</v>
       </c>
       <c r="H299" t="n">
         <v>254927</v>
@@ -9098,7 +9098,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G301" t="n">
-        <v>2.5357301235199</v>
+        <v>2.53573036193848</v>
       </c>
       <c r="H301" t="n">
         <v>356050</v>
@@ -9127,7 +9127,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53969860076904</v>
+        <v>2.53969836235046</v>
       </c>
       <c r="H302" t="n">
         <v>350932</v>
@@ -9156,7 +9156,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.53969860076904</v>
+        <v>2.53969836235046</v>
       </c>
       <c r="H303" t="n">
         <v>764260</v>
@@ -9214,7 +9214,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G305" t="n">
-        <v>2.61377310752869</v>
+        <v>2.61377286911011</v>
       </c>
       <c r="H305" t="n">
         <v>844898</v>
@@ -9243,7 +9243,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G306" t="n">
-        <v>2.59922289848328</v>
+        <v>2.59922242164612</v>
       </c>
       <c r="H306" t="n">
         <v>581605</v>
@@ -9330,7 +9330,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.57276701927185</v>
+        <v>2.57276749610901</v>
       </c>
       <c r="H309" t="n">
         <v>811458</v>
@@ -9359,7 +9359,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G310" t="n">
-        <v>2.58334922790527</v>
+        <v>2.58334946632385</v>
       </c>
       <c r="H310" t="n">
         <v>282406</v>
@@ -9388,7 +9388,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G311" t="n">
-        <v>2.59128570556641</v>
+        <v>2.59128642082214</v>
       </c>
       <c r="H311" t="n">
         <v>463030</v>
@@ -9417,7 +9417,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G312" t="n">
-        <v>2.58864045143127</v>
+        <v>2.58864068984985</v>
       </c>
       <c r="H312" t="n">
         <v>672881</v>
@@ -9475,7 +9475,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G314" t="n">
-        <v>2.60980486869812</v>
+        <v>2.60980463027954</v>
       </c>
       <c r="H314" t="n">
         <v>445032</v>
@@ -9504,7 +9504,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G315" t="n">
-        <v>2.60980486869812</v>
+        <v>2.60980463027954</v>
       </c>
       <c r="H315" t="n">
         <v>562538</v>
@@ -9562,7 +9562,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G317" t="n">
-        <v>2.67329716682434</v>
+        <v>2.67329692840576</v>
       </c>
       <c r="H317" t="n">
         <v>1408139</v>
@@ -9591,7 +9591,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G318" t="n">
-        <v>2.68917036056519</v>
+        <v>2.68916988372803</v>
       </c>
       <c r="H318" t="n">
         <v>660904</v>
@@ -9620,7 +9620,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G319" t="n">
-        <v>2.67594242095947</v>
+        <v>2.67594265937805</v>
       </c>
       <c r="H319" t="n">
         <v>576776</v>
@@ -9649,7 +9649,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G320" t="n">
-        <v>2.69710683822632</v>
+        <v>2.69710659980774</v>
       </c>
       <c r="H320" t="n">
         <v>496010</v>
@@ -9678,7 +9678,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>2.67858839035034</v>
+        <v>2.67858815193176</v>
       </c>
       <c r="H321" t="n">
         <v>476349</v>
@@ -9736,7 +9736,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>2.69842934608459</v>
+        <v>2.69842958450317</v>
       </c>
       <c r="H323" t="n">
         <v>561708</v>
@@ -9765,7 +9765,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G324" t="n">
-        <v>2.66932892799377</v>
+        <v>2.6693286895752</v>
       </c>
       <c r="H324" t="n">
         <v>337409</v>
@@ -9794,7 +9794,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G325" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H325" t="n">
         <v>687242</v>
@@ -9823,7 +9823,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G326" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H326" t="n">
         <v>753657</v>
@@ -9852,7 +9852,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G327" t="n">
-        <v>2.68784785270691</v>
+        <v>2.68784761428833</v>
       </c>
       <c r="H327" t="n">
         <v>473695</v>
@@ -9881,7 +9881,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G328" t="n">
-        <v>2.68784785270691</v>
+        <v>2.68784761428833</v>
       </c>
       <c r="H328" t="n">
         <v>332487</v>
@@ -9939,7 +9939,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>2.70504331588745</v>
+        <v>2.70504355430603</v>
       </c>
       <c r="H330" t="n">
         <v>618999</v>
@@ -9968,7 +9968,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>2.68520188331604</v>
+        <v>2.68520212173462</v>
       </c>
       <c r="H331" t="n">
         <v>771787</v>
@@ -9997,7 +9997,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G332" t="n">
-        <v>2.70107531547546</v>
+        <v>2.70107483863831</v>
       </c>
       <c r="H332" t="n">
         <v>431759</v>
@@ -10026,7 +10026,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G333" t="n">
-        <v>2.70107531547546</v>
+        <v>2.70107483863831</v>
       </c>
       <c r="H333" t="n">
         <v>1317493</v>
@@ -10055,7 +10055,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>2.65874648094177</v>
+        <v>2.65874671936035</v>
       </c>
       <c r="H334" t="n">
         <v>564957</v>
@@ -10084,7 +10084,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>2.67197465896606</v>
+        <v>2.67197418212891</v>
       </c>
       <c r="H335" t="n">
         <v>708093</v>
@@ -10113,7 +10113,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.74472618103027</v>
+        <v>2.74472641944885</v>
       </c>
       <c r="H336" t="n">
         <v>2911512</v>
@@ -10142,7 +10142,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G337" t="n">
-        <v>2.78837704658508</v>
+        <v>2.78837752342224</v>
       </c>
       <c r="H337" t="n">
         <v>2139808</v>
@@ -10229,7 +10229,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G340" t="n">
-        <v>2.88758444786072</v>
+        <v>2.88758420944214</v>
       </c>
       <c r="H340" t="n">
         <v>1378600</v>
@@ -10287,7 +10287,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G342" t="n">
-        <v>2.90742564201355</v>
+        <v>2.90742540359497</v>
       </c>
       <c r="H342" t="n">
         <v>1794819</v>
@@ -10345,7 +10345,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G344" t="n">
-        <v>2.95901322364807</v>
+        <v>2.95901346206665</v>
       </c>
       <c r="H344" t="n">
         <v>1122926</v>
@@ -10374,7 +10374,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G345" t="n">
-        <v>2.94843101501465</v>
+        <v>2.94843125343323</v>
       </c>
       <c r="H345" t="n">
         <v>1014769</v>
@@ -10403,7 +10403,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G346" t="n">
-        <v>2.97356295585632</v>
+        <v>2.97356343269348</v>
       </c>
       <c r="H346" t="n">
         <v>613331</v>
@@ -10432,7 +10432,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G347" t="n">
-        <v>2.96430397033691</v>
+        <v>2.96430420875549</v>
       </c>
       <c r="H347" t="n">
         <v>1313359</v>
@@ -10461,7 +10461,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G348" t="n">
-        <v>2.96827268600464</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H348" t="n">
         <v>1065152</v>
@@ -10490,7 +10490,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G349" t="n">
-        <v>2.95901322364807</v>
+        <v>2.95901346206665</v>
       </c>
       <c r="H349" t="n">
         <v>794496</v>
@@ -10519,7 +10519,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>2.99340486526489</v>
+        <v>2.99340510368347</v>
       </c>
       <c r="H350" t="n">
         <v>996164</v>
@@ -10548,7 +10548,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G351" t="n">
-        <v>3.01456904411316</v>
+        <v>3.01456928253174</v>
       </c>
       <c r="H351" t="n">
         <v>1271838</v>
@@ -10577,7 +10577,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03837847709656</v>
+        <v>3.03837895393372</v>
       </c>
       <c r="H352" t="n">
         <v>949730</v>
@@ -10606,7 +10606,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G353" t="n">
-        <v>3.03176474571228</v>
+        <v>3.03176498413086</v>
       </c>
       <c r="H353" t="n">
         <v>617623</v>
@@ -10635,7 +10635,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G354" t="n">
-        <v>3.1058394908905</v>
+        <v>3.10583996772766</v>
       </c>
       <c r="H354" t="n">
         <v>888394</v>
@@ -10693,7 +10693,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.00927829742432</v>
+        <v>3.0092785358429</v>
       </c>
       <c r="H356" t="n">
         <v>1663888</v>
@@ -10722,7 +10722,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G357" t="n">
-        <v>2.99605059623718</v>
+        <v>2.9960503578186</v>
       </c>
       <c r="H357" t="n">
         <v>1097676</v>
@@ -10751,7 +10751,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>3.01456904411316</v>
+        <v>3.01456928253174</v>
       </c>
       <c r="H358" t="n">
         <v>1277481</v>
@@ -10780,7 +10780,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>3.04234719276428</v>
+        <v>3.0423469543457</v>
       </c>
       <c r="H359" t="n">
         <v>1263796</v>
@@ -10809,7 +10809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G360" t="n">
-        <v>3.04631543159485</v>
+        <v>3.04631519317627</v>
       </c>
       <c r="H360" t="n">
         <v>1279493</v>
@@ -10896,7 +10896,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05557489395142</v>
+        <v>3.05557441711426</v>
       </c>
       <c r="H363" t="n">
         <v>841909</v>
@@ -10925,7 +10925,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G364" t="n">
-        <v>3.02515149116516</v>
+        <v>3.025151014328</v>
       </c>
       <c r="H364" t="n">
         <v>436276</v>
@@ -10954,7 +10954,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>2.98943662643433</v>
+        <v>2.98943638801575</v>
       </c>
       <c r="H365" t="n">
         <v>511496</v>
@@ -11041,7 +11041,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G368" t="n">
-        <v>2.97091794013977</v>
+        <v>2.97091817855835</v>
       </c>
       <c r="H368" t="n">
         <v>274659</v>
@@ -11099,7 +11099,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G370" t="n">
-        <v>2.97356295585632</v>
+        <v>2.97356343269348</v>
       </c>
       <c r="H370" t="n">
         <v>934664</v>
@@ -11128,7 +11128,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G371" t="n">
-        <v>2.96827268600464</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H371" t="n">
         <v>609342</v>
@@ -11186,7 +11186,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G373" t="n">
-        <v>3.02250552177429</v>
+        <v>3.02250576019287</v>
       </c>
       <c r="H373" t="n">
         <v>820789</v>
@@ -11215,7 +11215,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>2.94313955307007</v>
+        <v>2.94313979148865</v>
       </c>
       <c r="H374" t="n">
         <v>861518</v>
@@ -11273,7 +11273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>2.87700200080872</v>
+        <v>2.87700223922729</v>
       </c>
       <c r="H376" t="n">
         <v>558785</v>
@@ -11302,7 +11302,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G377" t="n">
-        <v>2.84922456741333</v>
+        <v>2.84922409057617</v>
       </c>
       <c r="H377" t="n">
         <v>531133</v>
@@ -11331,7 +11331,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G378" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583806037903</v>
       </c>
       <c r="H378" t="n">
         <v>654476</v>
@@ -11360,7 +11360,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G379" t="n">
-        <v>2.86509704589844</v>
+        <v>2.86509728431702</v>
       </c>
       <c r="H379" t="n">
         <v>765727</v>
@@ -11505,7 +11505,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583806037903</v>
       </c>
       <c r="H384" t="n">
         <v>424777</v>
@@ -11534,7 +11534,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G385" t="n">
-        <v>2.84922456741333</v>
+        <v>2.84922409057617</v>
       </c>
       <c r="H385" t="n">
         <v>471951</v>
@@ -11563,7 +11563,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.87700200080872</v>
+        <v>2.87700223922729</v>
       </c>
       <c r="H386" t="n">
         <v>431245</v>
@@ -11592,7 +11592,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.84525632858276</v>
+        <v>2.84525585174561</v>
       </c>
       <c r="H387" t="n">
         <v>570613</v>
@@ -11621,7 +11621,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.79763627052307</v>
+        <v>2.79763674736023</v>
       </c>
       <c r="H388" t="n">
         <v>888381</v>
@@ -11650,7 +11650,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705453872681</v>
+        <v>2.78705477714539</v>
       </c>
       <c r="H389" t="n">
         <v>1087808</v>
@@ -11679,7 +11679,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80689597129822</v>
+        <v>2.80689549446106</v>
       </c>
       <c r="H390" t="n">
         <v>516731</v>
@@ -11708,7 +11708,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G391" t="n">
-        <v>2.76589012145996</v>
+        <v>2.76589035987854</v>
       </c>
       <c r="H391" t="n">
         <v>1049142</v>
@@ -11737,7 +11737,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>2.80689597129822</v>
+        <v>2.80689549446106</v>
       </c>
       <c r="H392" t="n">
         <v>1039683</v>
@@ -11766,7 +11766,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>2.71165704727173</v>
+        <v>2.71165728569031</v>
       </c>
       <c r="H393" t="n">
         <v>1017959</v>
@@ -11795,7 +11795,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>2.75398540496826</v>
+        <v>2.75398564338684</v>
       </c>
       <c r="H394" t="n">
         <v>1009068</v>
@@ -11853,7 +11853,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G396" t="n">
-        <v>2.67329716682434</v>
+        <v>2.67329692840576</v>
       </c>
       <c r="H396" t="n">
         <v>563261</v>
@@ -11882,7 +11882,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69446086883545</v>
+        <v>2.69446110725403</v>
       </c>
       <c r="H397" t="n">
         <v>848281</v>
@@ -11969,7 +11969,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G400" t="n">
-        <v>2.7500171661377</v>
+        <v>2.75001692771912</v>
       </c>
       <c r="H400" t="n">
         <v>527748</v>
@@ -11998,7 +11998,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.75927639007568</v>
+        <v>2.75927686691284</v>
       </c>
       <c r="H401" t="n">
         <v>543737</v>
@@ -12056,7 +12056,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G403" t="n">
-        <v>2.76456737518311</v>
+        <v>2.76456761360168</v>
       </c>
       <c r="H403" t="n">
         <v>371911</v>
@@ -12085,7 +12085,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G404" t="n">
-        <v>2.72885274887085</v>
+        <v>2.72885298728943</v>
       </c>
       <c r="H404" t="n">
         <v>250945</v>
@@ -12114,7 +12114,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G405" t="n">
-        <v>2.72885274887085</v>
+        <v>2.72885298728943</v>
       </c>
       <c r="H405" t="n">
         <v>549004</v>
@@ -12143,7 +12143,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74472618103027</v>
+        <v>2.74472641944885</v>
       </c>
       <c r="H406" t="n">
         <v>449646</v>
@@ -12172,7 +12172,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>2.79102277755737</v>
+        <v>2.79102230072021</v>
       </c>
       <c r="H407" t="n">
         <v>384104</v>
@@ -12201,7 +12201,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73943495750427</v>
+        <v>2.73943543434143</v>
       </c>
       <c r="H408" t="n">
         <v>682369</v>
@@ -12230,7 +12230,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G409" t="n">
-        <v>2.76589012145996</v>
+        <v>2.76589035987854</v>
       </c>
       <c r="H409" t="n">
         <v>862849</v>
@@ -12259,7 +12259,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G410" t="n">
-        <v>2.72620797157288</v>
+        <v>2.72620749473572</v>
       </c>
       <c r="H410" t="n">
         <v>884762</v>
@@ -12288,7 +12288,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.66932892799377</v>
+        <v>2.6693286895752</v>
       </c>
       <c r="H411" t="n">
         <v>843867</v>
@@ -12346,7 +12346,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G413" t="n">
-        <v>2.76324486732483</v>
+        <v>2.76324462890625</v>
       </c>
       <c r="H413" t="n">
         <v>701284</v>
@@ -12375,7 +12375,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>2.75927639007568</v>
+        <v>2.75927686691284</v>
       </c>
       <c r="H414" t="n">
         <v>581298</v>
@@ -12433,7 +12433,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G416" t="n">
-        <v>2.79102277755737</v>
+        <v>2.79102230072021</v>
       </c>
       <c r="H416" t="n">
         <v>262750</v>
@@ -12462,7 +12462,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G417" t="n">
-        <v>2.85583758354187</v>
+        <v>2.85583806037903</v>
       </c>
       <c r="H417" t="n">
         <v>1518103</v>
@@ -12491,7 +12491,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G418" t="n">
-        <v>2.869065284729</v>
+        <v>2.86906552314758</v>
       </c>
       <c r="H418" t="n">
         <v>2152019</v>
@@ -12520,7 +12520,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G419" t="n">
-        <v>2.87303376197815</v>
+        <v>2.87303400039673</v>
       </c>
       <c r="H419" t="n">
         <v>1064225</v>
@@ -12549,7 +12549,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>2.91007113456726</v>
+        <v>2.91007137298584</v>
       </c>
       <c r="H420" t="n">
         <v>721209</v>
@@ -12607,7 +12607,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G422" t="n">
-        <v>2.86377477645874</v>
+        <v>2.86377429962158</v>
       </c>
       <c r="H422" t="n">
         <v>747318</v>
@@ -12694,7 +12694,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G425" t="n">
-        <v>2.79631352424622</v>
+        <v>2.79631400108337</v>
       </c>
       <c r="H425" t="n">
         <v>548843</v>
@@ -12723,7 +12723,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G426" t="n">
-        <v>2.81483268737793</v>
+        <v>2.81483244895935</v>
       </c>
       <c r="H426" t="n">
         <v>783217</v>
@@ -12752,7 +12752,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G427" t="n">
-        <v>2.79234552383423</v>
+        <v>2.79234528541565</v>
       </c>
       <c r="H427" t="n">
         <v>495666</v>
@@ -12781,7 +12781,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G428" t="n">
-        <v>2.83335137367249</v>
+        <v>2.83335113525391</v>
       </c>
       <c r="H428" t="n">
         <v>634478</v>
@@ -12839,7 +12839,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86642026901245</v>
+        <v>2.86642003059387</v>
       </c>
       <c r="H430" t="n">
         <v>602501</v>
@@ -12868,7 +12868,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G431" t="n">
-        <v>2.86642026901245</v>
+        <v>2.86642003059387</v>
       </c>
       <c r="H431" t="n">
         <v>546107</v>
@@ -12926,7 +12926,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.89022946357727</v>
+        <v>2.89022970199585</v>
       </c>
       <c r="H433" t="n">
         <v>641837</v>
@@ -12955,7 +12955,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G434" t="n">
-        <v>2.89419794082642</v>
+        <v>2.89419770240784</v>
       </c>
       <c r="H434" t="n">
         <v>713486</v>
@@ -13013,7 +13013,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G436" t="n">
-        <v>2.93123507499695</v>
+        <v>2.93123531341553</v>
       </c>
       <c r="H436" t="n">
         <v>487422</v>
@@ -13042,7 +13042,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94181728363037</v>
+        <v>2.94181704521179</v>
       </c>
       <c r="H437" t="n">
         <v>413076</v>
@@ -13100,7 +13100,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99208211898804</v>
+        <v>2.9920825958252</v>
       </c>
       <c r="H439" t="n">
         <v>796136</v>
@@ -13129,7 +13129,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G440" t="n">
-        <v>3.00795555114746</v>
+        <v>3.00795531272888</v>
       </c>
       <c r="H440" t="n">
         <v>894728</v>
@@ -13216,7 +13216,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520402908325</v>
+        <v>2.93520379066467</v>
       </c>
       <c r="H443" t="n">
         <v>1018294</v>
@@ -13245,7 +13245,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G444" t="n">
-        <v>2.94181728363037</v>
+        <v>2.94181704521179</v>
       </c>
       <c r="H444" t="n">
         <v>553049</v>
@@ -13274,7 +13274,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>2.95636749267578</v>
+        <v>2.95636773109436</v>
       </c>
       <c r="H445" t="n">
         <v>229109</v>
@@ -13303,7 +13303,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96827268600464</v>
+        <v>2.96827244758606</v>
       </c>
       <c r="H446" t="n">
         <v>588207</v>
@@ -13332,7 +13332,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>2.95636749267578</v>
+        <v>2.95636773109436</v>
       </c>
       <c r="H447" t="n">
         <v>241939</v>
@@ -13361,7 +13361,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G448" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H448" t="n">
         <v>369775</v>
@@ -13390,7 +13390,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G449" t="n">
-        <v>2.99075937271118</v>
+        <v>2.99075984954834</v>
       </c>
       <c r="H449" t="n">
         <v>251562</v>
@@ -13419,7 +13419,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.99208211898804</v>
+        <v>2.9920825958252</v>
       </c>
       <c r="H450" t="n">
         <v>365775</v>
@@ -13506,7 +13506,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G453" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H453" t="n">
         <v>403012</v>
@@ -13535,7 +13535,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G454" t="n">
-        <v>3.00398659706116</v>
+        <v>3.00398683547974</v>
       </c>
       <c r="H454" t="n">
         <v>359122</v>
@@ -13564,7 +13564,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G455" t="n">
-        <v>2.99737334251404</v>
+        <v>2.99737310409546</v>
       </c>
       <c r="H455" t="n">
         <v>614167</v>
@@ -13593,7 +13593,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>2.99605059623718</v>
+        <v>2.9960503578186</v>
       </c>
       <c r="H456" t="n">
         <v>373559</v>
@@ -13622,7 +13622,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92991232872009</v>
+        <v>2.92991256713867</v>
       </c>
       <c r="H457" t="n">
         <v>493247</v>
@@ -13680,7 +13680,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G459" t="n">
-        <v>2.98943662643433</v>
+        <v>2.98943638801575</v>
       </c>
       <c r="H459" t="n">
         <v>467969</v>
@@ -13825,7 +13825,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G464" t="n">
-        <v>2.89080119132996</v>
+        <v>2.89080095291138</v>
       </c>
       <c r="H464" t="n">
         <v>642124</v>
@@ -13854,7 +13854,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.92672920227051</v>
+        <v>2.92672944068909</v>
       </c>
       <c r="H465" t="n">
         <v>391973</v>
@@ -13970,7 +13970,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G469" t="n">
-        <v>2.87145566940308</v>
+        <v>2.87145590782166</v>
       </c>
       <c r="H469" t="n">
         <v>1192667</v>
@@ -14086,7 +14086,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G473" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H473" t="n">
         <v>617354</v>
@@ -14115,7 +14115,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G474" t="n">
-        <v>2.8825101852417</v>
+        <v>2.88250994682312</v>
       </c>
       <c r="H474" t="n">
         <v>648999</v>
@@ -14144,7 +14144,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G475" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H475" t="n">
         <v>676249</v>
@@ -14173,7 +14173,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H476" t="n">
         <v>917279</v>
@@ -14202,7 +14202,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>2.81894588470459</v>
+        <v>2.81894564628601</v>
       </c>
       <c r="H477" t="n">
         <v>580850</v>
@@ -14231,7 +14231,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>2.79130935668945</v>
+        <v>2.79130911827087</v>
       </c>
       <c r="H478" t="n">
         <v>484051</v>
@@ -14260,7 +14260,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H479" t="n">
         <v>470947</v>
@@ -14289,7 +14289,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G480" t="n">
-        <v>2.81203699111938</v>
+        <v>2.81203675270081</v>
       </c>
       <c r="H480" t="n">
         <v>589491</v>
@@ -14318,7 +14318,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>2.86731004714966</v>
+        <v>2.86731028556824</v>
       </c>
       <c r="H481" t="n">
         <v>2001875</v>
@@ -14347,7 +14347,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G482" t="n">
-        <v>2.92258334159851</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H482" t="n">
         <v>1544814</v>
@@ -14376,7 +14376,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G483" t="n">
-        <v>2.93502020835876</v>
+        <v>2.93502044677734</v>
       </c>
       <c r="H483" t="n">
         <v>910184</v>
@@ -14550,7 +14550,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.97371125221252</v>
+        <v>2.97371101379395</v>
       </c>
       <c r="H489" t="n">
         <v>488412</v>
@@ -14579,7 +14579,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G490" t="n">
-        <v>3.02345752716064</v>
+        <v>3.02345776557922</v>
       </c>
       <c r="H490" t="n">
         <v>692474</v>
@@ -14637,7 +14637,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>2.95989346504211</v>
+        <v>2.95989322662354</v>
       </c>
       <c r="H492" t="n">
         <v>427110</v>
@@ -14666,7 +14666,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G493" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818447113037</v>
       </c>
       <c r="H493" t="n">
         <v>355874</v>
@@ -14695,7 +14695,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G494" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818447113037</v>
       </c>
       <c r="H494" t="n">
         <v>219739</v>
@@ -14753,7 +14753,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G496" t="n">
-        <v>2.96818423271179</v>
+        <v>2.96818447113037</v>
       </c>
       <c r="H496" t="n">
         <v>351475</v>
@@ -14811,7 +14811,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G498" t="n">
-        <v>3.03036689758301</v>
+        <v>3.03036713600159</v>
       </c>
       <c r="H498" t="n">
         <v>620501</v>
@@ -14869,7 +14869,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G500" t="n">
-        <v>2.97923898696899</v>
+        <v>2.97923874855042</v>
       </c>
       <c r="H500" t="n">
         <v>1148402</v>
@@ -14956,7 +14956,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G503" t="n">
-        <v>3.01793050765991</v>
+        <v>3.01793026924133</v>
       </c>
       <c r="H503" t="n">
         <v>748907</v>
@@ -14985,7 +14985,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G504" t="n">
-        <v>3.0317485332489</v>
+        <v>3.03174877166748</v>
       </c>
       <c r="H504" t="n">
         <v>283521</v>
@@ -15014,7 +15014,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G505" t="n">
-        <v>3.05109405517578</v>
+        <v>3.05109429359436</v>
       </c>
       <c r="H505" t="n">
         <v>528783</v>
@@ -15072,7 +15072,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G507" t="n">
-        <v>3.11051344871521</v>
+        <v>3.11051321029663</v>
       </c>
       <c r="H507" t="n">
         <v>760040</v>
@@ -15101,7 +15101,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G508" t="n">
-        <v>3.14229559898376</v>
+        <v>3.14229536056519</v>
       </c>
       <c r="H508" t="n">
         <v>516954</v>
@@ -15159,7 +15159,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G510" t="n">
-        <v>3.07182192802429</v>
+        <v>3.07182216644287</v>
       </c>
       <c r="H510" t="n">
         <v>253760</v>
@@ -15188,7 +15188,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>3.04556703567505</v>
+        <v>3.04556679725647</v>
       </c>
       <c r="H511" t="n">
         <v>278984</v>
@@ -15217,7 +15217,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G512" t="n">
-        <v>3.05385804176331</v>
+        <v>3.05385828018188</v>
       </c>
       <c r="H512" t="n">
         <v>428701</v>
@@ -15246,7 +15246,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>3.04556703567505</v>
+        <v>3.04556679725647</v>
       </c>
       <c r="H513" t="n">
         <v>227183</v>
@@ -15275,7 +15275,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G514" t="n">
-        <v>3.05109405517578</v>
+        <v>3.05109429359436</v>
       </c>
       <c r="H514" t="n">
         <v>193023</v>
@@ -15304,7 +15304,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G515" t="n">
-        <v>3.04418563842773</v>
+        <v>3.04418540000916</v>
       </c>
       <c r="H515" t="n">
         <v>485465</v>
@@ -15333,7 +15333,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G516" t="n">
-        <v>3.02760314941406</v>
+        <v>3.02760291099548</v>
       </c>
       <c r="H516" t="n">
         <v>310444</v>
@@ -15362,7 +15362,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G517" t="n">
-        <v>3.02760314941406</v>
+        <v>3.02760291099548</v>
       </c>
       <c r="H517" t="n">
         <v>648168</v>
@@ -15449,7 +15449,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G520" t="n">
-        <v>3.03036689758301</v>
+        <v>3.03036713600159</v>
       </c>
       <c r="H520" t="n">
         <v>232235</v>
@@ -15478,7 +15478,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G521" t="n">
-        <v>3.02345752716064</v>
+        <v>3.02345776557922</v>
       </c>
       <c r="H521" t="n">
         <v>343913</v>
@@ -15507,7 +15507,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H522" t="n">
         <v>255665</v>
@@ -15565,7 +15565,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G524" t="n">
-        <v>2.99305701255798</v>
+        <v>2.99305725097656</v>
       </c>
       <c r="H524" t="n">
         <v>1167836</v>
@@ -15594,7 +15594,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G525" t="n">
-        <v>2.99582123756409</v>
+        <v>2.99582099914551</v>
       </c>
       <c r="H525" t="n">
         <v>364917</v>
@@ -15623,7 +15623,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G526" t="n">
-        <v>2.92258334159851</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H526" t="n">
         <v>778954</v>
@@ -15681,7 +15681,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>2.90185546875</v>
+        <v>2.90185570716858</v>
       </c>
       <c r="H528" t="n">
         <v>301253</v>
@@ -15739,7 +15739,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>2.92258334159851</v>
+        <v>2.92258358001709</v>
       </c>
       <c r="H530" t="n">
         <v>347945</v>
@@ -15768,7 +15768,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>2.9433114528656</v>
+        <v>2.94331169128418</v>
       </c>
       <c r="H531" t="n">
         <v>440550</v>
@@ -15797,7 +15797,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G532" t="n">
-        <v>2.93087482452393</v>
+        <v>2.93087458610535</v>
       </c>
       <c r="H532" t="n">
         <v>357082</v>
@@ -15826,7 +15826,7 @@
         <v>4.25</v>
       </c>
       <c r="G533" t="n">
-        <v>2.93640208244324</v>
+        <v>2.93640184402466</v>
       </c>
       <c r="H533" t="n">
         <v>173706</v>
@@ -15855,7 +15855,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G534" t="n">
-        <v>2.87283754348755</v>
+        <v>2.87283778190613</v>
       </c>
       <c r="H534" t="n">
         <v>449592</v>
@@ -15884,7 +15884,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94607496261597</v>
+        <v>2.94607448577881</v>
       </c>
       <c r="H535" t="n">
         <v>538665</v>
@@ -15913,7 +15913,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G536" t="n">
-        <v>2.95160222053528</v>
+        <v>2.9516019821167</v>
       </c>
       <c r="H536" t="n">
         <v>547729</v>
@@ -15971,7 +15971,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G538" t="n">
-        <v>2.94607496261597</v>
+        <v>2.94607448577881</v>
       </c>
       <c r="H538" t="n">
         <v>458621</v>
@@ -16000,7 +16000,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>2.9433114528656</v>
+        <v>2.94331169128418</v>
       </c>
       <c r="H539" t="n">
         <v>279372</v>
@@ -16029,7 +16029,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>2.91152906417847</v>
+        <v>2.91152882575989</v>
       </c>
       <c r="H540" t="n">
         <v>588609</v>
@@ -16058,7 +16058,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.92811107635498</v>
+        <v>2.9281108379364</v>
       </c>
       <c r="H541" t="n">
         <v>404056</v>
@@ -16087,7 +16087,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G542" t="n">
-        <v>2.95989346504211</v>
+        <v>2.95989322662354</v>
       </c>
       <c r="H542" t="n">
         <v>542766</v>
@@ -16145,7 +16145,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>2.99167561531067</v>
+        <v>2.99167537689209</v>
       </c>
       <c r="H544" t="n">
         <v>338875</v>
@@ -16203,7 +16203,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97371125221252</v>
+        <v>2.97371101379395</v>
       </c>
       <c r="H546" t="n">
         <v>335573</v>
@@ -16319,7 +16319,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G550" t="n">
-        <v>2.97233009338379</v>
+        <v>2.97232937812805</v>
       </c>
       <c r="H550" t="n">
         <v>970937</v>
@@ -16348,7 +16348,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G551" t="n">
-        <v>2.91291046142578</v>
+        <v>2.91291069984436</v>
       </c>
       <c r="H551" t="n">
         <v>668920</v>
@@ -16406,7 +16406,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>2.95712971687317</v>
+        <v>2.95712947845459</v>
       </c>
       <c r="H553" t="n">
         <v>433139</v>
@@ -16493,7 +16493,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G556" t="n">
-        <v>2.90323781967163</v>
+        <v>2.90323805809021</v>
       </c>
       <c r="H556" t="n">
         <v>274776</v>
@@ -16551,7 +16551,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G558" t="n">
-        <v>2.89632892608643</v>
+        <v>2.89632868766785</v>
       </c>
       <c r="H558" t="n">
         <v>319927</v>
@@ -16609,7 +16609,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G560" t="n">
-        <v>2.87007355690002</v>
+        <v>2.8700737953186</v>
       </c>
       <c r="H560" t="n">
         <v>244609</v>
@@ -16638,7 +16638,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>2.84658265113831</v>
+        <v>2.84658217430115</v>
       </c>
       <c r="H561" t="n">
         <v>476726</v>
@@ -16667,7 +16667,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G562" t="n">
-        <v>2.8134183883667</v>
+        <v>2.81341862678528</v>
       </c>
       <c r="H562" t="n">
         <v>864736</v>
@@ -16696,7 +16696,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G563" t="n">
-        <v>2.76090860366821</v>
+        <v>2.76090884208679</v>
       </c>
       <c r="H563" t="n">
         <v>625996</v>
@@ -16783,7 +16783,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G566" t="n">
-        <v>2.77610921859741</v>
+        <v>2.77610898017883</v>
       </c>
       <c r="H566" t="n">
         <v>1058281</v>
@@ -16812,7 +16812,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75261759757996</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H567" t="n">
         <v>559095</v>
@@ -16870,7 +16870,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H569" t="n">
         <v>246177</v>
@@ -16957,7 +16957,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G572" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H572" t="n">
         <v>457593</v>
@@ -17044,7 +17044,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G575" t="n">
-        <v>2.71669006347656</v>
+        <v>2.71668982505798</v>
       </c>
       <c r="H575" t="n">
         <v>399828</v>
@@ -17073,7 +17073,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>2.7360360622406</v>
+        <v>2.73603582382202</v>
       </c>
       <c r="H576" t="n">
         <v>219577</v>
@@ -17102,7 +17102,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G577" t="n">
-        <v>2.75261759757996</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H577" t="n">
         <v>253623</v>
@@ -17218,7 +17218,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77749061584473</v>
+        <v>2.77749085426331</v>
       </c>
       <c r="H581" t="n">
         <v>202226</v>
@@ -17334,7 +17334,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G585" t="n">
-        <v>2.75261759757996</v>
+        <v>2.75261783599854</v>
       </c>
       <c r="H585" t="n">
         <v>331776</v>
@@ -17363,7 +17363,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G586" t="n">
-        <v>2.74018144607544</v>
+        <v>2.74018120765686</v>
       </c>
       <c r="H586" t="n">
         <v>165727</v>
@@ -17392,7 +17392,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G587" t="n">
-        <v>2.75814533233643</v>
+        <v>2.75814509391785</v>
       </c>
       <c r="H587" t="n">
         <v>463180</v>
@@ -17450,7 +17450,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G589" t="n">
-        <v>2.73879933357239</v>
+        <v>2.73879909515381</v>
       </c>
       <c r="H589" t="n">
         <v>665011</v>
@@ -17595,7 +17595,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G594" t="n">
-        <v>2.87836456298828</v>
+        <v>2.87836503982544</v>
       </c>
       <c r="H594" t="n">
         <v>975352</v>
@@ -17653,7 +17653,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G596" t="n">
-        <v>2.86040067672729</v>
+        <v>2.86040091514587</v>
       </c>
       <c r="H596" t="n">
         <v>1036090</v>
@@ -17682,7 +17682,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G597" t="n">
-        <v>2.88389205932617</v>
+        <v>2.88389182090759</v>
       </c>
       <c r="H597" t="n">
         <v>605764</v>
@@ -17711,7 +17711,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>2.9433114528656</v>
+        <v>2.94331169128418</v>
       </c>
       <c r="H598" t="n">
         <v>1052192</v>
@@ -17740,7 +17740,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G599" t="n">
-        <v>2.91014671325684</v>
+        <v>2.91014695167542</v>
       </c>
       <c r="H599" t="n">
         <v>1120884</v>
@@ -17798,7 +17798,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>2.88527417182922</v>
+        <v>2.88527369499207</v>
       </c>
       <c r="H601" t="n">
         <v>1049953</v>
@@ -17885,7 +17885,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G604" t="n">
-        <v>2.92120146751404</v>
+        <v>2.9212019443512</v>
       </c>
       <c r="H604" t="n">
         <v>500397</v>
@@ -17914,7 +17914,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>2.88803768157959</v>
+        <v>2.88803791999817</v>
       </c>
       <c r="H605" t="n">
         <v>796514</v>
@@ -18001,7 +18001,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G608" t="n">
-        <v>2.85901880264282</v>
+        <v>2.8590190410614</v>
       </c>
       <c r="H608" t="n">
         <v>417011</v>
@@ -18030,7 +18030,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G609" t="n">
-        <v>2.84520053863525</v>
+        <v>2.84520077705383</v>
       </c>
       <c r="H609" t="n">
         <v>365525</v>
@@ -18059,7 +18059,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G610" t="n">
-        <v>2.86869192123413</v>
+        <v>2.86869168281555</v>
       </c>
       <c r="H610" t="n">
         <v>802117</v>
@@ -18088,7 +18088,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G611" t="n">
-        <v>2.91152906417847</v>
+        <v>2.91152882575989</v>
       </c>
       <c r="H611" t="n">
         <v>402937</v>
@@ -18117,7 +18117,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G612" t="n">
-        <v>2.90323781967163</v>
+        <v>2.90323805809021</v>
       </c>
       <c r="H612" t="n">
         <v>379452</v>
@@ -18146,7 +18146,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>2.87421917915344</v>
+        <v>2.87421894073486</v>
       </c>
       <c r="H613" t="n">
         <v>527133</v>
@@ -18175,7 +18175,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G614" t="n">
-        <v>2.84520053863525</v>
+        <v>2.84520077705383</v>
       </c>
       <c r="H614" t="n">
         <v>683120</v>
@@ -18204,7 +18204,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G615" t="n">
-        <v>2.86454677581787</v>
+        <v>2.86454653739929</v>
       </c>
       <c r="H615" t="n">
         <v>695451</v>
@@ -18233,7 +18233,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G616" t="n">
-        <v>2.89080119132996</v>
+        <v>2.89080095291138</v>
       </c>
       <c r="H616" t="n">
         <v>255638</v>
@@ -18262,7 +18262,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G617" t="n">
-        <v>2.89632892608643</v>
+        <v>2.89632868766785</v>
       </c>
       <c r="H617" t="n">
         <v>507785</v>
@@ -18291,7 +18291,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G618" t="n">
-        <v>2.92120146751404</v>
+        <v>2.9212019443512</v>
       </c>
       <c r="H618" t="n">
         <v>836606</v>
@@ -18320,7 +18320,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G619" t="n">
-        <v>2.93087482452393</v>
+        <v>2.93087458610535</v>
       </c>
       <c r="H619" t="n">
         <v>258418</v>
@@ -18407,7 +18407,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G622" t="n">
-        <v>2.98338413238525</v>
+        <v>2.98338437080383</v>
       </c>
       <c r="H622" t="n">
         <v>557576</v>
@@ -18523,7 +18523,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H626" t="n">
         <v>1249599</v>
@@ -18552,7 +18552,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G627" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898502349854</v>
       </c>
       <c r="H627" t="n">
         <v>241326</v>
@@ -18668,7 +18668,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G631" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898502349854</v>
       </c>
       <c r="H631" t="n">
         <v>472455</v>
@@ -18697,7 +18697,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G632" t="n">
-        <v>3.02898478507996</v>
+        <v>3.02898502349854</v>
       </c>
       <c r="H632" t="n">
         <v>518046</v>
@@ -18755,7 +18755,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G634" t="n">
-        <v>3.03036689758301</v>
+        <v>3.03036713600159</v>
       </c>
       <c r="H634" t="n">
         <v>523810</v>
@@ -18784,7 +18784,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G635" t="n">
-        <v>3.05109405517578</v>
+        <v>3.05109429359436</v>
       </c>
       <c r="H635" t="n">
         <v>573735</v>
@@ -18813,7 +18813,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H636" t="n">
         <v>165327</v>
@@ -18842,7 +18842,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G637" t="n">
-        <v>3.034512758255</v>
+        <v>3.03451228141785</v>
       </c>
       <c r="H637" t="n">
         <v>362948</v>
@@ -18871,7 +18871,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G638" t="n">
-        <v>3.0248396396637</v>
+        <v>3.02483940124512</v>
       </c>
       <c r="H638" t="n">
         <v>187474</v>
@@ -18900,7 +18900,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>3.08287668228149</v>
+        <v>3.08287644386292</v>
       </c>
       <c r="H639" t="n">
         <v>455246</v>
@@ -18929,7 +18929,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G640" t="n">
-        <v>3.08011293411255</v>
+        <v>3.08011317253113</v>
       </c>
       <c r="H640" t="n">
         <v>539646</v>
@@ -18987,7 +18987,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>3.04003977775574</v>
+        <v>3.04003953933716</v>
       </c>
       <c r="H642" t="n">
         <v>690661</v>
@@ -19016,7 +19016,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>3.08149456977844</v>
+        <v>3.08149480819702</v>
       </c>
       <c r="H643" t="n">
         <v>293010</v>
@@ -19045,7 +19045,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G644" t="n">
-        <v>3.09669470787048</v>
+        <v>3.09669494628906</v>
       </c>
       <c r="H644" t="n">
         <v>242340</v>
@@ -19103,7 +19103,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G646" t="n">
-        <v>3.14229559898376</v>
+        <v>3.14229536056519</v>
       </c>
       <c r="H646" t="n">
         <v>601188</v>
@@ -19132,7 +19132,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G647" t="n">
-        <v>3.06629490852356</v>
+        <v>3.06629467010498</v>
       </c>
       <c r="H647" t="n">
         <v>369408</v>
@@ -19190,7 +19190,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G649" t="n">
-        <v>3.09669470787048</v>
+        <v>3.09669494628906</v>
       </c>
       <c r="H649" t="n">
         <v>458945</v>
@@ -19248,7 +19248,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G651" t="n">
-        <v>3.10360383987427</v>
+        <v>3.10360479354858</v>
       </c>
       <c r="H651" t="n">
         <v>725248</v>
@@ -19277,7 +19277,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G652" t="n">
-        <v>3.12709522247314</v>
+        <v>3.12709546089172</v>
       </c>
       <c r="H652" t="n">
         <v>655086</v>
@@ -19364,7 +19364,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G655" t="n">
-        <v>3.11742258071899</v>
+        <v>3.11742281913757</v>
       </c>
       <c r="H655" t="n">
         <v>774559</v>
@@ -19393,7 +19393,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G656" t="n">
-        <v>3.0897855758667</v>
+        <v>3.08978629112244</v>
       </c>
       <c r="H656" t="n">
         <v>451701</v>
@@ -19509,7 +19509,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>3.11189532279968</v>
+        <v>3.11189556121826</v>
       </c>
       <c r="H660" t="n">
         <v>464575</v>
@@ -19567,7 +19567,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G662" t="n">
-        <v>3.13814949989319</v>
+        <v>3.13814973831177</v>
       </c>
       <c r="H662" t="n">
         <v>519012</v>
@@ -19625,7 +19625,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G664" t="n">
-        <v>3.12018585205078</v>
+        <v>3.12018609046936</v>
       </c>
       <c r="H664" t="n">
         <v>390842</v>
@@ -19654,7 +19654,7 @@
         <v>4.5</v>
       </c>
       <c r="G665" t="n">
-        <v>3.10913157463074</v>
+        <v>3.10913133621216</v>
       </c>
       <c r="H665" t="n">
         <v>605477</v>
@@ -19683,7 +19683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G666" t="n">
-        <v>3.10222220420837</v>
+        <v>3.10222196578979</v>
       </c>
       <c r="H666" t="n">
         <v>406879</v>
@@ -19712,7 +19712,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.10913157463074</v>
+        <v>3.10913133621216</v>
       </c>
       <c r="H667" t="n">
         <v>591269</v>
@@ -19741,7 +19741,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G668" t="n">
-        <v>3.10222220420837</v>
+        <v>3.10222196578979</v>
       </c>
       <c r="H668" t="n">
         <v>802632</v>
@@ -19770,7 +19770,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G669" t="n">
-        <v>3.26251530647278</v>
+        <v>3.26251554489136</v>
       </c>
       <c r="H669" t="n">
         <v>2348370</v>
@@ -19799,7 +19799,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G670" t="n">
-        <v>3.3122615814209</v>
+        <v>3.31226134300232</v>
       </c>
       <c r="H670" t="n">
         <v>1432256</v>
@@ -19857,7 +19857,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G672" t="n">
-        <v>3.3468074798584</v>
+        <v>3.34680724143982</v>
       </c>
       <c r="H672" t="n">
         <v>697587</v>
@@ -19915,7 +19915,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38411617279053</v>
+        <v>3.38411664962769</v>
       </c>
       <c r="H674" t="n">
         <v>577089</v>
@@ -20031,7 +20031,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>3.30535244941711</v>
+        <v>3.30535197257996</v>
       </c>
       <c r="H678" t="n">
         <v>478581</v>
@@ -20060,7 +20060,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G679" t="n">
-        <v>3.33575296401978</v>
+        <v>3.3357527256012</v>
       </c>
       <c r="H679" t="n">
         <v>357536</v>
@@ -20118,7 +20118,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G681" t="n">
-        <v>3.31502509117126</v>
+        <v>3.31502532958984</v>
       </c>
       <c r="H681" t="n">
         <v>329531</v>
@@ -20147,7 +20147,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G682" t="n">
-        <v>3.35648012161255</v>
+        <v>3.35647988319397</v>
       </c>
       <c r="H682" t="n">
         <v>547505</v>
@@ -20234,7 +20234,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G685" t="n">
-        <v>3.36615347862244</v>
+        <v>3.36615300178528</v>
       </c>
       <c r="H685" t="n">
         <v>497823</v>
@@ -20263,7 +20263,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G686" t="n">
-        <v>3.36615347862244</v>
+        <v>3.36615300178528</v>
       </c>
       <c r="H686" t="n">
         <v>412491</v>
@@ -20292,7 +20292,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G687" t="n">
-        <v>3.36615347862244</v>
+        <v>3.36615300178528</v>
       </c>
       <c r="H687" t="n">
         <v>264276</v>
@@ -20321,7 +20321,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G688" t="n">
-        <v>3.32469820976257</v>
+        <v>3.32469773292542</v>
       </c>
       <c r="H688" t="n">
         <v>384931</v>
@@ -20408,7 +20408,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31778836250305</v>
+        <v>3.31778883934021</v>
       </c>
       <c r="H691" t="n">
         <v>207705</v>
@@ -20466,7 +20466,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G693" t="n">
-        <v>3.3537163734436</v>
+        <v>3.35371661186218</v>
       </c>
       <c r="H693" t="n">
         <v>275517</v>
@@ -20495,7 +20495,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G694" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H694" t="n">
         <v>378541</v>
@@ -20524,7 +20524,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G695" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H695" t="n">
         <v>334779</v>
@@ -20582,7 +20582,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G697" t="n">
-        <v>3.33575296401978</v>
+        <v>3.3357527256012</v>
       </c>
       <c r="H697" t="n">
         <v>426921</v>
@@ -20611,7 +20611,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G698" t="n">
-        <v>3.3426616191864</v>
+        <v>3.34266185760498</v>
       </c>
       <c r="H698" t="n">
         <v>268858</v>
@@ -20698,7 +20698,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>3.37168049812317</v>
+        <v>3.37168025970459</v>
       </c>
       <c r="H701" t="n">
         <v>1574407</v>
@@ -20756,7 +20756,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G703" t="n">
-        <v>3.37168049812317</v>
+        <v>3.37168025970459</v>
       </c>
       <c r="H703" t="n">
         <v>496384</v>
@@ -20785,7 +20785,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G704" t="n">
-        <v>3.35648012161255</v>
+        <v>3.35647988319397</v>
       </c>
       <c r="H704" t="n">
         <v>234747</v>
@@ -20814,7 +20814,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G705" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H705" t="n">
         <v>215533</v>
@@ -20843,7 +20843,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G706" t="n">
-        <v>3.38273501396179</v>
+        <v>3.38273525238037</v>
       </c>
       <c r="H706" t="n">
         <v>370437</v>
@@ -20872,7 +20872,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G707" t="n">
-        <v>3.34957098960876</v>
+        <v>3.34957122802734</v>
       </c>
       <c r="H707" t="n">
         <v>440703</v>
@@ -20959,7 +20959,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G710" t="n">
-        <v>3.32469820976257</v>
+        <v>3.32469773292542</v>
       </c>
       <c r="H710" t="n">
         <v>248745</v>
@@ -21017,7 +21017,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G712" t="n">
-        <v>3.33575296401978</v>
+        <v>3.3357527256012</v>
       </c>
       <c r="H712" t="n">
         <v>415959</v>
@@ -21046,7 +21046,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G713" t="n">
-        <v>3.36200761795044</v>
+        <v>3.3620080947876</v>
       </c>
       <c r="H713" t="n">
         <v>399022</v>
@@ -21075,7 +21075,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G714" t="n">
-        <v>3.37029814720154</v>
+        <v>3.37029838562012</v>
       </c>
       <c r="H714" t="n">
         <v>307384</v>
@@ -21191,7 +21191,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G718" t="n">
-        <v>3.46236944198608</v>
+        <v>3.46236896514893</v>
       </c>
       <c r="H718" t="n">
         <v>296407</v>
@@ -21220,7 +21220,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G719" t="n">
-        <v>3.46092772483826</v>
+        <v>3.46092844009399</v>
       </c>
       <c r="H719" t="n">
         <v>505932</v>
@@ -21278,7 +21278,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>3.46957302093506</v>
+        <v>3.46957325935364</v>
       </c>
       <c r="H721" t="n">
         <v>1025779</v>
@@ -21307,7 +21307,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G722" t="n">
-        <v>3.4566056728363</v>
+        <v>3.45660543441772</v>
       </c>
       <c r="H722" t="n">
         <v>697211</v>
@@ -21394,7 +21394,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G725" t="n">
-        <v>3.553142786026</v>
+        <v>3.55314302444458</v>
       </c>
       <c r="H725" t="n">
         <v>854127</v>
@@ -21423,7 +21423,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G726" t="n">
-        <v>3.57475566864014</v>
+        <v>3.57475543022156</v>
       </c>
       <c r="H726" t="n">
         <v>985537</v>
@@ -21452,7 +21452,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G727" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H727" t="n">
         <v>685720</v>
@@ -21510,7 +21510,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G729" t="n">
-        <v>3.67777609825134</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H729" t="n">
         <v>630184</v>
@@ -21539,7 +21539,7 @@
         <v>5.125</v>
       </c>
       <c r="G730" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H730" t="n">
         <v>660523</v>
@@ -21568,7 +21568,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65976548194885</v>
+        <v>3.65976595878601</v>
       </c>
       <c r="H731" t="n">
         <v>458971</v>
@@ -21626,7 +21626,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>3.70659327507019</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H733" t="n">
         <v>827997</v>
@@ -21655,7 +21655,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G734" t="n">
-        <v>3.6525616645813</v>
+        <v>3.65256214141846</v>
       </c>
       <c r="H734" t="n">
         <v>522904</v>
@@ -21742,7 +21742,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>3.63094854354858</v>
+        <v>3.63094902038574</v>
       </c>
       <c r="H737" t="n">
         <v>602362</v>
@@ -21887,7 +21887,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G742" t="n">
-        <v>3.58484172821045</v>
+        <v>3.58484148979187</v>
       </c>
       <c r="H742" t="n">
         <v>346299</v>
@@ -21916,7 +21916,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.5444974899292</v>
+        <v>3.54449772834778</v>
       </c>
       <c r="H743" t="n">
         <v>449069</v>
@@ -21974,7 +21974,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G745" t="n">
-        <v>3.52288508415222</v>
+        <v>3.52288484573364</v>
       </c>
       <c r="H745" t="n">
         <v>2145807</v>
@@ -22003,7 +22003,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>3.5444974899292</v>
+        <v>3.54449772834778</v>
       </c>
       <c r="H746" t="n">
         <v>1059414</v>
@@ -22032,7 +22032,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G747" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H747" t="n">
         <v>607759</v>
@@ -22061,7 +22061,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G748" t="n">
-        <v>3.59925007820129</v>
+        <v>3.59924960136414</v>
       </c>
       <c r="H748" t="n">
         <v>415115</v>
@@ -22090,7 +22090,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G749" t="n">
-        <v>3.57619690895081</v>
+        <v>3.57619643211365</v>
       </c>
       <c r="H749" t="n">
         <v>582111</v>
@@ -22148,7 +22148,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G751" t="n">
-        <v>3.58051872253418</v>
+        <v>3.58051896095276</v>
       </c>
       <c r="H751" t="n">
         <v>386818</v>
@@ -22177,7 +22177,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G752" t="n">
-        <v>3.60933589935303</v>
+        <v>3.60933613777161</v>
       </c>
       <c r="H752" t="n">
         <v>272384</v>
@@ -22206,7 +22206,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.62014245986938</v>
+        <v>3.62014222145081</v>
       </c>
       <c r="H753" t="n">
         <v>353573</v>
@@ -22235,7 +22235,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G754" t="n">
-        <v>3.59780883789062</v>
+        <v>3.59780931472778</v>
       </c>
       <c r="H754" t="n">
         <v>281615</v>
@@ -22264,7 +22264,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G755" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H755" t="n">
         <v>308092</v>
@@ -22380,7 +22380,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H759" t="n">
         <v>333042</v>
@@ -22409,7 +22409,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G760" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H760" t="n">
         <v>144620</v>
@@ -22438,7 +22438,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G761" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H761" t="n">
         <v>140253</v>
@@ -22467,7 +22467,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G762" t="n">
-        <v>3.60573410987854</v>
+        <v>3.60573363304138</v>
       </c>
       <c r="H762" t="n">
         <v>233504</v>
@@ -22496,7 +22496,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57187390327454</v>
+        <v>3.57187461853027</v>
       </c>
       <c r="H763" t="n">
         <v>525060</v>
@@ -22525,7 +22525,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G764" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H764" t="n">
         <v>136835</v>
@@ -22554,7 +22554,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G765" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H765" t="n">
         <v>363470</v>
@@ -22583,7 +22583,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G766" t="n">
-        <v>3.57619690895081</v>
+        <v>3.57619643211365</v>
       </c>
       <c r="H766" t="n">
         <v>852645</v>
@@ -22612,7 +22612,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G767" t="n">
-        <v>3.59060525894165</v>
+        <v>3.59060502052307</v>
       </c>
       <c r="H767" t="n">
         <v>593676</v>
@@ -22670,7 +22670,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G769" t="n">
-        <v>3.6006908416748</v>
+        <v>3.60069108009338</v>
       </c>
       <c r="H769" t="n">
         <v>241517</v>
@@ -22699,7 +22699,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.56611037254333</v>
+        <v>3.56611061096191</v>
       </c>
       <c r="H770" t="n">
         <v>220728</v>
@@ -22728,7 +22728,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G771" t="n">
-        <v>3.57907819747925</v>
+        <v>3.57907795906067</v>
       </c>
       <c r="H771" t="n">
         <v>473966</v>
@@ -22757,7 +22757,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G772" t="n">
-        <v>3.67057275772095</v>
+        <v>3.67057228088379</v>
       </c>
       <c r="H772" t="n">
         <v>490175</v>
@@ -22873,7 +22873,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G776" t="n">
-        <v>3.70659327507019</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H776" t="n">
         <v>535968</v>
@@ -22902,7 +22902,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G777" t="n">
-        <v>3.70659327507019</v>
+        <v>3.70659351348877</v>
       </c>
       <c r="H777" t="n">
         <v>394359</v>
@@ -22931,7 +22931,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>3.67777609825134</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H778" t="n">
         <v>510087</v>
@@ -22960,7 +22960,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H779" t="n">
         <v>537475</v>
@@ -22989,7 +22989,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.72460436820984</v>
+        <v>3.72460460662842</v>
       </c>
       <c r="H780" t="n">
         <v>198706</v>
@@ -23047,7 +23047,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>3.75702333450317</v>
+        <v>3.75702357292175</v>
       </c>
       <c r="H782" t="n">
         <v>152644</v>
@@ -23076,7 +23076,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>3.71379828453064</v>
+        <v>3.71379780769348</v>
       </c>
       <c r="H783" t="n">
         <v>188130</v>
@@ -23105,7 +23105,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>3.71379828453064</v>
+        <v>3.71379780769348</v>
       </c>
       <c r="H784" t="n">
         <v>217194</v>
@@ -23192,7 +23192,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G787" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H787" t="n">
         <v>298424</v>
@@ -23221,7 +23221,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G788" t="n">
-        <v>3.7029914855957</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H788" t="n">
         <v>296476</v>
@@ -23337,7 +23337,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>3.71739983558655</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H792" t="n">
         <v>225935</v>
@@ -23366,7 +23366,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G793" t="n">
-        <v>3.7029914855957</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H793" t="n">
         <v>262081</v>
@@ -23424,7 +23424,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.64175510406494</v>
+        <v>3.64175486564636</v>
       </c>
       <c r="H795" t="n">
         <v>413188</v>
@@ -23453,7 +23453,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>3.62014245986938</v>
+        <v>3.62014222145081</v>
       </c>
       <c r="H796" t="n">
         <v>385770</v>
@@ -23540,7 +23540,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>3.67777609825134</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H799" t="n">
         <v>119947</v>
@@ -23569,7 +23569,7 @@
         <v>5.125</v>
       </c>
       <c r="G800" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H800" t="n">
         <v>156322</v>
@@ -23598,7 +23598,7 @@
         <v>5.125</v>
       </c>
       <c r="G801" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H801" t="n">
         <v>257011</v>
@@ -23627,7 +23627,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>3.67777609825134</v>
+        <v>3.6777765750885</v>
       </c>
       <c r="H802" t="n">
         <v>357933</v>
@@ -23714,7 +23714,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>3.69578766822815</v>
+        <v>3.69578719139099</v>
       </c>
       <c r="H805" t="n">
         <v>390641</v>
@@ -23743,7 +23743,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.67057275772095</v>
+        <v>3.67057228088379</v>
       </c>
       <c r="H806" t="n">
         <v>358329</v>
@@ -23772,7 +23772,7 @@
         <v>5.125</v>
       </c>
       <c r="G807" t="n">
-        <v>3.69218516349792</v>
+        <v>3.69218492507935</v>
       </c>
       <c r="H807" t="n">
         <v>331891</v>
@@ -23801,7 +23801,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G808" t="n">
-        <v>3.67057275772095</v>
+        <v>3.67057228088379</v>
       </c>
       <c r="H808" t="n">
         <v>272752</v>
@@ -23830,7 +23830,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H809" t="n">
         <v>629355</v>
@@ -23946,7 +23946,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H813" t="n">
         <v>202688</v>
@@ -23975,7 +23975,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H814" t="n">
         <v>370664</v>
@@ -24004,7 +24004,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G815" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H815" t="n">
         <v>312178</v>
@@ -24033,7 +24033,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G816" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H816" t="n">
         <v>225018</v>
@@ -24062,7 +24062,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H817" t="n">
         <v>140668</v>
@@ -24091,7 +24091,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>3.7462170124054</v>
+        <v>3.74621677398682</v>
       </c>
       <c r="H818" t="n">
         <v>255505</v>
@@ -24120,7 +24120,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342106819153</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H819" t="n">
         <v>228708</v>
@@ -24149,7 +24149,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>3.74981951713562</v>
+        <v>3.74981880187988</v>
       </c>
       <c r="H820" t="n">
         <v>270294</v>
@@ -24178,7 +24178,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>3.75702333450317</v>
+        <v>3.75702357292175</v>
       </c>
       <c r="H821" t="n">
         <v>217419</v>
@@ -24265,7 +24265,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>3.72460436820984</v>
+        <v>3.72460460662842</v>
       </c>
       <c r="H824" t="n">
         <v>343423</v>
@@ -24294,7 +24294,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342106819153</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H825" t="n">
         <v>242523</v>
@@ -24352,7 +24352,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G827" t="n">
-        <v>3.69938921928406</v>
+        <v>3.69938969612122</v>
       </c>
       <c r="H827" t="n">
         <v>236994</v>
@@ -24381,7 +24381,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G828" t="n">
-        <v>3.7029914855957</v>
+        <v>3.70299100875854</v>
       </c>
       <c r="H828" t="n">
         <v>168676</v>
@@ -24410,7 +24410,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>3.72460436820984</v>
+        <v>3.72460460662842</v>
       </c>
       <c r="H829" t="n">
         <v>248488</v>
@@ -24439,7 +24439,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G830" t="n">
-        <v>3.73180842399597</v>
+        <v>3.73180794715881</v>
       </c>
       <c r="H830" t="n">
         <v>177186</v>
@@ -24468,7 +24468,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>3.72460436820984</v>
+        <v>3.72460460662842</v>
       </c>
       <c r="H831" t="n">
         <v>204215</v>
@@ -24497,7 +24497,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G832" t="n">
-        <v>3.76062512397766</v>
+        <v>3.76062536239624</v>
       </c>
       <c r="H832" t="n">
         <v>268201</v>
@@ -24526,7 +24526,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584027290344</v>
       </c>
       <c r="H833" t="n">
         <v>158358</v>
@@ -24555,7 +24555,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G834" t="n">
-        <v>3.79304456710815</v>
+        <v>3.79304432868958</v>
       </c>
       <c r="H834" t="n">
         <v>288604</v>
@@ -24584,7 +24584,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>3.82546377182007</v>
+        <v>3.82546424865723</v>
       </c>
       <c r="H835" t="n">
         <v>526098</v>
@@ -24613,7 +24613,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G836" t="n">
-        <v>3.81465721130371</v>
+        <v>3.81465744972229</v>
       </c>
       <c r="H836" t="n">
         <v>353172</v>
@@ -24642,7 +24642,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342106819153</v>
+        <v>3.75342154502869</v>
       </c>
       <c r="H837" t="n">
         <v>261649</v>
@@ -24700,7 +24700,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>3.76422810554504</v>
+        <v>3.76422786712646</v>
       </c>
       <c r="H839" t="n">
         <v>155864</v>
@@ -24729,7 +24729,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.7858407497406</v>
+        <v>3.78584027290344</v>
       </c>
       <c r="H840" t="n">
         <v>309517</v>
@@ -24758,7 +24758,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.77863550186157</v>
+        <v>3.77863597869873</v>
       </c>
       <c r="H841" t="n">
         <v>231779</v>
@@ -24787,7 +24787,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>3.81465721130371</v>
+        <v>3.81465744972229</v>
       </c>
       <c r="H842" t="n">
         <v>316067</v>
@@ -24816,7 +24816,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148548126221</v>
+        <v>3.86148500442505</v>
       </c>
       <c r="H843" t="n">
         <v>518806</v>
@@ -24845,7 +24845,7 @@
         <v>5.375</v>
       </c>
       <c r="G844" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H844" t="n">
         <v>150028</v>
@@ -24874,7 +24874,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.82186150550842</v>
+        <v>3.82186126708984</v>
       </c>
       <c r="H845" t="n">
         <v>210214</v>
@@ -24961,7 +24961,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>3.76422810554504</v>
+        <v>3.76422786712646</v>
       </c>
       <c r="H848" t="n">
         <v>621281</v>
@@ -24990,7 +24990,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G849" t="n">
-        <v>3.78944301605225</v>
+        <v>3.78944277763367</v>
       </c>
       <c r="H849" t="n">
         <v>309778</v>
@@ -25019,7 +25019,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G850" t="n">
-        <v>3.86508727073669</v>
+        <v>3.86508750915527</v>
       </c>
       <c r="H850" t="n">
         <v>585661</v>
@@ -25048,7 +25048,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>3.82906556129456</v>
+        <v>3.82906603813171</v>
       </c>
       <c r="H851" t="n">
         <v>1005431</v>
@@ -25106,7 +25106,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G853" t="n">
-        <v>3.87589383125305</v>
+        <v>3.87589406967163</v>
       </c>
       <c r="H853" t="n">
         <v>449570</v>
@@ -25135,7 +25135,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80024933815002</v>
+        <v>3.8002495765686</v>
       </c>
       <c r="H854" t="n">
         <v>521291</v>
@@ -25193,7 +25193,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80024933815002</v>
+        <v>3.8002495765686</v>
       </c>
       <c r="H856" t="n">
         <v>340183</v>
@@ -25251,7 +25251,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80024933815002</v>
+        <v>3.8002495765686</v>
       </c>
       <c r="H858" t="n">
         <v>247892</v>
@@ -25338,7 +25338,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>3.8470766544342</v>
+        <v>3.84707641601562</v>
       </c>
       <c r="H861" t="n">
         <v>142215</v>
@@ -25367,7 +25367,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G862" t="n">
-        <v>3.83266830444336</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H862" t="n">
         <v>423140</v>
@@ -25396,7 +25396,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G863" t="n">
-        <v>3.81105542182922</v>
+        <v>3.81105518341064</v>
       </c>
       <c r="H863" t="n">
         <v>841113</v>
@@ -25483,7 +25483,7 @@
         <v>5.375</v>
       </c>
       <c r="G866" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H866" t="n">
         <v>334082</v>
@@ -25512,7 +25512,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>3.90831279754639</v>
+        <v>3.90831351280212</v>
       </c>
       <c r="H867" t="n">
         <v>679193</v>
@@ -25541,7 +25541,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>3.90471053123474</v>
+        <v>3.9047110080719</v>
       </c>
       <c r="H868" t="n">
         <v>1580647</v>
@@ -25570,7 +25570,7 @@
         <v>5.375</v>
       </c>
       <c r="G869" t="n">
-        <v>3.87229204177856</v>
+        <v>3.87229156494141</v>
       </c>
       <c r="H869" t="n">
         <v>307691</v>
@@ -25599,7 +25599,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.88309788703918</v>
+        <v>3.88309741020203</v>
       </c>
       <c r="H870" t="n">
         <v>376869</v>
@@ -25628,7 +25628,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G871" t="n">
-        <v>3.83266830444336</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H871" t="n">
         <v>429811</v>
@@ -25657,7 +25657,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91191506385803</v>
+        <v>3.91191530227661</v>
       </c>
       <c r="H872" t="n">
         <v>627265</v>
@@ -25715,7 +25715,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>3.80024933815002</v>
+        <v>3.8002495765686</v>
       </c>
       <c r="H874" t="n">
         <v>558719</v>
@@ -25744,7 +25744,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>3.83266830444336</v>
+        <v>3.83266878128052</v>
       </c>
       <c r="H875" t="n">
         <v>683792</v>
@@ -25773,7 +25773,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G876" t="n">
-        <v>3.91191506385803</v>
+        <v>3.91191530227661</v>
       </c>
       <c r="H876" t="n">
         <v>933919</v>
@@ -25802,7 +25802,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91191506385803</v>
+        <v>3.91191530227661</v>
       </c>
       <c r="H877" t="n">
         <v>497300</v>
@@ -25831,7 +25831,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G878" t="n">
-        <v>3.92632293701172</v>
+        <v>3.92632341384888</v>
       </c>
       <c r="H878" t="n">
         <v>368905</v>
@@ -25918,7 +25918,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97315120697021</v>
+        <v>3.97315144538879</v>
       </c>
       <c r="H881" t="n">
         <v>255729</v>
@@ -25947,7 +25947,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>4.01997900009155</v>
+        <v>4.01997852325439</v>
       </c>
       <c r="H882" t="n">
         <v>458370</v>
@@ -26121,7 +26121,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>4.2180962562561</v>
+        <v>4.21809577941895</v>
       </c>
       <c r="H888" t="n">
         <v>1316501</v>
@@ -26266,7 +26266,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G893" t="n">
-        <v>4.19648313522339</v>
+        <v>4.19648361206055</v>
       </c>
       <c r="H893" t="n">
         <v>718224</v>
@@ -26382,7 +26382,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>4.29013824462891</v>
+        <v>4.29013919830322</v>
       </c>
       <c r="H897" t="n">
         <v>461627</v>
@@ -26411,7 +26411,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G898" t="n">
-        <v>4.31895637512207</v>
+        <v>4.31895589828491</v>
       </c>
       <c r="H898" t="n">
         <v>927247</v>
@@ -26469,7 +26469,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>4.29374122619629</v>
+        <v>4.29374074935913</v>
       </c>
       <c r="H900" t="n">
         <v>741766</v>
@@ -26527,7 +26527,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>4.29374122619629</v>
+        <v>4.29374074935913</v>
       </c>
       <c r="H902" t="n">
         <v>663557</v>
@@ -26556,7 +26556,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G903" t="n">
-        <v>4.3261604309082</v>
+        <v>4.32616090774536</v>
       </c>
       <c r="H903" t="n">
         <v>982085</v>
@@ -26614,7 +26614,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G905" t="n">
-        <v>4.39820289611816</v>
+        <v>4.39820241928101</v>
       </c>
       <c r="H905" t="n">
         <v>530337</v>
@@ -26643,7 +26643,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G906" t="n">
-        <v>4.42702007293701</v>
+        <v>4.42702054977417</v>
       </c>
       <c r="H906" t="n">
         <v>303177</v>
@@ -26759,7 +26759,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>4.11723709106445</v>
+        <v>4.11723661422729</v>
       </c>
       <c r="H910" t="n">
         <v>1141771</v>
@@ -26846,7 +26846,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.89750719070435</v>
+        <v>3.89750647544861</v>
       </c>
       <c r="H913" t="n">
         <v>1781293</v>
@@ -26904,7 +26904,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>3.77863550186157</v>
+        <v>3.77863597869873</v>
       </c>
       <c r="H915" t="n">
         <v>1709583</v>
@@ -26933,7 +26933,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81826019287109</v>
+        <v>3.81825995445251</v>
       </c>
       <c r="H916" t="n">
         <v>1032190</v>
@@ -26962,7 +26962,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.71739983558655</v>
+        <v>3.71740007400513</v>
       </c>
       <c r="H917" t="n">
         <v>905147</v>
@@ -27049,7 +27049,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G920" t="n">
-        <v>3.24624109268188</v>
+        <v>3.24624133110046</v>
       </c>
       <c r="H920" t="n">
         <v>847418</v>
@@ -27078,7 +27078,7 @@
         <v>4.5</v>
       </c>
       <c r="G921" t="n">
-        <v>3.24191832542419</v>
+        <v>3.24191856384277</v>
       </c>
       <c r="H921" t="n">
         <v>1478690</v>
@@ -27107,7 +27107,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>2.95662975311279</v>
+        <v>2.95662999153137</v>
       </c>
       <c r="H922" t="n">
         <v>2073810</v>
@@ -27194,7 +27194,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G925" t="n">
-        <v>2.70448017120361</v>
+        <v>2.70448064804077</v>
       </c>
       <c r="H925" t="n">
         <v>2712504</v>
@@ -27223,7 +27223,7 @@
         <v>3.75</v>
       </c>
       <c r="G926" t="n">
-        <v>2.70159864425659</v>
+        <v>2.70159888267517</v>
       </c>
       <c r="H926" t="n">
         <v>1078695</v>
@@ -27252,7 +27252,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G927" t="n">
-        <v>2.58921241760254</v>
+        <v>2.58921217918396</v>
       </c>
       <c r="H927" t="n">
         <v>1414173</v>
@@ -27310,7 +27310,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G929" t="n">
-        <v>2.45809483528137</v>
+        <v>2.45809459686279</v>
       </c>
       <c r="H929" t="n">
         <v>1450159</v>
@@ -27629,7 +27629,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>2.9681568145752</v>
+        <v>2.96815657615662</v>
       </c>
       <c r="H940" t="n">
         <v>1265202</v>
@@ -27687,7 +27687,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>3.02579045295715</v>
+        <v>3.02579069137573</v>
       </c>
       <c r="H942" t="n">
         <v>878459</v>
@@ -27716,7 +27716,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G943" t="n">
-        <v>3.02579045295715</v>
+        <v>3.02579069137573</v>
       </c>
       <c r="H943" t="n">
         <v>717288</v>
@@ -27745,7 +27745,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G944" t="n">
-        <v>2.94798469543457</v>
+        <v>2.94798445701599</v>
       </c>
       <c r="H944" t="n">
         <v>974453</v>
@@ -27774,7 +27774,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>2.97536087036133</v>
+        <v>2.97536063194275</v>
       </c>
       <c r="H945" t="n">
         <v>961948</v>
@@ -27803,7 +27803,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G946" t="n">
-        <v>3.01138186454773</v>
+        <v>3.01138210296631</v>
       </c>
       <c r="H946" t="n">
         <v>521324</v>
@@ -27890,7 +27890,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G949" t="n">
-        <v>2.92349004745483</v>
+        <v>2.92349028587341</v>
       </c>
       <c r="H949" t="n">
         <v>497309</v>
@@ -27948,7 +27948,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9105224609375</v>
+        <v>2.91052198410034</v>
       </c>
       <c r="H951" t="n">
         <v>231048</v>
@@ -27977,7 +27977,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G952" t="n">
-        <v>2.9047589302063</v>
+        <v>2.90475916862488</v>
       </c>
       <c r="H952" t="n">
         <v>422359</v>
@@ -28006,7 +28006,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G953" t="n">
-        <v>2.95662975311279</v>
+        <v>2.95662999153137</v>
       </c>
       <c r="H953" t="n">
         <v>525699</v>
@@ -28093,7 +28093,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G956" t="n">
-        <v>2.84280252456665</v>
+        <v>2.84280228614807</v>
       </c>
       <c r="H956" t="n">
         <v>328686</v>
@@ -28122,7 +28122,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G957" t="n">
-        <v>2.85576987266541</v>
+        <v>2.85577011108398</v>
       </c>
       <c r="H957" t="n">
         <v>405808</v>
@@ -28180,7 +28180,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G959" t="n">
-        <v>2.79237270355225</v>
+        <v>2.79237246513367</v>
       </c>
       <c r="H959" t="n">
         <v>343820</v>
@@ -28238,7 +28238,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>2.79525423049927</v>
+        <v>2.79525446891785</v>
       </c>
       <c r="H961" t="n">
         <v>226234</v>
@@ -28267,7 +28267,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G962" t="n">
-        <v>2.78804993629456</v>
+        <v>2.78804969787598</v>
       </c>
       <c r="H962" t="n">
         <v>543234</v>
@@ -28296,7 +28296,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G963" t="n">
-        <v>2.78228664398193</v>
+        <v>2.78228688240051</v>
       </c>
       <c r="H963" t="n">
         <v>329641</v>
@@ -28441,7 +28441,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G968" t="n">
-        <v>2.95662975311279</v>
+        <v>2.95662999153137</v>
       </c>
       <c r="H968" t="n">
         <v>809737</v>
@@ -28470,7 +28470,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G969" t="n">
-        <v>2.93357586860657</v>
+        <v>2.93357610702515</v>
       </c>
       <c r="H969" t="n">
         <v>560198</v>
@@ -28499,7 +28499,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G970" t="n">
-        <v>2.99553275108337</v>
+        <v>2.99553298950195</v>
       </c>
       <c r="H970" t="n">
         <v>1758990</v>
@@ -28528,7 +28528,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G971" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H971" t="n">
         <v>839198</v>
@@ -28789,7 +28789,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G980" t="n">
-        <v>3.4472222328186</v>
+        <v>3.44722199440002</v>
       </c>
       <c r="H980" t="n">
         <v>2133114</v>
@@ -28818,7 +28818,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.33797931671143</v>
+        <v>3.33797955513</v>
       </c>
       <c r="H981" t="n">
         <v>1863975</v>
@@ -28847,7 +28847,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G982" t="n">
-        <v>3.24694323539734</v>
+        <v>3.24694347381592</v>
       </c>
       <c r="H982" t="n">
         <v>979427</v>
@@ -28876,7 +28876,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G983" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H983" t="n">
         <v>1121954</v>
@@ -29021,7 +29021,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G988" t="n">
-        <v>3.14528679847717</v>
+        <v>3.14528656005859</v>
       </c>
       <c r="H988" t="n">
         <v>927499</v>
@@ -29050,7 +29050,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>3.13466572761536</v>
+        <v>3.13466596603394</v>
       </c>
       <c r="H989" t="n">
         <v>410573</v>
@@ -29079,7 +29079,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G990" t="n">
-        <v>3.06031966209412</v>
+        <v>3.0603199005127</v>
       </c>
       <c r="H990" t="n">
         <v>808635</v>
@@ -29369,7 +29369,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1000" t="n">
         <v>344826</v>
@@ -29398,7 +29398,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.17714929580688</v>
+        <v>3.17714953422546</v>
       </c>
       <c r="H1001" t="n">
         <v>500947</v>
@@ -29427,7 +29427,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.19080448150635</v>
+        <v>3.19080424308777</v>
       </c>
       <c r="H1002" t="n">
         <v>891668</v>
@@ -29804,7 +29804,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.67038345336914</v>
+        <v>2.67038321495056</v>
       </c>
       <c r="H1015" t="n">
         <v>720352</v>
@@ -29833,7 +29833,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.63852071762085</v>
+        <v>2.63852047920227</v>
       </c>
       <c r="H1016" t="n">
         <v>694882</v>
@@ -29891,7 +29891,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.61424446105957</v>
+        <v>2.61424469947815</v>
       </c>
       <c r="H1018" t="n">
         <v>419154</v>
@@ -29949,7 +29949,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.62941718101501</v>
+        <v>2.62941741943359</v>
       </c>
       <c r="H1020" t="n">
         <v>742850</v>
@@ -30065,7 +30065,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.73562574386597</v>
+        <v>2.73562550544739</v>
       </c>
       <c r="H1024" t="n">
         <v>1002369</v>
@@ -30239,7 +30239,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.83424782752991</v>
+        <v>2.83424758911133</v>
       </c>
       <c r="H1030" t="n">
         <v>690968</v>
@@ -30297,7 +30297,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.73107361793518</v>
+        <v>2.73107385635376</v>
       </c>
       <c r="H1032" t="n">
         <v>649276</v>
@@ -30326,7 +30326,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.73714280128479</v>
+        <v>2.73714303970337</v>
       </c>
       <c r="H1033" t="n">
         <v>425341</v>
@@ -30355,7 +30355,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.73107361793518</v>
+        <v>2.73107385635376</v>
       </c>
       <c r="H1034" t="n">
         <v>719237</v>
@@ -30413,7 +30413,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.77355694770813</v>
+        <v>2.77355718612671</v>
       </c>
       <c r="H1036" t="n">
         <v>610073</v>
@@ -30471,7 +30471,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.71134924888611</v>
+        <v>2.71134948730469</v>
       </c>
       <c r="H1038" t="n">
         <v>711198</v>
@@ -30500,7 +30500,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.73714280128479</v>
+        <v>2.73714303970337</v>
       </c>
       <c r="H1039" t="n">
         <v>786436</v>
@@ -30558,7 +30558,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.67038345336914</v>
+        <v>2.67038321495056</v>
       </c>
       <c r="H1041" t="n">
         <v>686287</v>
@@ -30587,7 +30587,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.67493486404419</v>
+        <v>2.67493510246277</v>
       </c>
       <c r="H1042" t="n">
         <v>642529</v>
@@ -30703,7 +30703,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.68252158164978</v>
+        <v>2.6825213432312</v>
       </c>
       <c r="H1046" t="n">
         <v>397383</v>
@@ -30877,7 +30877,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.72348761558533</v>
+        <v>2.72348737716675</v>
       </c>
       <c r="H1052" t="n">
         <v>1420563</v>
@@ -31022,7 +31022,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.55658864974976</v>
+        <v>2.55658841133118</v>
       </c>
       <c r="H1057" t="n">
         <v>603020</v>
@@ -31254,7 +31254,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.38665509223938</v>
+        <v>2.3866548538208</v>
       </c>
       <c r="H1065" t="n">
         <v>769602</v>
@@ -31283,7 +31283,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.36844778060913</v>
+        <v>2.36844754219055</v>
       </c>
       <c r="H1066" t="n">
         <v>904125</v>
@@ -31370,7 +31370,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.43520736694336</v>
+        <v>2.43520760536194</v>
       </c>
       <c r="H1069" t="n">
         <v>605908</v>
@@ -31399,7 +31399,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.44734573364258</v>
+        <v>2.44734597206116</v>
       </c>
       <c r="H1070" t="n">
         <v>553996</v>
@@ -31515,7 +31515,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.44431090354919</v>
+        <v>2.44431114196777</v>
       </c>
       <c r="H1074" t="n">
         <v>584948</v>
@@ -31544,7 +31544,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.40637969970703</v>
+        <v>2.40637946128845</v>
       </c>
       <c r="H1075" t="n">
         <v>559400</v>
@@ -31979,7 +31979,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.34265446662903</v>
+        <v>2.34265422821045</v>
       </c>
       <c r="H1090" t="n">
         <v>571552</v>
@@ -32066,7 +32066,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.78569507598877</v>
+        <v>2.78569531440735</v>
       </c>
       <c r="H1093" t="n">
         <v>1101842</v>
@@ -32095,7 +32095,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.74017715454102</v>
+        <v>2.74017739295959</v>
       </c>
       <c r="H1094" t="n">
         <v>1055336</v>
@@ -32124,7 +32124,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.74321174621582</v>
+        <v>2.7432119846344</v>
       </c>
       <c r="H1095" t="n">
         <v>457898</v>
@@ -32153,7 +32153,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.90555906295776</v>
+        <v>2.90555882453918</v>
       </c>
       <c r="H1096" t="n">
         <v>1911630</v>
@@ -32182,7 +32182,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.9768705368042</v>
+        <v>2.97687029838562</v>
       </c>
       <c r="H1097" t="n">
         <v>1619676</v>
@@ -32240,7 +32240,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.90252447128296</v>
+        <v>2.90252423286438</v>
       </c>
       <c r="H1099" t="n">
         <v>633533</v>
@@ -32356,7 +32356,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.96169781684875</v>
+        <v>2.96169805526733</v>
       </c>
       <c r="H1103" t="n">
         <v>675063</v>
@@ -32501,7 +32501,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.8266613483429</v>
+        <v>2.82666158676147</v>
       </c>
       <c r="H1108" t="n">
         <v>610729</v>
@@ -32994,7 +32994,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.76445317268372</v>
+        <v>2.76445341110229</v>
       </c>
       <c r="H1125" t="n">
         <v>545031</v>
@@ -33139,7 +33139,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.73107361793518</v>
+        <v>2.73107385635376</v>
       </c>
       <c r="H1130" t="n">
         <v>750648</v>
@@ -33197,7 +33197,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.73107361793518</v>
+        <v>2.73107385635376</v>
       </c>
       <c r="H1132" t="n">
         <v>550634</v>
@@ -33226,7 +33226,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.71134924888611</v>
+        <v>2.71134948730469</v>
       </c>
       <c r="H1133" t="n">
         <v>469665</v>
@@ -33284,7 +33284,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.72045278549194</v>
+        <v>2.72045302391052</v>
       </c>
       <c r="H1135" t="n">
         <v>354515</v>
@@ -33371,7 +33371,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.73714280128479</v>
+        <v>2.73714303970337</v>
       </c>
       <c r="H1138" t="n">
         <v>434683</v>
@@ -33400,7 +33400,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.76900553703308</v>
+        <v>2.7690052986145</v>
       </c>
       <c r="H1139" t="n">
         <v>618522</v>
@@ -33545,7 +33545,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.60362339019775</v>
+        <v>2.60362362861633</v>
       </c>
       <c r="H1144" t="n">
         <v>785344</v>
@@ -33632,7 +33632,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.65672779083252</v>
+        <v>2.6567280292511</v>
       </c>
       <c r="H1147" t="n">
         <v>304370</v>
@@ -33806,7 +33806,7 @@
         <v>3.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.84486842155457</v>
+        <v>2.84486865997314</v>
       </c>
       <c r="H1153" t="n">
         <v>806021</v>
@@ -33864,7 +33864,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1155" t="n">
         <v>1086715</v>
@@ -33922,7 +33922,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.89038610458374</v>
+        <v>2.89038634300232</v>
       </c>
       <c r="H1157" t="n">
         <v>740083</v>
@@ -34154,7 +34154,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.06031966209412</v>
+        <v>3.0603199005127</v>
       </c>
       <c r="H1165" t="n">
         <v>859551</v>
@@ -34212,7 +34212,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.06942319869995</v>
+        <v>3.06942343711853</v>
       </c>
       <c r="H1167" t="n">
         <v>834268</v>
@@ -34241,7 +34241,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.01783633232117</v>
+        <v>3.01783657073975</v>
       </c>
       <c r="H1168" t="n">
         <v>829113</v>
@@ -34299,7 +34299,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.96624970436096</v>
+        <v>2.96624946594238</v>
       </c>
       <c r="H1170" t="n">
         <v>774545</v>
@@ -34444,7 +34444,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.3182544708252</v>
+        <v>3.31825494766235</v>
       </c>
       <c r="H1175" t="n">
         <v>1017835</v>
@@ -34531,7 +34531,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.2863917350769</v>
+        <v>3.28639197349548</v>
       </c>
       <c r="H1178" t="n">
         <v>774498</v>
@@ -34647,7 +34647,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.18321824073792</v>
+        <v>3.18321847915649</v>
       </c>
       <c r="H1182" t="n">
         <v>635502</v>
@@ -34734,7 +34734,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1185" t="n">
         <v>456650</v>
@@ -34792,7 +34792,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.18321824073792</v>
+        <v>3.18321847915649</v>
       </c>
       <c r="H1187" t="n">
         <v>316805</v>
@@ -34821,7 +34821,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.17714929580688</v>
+        <v>3.17714953422546</v>
       </c>
       <c r="H1188" t="n">
         <v>664798</v>
@@ -34879,7 +34879,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.20142531394958</v>
+        <v>3.20142507553101</v>
       </c>
       <c r="H1190" t="n">
         <v>941312</v>
@@ -34937,7 +34937,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.17259740829468</v>
+        <v>3.1725971698761</v>
       </c>
       <c r="H1192" t="n">
         <v>860479</v>
@@ -35024,7 +35024,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.10735511779785</v>
+        <v>3.10735487937927</v>
       </c>
       <c r="H1195" t="n">
         <v>478326</v>
@@ -35111,7 +35111,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.01935410499573</v>
+        <v>3.01935386657715</v>
       </c>
       <c r="H1198" t="n">
         <v>1026278</v>
@@ -35343,7 +35343,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.92224884033203</v>
+        <v>2.92224907875061</v>
       </c>
       <c r="H1206" t="n">
         <v>662631</v>
@@ -35546,7 +35546,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.90404200553894</v>
+        <v>2.90404176712036</v>
       </c>
       <c r="H1213" t="n">
         <v>851897</v>
@@ -35720,7 +35720,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1219" t="n">
         <v>2209640</v>
@@ -35749,7 +35749,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.91011095046997</v>
+        <v>2.91011118888855</v>
       </c>
       <c r="H1220" t="n">
         <v>1296831</v>
@@ -35807,7 +35807,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.88280010223389</v>
+        <v>2.88279986381531</v>
       </c>
       <c r="H1222" t="n">
         <v>1397317</v>
@@ -35894,7 +35894,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.88280010223389</v>
+        <v>2.88279986381531</v>
       </c>
       <c r="H1225" t="n">
         <v>905427</v>
@@ -36010,7 +36010,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.89797258377075</v>
+        <v>2.89797282218933</v>
       </c>
       <c r="H1229" t="n">
         <v>1754855</v>
@@ -36242,7 +36242,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.11190676689148</v>
+        <v>3.11190700531006</v>
       </c>
       <c r="H1237" t="n">
         <v>1142315</v>
@@ -36590,7 +36590,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.01935410499573</v>
+        <v>3.01935386657715</v>
       </c>
       <c r="H1249" t="n">
         <v>606038</v>
@@ -36677,7 +36677,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.88280010223389</v>
+        <v>2.88279986381531</v>
       </c>
       <c r="H1252" t="n">
         <v>1133314</v>
@@ -36735,7 +36735,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.90404200553894</v>
+        <v>2.90404176712036</v>
       </c>
       <c r="H1254" t="n">
         <v>499348</v>
@@ -36822,7 +36822,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.91011095046997</v>
+        <v>2.91011118888855</v>
       </c>
       <c r="H1257" t="n">
         <v>559808</v>
@@ -36851,7 +36851,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066173553467</v>
       </c>
       <c r="H1258" t="n">
         <v>731494</v>
@@ -36880,7 +36880,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.89493823051453</v>
+        <v>2.89493799209595</v>
       </c>
       <c r="H1259" t="n">
         <v>393668</v>
@@ -36909,7 +36909,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.88280010223389</v>
+        <v>2.88279986381531</v>
       </c>
       <c r="H1260" t="n">
         <v>515873</v>
@@ -37141,7 +37141,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066173553467</v>
       </c>
       <c r="H1268" t="n">
         <v>420158</v>
@@ -37170,7 +37170,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.90100693702698</v>
+        <v>2.90100717544556</v>
       </c>
       <c r="H1269" t="n">
         <v>435035</v>
@@ -37199,7 +37199,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.91011095046997</v>
+        <v>2.91011118888855</v>
       </c>
       <c r="H1270" t="n">
         <v>446474</v>
@@ -37373,7 +37373,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.88583469390869</v>
+        <v>2.88583445549011</v>
       </c>
       <c r="H1276" t="n">
         <v>961401</v>
@@ -37402,7 +37402,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1277" t="n">
         <v>2406305</v>
@@ -37489,7 +37489,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066173553467</v>
       </c>
       <c r="H1280" t="n">
         <v>380270</v>
@@ -37518,7 +37518,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.87066197395325</v>
+        <v>2.87066173553467</v>
       </c>
       <c r="H1281" t="n">
         <v>293660</v>
@@ -37605,7 +37605,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.88128280639648</v>
+        <v>2.88128304481506</v>
       </c>
       <c r="H1284" t="n">
         <v>547091</v>
@@ -37692,7 +37692,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1287" t="n">
         <v>751635</v>
@@ -37837,7 +37837,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1292" t="n">
         <v>333025</v>
@@ -37982,7 +37982,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.81755757331848</v>
+        <v>2.81755781173706</v>
       </c>
       <c r="H1297" t="n">
         <v>609006</v>
@@ -38040,7 +38040,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.78721261024475</v>
+        <v>2.78721237182617</v>
       </c>
       <c r="H1299" t="n">
         <v>358674</v>
@@ -38069,7 +38069,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.77355694770813</v>
+        <v>2.77355718612671</v>
       </c>
       <c r="H1300" t="n">
         <v>604686</v>
@@ -38127,7 +38127,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.76900553703308</v>
+        <v>2.7690052986145</v>
       </c>
       <c r="H1302" t="n">
         <v>844044</v>
@@ -38156,7 +38156,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.76900553703308</v>
+        <v>2.7690052986145</v>
       </c>
       <c r="H1303" t="n">
         <v>550632</v>
@@ -38243,7 +38243,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.78872990608215</v>
+        <v>2.78872966766357</v>
       </c>
       <c r="H1306" t="n">
         <v>1331307</v>
@@ -38301,7 +38301,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.83576464653015</v>
+        <v>2.83576488494873</v>
       </c>
       <c r="H1308" t="n">
         <v>1430517</v>
@@ -38446,7 +38446,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.95714592933655</v>
+        <v>2.95714569091797</v>
       </c>
       <c r="H1313" t="n">
         <v>907238</v>
@@ -38852,7 +38852,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.01480174064636</v>
+        <v>3.01480197906494</v>
       </c>
       <c r="H1327" t="n">
         <v>237191</v>
@@ -38968,7 +38968,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.03300905227661</v>
+        <v>3.03300929069519</v>
       </c>
       <c r="H1331" t="n">
         <v>337172</v>
@@ -39084,7 +39084,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.94349050521851</v>
+        <v>2.94349074363708</v>
       </c>
       <c r="H1335" t="n">
         <v>769899</v>
@@ -39113,7 +39113,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.96624970436096</v>
+        <v>2.96624946594238</v>
       </c>
       <c r="H1336" t="n">
         <v>591694</v>
@@ -39171,7 +39171,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.91011095046997</v>
+        <v>2.91011118888855</v>
       </c>
       <c r="H1338" t="n">
         <v>445579</v>
@@ -39403,7 +39403,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.17259740829468</v>
+        <v>3.1725971698761</v>
       </c>
       <c r="H1346" t="n">
         <v>919731</v>
@@ -39519,7 +39519,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.19990825653076</v>
+        <v>3.19990801811218</v>
       </c>
       <c r="H1350" t="n">
         <v>882238</v>
@@ -39548,7 +39548,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.19080448150635</v>
+        <v>3.19080424308777</v>
       </c>
       <c r="H1351" t="n">
         <v>684309</v>
@@ -39577,7 +39577,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.1270797252655</v>
+        <v>3.12707948684692</v>
       </c>
       <c r="H1352" t="n">
         <v>748528</v>
@@ -39606,7 +39606,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1353" t="n">
         <v>563496</v>
@@ -39722,7 +39722,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.95714592933655</v>
+        <v>2.95714569091797</v>
       </c>
       <c r="H1357" t="n">
         <v>517977</v>
@@ -39838,7 +39838,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.77810907363892</v>
+        <v>2.77810883522034</v>
       </c>
       <c r="H1361" t="n">
         <v>1161975</v>
@@ -39896,7 +39896,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1363" t="n">
-        <v>2.80845403671265</v>
+        <v>2.80845427513123</v>
       </c>
       <c r="H1363" t="n">
         <v>709578</v>
@@ -39925,7 +39925,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>2.83424782752991</v>
+        <v>2.83424758911133</v>
       </c>
       <c r="H1364" t="n">
         <v>518021</v>
@@ -40215,7 +40215,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.8919038772583</v>
+        <v>2.89190363883972</v>
       </c>
       <c r="H1374" t="n">
         <v>317269</v>
@@ -40476,7 +40476,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.06031966209412</v>
+        <v>3.0603199005127</v>
       </c>
       <c r="H1383" t="n">
         <v>618444</v>
@@ -40708,7 +40708,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.13163113594055</v>
+        <v>3.13163137435913</v>
       </c>
       <c r="H1391" t="n">
         <v>235611</v>
@@ -40766,7 +40766,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1393" t="n">
         <v>343828</v>
@@ -40824,7 +40824,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.13618302345276</v>
+        <v>3.13618278503418</v>
       </c>
       <c r="H1395" t="n">
         <v>442760</v>
@@ -40998,7 +40998,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.08459639549255</v>
+        <v>3.08459615707397</v>
       </c>
       <c r="H1401" t="n">
         <v>359292</v>
@@ -41085,7 +41085,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.15590763092041</v>
+        <v>3.15590739250183</v>
       </c>
       <c r="H1404" t="n">
         <v>368125</v>
@@ -41172,7 +41172,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.06487154960632</v>
+        <v>3.06487131118774</v>
       </c>
       <c r="H1407" t="n">
         <v>357189</v>
@@ -41201,7 +41201,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.95259404182434</v>
+        <v>2.95259428024292</v>
       </c>
       <c r="H1408" t="n">
         <v>1114048</v>
@@ -41259,7 +41259,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.15590763092041</v>
+        <v>3.15590739250183</v>
       </c>
       <c r="H1410" t="n">
         <v>993535</v>
@@ -41346,7 +41346,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.08156156539917</v>
+        <v>3.08156132698059</v>
       </c>
       <c r="H1413" t="n">
         <v>1369822</v>
@@ -41462,7 +41462,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.1270797252655</v>
+        <v>3.12707948684692</v>
       </c>
       <c r="H1417" t="n">
         <v>324389</v>
@@ -41578,7 +41578,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.03604364395142</v>
+        <v>3.03604388237</v>
       </c>
       <c r="H1421" t="n">
         <v>1087442</v>
@@ -41607,7 +41607,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.10735511779785</v>
+        <v>3.10735487937927</v>
       </c>
       <c r="H1422" t="n">
         <v>919096</v>
@@ -41665,7 +41665,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.00569820404053</v>
+        <v>3.00569844245911</v>
       </c>
       <c r="H1424" t="n">
         <v>811906</v>
@@ -41810,7 +41810,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.78266048431396</v>
+        <v>2.78266072273254</v>
       </c>
       <c r="H1429" t="n">
         <v>1054096</v>
@@ -41926,7 +41926,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.9768705368042</v>
+        <v>2.97687029838562</v>
       </c>
       <c r="H1433" t="n">
         <v>454366</v>
@@ -41984,7 +41984,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H1435" t="n">
         <v>593290</v>
@@ -42042,7 +42042,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.07397556304932</v>
+        <v>3.07397532463074</v>
       </c>
       <c r="H1437" t="n">
         <v>576360</v>
@@ -42071,7 +42071,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.01480174064636</v>
+        <v>3.01480197906494</v>
       </c>
       <c r="H1438" t="n">
         <v>336601</v>
@@ -42303,7 +42303,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1446" t="n">
         <v>1656008</v>
@@ -42361,7 +42361,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.24694323539734</v>
+        <v>3.24694347381592</v>
       </c>
       <c r="H1448" t="n">
         <v>602536</v>
@@ -42390,7 +42390,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.24846053123474</v>
+        <v>3.24846076965332</v>
       </c>
       <c r="H1449" t="n">
         <v>506516</v>
@@ -42535,7 +42535,7 @@
         <v>4.42600011825562</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.35770344734192</v>
+        <v>3.3577036857605</v>
       </c>
       <c r="H1454" t="n">
         <v>366607</v>
@@ -42564,7 +42564,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.41535949707031</v>
+        <v>3.41535973548889</v>
       </c>
       <c r="H1455" t="n">
         <v>502197</v>
@@ -42680,7 +42680,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.41991138458252</v>
+        <v>3.41991114616394</v>
       </c>
       <c r="H1459" t="n">
         <v>599042</v>
@@ -42767,7 +42767,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.37591052055359</v>
+        <v>3.37591028213501</v>
       </c>
       <c r="H1462" t="n">
         <v>412208</v>
@@ -42796,7 +42796,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.33797931671143</v>
+        <v>3.33797955513</v>
       </c>
       <c r="H1463" t="n">
         <v>285885</v>
@@ -42854,7 +42854,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.34253120422363</v>
+        <v>3.34253072738647</v>
       </c>
       <c r="H1465" t="n">
         <v>331814</v>
@@ -42883,7 +42883,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.31066823005676</v>
+        <v>3.31066799163818</v>
       </c>
       <c r="H1466" t="n">
         <v>319646</v>
@@ -42912,7 +42912,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.37439346313477</v>
+        <v>3.37439322471619</v>
       </c>
       <c r="H1467" t="n">
         <v>351083</v>
@@ -43086,7 +43086,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.29094362258911</v>
+        <v>3.29094338417053</v>
       </c>
       <c r="H1473" t="n">
         <v>390507</v>
@@ -43231,7 +43231,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.26666784286499</v>
+        <v>3.26666808128357</v>
       </c>
       <c r="H1478" t="n">
         <v>317207</v>
@@ -43289,7 +43289,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.25452947616577</v>
+        <v>3.25452971458435</v>
       </c>
       <c r="H1480" t="n">
         <v>227378</v>
@@ -43492,7 +43492,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.26666784286499</v>
+        <v>3.26666808128357</v>
       </c>
       <c r="H1487" t="n">
         <v>389756</v>
@@ -43521,7 +43521,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.25908136367798</v>
+        <v>3.2590811252594</v>
       </c>
       <c r="H1488" t="n">
         <v>173956</v>
@@ -43608,7 +43608,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.30308222770691</v>
+        <v>3.30308198928833</v>
       </c>
       <c r="H1491" t="n">
         <v>317705</v>
@@ -43695,7 +43695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1494" t="n">
         <v>518313</v>
@@ -43811,7 +43811,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.99356055259705</v>
+        <v>2.99356031417847</v>
       </c>
       <c r="H1498" t="n">
         <v>373985</v>
@@ -44072,7 +44072,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.1225278377533</v>
+        <v>3.12252807617188</v>
       </c>
       <c r="H1507" t="n">
         <v>416311</v>
@@ -44130,7 +44130,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.02390551567078</v>
+        <v>3.02390575408936</v>
       </c>
       <c r="H1509" t="n">
         <v>408312</v>
@@ -44275,7 +44275,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.01480174064636</v>
+        <v>3.01480197906494</v>
       </c>
       <c r="H1514" t="n">
         <v>243119</v>
@@ -44304,7 +44304,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.03300905227661</v>
+        <v>3.03300929069519</v>
       </c>
       <c r="H1515" t="n">
         <v>189223</v>
@@ -44391,7 +44391,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.04969882965088</v>
+        <v>3.04969906806946</v>
       </c>
       <c r="H1518" t="n">
         <v>105502</v>
@@ -44594,7 +44594,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.19990825653076</v>
+        <v>3.19990801811218</v>
       </c>
       <c r="H1525" t="n">
         <v>308905</v>
@@ -44623,7 +44623,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1526" t="n">
         <v>227220</v>
@@ -44681,7 +44681,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.16956281661987</v>
+        <v>3.16956257820129</v>
       </c>
       <c r="H1528" t="n">
         <v>115488</v>
@@ -44710,7 +44710,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1529" t="n">
         <v>156797</v>
@@ -44826,7 +44826,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.3197717666626</v>
+        <v>3.31977200508118</v>
       </c>
       <c r="H1533" t="n">
         <v>379962</v>
@@ -44884,7 +44884,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.25756430625916</v>
+        <v>3.25756406784058</v>
       </c>
       <c r="H1535" t="n">
         <v>278442</v>
@@ -45145,7 +45145,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.20901155471802</v>
+        <v>3.2090117931366</v>
       </c>
       <c r="H1544" t="n">
         <v>146185</v>
@@ -45174,7 +45174,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.17866635322571</v>
+        <v>3.17866611480713</v>
       </c>
       <c r="H1545" t="n">
         <v>211170</v>
@@ -45319,7 +45319,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11190676689148</v>
+        <v>3.11190700531006</v>
       </c>
       <c r="H1550" t="n">
         <v>104079</v>
@@ -45377,7 +45377,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.13163113594055</v>
+        <v>3.13163137435913</v>
       </c>
       <c r="H1552" t="n">
         <v>226899</v>
@@ -45522,7 +45522,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.07397556304932</v>
+        <v>3.07397532463074</v>
       </c>
       <c r="H1557" t="n">
         <v>162365</v>
@@ -45551,7 +45551,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.14376926422119</v>
+        <v>3.14376950263977</v>
       </c>
       <c r="H1558" t="n">
         <v>185411</v>
@@ -45580,7 +45580,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.18625259399414</v>
+        <v>3.18625283241272</v>
       </c>
       <c r="H1559" t="n">
         <v>310762</v>
@@ -45754,7 +45754,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.13466572761536</v>
+        <v>3.13466596603394</v>
       </c>
       <c r="H1565" t="n">
         <v>177784</v>
@@ -46131,7 +46131,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.78569507598877</v>
+        <v>2.78569531440735</v>
       </c>
       <c r="H1578" t="n">
         <v>222101</v>
@@ -46276,7 +46276,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.77355694770813</v>
+        <v>2.77355718612671</v>
       </c>
       <c r="H1583" t="n">
         <v>180777</v>
@@ -46392,7 +46392,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.83576464653015</v>
+        <v>2.83576488494873</v>
       </c>
       <c r="H1587" t="n">
         <v>208957</v>
@@ -46421,7 +46421,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.8266613483429</v>
+        <v>2.82666158676147</v>
       </c>
       <c r="H1588" t="n">
         <v>170544</v>
@@ -46566,7 +46566,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.00751209259033</v>
+        <v>3.00751233100891</v>
       </c>
       <c r="H1593" t="n">
         <v>386716</v>
@@ -46595,7 +46595,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.01063847541809</v>
+        <v>3.01063871383667</v>
       </c>
       <c r="H1594" t="n">
         <v>176564</v>
@@ -46653,7 +46653,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.05440664291382</v>
+        <v>3.0544068813324</v>
       </c>
       <c r="H1596" t="n">
         <v>142847</v>
@@ -46682,7 +46682,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.04659104347229</v>
+        <v>3.04659080505371</v>
       </c>
       <c r="H1597" t="n">
         <v>588330</v>
@@ -46769,7 +46769,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.03252267837524</v>
+        <v>3.03252291679382</v>
       </c>
       <c r="H1600" t="n">
         <v>381944</v>
@@ -46827,7 +46827,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.982501745224</v>
+        <v>2.98250150680542</v>
       </c>
       <c r="H1602" t="n">
         <v>358466</v>
@@ -46943,7 +46943,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.14194321632385</v>
+        <v>3.14194345474243</v>
       </c>
       <c r="H1606" t="n">
         <v>1027100</v>
@@ -47088,7 +47088,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.29825901985168</v>
+        <v>3.29825878143311</v>
       </c>
       <c r="H1611" t="n">
         <v>297510</v>
@@ -47117,7 +47117,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.34671688079834</v>
+        <v>3.34671711921692</v>
       </c>
       <c r="H1612" t="n">
         <v>400431</v>
@@ -47146,7 +47146,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.35609602928162</v>
+        <v>3.35609579086304</v>
       </c>
       <c r="H1613" t="n">
         <v>205646</v>
@@ -47320,7 +47320,7 @@
         <v>4.31400012969971</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.37172722816467</v>
+        <v>3.37172770500183</v>
       </c>
       <c r="H1619" t="n">
         <v>421861</v>
@@ -47349,7 +47349,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.35765886306763</v>
+        <v>3.35765862464905</v>
       </c>
       <c r="H1620" t="n">
         <v>255481</v>
@@ -47407,7 +47407,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.2873170375824</v>
+        <v>3.28731679916382</v>
       </c>
       <c r="H1622" t="n">
         <v>185455</v>
@@ -47581,7 +47581,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.17476963996887</v>
+        <v>3.17476940155029</v>
       </c>
       <c r="H1628" t="n">
         <v>336825</v>
@@ -47813,7 +47813,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.09817504882812</v>
+        <v>3.0981752872467</v>
       </c>
       <c r="H1636" t="n">
         <v>122218</v>
@@ -47900,7 +47900,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.11536979675293</v>
+        <v>3.11537003517151</v>
       </c>
       <c r="H1639" t="n">
         <v>100419</v>
@@ -47929,7 +47929,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.16695427894592</v>
+        <v>3.16695404052734</v>
       </c>
       <c r="H1640" t="n">
         <v>251186</v>
@@ -48016,7 +48016,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.19509053230286</v>
+        <v>3.19509077072144</v>
       </c>
       <c r="H1643" t="n">
         <v>90490</v>
@@ -48045,7 +48045,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1644" t="n">
         <v>230657</v>
@@ -48103,7 +48103,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.27481198310852</v>
+        <v>3.27481174468994</v>
       </c>
       <c r="H1646" t="n">
         <v>305247</v>
@@ -48219,7 +48219,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.2873170375824</v>
+        <v>3.28731679916382</v>
       </c>
       <c r="H1650" t="n">
         <v>147979</v>
@@ -48277,7 +48277,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.22635364532471</v>
+        <v>3.22635388374329</v>
       </c>
       <c r="H1652" t="n">
         <v>181208</v>
@@ -48393,7 +48393,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.38423275947571</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1656" t="n">
         <v>233036</v>
@@ -48538,7 +48538,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.34359073638916</v>
+        <v>3.34359049797058</v>
       </c>
       <c r="H1661" t="n">
         <v>255129</v>
@@ -48654,7 +48654,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.37485337257385</v>
+        <v>3.37485361099243</v>
       </c>
       <c r="H1665" t="n">
         <v>211448</v>
@@ -48712,7 +48712,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.38423275947571</v>
+        <v>3.38423252105713</v>
       </c>
       <c r="H1667" t="n">
         <v>164728</v>
@@ -48799,7 +48799,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1670" t="n">
         <v>276264</v>
@@ -49060,7 +49060,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.26543283462524</v>
+        <v>3.26543259620667</v>
       </c>
       <c r="H1679" t="n">
         <v>194885</v>
@@ -49089,7 +49089,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.26543283462524</v>
+        <v>3.26543259620667</v>
       </c>
       <c r="H1680" t="n">
         <v>378362</v>
@@ -49118,7 +49118,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.23573279380798</v>
+        <v>3.23573303222656</v>
       </c>
       <c r="H1681" t="n">
         <v>155172</v>
@@ -49205,7 +49205,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.27481198310852</v>
+        <v>3.27481174468994</v>
       </c>
       <c r="H1684" t="n">
         <v>150462</v>
@@ -49234,7 +49234,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.27324867248535</v>
+        <v>3.27324891090393</v>
       </c>
       <c r="H1685" t="n">
         <v>185135</v>
@@ -49350,7 +49350,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.15757513046265</v>
+        <v>3.15757489204407</v>
       </c>
       <c r="H1689" t="n">
         <v>357386</v>
@@ -49379,7 +49379,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.22635364532471</v>
+        <v>3.22635388374329</v>
       </c>
       <c r="H1690" t="n">
         <v>173441</v>
@@ -49437,7 +49437,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.08410668373108</v>
+        <v>3.0841064453125</v>
       </c>
       <c r="H1692" t="n">
         <v>697245</v>
@@ -49553,7 +49553,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.05440664291382</v>
+        <v>3.0544068813324</v>
       </c>
       <c r="H1696" t="n">
         <v>504766</v>
@@ -49930,7 +49930,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.16226434707642</v>
+        <v>3.162264585495</v>
       </c>
       <c r="H1709" t="n">
         <v>648898</v>
@@ -49959,7 +49959,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.21697497367859</v>
+        <v>3.21697521209717</v>
       </c>
       <c r="H1710" t="n">
         <v>573601</v>
@@ -49988,7 +49988,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.2060329914093</v>
+        <v>3.20603322982788</v>
       </c>
       <c r="H1711" t="n">
         <v>242552</v>
@@ -50162,7 +50162,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.268559217453</v>
+        <v>3.26855897903442</v>
       </c>
       <c r="H1717" t="n">
         <v>258927</v>
@@ -50191,7 +50191,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.27950119972229</v>
+        <v>3.27950143814087</v>
       </c>
       <c r="H1718" t="n">
         <v>355421</v>
@@ -50452,7 +50452,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.22166466712952</v>
+        <v>3.22166442871094</v>
       </c>
       <c r="H1727" t="n">
         <v>278266</v>
@@ -50771,7 +50771,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.15288519859314</v>
+        <v>3.15288543701172</v>
       </c>
       <c r="H1738" t="n">
         <v>187427</v>
@@ -50800,7 +50800,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.11849617958069</v>
+        <v>3.11849641799927</v>
       </c>
       <c r="H1739" t="n">
         <v>166094</v>
@@ -51003,7 +51003,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.12787485122681</v>
+        <v>3.12787508964539</v>
       </c>
       <c r="H1746" t="n">
         <v>485176</v>
@@ -51061,7 +51061,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.09661173820496</v>
+        <v>3.09661197662354</v>
       </c>
       <c r="H1748" t="n">
         <v>260833</v>
@@ -51148,7 +51148,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.09817504882812</v>
+        <v>3.0981752872467</v>
       </c>
       <c r="H1751" t="n">
         <v>141683</v>
@@ -51583,7 +51583,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691193580627</v>
       </c>
       <c r="H1766" t="n">
         <v>179289</v>
@@ -51612,7 +51612,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.05440664291382</v>
+        <v>3.0544068813324</v>
       </c>
       <c r="H1767" t="n">
         <v>231550</v>
@@ -51670,7 +51670,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.97312259674072</v>
+        <v>2.97312235832214</v>
       </c>
       <c r="H1769" t="n">
         <v>759401</v>
@@ -51960,7 +51960,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.04190135002136</v>
+        <v>3.04190158843994</v>
       </c>
       <c r="H1779" t="n">
         <v>280743</v>
@@ -52018,7 +52018,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.03721189498901</v>
+        <v>3.03721165657043</v>
       </c>
       <c r="H1781" t="n">
         <v>380393</v>
@@ -52163,7 +52163,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.05128049850464</v>
+        <v>3.05128073692322</v>
       </c>
       <c r="H1786" t="n">
         <v>378015</v>
@@ -52308,7 +52308,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.90278029441833</v>
+        <v>2.90278053283691</v>
       </c>
       <c r="H1791" t="n">
         <v>397165</v>
@@ -52453,7 +52453,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.88245964050293</v>
+        <v>2.88245940208435</v>
       </c>
       <c r="H1796" t="n">
         <v>395968</v>
@@ -52482,7 +52482,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.85275983810425</v>
+        <v>2.85275959968567</v>
       </c>
       <c r="H1797" t="n">
         <v>348055</v>
@@ -52598,7 +52598,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.85744881629944</v>
+        <v>2.85744905471802</v>
       </c>
       <c r="H1801" t="n">
         <v>234603</v>
@@ -52627,7 +52627,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.85744881629944</v>
+        <v>2.85744905471802</v>
       </c>
       <c r="H1802" t="n">
         <v>217632</v>
@@ -52714,7 +52714,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.88245964050293</v>
+        <v>2.88245940208435</v>
       </c>
       <c r="H1805" t="n">
         <v>152166</v>
@@ -52743,7 +52743,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.92466473579407</v>
+        <v>2.92466497421265</v>
       </c>
       <c r="H1806" t="n">
         <v>324520</v>
@@ -52772,7 +52772,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.92153835296631</v>
+        <v>2.92153859138489</v>
       </c>
       <c r="H1807" t="n">
         <v>234456</v>
@@ -53149,7 +53149,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.82305955886841</v>
+        <v>2.82305979728699</v>
       </c>
       <c r="H1820" t="n">
         <v>491195</v>
@@ -53265,7 +53265,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.80586504936218</v>
+        <v>2.8058648109436</v>
       </c>
       <c r="H1824" t="n">
         <v>262774</v>
@@ -53294,7 +53294,7 @@
         <v>3.45799994468689</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.70269656181335</v>
+        <v>2.70269680023193</v>
       </c>
       <c r="H1825" t="n">
         <v>939263</v>
@@ -53323,7 +53323,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68393850326538</v>
+        <v>2.68393874168396</v>
       </c>
       <c r="H1826" t="n">
         <v>842330</v>
@@ -53352,7 +53352,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70894932746887</v>
+        <v>2.70894956588745</v>
       </c>
       <c r="H1827" t="n">
         <v>321163</v>
@@ -53671,7 +53671,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.6245391368866</v>
+        <v>2.62453889846802</v>
       </c>
       <c r="H1838" t="n">
         <v>574992</v>
@@ -53729,7 +53729,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.57764434814453</v>
+        <v>2.57764410972595</v>
       </c>
       <c r="H1840" t="n">
         <v>493431</v>
@@ -53816,7 +53816,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.49792313575745</v>
+        <v>2.49792337417603</v>
       </c>
       <c r="H1843" t="n">
         <v>500311</v>
@@ -76007,6 +76007,35 @@
         <v>324036</v>
       </c>
       <c r="I2608" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2609" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2609" t="n">
+        <v>5.11499977111816</v>
+      </c>
+      <c r="D2609" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="E2609" t="n">
+        <v>5.09499979019165</v>
+      </c>
+      <c r="F2609" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="G2609" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="H2609" t="n">
+        <v>350224</v>
+      </c>
+      <c r="I2609" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENAV.MI.xlsx
+++ b/data/ENAV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H2" t="n">
         <v>73776221</v>
@@ -456,7 +456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H3" t="n">
         <v>8746746</v>
@@ -485,7 +485,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26321339607239</v>
+        <v>2.26321387290955</v>
       </c>
       <c r="H4" t="n">
         <v>8182968</v>
@@ -543,7 +543,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3048210144043</v>
+        <v>2.30482125282288</v>
       </c>
       <c r="H6" t="n">
         <v>4016992</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>2.33256030082703</v>
+        <v>2.33255982398987</v>
       </c>
       <c r="H7" t="n">
         <v>3592063</v>
@@ -601,7 +601,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33256030082703</v>
+        <v>2.33255982398987</v>
       </c>
       <c r="H8" t="n">
         <v>2256529</v>
@@ -630,7 +630,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38677620887756</v>
+        <v>2.38677644729614</v>
       </c>
       <c r="H9" t="n">
         <v>3631224</v>
@@ -659,7 +659,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33886432647705</v>
+        <v>2.33886408805847</v>
       </c>
       <c r="H10" t="n">
         <v>883891</v>
@@ -688,7 +688,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33886432647705</v>
+        <v>2.33886408805847</v>
       </c>
       <c r="H11" t="n">
         <v>2186928</v>
@@ -746,7 +746,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34895086288452</v>
+        <v>2.34895062446594</v>
       </c>
       <c r="H13" t="n">
         <v>1874026</v>
@@ -775,7 +775,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G14" t="n">
-        <v>2.37921118736267</v>
+        <v>2.37921094894409</v>
       </c>
       <c r="H14" t="n">
         <v>2690138</v>
@@ -804,7 +804,7 @@
         <v>3.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H15" t="n">
         <v>910155</v>
@@ -862,7 +862,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26951766014099</v>
+        <v>2.26951789855957</v>
       </c>
       <c r="H17" t="n">
         <v>1072096</v>
@@ -920,7 +920,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29599547386169</v>
+        <v>2.29599523544312</v>
       </c>
       <c r="H19" t="n">
         <v>853812</v>
@@ -978,7 +978,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28590869903564</v>
+        <v>2.28590846061707</v>
       </c>
       <c r="H21" t="n">
         <v>1248337</v>
@@ -1036,7 +1036,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.30103921890259</v>
+        <v>2.30103898048401</v>
       </c>
       <c r="H23" t="n">
         <v>972167</v>
@@ -1065,7 +1065,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.33508157730103</v>
+        <v>2.33508205413818</v>
       </c>
       <c r="H24" t="n">
         <v>434879</v>
@@ -1094,7 +1094,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32877707481384</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H25" t="n">
         <v>276607</v>
@@ -1123,7 +1123,7 @@
         <v>3.75</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H26" t="n">
         <v>594438</v>
@@ -1181,7 +1181,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G28" t="n">
-        <v>2.37542843818665</v>
+        <v>2.37542819976807</v>
       </c>
       <c r="H28" t="n">
         <v>1425652</v>
@@ -1239,7 +1239,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>2.39560222625732</v>
+        <v>2.39560198783875</v>
       </c>
       <c r="H30" t="n">
         <v>934202</v>
@@ -1297,7 +1297,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G32" t="n">
-        <v>2.35903763771057</v>
+        <v>2.35903787612915</v>
       </c>
       <c r="H32" t="n">
         <v>1087468</v>
@@ -1326,7 +1326,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32877707481384</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H33" t="n">
         <v>635450</v>
@@ -1384,7 +1384,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G35" t="n">
-        <v>2.23799681663513</v>
+        <v>2.23799657821655</v>
       </c>
       <c r="H35" t="n">
         <v>2200031</v>
@@ -1442,7 +1442,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G37" t="n">
-        <v>2.21782326698303</v>
+        <v>2.21782350540161</v>
       </c>
       <c r="H37" t="n">
         <v>2049268</v>
@@ -1471,7 +1471,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.23799681663513</v>
+        <v>2.23799657821655</v>
       </c>
       <c r="H38" t="n">
         <v>508600</v>
@@ -1500,7 +1500,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G39" t="n">
-        <v>2.20521450042725</v>
+        <v>2.20521473884583</v>
       </c>
       <c r="H39" t="n">
         <v>724649</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.20647573471069</v>
+        <v>2.20647549629211</v>
       </c>
       <c r="H40" t="n">
         <v>582571</v>
@@ -1587,7 +1587,7 @@
         <v>3.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.20647573471069</v>
+        <v>2.20647549629211</v>
       </c>
       <c r="H42" t="n">
         <v>671983</v>
@@ -1616,7 +1616,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>2.21908402442932</v>
+        <v>2.2190842628479</v>
       </c>
       <c r="H43" t="n">
         <v>692846</v>
@@ -1703,7 +1703,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G46" t="n">
-        <v>2.21404075622559</v>
+        <v>2.21404051780701</v>
       </c>
       <c r="H46" t="n">
         <v>923623</v>
@@ -1732,7 +1732,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22538876533508</v>
+        <v>2.22538828849792</v>
       </c>
       <c r="H47" t="n">
         <v>657985</v>
@@ -1790,7 +1790,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G49" t="n">
-        <v>2.30608224868774</v>
+        <v>2.30608248710632</v>
       </c>
       <c r="H49" t="n">
         <v>1124621</v>
@@ -1819,7 +1819,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.26951766014099</v>
+        <v>2.26951789855957</v>
       </c>
       <c r="H50" t="n">
         <v>664973</v>
@@ -1877,7 +1877,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.23169207572937</v>
+        <v>2.23169231414795</v>
       </c>
       <c r="H52" t="n">
         <v>743120</v>
@@ -1906,7 +1906,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.21782326698303</v>
+        <v>2.21782350540161</v>
       </c>
       <c r="H53" t="n">
         <v>1181993</v>
@@ -1993,7 +1993,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G56" t="n">
-        <v>2.21151900291443</v>
+        <v>2.21151876449585</v>
       </c>
       <c r="H56" t="n">
         <v>170592</v>
@@ -2022,7 +2022,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G57" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H57" t="n">
         <v>823761</v>
@@ -2080,7 +2080,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G59" t="n">
-        <v>2.20773649215698</v>
+        <v>2.20773673057556</v>
       </c>
       <c r="H59" t="n">
         <v>787033</v>
@@ -2109,7 +2109,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G60" t="n">
-        <v>2.18251943588257</v>
+        <v>2.18251967430115</v>
       </c>
       <c r="H60" t="n">
         <v>567481</v>
@@ -2138,7 +2138,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15478134155273</v>
+        <v>2.15478110313416</v>
       </c>
       <c r="H61" t="n">
         <v>1863931</v>
@@ -2167,7 +2167,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G62" t="n">
-        <v>2.17873692512512</v>
+        <v>2.1787371635437</v>
       </c>
       <c r="H62" t="n">
         <v>1348975</v>
@@ -2196,7 +2196,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G63" t="n">
-        <v>2.17873692512512</v>
+        <v>2.1787371635437</v>
       </c>
       <c r="H63" t="n">
         <v>323909</v>
@@ -2225,7 +2225,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G64" t="n">
-        <v>2.16991090774536</v>
+        <v>2.16991138458252</v>
       </c>
       <c r="H64" t="n">
         <v>368716</v>
@@ -2254,7 +2254,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G65" t="n">
-        <v>2.14721584320068</v>
+        <v>2.14721608161926</v>
       </c>
       <c r="H65" t="n">
         <v>1473153</v>
@@ -2283,7 +2283,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G66" t="n">
-        <v>2.16865062713623</v>
+        <v>2.16865015029907</v>
       </c>
       <c r="H66" t="n">
         <v>1102800</v>
@@ -2312,7 +2312,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H67" t="n">
         <v>887821</v>
@@ -2341,7 +2341,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G68" t="n">
-        <v>2.14973759651184</v>
+        <v>2.14973735809326</v>
       </c>
       <c r="H68" t="n">
         <v>894808</v>
@@ -2370,7 +2370,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G69" t="n">
-        <v>2.14973759651184</v>
+        <v>2.14973735809326</v>
       </c>
       <c r="H69" t="n">
         <v>704511</v>
@@ -2428,7 +2428,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G71" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H71" t="n">
         <v>213630</v>
@@ -2515,7 +2515,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.12452054023743</v>
+        <v>2.12452077865601</v>
       </c>
       <c r="H74" t="n">
         <v>584909</v>
@@ -2544,7 +2544,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G75" t="n">
-        <v>2.12830352783203</v>
+        <v>2.12830328941345</v>
       </c>
       <c r="H75" t="n">
         <v>439704</v>
@@ -2573,7 +2573,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>2.12452054023743</v>
+        <v>2.12452077865601</v>
       </c>
       <c r="H76" t="n">
         <v>361920</v>
@@ -2660,7 +2660,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97195887565613</v>
+        <v>1.97195911407471</v>
       </c>
       <c r="H79" t="n">
         <v>3135081</v>
@@ -2689,7 +2689,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93161165714264</v>
+        <v>1.93161153793335</v>
       </c>
       <c r="H80" t="n">
         <v>2685175</v>
@@ -2718,7 +2718,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G81" t="n">
-        <v>1.93917679786682</v>
+        <v>1.93917691707611</v>
       </c>
       <c r="H81" t="n">
         <v>2261017</v>
@@ -2747,7 +2747,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>1.92908978462219</v>
+        <v>1.92909014225006</v>
       </c>
       <c r="H82" t="n">
         <v>1535844</v>
@@ -2805,7 +2805,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G84" t="n">
-        <v>1.94800305366516</v>
+        <v>1.94800317287445</v>
       </c>
       <c r="H84" t="n">
         <v>3748342</v>
@@ -2834,7 +2834,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>1.90387332439423</v>
+        <v>1.90387320518494</v>
       </c>
       <c r="H85" t="n">
         <v>1188561</v>
@@ -2863,7 +2863,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.90387332439423</v>
+        <v>1.90387320518494</v>
       </c>
       <c r="H86" t="n">
         <v>2920431</v>
@@ -2892,7 +2892,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>1.92782950401306</v>
+        <v>1.92782938480377</v>
       </c>
       <c r="H87" t="n">
         <v>1922023</v>
@@ -2950,7 +2950,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G89" t="n">
-        <v>1.97321999073029</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H89" t="n">
         <v>736410</v>
@@ -2979,7 +2979,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G90" t="n">
-        <v>1.99339294433594</v>
+        <v>1.99339306354523</v>
       </c>
       <c r="H90" t="n">
         <v>1831237</v>
@@ -3037,7 +3037,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G92" t="n">
-        <v>2.01104474067688</v>
+        <v>2.01104497909546</v>
       </c>
       <c r="H92" t="n">
         <v>6813289</v>
@@ -3066,7 +3066,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>2.00474095344543</v>
+        <v>2.00474071502686</v>
       </c>
       <c r="H93" t="n">
         <v>1346621</v>
@@ -3124,7 +3124,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>1.95430672168732</v>
+        <v>1.9543069601059</v>
       </c>
       <c r="H95" t="n">
         <v>1270656</v>
@@ -3153,7 +3153,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G96" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213230609894</v>
       </c>
       <c r="H96" t="n">
         <v>3064119</v>
@@ -3182,7 +3182,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>1.97321999073029</v>
+        <v>1.97321975231171</v>
       </c>
       <c r="H97" t="n">
         <v>1754313</v>
@@ -3211,7 +3211,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G98" t="n">
-        <v>1.91017758846283</v>
+        <v>1.91017746925354</v>
       </c>
       <c r="H98" t="n">
         <v>1613932</v>
@@ -3240,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89126479625702</v>
+        <v>1.8912650346756</v>
       </c>
       <c r="H99" t="n">
         <v>3568973</v>
@@ -3298,7 +3298,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G101" t="n">
-        <v>1.93917679786682</v>
+        <v>1.93917691707611</v>
       </c>
       <c r="H101" t="n">
         <v>2183788</v>
@@ -3327,7 +3327,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G102" t="n">
-        <v>2.00474095344543</v>
+        <v>2.00474071502686</v>
       </c>
       <c r="H102" t="n">
         <v>2523085</v>
@@ -3385,7 +3385,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G104" t="n">
-        <v>2.0892174243927</v>
+        <v>2.08921718597412</v>
       </c>
       <c r="H104" t="n">
         <v>8365602</v>
@@ -3414,7 +3414,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G105" t="n">
-        <v>2.05643534660339</v>
+        <v>2.05643558502197</v>
       </c>
       <c r="H105" t="n">
         <v>1912960</v>
@@ -3443,7 +3443,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H106" t="n">
         <v>1234594</v>
@@ -3472,7 +3472,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G107" t="n">
-        <v>2.07030463218689</v>
+        <v>2.07030439376831</v>
       </c>
       <c r="H107" t="n">
         <v>701279</v>
@@ -3530,7 +3530,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H109" t="n">
         <v>908570</v>
@@ -3588,7 +3588,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.06147861480713</v>
+        <v>2.06147837638855</v>
       </c>
       <c r="H111" t="n">
         <v>436432</v>
@@ -3617,7 +3617,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G112" t="n">
-        <v>2.07913088798523</v>
+        <v>2.07913064956665</v>
       </c>
       <c r="H112" t="n">
         <v>627812</v>
@@ -3646,7 +3646,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G113" t="n">
-        <v>2.07030463218689</v>
+        <v>2.07030439376831</v>
       </c>
       <c r="H113" t="n">
         <v>483565</v>
@@ -3704,7 +3704,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G115" t="n">
-        <v>2.11569499969482</v>
+        <v>2.11569476127625</v>
       </c>
       <c r="H115" t="n">
         <v>1496867</v>
@@ -3733,7 +3733,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H116" t="n">
         <v>959348</v>
@@ -3791,7 +3791,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G118" t="n">
-        <v>2.14091181755066</v>
+        <v>2.14091205596924</v>
       </c>
       <c r="H118" t="n">
         <v>272440</v>
@@ -3820,7 +3820,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H119" t="n">
         <v>854222</v>
@@ -3907,7 +3907,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.15604186058044</v>
+        <v>2.15604209899902</v>
       </c>
       <c r="H122" t="n">
         <v>505790</v>
@@ -3965,7 +3965,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G124" t="n">
-        <v>2.16738963127136</v>
+        <v>2.16738939285278</v>
       </c>
       <c r="H124" t="n">
         <v>711853</v>
@@ -3994,7 +3994,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G125" t="n">
-        <v>2.16991090774536</v>
+        <v>2.16991138458252</v>
       </c>
       <c r="H125" t="n">
         <v>416120</v>
@@ -4023,7 +4023,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G126" t="n">
-        <v>2.14847660064697</v>
+        <v>2.14847683906555</v>
       </c>
       <c r="H126" t="n">
         <v>602771</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.15604186058044</v>
+        <v>2.15604209899902</v>
       </c>
       <c r="H127" t="n">
         <v>556151</v>
@@ -4081,7 +4081,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G128" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H128" t="n">
         <v>638147</v>
@@ -4110,7 +4110,7 @@
         <v>3.41599988937378</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15352034568787</v>
+        <v>2.15352010726929</v>
       </c>
       <c r="H129" t="n">
         <v>520370</v>
@@ -4168,7 +4168,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G131" t="n">
-        <v>2.11191248893738</v>
+        <v>2.1119122505188</v>
       </c>
       <c r="H131" t="n">
         <v>982502</v>
@@ -4197,7 +4197,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>2.11191248893738</v>
+        <v>2.1119122505188</v>
       </c>
       <c r="H132" t="n">
         <v>983090</v>
@@ -4255,7 +4255,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G134" t="n">
-        <v>2.0425660610199</v>
+        <v>2.04256582260132</v>
       </c>
       <c r="H134" t="n">
         <v>446178</v>
@@ -4284,7 +4284,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G135" t="n">
-        <v>2.0425660610199</v>
+        <v>2.04256582260132</v>
       </c>
       <c r="H135" t="n">
         <v>1021203</v>
@@ -4342,7 +4342,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G137" t="n">
-        <v>2.02491426467896</v>
+        <v>2.02491402626038</v>
       </c>
       <c r="H137" t="n">
         <v>613132</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.0425660610199</v>
+        <v>2.04256582260132</v>
       </c>
       <c r="H138" t="n">
         <v>873840</v>
@@ -4400,7 +4400,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>1.99213242530823</v>
+        <v>1.99213230609894</v>
       </c>
       <c r="H139" t="n">
         <v>526097</v>
@@ -4429,7 +4429,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G140" t="n">
-        <v>1.97069811820984</v>
+        <v>1.97069787979126</v>
       </c>
       <c r="H140" t="n">
         <v>655592</v>
@@ -4487,7 +4487,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>2.01734900474548</v>
+        <v>2.01734924316406</v>
       </c>
       <c r="H142" t="n">
         <v>1211840</v>
@@ -4516,7 +4516,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>2.05643534660339</v>
+        <v>2.05643558502197</v>
       </c>
       <c r="H143" t="n">
         <v>591488</v>
@@ -4574,7 +4574,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G145" t="n">
-        <v>2.06400012969971</v>
+        <v>2.06400036811829</v>
       </c>
       <c r="H145" t="n">
         <v>430023</v>
@@ -4603,7 +4603,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G146" t="n">
-        <v>2.11191248893738</v>
+        <v>2.1119122505188</v>
       </c>
       <c r="H146" t="n">
         <v>1000881</v>
@@ -4632,7 +4632,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G147" t="n">
-        <v>2.13712930679321</v>
+        <v>2.13712954521179</v>
       </c>
       <c r="H147" t="n">
         <v>886586</v>
@@ -4661,7 +4661,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G148" t="n">
-        <v>2.14973759651184</v>
+        <v>2.14973735809326</v>
       </c>
       <c r="H148" t="n">
         <v>660518</v>
@@ -4690,7 +4690,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G149" t="n">
-        <v>2.152259349823</v>
+        <v>2.15225958824158</v>
       </c>
       <c r="H149" t="n">
         <v>659705</v>
@@ -4719,7 +4719,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>2.1434338092804</v>
+        <v>2.14343333244324</v>
       </c>
       <c r="H150" t="n">
         <v>618937</v>
@@ -4748,7 +4748,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G151" t="n">
-        <v>2.16486811637878</v>
+        <v>2.16486763954163</v>
       </c>
       <c r="H151" t="n">
         <v>993672</v>
@@ -4777,7 +4777,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G152" t="n">
-        <v>2.12199902534485</v>
+        <v>2.12199926376343</v>
       </c>
       <c r="H152" t="n">
         <v>878730</v>
@@ -4806,7 +4806,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G153" t="n">
-        <v>2.09552145004272</v>
+        <v>2.09552121162415</v>
       </c>
       <c r="H153" t="n">
         <v>692808</v>
@@ -4893,7 +4893,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G156" t="n">
-        <v>2.13712930679321</v>
+        <v>2.13712954521179</v>
       </c>
       <c r="H156" t="n">
         <v>566431</v>
@@ -4922,7 +4922,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G157" t="n">
-        <v>2.12452054023743</v>
+        <v>2.12452077865601</v>
       </c>
       <c r="H157" t="n">
         <v>566734</v>
@@ -4951,7 +4951,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.12452054023743</v>
+        <v>2.12452077865601</v>
       </c>
       <c r="H158" t="n">
         <v>451572</v>
@@ -5009,7 +5009,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G160" t="n">
-        <v>2.12704277038574</v>
+        <v>2.12704253196716</v>
       </c>
       <c r="H160" t="n">
         <v>735413</v>
@@ -5125,7 +5125,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G164" t="n">
-        <v>2.14595508575439</v>
+        <v>2.14595532417297</v>
       </c>
       <c r="H164" t="n">
         <v>656848</v>
@@ -5212,7 +5212,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G167" t="n">
-        <v>2.21277976036072</v>
+        <v>2.2127799987793</v>
       </c>
       <c r="H167" t="n">
         <v>1593490</v>
@@ -5241,7 +5241,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G168" t="n">
-        <v>2.33129930496216</v>
+        <v>2.331298828125</v>
       </c>
       <c r="H168" t="n">
         <v>1990731</v>
@@ -5357,7 +5357,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.3514723777771</v>
+        <v>2.35147261619568</v>
       </c>
       <c r="H172" t="n">
         <v>1771997</v>
@@ -5473,7 +5473,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G176" t="n">
-        <v>2.32877707481384</v>
+        <v>2.328777551651</v>
       </c>
       <c r="H176" t="n">
         <v>959599</v>
@@ -5531,7 +5531,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G178" t="n">
-        <v>2.4031674861908</v>
+        <v>2.40316700935364</v>
       </c>
       <c r="H178" t="n">
         <v>2956792</v>
@@ -5589,7 +5589,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.32247352600098</v>
+        <v>2.32247304916382</v>
       </c>
       <c r="H180" t="n">
         <v>1030102</v>
@@ -5618,7 +5618,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G181" t="n">
-        <v>2.3918194770813</v>
+        <v>2.39181971549988</v>
       </c>
       <c r="H181" t="n">
         <v>1136549</v>
@@ -5647,7 +5647,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G182" t="n">
-        <v>2.37038516998291</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H182" t="n">
         <v>1371992</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>2.39560222625732</v>
+        <v>2.39560198783875</v>
       </c>
       <c r="H183" t="n">
         <v>1547599</v>
@@ -5705,7 +5705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>2.39560222625732</v>
+        <v>2.39560198783875</v>
       </c>
       <c r="H184" t="n">
         <v>1699128</v>
@@ -5763,7 +5763,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G186" t="n">
-        <v>2.41703653335571</v>
+        <v>2.41703677177429</v>
       </c>
       <c r="H186" t="n">
         <v>906431</v>
@@ -5821,7 +5821,7 @@
         <v>3.75</v>
       </c>
       <c r="G188" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H188" t="n">
         <v>550329</v>
@@ -5850,7 +5850,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G189" t="n">
-        <v>2.36534190177917</v>
+        <v>2.36534214019775</v>
       </c>
       <c r="H189" t="n">
         <v>713369</v>
@@ -5879,7 +5879,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G190" t="n">
-        <v>2.3628203868866</v>
+        <v>2.36282014846802</v>
       </c>
       <c r="H190" t="n">
         <v>864165</v>
@@ -5937,7 +5937,7 @@
         <v>3.75</v>
       </c>
       <c r="G192" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H192" t="n">
         <v>1026811</v>
@@ -5966,7 +5966,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G193" t="n">
-        <v>2.3552553653717</v>
+        <v>2.35525512695312</v>
       </c>
       <c r="H193" t="n">
         <v>554537</v>
@@ -6024,7 +6024,7 @@
         <v>3.75</v>
       </c>
       <c r="G195" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H195" t="n">
         <v>889289</v>
@@ -6053,7 +6053,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G196" t="n">
-        <v>2.37038516998291</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H196" t="n">
         <v>930629</v>
@@ -6111,7 +6111,7 @@
         <v>3.75</v>
       </c>
       <c r="G198" t="n">
-        <v>2.36408090591431</v>
+        <v>2.36408066749573</v>
       </c>
       <c r="H198" t="n">
         <v>542591</v>
@@ -6140,7 +6140,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39560222625732</v>
+        <v>2.39560198783875</v>
       </c>
       <c r="H199" t="n">
         <v>1166747</v>
@@ -6169,7 +6169,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>2.42964506149292</v>
+        <v>2.42964458465576</v>
       </c>
       <c r="H200" t="n">
         <v>722953</v>
@@ -6227,7 +6227,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.4523401260376</v>
+        <v>2.45234060287476</v>
       </c>
       <c r="H202" t="n">
         <v>1065606</v>
@@ -6256,7 +6256,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G203" t="n">
-        <v>2.43847107887268</v>
+        <v>2.43847060203552</v>
       </c>
       <c r="H203" t="n">
         <v>749019</v>
@@ -6314,7 +6314,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G205" t="n">
-        <v>2.44603586196899</v>
+        <v>2.44603610038757</v>
       </c>
       <c r="H205" t="n">
         <v>915733</v>
@@ -6343,7 +6343,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.4586443901062</v>
+        <v>2.45864462852478</v>
       </c>
       <c r="H206" t="n">
         <v>901759</v>
@@ -6372,7 +6372,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G207" t="n">
-        <v>2.44603586196899</v>
+        <v>2.44603610038757</v>
       </c>
       <c r="H207" t="n">
         <v>364301</v>
@@ -6401,7 +6401,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>2.38677620887756</v>
+        <v>2.38677644729614</v>
       </c>
       <c r="H208" t="n">
         <v>998514</v>
@@ -6459,7 +6459,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G210" t="n">
-        <v>2.37038516998291</v>
+        <v>2.37038540840149</v>
       </c>
       <c r="H210" t="n">
         <v>2706748</v>
@@ -6517,7 +6517,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G212" t="n">
-        <v>2.39816308021545</v>
+        <v>2.39816331863403</v>
       </c>
       <c r="H212" t="n">
         <v>905628</v>
@@ -6604,7 +6604,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G215" t="n">
-        <v>2.51721167564392</v>
+        <v>2.51721119880676</v>
       </c>
       <c r="H215" t="n">
         <v>1570341</v>
@@ -6662,7 +6662,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>2.4669463634491</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H217" t="n">
         <v>1320391</v>
@@ -6691,7 +6691,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G218" t="n">
-        <v>2.48149704933167</v>
+        <v>2.48149728775024</v>
       </c>
       <c r="H218" t="n">
         <v>2972831</v>
@@ -6720,7 +6720,7 @@
         <v>3.75</v>
       </c>
       <c r="G219" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H219" t="n">
         <v>1382829</v>
@@ -6778,7 +6778,7 @@
         <v>3.75</v>
       </c>
       <c r="G221" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H221" t="n">
         <v>514242</v>
@@ -6807,7 +6807,7 @@
         <v>3.75</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H222" t="n">
         <v>1022566</v>
@@ -6865,7 +6865,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G224" t="n">
-        <v>2.49737024307251</v>
+        <v>2.49737000465393</v>
       </c>
       <c r="H224" t="n">
         <v>1878448</v>
@@ -6894,7 +6894,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G225" t="n">
-        <v>2.52250266075134</v>
+        <v>2.52250242233276</v>
       </c>
       <c r="H225" t="n">
         <v>1838179</v>
@@ -6923,7 +6923,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G226" t="n">
-        <v>2.48546504974365</v>
+        <v>2.48546528816223</v>
       </c>
       <c r="H226" t="n">
         <v>1137067</v>
@@ -6952,7 +6952,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G227" t="n">
-        <v>2.50530672073364</v>
+        <v>2.50530695915222</v>
       </c>
       <c r="H227" t="n">
         <v>982862</v>
@@ -7010,7 +7010,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>2.49340200424194</v>
+        <v>2.49340152740479</v>
       </c>
       <c r="H229" t="n">
         <v>2545491</v>
@@ -7039,7 +7039,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>2.4669463634491</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H230" t="n">
         <v>3703950</v>
@@ -7068,7 +7068,7 @@
         <v>3.75</v>
       </c>
       <c r="G231" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H231" t="n">
         <v>630800</v>
@@ -7097,7 +7097,7 @@
         <v>3.75</v>
       </c>
       <c r="G232" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H232" t="n">
         <v>2066418</v>
@@ -7155,7 +7155,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>2.47356009483337</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H234" t="n">
         <v>365542</v>
@@ -7184,7 +7184,7 @@
         <v>3.75</v>
       </c>
       <c r="G235" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H235" t="n">
         <v>612027</v>
@@ -7213,7 +7213,7 @@
         <v>3.75</v>
       </c>
       <c r="G236" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H236" t="n">
         <v>1886715</v>
@@ -7242,7 +7242,7 @@
         <v>3.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.48017430305481</v>
+        <v>2.48017406463623</v>
       </c>
       <c r="H237" t="n">
         <v>1004577</v>
@@ -7271,7 +7271,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G238" t="n">
-        <v>2.45239615440369</v>
+        <v>2.45239639282227</v>
       </c>
       <c r="H238" t="n">
         <v>975866</v>
@@ -7416,7 +7416,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>2.4669463634491</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H243" t="n">
         <v>279712</v>
@@ -7503,7 +7503,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>2.4669463634491</v>
+        <v>2.46694660186768</v>
       </c>
       <c r="H246" t="n">
         <v>235874</v>
@@ -7590,7 +7590,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>2.49340200424194</v>
+        <v>2.49340152740479</v>
       </c>
       <c r="H249" t="n">
         <v>558538</v>
@@ -7706,7 +7706,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G253" t="n">
-        <v>2.44975090026855</v>
+        <v>2.44975066184998</v>
       </c>
       <c r="H253" t="n">
         <v>622270</v>
@@ -7735,7 +7735,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>2.45371913909912</v>
+        <v>2.45371890068054</v>
       </c>
       <c r="H254" t="n">
         <v>628873</v>
@@ -7764,7 +7764,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H255" t="n">
         <v>460966</v>
@@ -7793,7 +7793,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G256" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H256" t="n">
         <v>262852</v>
@@ -7851,7 +7851,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>2.47356009483337</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H258" t="n">
         <v>335894</v>
@@ -7880,7 +7880,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G259" t="n">
-        <v>2.50927495956421</v>
+        <v>2.50927472114563</v>
       </c>
       <c r="H259" t="n">
         <v>381908</v>
@@ -7909,7 +7909,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>2.51456618309021</v>
+        <v>2.51456594467163</v>
       </c>
       <c r="H260" t="n">
         <v>440530</v>
@@ -7938,7 +7938,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G261" t="n">
-        <v>2.56483125686646</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H261" t="n">
         <v>524937</v>
@@ -7967,7 +7967,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55689406394958</v>
+        <v>2.55689430236816</v>
       </c>
       <c r="H262" t="n">
         <v>748895</v>
@@ -7996,7 +7996,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G263" t="n">
-        <v>2.57144474983215</v>
+        <v>2.57144451141357</v>
       </c>
       <c r="H263" t="n">
         <v>328662</v>
@@ -8054,7 +8054,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G265" t="n">
-        <v>2.56483125686646</v>
+        <v>2.56483101844788</v>
       </c>
       <c r="H265" t="n">
         <v>514836</v>
@@ -8083,7 +8083,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G266" t="n">
-        <v>2.56615400314331</v>
+        <v>2.56615352630615</v>
       </c>
       <c r="H266" t="n">
         <v>481921</v>
@@ -8228,7 +8228,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>2.53308463096619</v>
+        <v>2.53308439254761</v>
       </c>
       <c r="H271" t="n">
         <v>286015</v>
@@ -8315,7 +8315,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.49340200424194</v>
+        <v>2.49340152740479</v>
       </c>
       <c r="H274" t="n">
         <v>879590</v>
@@ -8344,7 +8344,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>2.47356009483337</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H275" t="n">
         <v>409245</v>
@@ -8402,7 +8402,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>2.47356009483337</v>
+        <v>2.47356057167053</v>
       </c>
       <c r="H277" t="n">
         <v>374003</v>
@@ -8431,7 +8431,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.48678803443909</v>
+        <v>2.48678827285767</v>
       </c>
       <c r="H278" t="n">
         <v>277590</v>
@@ -8460,7 +8460,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G279" t="n">
-        <v>2.47488307952881</v>
+        <v>2.47488331794739</v>
       </c>
       <c r="H279" t="n">
         <v>167600</v>
@@ -8489,7 +8489,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G280" t="n">
-        <v>2.44842791557312</v>
+        <v>2.4484281539917</v>
       </c>
       <c r="H280" t="n">
         <v>191020</v>
@@ -8518,7 +8518,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G281" t="n">
-        <v>2.42858672142029</v>
+        <v>2.42858648300171</v>
       </c>
       <c r="H281" t="n">
         <v>622612</v>
@@ -8576,7 +8576,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G283" t="n">
-        <v>2.45900988578796</v>
+        <v>2.45901012420654</v>
       </c>
       <c r="H283" t="n">
         <v>414099</v>
@@ -8605,7 +8605,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G284" t="n">
-        <v>2.47752904891968</v>
+        <v>2.4775288105011</v>
       </c>
       <c r="H284" t="n">
         <v>405263</v>
@@ -8692,7 +8692,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>2.43652272224426</v>
+        <v>2.4365234375</v>
       </c>
       <c r="H287" t="n">
         <v>539242</v>
@@ -8721,7 +8721,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G288" t="n">
-        <v>2.49869275093079</v>
+        <v>2.49869298934937</v>
       </c>
       <c r="H288" t="n">
         <v>633611</v>
@@ -8808,7 +8808,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G291" t="n">
-        <v>2.53837585449219</v>
+        <v>2.53837561607361</v>
       </c>
       <c r="H291" t="n">
         <v>385349</v>
@@ -8837,7 +8837,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G292" t="n">
-        <v>2.53573036193848</v>
+        <v>2.5357301235199</v>
       </c>
       <c r="H292" t="n">
         <v>257047</v>
@@ -8866,7 +8866,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G293" t="n">
-        <v>2.5344078540802</v>
+        <v>2.53440761566162</v>
       </c>
       <c r="H293" t="n">
         <v>472169</v>
@@ -8895,7 +8895,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G294" t="n">
-        <v>2.5304388999939</v>
+        <v>2.53043913841248</v>
       </c>
       <c r="H294" t="n">
         <v>973552</v>
@@ -8924,7 +8924,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G295" t="n">
-        <v>2.53176188468933</v>
+        <v>2.53176212310791</v>
       </c>
       <c r="H295" t="n">
         <v>569194</v>
@@ -8953,7 +8953,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G296" t="n">
-        <v>2.54102110862732</v>
+        <v>2.5410213470459</v>
       </c>
       <c r="H296" t="n">
         <v>538902</v>
@@ -8982,7 +8982,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G297" t="n">
-        <v>2.52779340744019</v>
+        <v>2.52779388427734</v>
       </c>
       <c r="H297" t="n">
         <v>420940</v>
@@ -9011,7 +9011,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G298" t="n">
-        <v>2.51456618309021</v>
+        <v>2.51456594467163</v>
       </c>
       <c r="H298" t="n">
         <v>271055</v>
@@ -9040,7 +9040,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G299" t="n">
-        <v>2.51721167564392</v>
+        <v>2.51721119880676</v>
       </c>
       <c r="H299" t="n">
         <v>254927</v>
@@ -9069,7 +9069,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53308463096619</v>
+        <v>2.53308439254761</v>
       </c>
       <c r="H300" t="n">
         <v>622766</v>
@@ -9098,7 +9098,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G301" t="n">
-        <v>2.53573036193848</v>
+        <v>2.5357301235199</v>
       </c>
       <c r="H301" t="n">
         <v>356050</v>
@@ -9214,7 +9214,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G305" t="n">
-        <v>2.61377286911011</v>
+        <v>2.61377310752869</v>
       </c>
       <c r="H305" t="n">
         <v>844898</v>
@@ -9243,7 +9243,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G306" t="n">
-        <v>2.59922242164612</v>
+        <v>2.5992226600647</v>
       </c>
       <c r="H306" t="n">
         <v>581605</v>
@@ -9330,7 +9330,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.57276749610901</v>
+        <v>2.57276701927185</v>
       </c>
       <c r="H309" t="n">
         <v>811458</v>
@@ -9388,7 +9388,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G311" t="n">
-        <v>2.59128642082214</v>
+        <v>2.59128594398499</v>
       </c>
       <c r="H311" t="n">
         <v>463030</v>
@@ -9417,7 +9417,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G312" t="n">
-        <v>2.58864068984985</v>
+        <v>2.5886402130127</v>
       </c>
       <c r="H312" t="n">
         <v>672881</v>
@@ -9446,7 +9446,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G313" t="n">
-        <v>2.62700057029724</v>
+        <v>2.62700033187866</v>
       </c>
       <c r="H313" t="n">
         <v>774969</v>
@@ -9475,7 +9475,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G314" t="n">
-        <v>2.60980463027954</v>
+        <v>2.60980486869812</v>
       </c>
       <c r="H314" t="n">
         <v>445032</v>
@@ -9504,7 +9504,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G315" t="n">
-        <v>2.60980463027954</v>
+        <v>2.60980486869812</v>
       </c>
       <c r="H315" t="n">
         <v>562538</v>
@@ -9591,7 +9591,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G318" t="n">
-        <v>2.68916988372803</v>
+        <v>2.68917036056519</v>
       </c>
       <c r="H318" t="n">
         <v>660904</v>
@@ -9620,7 +9620,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G319" t="n">
-        <v>2.67594265937805</v>
+        <v>2.67594289779663</v>
       </c>
       <c r="H319" t="n">
         <v>576776</v>
@@ -9707,7 +9707,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G322" t="n">
-        <v>2.64816498756409</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H322" t="n">
         <v>362068</v>
@@ -9997,7 +9997,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G332" t="n">
-        <v>2.70107483863831</v>
+        <v>2.70107507705688</v>
       </c>
       <c r="H332" t="n">
         <v>431759</v>
@@ -10026,7 +10026,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G333" t="n">
-        <v>2.70107483863831</v>
+        <v>2.70107507705688</v>
       </c>
       <c r="H333" t="n">
         <v>1317493</v>
@@ -10055,7 +10055,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>2.65874671936035</v>
+        <v>2.65874695777893</v>
       </c>
       <c r="H334" t="n">
         <v>564957</v>
@@ -10142,7 +10142,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G337" t="n">
-        <v>2.78837752342224</v>
+        <v>2.78837704658508</v>
       </c>
       <c r="H337" t="n">
         <v>2139808</v>
@@ -10171,7 +10171,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054707527161</v>
       </c>
       <c r="H338" t="n">
         <v>1428133</v>
@@ -10200,7 +10200,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G339" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H339" t="n">
         <v>425935</v>
@@ -10258,7 +10258,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G341" t="n">
-        <v>2.9034571647644</v>
+        <v>2.90345740318298</v>
       </c>
       <c r="H341" t="n">
         <v>1248384</v>
@@ -10287,7 +10287,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G342" t="n">
-        <v>2.90742540359497</v>
+        <v>2.90742564201355</v>
       </c>
       <c r="H342" t="n">
         <v>1794819</v>
@@ -10316,7 +10316,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G343" t="n">
-        <v>2.94578528404236</v>
+        <v>2.94578552246094</v>
       </c>
       <c r="H343" t="n">
         <v>1446520</v>
@@ -10345,7 +10345,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G344" t="n">
-        <v>2.95901346206665</v>
+        <v>2.95901274681091</v>
       </c>
       <c r="H344" t="n">
         <v>1122926</v>
@@ -10461,7 +10461,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G348" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H348" t="n">
         <v>1065152</v>
@@ -10490,7 +10490,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G349" t="n">
-        <v>2.95901346206665</v>
+        <v>2.95901274681091</v>
       </c>
       <c r="H349" t="n">
         <v>794496</v>
@@ -10519,7 +10519,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G350" t="n">
-        <v>2.99340510368347</v>
+        <v>2.99340486526489</v>
       </c>
       <c r="H350" t="n">
         <v>996164</v>
@@ -10577,7 +10577,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03837895393372</v>
+        <v>3.03837871551514</v>
       </c>
       <c r="H352" t="n">
         <v>949730</v>
@@ -10606,7 +10606,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G353" t="n">
-        <v>3.03176498413086</v>
+        <v>3.03176474571228</v>
       </c>
       <c r="H353" t="n">
         <v>617623</v>
@@ -10635,7 +10635,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G354" t="n">
-        <v>3.10583996772766</v>
+        <v>3.10583972930908</v>
       </c>
       <c r="H354" t="n">
         <v>888394</v>
@@ -10693,7 +10693,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.0092785358429</v>
+        <v>3.00927829742432</v>
       </c>
       <c r="H356" t="n">
         <v>1663888</v>
@@ -10780,7 +10780,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>3.0423469543457</v>
+        <v>3.04234719276428</v>
       </c>
       <c r="H359" t="n">
         <v>1263796</v>
@@ -10809,7 +10809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G360" t="n">
-        <v>3.04631519317627</v>
+        <v>3.04631567001343</v>
       </c>
       <c r="H360" t="n">
         <v>1279493</v>
@@ -10925,7 +10925,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G364" t="n">
-        <v>3.025151014328</v>
+        <v>3.02515077590942</v>
       </c>
       <c r="H364" t="n">
         <v>436276</v>
@@ -10954,7 +10954,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>2.98943638801575</v>
+        <v>2.98943686485291</v>
       </c>
       <c r="H365" t="n">
         <v>511496</v>
@@ -11128,7 +11128,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G371" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H371" t="n">
         <v>609342</v>
@@ -11215,7 +11215,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>2.94313979148865</v>
+        <v>2.94314002990723</v>
       </c>
       <c r="H374" t="n">
         <v>861518</v>
@@ -11244,7 +11244,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G375" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054707527161</v>
       </c>
       <c r="H375" t="n">
         <v>2514673</v>
@@ -11302,7 +11302,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G377" t="n">
-        <v>2.84922409057617</v>
+        <v>2.84922456741333</v>
       </c>
       <c r="H377" t="n">
         <v>531133</v>
@@ -11331,7 +11331,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G378" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H378" t="n">
         <v>654476</v>
@@ -11389,7 +11389,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>2.84393358230591</v>
+        <v>2.84393310546875</v>
       </c>
       <c r="H380" t="n">
         <v>657743</v>
@@ -11418,7 +11418,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G381" t="n">
-        <v>2.85980629920959</v>
+        <v>2.85980606079102</v>
       </c>
       <c r="H381" t="n">
         <v>559669</v>
@@ -11476,7 +11476,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G383" t="n">
-        <v>2.8307056427002</v>
+        <v>2.83070588111877</v>
       </c>
       <c r="H383" t="n">
         <v>646536</v>
@@ -11505,7 +11505,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G384" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H384" t="n">
         <v>424777</v>
@@ -11534,7 +11534,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G385" t="n">
-        <v>2.84922409057617</v>
+        <v>2.84922456741333</v>
       </c>
       <c r="H385" t="n">
         <v>471951</v>
@@ -11621,7 +11621,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.79763674736023</v>
+        <v>2.79763650894165</v>
       </c>
       <c r="H388" t="n">
         <v>888381</v>
@@ -11650,7 +11650,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.78705477714539</v>
+        <v>2.78705406188965</v>
       </c>
       <c r="H389" t="n">
         <v>1087808</v>
@@ -11679,7 +11679,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80689549446106</v>
+        <v>2.80689573287964</v>
       </c>
       <c r="H390" t="n">
         <v>516731</v>
@@ -11737,7 +11737,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G392" t="n">
-        <v>2.80689549446106</v>
+        <v>2.80689573287964</v>
       </c>
       <c r="H392" t="n">
         <v>1039683</v>
@@ -11766,7 +11766,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>2.71165728569031</v>
+        <v>2.71165704727173</v>
       </c>
       <c r="H393" t="n">
         <v>1017959</v>
@@ -11882,7 +11882,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G397" t="n">
-        <v>2.69446110725403</v>
+        <v>2.69446134567261</v>
       </c>
       <c r="H397" t="n">
         <v>848281</v>
@@ -11969,7 +11969,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G400" t="n">
-        <v>2.75001692771912</v>
+        <v>2.7500171661377</v>
       </c>
       <c r="H400" t="n">
         <v>527748</v>
@@ -11998,7 +11998,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.75927686691284</v>
+        <v>2.7592761516571</v>
       </c>
       <c r="H401" t="n">
         <v>543737</v>
@@ -12027,7 +12027,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G402" t="n">
-        <v>2.75663137435913</v>
+        <v>2.75663113594055</v>
       </c>
       <c r="H402" t="n">
         <v>289481</v>
@@ -12056,7 +12056,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G403" t="n">
-        <v>2.76456761360168</v>
+        <v>2.76456737518311</v>
       </c>
       <c r="H403" t="n">
         <v>371911</v>
@@ -12172,7 +12172,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G407" t="n">
-        <v>2.79102230072021</v>
+        <v>2.79102253913879</v>
       </c>
       <c r="H407" t="n">
         <v>384104</v>
@@ -12201,7 +12201,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G408" t="n">
-        <v>2.73943543434143</v>
+        <v>2.73943519592285</v>
       </c>
       <c r="H408" t="n">
         <v>682369</v>
@@ -12259,7 +12259,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G410" t="n">
-        <v>2.72620749473572</v>
+        <v>2.7262077331543</v>
       </c>
       <c r="H410" t="n">
         <v>884762</v>
@@ -12375,7 +12375,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>2.75927686691284</v>
+        <v>2.7592761516571</v>
       </c>
       <c r="H414" t="n">
         <v>581298</v>
@@ -12404,7 +12404,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G415" t="n">
-        <v>2.78044080734253</v>
+        <v>2.78044056892395</v>
       </c>
       <c r="H415" t="n">
         <v>641497</v>
@@ -12433,7 +12433,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G416" t="n">
-        <v>2.79102230072021</v>
+        <v>2.79102253913879</v>
       </c>
       <c r="H416" t="n">
         <v>262750</v>
@@ -12462,7 +12462,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G417" t="n">
-        <v>2.85583806037903</v>
+        <v>2.85583758354187</v>
       </c>
       <c r="H417" t="n">
         <v>1518103</v>
@@ -12520,7 +12520,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G419" t="n">
-        <v>2.87303400039673</v>
+        <v>2.87303376197815</v>
       </c>
       <c r="H419" t="n">
         <v>1064225</v>
@@ -12549,7 +12549,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>2.91007137298584</v>
+        <v>2.91007089614868</v>
       </c>
       <c r="H420" t="n">
         <v>721209</v>
@@ -12578,7 +12578,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G421" t="n">
-        <v>2.88890695571899</v>
+        <v>2.88890719413757</v>
       </c>
       <c r="H421" t="n">
         <v>630370</v>
@@ -12636,7 +12636,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G423" t="n">
-        <v>2.89287495613098</v>
+        <v>2.89287519454956</v>
       </c>
       <c r="H423" t="n">
         <v>451656</v>
@@ -12665,7 +12665,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G424" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H424" t="n">
         <v>511038</v>
@@ -12723,7 +12723,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G426" t="n">
-        <v>2.81483244895935</v>
+        <v>2.81483221054077</v>
       </c>
       <c r="H426" t="n">
         <v>783217</v>
@@ -12752,7 +12752,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G427" t="n">
-        <v>2.79234528541565</v>
+        <v>2.79234552383423</v>
       </c>
       <c r="H427" t="n">
         <v>495666</v>
@@ -12781,7 +12781,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G428" t="n">
-        <v>2.83335113525391</v>
+        <v>2.83335137367249</v>
       </c>
       <c r="H428" t="n">
         <v>634478</v>
@@ -12810,7 +12810,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G429" t="n">
-        <v>2.8479015827179</v>
+        <v>2.84790182113647</v>
       </c>
       <c r="H429" t="n">
         <v>1135467</v>
@@ -12897,7 +12897,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.85054683685303</v>
+        <v>2.85054707527161</v>
       </c>
       <c r="H432" t="n">
         <v>482261</v>
@@ -12926,7 +12926,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>2.89022970199585</v>
+        <v>2.89022922515869</v>
       </c>
       <c r="H433" t="n">
         <v>641837</v>
@@ -12984,7 +12984,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G435" t="n">
-        <v>2.90610313415527</v>
+        <v>2.90610265731812</v>
       </c>
       <c r="H435" t="n">
         <v>364698</v>
@@ -13013,7 +13013,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G436" t="n">
-        <v>2.93123531341553</v>
+        <v>2.93123507499695</v>
       </c>
       <c r="H436" t="n">
         <v>487422</v>
@@ -13042,7 +13042,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.94181704521179</v>
+        <v>2.94181728363037</v>
       </c>
       <c r="H437" t="n">
         <v>413076</v>
@@ -13100,7 +13100,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G439" t="n">
-        <v>2.9920825958252</v>
+        <v>2.99208235740662</v>
       </c>
       <c r="H439" t="n">
         <v>796136</v>
@@ -13216,7 +13216,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G443" t="n">
-        <v>2.93520379066467</v>
+        <v>2.93520355224609</v>
       </c>
       <c r="H443" t="n">
         <v>1018294</v>
@@ -13245,7 +13245,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G444" t="n">
-        <v>2.94181704521179</v>
+        <v>2.94181728363037</v>
       </c>
       <c r="H444" t="n">
         <v>553049</v>
@@ -13274,7 +13274,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G445" t="n">
-        <v>2.95636773109436</v>
+        <v>2.9563672542572</v>
       </c>
       <c r="H445" t="n">
         <v>229109</v>
@@ -13303,7 +13303,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96827244758606</v>
+        <v>2.96827220916748</v>
       </c>
       <c r="H446" t="n">
         <v>588207</v>
@@ -13332,7 +13332,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G447" t="n">
-        <v>2.95636773109436</v>
+        <v>2.9563672542572</v>
       </c>
       <c r="H447" t="n">
         <v>241939</v>
@@ -13390,7 +13390,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G449" t="n">
-        <v>2.99075984954834</v>
+        <v>2.99075961112976</v>
       </c>
       <c r="H449" t="n">
         <v>251562</v>
@@ -13419,7 +13419,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.9920825958252</v>
+        <v>2.99208235740662</v>
       </c>
       <c r="H450" t="n">
         <v>365775</v>
@@ -13448,7 +13448,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G451" t="n">
-        <v>3.01721429824829</v>
+        <v>3.01721453666687</v>
       </c>
       <c r="H451" t="n">
         <v>457814</v>
@@ -13622,7 +13622,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92991256713867</v>
+        <v>2.92991232872009</v>
       </c>
       <c r="H457" t="n">
         <v>493247</v>
@@ -13680,7 +13680,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G459" t="n">
-        <v>2.98943638801575</v>
+        <v>2.98943686485291</v>
       </c>
       <c r="H459" t="n">
         <v>467969</v>
@@ -13738,7 +13738,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94710826873779</v>
+        <v>2.94710803031921</v>
       </c>
       <c r="H461" t="n">
         <v>1603800</v>
@@ -13767,7 +13767,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G462" t="n">
-        <v>2.89684367179871</v>
+        <v>2.89684319496155</v>
       </c>
       <c r="H462" t="n">
         <v>974266</v>
@@ -13825,7 +13825,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G464" t="n">
-        <v>2.89080095291138</v>
+        <v>2.89080142974854</v>
       </c>
       <c r="H464" t="n">
         <v>642124</v>
@@ -13854,7 +13854,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.92672944068909</v>
+        <v>2.92672920227051</v>
       </c>
       <c r="H465" t="n">
         <v>391973</v>
@@ -13883,7 +13883,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>2.89494705200195</v>
+        <v>2.89494681358337</v>
       </c>
       <c r="H466" t="n">
         <v>816758</v>
@@ -13912,7 +13912,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G467" t="n">
-        <v>2.90876531600952</v>
+        <v>2.9087655544281</v>
       </c>
       <c r="H467" t="n">
         <v>575040</v>
@@ -13941,7 +13941,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G468" t="n">
-        <v>2.88112854957581</v>
+        <v>2.88112878799438</v>
       </c>
       <c r="H468" t="n">
         <v>579088</v>
@@ -14057,7 +14057,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G472" t="n">
-        <v>2.84796476364136</v>
+        <v>2.8479642868042</v>
       </c>
       <c r="H472" t="n">
         <v>612992</v>
@@ -14202,7 +14202,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>2.81894564628601</v>
+        <v>2.81894588470459</v>
       </c>
       <c r="H477" t="n">
         <v>580850</v>
@@ -14231,7 +14231,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>2.79130911827087</v>
+        <v>2.79130887985229</v>
       </c>
       <c r="H478" t="n">
         <v>484051</v>
@@ -14434,7 +14434,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G485" t="n">
-        <v>2.99858474731445</v>
+        <v>2.99858498573303</v>
       </c>
       <c r="H485" t="n">
         <v>2322061</v>
@@ -14463,7 +14463,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G486" t="n">
-        <v>3.01240301132202</v>
+        <v>3.01240277290344</v>
       </c>
       <c r="H486" t="n">
         <v>616403</v>
@@ -14521,7 +14521,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931142807007</v>
       </c>
       <c r="H488" t="n">
         <v>1239936</v>
@@ -14550,7 +14550,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G489" t="n">
-        <v>2.97371101379395</v>
+        <v>2.9737114906311</v>
       </c>
       <c r="H489" t="n">
         <v>488412</v>
@@ -14608,7 +14608,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97785687446594</v>
+        <v>2.97785711288452</v>
       </c>
       <c r="H491" t="n">
         <v>736849</v>
@@ -14637,7 +14637,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>2.95989322662354</v>
+        <v>2.95989346504211</v>
       </c>
       <c r="H492" t="n">
         <v>427110</v>
@@ -14666,7 +14666,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G493" t="n">
-        <v>2.96818447113037</v>
+        <v>2.96818423271179</v>
       </c>
       <c r="H493" t="n">
         <v>355874</v>
@@ -14695,7 +14695,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G494" t="n">
-        <v>2.96818447113037</v>
+        <v>2.96818423271179</v>
       </c>
       <c r="H494" t="n">
         <v>219739</v>
@@ -14753,7 +14753,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G496" t="n">
-        <v>2.96818447113037</v>
+        <v>2.96818423271179</v>
       </c>
       <c r="H496" t="n">
         <v>351475</v>
@@ -14782,7 +14782,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>2.99858474731445</v>
+        <v>2.99858498573303</v>
       </c>
       <c r="H497" t="n">
         <v>268490</v>
@@ -14840,7 +14840,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G499" t="n">
-        <v>2.97509360313416</v>
+        <v>2.97509336471558</v>
       </c>
       <c r="H499" t="n">
         <v>576760</v>
@@ -14869,7 +14869,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G500" t="n">
-        <v>2.97923874855042</v>
+        <v>2.97923898696899</v>
       </c>
       <c r="H500" t="n">
         <v>1148402</v>
@@ -14898,7 +14898,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G501" t="n">
-        <v>2.94054770469666</v>
+        <v>2.94054746627808</v>
       </c>
       <c r="H501" t="n">
         <v>933889</v>
@@ -14927,7 +14927,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G502" t="n">
-        <v>2.95851135253906</v>
+        <v>2.95851159095764</v>
       </c>
       <c r="H502" t="n">
         <v>717824</v>
@@ -14956,7 +14956,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G503" t="n">
-        <v>3.01793026924133</v>
+        <v>3.01793050765991</v>
       </c>
       <c r="H503" t="n">
         <v>748907</v>
@@ -14985,7 +14985,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G504" t="n">
-        <v>3.03174877166748</v>
+        <v>3.0317485332489</v>
       </c>
       <c r="H504" t="n">
         <v>283521</v>
@@ -15043,7 +15043,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G506" t="n">
-        <v>3.10498595237732</v>
+        <v>3.1049861907959</v>
       </c>
       <c r="H506" t="n">
         <v>709039</v>
@@ -15072,7 +15072,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G507" t="n">
-        <v>3.11051321029663</v>
+        <v>3.11051297187805</v>
       </c>
       <c r="H507" t="n">
         <v>760040</v>
@@ -15101,7 +15101,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G508" t="n">
-        <v>3.14229536056519</v>
+        <v>3.14229559898376</v>
       </c>
       <c r="H508" t="n">
         <v>516954</v>
@@ -15159,7 +15159,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G510" t="n">
-        <v>3.07182216644287</v>
+        <v>3.07182168960571</v>
       </c>
       <c r="H510" t="n">
         <v>253760</v>
@@ -15188,7 +15188,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>3.04556679725647</v>
+        <v>3.04556727409363</v>
       </c>
       <c r="H511" t="n">
         <v>278984</v>
@@ -15246,7 +15246,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G513" t="n">
-        <v>3.04556679725647</v>
+        <v>3.04556727409363</v>
       </c>
       <c r="H513" t="n">
         <v>227183</v>
@@ -15304,7 +15304,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G515" t="n">
-        <v>3.04418540000916</v>
+        <v>3.04418516159058</v>
       </c>
       <c r="H515" t="n">
         <v>485465</v>
@@ -15333,7 +15333,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G516" t="n">
-        <v>3.02760291099548</v>
+        <v>3.02760338783264</v>
       </c>
       <c r="H516" t="n">
         <v>310444</v>
@@ -15362,7 +15362,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G517" t="n">
-        <v>3.02760291099548</v>
+        <v>3.02760338783264</v>
       </c>
       <c r="H517" t="n">
         <v>648168</v>
@@ -15391,7 +15391,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G518" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H518" t="n">
         <v>854391</v>
@@ -15536,7 +15536,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931142807007</v>
       </c>
       <c r="H523" t="n">
         <v>289490</v>
@@ -15565,7 +15565,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G524" t="n">
-        <v>2.99305725097656</v>
+        <v>2.99305701255798</v>
       </c>
       <c r="H524" t="n">
         <v>1167836</v>
@@ -15652,7 +15652,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G527" t="n">
-        <v>2.91843795776367</v>
+        <v>2.91843819618225</v>
       </c>
       <c r="H527" t="n">
         <v>214673</v>
@@ -15681,7 +15681,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>2.90185570716858</v>
+        <v>2.90185594558716</v>
       </c>
       <c r="H528" t="n">
         <v>301253</v>
@@ -15710,7 +15710,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G529" t="n">
-        <v>2.91981983184814</v>
+        <v>2.91982007026672</v>
       </c>
       <c r="H529" t="n">
         <v>295775</v>
@@ -15768,7 +15768,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94331169128418</v>
+        <v>2.94331121444702</v>
       </c>
       <c r="H531" t="n">
         <v>440550</v>
@@ -15826,7 +15826,7 @@
         <v>4.25</v>
       </c>
       <c r="G533" t="n">
-        <v>2.93640184402466</v>
+        <v>2.93640208244324</v>
       </c>
       <c r="H533" t="n">
         <v>173706</v>
@@ -15855,7 +15855,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G534" t="n">
-        <v>2.87283778190613</v>
+        <v>2.87283730506897</v>
       </c>
       <c r="H534" t="n">
         <v>449592</v>
@@ -15884,7 +15884,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94607448577881</v>
+        <v>2.94607472419739</v>
       </c>
       <c r="H535" t="n">
         <v>538665</v>
@@ -15942,7 +15942,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94192934036255</v>
+        <v>2.94192910194397</v>
       </c>
       <c r="H537" t="n">
         <v>572190</v>
@@ -15971,7 +15971,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G538" t="n">
-        <v>2.94607448577881</v>
+        <v>2.94607472419739</v>
       </c>
       <c r="H538" t="n">
         <v>458621</v>
@@ -16000,7 +16000,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G539" t="n">
-        <v>2.94331169128418</v>
+        <v>2.94331121444702</v>
       </c>
       <c r="H539" t="n">
         <v>279372</v>
@@ -16058,7 +16058,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G541" t="n">
-        <v>2.9281108379364</v>
+        <v>2.92811107635498</v>
       </c>
       <c r="H541" t="n">
         <v>404056</v>
@@ -16087,7 +16087,7 @@
         <v>4.28399991989136</v>
       </c>
       <c r="G542" t="n">
-        <v>2.95989322662354</v>
+        <v>2.95989346504211</v>
       </c>
       <c r="H542" t="n">
         <v>542766</v>
@@ -16116,7 +16116,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H543" t="n">
         <v>678637</v>
@@ -16174,7 +16174,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G545" t="n">
-        <v>2.96265697479248</v>
+        <v>2.9626567363739</v>
       </c>
       <c r="H545" t="n">
         <v>512771</v>
@@ -16203,7 +16203,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G546" t="n">
-        <v>2.97371101379395</v>
+        <v>2.9737114906311</v>
       </c>
       <c r="H546" t="n">
         <v>335573</v>
@@ -16232,7 +16232,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G547" t="n">
-        <v>3.06491279602051</v>
+        <v>3.06491303443909</v>
       </c>
       <c r="H547" t="n">
         <v>681594</v>
@@ -16261,7 +16261,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G548" t="n">
-        <v>3.00134825706482</v>
+        <v>3.00134801864624</v>
       </c>
       <c r="H548" t="n">
         <v>523849</v>
@@ -16290,7 +16290,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G549" t="n">
-        <v>3.01240301132202</v>
+        <v>3.01240277290344</v>
       </c>
       <c r="H549" t="n">
         <v>187588</v>
@@ -16319,7 +16319,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G550" t="n">
-        <v>2.97232937812805</v>
+        <v>2.97232961654663</v>
       </c>
       <c r="H550" t="n">
         <v>970937</v>
@@ -16348,7 +16348,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G551" t="n">
-        <v>2.91291069984436</v>
+        <v>2.91291046142578</v>
       </c>
       <c r="H551" t="n">
         <v>668920</v>
@@ -16406,7 +16406,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>2.95712947845459</v>
+        <v>2.95712971687317</v>
       </c>
       <c r="H553" t="n">
         <v>433139</v>
@@ -16435,7 +16435,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G554" t="n">
-        <v>2.96265697479248</v>
+        <v>2.9626567363739</v>
       </c>
       <c r="H554" t="n">
         <v>220522</v>
@@ -16464,7 +16464,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G555" t="n">
-        <v>2.95298409461975</v>
+        <v>2.95298433303833</v>
       </c>
       <c r="H555" t="n">
         <v>212164</v>
@@ -16522,7 +16522,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G557" t="n">
-        <v>2.90047407150269</v>
+        <v>2.90047430992126</v>
       </c>
       <c r="H557" t="n">
         <v>1783781</v>
@@ -16551,7 +16551,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G558" t="n">
-        <v>2.89632868766785</v>
+        <v>2.89632892608643</v>
       </c>
       <c r="H558" t="n">
         <v>319927</v>
@@ -16580,7 +16580,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.85349178314209</v>
+        <v>2.85349154472351</v>
       </c>
       <c r="H559" t="n">
         <v>633026</v>
@@ -16638,7 +16638,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>2.84658217430115</v>
+        <v>2.84658241271973</v>
       </c>
       <c r="H561" t="n">
         <v>476726</v>
@@ -16696,7 +16696,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G563" t="n">
-        <v>2.76090884208679</v>
+        <v>2.76090860366821</v>
       </c>
       <c r="H563" t="n">
         <v>625996</v>
@@ -16783,7 +16783,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G566" t="n">
-        <v>2.77610898017883</v>
+        <v>2.77610874176025</v>
       </c>
       <c r="H566" t="n">
         <v>1058281</v>
@@ -16812,7 +16812,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G567" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H567" t="n">
         <v>559095</v>
@@ -16870,7 +16870,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.77749085426331</v>
+        <v>2.77749061584473</v>
       </c>
       <c r="H569" t="n">
         <v>246177</v>
@@ -16899,7 +16899,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G570" t="n">
-        <v>2.73327207565308</v>
+        <v>2.73327231407166</v>
       </c>
       <c r="H570" t="n">
         <v>306755</v>
@@ -16957,7 +16957,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G572" t="n">
-        <v>2.77749085426331</v>
+        <v>2.77749061584473</v>
       </c>
       <c r="H572" t="n">
         <v>457593</v>
@@ -16986,7 +16986,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G573" t="n">
-        <v>2.76505398750305</v>
+        <v>2.76505422592163</v>
       </c>
       <c r="H573" t="n">
         <v>274810</v>
@@ -17015,7 +17015,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>2.74985408782959</v>
+        <v>2.74985432624817</v>
       </c>
       <c r="H574" t="n">
         <v>474610</v>
@@ -17073,7 +17073,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>2.73603582382202</v>
+        <v>2.73603558540344</v>
       </c>
       <c r="H576" t="n">
         <v>219577</v>
@@ -17102,7 +17102,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G577" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H577" t="n">
         <v>253623</v>
@@ -17131,7 +17131,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G578" t="n">
-        <v>2.78716349601746</v>
+        <v>2.78716397285461</v>
       </c>
       <c r="H578" t="n">
         <v>440620</v>
@@ -17218,7 +17218,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77749085426331</v>
+        <v>2.77749061584473</v>
       </c>
       <c r="H581" t="n">
         <v>202226</v>
@@ -17247,7 +17247,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G582" t="n">
-        <v>2.74985408782959</v>
+        <v>2.74985432624817</v>
       </c>
       <c r="H582" t="n">
         <v>296696</v>
@@ -17305,7 +17305,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>2.72221732139587</v>
+        <v>2.72221755981445</v>
       </c>
       <c r="H584" t="n">
         <v>349909</v>
@@ -17334,7 +17334,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G585" t="n">
-        <v>2.75261783599854</v>
+        <v>2.75261759757996</v>
       </c>
       <c r="H585" t="n">
         <v>331776</v>
@@ -17363,7 +17363,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G586" t="n">
-        <v>2.74018120765686</v>
+        <v>2.74018144607544</v>
       </c>
       <c r="H586" t="n">
         <v>165727</v>
@@ -17421,7 +17421,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G588" t="n">
-        <v>2.73050832748413</v>
+        <v>2.73050856590271</v>
       </c>
       <c r="H588" t="n">
         <v>718141</v>
@@ -17566,7 +17566,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G593" t="n">
-        <v>2.89494705200195</v>
+        <v>2.89494681358337</v>
       </c>
       <c r="H593" t="n">
         <v>529768</v>
@@ -17595,7 +17595,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G594" t="n">
-        <v>2.87836503982544</v>
+        <v>2.87836480140686</v>
       </c>
       <c r="H594" t="n">
         <v>975352</v>
@@ -17711,7 +17711,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>2.94331169128418</v>
+        <v>2.94331121444702</v>
       </c>
       <c r="H598" t="n">
         <v>1052192</v>
@@ -17769,7 +17769,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G600" t="n">
-        <v>2.89909219741821</v>
+        <v>2.89909291267395</v>
       </c>
       <c r="H600" t="n">
         <v>744183</v>
@@ -17798,7 +17798,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>2.88527369499207</v>
+        <v>2.88527393341064</v>
       </c>
       <c r="H601" t="n">
         <v>1049953</v>
@@ -17827,7 +17827,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G602" t="n">
-        <v>2.90047407150269</v>
+        <v>2.90047430992126</v>
       </c>
       <c r="H602" t="n">
         <v>1324299</v>
@@ -17856,7 +17856,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.90876531600952</v>
+        <v>2.9087655544281</v>
       </c>
       <c r="H603" t="n">
         <v>845447</v>
@@ -17914,7 +17914,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>2.88803791999817</v>
+        <v>2.88803768157959</v>
       </c>
       <c r="H605" t="n">
         <v>796514</v>
@@ -17943,7 +17943,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G606" t="n">
-        <v>2.84796476364136</v>
+        <v>2.8479642868042</v>
       </c>
       <c r="H606" t="n">
         <v>745572</v>
@@ -17972,7 +17972,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G607" t="n">
-        <v>2.88112854957581</v>
+        <v>2.88112878799438</v>
       </c>
       <c r="H607" t="n">
         <v>674286</v>
@@ -18001,7 +18001,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G608" t="n">
-        <v>2.8590190410614</v>
+        <v>2.85901951789856</v>
       </c>
       <c r="H608" t="n">
         <v>417011</v>
@@ -18059,7 +18059,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G610" t="n">
-        <v>2.86869168281555</v>
+        <v>2.86869192123413</v>
       </c>
       <c r="H610" t="n">
         <v>802117</v>
@@ -18146,7 +18146,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>2.87421894073486</v>
+        <v>2.87421917915344</v>
       </c>
       <c r="H613" t="n">
         <v>527133</v>
@@ -18233,7 +18233,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G616" t="n">
-        <v>2.89080095291138</v>
+        <v>2.89080142974854</v>
       </c>
       <c r="H616" t="n">
         <v>255638</v>
@@ -18262,7 +18262,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G617" t="n">
-        <v>2.89632868766785</v>
+        <v>2.89632892608643</v>
       </c>
       <c r="H617" t="n">
         <v>507785</v>
@@ -18349,7 +18349,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G620" t="n">
-        <v>2.89909219741821</v>
+        <v>2.89909291267395</v>
       </c>
       <c r="H620" t="n">
         <v>492515</v>
@@ -18378,7 +18378,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G621" t="n">
-        <v>2.97509360313416</v>
+        <v>2.97509336471558</v>
       </c>
       <c r="H621" t="n">
         <v>601405</v>
@@ -18407,7 +18407,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G622" t="n">
-        <v>2.98338437080383</v>
+        <v>2.98338413238525</v>
       </c>
       <c r="H622" t="n">
         <v>557576</v>
@@ -18436,7 +18436,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G623" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H623" t="n">
         <v>220839</v>
@@ -18465,7 +18465,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G624" t="n">
-        <v>2.96265697479248</v>
+        <v>2.9626567363739</v>
       </c>
       <c r="H624" t="n">
         <v>486020</v>
@@ -18494,7 +18494,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.01931190490723</v>
+        <v>3.01931142807007</v>
       </c>
       <c r="H625" t="n">
         <v>641122</v>
@@ -18552,7 +18552,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G627" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H627" t="n">
         <v>241326</v>
@@ -18610,7 +18610,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G629" t="n">
-        <v>2.99443936347961</v>
+        <v>2.99443912506104</v>
       </c>
       <c r="H629" t="n">
         <v>363346</v>
@@ -18639,7 +18639,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G630" t="n">
-        <v>3.01240301132202</v>
+        <v>3.01240277290344</v>
       </c>
       <c r="H630" t="n">
         <v>353159</v>
@@ -18668,7 +18668,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G631" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H631" t="n">
         <v>472455</v>
@@ -18697,7 +18697,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G632" t="n">
-        <v>3.02898502349854</v>
+        <v>3.02898478507996</v>
       </c>
       <c r="H632" t="n">
         <v>518046</v>
@@ -18900,7 +18900,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>3.08287644386292</v>
+        <v>3.08287668228149</v>
       </c>
       <c r="H639" t="n">
         <v>455246</v>
@@ -19016,7 +19016,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>3.08149480819702</v>
+        <v>3.08149456977844</v>
       </c>
       <c r="H643" t="n">
         <v>293010</v>
@@ -19045,7 +19045,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G644" t="n">
-        <v>3.09669494628906</v>
+        <v>3.09669470787048</v>
       </c>
       <c r="H644" t="n">
         <v>242340</v>
@@ -19103,7 +19103,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G646" t="n">
-        <v>3.14229536056519</v>
+        <v>3.14229559898376</v>
       </c>
       <c r="H646" t="n">
         <v>601188</v>
@@ -19161,7 +19161,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G648" t="n">
-        <v>3.04694890975952</v>
+        <v>3.0469491481781</v>
       </c>
       <c r="H648" t="n">
         <v>341481</v>
@@ -19190,7 +19190,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G649" t="n">
-        <v>3.09669494628906</v>
+        <v>3.09669470787048</v>
       </c>
       <c r="H649" t="n">
         <v>458945</v>
@@ -19219,7 +19219,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12294960021973</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H650" t="n">
         <v>592680</v>
@@ -19248,7 +19248,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G651" t="n">
-        <v>3.10360479354858</v>
+        <v>3.10360455513</v>
       </c>
       <c r="H651" t="n">
         <v>725248</v>
@@ -19277,7 +19277,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G652" t="n">
-        <v>3.12709546089172</v>
+        <v>3.12709522247314</v>
       </c>
       <c r="H652" t="n">
         <v>655086</v>
@@ -19335,7 +19335,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G654" t="n">
-        <v>3.12294960021973</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H654" t="n">
         <v>440007</v>
@@ -19364,7 +19364,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G655" t="n">
-        <v>3.11742281913757</v>
+        <v>3.11742234230042</v>
       </c>
       <c r="H655" t="n">
         <v>774559</v>
@@ -19393,7 +19393,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G656" t="n">
-        <v>3.08978629112244</v>
+        <v>3.08978605270386</v>
       </c>
       <c r="H656" t="n">
         <v>451701</v>
@@ -19480,7 +19480,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G659" t="n">
-        <v>3.10498595237732</v>
+        <v>3.1049861907959</v>
       </c>
       <c r="H659" t="n">
         <v>713844</v>
@@ -19509,7 +19509,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>3.11189556121826</v>
+        <v>3.1118950843811</v>
       </c>
       <c r="H660" t="n">
         <v>464575</v>
@@ -19538,7 +19538,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>3.12294960021973</v>
+        <v>3.12294983863831</v>
       </c>
       <c r="H661" t="n">
         <v>500812</v>
@@ -19654,7 +19654,7 @@
         <v>4.5</v>
       </c>
       <c r="G665" t="n">
-        <v>3.10913133621216</v>
+        <v>3.10913157463074</v>
       </c>
       <c r="H665" t="n">
         <v>605477</v>
@@ -19683,7 +19683,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G666" t="n">
-        <v>3.10222196578979</v>
+        <v>3.10222220420837</v>
       </c>
       <c r="H666" t="n">
         <v>406879</v>
@@ -19712,7 +19712,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.10913133621216</v>
+        <v>3.10913157463074</v>
       </c>
       <c r="H667" t="n">
         <v>591269</v>
@@ -19741,7 +19741,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G668" t="n">
-        <v>3.10222196578979</v>
+        <v>3.10222220420837</v>
       </c>
       <c r="H668" t="n">
         <v>802632</v>
@@ -19770,7 +19770,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G669" t="n">
-        <v>3.26251554489136</v>
+        <v>3.26251530647278</v>
       </c>
       <c r="H669" t="n">
         <v>2348370</v>
@@ -19828,7 +19828,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>3.34542536735535</v>
+        <v>3.34542512893677</v>
       </c>
       <c r="H671" t="n">
         <v>836124</v>
@@ -19915,7 +19915,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G674" t="n">
-        <v>3.38411664962769</v>
+        <v>3.38411641120911</v>
       </c>
       <c r="H674" t="n">
         <v>577089</v>
@@ -19973,7 +19973,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G676" t="n">
-        <v>3.37997126579285</v>
+        <v>3.37997150421143</v>
       </c>
       <c r="H676" t="n">
         <v>299664</v>
@@ -20002,7 +20002,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>3.34542536735535</v>
+        <v>3.34542512893677</v>
       </c>
       <c r="H677" t="n">
         <v>220591</v>
@@ -20031,7 +20031,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G678" t="n">
-        <v>3.30535197257996</v>
+        <v>3.30535244941711</v>
       </c>
       <c r="H678" t="n">
         <v>478581</v>
@@ -20060,7 +20060,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G679" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H679" t="n">
         <v>357536</v>
@@ -20089,7 +20089,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G680" t="n">
-        <v>3.33022546768188</v>
+        <v>3.33022522926331</v>
       </c>
       <c r="H680" t="n">
         <v>395074</v>
@@ -20118,7 +20118,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G681" t="n">
-        <v>3.31502532958984</v>
+        <v>3.31502509117126</v>
       </c>
       <c r="H681" t="n">
         <v>329531</v>
@@ -20147,7 +20147,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G682" t="n">
-        <v>3.35647988319397</v>
+        <v>3.35648012161255</v>
       </c>
       <c r="H682" t="n">
         <v>547505</v>
@@ -20176,7 +20176,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G683" t="n">
-        <v>3.37858939170837</v>
+        <v>3.37858963012695</v>
       </c>
       <c r="H683" t="n">
         <v>448925</v>
@@ -20205,7 +20205,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G684" t="n">
-        <v>3.37444400787354</v>
+        <v>3.37444353103638</v>
       </c>
       <c r="H684" t="n">
         <v>470290</v>
@@ -20234,7 +20234,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G685" t="n">
-        <v>3.36615300178528</v>
+        <v>3.3661527633667</v>
       </c>
       <c r="H685" t="n">
         <v>497823</v>
@@ -20263,7 +20263,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G686" t="n">
-        <v>3.36615300178528</v>
+        <v>3.3661527633667</v>
       </c>
       <c r="H686" t="n">
         <v>412491</v>
@@ -20292,7 +20292,7 @@
         <v>4.87200021743774</v>
       </c>
       <c r="G687" t="n">
-        <v>3.36615300178528</v>
+        <v>3.3661527633667</v>
       </c>
       <c r="H687" t="n">
         <v>264276</v>
@@ -20321,7 +20321,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G688" t="n">
-        <v>3.32469773292542</v>
+        <v>3.32469749450684</v>
       </c>
       <c r="H688" t="n">
         <v>384931</v>
@@ -20379,7 +20379,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G690" t="n">
-        <v>3.29015183448792</v>
+        <v>3.29015254974365</v>
       </c>
       <c r="H690" t="n">
         <v>515539</v>
@@ -20466,7 +20466,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G693" t="n">
-        <v>3.35371661186218</v>
+        <v>3.35371685028076</v>
       </c>
       <c r="H693" t="n">
         <v>275517</v>
@@ -20495,7 +20495,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G694" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957075119019</v>
       </c>
       <c r="H694" t="n">
         <v>378541</v>
@@ -20524,7 +20524,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G695" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957075119019</v>
       </c>
       <c r="H695" t="n">
         <v>334779</v>
@@ -20582,7 +20582,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G697" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H697" t="n">
         <v>426921</v>
@@ -20611,7 +20611,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G698" t="n">
-        <v>3.34266185760498</v>
+        <v>3.3426616191864</v>
       </c>
       <c r="H698" t="n">
         <v>268858</v>
@@ -20640,7 +20640,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.32331585884094</v>
+        <v>3.32331609725952</v>
       </c>
       <c r="H699" t="n">
         <v>272666</v>
@@ -20785,7 +20785,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G704" t="n">
-        <v>3.35647988319397</v>
+        <v>3.35648012161255</v>
       </c>
       <c r="H704" t="n">
         <v>234747</v>
@@ -20814,7 +20814,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G705" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957075119019</v>
       </c>
       <c r="H705" t="n">
         <v>215533</v>
@@ -20843,7 +20843,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G706" t="n">
-        <v>3.38273525238037</v>
+        <v>3.38273501396179</v>
       </c>
       <c r="H706" t="n">
         <v>370437</v>
@@ -20872,7 +20872,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G707" t="n">
-        <v>3.34957122802734</v>
+        <v>3.34957075119019</v>
       </c>
       <c r="H707" t="n">
         <v>440703</v>
@@ -20901,7 +20901,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G708" t="n">
-        <v>3.34127998352051</v>
+        <v>3.34128022193909</v>
       </c>
       <c r="H708" t="n">
         <v>227136</v>
@@ -20930,7 +20930,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G709" t="n">
-        <v>3.33437085151672</v>
+        <v>3.3343710899353</v>
       </c>
       <c r="H709" t="n">
         <v>886827</v>
@@ -20959,7 +20959,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G710" t="n">
-        <v>3.32469773292542</v>
+        <v>3.32469749450684</v>
       </c>
       <c r="H710" t="n">
         <v>248745</v>
@@ -20988,7 +20988,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>3.38549900054932</v>
+        <v>3.38549876213074</v>
       </c>
       <c r="H711" t="n">
         <v>312454</v>
@@ -21017,7 +21017,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G712" t="n">
-        <v>3.3357527256012</v>
+        <v>3.33575248718262</v>
       </c>
       <c r="H712" t="n">
         <v>415959</v>
@@ -21075,7 +21075,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G714" t="n">
-        <v>3.37029838562012</v>
+        <v>3.3702986240387</v>
       </c>
       <c r="H714" t="n">
         <v>307384</v>
@@ -21104,7 +21104,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G715" t="n">
-        <v>3.44219732284546</v>
+        <v>3.4421968460083</v>
       </c>
       <c r="H715" t="n">
         <v>471054</v>
@@ -21191,7 +21191,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G718" t="n">
-        <v>3.46236896514893</v>
+        <v>3.4623692035675</v>
       </c>
       <c r="H718" t="n">
         <v>296407</v>
@@ -21220,7 +21220,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G719" t="n">
-        <v>3.46092844009399</v>
+        <v>3.46092820167542</v>
       </c>
       <c r="H719" t="n">
         <v>505932</v>
@@ -21249,7 +21249,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G720" t="n">
-        <v>3.48109984397888</v>
+        <v>3.48110032081604</v>
       </c>
       <c r="H720" t="n">
         <v>314563</v>
@@ -21278,7 +21278,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>3.46957325935364</v>
+        <v>3.46957302093506</v>
       </c>
       <c r="H721" t="n">
         <v>1025779</v>
@@ -21307,7 +21307,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G722" t="n">
-        <v>3.45660543441772</v>
+        <v>3.4566056728363</v>
       </c>
       <c r="H722" t="n">
         <v>697211</v>
@@ -21336,7 +21336,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G723" t="n">
-        <v>3.48109984397888</v>
+        <v>3.48110032081604</v>
       </c>
       <c r="H723" t="n">
         <v>368085</v>
@@ -21365,7 +21365,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>3.49406766891479</v>
+        <v>3.49406743049622</v>
       </c>
       <c r="H724" t="n">
         <v>1001017</v>
@@ -21423,7 +21423,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G726" t="n">
-        <v>3.57475543022156</v>
+        <v>3.57475566864014</v>
       </c>
       <c r="H726" t="n">
         <v>985537</v>
@@ -21452,7 +21452,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G727" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H727" t="n">
         <v>685720</v>
@@ -21510,7 +21510,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G729" t="n">
-        <v>3.6777765750885</v>
+        <v>3.67777681350708</v>
       </c>
       <c r="H729" t="n">
         <v>630184</v>
@@ -21539,7 +21539,7 @@
         <v>5.125</v>
       </c>
       <c r="G730" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218516349792</v>
       </c>
       <c r="H730" t="n">
         <v>660523</v>
@@ -21568,7 +21568,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65976595878601</v>
+        <v>3.65976572036743</v>
       </c>
       <c r="H731" t="n">
         <v>458971</v>
@@ -21626,7 +21626,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659327507019</v>
       </c>
       <c r="H733" t="n">
         <v>827997</v>
@@ -21713,7 +21713,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G736" t="n">
-        <v>3.68137860298157</v>
+        <v>3.68137812614441</v>
       </c>
       <c r="H736" t="n">
         <v>430174</v>
@@ -21742,7 +21742,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>3.63094902038574</v>
+        <v>3.63094854354858</v>
       </c>
       <c r="H737" t="n">
         <v>602362</v>
@@ -21800,7 +21800,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G739" t="n">
-        <v>3.68498039245605</v>
+        <v>3.68498086929321</v>
       </c>
       <c r="H739" t="n">
         <v>2546011</v>
@@ -21829,7 +21829,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>3.68858289718628</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H740" t="n">
         <v>394292</v>
@@ -21858,7 +21858,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G741" t="n">
-        <v>3.62374472618103</v>
+        <v>3.62374496459961</v>
       </c>
       <c r="H741" t="n">
         <v>214957</v>
@@ -21887,7 +21887,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G742" t="n">
-        <v>3.58484148979187</v>
+        <v>3.58484101295471</v>
       </c>
       <c r="H742" t="n">
         <v>346299</v>
@@ -21945,7 +21945,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G744" t="n">
-        <v>3.59492754936218</v>
+        <v>3.5949273109436</v>
       </c>
       <c r="H744" t="n">
         <v>517127</v>
@@ -22032,7 +22032,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G747" t="n">
-        <v>3.60573363304138</v>
+        <v>3.60573387145996</v>
       </c>
       <c r="H747" t="n">
         <v>607759</v>
@@ -22061,7 +22061,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G748" t="n">
-        <v>3.59924960136414</v>
+        <v>3.59924983978271</v>
       </c>
       <c r="H748" t="n">
         <v>415115</v>
@@ -22090,7 +22090,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G749" t="n">
-        <v>3.57619643211365</v>
+        <v>3.57619667053223</v>
       </c>
       <c r="H749" t="n">
         <v>582111</v>
@@ -22148,7 +22148,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G751" t="n">
-        <v>3.58051896095276</v>
+        <v>3.58051872253418</v>
       </c>
       <c r="H751" t="n">
         <v>386818</v>
@@ -22177,7 +22177,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G752" t="n">
-        <v>3.60933613777161</v>
+        <v>3.60933589935303</v>
       </c>
       <c r="H752" t="n">
         <v>272384</v>
@@ -22206,7 +22206,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.62014222145081</v>
+        <v>3.62014245986938</v>
       </c>
       <c r="H753" t="n">
         <v>353573</v>
@@ -22264,7 +22264,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G755" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H755" t="n">
         <v>308092</v>
@@ -22380,7 +22380,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>3.60573363304138</v>
+        <v>3.60573387145996</v>
       </c>
       <c r="H759" t="n">
         <v>333042</v>
@@ -22409,7 +22409,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H760" t="n">
         <v>144620</v>
@@ -22438,7 +22438,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G761" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H761" t="n">
         <v>140253</v>
@@ -22467,7 +22467,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G762" t="n">
-        <v>3.60573363304138</v>
+        <v>3.60573387145996</v>
       </c>
       <c r="H762" t="n">
         <v>233504</v>
@@ -22496,7 +22496,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57187461853027</v>
+        <v>3.57187390327454</v>
       </c>
       <c r="H763" t="n">
         <v>525060</v>
@@ -22525,7 +22525,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G764" t="n">
-        <v>3.57907795906067</v>
+        <v>3.57907819747925</v>
       </c>
       <c r="H764" t="n">
         <v>136835</v>
@@ -22554,7 +22554,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G765" t="n">
-        <v>3.57907795906067</v>
+        <v>3.57907819747925</v>
       </c>
       <c r="H765" t="n">
         <v>363470</v>
@@ -22583,7 +22583,7 @@
         <v>4.96400022506714</v>
       </c>
       <c r="G766" t="n">
-        <v>3.57619643211365</v>
+        <v>3.57619667053223</v>
       </c>
       <c r="H766" t="n">
         <v>852645</v>
@@ -22612,7 +22612,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G767" t="n">
-        <v>3.59060502052307</v>
+        <v>3.59060454368591</v>
       </c>
       <c r="H767" t="n">
         <v>593676</v>
@@ -22641,7 +22641,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G768" t="n">
-        <v>3.62374472618103</v>
+        <v>3.62374496459961</v>
       </c>
       <c r="H768" t="n">
         <v>430153</v>
@@ -22670,7 +22670,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G769" t="n">
-        <v>3.60069108009338</v>
+        <v>3.6006908416748</v>
       </c>
       <c r="H769" t="n">
         <v>241517</v>
@@ -22699,7 +22699,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.56611061096191</v>
+        <v>3.56611037254333</v>
       </c>
       <c r="H770" t="n">
         <v>220728</v>
@@ -22728,7 +22728,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G771" t="n">
-        <v>3.57907795906067</v>
+        <v>3.57907819747925</v>
       </c>
       <c r="H771" t="n">
         <v>473966</v>
@@ -22786,7 +22786,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>3.71019577980042</v>
+        <v>3.71019625663757</v>
       </c>
       <c r="H773" t="n">
         <v>318698</v>
@@ -22844,7 +22844,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G775" t="n">
-        <v>3.66697025299072</v>
+        <v>3.66697001457214</v>
       </c>
       <c r="H775" t="n">
         <v>116327</v>
@@ -22873,7 +22873,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G776" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659327507019</v>
       </c>
       <c r="H776" t="n">
         <v>535968</v>
@@ -22902,7 +22902,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G777" t="n">
-        <v>3.70659351348877</v>
+        <v>3.70659327507019</v>
       </c>
       <c r="H777" t="n">
         <v>394359</v>
@@ -22931,7 +22931,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G778" t="n">
-        <v>3.6777765750885</v>
+        <v>3.67777681350708</v>
       </c>
       <c r="H778" t="n">
         <v>510087</v>
@@ -22960,7 +22960,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H779" t="n">
         <v>537475</v>
@@ -22989,7 +22989,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.72460460662842</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H780" t="n">
         <v>198706</v>
@@ -23018,7 +23018,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>3.76782965660095</v>
+        <v>3.76783013343811</v>
       </c>
       <c r="H781" t="n">
         <v>213433</v>
@@ -23047,7 +23047,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G782" t="n">
-        <v>3.75702357292175</v>
+        <v>3.75702333450317</v>
       </c>
       <c r="H782" t="n">
         <v>152644</v>
@@ -23134,7 +23134,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G785" t="n">
-        <v>3.77503347396851</v>
+        <v>3.77503371238708</v>
       </c>
       <c r="H785" t="n">
         <v>221413</v>
@@ -23163,7 +23163,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G786" t="n">
-        <v>3.73901271820068</v>
+        <v>3.73901295661926</v>
       </c>
       <c r="H786" t="n">
         <v>268804</v>
@@ -23192,7 +23192,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G787" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H787" t="n">
         <v>298424</v>
@@ -23250,7 +23250,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>3.72100210189819</v>
+        <v>3.72100186347961</v>
       </c>
       <c r="H789" t="n">
         <v>115274</v>
@@ -23279,7 +23279,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G790" t="n">
-        <v>3.68858289718628</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H790" t="n">
         <v>402408</v>
@@ -23308,7 +23308,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>3.72100210189819</v>
+        <v>3.72100186347961</v>
       </c>
       <c r="H791" t="n">
         <v>202767</v>
@@ -23395,7 +23395,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G794" t="n">
-        <v>3.67417407035828</v>
+        <v>3.67417454719543</v>
       </c>
       <c r="H794" t="n">
         <v>251245</v>
@@ -23424,7 +23424,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.64175486564636</v>
+        <v>3.6417555809021</v>
       </c>
       <c r="H795" t="n">
         <v>413188</v>
@@ -23453,7 +23453,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>3.62014222145081</v>
+        <v>3.62014245986938</v>
       </c>
       <c r="H796" t="n">
         <v>385770</v>
@@ -23482,7 +23482,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>3.71019577980042</v>
+        <v>3.71019625663757</v>
       </c>
       <c r="H797" t="n">
         <v>879092</v>
@@ -23511,7 +23511,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.68858289718628</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H798" t="n">
         <v>166019</v>
@@ -23540,7 +23540,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>3.6777765750885</v>
+        <v>3.67777681350708</v>
       </c>
       <c r="H799" t="n">
         <v>119947</v>
@@ -23569,7 +23569,7 @@
         <v>5.125</v>
       </c>
       <c r="G800" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218516349792</v>
       </c>
       <c r="H800" t="n">
         <v>156322</v>
@@ -23598,7 +23598,7 @@
         <v>5.125</v>
       </c>
       <c r="G801" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218516349792</v>
       </c>
       <c r="H801" t="n">
         <v>257011</v>
@@ -23627,7 +23627,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G802" t="n">
-        <v>3.6777765750885</v>
+        <v>3.67777681350708</v>
       </c>
       <c r="H802" t="n">
         <v>357933</v>
@@ -23656,7 +23656,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>3.66697025299072</v>
+        <v>3.66697001457214</v>
       </c>
       <c r="H803" t="n">
         <v>178529</v>
@@ -23685,7 +23685,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.67417407035828</v>
+        <v>3.67417454719543</v>
       </c>
       <c r="H804" t="n">
         <v>184382</v>
@@ -23714,7 +23714,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G805" t="n">
-        <v>3.69578719139099</v>
+        <v>3.69578766822815</v>
       </c>
       <c r="H805" t="n">
         <v>390641</v>
@@ -23772,7 +23772,7 @@
         <v>5.125</v>
       </c>
       <c r="G807" t="n">
-        <v>3.69218492507935</v>
+        <v>3.69218516349792</v>
       </c>
       <c r="H807" t="n">
         <v>331891</v>
@@ -23830,7 +23830,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H809" t="n">
         <v>629355</v>
@@ -23859,7 +23859,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>3.7354109287262</v>
+        <v>3.73541045188904</v>
       </c>
       <c r="H810" t="n">
         <v>395323</v>
@@ -23888,7 +23888,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G811" t="n">
-        <v>3.71019577980042</v>
+        <v>3.71019625663757</v>
       </c>
       <c r="H811" t="n">
         <v>326971</v>
@@ -23917,7 +23917,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>3.68858289718628</v>
+        <v>3.6885826587677</v>
       </c>
       <c r="H812" t="n">
         <v>198291</v>
@@ -23946,7 +23946,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H813" t="n">
         <v>202688</v>
@@ -23975,7 +23975,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H814" t="n">
         <v>370664</v>
@@ -24004,7 +24004,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G815" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H815" t="n">
         <v>312178</v>
@@ -24033,7 +24033,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G816" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H816" t="n">
         <v>225018</v>
@@ -24062,7 +24062,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H817" t="n">
         <v>140668</v>
@@ -24091,7 +24091,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>3.74621677398682</v>
+        <v>3.7462170124054</v>
       </c>
       <c r="H818" t="n">
         <v>255505</v>
@@ -24120,7 +24120,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342106819153</v>
       </c>
       <c r="H819" t="n">
         <v>228708</v>
@@ -24149,7 +24149,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>3.74981880187988</v>
+        <v>3.74981904029846</v>
       </c>
       <c r="H820" t="n">
         <v>270294</v>
@@ -24178,7 +24178,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>3.75702357292175</v>
+        <v>3.75702333450317</v>
       </c>
       <c r="H821" t="n">
         <v>217419</v>
@@ -24207,7 +24207,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>3.73901271820068</v>
+        <v>3.73901295661926</v>
       </c>
       <c r="H822" t="n">
         <v>211229</v>
@@ -24236,7 +24236,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>3.76782965660095</v>
+        <v>3.76783013343811</v>
       </c>
       <c r="H823" t="n">
         <v>438530</v>
@@ -24265,7 +24265,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>3.72460460662842</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H824" t="n">
         <v>343423</v>
@@ -24294,7 +24294,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342106819153</v>
       </c>
       <c r="H825" t="n">
         <v>242523</v>
@@ -24323,7 +24323,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G826" t="n">
-        <v>3.68137860298157</v>
+        <v>3.68137812614441</v>
       </c>
       <c r="H826" t="n">
         <v>229614</v>
@@ -24352,7 +24352,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G827" t="n">
-        <v>3.69938969612122</v>
+        <v>3.69938921928406</v>
       </c>
       <c r="H827" t="n">
         <v>236994</v>
@@ -24410,7 +24410,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>3.72460460662842</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H829" t="n">
         <v>248488</v>
@@ -24439,7 +24439,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G830" t="n">
-        <v>3.73180794715881</v>
+        <v>3.73180842399597</v>
       </c>
       <c r="H830" t="n">
         <v>177186</v>
@@ -24468,7 +24468,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>3.72460460662842</v>
+        <v>3.72460389137268</v>
       </c>
       <c r="H831" t="n">
         <v>204215</v>
@@ -24497,7 +24497,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G832" t="n">
-        <v>3.76062536239624</v>
+        <v>3.76062560081482</v>
       </c>
       <c r="H832" t="n">
         <v>268201</v>
@@ -24526,7 +24526,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G833" t="n">
-        <v>3.78584027290344</v>
+        <v>3.78584051132202</v>
       </c>
       <c r="H833" t="n">
         <v>158358</v>
@@ -24555,7 +24555,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G834" t="n">
-        <v>3.79304432868958</v>
+        <v>3.79304480552673</v>
       </c>
       <c r="H834" t="n">
         <v>288604</v>
@@ -24584,7 +24584,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>3.82546424865723</v>
+        <v>3.82546377182007</v>
       </c>
       <c r="H835" t="n">
         <v>526098</v>
@@ -24642,7 +24642,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>3.75342154502869</v>
+        <v>3.75342106819153</v>
       </c>
       <c r="H837" t="n">
         <v>261649</v>
@@ -24671,7 +24671,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>3.77503347396851</v>
+        <v>3.77503371238708</v>
       </c>
       <c r="H838" t="n">
         <v>184338</v>
@@ -24729,7 +24729,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G840" t="n">
-        <v>3.78584027290344</v>
+        <v>3.78584051132202</v>
       </c>
       <c r="H840" t="n">
         <v>309517</v>
@@ -24816,7 +24816,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G843" t="n">
-        <v>3.86148500442505</v>
+        <v>3.86148548126221</v>
       </c>
       <c r="H843" t="n">
         <v>518806</v>
@@ -24845,7 +24845,7 @@
         <v>5.375</v>
       </c>
       <c r="G844" t="n">
-        <v>3.87229156494141</v>
+        <v>3.87229108810425</v>
       </c>
       <c r="H844" t="n">
         <v>150028</v>
@@ -24874,7 +24874,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.82186126708984</v>
+        <v>3.821861743927</v>
       </c>
       <c r="H845" t="n">
         <v>210214</v>
@@ -24903,7 +24903,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664659500122</v>
       </c>
       <c r="H846" t="n">
         <v>882140</v>
@@ -24932,7 +24932,7 @@
         <v>5.25</v>
       </c>
       <c r="G847" t="n">
-        <v>3.78223848342896</v>
+        <v>3.78223896026611</v>
       </c>
       <c r="H847" t="n">
         <v>330835</v>
@@ -24990,7 +24990,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G849" t="n">
-        <v>3.78944277763367</v>
+        <v>3.78944301605225</v>
       </c>
       <c r="H849" t="n">
         <v>309778</v>
@@ -25048,7 +25048,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>3.82906603813171</v>
+        <v>3.82906556129456</v>
       </c>
       <c r="H851" t="n">
         <v>1005431</v>
@@ -25164,7 +25164,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664659500122</v>
       </c>
       <c r="H855" t="n">
         <v>531608</v>
@@ -25222,7 +25222,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G857" t="n">
-        <v>3.80385136604309</v>
+        <v>3.80385088920593</v>
       </c>
       <c r="H857" t="n">
         <v>236744</v>
@@ -25280,7 +25280,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.85067892074585</v>
+        <v>3.85067844390869</v>
       </c>
       <c r="H859" t="n">
         <v>429041</v>
@@ -25338,7 +25338,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>3.84707641601562</v>
+        <v>3.84707689285278</v>
       </c>
       <c r="H861" t="n">
         <v>142215</v>
@@ -25396,7 +25396,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G863" t="n">
-        <v>3.81105518341064</v>
+        <v>3.8110556602478</v>
       </c>
       <c r="H863" t="n">
         <v>841113</v>
@@ -25425,7 +25425,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>3.79664707183838</v>
+        <v>3.79664659500122</v>
       </c>
       <c r="H864" t="n">
         <v>272878</v>
@@ -25483,7 +25483,7 @@
         <v>5.375</v>
       </c>
       <c r="G866" t="n">
-        <v>3.87229156494141</v>
+        <v>3.87229108810425</v>
       </c>
       <c r="H866" t="n">
         <v>334082</v>
@@ -25512,7 +25512,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>3.90831351280212</v>
+        <v>3.90831303596497</v>
       </c>
       <c r="H867" t="n">
         <v>679193</v>
@@ -25570,7 +25570,7 @@
         <v>5.375</v>
       </c>
       <c r="G869" t="n">
-        <v>3.87229156494141</v>
+        <v>3.87229108810425</v>
       </c>
       <c r="H869" t="n">
         <v>307691</v>
@@ -25599,7 +25599,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.88309741020203</v>
+        <v>3.88309788703918</v>
       </c>
       <c r="H870" t="n">
         <v>376869</v>
@@ -25657,7 +25657,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91191530227661</v>
+        <v>3.91191482543945</v>
       </c>
       <c r="H872" t="n">
         <v>627265</v>
@@ -25773,7 +25773,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G876" t="n">
-        <v>3.91191530227661</v>
+        <v>3.91191482543945</v>
       </c>
       <c r="H876" t="n">
         <v>933919</v>
@@ -25802,7 +25802,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91191530227661</v>
+        <v>3.91191482543945</v>
       </c>
       <c r="H877" t="n">
         <v>497300</v>
@@ -25831,7 +25831,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G878" t="n">
-        <v>3.92632341384888</v>
+        <v>3.92632293701172</v>
       </c>
       <c r="H878" t="n">
         <v>368905</v>
@@ -25889,7 +25889,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99836659431458</v>
+        <v>3.99836611747742</v>
       </c>
       <c r="H880" t="n">
         <v>518932</v>
@@ -25947,7 +25947,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>4.01997852325439</v>
+        <v>4.01997947692871</v>
       </c>
       <c r="H882" t="n">
         <v>458370</v>
@@ -26034,7 +26034,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G885" t="n">
-        <v>4.06680679321289</v>
+        <v>4.06680631637573</v>
       </c>
       <c r="H885" t="n">
         <v>226888</v>
@@ -26063,7 +26063,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>4.08841896057129</v>
+        <v>4.08841943740845</v>
       </c>
       <c r="H886" t="n">
         <v>668689</v>
@@ -26121,7 +26121,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>4.21809577941895</v>
+        <v>4.21809530258179</v>
       </c>
       <c r="H888" t="n">
         <v>1316501</v>
@@ -26150,7 +26150,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18567752838135</v>
+        <v>4.18567705154419</v>
       </c>
       <c r="H889" t="n">
         <v>1255135</v>
@@ -26295,7 +26295,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.21089172363281</v>
+        <v>4.21089220046997</v>
       </c>
       <c r="H894" t="n">
         <v>582523</v>
@@ -26382,7 +26382,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>4.29013919830322</v>
+        <v>4.29013872146606</v>
       </c>
       <c r="H897" t="n">
         <v>461627</v>
@@ -26411,7 +26411,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G898" t="n">
-        <v>4.31895589828491</v>
+        <v>4.31895637512207</v>
       </c>
       <c r="H898" t="n">
         <v>927247</v>
@@ -26440,7 +26440,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G899" t="n">
-        <v>4.31175184249878</v>
+        <v>4.31175136566162</v>
       </c>
       <c r="H899" t="n">
         <v>306181</v>
@@ -26469,7 +26469,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>4.29374074935913</v>
+        <v>4.29374122619629</v>
       </c>
       <c r="H900" t="n">
         <v>741766</v>
@@ -26498,7 +26498,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>4.26492404937744</v>
+        <v>4.2649245262146</v>
       </c>
       <c r="H901" t="n">
         <v>804635</v>
@@ -26527,7 +26527,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>4.29374074935913</v>
+        <v>4.29374122619629</v>
       </c>
       <c r="H902" t="n">
         <v>663557</v>
@@ -26556,7 +26556,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G903" t="n">
-        <v>4.32616090774536</v>
+        <v>4.3261604309082</v>
       </c>
       <c r="H903" t="n">
         <v>982085</v>
@@ -26643,7 +26643,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G906" t="n">
-        <v>4.42702054977417</v>
+        <v>4.42701959609985</v>
       </c>
       <c r="H906" t="n">
         <v>303177</v>
@@ -26701,7 +26701,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>4.35497760772705</v>
+        <v>4.35497713088989</v>
       </c>
       <c r="H908" t="n">
         <v>758622</v>
@@ -26730,7 +26730,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>4.18567752838135</v>
+        <v>4.18567705154419</v>
       </c>
       <c r="H909" t="n">
         <v>1255336</v>
@@ -26875,7 +26875,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G914" t="n">
-        <v>3.71019577980042</v>
+        <v>3.71019625663757</v>
       </c>
       <c r="H914" t="n">
         <v>2989353</v>
@@ -27020,7 +27020,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G919" t="n">
-        <v>3.33413290977478</v>
+        <v>3.33413314819336</v>
       </c>
       <c r="H919" t="n">
         <v>2052459</v>
@@ -27049,7 +27049,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G920" t="n">
-        <v>3.24624133110046</v>
+        <v>3.24624109268188</v>
       </c>
       <c r="H920" t="n">
         <v>847418</v>
@@ -27107,7 +27107,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H922" t="n">
         <v>2073810</v>
@@ -27281,7 +27281,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G928" t="n">
-        <v>2.52437376976013</v>
+        <v>2.52437400817871</v>
       </c>
       <c r="H928" t="n">
         <v>823310</v>
@@ -27310,7 +27310,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G929" t="n">
-        <v>2.45809459686279</v>
+        <v>2.45809483528137</v>
       </c>
       <c r="H929" t="n">
         <v>1450159</v>
@@ -27397,7 +27397,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G932" t="n">
-        <v>2.87306022644043</v>
+        <v>2.87306046485901</v>
       </c>
       <c r="H932" t="n">
         <v>845367</v>
@@ -27484,7 +27484,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G935" t="n">
-        <v>2.89035058021545</v>
+        <v>2.89035081863403</v>
       </c>
       <c r="H935" t="n">
         <v>943520</v>
@@ -27513,7 +27513,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G936" t="n">
-        <v>2.83127570152283</v>
+        <v>2.83127593994141</v>
       </c>
       <c r="H936" t="n">
         <v>874334</v>
@@ -27600,7 +27600,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G939" t="n">
-        <v>2.89035058021545</v>
+        <v>2.89035081863403</v>
       </c>
       <c r="H939" t="n">
         <v>639112</v>
@@ -27629,7 +27629,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96815657615662</v>
+        <v>2.96815633773804</v>
       </c>
       <c r="H940" t="n">
         <v>1265202</v>
@@ -27687,7 +27687,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G942" t="n">
-        <v>3.02579069137573</v>
+        <v>3.02579045295715</v>
       </c>
       <c r="H942" t="n">
         <v>878459</v>
@@ -27716,7 +27716,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G943" t="n">
-        <v>3.02579069137573</v>
+        <v>3.02579045295715</v>
       </c>
       <c r="H943" t="n">
         <v>717288</v>
@@ -27745,7 +27745,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G944" t="n">
-        <v>2.94798445701599</v>
+        <v>2.94798469543457</v>
       </c>
       <c r="H944" t="n">
         <v>974453</v>
@@ -27832,7 +27832,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G947" t="n">
-        <v>2.9494252204895</v>
+        <v>2.94942545890808</v>
       </c>
       <c r="H947" t="n">
         <v>765074</v>
@@ -27919,7 +27919,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G950" t="n">
-        <v>2.91772699356079</v>
+        <v>2.91772675514221</v>
       </c>
       <c r="H950" t="n">
         <v>718280</v>
@@ -27948,7 +27948,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.91052198410034</v>
+        <v>2.91052222251892</v>
       </c>
       <c r="H951" t="n">
         <v>231048</v>
@@ -28006,7 +28006,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G953" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H953" t="n">
         <v>525699</v>
@@ -28122,7 +28122,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G957" t="n">
-        <v>2.85577011108398</v>
+        <v>2.85576987266541</v>
       </c>
       <c r="H957" t="n">
         <v>405808</v>
@@ -28238,7 +28238,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G961" t="n">
-        <v>2.79525446891785</v>
+        <v>2.79525423049927</v>
       </c>
       <c r="H961" t="n">
         <v>226234</v>
@@ -28296,7 +28296,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G963" t="n">
-        <v>2.78228688240051</v>
+        <v>2.78228640556335</v>
       </c>
       <c r="H963" t="n">
         <v>329641</v>
@@ -28325,7 +28325,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G964" t="n">
-        <v>2.75346946716309</v>
+        <v>2.75346970558167</v>
       </c>
       <c r="H964" t="n">
         <v>407303</v>
@@ -28383,7 +28383,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G966" t="n">
-        <v>3.02434945106506</v>
+        <v>3.02434992790222</v>
       </c>
       <c r="H966" t="n">
         <v>586431</v>
@@ -28412,7 +28412,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G967" t="n">
-        <v>2.95230722427368</v>
+        <v>2.9523069858551</v>
       </c>
       <c r="H967" t="n">
         <v>775973</v>
@@ -28441,7 +28441,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G968" t="n">
-        <v>2.95662999153137</v>
+        <v>2.95662975311279</v>
       </c>
       <c r="H968" t="n">
         <v>809737</v>
@@ -28499,7 +28499,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G970" t="n">
-        <v>2.99553298950195</v>
+        <v>2.99553251266479</v>
       </c>
       <c r="H970" t="n">
         <v>1758990</v>
@@ -28528,7 +28528,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G971" t="n">
-        <v>3.04969906806946</v>
+        <v>3.04969882965088</v>
       </c>
       <c r="H971" t="n">
         <v>839198</v>
@@ -28557,7 +28557,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G972" t="n">
-        <v>3.12404465675354</v>
+        <v>3.12404489517212</v>
       </c>
       <c r="H972" t="n">
         <v>1072358</v>
@@ -28731,7 +28731,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G978" t="n">
-        <v>3.36984157562256</v>
+        <v>3.36984133720398</v>
       </c>
       <c r="H978" t="n">
         <v>1837773</v>
@@ -28760,7 +28760,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G979" t="n">
-        <v>3.46694612503052</v>
+        <v>3.46694660186768</v>
       </c>
       <c r="H979" t="n">
         <v>1270556</v>
@@ -28789,7 +28789,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G980" t="n">
-        <v>3.44722199440002</v>
+        <v>3.44722247123718</v>
       </c>
       <c r="H980" t="n">
         <v>2133114</v>
@@ -28818,7 +28818,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.33797955513</v>
+        <v>3.33797907829285</v>
       </c>
       <c r="H981" t="n">
         <v>1863975</v>
@@ -28876,7 +28876,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G983" t="n">
-        <v>3.18625283241272</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H983" t="n">
         <v>1121954</v>
@@ -28905,7 +28905,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G984" t="n">
-        <v>3.12404465675354</v>
+        <v>3.12404489517212</v>
       </c>
       <c r="H984" t="n">
         <v>1636453</v>
@@ -28934,7 +28934,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G985" t="n">
-        <v>3.13921761512756</v>
+        <v>3.13921785354614</v>
       </c>
       <c r="H985" t="n">
         <v>1200608</v>
@@ -28963,7 +28963,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G986" t="n">
-        <v>3.1255624294281</v>
+        <v>3.12556219100952</v>
       </c>
       <c r="H986" t="n">
         <v>593457</v>
@@ -28992,7 +28992,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G987" t="n">
-        <v>3.15287303924561</v>
+        <v>3.15287327766418</v>
       </c>
       <c r="H987" t="n">
         <v>849857</v>
@@ -29050,7 +29050,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>3.13466596603394</v>
+        <v>3.13466572761536</v>
       </c>
       <c r="H989" t="n">
         <v>410573</v>
@@ -29166,7 +29166,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G993" t="n">
-        <v>3.01631927490234</v>
+        <v>3.01631951332092</v>
       </c>
       <c r="H993" t="n">
         <v>608831</v>
@@ -29195,7 +29195,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G994" t="n">
-        <v>2.98900866508484</v>
+        <v>2.98900842666626</v>
       </c>
       <c r="H994" t="n">
         <v>490566</v>
@@ -29224,7 +29224,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G995" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H995" t="n">
         <v>568790</v>
@@ -29253,7 +29253,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G996" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H996" t="n">
         <v>335015</v>
@@ -29311,7 +29311,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G998" t="n">
-        <v>3.07245826721191</v>
+        <v>3.07245802879333</v>
       </c>
       <c r="H998" t="n">
         <v>615615</v>
@@ -29340,7 +29340,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G999" t="n">
-        <v>3.10583758354187</v>
+        <v>3.10583782196045</v>
       </c>
       <c r="H999" t="n">
         <v>786692</v>
@@ -29369,7 +29369,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1000" t="n">
         <v>344826</v>
@@ -29398,7 +29398,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.17714953422546</v>
+        <v>3.17714929580688</v>
       </c>
       <c r="H1001" t="n">
         <v>500947</v>
@@ -29427,7 +29427,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.19080424308777</v>
+        <v>3.19080448150635</v>
       </c>
       <c r="H1002" t="n">
         <v>891668</v>
@@ -29456,7 +29456,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.11949324607849</v>
+        <v>3.11949300765991</v>
       </c>
       <c r="H1003" t="n">
         <v>520443</v>
@@ -29485,7 +29485,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.04059529304504</v>
+        <v>3.04059553146362</v>
       </c>
       <c r="H1004" t="n">
         <v>584857</v>
@@ -29572,7 +29572,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210922241211</v>
       </c>
       <c r="H1007" t="n">
         <v>2396617</v>
@@ -29601,7 +29601,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.81604027748108</v>
+        <v>2.81604051589966</v>
       </c>
       <c r="H1008" t="n">
         <v>1731107</v>
@@ -29630,7 +29630,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.81604027748108</v>
+        <v>2.81604051589966</v>
       </c>
       <c r="H1009" t="n">
         <v>1353365</v>
@@ -29688,7 +29688,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.741694688797</v>
+        <v>2.74169445037842</v>
       </c>
       <c r="H1011" t="n">
         <v>1279412</v>
@@ -29804,7 +29804,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.67038321495056</v>
+        <v>2.67038345336914</v>
       </c>
       <c r="H1015" t="n">
         <v>720352</v>
@@ -29949,7 +29949,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.62941741943359</v>
+        <v>2.62941718101501</v>
       </c>
       <c r="H1020" t="n">
         <v>742850</v>
@@ -29978,7 +29978,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.64610719680786</v>
+        <v>2.64610695838928</v>
       </c>
       <c r="H1021" t="n">
         <v>439971</v>
@@ -30094,7 +30094,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.76597094535828</v>
+        <v>2.7659707069397</v>
       </c>
       <c r="H1025" t="n">
         <v>968819</v>
@@ -30123,7 +30123,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1026" t="n">
         <v>442819</v>
@@ -30210,7 +30210,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.89645552635193</v>
+        <v>2.89645576477051</v>
       </c>
       <c r="H1029" t="n">
         <v>1068446</v>
@@ -30239,7 +30239,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.83424758911133</v>
+        <v>2.83424782752991</v>
       </c>
       <c r="H1030" t="n">
         <v>690968</v>
@@ -30297,7 +30297,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.73107385635376</v>
+        <v>2.73107361793518</v>
       </c>
       <c r="H1032" t="n">
         <v>649276</v>
@@ -30326,7 +30326,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.73714303970337</v>
+        <v>2.73714280128479</v>
       </c>
       <c r="H1033" t="n">
         <v>425341</v>
@@ -30355,7 +30355,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.73107385635376</v>
+        <v>2.73107361793518</v>
       </c>
       <c r="H1034" t="n">
         <v>719237</v>
@@ -30384,7 +30384,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1035" t="n">
         <v>648955</v>
@@ -30500,7 +30500,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.73714303970337</v>
+        <v>2.73714280128479</v>
       </c>
       <c r="H1039" t="n">
         <v>786436</v>
@@ -30558,7 +30558,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.67038321495056</v>
+        <v>2.67038345336914</v>
       </c>
       <c r="H1041" t="n">
         <v>686287</v>
@@ -30674,7 +30674,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.67190074920654</v>
+        <v>2.67190051078796</v>
       </c>
       <c r="H1045" t="n">
         <v>696676</v>
@@ -31022,7 +31022,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.55658841133118</v>
+        <v>2.55658864974976</v>
       </c>
       <c r="H1057" t="n">
         <v>603020</v>
@@ -31138,7 +31138,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.55051946640015</v>
+        <v>2.55051970481873</v>
       </c>
       <c r="H1061" t="n">
         <v>420030</v>
@@ -31254,7 +31254,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.3866548538208</v>
+        <v>2.38665509223938</v>
       </c>
       <c r="H1065" t="n">
         <v>769602</v>
@@ -31283,7 +31283,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.36844754219055</v>
+        <v>2.36844801902771</v>
       </c>
       <c r="H1066" t="n">
         <v>904125</v>
@@ -31312,7 +31312,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.47769093513489</v>
+        <v>2.47769069671631</v>
       </c>
       <c r="H1067" t="n">
         <v>1137561</v>
@@ -31370,7 +31370,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.43520760536194</v>
+        <v>2.43520736694336</v>
       </c>
       <c r="H1069" t="n">
         <v>605908</v>
@@ -31399,7 +31399,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.44734597206116</v>
+        <v>2.44734573364258</v>
       </c>
       <c r="H1070" t="n">
         <v>553996</v>
@@ -31457,7 +31457,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.45038032531738</v>
+        <v>2.4503800868988</v>
       </c>
       <c r="H1072" t="n">
         <v>540458</v>
@@ -31544,7 +31544,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.40637946128845</v>
+        <v>2.40637969970703</v>
       </c>
       <c r="H1075" t="n">
         <v>559400</v>
@@ -31573,7 +31573,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.40334486961365</v>
+        <v>2.40334510803223</v>
       </c>
       <c r="H1076" t="n">
         <v>570991</v>
@@ -31747,7 +31747,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.24858403205872</v>
+        <v>2.24858427047729</v>
       </c>
       <c r="H1082" t="n">
         <v>995249</v>
@@ -31834,7 +31834,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.26072216033936</v>
+        <v>2.26072239875793</v>
       </c>
       <c r="H1085" t="n">
         <v>923284</v>
@@ -31863,7 +31863,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.35327506065369</v>
+        <v>2.35327482223511</v>
       </c>
       <c r="H1086" t="n">
         <v>597211</v>
@@ -31921,7 +31921,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.37603425979614</v>
+        <v>2.37603402137756</v>
       </c>
       <c r="H1088" t="n">
         <v>749371</v>
@@ -32037,7 +32037,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210922241211</v>
       </c>
       <c r="H1092" t="n">
         <v>1364511</v>
@@ -32066,7 +32066,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.78569531440735</v>
+        <v>2.78569507598877</v>
       </c>
       <c r="H1093" t="n">
         <v>1101842</v>
@@ -32124,7 +32124,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.7432119846344</v>
+        <v>2.74321174621582</v>
       </c>
       <c r="H1095" t="n">
         <v>457898</v>
@@ -32182,7 +32182,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.97687029838562</v>
+        <v>2.9768705368042</v>
       </c>
       <c r="H1097" t="n">
         <v>1619676</v>
@@ -32211,7 +32211,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.94045615196228</v>
+        <v>2.9404559135437</v>
       </c>
       <c r="H1098" t="n">
         <v>1870774</v>
@@ -32327,7 +32327,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.98900866508484</v>
+        <v>2.98900842666626</v>
       </c>
       <c r="H1102" t="n">
         <v>1029441</v>
@@ -32443,7 +32443,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1106" t="n">
         <v>1402040</v>
@@ -32559,7 +32559,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.8327305316925</v>
+        <v>2.83273029327393</v>
       </c>
       <c r="H1110" t="n">
         <v>390191</v>
@@ -32588,7 +32588,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.79935050010681</v>
+        <v>2.79935073852539</v>
       </c>
       <c r="H1111" t="n">
         <v>531696</v>
@@ -32617,7 +32617,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1112" t="n">
         <v>343500</v>
@@ -32646,7 +32646,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.77962636947632</v>
+        <v>2.77962613105774</v>
       </c>
       <c r="H1113" t="n">
         <v>500943</v>
@@ -32762,7 +32762,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.8281786441803</v>
+        <v>2.82817840576172</v>
       </c>
       <c r="H1117" t="n">
         <v>699859</v>
@@ -32791,7 +32791,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.8327305316925</v>
+        <v>2.83273029327393</v>
       </c>
       <c r="H1118" t="n">
         <v>903623</v>
@@ -32849,7 +32849,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.69921135902405</v>
+        <v>2.69921112060547</v>
       </c>
       <c r="H1120" t="n">
         <v>1351121</v>
@@ -33139,7 +33139,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.73107385635376</v>
+        <v>2.73107361793518</v>
       </c>
       <c r="H1130" t="n">
         <v>750648</v>
@@ -33168,7 +33168,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.73865985870361</v>
+        <v>2.73866009712219</v>
       </c>
       <c r="H1131" t="n">
         <v>621804</v>
@@ -33197,7 +33197,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.73107385635376</v>
+        <v>2.73107361793518</v>
       </c>
       <c r="H1132" t="n">
         <v>550634</v>
@@ -33284,7 +33284,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.72045302391052</v>
+        <v>2.72045278549194</v>
       </c>
       <c r="H1135" t="n">
         <v>354515</v>
@@ -33371,7 +33371,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.73714303970337</v>
+        <v>2.73714280128479</v>
       </c>
       <c r="H1138" t="n">
         <v>434683</v>
@@ -33429,7 +33429,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.6794867515564</v>
+        <v>2.67948698997498</v>
       </c>
       <c r="H1140" t="n">
         <v>725495</v>
@@ -33487,7 +33487,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.55051946640015</v>
+        <v>2.55051970481873</v>
       </c>
       <c r="H1142" t="n">
         <v>912227</v>
@@ -33545,7 +33545,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.60362362861633</v>
+        <v>2.60362339019775</v>
       </c>
       <c r="H1144" t="n">
         <v>785344</v>
@@ -33806,7 +33806,7 @@
         <v>3.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.84486865997314</v>
+        <v>2.84486842155457</v>
       </c>
       <c r="H1153" t="n">
         <v>806021</v>
@@ -33893,7 +33893,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.8281786441803</v>
+        <v>2.82817840576172</v>
       </c>
       <c r="H1156" t="n">
         <v>1242794</v>
@@ -33980,7 +33980,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.87521386146545</v>
+        <v>2.87521409988403</v>
       </c>
       <c r="H1159" t="n">
         <v>329197</v>
@@ -34009,7 +34009,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728241920471</v>
       </c>
       <c r="H1160" t="n">
         <v>1375070</v>
@@ -34038,7 +34038,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728241920471</v>
       </c>
       <c r="H1161" t="n">
         <v>929022</v>
@@ -34096,7 +34096,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.11949324607849</v>
+        <v>3.11949300765991</v>
       </c>
       <c r="H1163" t="n">
         <v>2064828</v>
@@ -34183,7 +34183,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.02997493743896</v>
+        <v>3.02997469902039</v>
       </c>
       <c r="H1166" t="n">
         <v>761418</v>
@@ -34241,7 +34241,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.01783657073975</v>
+        <v>3.01783633232117</v>
       </c>
       <c r="H1168" t="n">
         <v>829113</v>
@@ -34299,7 +34299,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.96624946594238</v>
+        <v>2.96624970436096</v>
       </c>
       <c r="H1170" t="n">
         <v>774545</v>
@@ -34386,7 +34386,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1173" t="n">
         <v>1864436</v>
@@ -34415,7 +34415,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.3000476360321</v>
+        <v>3.30004739761353</v>
       </c>
       <c r="H1174" t="n">
         <v>1347515</v>
@@ -34444,7 +34444,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.31825494766235</v>
+        <v>3.3182544708252</v>
       </c>
       <c r="H1175" t="n">
         <v>1017835</v>
@@ -34647,7 +34647,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.18321847915649</v>
+        <v>3.18321871757507</v>
       </c>
       <c r="H1182" t="n">
         <v>635502</v>
@@ -34705,7 +34705,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.16804575920105</v>
+        <v>3.16804552078247</v>
       </c>
       <c r="H1184" t="n">
         <v>742349</v>
@@ -34734,7 +34734,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.18625283241272</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1185" t="n">
         <v>456650</v>
@@ -34792,7 +34792,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.18321847915649</v>
+        <v>3.18321871757507</v>
       </c>
       <c r="H1187" t="n">
         <v>316805</v>
@@ -34821,7 +34821,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.17714953422546</v>
+        <v>3.17714929580688</v>
       </c>
       <c r="H1188" t="n">
         <v>664798</v>
@@ -34879,7 +34879,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.20142507553101</v>
+        <v>3.20142531394958</v>
       </c>
       <c r="H1190" t="n">
         <v>941312</v>
@@ -34937,7 +34937,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.1725971698761</v>
+        <v>3.17259740829468</v>
       </c>
       <c r="H1192" t="n">
         <v>860479</v>
@@ -34966,7 +34966,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.1255624294281</v>
+        <v>3.12556219100952</v>
       </c>
       <c r="H1193" t="n">
         <v>683853</v>
@@ -35024,7 +35024,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.10735487937927</v>
+        <v>3.10735511779785</v>
       </c>
       <c r="H1195" t="n">
         <v>478326</v>
@@ -35111,7 +35111,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.01935386657715</v>
+        <v>3.01935410499573</v>
       </c>
       <c r="H1198" t="n">
         <v>1026278</v>
@@ -35169,7 +35169,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.02542281150818</v>
+        <v>3.02542304992676</v>
       </c>
       <c r="H1200" t="n">
         <v>906035</v>
@@ -35227,7 +35227,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1202" t="n">
         <v>1535372</v>
@@ -35343,7 +35343,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.92224907875061</v>
+        <v>2.92224884033203</v>
       </c>
       <c r="H1206" t="n">
         <v>662631</v>
@@ -35430,7 +35430,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1209" t="n">
         <v>740997</v>
@@ -35488,7 +35488,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.94500780105591</v>
+        <v>2.94500803947449</v>
       </c>
       <c r="H1211" t="n">
         <v>993107</v>
@@ -35604,7 +35604,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.96776700019836</v>
+        <v>2.96776676177979</v>
       </c>
       <c r="H1215" t="n">
         <v>677275</v>
@@ -35633,7 +35633,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.92983531951904</v>
+        <v>2.92983508110046</v>
       </c>
       <c r="H1216" t="n">
         <v>737122</v>
@@ -35691,7 +35691,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.89645552635193</v>
+        <v>2.89645576477051</v>
       </c>
       <c r="H1218" t="n">
         <v>1266372</v>
@@ -35749,7 +35749,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.91011118888855</v>
+        <v>2.91011095046997</v>
       </c>
       <c r="H1220" t="n">
         <v>1296831</v>
@@ -35778,7 +35778,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.89645552635193</v>
+        <v>2.89645576477051</v>
       </c>
       <c r="H1221" t="n">
         <v>1820089</v>
@@ -35807,7 +35807,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.88279986381531</v>
+        <v>2.88280010223389</v>
       </c>
       <c r="H1222" t="n">
         <v>1397317</v>
@@ -35894,7 +35894,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.88279986381531</v>
+        <v>2.88280010223389</v>
       </c>
       <c r="H1225" t="n">
         <v>905427</v>
@@ -35981,7 +35981,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728241920471</v>
       </c>
       <c r="H1228" t="n">
         <v>1071557</v>
@@ -36010,7 +36010,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.89797282218933</v>
+        <v>2.89797258377075</v>
       </c>
       <c r="H1229" t="n">
         <v>1754855</v>
@@ -36126,7 +36126,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.06638884544373</v>
+        <v>3.06638860702515</v>
       </c>
       <c r="H1233" t="n">
         <v>1932001</v>
@@ -36213,7 +36213,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.07094049453735</v>
+        <v>3.07094073295593</v>
       </c>
       <c r="H1236" t="n">
         <v>1307866</v>
@@ -36358,7 +36358,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.16804575920105</v>
+        <v>3.16804552078247</v>
       </c>
       <c r="H1241" t="n">
         <v>1460048</v>
@@ -36590,7 +36590,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.01935386657715</v>
+        <v>3.01935410499573</v>
       </c>
       <c r="H1249" t="n">
         <v>606038</v>
@@ -36677,7 +36677,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.88279986381531</v>
+        <v>2.88280010223389</v>
       </c>
       <c r="H1252" t="n">
         <v>1133314</v>
@@ -36706,7 +36706,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.89645552635193</v>
+        <v>2.89645576477051</v>
       </c>
       <c r="H1253" t="n">
         <v>985545</v>
@@ -36822,7 +36822,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.91011118888855</v>
+        <v>2.91011095046997</v>
       </c>
       <c r="H1257" t="n">
         <v>559808</v>
@@ -36851,7 +36851,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.87066173553467</v>
+        <v>2.87066149711609</v>
       </c>
       <c r="H1258" t="n">
         <v>731494</v>
@@ -36880,7 +36880,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.89493799209595</v>
+        <v>2.89493823051453</v>
       </c>
       <c r="H1259" t="n">
         <v>393668</v>
@@ -36909,7 +36909,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.88279986381531</v>
+        <v>2.88280010223389</v>
       </c>
       <c r="H1260" t="n">
         <v>515873</v>
@@ -36967,7 +36967,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.85093760490417</v>
+        <v>2.8509373664856</v>
       </c>
       <c r="H1262" t="n">
         <v>559507</v>
@@ -37141,7 +37141,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.87066173553467</v>
+        <v>2.87066149711609</v>
       </c>
       <c r="H1268" t="n">
         <v>420158</v>
@@ -37199,7 +37199,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.91011118888855</v>
+        <v>2.91011095046997</v>
       </c>
       <c r="H1270" t="n">
         <v>446474</v>
@@ -37315,7 +37315,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.95866346359253</v>
+        <v>2.95866322517395</v>
       </c>
       <c r="H1274" t="n">
         <v>482145</v>
@@ -37344,7 +37344,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.98900866508484</v>
+        <v>2.98900842666626</v>
       </c>
       <c r="H1275" t="n">
         <v>337586</v>
@@ -37373,7 +37373,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.88583445549011</v>
+        <v>2.88583469390869</v>
       </c>
       <c r="H1276" t="n">
         <v>961401</v>
@@ -37402,7 +37402,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.80845427513123</v>
+        <v>2.80845403671265</v>
       </c>
       <c r="H1277" t="n">
         <v>2406305</v>
@@ -37489,7 +37489,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.87066173553467</v>
+        <v>2.87066149711609</v>
       </c>
       <c r="H1280" t="n">
         <v>380270</v>
@@ -37518,7 +37518,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.87066173553467</v>
+        <v>2.87066149711609</v>
       </c>
       <c r="H1281" t="n">
         <v>293660</v>
@@ -37605,7 +37605,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.88128304481506</v>
+        <v>2.88128280639648</v>
       </c>
       <c r="H1284" t="n">
         <v>547091</v>
@@ -37663,7 +37663,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.7932813167572</v>
+        <v>2.79328155517578</v>
       </c>
       <c r="H1286" t="n">
         <v>1137489</v>
@@ -37692,7 +37692,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.80845427513123</v>
+        <v>2.80845403671265</v>
       </c>
       <c r="H1287" t="n">
         <v>751635</v>
@@ -37721,7 +37721,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1288" t="n">
         <v>603892</v>
@@ -37779,7 +37779,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.81907486915588</v>
+        <v>2.81907510757446</v>
       </c>
       <c r="H1290" t="n">
         <v>1188135</v>
@@ -37837,7 +37837,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.80845427513123</v>
+        <v>2.80845403671265</v>
       </c>
       <c r="H1292" t="n">
         <v>333025</v>
@@ -37866,7 +37866,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.79176425933838</v>
+        <v>2.79176449775696</v>
       </c>
       <c r="H1293" t="n">
         <v>277477</v>
@@ -37924,7 +37924,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210922241211</v>
       </c>
       <c r="H1295" t="n">
         <v>392380</v>
@@ -38011,7 +38011,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210922241211</v>
       </c>
       <c r="H1298" t="n">
         <v>289927</v>
@@ -38098,7 +38098,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.741694688797</v>
+        <v>2.74169445037842</v>
       </c>
       <c r="H1301" t="n">
         <v>650684</v>
@@ -38214,7 +38214,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.7947986125946</v>
+        <v>2.79479885101318</v>
       </c>
       <c r="H1305" t="n">
         <v>555953</v>
@@ -38243,7 +38243,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.78872966766357</v>
+        <v>2.78872990608215</v>
       </c>
       <c r="H1306" t="n">
         <v>1331307</v>
@@ -38446,7 +38446,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.95714569091797</v>
+        <v>2.95714592933655</v>
       </c>
       <c r="H1313" t="n">
         <v>907238</v>
@@ -38562,7 +38562,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.07094049453735</v>
+        <v>3.07094073295593</v>
       </c>
       <c r="H1317" t="n">
         <v>676463</v>
@@ -38591,7 +38591,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.07094049453735</v>
+        <v>3.07094073295593</v>
       </c>
       <c r="H1318" t="n">
         <v>751918</v>
@@ -38707,7 +38707,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.02997493743896</v>
+        <v>3.02997469902039</v>
       </c>
       <c r="H1322" t="n">
         <v>728288</v>
@@ -38736,7 +38736,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.04666423797607</v>
+        <v>3.04666447639465</v>
       </c>
       <c r="H1323" t="n">
         <v>376389</v>
@@ -38823,7 +38823,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.02997493743896</v>
+        <v>3.02997469902039</v>
       </c>
       <c r="H1326" t="n">
         <v>245581</v>
@@ -38852,7 +38852,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480174064636</v>
       </c>
       <c r="H1327" t="n">
         <v>237191</v>
@@ -38968,7 +38968,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.03300929069519</v>
+        <v>3.03300905227661</v>
       </c>
       <c r="H1331" t="n">
         <v>337172</v>
@@ -39026,7 +39026,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.97990465164185</v>
+        <v>2.97990489006042</v>
       </c>
       <c r="H1333" t="n">
         <v>233108</v>
@@ -39113,7 +39113,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.96624946594238</v>
+        <v>2.96624970436096</v>
       </c>
       <c r="H1336" t="n">
         <v>591694</v>
@@ -39171,7 +39171,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.91011118888855</v>
+        <v>2.91011095046997</v>
       </c>
       <c r="H1338" t="n">
         <v>445579</v>
@@ -39200,7 +39200,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.87521386146545</v>
+        <v>2.87521409988403</v>
       </c>
       <c r="H1339" t="n">
         <v>499459</v>
@@ -39229,7 +39229,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.92073154449463</v>
+        <v>2.92073178291321</v>
       </c>
       <c r="H1340" t="n">
         <v>362090</v>
@@ -39287,7 +39287,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.01631927490234</v>
+        <v>3.01631951332092</v>
       </c>
       <c r="H1342" t="n">
         <v>772547</v>
@@ -39316,7 +39316,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.15287303924561</v>
+        <v>3.15287327766418</v>
       </c>
       <c r="H1343" t="n">
         <v>5050376</v>
@@ -39345,7 +39345,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.2378396987915</v>
+        <v>3.23783993721008</v>
       </c>
       <c r="H1344" t="n">
         <v>1846837</v>
@@ -39403,7 +39403,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.1725971698761</v>
+        <v>3.17259740829468</v>
       </c>
       <c r="H1346" t="n">
         <v>919731</v>
@@ -39432,7 +39432,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.16349387168884</v>
+        <v>3.16349411010742</v>
       </c>
       <c r="H1347" t="n">
         <v>632047</v>
@@ -39461,7 +39461,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.15439009666443</v>
+        <v>3.15438985824585</v>
       </c>
       <c r="H1348" t="n">
         <v>596551</v>
@@ -39490,7 +39490,7 @@
         <v>4.21400022506714</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.19687366485596</v>
+        <v>3.19687342643738</v>
       </c>
       <c r="H1349" t="n">
         <v>1067726</v>
@@ -39548,7 +39548,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.19080424308777</v>
+        <v>3.19080448150635</v>
       </c>
       <c r="H1351" t="n">
         <v>684309</v>
@@ -39606,7 +39606,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1353" t="n">
         <v>563496</v>
@@ -39635,7 +39635,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.99659466743469</v>
+        <v>2.99659490585327</v>
       </c>
       <c r="H1354" t="n">
         <v>805425</v>
@@ -39693,7 +39693,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.94652533531189</v>
+        <v>2.94652509689331</v>
       </c>
       <c r="H1356" t="n">
         <v>628394</v>
@@ -39722,7 +39722,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.95714569091797</v>
+        <v>2.95714592933655</v>
       </c>
       <c r="H1357" t="n">
         <v>517977</v>
@@ -39809,7 +39809,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.81907486915588</v>
+        <v>2.81907510757446</v>
       </c>
       <c r="H1360" t="n">
         <v>956603</v>
@@ -39838,7 +39838,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.77810883522034</v>
+        <v>2.77810907363892</v>
       </c>
       <c r="H1361" t="n">
         <v>1161975</v>
@@ -39896,7 +39896,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1363" t="n">
-        <v>2.80845427513123</v>
+        <v>2.80845403671265</v>
       </c>
       <c r="H1363" t="n">
         <v>709578</v>
@@ -39925,7 +39925,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>2.83424758911133</v>
+        <v>2.83424782752991</v>
       </c>
       <c r="H1364" t="n">
         <v>518021</v>
@@ -39954,7 +39954,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.92073154449463</v>
+        <v>2.92073178291321</v>
       </c>
       <c r="H1365" t="n">
         <v>640710</v>
@@ -40041,7 +40041,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1368" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728241920471</v>
       </c>
       <c r="H1368" t="n">
         <v>509622</v>
@@ -40099,7 +40099,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1370" t="n">
-        <v>2.79935050010681</v>
+        <v>2.79935073852539</v>
       </c>
       <c r="H1370" t="n">
         <v>319342</v>
@@ -40128,7 +40128,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.84942030906677</v>
+        <v>2.84942007064819</v>
       </c>
       <c r="H1371" t="n">
         <v>746231</v>
@@ -40157,7 +40157,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210922241211</v>
       </c>
       <c r="H1372" t="n">
         <v>249851</v>
@@ -40186,7 +40186,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G1373" t="n">
-        <v>2.85852384567261</v>
+        <v>2.85852408409119</v>
       </c>
       <c r="H1373" t="n">
         <v>349137</v>
@@ -40215,7 +40215,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.89190363883972</v>
+        <v>2.89190340042114</v>
       </c>
       <c r="H1374" t="n">
         <v>317269</v>
@@ -40273,7 +40273,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>2.91314554214478</v>
+        <v>2.9131453037262</v>
       </c>
       <c r="H1376" t="n">
         <v>508884</v>
@@ -40360,7 +40360,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1379" t="n">
-        <v>2.95866346359253</v>
+        <v>2.95866322517395</v>
       </c>
       <c r="H1379" t="n">
         <v>218394</v>
@@ -40534,7 +40534,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.10583758354187</v>
+        <v>3.10583782196045</v>
       </c>
       <c r="H1385" t="n">
         <v>352308</v>
@@ -40563,7 +40563,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.11949324607849</v>
+        <v>3.11949300765991</v>
       </c>
       <c r="H1386" t="n">
         <v>667580</v>
@@ -40592,7 +40592,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.10583758354187</v>
+        <v>3.10583782196045</v>
       </c>
       <c r="H1387" t="n">
         <v>339953</v>
@@ -40650,7 +40650,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.1255624294281</v>
+        <v>3.12556219100952</v>
       </c>
       <c r="H1389" t="n">
         <v>563771</v>
@@ -40737,7 +40737,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.15287303924561</v>
+        <v>3.15287327766418</v>
       </c>
       <c r="H1392" t="n">
         <v>600781</v>
@@ -40766,7 +40766,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1393" t="n">
         <v>343828</v>
@@ -41027,7 +41027,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.07094049453735</v>
+        <v>3.07094073295593</v>
       </c>
       <c r="H1402" t="n">
         <v>347185</v>
@@ -41085,7 +41085,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.15590739250183</v>
+        <v>3.15590715408325</v>
       </c>
       <c r="H1404" t="n">
         <v>368125</v>
@@ -41114,7 +41114,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.09976863861084</v>
+        <v>3.09976887702942</v>
       </c>
       <c r="H1405" t="n">
         <v>316695</v>
@@ -41172,7 +41172,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.06487131118774</v>
+        <v>3.06487154960632</v>
       </c>
       <c r="H1407" t="n">
         <v>357189</v>
@@ -41201,7 +41201,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.95259428024292</v>
+        <v>2.95259404182434</v>
       </c>
       <c r="H1408" t="n">
         <v>1114048</v>
@@ -41230,7 +41230,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1409" t="n">
-        <v>3.02997493743896</v>
+        <v>3.02997469902039</v>
       </c>
       <c r="H1409" t="n">
         <v>664173</v>
@@ -41259,7 +41259,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.15590739250183</v>
+        <v>3.15590715408325</v>
       </c>
       <c r="H1410" t="n">
         <v>993535</v>
@@ -41317,7 +41317,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1412" t="n">
         <v>433525</v>
@@ -41346,7 +41346,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.08156132698059</v>
+        <v>3.08156156539917</v>
       </c>
       <c r="H1413" t="n">
         <v>1369822</v>
@@ -41404,7 +41404,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.15439009666443</v>
+        <v>3.15438985824585</v>
       </c>
       <c r="H1415" t="n">
         <v>333250</v>
@@ -41433,7 +41433,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1483211517334</v>
+        <v>3.14832139015198</v>
       </c>
       <c r="H1416" t="n">
         <v>319129</v>
@@ -41491,7 +41491,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.07852697372437</v>
+        <v>3.07852721214294</v>
       </c>
       <c r="H1418" t="n">
         <v>298915</v>
@@ -41520,7 +41520,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.11494135856628</v>
+        <v>3.11494112014771</v>
       </c>
       <c r="H1419" t="n">
         <v>546906</v>
@@ -41578,7 +41578,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.03604388237</v>
+        <v>3.03604364395142</v>
       </c>
       <c r="H1421" t="n">
         <v>1087442</v>
@@ -41607,7 +41607,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.10735487937927</v>
+        <v>3.10735511779785</v>
       </c>
       <c r="H1422" t="n">
         <v>919096</v>
@@ -41636,7 +41636,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.11494135856628</v>
+        <v>3.11494112014771</v>
       </c>
       <c r="H1423" t="n">
         <v>472374</v>
@@ -41665,7 +41665,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.00569844245911</v>
+        <v>3.00569820404053</v>
       </c>
       <c r="H1424" t="n">
         <v>811906</v>
@@ -41694,7 +41694,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.01631927490234</v>
+        <v>3.01631951332092</v>
       </c>
       <c r="H1425" t="n">
         <v>626343</v>
@@ -41752,7 +41752,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.77507424354553</v>
+        <v>2.77507448196411</v>
       </c>
       <c r="H1427" t="n">
         <v>790685</v>
@@ -41897,7 +41897,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.94500780105591</v>
+        <v>2.94500803947449</v>
       </c>
       <c r="H1432" t="n">
         <v>631432</v>
@@ -41926,7 +41926,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.97687029838562</v>
+        <v>2.9768705368042</v>
       </c>
       <c r="H1433" t="n">
         <v>454366</v>
@@ -41955,7 +41955,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.01631927490234</v>
+        <v>3.01631951332092</v>
       </c>
       <c r="H1434" t="n">
         <v>670259</v>
@@ -41984,7 +41984,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.04969906806946</v>
+        <v>3.04969882965088</v>
       </c>
       <c r="H1435" t="n">
         <v>593290</v>
@@ -42071,7 +42071,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480174064636</v>
       </c>
       <c r="H1438" t="n">
         <v>336601</v>
@@ -42100,7 +42100,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576777458191</v>
       </c>
       <c r="H1439" t="n">
         <v>331126</v>
@@ -42129,7 +42129,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.04818201065063</v>
+        <v>3.04818177223206</v>
       </c>
       <c r="H1440" t="n">
         <v>387125</v>
@@ -42158,7 +42158,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576777458191</v>
       </c>
       <c r="H1441" t="n">
         <v>366787</v>
@@ -42245,7 +42245,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.13011360168457</v>
+        <v>3.13011384010315</v>
       </c>
       <c r="H1444" t="n">
         <v>542482</v>
@@ -42303,7 +42303,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.18625283241272</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1446" t="n">
         <v>1656008</v>
@@ -42506,7 +42506,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.40929055213928</v>
+        <v>3.40929079055786</v>
       </c>
       <c r="H1453" t="n">
         <v>761354</v>
@@ -42564,7 +42564,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.41535973548889</v>
+        <v>3.41535902023315</v>
       </c>
       <c r="H1455" t="n">
         <v>502197</v>
@@ -42622,7 +42622,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.56556844711304</v>
+        <v>3.56556820869446</v>
       </c>
       <c r="H1457" t="n">
         <v>669265</v>
@@ -42651,7 +42651,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.56556844711304</v>
+        <v>3.56556820869446</v>
       </c>
       <c r="H1458" t="n">
         <v>425019</v>
@@ -42680,7 +42680,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.41991114616394</v>
+        <v>3.41991138458252</v>
       </c>
       <c r="H1459" t="n">
         <v>599042</v>
@@ -42709,7 +42709,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.36225533485413</v>
+        <v>3.36225509643555</v>
       </c>
       <c r="H1460" t="n">
         <v>1645239</v>
@@ -42767,7 +42767,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.37591028213501</v>
+        <v>3.37591075897217</v>
       </c>
       <c r="H1462" t="n">
         <v>412208</v>
@@ -42796,7 +42796,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.33797955513</v>
+        <v>3.33797907829285</v>
       </c>
       <c r="H1463" t="n">
         <v>285885</v>
@@ -42883,7 +42883,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.31066799163818</v>
+        <v>3.31066823005676</v>
       </c>
       <c r="H1466" t="n">
         <v>319646</v>
@@ -42941,7 +42941,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.35466885566711</v>
+        <v>3.35466909408569</v>
       </c>
       <c r="H1468" t="n">
         <v>357288</v>
@@ -42970,7 +42970,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.36984157562256</v>
+        <v>3.36984133720398</v>
       </c>
       <c r="H1469" t="n">
         <v>293364</v>
@@ -43086,7 +43086,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.29094338417053</v>
+        <v>3.29094362258911</v>
       </c>
       <c r="H1473" t="n">
         <v>390507</v>
@@ -43115,7 +43115,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.15742492675781</v>
+        <v>3.15742468833923</v>
       </c>
       <c r="H1474" t="n">
         <v>569682</v>
@@ -43202,7 +43202,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.27880597114563</v>
+        <v>3.27880573272705</v>
       </c>
       <c r="H1477" t="n">
         <v>313515</v>
@@ -43231,7 +43231,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.26666808128357</v>
+        <v>3.26666784286499</v>
       </c>
       <c r="H1478" t="n">
         <v>317207</v>
@@ -43289,7 +43289,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.25452971458435</v>
+        <v>3.25452947616577</v>
       </c>
       <c r="H1480" t="n">
         <v>227378</v>
@@ -43376,7 +43376,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.23177099227905</v>
+        <v>3.23177075386047</v>
       </c>
       <c r="H1483" t="n">
         <v>228707</v>
@@ -43463,7 +43463,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.3000476360321</v>
+        <v>3.30004739761353</v>
       </c>
       <c r="H1486" t="n">
         <v>471587</v>
@@ -43492,7 +43492,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.26666808128357</v>
+        <v>3.26666784286499</v>
       </c>
       <c r="H1487" t="n">
         <v>389756</v>
@@ -43521,7 +43521,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.2590811252594</v>
+        <v>3.25908136367798</v>
       </c>
       <c r="H1488" t="n">
         <v>173956</v>
@@ -43550,7 +43550,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.25149488449097</v>
+        <v>3.25149464607239</v>
       </c>
       <c r="H1489" t="n">
         <v>79380</v>
@@ -43579,7 +43579,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1490" t="n">
         <v>164422</v>
@@ -43608,7 +43608,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.30308198928833</v>
+        <v>3.30308222770691</v>
       </c>
       <c r="H1491" t="n">
         <v>317705</v>
@@ -43666,7 +43666,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24087429046631</v>
+        <v>3.24087405204773</v>
       </c>
       <c r="H1493" t="n">
         <v>230814</v>
@@ -43695,7 +43695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.18625283241272</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1494" t="n">
         <v>518313</v>
@@ -43724,7 +43724,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.06638884544373</v>
+        <v>3.06638860702515</v>
       </c>
       <c r="H1495" t="n">
         <v>608019</v>
@@ -43753,7 +43753,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.95562863349915</v>
+        <v>2.95562887191772</v>
       </c>
       <c r="H1496" t="n">
         <v>320216</v>
@@ -43782,7 +43782,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.93893885612488</v>
+        <v>2.93893909454346</v>
       </c>
       <c r="H1497" t="n">
         <v>394520</v>
@@ -43840,7 +43840,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.99811196327209</v>
+        <v>2.99811220169067</v>
       </c>
       <c r="H1499" t="n">
         <v>533885</v>
@@ -43869,7 +43869,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.05576801300049</v>
+        <v>3.05576777458191</v>
       </c>
       <c r="H1500" t="n">
         <v>328315</v>
@@ -43985,7 +43985,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.07549238204956</v>
+        <v>3.07549214363098</v>
       </c>
       <c r="H1504" t="n">
         <v>214319</v>
@@ -44101,7 +44101,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.07852697372437</v>
+        <v>3.07852721214294</v>
       </c>
       <c r="H1508" t="n">
         <v>181143</v>
@@ -44130,7 +44130,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.02390575408936</v>
+        <v>3.02390551567078</v>
       </c>
       <c r="H1509" t="n">
         <v>408312</v>
@@ -44159,7 +44159,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.02542281150818</v>
+        <v>3.02542304992676</v>
       </c>
       <c r="H1510" t="n">
         <v>125926</v>
@@ -44275,7 +44275,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.01480197906494</v>
+        <v>3.01480174064636</v>
       </c>
       <c r="H1514" t="n">
         <v>243119</v>
@@ -44304,7 +44304,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.03300929069519</v>
+        <v>3.03300905227661</v>
       </c>
       <c r="H1515" t="n">
         <v>189223</v>
@@ -44391,7 +44391,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.04969906806946</v>
+        <v>3.04969882965088</v>
       </c>
       <c r="H1518" t="n">
         <v>105502</v>
@@ -44507,7 +44507,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.19383907318115</v>
+        <v>3.19383931159973</v>
       </c>
       <c r="H1522" t="n">
         <v>253011</v>
@@ -44565,7 +44565,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.10583758354187</v>
+        <v>3.10583782196045</v>
       </c>
       <c r="H1524" t="n">
         <v>273886</v>
@@ -44623,7 +44623,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1526" t="n">
         <v>227220</v>
@@ -44652,7 +44652,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.18928742408752</v>
+        <v>3.18928718566895</v>
       </c>
       <c r="H1527" t="n">
         <v>216398</v>
@@ -44681,7 +44681,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.16956257820129</v>
+        <v>3.16956281661987</v>
       </c>
       <c r="H1528" t="n">
         <v>115488</v>
@@ -44710,7 +44710,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.18625283241272</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1529" t="n">
         <v>156797</v>
@@ -44768,7 +44768,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.22570133209229</v>
+        <v>3.22570157051086</v>
       </c>
       <c r="H1531" t="n">
         <v>181014</v>
@@ -44797,7 +44797,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.23480534553528</v>
+        <v>3.2348051071167</v>
       </c>
       <c r="H1532" t="n">
         <v>196107</v>
@@ -44826,7 +44826,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.31977200508118</v>
+        <v>3.3197717666626</v>
       </c>
       <c r="H1533" t="n">
         <v>379962</v>
@@ -44884,7 +44884,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.25756406784058</v>
+        <v>3.25756430625916</v>
       </c>
       <c r="H1535" t="n">
         <v>278442</v>
@@ -44913,7 +44913,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.28790950775146</v>
+        <v>3.28790926933289</v>
       </c>
       <c r="H1536" t="n">
         <v>422360</v>
@@ -44942,7 +44942,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.23177099227905</v>
+        <v>3.23177075386047</v>
       </c>
       <c r="H1537" t="n">
         <v>343058</v>
@@ -45029,7 +45029,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.22570133209229</v>
+        <v>3.22570157051086</v>
       </c>
       <c r="H1540" t="n">
         <v>79916</v>
@@ -45058,7 +45058,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.2378396987915</v>
+        <v>3.23783993721008</v>
       </c>
       <c r="H1541" t="n">
         <v>181142</v>
@@ -45087,7 +45087,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1542" t="n">
         <v>119327</v>
@@ -45116,7 +45116,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.21052885055542</v>
+        <v>3.21052861213684</v>
       </c>
       <c r="H1543" t="n">
         <v>44780</v>
@@ -45145,7 +45145,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.2090117931366</v>
+        <v>3.20901155471802</v>
       </c>
       <c r="H1544" t="n">
         <v>146185</v>
@@ -45290,7 +45290,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.15287303924561</v>
+        <v>3.15287327766418</v>
       </c>
       <c r="H1549" t="n">
         <v>97630</v>
@@ -45348,7 +45348,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.1255624294281</v>
+        <v>3.12556219100952</v>
       </c>
       <c r="H1551" t="n">
         <v>95083</v>
@@ -45464,7 +45464,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.04818201065063</v>
+        <v>3.04818177223206</v>
       </c>
       <c r="H1555" t="n">
         <v>65866</v>
@@ -45551,7 +45551,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.14376950263977</v>
+        <v>3.14376902580261</v>
       </c>
       <c r="H1558" t="n">
         <v>185411</v>
@@ -45580,7 +45580,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.18625283241272</v>
+        <v>3.18625259399414</v>
       </c>
       <c r="H1559" t="n">
         <v>310762</v>
@@ -45754,7 +45754,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.13466596603394</v>
+        <v>3.13466572761536</v>
       </c>
       <c r="H1565" t="n">
         <v>177784</v>
@@ -45841,7 +45841,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1568" t="n">
-        <v>2.95866346359253</v>
+        <v>2.95866322517395</v>
       </c>
       <c r="H1568" t="n">
         <v>301425</v>
@@ -45870,7 +45870,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728241920471</v>
       </c>
       <c r="H1569" t="n">
         <v>271414</v>
@@ -45986,7 +45986,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.73865985870361</v>
+        <v>2.73866009712219</v>
       </c>
       <c r="H1573" t="n">
         <v>294443</v>
@@ -46015,7 +46015,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.83728218078613</v>
+        <v>2.83728241920471</v>
       </c>
       <c r="H1574" t="n">
         <v>506701</v>
@@ -46073,7 +46073,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.91314554214478</v>
+        <v>2.9131453037262</v>
       </c>
       <c r="H1576" t="n">
         <v>146290</v>
@@ -46102,7 +46102,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.81604027748108</v>
+        <v>2.81604051589966</v>
       </c>
       <c r="H1577" t="n">
         <v>291608</v>
@@ -46131,7 +46131,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.78569531440735</v>
+        <v>2.78569507598877</v>
       </c>
       <c r="H1578" t="n">
         <v>222101</v>
@@ -46160,7 +46160,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.79935050010681</v>
+        <v>2.79935073852539</v>
       </c>
       <c r="H1579" t="n">
         <v>175350</v>
@@ -46189,7 +46189,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.79935050010681</v>
+        <v>2.79935073852539</v>
       </c>
       <c r="H1580" t="n">
         <v>242347</v>
@@ -46334,7 +46334,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.82210946083069</v>
+        <v>2.82210922241211</v>
       </c>
       <c r="H1585" t="n">
         <v>140503</v>
@@ -46450,7 +46450,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.7932813167572</v>
+        <v>2.79328155517578</v>
       </c>
       <c r="H1589" t="n">
         <v>299482</v>
@@ -46566,7 +46566,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.00751233100891</v>
+        <v>3.00751209259033</v>
       </c>
       <c r="H1593" t="n">
         <v>386716</v>
@@ -46595,7 +46595,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.01063871383667</v>
+        <v>3.01063847541809</v>
       </c>
       <c r="H1594" t="n">
         <v>176564</v>
@@ -46653,7 +46653,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.0544068813324</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1596" t="n">
         <v>142847</v>
@@ -46682,7 +46682,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.04659080505371</v>
+        <v>3.04659104347229</v>
       </c>
       <c r="H1597" t="n">
         <v>588330</v>
@@ -46769,7 +46769,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.03252291679382</v>
+        <v>3.03252267837524</v>
       </c>
       <c r="H1600" t="n">
         <v>381944</v>
@@ -46827,7 +46827,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.98250150680542</v>
+        <v>2.982501745224</v>
       </c>
       <c r="H1602" t="n">
         <v>358466</v>
@@ -46943,7 +46943,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.14194345474243</v>
+        <v>3.14194321632385</v>
       </c>
       <c r="H1606" t="n">
         <v>1027100</v>
@@ -47088,7 +47088,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.29825878143311</v>
+        <v>3.29825901985168</v>
       </c>
       <c r="H1611" t="n">
         <v>297510</v>
@@ -47117,7 +47117,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.34671711921692</v>
+        <v>3.34671688079834</v>
       </c>
       <c r="H1612" t="n">
         <v>400431</v>
@@ -47146,7 +47146,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.35609579086304</v>
+        <v>3.35609602928162</v>
       </c>
       <c r="H1613" t="n">
         <v>205646</v>
@@ -47320,7 +47320,7 @@
         <v>4.31400012969971</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.37172770500183</v>
+        <v>3.37172722816467</v>
       </c>
       <c r="H1619" t="n">
         <v>421861</v>
@@ -47349,7 +47349,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.35765862464905</v>
+        <v>3.35765886306763</v>
       </c>
       <c r="H1620" t="n">
         <v>255481</v>
@@ -47407,7 +47407,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.28731679916382</v>
+        <v>3.2873170375824</v>
       </c>
       <c r="H1622" t="n">
         <v>185455</v>
@@ -47581,7 +47581,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.17476940155029</v>
+        <v>3.17476963996887</v>
       </c>
       <c r="H1628" t="n">
         <v>336825</v>
@@ -47813,7 +47813,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.0981752872467</v>
+        <v>3.09817504882812</v>
       </c>
       <c r="H1636" t="n">
         <v>122218</v>
@@ -47900,7 +47900,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.11537003517151</v>
+        <v>3.11536979675293</v>
       </c>
       <c r="H1639" t="n">
         <v>100419</v>
@@ -47929,7 +47929,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.16695404052734</v>
+        <v>3.16695427894592</v>
       </c>
       <c r="H1640" t="n">
         <v>251186</v>
@@ -48016,7 +48016,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.19509077072144</v>
+        <v>3.19509053230286</v>
       </c>
       <c r="H1643" t="n">
         <v>90490</v>
@@ -48045,7 +48045,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.26855897903442</v>
+        <v>3.268559217453</v>
       </c>
       <c r="H1644" t="n">
         <v>230657</v>
@@ -48103,7 +48103,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.27481174468994</v>
+        <v>3.27481198310852</v>
       </c>
       <c r="H1646" t="n">
         <v>305247</v>
@@ -48219,7 +48219,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.28731679916382</v>
+        <v>3.2873170375824</v>
       </c>
       <c r="H1650" t="n">
         <v>147979</v>
@@ -48277,7 +48277,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.22635388374329</v>
+        <v>3.22635364532471</v>
       </c>
       <c r="H1652" t="n">
         <v>181208</v>
@@ -48393,7 +48393,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.38423252105713</v>
+        <v>3.38423275947571</v>
       </c>
       <c r="H1656" t="n">
         <v>233036</v>
@@ -48538,7 +48538,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.34359049797058</v>
+        <v>3.34359073638916</v>
       </c>
       <c r="H1661" t="n">
         <v>255129</v>
@@ -48654,7 +48654,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.37485361099243</v>
+        <v>3.37485337257385</v>
       </c>
       <c r="H1665" t="n">
         <v>211448</v>
@@ -48712,7 +48712,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.38423252105713</v>
+        <v>3.38423275947571</v>
       </c>
       <c r="H1667" t="n">
         <v>164728</v>
@@ -48799,7 +48799,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.26855897903442</v>
+        <v>3.268559217453</v>
       </c>
       <c r="H1670" t="n">
         <v>276264</v>
@@ -49060,7 +49060,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.26543259620667</v>
+        <v>3.26543283462524</v>
       </c>
       <c r="H1679" t="n">
         <v>194885</v>
@@ -49089,7 +49089,7 @@
         <v>4.17799997329712</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.26543259620667</v>
+        <v>3.26543283462524</v>
       </c>
       <c r="H1680" t="n">
         <v>378362</v>
@@ -49118,7 +49118,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.23573303222656</v>
+        <v>3.23573279380798</v>
       </c>
       <c r="H1681" t="n">
         <v>155172</v>
@@ -49205,7 +49205,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.27481174468994</v>
+        <v>3.27481198310852</v>
       </c>
       <c r="H1684" t="n">
         <v>150462</v>
@@ -49234,7 +49234,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.27324891090393</v>
+        <v>3.27324867248535</v>
       </c>
       <c r="H1685" t="n">
         <v>185135</v>
@@ -49350,7 +49350,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.15757489204407</v>
+        <v>3.15757513046265</v>
       </c>
       <c r="H1689" t="n">
         <v>357386</v>
@@ -49379,7 +49379,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.22635388374329</v>
+        <v>3.22635364532471</v>
       </c>
       <c r="H1690" t="n">
         <v>173441</v>
@@ -49437,7 +49437,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.0841064453125</v>
+        <v>3.08410668373108</v>
       </c>
       <c r="H1692" t="n">
         <v>697245</v>
@@ -49553,7 +49553,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.0544068813324</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1696" t="n">
         <v>504766</v>
@@ -49930,7 +49930,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.162264585495</v>
+        <v>3.16226434707642</v>
       </c>
       <c r="H1709" t="n">
         <v>648898</v>
@@ -49959,7 +49959,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.21697521209717</v>
+        <v>3.21697497367859</v>
       </c>
       <c r="H1710" t="n">
         <v>573601</v>
@@ -49988,7 +49988,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.20603322982788</v>
+        <v>3.2060329914093</v>
       </c>
       <c r="H1711" t="n">
         <v>242552</v>
@@ -50162,7 +50162,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.26855897903442</v>
+        <v>3.268559217453</v>
       </c>
       <c r="H1717" t="n">
         <v>258927</v>
@@ -50191,7 +50191,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.27950143814087</v>
+        <v>3.27950119972229</v>
       </c>
       <c r="H1718" t="n">
         <v>355421</v>
@@ -50452,7 +50452,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.22166442871094</v>
+        <v>3.22166466712952</v>
       </c>
       <c r="H1727" t="n">
         <v>278266</v>
@@ -50771,7 +50771,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.15288543701172</v>
+        <v>3.15288519859314</v>
       </c>
       <c r="H1738" t="n">
         <v>187427</v>
@@ -50800,7 +50800,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.11849641799927</v>
+        <v>3.11849617958069</v>
       </c>
       <c r="H1739" t="n">
         <v>166094</v>
@@ -51003,7 +51003,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.12787508964539</v>
+        <v>3.12787485122681</v>
       </c>
       <c r="H1746" t="n">
         <v>485176</v>
@@ -51061,7 +51061,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.09661197662354</v>
+        <v>3.09661173820496</v>
       </c>
       <c r="H1748" t="n">
         <v>260833</v>
@@ -51148,7 +51148,7 @@
         <v>3.96399998664856</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.0981752872467</v>
+        <v>3.09817504882812</v>
       </c>
       <c r="H1751" t="n">
         <v>141683</v>
@@ -51583,7 +51583,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.06691193580627</v>
+        <v>3.06691217422485</v>
       </c>
       <c r="H1766" t="n">
         <v>179289</v>
@@ -51612,7 +51612,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.0544068813324</v>
+        <v>3.05440664291382</v>
       </c>
       <c r="H1767" t="n">
         <v>231550</v>
@@ -51670,7 +51670,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.97312235832214</v>
+        <v>2.97312259674072</v>
       </c>
       <c r="H1769" t="n">
         <v>759401</v>
@@ -51960,7 +51960,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.04190158843994</v>
+        <v>3.04190135002136</v>
       </c>
       <c r="H1779" t="n">
         <v>280743</v>
@@ -52018,7 +52018,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.03721165657043</v>
+        <v>3.03721189498901</v>
       </c>
       <c r="H1781" t="n">
         <v>380393</v>
@@ -52163,7 +52163,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.05128073692322</v>
+        <v>3.05128049850464</v>
       </c>
       <c r="H1786" t="n">
         <v>378015</v>
@@ -52308,7 +52308,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.90278053283691</v>
+        <v>2.90278029441833</v>
       </c>
       <c r="H1791" t="n">
         <v>397165</v>
@@ -52453,7 +52453,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.88245940208435</v>
+        <v>2.88245964050293</v>
       </c>
       <c r="H1796" t="n">
         <v>395968</v>
@@ -52482,7 +52482,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.85275959968567</v>
+        <v>2.85275983810425</v>
       </c>
       <c r="H1797" t="n">
         <v>348055</v>
@@ -52598,7 +52598,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.85744905471802</v>
+        <v>2.85744881629944</v>
       </c>
       <c r="H1801" t="n">
         <v>234603</v>
@@ -52627,7 +52627,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.85744905471802</v>
+        <v>2.85744881629944</v>
       </c>
       <c r="H1802" t="n">
         <v>217632</v>
@@ -52714,7 +52714,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.88245940208435</v>
+        <v>2.88245964050293</v>
       </c>
       <c r="H1805" t="n">
         <v>152166</v>
@@ -52743,7 +52743,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.92466497421265</v>
+        <v>2.92466473579407</v>
       </c>
       <c r="H1806" t="n">
         <v>324520</v>
@@ -52772,7 +52772,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.92153859138489</v>
+        <v>2.92153835296631</v>
       </c>
       <c r="H1807" t="n">
         <v>234456</v>
@@ -53149,7 +53149,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.82305979728699</v>
+        <v>2.82305955886841</v>
       </c>
       <c r="H1820" t="n">
         <v>491195</v>
@@ -53265,7 +53265,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.8058648109436</v>
+        <v>2.80586504936218</v>
       </c>
       <c r="H1824" t="n">
         <v>262774</v>
@@ -53294,7 +53294,7 @@
         <v>3.45799994468689</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.70269680023193</v>
+        <v>2.70269656181335</v>
       </c>
       <c r="H1825" t="n">
         <v>939263</v>
@@ -53323,7 +53323,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68393874168396</v>
+        <v>2.68393850326538</v>
       </c>
       <c r="H1826" t="n">
         <v>842330</v>
@@ -53352,7 +53352,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.70894956588745</v>
+        <v>2.70894932746887</v>
       </c>
       <c r="H1827" t="n">
         <v>321163</v>
@@ -53671,7 +53671,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.62453889846802</v>
+        <v>2.6245391368866</v>
       </c>
       <c r="H1838" t="n">
         <v>574992</v>
@@ -53729,7 +53729,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.57764410972595</v>
+        <v>2.57764434814453</v>
       </c>
       <c r="H1840" t="n">
         <v>493431</v>
@@ -53816,7 +53816,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.49792337417603</v>
+        <v>2.49792313575745</v>
       </c>
       <c r="H1843" t="n">
         <v>500311</v>
@@ -76036,6 +76036,35 @@
         <v>350224</v>
       </c>
       <c r="I2609" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2610">
+      <c r="A2610" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2610" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2610" t="n">
+        <v>5.13000011444092</v>
+      </c>
+      <c r="D2610" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="E2610" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F2610" t="n">
+        <v>5.19000005722046</v>
+      </c>
+      <c r="G2610" t="n">
+        <v>5.19000005722046</v>
+      </c>
+      <c r="H2610" t="n">
+        <v>506014</v>
+      </c>
+      <c r="I2610" t="s">
         <v>9</v>
       </c>
     </row>
